--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键功能清单" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源规划" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P1优先启动计划" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$19</definedName>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,6 +96,18 @@
     <font>
       <name val="Arial"/>
       <color rgb="00E53935"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="001B3275"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -215,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -328,6 +341,27 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1315,17 +1349,17 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
-          <t>Brinson归因+固收久期优化</t>
+          <t>17项功能含量化底座集成；Slide44全景展开</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3484,12 +3518,12 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>多维度组合构建</t>
+          <t>债券横截面与时序分析</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>因子约束/跟踪误差/久期目标等多目标组合优化</t>
+          <t>跨品种横截面信号挖掘（利差、久期偏差），历史时序趋势/均值回归分析</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3503,7 +3537,7 @@
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
@@ -3524,12 +3558,12 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>再平衡引擎</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>基于信号/规则自动生成调仓指令，考虑交易成本与冲击</t>
+          <t>利差/Z-spread/OAS相对价值，历史分位数定位，套利信号识别</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3564,26 +3598,26 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Brinson绩效归因</t>
+          <t>组合相关度分析</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Brinson-Hood-Beebower模型，资产配置/个券选择/交互效应</t>
+          <t>资产间收益相关矩阵计算，组合集中度风险识别，分散化系数监控</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G45" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G45" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
@@ -3604,26 +3638,26 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>固收久期/凸度管理</t>
+          <t>情景分析</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>组合DV01/凸度实时监控，与风险计量平台对接</t>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G46" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
@@ -3644,26 +3678,26 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>基准指数对比</t>
+          <t>敏感度分析</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>跟踪误差计算，超额收益（Alpha）归因，信息比率监控</t>
+          <t>久期/DV01/凸度/利差敏感度多因子并行计算，组合对冲比率建议</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G47" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
@@ -3684,12 +3718,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>实时PnL归因</t>
+          <t>极端事件分析</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>已实现/未实现PnL按因子/资产/策略三维归因</t>
+          <t>历史极端情景（924行情/2015股灾/2020疫情）组合压测，尾部损失分布</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -3706,17 +3740,50 @@
         <v>30</v>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
-        </is>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>F07-07</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>指数比较分析</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）实时监控，超额Alpha分解</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G49" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3726,17 +3793,17 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>F08-01</t>
+          <t>F07-08</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>因子模型框架</t>
+          <t>绩效归因（Brinson）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+          <t>BHB模型三效应：资产配置/个券选择/交互效应，日频计算，周/月/季报自动生成</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
@@ -3756,7 +3823,7 @@
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3766,37 +3833,37 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F07-09</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>虚拟组合分析</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+          <t>组合调整前后效果模拟（净值/风险/收益），交易冲击成本预估，方案比较</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G51" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H51" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3806,17 +3873,17 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F07-10</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>信号生成与调度</t>
+          <t>再平衡方案试算与比较</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+          <t>久期/集中度/流动性约束联合优化，多方案并行试算，最优路径推荐</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -3830,13 +3897,13 @@
         </is>
       </c>
       <c r="H52" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3846,491 +3913,491 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>F08-04</t>
+          <t>F07-11</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>低延迟执行接口</t>
+          <t>资产配置策略分析</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+          <t>宏观因子驱动大类资产配置模型（利率/信用/权益），动态权重优化建议</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G53" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>F07-12</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>固收+策略分析</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解，固收+产品净值模拟</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>F07-13</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>量化策略组合分析</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤监控</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>F07-14</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>流动性分析</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失估算</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G56" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>F07-15</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>定价计算集成</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>调用量化定价引擎实时估值与Greeks，支持含权债/可转债，结果缓存与推送</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/信用），曲线因子提取（水平/斜率/曲率），敏感度映射</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G58" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>F07-17</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>因子模型</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库，因子暴露实时计算</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
           <t>策略投资/量化</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>因子模型框架</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G61" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Tick级回测引擎</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G62" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>信号生成与调度</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G63" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>低延迟执行接口</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G64" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>F08-05</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>实时策略监控</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>持仓/PnL/回撤/Sharpe实时看板，风险触发自动平仓</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G54" s="25" t="inlineStr">
+      <c r="G65" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H54" s="8" t="n">
+      <c r="H65" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="28" t="inlineStr">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t>【P2】 量化定价引擎  (Quant Pricing Engine)</t>
         </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D56" s="29" t="inlineStr">
-        <is>
-          <t>期限结构模型</t>
-        </is>
-      </c>
-      <c r="E56" s="11" t="inlineStr">
-        <is>
-          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G56" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>F09-02</t>
-        </is>
-      </c>
-      <c r="D57" s="29" t="inlineStr">
-        <is>
-          <t>蒙特卡洛求解器</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="inlineStr">
-        <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
-        </is>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G57" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H57" s="14" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>F09-03</t>
-        </is>
-      </c>
-      <c r="D58" s="29" t="inlineStr">
-        <is>
-          <t>有限差分（PDE）</t>
-        </is>
-      </c>
-      <c r="E58" s="11" t="inlineStr">
-        <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G58" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H58" s="14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t>F09-04</t>
-        </is>
-      </c>
-      <c r="D59" s="29" t="inlineStr">
-        <is>
-          <t>实时Greeks</t>
-        </is>
-      </c>
-      <c r="E59" s="11" t="inlineStr">
-        <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
-        </is>
-      </c>
-      <c r="F59" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G59" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H59" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>F09-05</t>
-        </is>
-      </c>
-      <c r="D60" s="29" t="inlineStr">
-        <is>
-          <t>定价服务微服务架构</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G60" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H60" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>F09-06</t>
-        </is>
-      </c>
-      <c r="D61" s="29" t="inlineStr">
-        <is>
-          <t>历史估值回测</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="inlineStr">
-        <is>
-          <t>基于历史行情重放定价误差分析，模型验证框架</t>
-        </is>
-      </c>
-      <c r="F61" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G61" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H61" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 利率衍生品  (Interest Rate Derivatives)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>F10-01</t>
-        </is>
-      </c>
-      <c r="D63" s="29" t="inlineStr">
-        <is>
-          <t>IRS/OIS/CCS定价</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>利率互换标准与非标结构定价，折现曲线OIS</t>
-        </is>
-      </c>
-      <c r="F63" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G63" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H63" s="14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>F10-02</t>
-        </is>
-      </c>
-      <c r="D64" s="29" t="inlineStr">
-        <is>
-          <t>久期/DV01/凸度</t>
-        </is>
-      </c>
-      <c r="E64" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品Greeks实时计算，组合对冲比率</t>
-        </is>
-      </c>
-      <c r="F64" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G64" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H64" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>F10-03</t>
-        </is>
-      </c>
-      <c r="D65" s="29" t="inlineStr">
-        <is>
-          <t>LCH/上清所CCP接口</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>标准化IRS中央清算，保证金（IM/VM）计算</t>
-        </is>
-      </c>
-      <c r="F65" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G65" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H65" s="14" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>F10-04</t>
-        </is>
-      </c>
-      <c r="D66" s="29" t="inlineStr">
-        <is>
-          <t>压力测试/情景分析</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>利率曲线平移/扭转/蝶式情景，组合P&amp;L影响</t>
-        </is>
-      </c>
-      <c r="F66" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G66" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H66" s="14" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>利率衍生品</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B67" s="10" t="inlineStr">
@@ -4340,44 +4407,77 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>F10-05</t>
+          <t>F09-01</t>
         </is>
       </c>
       <c r="D67" s="29" t="inlineStr">
         <is>
-          <t>利率曲线发布</t>
+          <t>期限结构模型</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>多曲线框架（OIS/Libor过渡/中债曲线）实时发布</t>
+          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G67" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G67" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H67" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
-        </is>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>量化定价引擎</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>F09-02</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>蒙特卡洛求解器</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G68" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B69" s="10" t="inlineStr">
@@ -4387,37 +4487,37 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>F11-01</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G69" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G69" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H69" s="14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -4427,37 +4527,37 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>CDS/CLN定价</t>
+          <t>实时Greeks</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G70" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H70" s="14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B71" s="10" t="inlineStr">
@@ -4467,37 +4567,37 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D71" s="29" t="inlineStr">
         <is>
-          <t>信用评级动态监控</t>
+          <t>定价服务微服务架构</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G71" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H71" s="14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -4507,17 +4607,17 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D72" s="29" t="inlineStr">
         <is>
-          <t>违约概率（PD）建模</t>
+          <t>历史估值回测</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>基于历史行情重放定价误差分析，模型验证框架</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr">
@@ -4531,60 +4631,60 @@
         </is>
       </c>
       <c r="H72" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 利率衍生品  (Interest Rate Derivatives)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>利率衍生品</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>F11-05</t>
-        </is>
-      </c>
-      <c r="D73" s="29" t="inlineStr">
-        <is>
-          <t>集中度限额管理</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>行业/发行人/评级集中度多维限额，超限预警</t>
-        </is>
-      </c>
-      <c r="F73" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G73" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H73" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 数据管理/行情平台  (Market Data Platform)</t>
-        </is>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>F10-01</t>
+        </is>
+      </c>
+      <c r="D74" s="29" t="inlineStr">
+        <is>
+          <t>IRS/OIS/CCS定价</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>利率互换标准与非标结构定价，折现曲线OIS</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G74" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B75" s="10" t="inlineStr">
@@ -4594,17 +4694,17 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>F12-01</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
         <is>
-          <t>多源行情聚合</t>
+          <t>久期/DV01/凸度</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Bloomberg/Wind/中汇信/Refinitiv多源融合，冲突解析</t>
+          <t>利率衍生品Greeks实时计算，组合对冲比率</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
@@ -4618,13 +4718,13 @@
         </is>
       </c>
       <c r="H75" s="14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -4634,37 +4734,37 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D76" s="29" t="inlineStr">
         <is>
-          <t>数据质量校验</t>
+          <t>LCH/上清所CCP接口</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>异常值/缺失值/跳价自动检测，修复建议与人工审核</t>
+          <t>标准化IRS中央清算，保证金（IM/VM）计算</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G76" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H76" s="14" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B77" s="10" t="inlineStr">
@@ -4674,17 +4774,17 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D77" s="29" t="inlineStr">
         <is>
-          <t>历史数据仓库</t>
+          <t>压力测试/情景分析</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Tick/日频历史行情存储，高效查询（ClickHouse/TimescaleDB）</t>
+          <t>利率曲线平移/扭转/蝶式情景，组合P&amp;L影响</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -4698,13 +4798,13 @@
         </is>
       </c>
       <c r="H77" s="14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -4714,17 +4814,17 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D78" s="29" t="inlineStr">
         <is>
-          <t>收益率曲线发布</t>
+          <t>利率曲线发布</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>国债/政策行/高等级信用曲线实时发布，Kafka广播</t>
+          <t>多曲线框架（OIS/Libor过渡/中债曲线）实时发布</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr">
@@ -4738,60 +4838,60 @@
         </is>
       </c>
       <c r="H78" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>数据管理/行情平台</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>F12-05</t>
-        </is>
-      </c>
-      <c r="D79" s="29" t="inlineStr">
-        <is>
-          <t>估值价格服务</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>非活跃债券估值价格（中债估值基准），API接口提供</t>
-        </is>
-      </c>
-      <c r="F79" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G79" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H79" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 交易对手管理  (Counterparty Management)</t>
-        </is>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>F11-01</t>
+        </is>
+      </c>
+      <c r="D80" s="29" t="inlineStr">
+        <is>
+          <t>信用利差分析</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G80" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B81" s="10" t="inlineStr">
@@ -4801,37 +4901,37 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D81" s="29" t="inlineStr">
         <is>
-          <t>对手方评级与审批</t>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>内部信用评级模型，新增/变更交易对手审批流</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G81" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G81" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H81" s="14" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -4841,37 +4941,37 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>实时敞口聚合</t>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>跨产品交易对手名义/MtM敞口实时聚合，压力敞口（EPE）</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G82" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G82" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H82" s="14" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B83" s="10" t="inlineStr">
@@ -4881,17 +4981,17 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F11-04</t>
         </is>
       </c>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>ISDA/CSA协议管理</t>
+          <t>违约概率（PD）建模</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>主协议文档管理，净额结算协议（Netting Set）配置</t>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -4905,13 +5005,13 @@
         </is>
       </c>
       <c r="H83" s="14" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -4921,84 +5021,84 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F11-05</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>CVA/DVA/FVA计算</t>
+          <t>集中度限额管理</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>信用/债务/资金估值调整实时估算，敞口报告</t>
+          <t>行业/发行人/评级集中度多维限额，超限预警</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G84" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G84" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H84" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="A85" s="11" t="inlineStr">
-        <is>
-          <t>交易对手管理</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 数据管理/行情平台  (Market Data Platform)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>F13-05</t>
-        </is>
-      </c>
-      <c r="D85" s="29" t="inlineStr">
-        <is>
-          <t>集中度与限额</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="inlineStr">
-        <is>
-          <t>对手方/集团合并敞口限额，超限审批与记录</t>
-        </is>
-      </c>
-      <c r="F85" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G85" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H85" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 清算结算后台  (Clearing &amp; Settlement)</t>
-        </is>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>F12-01</t>
+        </is>
+      </c>
+      <c r="D86" s="29" t="inlineStr">
+        <is>
+          <t>多源行情聚合</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>Bloomberg/Wind/中汇信/Refinitiv多源融合，冲突解析</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H86" s="14" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="87" ht="28" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>数据管理/行情平台</t>
         </is>
       </c>
       <c r="B87" s="10" t="inlineStr">
@@ -5008,37 +5108,37 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>F14-01</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>DVP/FOP指令生成</t>
+          <t>数据质量校验</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>成交后自动生成交割指令，批量/单笔支持</t>
+          <t>异常值/缺失值/跳价自动检测，修复建议与人工审核</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G87" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G87" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>数据管理/行情平台</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -5048,37 +5148,37 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>F14-02</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D88" s="29" t="inlineStr">
         <is>
-          <t>中登/中债登接口</t>
+          <t>历史数据仓库</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>银行间债券（中债登）和交易所债券（中登）接口对接</t>
+          <t>Tick/日频历史行情存储，高效查询（ClickHouse/TimescaleDB）</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G88" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H88" s="14" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>数据管理/行情平台</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -5088,17 +5188,17 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>F14-03</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>待交割明细管理</t>
+          <t>收益率曲线发布</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>T+0/T+1待交割跟踪，提前预警可能失败交割</t>
+          <t>国债/政策行/高等级信用曲线实时发布，Kafka广播</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -5112,533 +5212,907 @@
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>F12-05</t>
+        </is>
+      </c>
+      <c r="D90" s="29" t="inlineStr">
+        <is>
+          <t>估值价格服务</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>非活跃债券估值价格（中债估值基准），API接口提供</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G90" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H90" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 交易对手管理  (Counterparty Management)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D92" s="29" t="inlineStr">
+        <is>
+          <t>对手方评级与审批</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>内部信用评级模型，新增/变更交易对手审批流</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G92" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H92" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D93" s="29" t="inlineStr">
+        <is>
+          <t>实时敞口聚合</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>跨产品交易对手名义/MtM敞口实时聚合，压力敞口（EPE）</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H93" s="14" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="94" ht="28" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D94" s="29" t="inlineStr">
+        <is>
+          <t>ISDA/CSA协议管理</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>主协议文档管理，净额结算协议（Netting Set）配置</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G94" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H94" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D95" s="29" t="inlineStr">
+        <is>
+          <t>CVA/DVA/FVA计算</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>信用/债务/资金估值调整实时估算，敞口报告</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G95" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H95" s="14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D96" s="29" t="inlineStr">
+        <is>
+          <t>集中度与限额</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>对手方/集团合并敞口限额，超限审批与记录</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G96" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H96" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 清算结算后台  (Clearing &amp; Settlement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
           <t>清算结算后台</t>
         </is>
       </c>
-      <c r="B90" s="10" t="inlineStr">
+      <c r="B98" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>F14-01</t>
+        </is>
+      </c>
+      <c r="D98" s="29" t="inlineStr">
+        <is>
+          <t>DVP/FOP指令生成</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>成交后自动生成交割指令，批量/单笔支持</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G98" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>F14-02</t>
+        </is>
+      </c>
+      <c r="D99" s="29" t="inlineStr">
+        <is>
+          <t>中登/中债登接口</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>银行间债券（中债登）和交易所债券（中登）接口对接</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G99" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>F14-03</t>
+        </is>
+      </c>
+      <c r="D100" s="29" t="inlineStr">
+        <is>
+          <t>待交割明细管理</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>T+0/T+1待交割跟踪，提前预警可能失败交割</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G100" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>F14-04</t>
         </is>
       </c>
-      <c r="D90" s="29" t="inlineStr">
+      <c r="D101" s="29" t="inlineStr">
         <is>
           <t>资金调拨确认</t>
         </is>
       </c>
-      <c r="E90" s="11" t="inlineStr">
+      <c r="E101" s="11" t="inlineStr">
         <is>
           <t>资金划拨指令生成，银行资金头寸确认，轧差净额</t>
         </is>
       </c>
-      <c r="F90" s="11" t="inlineStr">
+      <c r="F101" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G90" s="24" t="inlineStr">
+      <c r="G101" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H90" s="14" t="n">
+      <c r="H101" s="14" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="91" ht="28" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>清算结算后台</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C91" s="10" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>F14-05</t>
         </is>
       </c>
-      <c r="D91" s="29" t="inlineStr">
+      <c r="D102" s="29" t="inlineStr">
         <is>
           <t>交割失败处理</t>
         </is>
       </c>
-      <c r="E91" s="11" t="inlineStr">
+      <c r="E102" s="11" t="inlineStr">
         <is>
           <t>失败交割自动识别，补交割流程，罚息计算</t>
         </is>
       </c>
-      <c r="F91" s="11" t="inlineStr">
+      <c r="F102" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G91" s="25" t="inlineStr">
+      <c r="G102" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H91" s="14" t="n">
+      <c r="H102" s="14" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="30" t="inlineStr">
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="30" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="A93" s="17" t="inlineStr">
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B93" s="16" t="inlineStr">
+      <c r="B104" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C93" s="16" t="inlineStr">
+      <c r="C104" s="16" t="inlineStr">
         <is>
           <t>F15-01</t>
         </is>
       </c>
-      <c r="D93" s="31" t="inlineStr">
+      <c r="D104" s="31" t="inlineStr">
         <is>
           <t>双边报价引擎</t>
         </is>
       </c>
-      <c r="E93" s="17" t="inlineStr">
+      <c r="E104" s="17" t="inlineStr">
         <is>
           <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
-      <c r="F93" s="17" t="inlineStr">
+      <c r="F104" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G93" s="27" t="inlineStr">
+      <c r="G104" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H93" s="19" t="n">
+      <c r="H104" s="19" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="94" ht="28" customHeight="1">
-      <c r="A94" s="17" t="inlineStr">
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B94" s="16" t="inlineStr">
+      <c r="B105" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C94" s="16" t="inlineStr">
+      <c r="C105" s="16" t="inlineStr">
         <is>
           <t>F15-02</t>
         </is>
       </c>
-      <c r="D94" s="31" t="inlineStr">
+      <c r="D105" s="31" t="inlineStr">
         <is>
           <t>库存风险实时管理</t>
         </is>
       </c>
-      <c r="E94" s="17" t="inlineStr">
+      <c r="E105" s="17" t="inlineStr">
         <is>
           <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
-      <c r="F94" s="17" t="inlineStr">
+      <c r="F105" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G94" s="27" t="inlineStr">
+      <c r="G105" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H94" s="19" t="n">
+      <c r="H105" s="19" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="95" ht="28" customHeight="1">
-      <c r="A95" s="17" t="inlineStr">
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B95" s="16" t="inlineStr">
+      <c r="B106" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C95" s="16" t="inlineStr">
+      <c r="C106" s="16" t="inlineStr">
         <is>
           <t>F15-03</t>
         </is>
       </c>
-      <c r="D95" s="31" t="inlineStr">
+      <c r="D106" s="31" t="inlineStr">
         <is>
           <t>报价优化算法</t>
         </is>
       </c>
-      <c r="E95" s="17" t="inlineStr">
+      <c r="E106" s="17" t="inlineStr">
         <is>
           <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
-      <c r="F95" s="17" t="inlineStr">
+      <c r="F106" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G95" s="27" t="inlineStr">
+      <c r="G106" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H95" s="19" t="n">
+      <c r="H106" s="19" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="A96" s="17" t="inlineStr">
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B96" s="16" t="inlineStr">
+      <c r="B107" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C96" s="16" t="inlineStr">
+      <c r="C107" s="16" t="inlineStr">
         <is>
           <t>F15-04</t>
         </is>
       </c>
-      <c r="D96" s="31" t="inlineStr">
+      <c r="D107" s="31" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E96" s="17" t="inlineStr">
+      <c r="E107" s="17" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，策略调优</t>
         </is>
       </c>
-      <c r="F96" s="17" t="inlineStr">
+      <c r="F107" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G96" s="24" t="inlineStr">
+      <c r="G107" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H96" s="19" t="n">
+      <c r="H107" s="19" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="97" ht="28" customHeight="1">
-      <c r="A97" s="17" t="inlineStr">
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B97" s="16" t="inlineStr">
+      <c r="B108" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C97" s="16" t="inlineStr">
+      <c r="C108" s="16" t="inlineStr">
         <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D97" s="31" t="inlineStr">
+      <c r="D108" s="31" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E97" s="17" t="inlineStr">
+      <c r="E108" s="17" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F97" s="17" t="inlineStr">
+      <c r="F108" s="17" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G97" s="25" t="inlineStr">
+      <c r="G108" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H97" s="19" t="n">
+      <c r="H108" s="19" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="30" t="inlineStr">
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="30" t="inlineStr">
         <is>
           <t>【P3】 外汇/外汇衍生品  (FX &amp; FX Derivatives)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="28" customHeight="1">
-      <c r="A99" s="17" t="inlineStr">
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B99" s="16" t="inlineStr">
+      <c r="B110" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C99" s="16" t="inlineStr">
+      <c r="C110" s="16" t="inlineStr">
         <is>
           <t>F16-01</t>
         </is>
       </c>
-      <c r="D99" s="31" t="inlineStr">
+      <c r="D110" s="31" t="inlineStr">
         <is>
           <t>即期/远期报价</t>
         </is>
       </c>
-      <c r="E99" s="17" t="inlineStr">
+      <c r="E110" s="17" t="inlineStr">
         <is>
           <t>USD/CNY等主要货币对即期汇率+远期点数报价</t>
         </is>
       </c>
-      <c r="F99" s="17" t="inlineStr">
+      <c r="F110" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G99" s="24" t="inlineStr">
+      <c r="G110" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H99" s="19" t="n">
+      <c r="H110" s="19" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="100" ht="28" customHeight="1">
-      <c r="A100" s="17" t="inlineStr">
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B100" s="16" t="inlineStr">
+      <c r="B111" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C100" s="16" t="inlineStr">
+      <c r="C111" s="16" t="inlineStr">
         <is>
           <t>F16-02</t>
         </is>
       </c>
-      <c r="D100" s="31" t="inlineStr">
+      <c r="D111" s="31" t="inlineStr">
         <is>
           <t>外汇期权（FXO）</t>
         </is>
       </c>
-      <c r="E100" s="17" t="inlineStr">
+      <c r="E111" s="17" t="inlineStr">
         <is>
           <t>欧式/美式FXO定价（Garman-Kohlhagen），Greeks</t>
         </is>
       </c>
-      <c r="F100" s="17" t="inlineStr">
+      <c r="F111" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G100" s="27" t="inlineStr">
+      <c r="G111" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H100" s="19" t="n">
+      <c r="H111" s="19" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="A101" s="17" t="inlineStr">
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B101" s="16" t="inlineStr">
+      <c r="B112" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C101" s="16" t="inlineStr">
+      <c r="C112" s="16" t="inlineStr">
         <is>
           <t>F16-03</t>
         </is>
       </c>
-      <c r="D101" s="31" t="inlineStr">
+      <c r="D112" s="31" t="inlineStr">
         <is>
           <t>NDF/NDO定价</t>
         </is>
       </c>
-      <c r="E101" s="17" t="inlineStr">
+      <c r="E112" s="17" t="inlineStr">
         <is>
           <t>不可交割远期/期权定价，境外对手对接</t>
         </is>
       </c>
-      <c r="F101" s="17" t="inlineStr">
+      <c r="F112" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G101" s="27" t="inlineStr">
+      <c r="G112" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H101" s="19" t="n">
+      <c r="H112" s="19" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="102" ht="28" customHeight="1">
-      <c r="A102" s="17" t="inlineStr">
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B102" s="16" t="inlineStr">
+      <c r="B113" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C102" s="16" t="inlineStr">
+      <c r="C113" s="16" t="inlineStr">
         <is>
           <t>F16-04</t>
         </is>
       </c>
-      <c r="D102" s="31" t="inlineStr">
+      <c r="D113" s="31" t="inlineStr">
         <is>
           <t>跨货币敞口汇总</t>
         </is>
       </c>
-      <c r="E102" s="17" t="inlineStr">
+      <c r="E113" s="17" t="inlineStr">
         <is>
           <t>多币种资产折算人民币敞口，汇率风险VaR</t>
         </is>
       </c>
-      <c r="F102" s="17" t="inlineStr">
+      <c r="F113" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G102" s="24" t="inlineStr">
+      <c r="G113" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H102" s="19" t="n">
+      <c r="H113" s="19" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="A103" s="17" t="inlineStr">
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B103" s="16" t="inlineStr">
+      <c r="B114" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C103" s="16" t="inlineStr">
+      <c r="C114" s="16" t="inlineStr">
         <is>
           <t>F16-05</t>
         </is>
       </c>
-      <c r="D103" s="31" t="inlineStr">
+      <c r="D114" s="31" t="inlineStr">
         <is>
           <t>CFETS/外汇局接口</t>
         </is>
       </c>
-      <c r="E103" s="17" t="inlineStr">
+      <c r="E114" s="17" t="inlineStr">
         <is>
           <t>银行间外汇市场CFETS接口，外汇局合规报送</t>
         </is>
       </c>
-      <c r="F103" s="17" t="inlineStr">
+      <c r="F114" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G103" s="24" t="inlineStr">
+      <c r="G114" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H103" s="19" t="n">
+      <c r="H114" s="19" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="20" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="20" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H104" s="21">
-        <f>SUM(H3:H103)</f>
+      <c r="H115" s="21">
+        <f>SUM(H3:H114)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A62:H62"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A109:H109"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A115:G115"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A98:H98"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A85:H85"/>
     <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A104:G104"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A103:H103"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A74:H74"/>
+    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A97:H97"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6711,4 +7185,1005 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>系统详情：组合管理+绩效归因  |  Portfolio Management &amp; Performance Attribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>核心目标（Slide 44）：为FICC投资组合管理提供全面解决方案，通过分析投资组合头寸、风险计量、绩效归因，为投资经理在资产管理、组合构建、组合再平衡、指数投资等方面赋能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>架构层次：  【数据层】交易数据 / 头寸数据 / 行情数据 / 估值数据  →  【量化底座】定价计算 · 利率曲线 · 因子模型  →  【组合分析平台】6大功能域（见下表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述（来源Slide44）</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>A. 组合分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A. 组合分析</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>F07-01</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>债券横截面与时序分析</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析，支持日/周/月时间窗口</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>横截面信号与实际收益相关性&gt;0.3；时序模型回测夏普&gt;0.5</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情平台 / 估值数据</t>
+        </is>
+      </c>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Slide44首项分析能力</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A. 组合分析</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>F07-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>相对价值分析</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别，个券评分</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>OAS计算误差&lt;1bps；分位数计算覆盖5年历史</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>量化定价引擎 / AMD行情</t>
+        </is>
+      </c>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>投资经理最常用分析工具</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A. 组合分析</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F07-03</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>组合相关度分析</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>资产间收益相关矩阵计算（滚动窗口60/120/250日），组合集中度风险识别，分散化系数监控</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>相关矩阵计算耗时&lt;30s（500券组合）</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>IBOR头寸 / AMD历史行情</t>
+        </is>
+      </c>
+      <c r="G8" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>B. 风险计量</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>B. 风险计量</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>F07-04</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>情景分析</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>利率平移/扭转/蝶式、信用利差扩大、流动性冲击三类情景；自定义情景编辑器；多情景P&amp;L并行对比</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>情景P&amp;L计算与手工核算误差&lt;0.5%；支持≥20个情景并行</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台 / 量化定价引擎</t>
+        </is>
+      </c>
+      <c r="G10" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>复用风险计量模块情景库</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>B. 风险计量</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>F07-05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>敏感度分析</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合层面聚合，对冲比率建议输出</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>量化定价引擎Greeks接口</t>
+        </is>
+      </c>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>B. 风险计量</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>F07-06</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>极端事件分析</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>内置924行情/2015股灾/2020疫情等8+极端情景，组合尾部损失分布，ES(99%)计算</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>历史情景复现误差&lt;1%；与风险计量平台情景库共享</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台</t>
+        </is>
+      </c>
+      <c r="G12" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>与风险计量平台共享情景库</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="44" t="inlineStr">
+        <is>
+          <t>C. 绩效归因</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>C. 绩效归因</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>F07-07</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>指数比较分析</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>对标中债综合/信用/政策行/定制基准指数；跟踪误差（TE）日频实时监控；超额Alpha三因子分解</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>TE计算误差&lt;1bps；支持≥10个基准指数同时跟踪</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>AMD中债估值 / IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G14" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>中债指数数据接入为前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>C. 绩效归因</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>F07-08</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>绩效归因（Brinson模型）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>BHB三效应：资产配置/个券选择/交互效应；日/周/月/季多时间维度；报告PDF自动生成</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Brinson归因结果与Bloomberg AIM误差&lt;0.1%；报告T+1 9:00前自动生成</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>IBOR持仓 / AMD行情 / 指数数据</t>
+        </is>
+      </c>
+      <c r="G15" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>核心差异化功能，对标SimCorp/Aladdin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>F07-09</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>虚拟组合分析</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易）；市场冲击成本预估；多方案结果对比展示</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>虚拟组合模拟结果与真实执行偏差&lt;0.3%</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>IBOR / 现券交易系统（冲击模型）</t>
+        </is>
+      </c>
+      <c r="G17" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>F07-10</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>再平衡方案试算与比较</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>QP求解100券组合&lt;5s；约束满足率100%</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规 / IBOR / 现券系统</t>
+        </is>
+      </c>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>QP求解器选型：CVXPY/Gurobi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>F07-11</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>资产配置策略分析</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>宏观因子（利率周期/信用周期/流动性）驱动大类资产配置模型；动态权重优化建议；历史回测验证</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>回测期≥5年；模型收益预测方向胜率&gt;55%</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>AMD宏观数据 / 因子模型</t>
+        </is>
+      </c>
+      <c r="G19" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1后期或Phase 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>F07-12</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>固收+策略分析</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+产品净值模拟</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>IBOR / 利率衍生品系统（Phase 2）</t>
+        </is>
+      </c>
+      <c r="G20" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>依赖利率衍生品模块</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>F07-13</t>
+        </is>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>量化策略组合分析</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控，策略权重优化</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>策略容量计算误差&lt;5%；组合Sharpe≥1.2（回测）</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>策略投资/量化系统</t>
+        </is>
+      </c>
+      <c r="G21" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>与策略投资模块深度整合</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>E. 流动性管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>E. 流动性管理</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>F07-14</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>流动性分析</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>逐券换手率/市场深度评估（日均成交量法），组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>LVaR计算与市场基准误差&lt;5%；日均成交量数据覆盖≥95%持仓</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情（成交量） / IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G23" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>监管流动性要求驱动</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="45" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>F07-15</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="inlineStr">
+        <is>
+          <t>定价计算集成</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>调用量化定价引擎实时估值与Greeks；支持含权债/可转债/IRS；结果缓存（Redis）与Kafka推送</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>定价API p99&lt;200ms；日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>量化定价引擎（P2模块）</t>
+        </is>
+      </c>
+      <c r="G25" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1用AMD估值代替，Phase 2升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS）；Nelson-Siegel参数提取（水平/斜率/曲率）；敏感度映射</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s；NS参数拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情平台 / 量化定价引擎</t>
+        </is>
+      </c>
+      <c r="G26" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>F07-17</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>因子模型</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（利率/信用/流动性/行业因子）；Alpha因子库（≥20个因子）；因子暴露实时计算与归因</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>因子模型解释方差&gt;80%；Alpha IC均值&gt;0.05</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>AMD历史行情 / IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G27" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>复用策略投资模块因子库</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>合计 17项功能  |  P1: 12项  |  P2: 5项  |  来源：Slide 44 + 扩展</t>
+        </is>
+      </c>
+      <c r="H28" s="21">
+        <f>SUM(H5:H27)</f>
+        <v/>
+      </c>
+      <c r="I28" s="35" t="inlineStr"/>
+      <c r="J28" s="35" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A13:J13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="关键功能清单" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源规划" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P1优先启动计划" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_IBOR投资账薄管理" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$19</definedName>
@@ -905,17 +906,17 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O3" s="8" t="n">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>整个FICC平台的账薄主干，先建先通</t>
+          <t>整个FICC平台的账薄主干，27项功能覆盖持仓/现金/估值/事件/对账/合规/试算全链路</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2156,17 +2157,17 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>跨资产持仓实时净值</t>
+          <t>跨资产实时头寸</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>支持债券/利率衍生品/回购全品种实时估值，T+0净值计算</t>
+          <t>债券/回购/利率衍生品全品种T0实时持仓，含未交割与待交割敞口分层展示</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>持仓更新延迟&lt;500ms，全品种覆盖率100%</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
@@ -2175,7 +2176,7 @@
         </is>
       </c>
       <c r="H4" s="8" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
@@ -2196,17 +2197,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>多账户层级管理</t>
+          <t>多账户层级汇总</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>账户/策略/产品/公司层级合并与分拆，含多级组合结构</t>
+          <t>基金/策略/组合/公司四级持仓合并与分拆，支持跨基金同标的穿透聚合</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>层级汇总数据与单账户加总误差为零</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
@@ -2215,7 +2216,7 @@
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
@@ -2236,26 +2237,26 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>现金流预测</t>
+          <t>账薄T0/T1切换</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>回购到期/票息支付/衍生品结算现金流7天预测，流动性缓冲预警</t>
+          <t>交易日账薄（含未交割）与结算账薄（T+1已交割）自动切换，切换耗时&lt;1min</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G6" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>T0/T1持仓差=未交割敞口，自动核验通过率&gt;99%</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
@@ -2276,17 +2277,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>账薄T0/T1切换</t>
+          <t>可用券与冻结管理</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>日内账薄（含未交割）与结算账薄自动切换，支持对账差异分析</t>
+          <t>质押券/司法冻结券/回购占用券从可用头寸自动剔除，前台实时可用量查询</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>可用量计算误差为零，冻结事件&lt;30s生效</t>
         </is>
       </c>
       <c r="G7" s="25" t="inlineStr">
@@ -2295,7 +2296,7 @@
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -2311,31 +2312,31 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>F01-05</t>
+          <t>F01-27</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>托管行对账接口</t>
+          <t>资产打标与组合树管理</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>与中登、中债登、托管银行日终对账，差异自动推送告警</t>
+          <t>多维度资产标签体系（评级/行业/策略/流动性层级/会计分类）灵活配置，支持自定义组合树构建多分析视角；标签驱动持仓穿透聚合和报表分组</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>标签体系支持≥10维度，组合树层级≥4级，标签变更&lt;1min生效影响所有聚合视图</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -2351,44 +2352,77 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>F01-05</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>实时现金余额</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>多账户已结算/未结算现金实时汇总，T0资金头寸含日间资金划拨记录</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>现金余额与银行回单误差为零，日中更新频率≥每分钟</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>IBOR投资账薄管理</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
           <t>F01-06</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>估值价格接入</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>接入AMD/Bloomberg/Wind估值价格服务，支持估值覆盖</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G9" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 现券交易系统  (Bond Trading)</t>
-        </is>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>现金流预测</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>回购到期/票息支付/衍生品结算现金流7-30日滚动预测，流动性缺口预警</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>7日现金流预测准确率&gt;95%，流动性预警提前24h触发</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>现券交易系统</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2398,37 +2432,37 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>F02-01</t>
+          <t>F01-07</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>银行间双边报价</t>
+          <t>多币种资金管理</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>CFETS/X-Bond两板块报价，支持询价（RFQ）和竞价</t>
+          <t>CNY/USD/HKD等多币种现金分账户轧差，FX即期换算折算人民币净敞口</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G11" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>多币种折算汇率误差&lt;0.01%，轧差结果实时刷新</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>现券交易系统</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2438,37 +2472,37 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>F02-02</t>
+          <t>F01-08</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>交易所债券委托</t>
+          <t>实时市值计算</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>上交所/深交所债券买卖下单，支持限价/市价/条件单</t>
+          <t>接入AMD/Bloomberg/Wind估值价格，全持仓实时MtM与日内PnL计算，支持估值价格覆盖</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G12" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>MtM更新延迟&lt;1s，估值覆盖审批留痕100%</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H12" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>现券交易系统</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2478,22 +2512,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>F02-03</t>
+          <t>F01-09</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>收益率/价格计算</t>
+          <t>应计利息计算</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>全品种YTM/价格双向转换，含含权债修正久期计算</t>
+          <t>债券应计利息按实际/365、实际/360、30/360多计息基准精确计算，日终净值自动生成</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>应计利息与Bloomberg基准误差&lt;0.01元/百元面值</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
@@ -2502,13 +2536,13 @@
         </is>
       </c>
       <c r="H13" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>现券交易系统</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2518,37 +2552,37 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>F02-04</t>
+          <t>F01-10</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>交易前风险校验</t>
+          <t>衍生品逐日盯市</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>调用事前风控接口，单笔限额/集中度/利率风险实时拦截</t>
+          <t>IRS/CDS/国债期货逐日MtM计算，保证金余额实时更新，追加保证金（Margin Call）自动触发</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G14" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>衍生品MtM与对手方差异&lt;0.5bps，Margin Call触发延迟&lt;5min</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>现券交易系统</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2558,22 +2592,22 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>F02-05</t>
+          <t>F01-11</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>交易确认与指令生成</t>
+          <t>付息与到期处理</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>成交确认后自动生成DVP/FOP清算指令，推送清算结算模块</t>
+          <t>债券票息自动计算并入账，到期本金偿还自动处理，含权债（可赎回/可回售）行权事件提醒与执行</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>付息/到期处理T+0完成，含权债提前5交易日发起行权提示</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
@@ -2582,13 +2616,13 @@
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>现券交易系统</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2598,44 +2632,77 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>F02-06</t>
+          <t>F01-12</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>做市/询价接口</t>
+          <t>回购滚动管理</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>支持双边报价模式，库存自动刷新，与做市商系统预留接口</t>
+          <t>质押式/买断式回购到期自动识别，支持一键续作指令生成，回购占用券随生命周期自动更新</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G16" s="25" t="inlineStr">
+          <t>到期回购提前1日预警，续作指令生成成功率&gt;99%</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>IBOR投资账薄管理</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>F01-13</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>公司行为通知</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>债券评级变动/提前偿还/强制赎回等公司行为实时推送，影响持仓自动标注，处理决策记录留痕</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>公司行为推送延迟&lt;30min，影响持仓标注覆盖率100%</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H16" s="8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 回购管理  (Repo Management)</t>
-        </is>
+      <c r="H17" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2645,22 +2712,22 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>F03-01</t>
+          <t>F01-14</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>正/逆回购全周期</t>
+          <t>托管行持仓对账</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>协议回购（GC/质押式）发起、续做、到期，双方确认闭环</t>
+          <t>与中登（交易所债券）、中债登（银行间债券）日终持仓对账，差异自动分类（未交割/错误/缺漏）并推送告警</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>日终对账完成时间&lt;8:00AM，差异识别率100%，自动匹配率&gt;95%</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
@@ -2675,7 +2742,7 @@
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2685,37 +2752,37 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>F03-02</t>
+          <t>F01-15</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>质押品篮子管理</t>
+          <t>IBOR-ABOR差异对比</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>多类质押品估值与折扣率，支持替换与追加保证金（Margin Call）</t>
+          <t>投资账薄（实时）与会计账薄（已结算）差异对比，差异原因自动分类（未结算/估值差/计提差），供中台复核</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>IBOR-ABOR差异原因分类准确率&gt;98%，日终净值差=0（已结算口径）</t>
+        </is>
+      </c>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2725,22 +2792,22 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>F03-03</t>
+          <t>F01-16</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>资金头寸监控</t>
+          <t>交割失败追踪</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>日内融资头寸实时监控，资金缺口预警，与IBOR现金流对接</t>
+          <t>未交割记录全生命周期管理，T+N逾期告警，补交割流程触发，交割失败率统计分析</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>交割失败识别延迟&lt;1h，补交割触发成功率&gt;95%</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
@@ -2749,13 +2816,13 @@
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2765,37 +2832,37 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>F03-04</t>
+          <t>F01-17</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>到期自动提醒</t>
+          <t>实时合规检查</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>到期前T-1/T-3提醒，支持批量续作规则配置</t>
+          <t>投资授权范围/单券集中度/久期限额/评级限额实时监控，违规自动告警并阻断交易指令</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G21" s="26" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>合规检查响应&lt;200ms，零漏报，误报率&lt;0.1%</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H21" s="8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2805,44 +2872,77 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>F03-05</t>
+          <t>F01-18</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>CCP/上清所接口</t>
+          <t>监管报送数据支持</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>标准化质押式回购通过上清所CCP清算，接口对接</t>
+          <t>按人民银行/证监会/银保监会格式提取持仓/交易/资金数据，支持报表模板配置与定时推送</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G22" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>报送数据与IBOR源数据一致性100%，定时推送准时率&gt;99.9%</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H22" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 FICC风险计量平台  (FICC Risk Measurement)</t>
-        </is>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IBOR投资账薄管理</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>F01-19</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>行情数据接入</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>接入AMD/Bloomberg/Wind实时行情（中债估值/利率曲线/信用利差/波动率曲面），标准化清洗后推送至IBOR定价层</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>行情延迟&lt;1s，数据完整性&gt;99.9%，异常行情自动过滤告警</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2852,37 +2952,37 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>F04-01</t>
+          <t>F01-20</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>VaR/CVaR/ES计算</t>
+          <t>交易数据接入</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>历史模拟法/参数法/蒙特卡洛三模式，置信度99%/99.5%可选</t>
+          <t>从OMS/交易终端实时获取成交回报（债券/回购/衍生品），含完整交易状态机（报盘/成交/撤单/部分成交）追踪</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G24" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>成交回报接收延迟&lt;200ms，数据完整性100%，状态机覆盖全交易生命周期</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H24" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2892,37 +2992,37 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>F04-02</t>
+          <t>F01-21</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>压力测试情景库</t>
+          <t>持仓数据获取</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>内置924行情/2015股灾/2020疫情等10+情景，支持自定义</t>
+          <t>期初从托管行/清算系统获取存量持仓，日间成交驱动增量更新，支持多来源持仓比对与主数据确认</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G25" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>期初持仓加载完成&lt;7:00AM，日间增量延迟&lt;500ms，多源持仓一致性核验通过率&gt;99%</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H25" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2932,22 +3032,22 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>F04-03</t>
+          <t>F01-22</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>限额体系与超限预警</t>
+          <t>多时态头寸视图</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>交易员/策略/产品/公司4级限额，实时穿透预警，告警推送</t>
+          <t>按任意历史as-of/as-on日期提取头寸快照（历史切片），同时支持基于未来现金流和已知事件的预测头寸视图，满足绩效复盘与流动性预判双场景</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>历史快照查询任意日期延迟&lt;3s，预测视图覆盖30日前瞻</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -2962,7 +3062,7 @@
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2972,37 +3072,37 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>F04-04</t>
+          <t>F01-23</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>信用风险（CCR）</t>
+          <t>会计分类估值与稽核</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>交易对手敞口实时聚合，EEPE/PFE/CVA估算</t>
+          <t>按FVTPL（市值法）/FVOCI（可供出售）/AMC（摊余成本法）三类会计分类配置估值方法，颗粒度支持个券维度；内嵌估值稽核规则引擎与ABOR系统定期核对，差异自动预警</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G27" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>估值方法配置覆盖全品种，稽核规则命中率&gt;99%，核对差异&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -3012,37 +3112,37 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>F04-05</t>
+          <t>F01-24</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>希腊字母（Greeks）</t>
+          <t>手工补录与审批工作流</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/DV01日内实时计算，覆盖固收+衍生品</t>
+          <t>对上游系统缺失或错误数据支持手工增删改操作，修改后自动触发双级审批工作流，全操作记录审计日志，支持待办集中处理与历史审批检索</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G28" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>审批流配置覆盖100%手工操作类型，操作日志不可篡改，审批完成后数据生效&lt;1min</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3052,84 +3152,84 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>F04-06</t>
+          <t>F01-25</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>风险报告自动化</t>
+          <t>当日模拟试算</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>每日风险报告（Excel/PDF）自动生成，支持监管报送格式</t>
+          <t>投资经理下达模拟交易指令（不实际成交），IBOR实时计算试算前后组合持仓/MtM/DV01/风险敞口变化，支持多方案并行对比及最优路径推荐</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G29" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>模拟指令生效&lt;2s，试算结果与真实成交后结果误差&lt;0.1%，支持≥10方案并行</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H29" s="8" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>异常交易风控</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>F05-01</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>实时CEP监控引擎</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>基于复杂事件处理（CEP），毫秒级事件流检测，滑动窗口聚合</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G31" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>50</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>IBOR投资账薄管理</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>F01-26</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>未来情景试算</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>基于假设的未来交易路径和市场情景（利率平移/信用冲击/流动性压力），预测未来N日组合持仓状态、现金流和风险敞口，输出情景P&amp;L分布</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>支持≥3类情景参数配置，N日预测（N≤30）计算完成&lt;30s</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 现券交易系统  (Bond Trading)</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -3139,17 +3239,17 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>F05-02</t>
+          <t>F02-01</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>异常价格检测</t>
+          <t>银行间双边报价</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>基于历史分位数/实时行情计算价格偏离度，动态阈值自适应</t>
+          <t>CFETS/X-Bond两板块报价，支持询价（RFQ）和竞价</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -3163,13 +3263,13 @@
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -3179,37 +3279,37 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>F05-03</t>
+          <t>F02-02</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>AI异常识别模型</t>
+          <t>交易所债券委托</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>机器学习（XGBoost/LSTM）训练异常交易识别模型，在线推理</t>
+          <t>上交所/深交所债券买卖下单，支持限价/市价/条件单</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G33" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H33" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -3219,17 +3319,17 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>F05-04</t>
+          <t>F02-03</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>规则引擎（可配置）</t>
+          <t>收益率/价格计算</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>No-Code规则配置界面，合规人员自助维护检测规则</t>
+          <t>全品种YTM/价格双向转换，含含权债修正久期计算</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -3243,13 +3343,13 @@
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -3259,17 +3359,17 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>F05-05</t>
+          <t>F02-04</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>监管报送自动化</t>
+          <t>交易前风险校验</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>一键生成证监会/人行格式异常交易报告，历史追溯查询</t>
+          <t>调用事前风控接口，单笔限额/集中度/利率风险实时拦截</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -3283,20 +3383,53 @@
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
-        </is>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>现券交易系统</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>F02-05</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>交易确认与指令生成</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>成交确认后自动生成DVP/FOP清算指令，推送清算结算模块</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -3306,77 +3439,44 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>F06-01</t>
+          <t>F02-06</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>投资策略合规规则库</t>
+          <t>做市/询价接口</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
+          <t>支持双边报价模式，库存自动刷新，与做市商系统预留接口</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G37" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>事前风控/合规</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>F06-02</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>实时订单拦截</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G38" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 回购管理  (Repo Management)</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>回购管理</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3386,17 +3486,17 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>F06-03</t>
+          <t>F03-01</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>限额多维度检查</t>
+          <t>正/逆回购全周期</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
+          <t>协议回购（GC/质押式）发起、续做、到期，双方确认闭环</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3410,13 +3510,13 @@
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>回购管理</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3426,37 +3526,37 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>F06-04</t>
+          <t>F03-02</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>合规审批工作流</t>
+          <t>质押品篮子管理</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>超限申请→审批→记录全流程，支持移动端审批</t>
+          <t>多类质押品估值与折扣率，支持替换与追加保证金（Margin Call）</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G40" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>回购管理</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3466,17 +3566,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>F06-05</t>
+          <t>F03-03</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>监管白/黑名单</t>
+          <t>资金头寸监控</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
+          <t>日内融资头寸实时监控，资金缺口预警，与IBOR现金流对接</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -3490,20 +3590,53 @@
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
-        </is>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>回购管理</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>F03-04</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>到期自动提醒</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>到期前T-1/T-3提醒，支持批量续作规则配置</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>回购管理</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3513,17 +3646,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>F07-01</t>
+          <t>F03-05</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>债券横截面与时序分析</t>
+          <t>CCP/上清所接口</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>跨品种横截面信号挖掘（利差、久期偏差），历史时序趋势/均值回归分析</t>
+          <t>标准化质押式回购通过上清所CCP清算，接口对接</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -3537,53 +3670,20 @@
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>F07-02</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>相对价值分析</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>利差/Z-spread/OAS相对价值，历史分位数定位，套利信号识别</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 FICC风险计量平台  (FICC Risk Measurement)</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3593,37 +3693,37 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>F07-03</t>
+          <t>F04-01</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>组合相关度分析</t>
+          <t>VaR/CVaR/ES计算</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算，组合集中度风险识别，分散化系数监控</t>
+          <t>历史模拟法/参数法/蒙特卡洛三模式，置信度99%/99.5%可选</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G45" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G45" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3633,17 +3733,17 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F04-02</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>压力测试情景库</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+          <t>内置924行情/2015股灾/2020疫情等10+情景，支持自定义</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -3657,13 +3757,13 @@
         </is>
       </c>
       <c r="H46" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3673,17 +3773,17 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>F07-05</t>
+          <t>F04-03</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析</t>
+          <t>限额体系与超限预警</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差敏感度多因子并行计算，组合对冲比率建议</t>
+          <t>交易员/策略/产品/公司4级限额，实时穿透预警，告警推送</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3697,13 +3797,13 @@
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3713,37 +3813,37 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F04-04</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>极端事件分析</t>
+          <t>信用风险（CCR）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情）组合压测，尾部损失分布</t>
+          <t>交易对手敞口实时聚合，EEPE/PFE/CVA估算</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G48" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3753,37 +3853,37 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>F07-07</t>
+          <t>F04-05</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>指数比较分析</t>
+          <t>希腊字母（Greeks）</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）实时监控，超额Alpha分解</t>
+          <t>Delta/Gamma/Vega/Theta/DV01日内实时计算，覆盖固收+衍生品</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G49" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3793,77 +3893,44 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F04-06</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>风险报告自动化</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>BHB模型三效应：资产配置/个券选择/交互效应，日频计算，周/月/季报自动生成</t>
+          <t>每日风险报告（Excel/PDF）自动生成，支持监管报送格式</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G50" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H50" s="8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>F07-09</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>虚拟组合分析</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>组合调整前后效果模拟（净值/风险/收益），交易冲击成本预估，方案比较</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3873,37 +3940,37 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>F07-10</t>
+          <t>F05-01</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>再平衡方案试算与比较</t>
+          <t>实时CEP监控引擎</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>久期/集中度/流动性约束联合优化，多方案并行试算，最优路径推荐</t>
+          <t>基于复杂事件处理（CEP），毫秒级事件流检测，滑动窗口聚合</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G52" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3913,17 +3980,17 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>F07-11</t>
+          <t>F05-02</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>异常价格检测</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>宏观因子驱动大类资产配置模型（利率/信用/权益），动态权重优化建议</t>
+          <t>基于历史分位数/实时行情计算价格偏离度，动态阈值自适应</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -3937,13 +4004,13 @@
         </is>
       </c>
       <c r="H53" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3953,17 +4020,17 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>F07-12</t>
+          <t>F05-03</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>固收+策略分析</t>
+          <t>AI异常识别模型</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解，固收+产品净值模拟</t>
+          <t>机器学习（XGBoost/LSTM）训练异常交易识别模型，在线推理</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -3977,13 +4044,13 @@
         </is>
       </c>
       <c r="H54" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3993,37 +4060,37 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>F07-13</t>
+          <t>F05-04</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>量化策略组合分析</t>
+          <t>规则引擎（可配置）</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤监控</t>
+          <t>No-Code规则配置界面，合规人员自助维护检测规则</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G55" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G55" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4033,17 +4100,17 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>F07-14</t>
+          <t>F05-05</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>流动性分析</t>
+          <t>监管报送自动化</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失估算</t>
+          <t>一键生成证监会/人行格式异常交易报告，历史追溯查询</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -4057,53 +4124,20 @@
         </is>
       </c>
       <c r="H56" s="8" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>F07-15</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>定价计算集成</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>调用量化定价引擎实时估值与Greeks，支持含权债/可转债，结果缓存与推送</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H57" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -4113,37 +4147,37 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>F07-16</t>
+          <t>F06-01</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>利率曲线集成</t>
+          <t>投资策略合规规则库</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/信用），曲线因子提取（水平/斜率/曲率），敏感度映射</t>
+          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G58" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4153,44 +4187,77 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>F07-17</t>
+          <t>F06-02</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>因子模型</t>
+          <t>实时订单拦截</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库，因子暴露实时计算</t>
+          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G59" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>F06-03</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>限额多维度检查</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G59" s="24" t="inlineStr">
+      <c r="G60" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H59" s="8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
-        </is>
+      <c r="H60" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4200,37 +4267,37 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>F08-01</t>
+          <t>F06-04</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>因子模型框架</t>
+          <t>合规审批工作流</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+          <t>超限申请→审批→记录全流程，支持移动端审批</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G61" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G61" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4240,77 +4307,44 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F06-05</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>监管白/黑名单</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G62" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G62" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H62" s="8" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>策略投资/量化</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>F08-03</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>信号生成与调度</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G63" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H63" s="8" t="n">
-        <v>40</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4320,825 +4354,891 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>F08-04</t>
+          <t>F07-01</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>低延迟执行接口</t>
+          <t>债券横截面与时序分析</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G64" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>横截面信号与实际收益相关性&gt;0.3</t>
+        </is>
+      </c>
+      <c r="G64" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>F07-02</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>相对价值分析</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>F07-03</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>组合相关度分析</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>相关矩阵计算&lt;30s（500券组合）</t>
+        </is>
+      </c>
+      <c r="G66" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>F07-04</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>情景分析</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
+        </is>
+      </c>
+      <c r="G67" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>F07-05</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>敏感度分析</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>F07-06</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>极端事件分析</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>历史情景复现误差&lt;1%</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>F07-07</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>指数比较分析</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
+        </is>
+      </c>
+      <c r="G70" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>F07-08</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>绩效归因（Brinson）</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>F07-09</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>虚拟组合分析</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>F07-10</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>再平衡方案试算与比较</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+        </is>
+      </c>
+      <c r="G73" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>F07-11</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>资产配置策略分析</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+        </is>
+      </c>
+      <c r="G74" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" ht="28" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>F07-12</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>固收+策略分析</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>F07-13</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>量化策略组合分析</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>策略容量计算误差&lt;5%</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" ht="28" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>F07-14</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>流动性分析</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+        </is>
+      </c>
+      <c r="G77" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" ht="28" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>F07-15</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>定价计算集成</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="G78" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G79" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>F07-17</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>因子模型</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+        </is>
+      </c>
+      <c r="G80" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="28" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
           <t>策略投资/量化</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>因子模型框架</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" ht="28" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Tick级回测引擎</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G83" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84" ht="28" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>信号生成与调度</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>低延迟执行接口</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G85" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>F08-05</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>实时策略监控</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
         <is>
           <t>持仓/PnL/回撤/Sharpe实时看板，风险触发自动平仓</t>
         </is>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F86" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G65" s="25" t="inlineStr">
+      <c r="G86" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H65" s="8" t="n">
+      <c r="H86" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="28" t="inlineStr">
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="28" t="inlineStr">
         <is>
           <t>【P2】 量化定价引擎  (Quant Pricing Engine)</t>
         </is>
-      </c>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D67" s="29" t="inlineStr">
-        <is>
-          <t>期限结构模型</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
-        </is>
-      </c>
-      <c r="F67" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G67" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H67" s="14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>F09-02</t>
-        </is>
-      </c>
-      <c r="D68" s="29" t="inlineStr">
-        <is>
-          <t>蒙特卡洛求解器</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
-        </is>
-      </c>
-      <c r="F68" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G68" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>F09-03</t>
-        </is>
-      </c>
-      <c r="D69" s="29" t="inlineStr">
-        <is>
-          <t>有限差分（PDE）</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
-        </is>
-      </c>
-      <c r="F69" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G69" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H69" s="14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>F09-04</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>实时Greeks</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
-        </is>
-      </c>
-      <c r="F70" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G70" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H70" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>F09-05</t>
-        </is>
-      </c>
-      <c r="D71" s="29" t="inlineStr">
-        <is>
-          <t>定价服务微服务架构</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
-        </is>
-      </c>
-      <c r="F71" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G71" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H71" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="72" ht="28" customHeight="1">
-      <c r="A72" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>F09-06</t>
-        </is>
-      </c>
-      <c r="D72" s="29" t="inlineStr">
-        <is>
-          <t>历史估值回测</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>基于历史行情重放定价误差分析，模型验证框架</t>
-        </is>
-      </c>
-      <c r="F72" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G72" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H72" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 利率衍生品  (Interest Rate Derivatives)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>F10-01</t>
-        </is>
-      </c>
-      <c r="D74" s="29" t="inlineStr">
-        <is>
-          <t>IRS/OIS/CCS定价</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>利率互换标准与非标结构定价，折现曲线OIS</t>
-        </is>
-      </c>
-      <c r="F74" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G74" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H74" s="14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>F10-02</t>
-        </is>
-      </c>
-      <c r="D75" s="29" t="inlineStr">
-        <is>
-          <t>久期/DV01/凸度</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品Greeks实时计算，组合对冲比率</t>
-        </is>
-      </c>
-      <c r="F75" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G75" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H75" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>F10-03</t>
-        </is>
-      </c>
-      <c r="D76" s="29" t="inlineStr">
-        <is>
-          <t>LCH/上清所CCP接口</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>标准化IRS中央清算，保证金（IM/VM）计算</t>
-        </is>
-      </c>
-      <c r="F76" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G76" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H76" s="14" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="77" ht="28" customHeight="1">
-      <c r="A77" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>F10-04</t>
-        </is>
-      </c>
-      <c r="D77" s="29" t="inlineStr">
-        <is>
-          <t>压力测试/情景分析</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>利率曲线平移/扭转/蝶式情景，组合P&amp;L影响</t>
-        </is>
-      </c>
-      <c r="F77" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G77" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H77" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="78" ht="28" customHeight="1">
-      <c r="A78" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>F10-05</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>利率曲线发布</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>多曲线框架（OIS/Libor过渡/中债曲线）实时发布</t>
-        </is>
-      </c>
-      <c r="F78" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G78" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H78" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>F11-01</t>
-        </is>
-      </c>
-      <c r="D80" s="29" t="inlineStr">
-        <is>
-          <t>信用利差分析</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
-        </is>
-      </c>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G80" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H80" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>F11-02</t>
-        </is>
-      </c>
-      <c r="D81" s="29" t="inlineStr">
-        <is>
-          <t>CDS/CLN定价</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
-        </is>
-      </c>
-      <c r="F81" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G81" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H81" s="14" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>F11-03</t>
-        </is>
-      </c>
-      <c r="D82" s="29" t="inlineStr">
-        <is>
-          <t>信用评级动态监控</t>
-        </is>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
-        </is>
-      </c>
-      <c r="F82" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G82" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H82" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" ht="28" customHeight="1">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>F11-04</t>
-        </is>
-      </c>
-      <c r="D83" s="29" t="inlineStr">
-        <is>
-          <t>违约概率（PD）建模</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
-        </is>
-      </c>
-      <c r="F83" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G83" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H83" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" ht="28" customHeight="1">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>F11-05</t>
-        </is>
-      </c>
-      <c r="D84" s="29" t="inlineStr">
-        <is>
-          <t>集中度限额管理</t>
-        </is>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>行业/发行人/评级集中度多维限额，超限预警</t>
-        </is>
-      </c>
-      <c r="F84" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G84" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H84" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 数据管理/行情平台  (Market Data Platform)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="28" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t>数据管理/行情平台</t>
-        </is>
-      </c>
-      <c r="B86" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>F12-01</t>
-        </is>
-      </c>
-      <c r="D86" s="29" t="inlineStr">
-        <is>
-          <t>多源行情聚合</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="inlineStr">
-        <is>
-          <t>Bloomberg/Wind/中汇信/Refinitiv多源融合，冲突解析</t>
-        </is>
-      </c>
-      <c r="F86" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G86" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H86" s="14" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="87" ht="28" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>数据管理/行情平台</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>F12-02</t>
-        </is>
-      </c>
-      <c r="D87" s="29" t="inlineStr">
-        <is>
-          <t>数据质量校验</t>
-        </is>
-      </c>
-      <c r="E87" s="11" t="inlineStr">
-        <is>
-          <t>异常值/缺失值/跳价自动检测，修复建议与人工审核</t>
-        </is>
-      </c>
-      <c r="F87" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G87" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H87" s="14" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -5148,37 +5248,37 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F09-01</t>
         </is>
       </c>
       <c r="D88" s="29" t="inlineStr">
         <is>
-          <t>历史数据仓库</t>
+          <t>期限结构模型</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>Tick/日频历史行情存储，高效查询（ClickHouse/TimescaleDB）</t>
+          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G88" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G88" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H88" s="14" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B89" s="10" t="inlineStr">
@@ -5188,37 +5288,37 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F09-02</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>收益率曲线发布</t>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>国债/政策行/高等级信用曲线实时发布，Kafka广播</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G89" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G89" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -5228,44 +5328,77 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D90" s="29" t="inlineStr">
         <is>
-          <t>估值价格服务</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>非活跃债券估值价格（中债估值基准），API接口提供</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G90" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G90" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H90" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 交易对手管理  (Counterparty Management)</t>
-        </is>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>量化定价引擎</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>F09-04</t>
+        </is>
+      </c>
+      <c r="D91" s="29" t="inlineStr">
+        <is>
+          <t>实时Greeks</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H91" s="14" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -5275,37 +5408,37 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>对手方评级与审批</t>
+          <t>定价服务微服务架构</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>内部信用评级模型，新增/变更交易对手审批流</t>
+          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G92" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H92" s="14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93" ht="28" customHeight="1">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
@@ -5315,17 +5448,17 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>实时敞口聚合</t>
+          <t>历史估值回测</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>跨产品交易对手名义/MtM敞口实时聚合，压力敞口（EPE）</t>
+          <t>基于历史行情重放定价误差分析，模型验证框架</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -5339,53 +5472,20 @@
         </is>
       </c>
       <c r="H93" s="14" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="94" ht="28" customHeight="1">
-      <c r="A94" s="11" t="inlineStr">
-        <is>
-          <t>交易对手管理</t>
-        </is>
-      </c>
-      <c r="B94" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C94" s="10" t="inlineStr">
-        <is>
-          <t>F13-03</t>
-        </is>
-      </c>
-      <c r="D94" s="29" t="inlineStr">
-        <is>
-          <t>ISDA/CSA协议管理</t>
-        </is>
-      </c>
-      <c r="E94" s="11" t="inlineStr">
-        <is>
-          <t>主协议文档管理，净额结算协议（Netting Set）配置</t>
-        </is>
-      </c>
-      <c r="F94" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G94" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H94" s="14" t="n">
-        <v>25</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 利率衍生品  (Interest Rate Derivatives)</t>
+        </is>
       </c>
     </row>
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
@@ -5395,17 +5495,17 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>CVA/DVA/FVA计算</t>
+          <t>IRS/OIS/CCS定价</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>信用/债务/资金估值调整实时估算，敞口报告</t>
+          <t>利率互换标准与非标结构定价，折现曲线OIS</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -5419,13 +5519,13 @@
         </is>
       </c>
       <c r="H95" s="14" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -5435,44 +5535,77 @@
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D96" s="29" t="inlineStr">
         <is>
-          <t>集中度与限额</t>
+          <t>久期/DV01/凸度</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>对手方/集团合并敞口限额，超限审批与记录</t>
+          <t>利率衍生品Greeks实时计算，组合对冲比率</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G96" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G96" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H96" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 清算结算后台  (Clearing &amp; Settlement)</t>
-        </is>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" ht="28" customHeight="1">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>利率衍生品</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>F10-03</t>
+        </is>
+      </c>
+      <c r="D97" s="29" t="inlineStr">
+        <is>
+          <t>LCH/上清所CCP接口</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>标准化IRS中央清算，保证金（IM/VM）计算</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G97" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H97" s="14" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -5482,17 +5615,17 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>F14-01</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>DVP/FOP指令生成</t>
+          <t>压力测试/情景分析</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>成交后自动生成交割指令，批量/单笔支持</t>
+          <t>利率曲线平移/扭转/蝶式情景，组合P&amp;L影响</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -5506,13 +5639,13 @@
         </is>
       </c>
       <c r="H98" s="14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" ht="28" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
@@ -5522,77 +5655,44 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>F14-02</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D99" s="29" t="inlineStr">
         <is>
-          <t>中登/中债登接口</t>
+          <t>利率曲线发布</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>银行间债券（中债登）和交易所债券（中登）接口对接</t>
+          <t>多曲线框架（OIS/中债曲线）实时发布</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G99" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G99" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H99" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="100" ht="28" customHeight="1">
-      <c r="A100" s="11" t="inlineStr">
-        <is>
-          <t>清算结算后台</t>
-        </is>
-      </c>
-      <c r="B100" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C100" s="10" t="inlineStr">
-        <is>
-          <t>F14-03</t>
-        </is>
-      </c>
-      <c r="D100" s="29" t="inlineStr">
-        <is>
-          <t>待交割明细管理</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="inlineStr">
-        <is>
-          <t>T+0/T+1待交割跟踪，提前预警可能失败交割</t>
-        </is>
-      </c>
-      <c r="F100" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G100" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H100" s="14" t="n">
-        <v>25</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+        </is>
       </c>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
@@ -5602,17 +5702,17 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>F14-04</t>
+          <t>F11-01</t>
         </is>
       </c>
       <c r="D101" s="29" t="inlineStr">
         <is>
-          <t>资金调拨确认</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>资金划拨指令生成，银行资金头寸确认，轧差净额</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -5626,494 +5726,1235 @@
         </is>
       </c>
       <c r="H101" s="14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="11" t="inlineStr">
         <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>F11-02</t>
+        </is>
+      </c>
+      <c r="D102" s="29" t="inlineStr">
+        <is>
+          <t>CDS/CLN定价</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G102" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>F11-03</t>
+        </is>
+      </c>
+      <c r="D103" s="29" t="inlineStr">
+        <is>
+          <t>信用评级动态监控</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G103" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H103" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>F11-04</t>
+        </is>
+      </c>
+      <c r="D104" s="29" t="inlineStr">
+        <is>
+          <t>违约概率（PD）建模</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G104" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>F11-05</t>
+        </is>
+      </c>
+      <c r="D105" s="29" t="inlineStr">
+        <is>
+          <t>集中度限额管理</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>行业/发行人/评级集中度多维限额，超限预警</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G105" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 数据管理/行情平台  (Market Data Platform)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>F12-01</t>
+        </is>
+      </c>
+      <c r="D107" s="29" t="inlineStr">
+        <is>
+          <t>多源行情聚合</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Bloomberg/Wind/中汇信/Refinitiv多源融合，冲突解析</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G107" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H107" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>F12-02</t>
+        </is>
+      </c>
+      <c r="D108" s="29" t="inlineStr">
+        <is>
+          <t>数据质量校验</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>异常值/缺失值/跳价自动检测，修复建议与人工审核</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G108" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H108" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>F12-03</t>
+        </is>
+      </c>
+      <c r="D109" s="29" t="inlineStr">
+        <is>
+          <t>历史数据仓库</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Tick/日频历史行情存储，高效查询（ClickHouse/TimescaleDB）</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G109" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H109" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>F12-04</t>
+        </is>
+      </c>
+      <c r="D110" s="29" t="inlineStr">
+        <is>
+          <t>收益率曲线发布</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>国债/政策行/高等级信用曲线实时发布，Kafka广播</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G110" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H110" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>F12-05</t>
+        </is>
+      </c>
+      <c r="D111" s="29" t="inlineStr">
+        <is>
+          <t>估值价格服务</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>非活跃债券估值价格（中债估值基准），API接口提供</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G111" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H111" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 交易对手管理  (Counterparty Management)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D113" s="29" t="inlineStr">
+        <is>
+          <t>对手方评级与审批</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>内部信用评级模型，新增/变更交易对手审批流</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G113" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H113" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D114" s="29" t="inlineStr">
+        <is>
+          <t>实时敞口聚合</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>跨产品交易对手名义/MtM敞口实时聚合，压力敞口（EPE）</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G114" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H114" s="14" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C115" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D115" s="29" t="inlineStr">
+        <is>
+          <t>ISDA/CSA协议管理</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>主协议文档管理，净额结算协议（Netting Set）配置</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G115" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H115" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D116" s="29" t="inlineStr">
+        <is>
+          <t>CVA/DVA/FVA计算</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>信用/债务/资金估值调整实时估算，敞口报告</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G116" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H116" s="14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C117" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D117" s="29" t="inlineStr">
+        <is>
+          <t>集中度与限额</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>对手方/集团合并敞口限额，超限审批与记录</t>
+        </is>
+      </c>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G117" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H117" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 清算结算后台  (Clearing &amp; Settlement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="28" customHeight="1">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
           <t>清算结算后台</t>
         </is>
       </c>
-      <c r="B102" s="10" t="inlineStr">
+      <c r="B119" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>F14-01</t>
+        </is>
+      </c>
+      <c r="D119" s="29" t="inlineStr">
+        <is>
+          <t>DVP/FOP指令生成</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>成交后自动生成交割指令，批量/单笔支持</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G119" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H119" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" ht="28" customHeight="1">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C120" s="10" t="inlineStr">
+        <is>
+          <t>F14-02</t>
+        </is>
+      </c>
+      <c r="D120" s="29" t="inlineStr">
+        <is>
+          <t>中登/中债登接口</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>银行间债券（中债登）和交易所债券（中登）接口对接</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G120" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="121" ht="28" customHeight="1">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C121" s="10" t="inlineStr">
+        <is>
+          <t>F14-03</t>
+        </is>
+      </c>
+      <c r="D121" s="29" t="inlineStr">
+        <is>
+          <t>待交割明细管理</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>T+0/T+1待交割跟踪，提前预警可能失败交割</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G121" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H121" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
+          <t>F14-04</t>
+        </is>
+      </c>
+      <c r="D122" s="29" t="inlineStr">
+        <is>
+          <t>资金调拨确认</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>资金划拨指令生成，银行资金头寸确认，轧差净额</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G122" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
         <is>
           <t>F14-05</t>
         </is>
       </c>
-      <c r="D102" s="29" t="inlineStr">
+      <c r="D123" s="29" t="inlineStr">
         <is>
           <t>交割失败处理</t>
         </is>
       </c>
-      <c r="E102" s="11" t="inlineStr">
+      <c r="E123" s="11" t="inlineStr">
         <is>
           <t>失败交割自动识别，补交割流程，罚息计算</t>
         </is>
       </c>
-      <c r="F102" s="11" t="inlineStr">
+      <c r="F123" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G102" s="25" t="inlineStr">
+      <c r="G123" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H102" s="14" t="n">
+      <c r="H123" s="14" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="30" t="inlineStr">
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="30" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="28" customHeight="1">
-      <c r="A104" s="17" t="inlineStr">
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B104" s="16" t="inlineStr">
+      <c r="B125" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C104" s="16" t="inlineStr">
+      <c r="C125" s="16" t="inlineStr">
         <is>
           <t>F15-01</t>
         </is>
       </c>
-      <c r="D104" s="31" t="inlineStr">
+      <c r="D125" s="31" t="inlineStr">
         <is>
           <t>双边报价引擎</t>
         </is>
       </c>
-      <c r="E104" s="17" t="inlineStr">
+      <c r="E125" s="17" t="inlineStr">
         <is>
           <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
-      <c r="F104" s="17" t="inlineStr">
+      <c r="F125" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G104" s="27" t="inlineStr">
+      <c r="G125" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H104" s="19" t="n">
+      <c r="H125" s="19" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="17" t="inlineStr">
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B105" s="16" t="inlineStr">
+      <c r="B126" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C105" s="16" t="inlineStr">
+      <c r="C126" s="16" t="inlineStr">
         <is>
           <t>F15-02</t>
         </is>
       </c>
-      <c r="D105" s="31" t="inlineStr">
+      <c r="D126" s="31" t="inlineStr">
         <is>
           <t>库存风险实时管理</t>
         </is>
       </c>
-      <c r="E105" s="17" t="inlineStr">
+      <c r="E126" s="17" t="inlineStr">
         <is>
           <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
-      <c r="F105" s="17" t="inlineStr">
+      <c r="F126" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G105" s="27" t="inlineStr">
+      <c r="G126" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H105" s="19" t="n">
+      <c r="H126" s="19" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="106" ht="28" customHeight="1">
-      <c r="A106" s="17" t="inlineStr">
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B106" s="16" t="inlineStr">
+      <c r="B127" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C106" s="16" t="inlineStr">
+      <c r="C127" s="16" t="inlineStr">
         <is>
           <t>F15-03</t>
         </is>
       </c>
-      <c r="D106" s="31" t="inlineStr">
+      <c r="D127" s="31" t="inlineStr">
         <is>
           <t>报价优化算法</t>
         </is>
       </c>
-      <c r="E106" s="17" t="inlineStr">
+      <c r="E127" s="17" t="inlineStr">
         <is>
           <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
-      <c r="F106" s="17" t="inlineStr">
+      <c r="F127" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G106" s="27" t="inlineStr">
+      <c r="G127" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H106" s="19" t="n">
+      <c r="H127" s="19" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="107" ht="28" customHeight="1">
-      <c r="A107" s="17" t="inlineStr">
+    <row r="128" ht="28" customHeight="1">
+      <c r="A128" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B107" s="16" t="inlineStr">
+      <c r="B128" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C107" s="16" t="inlineStr">
+      <c r="C128" s="16" t="inlineStr">
         <is>
           <t>F15-04</t>
         </is>
       </c>
-      <c r="D107" s="31" t="inlineStr">
+      <c r="D128" s="31" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E107" s="17" t="inlineStr">
+      <c r="E128" s="17" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，策略调优</t>
         </is>
       </c>
-      <c r="F107" s="17" t="inlineStr">
+      <c r="F128" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G107" s="24" t="inlineStr">
+      <c r="G128" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H107" s="19" t="n">
+      <c r="H128" s="19" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="A108" s="17" t="inlineStr">
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B108" s="16" t="inlineStr">
+      <c r="B129" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C108" s="16" t="inlineStr">
+      <c r="C129" s="16" t="inlineStr">
         <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D108" s="31" t="inlineStr">
+      <c r="D129" s="31" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E108" s="17" t="inlineStr">
+      <c r="E129" s="17" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F108" s="17" t="inlineStr">
+      <c r="F129" s="17" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G108" s="25" t="inlineStr">
+      <c r="G129" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H108" s="19" t="n">
+      <c r="H129" s="19" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="30" t="inlineStr">
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="30" t="inlineStr">
         <is>
           <t>【P3】 外汇/外汇衍生品  (FX &amp; FX Derivatives)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="28" customHeight="1">
-      <c r="A110" s="17" t="inlineStr">
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B110" s="16" t="inlineStr">
+      <c r="B131" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C110" s="16" t="inlineStr">
+      <c r="C131" s="16" t="inlineStr">
         <is>
           <t>F16-01</t>
         </is>
       </c>
-      <c r="D110" s="31" t="inlineStr">
+      <c r="D131" s="31" t="inlineStr">
         <is>
           <t>即期/远期报价</t>
         </is>
       </c>
-      <c r="E110" s="17" t="inlineStr">
+      <c r="E131" s="17" t="inlineStr">
         <is>
           <t>USD/CNY等主要货币对即期汇率+远期点数报价</t>
         </is>
       </c>
-      <c r="F110" s="17" t="inlineStr">
+      <c r="F131" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G110" s="24" t="inlineStr">
+      <c r="G131" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H110" s="19" t="n">
+      <c r="H131" s="19" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="17" t="inlineStr">
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B111" s="16" t="inlineStr">
+      <c r="B132" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C111" s="16" t="inlineStr">
+      <c r="C132" s="16" t="inlineStr">
         <is>
           <t>F16-02</t>
         </is>
       </c>
-      <c r="D111" s="31" t="inlineStr">
+      <c r="D132" s="31" t="inlineStr">
         <is>
           <t>外汇期权（FXO）</t>
         </is>
       </c>
-      <c r="E111" s="17" t="inlineStr">
+      <c r="E132" s="17" t="inlineStr">
         <is>
           <t>欧式/美式FXO定价（Garman-Kohlhagen），Greeks</t>
         </is>
       </c>
-      <c r="F111" s="17" t="inlineStr">
+      <c r="F132" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G111" s="27" t="inlineStr">
+      <c r="G132" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H111" s="19" t="n">
+      <c r="H132" s="19" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="A112" s="17" t="inlineStr">
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B112" s="16" t="inlineStr">
+      <c r="B133" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C112" s="16" t="inlineStr">
+      <c r="C133" s="16" t="inlineStr">
         <is>
           <t>F16-03</t>
         </is>
       </c>
-      <c r="D112" s="31" t="inlineStr">
+      <c r="D133" s="31" t="inlineStr">
         <is>
           <t>NDF/NDO定价</t>
         </is>
       </c>
-      <c r="E112" s="17" t="inlineStr">
+      <c r="E133" s="17" t="inlineStr">
         <is>
           <t>不可交割远期/期权定价，境外对手对接</t>
         </is>
       </c>
-      <c r="F112" s="17" t="inlineStr">
+      <c r="F133" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G112" s="27" t="inlineStr">
+      <c r="G133" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H112" s="19" t="n">
+      <c r="H133" s="19" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="113" ht="28" customHeight="1">
-      <c r="A113" s="17" t="inlineStr">
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B113" s="16" t="inlineStr">
+      <c r="B134" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C113" s="16" t="inlineStr">
+      <c r="C134" s="16" t="inlineStr">
         <is>
           <t>F16-04</t>
         </is>
       </c>
-      <c r="D113" s="31" t="inlineStr">
+      <c r="D134" s="31" t="inlineStr">
         <is>
           <t>跨货币敞口汇总</t>
         </is>
       </c>
-      <c r="E113" s="17" t="inlineStr">
+      <c r="E134" s="17" t="inlineStr">
         <is>
           <t>多币种资产折算人民币敞口，汇率风险VaR</t>
         </is>
       </c>
-      <c r="F113" s="17" t="inlineStr">
+      <c r="F134" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G113" s="24" t="inlineStr">
+      <c r="G134" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H113" s="19" t="n">
+      <c r="H134" s="19" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="114" ht="28" customHeight="1">
-      <c r="A114" s="17" t="inlineStr">
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B114" s="16" t="inlineStr">
+      <c r="B135" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C114" s="16" t="inlineStr">
+      <c r="C135" s="16" t="inlineStr">
         <is>
           <t>F16-05</t>
         </is>
       </c>
-      <c r="D114" s="31" t="inlineStr">
+      <c r="D135" s="31" t="inlineStr">
         <is>
           <t>CFETS/外汇局接口</t>
         </is>
       </c>
-      <c r="E114" s="17" t="inlineStr">
+      <c r="E135" s="17" t="inlineStr">
         <is>
           <t>银行间外汇市场CFETS接口，外汇局合规报送</t>
         </is>
       </c>
-      <c r="F114" s="17" t="inlineStr">
+      <c r="F135" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G114" s="24" t="inlineStr">
+      <c r="G135" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H114" s="19" t="n">
+      <c r="H135" s="19" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H115" s="21">
-        <f>SUM(H3:H114)</f>
+      <c r="H136" s="21">
+        <f>SUM(H3:H135)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="A100:H100"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="A109:H109"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A115:G115"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="A106:H106"/>
+    <mergeCell ref="A124:H124"/>
+    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A136:G136"/>
+    <mergeCell ref="A112:H112"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A118:H118"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6886,7 +7727,7 @@
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>3. 现券交易系统</t>
+          <t>3. IBOR投资账薄管理</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -6896,70 +7737,70 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上线：银行间+交易所双市场报盘</t>
+          <t>上线：实时持仓净值，T0对账零差异</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>替换某券商现有债券交易终端</t>
+          <t>资管公司债券持仓实时账薄</t>
         </is>
       </c>
       <c r="E5" s="37" t="inlineStr">
         <is>
-          <t>CFETS接口稳定性</t>
+          <t>多资产估值覆盖率</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>早期接入测试环境联调</t>
+          <t>分批上线（先债券，后衍生品）</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>交易系统组</t>
+          <t>平台基础组</t>
         </is>
       </c>
       <c r="H5" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>替换恒生/金证，直接竞争替代</t>
+          <t>平台锁定效应，长期替换衡泰IBOR</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>4. 回购管理</t>
+          <t>4. 现券交易系统</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上线：正回购全周期，质押替换</t>
+          <t>上线：银行间+交易所双市场报盘</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>某券商质押式回购融资管理</t>
+          <t>替换某券商现有债券交易终端</t>
         </is>
       </c>
       <c r="E6" s="37" t="inlineStr">
         <is>
-          <t>中登/上清所接口联调</t>
+          <t>CFETS接口稳定性</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>建立完整沙箱测试套件</t>
+          <t>早期接入测试环境联调</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -6968,206 +7809,206 @@
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>与现券交易捆绑，提升粘性</t>
+          <t>替换恒生/金证，直接竞争替代</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>5. IBOR投资账薄</t>
+          <t>5. 回购管理</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上线：实时持仓净值，T0对账零差异</t>
+          <t>上线：正回购全周期，质押替换</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>资管公司债券持仓实时账薄</t>
+          <t>某券商质押式回购融资管理</t>
         </is>
       </c>
       <c r="E7" s="37" t="inlineStr">
         <is>
-          <t>多资产估值覆盖率</t>
+          <t>中登/上清所接口联调</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>分批上线（先债券，后衍生品）</t>
+          <t>建立完整沙箱测试套件</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>平台基础组</t>
+          <t>交易系统组</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>平台锁定效应，长期替换衡泰IBOR</t>
+          <t>与现券交易捆绑，提升粘性</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>6. 组合管理+绩效归因</t>
+          <t>6. FICC风险计量平台</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上线：Brinson归因，周报自动生成</t>
+          <t>上线：VaR/压测，监管格式报告</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>资管公司固收组合绩效分析</t>
+          <t>某券商FICC组合风险日报</t>
         </is>
       </c>
       <c r="E8" s="37" t="inlineStr">
         <is>
-          <t>Brinson模型精度验证</t>
+          <t>模型精度vs衡泰基准</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>对标Bloomberg绩效分析基准</t>
+          <t>首期仅VaR/ES，CVA后置</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>投资管理组</t>
+          <t>风控平台组</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>10</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>高端客户差异化，替代SimCorp/衡泰</t>
+          <t>直接替代衡泰，高溢价定价</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>7. 策略投资/量化</t>
+          <t>7. 组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上线：回测引擎，3个策略实盘验证</t>
+          <t>上线：Brinson归因，周报自动生成</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>自营量化部门策略回测平台</t>
+          <t>资管公司固收组合绩效分析</t>
         </is>
       </c>
       <c r="E9" s="37" t="inlineStr">
         <is>
-          <t>Tick回测数据质量</t>
+          <t>Brinson模型精度验证</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>先与AMD行情平台深度整合</t>
+          <t>对标Bloomberg绩效分析基准</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>量化研究组</t>
+          <t>投资管理组</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>12</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>高壁垒护城河，未来SaaS化</t>
+          <t>高端客户差异化，替代SimCorp/衡泰</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>8. FICC风险计量</t>
+          <t>8. 策略投资/量化</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上线：VaR/压测，监管格式报告</t>
+          <t>上线：回测引擎，3个策略实盘验证</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>某券商FICC组合风险日报</t>
+          <t>自营量化部门策略回测平台</t>
         </is>
       </c>
       <c r="E10" s="37" t="inlineStr">
         <is>
-          <t>模型精度vs衡泰基准</t>
+          <t>Tick回测数据质量</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>首期仅VaR/ES，CVA后置</t>
+          <t>先与AMD行情平台深度整合</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>风控平台组</t>
+          <t>量化研究组</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
         <v>10</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>直接替代衡泰，高溢价定价</t>
+          <t>高壁垒护城河，未来SaaS化</t>
         </is>
       </c>
     </row>
@@ -7188,6 +8029,1431 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>系统详情：IBOR投资账薄管理  |  IBOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>战略定位：整个FICC平台的账薄主干，27项功能覆盖持仓/现金/估值/事件/对账/合规/试算全链路   |   数据输入：交易指令数据 / 行情/估值数据 / 资产主数据 / 托管行结算通知   |   量化底座：账户体系(AMI/AMDB) · Kafka实时消息 · Redis分布式缓存</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>模块：IBOR投资账薄管理  (IBOR)  |  优先级：P1  |  竞品：衡泰(老旧)  |  华锐基础：AMI/AMDB账户体系  |  工期：12月  团队：14人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>A. 实时持仓管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A. 实时持仓管理</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>F01-01</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>跨资产实时头寸</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>债券/回购/利率衍生品全品种T0实时持仓，含未交割与待交割敞口分层展示</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>持仓更新延迟&lt;500ms，全品种覆盖率100%</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>交易系统OMS/ATP报盘接口</t>
+        </is>
+      </c>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A. 实时持仓管理</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>F01-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>多账户层级汇总</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>基金/策略/组合/公司四级持仓合并与分拆，支持跨基金同标的穿透聚合</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>层级汇总数据与单账户加总误差为零</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>AMI/AMDB账户主数据</t>
+        </is>
+      </c>
+      <c r="G7" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A. 实时持仓管理</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F01-03</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>账薄T0/T1切换</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>交易日账薄（含未交割）与结算账薄（T+1已交割）自动切换，切换耗时&lt;1min</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>T0/T1持仓差=未交割敞口，自动核验通过率&gt;99%</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>中登/中债登结算接口</t>
+        </is>
+      </c>
+      <c r="G8" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>A. 实时持仓管理</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>F01-04</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>可用券与冻结管理</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>质押券/司法冻结券/回购占用券从可用头寸自动剔除，前台实时可用量查询</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>可用量计算误差为零，冻结事件&lt;30s生效</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>回购管理系统/风控系统</t>
+        </is>
+      </c>
+      <c r="G9" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>A. 实时持仓管理</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>F01-27</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>资产打标与组合树管理</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>多维度资产标签体系（评级/行业/策略/流动性层级/会计分类）灵活配置，支持自定义组合树构建多分析视角；标签驱动持仓穿透聚合和报表分组</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>标签体系支持≥10维度，组合树层级≥4级，标签变更&lt;1min生效影响所有聚合视图</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>资产主数据/IBOR持仓引擎/报表系统</t>
+        </is>
+      </c>
+      <c r="G10" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>B. 现金管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>B. 现金管理</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>F01-05</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>实时现金余额</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>多账户已结算/未结算现金实时汇总，T0资金头寸含日间资金划拨记录</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>现金余额与银行回单误差为零，日中更新频率≥每分钟</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>资金系统/清算结算接口</t>
+        </is>
+      </c>
+      <c r="G12" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>B. 现金管理</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>F01-06</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>现金流预测</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>回购到期/票息支付/衍生品结算现金流7-30日滚动预测，流动性缺口预警</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>7日现金流预测准确率&gt;95%，流动性预警提前24h触发</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>回购管理/利率衍生品/IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G13" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>B. 现金管理</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>F01-07</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>多币种资金管理</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>CNY/USD/HKD等多币种现金分账户轧差，FX即期换算折算人民币净敞口</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>多币种折算汇率误差&lt;0.01%，轧差结果实时刷新</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>外汇系统/AMD行情平台</t>
+        </is>
+      </c>
+      <c r="G14" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>C. 估值与净值</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>C. 估值与净值</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>F01-08</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>实时市值计算</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>接入AMD/Bloomberg/Wind估值价格，全持仓实时MtM与日内PnL计算，支持估值价格覆盖</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>MtM更新延迟&lt;1s，估值覆盖审批留痕100%</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情平台/Bloomberg数据接口</t>
+        </is>
+      </c>
+      <c r="G16" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>C. 估值与净值</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>F01-09</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>应计利息计算</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>债券应计利息按实际/365、实际/360、30/360多计息基准精确计算，日终净值自动生成</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>应计利息与Bloomberg基准误差&lt;0.01元/百元面值</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>资产主数据（票面率/计息基准/付息频率）</t>
+        </is>
+      </c>
+      <c r="G17" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>C. 估值与净值</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>F01-10</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>衍生品逐日盯市</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>IRS/CDS/国债期货逐日MtM计算，保证金余额实时更新，追加保证金（Margin Call）自动触发</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>衍生品MtM与对手方差异&lt;0.5bps，Margin Call触发延迟&lt;5min</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>量化定价引擎/交易对手管理</t>
+        </is>
+      </c>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>D. 事件处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>D. 事件处理</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>F01-11</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>付息与到期处理</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>债券票息自动计算并入账，到期本金偿还自动处理，含权债（可赎回/可回售）行权事件提醒与执行</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>付息/到期处理T+0完成，含权债提前5交易日发起行权提示</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>资产主数据/托管行结算通知</t>
+        </is>
+      </c>
+      <c r="G20" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>D. 事件处理</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>F01-12</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>回购滚动管理</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>质押式/买断式回购到期自动识别，支持一键续作指令生成，回购占用券随生命周期自动更新</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>到期回购提前1日预警，续作指令生成成功率&gt;99%</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>回购管理系统/IBOR头寸</t>
+        </is>
+      </c>
+      <c r="G21" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>D. 事件处理</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>F01-13</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>公司行为通知</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>债券评级变动/提前偿还/强制赎回等公司行为实时推送，影响持仓自动标注，处理决策记录留痕</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>公司行为推送延迟&lt;30min，影响持仓标注覆盖率100%</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>AMD行情平台/资产主数据</t>
+        </is>
+      </c>
+      <c r="G22" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>E. 对账与数据质量</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>E. 对账与数据质量</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>F01-14</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>托管行持仓对账</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>与中登（交易所债券）、中债登（银行间债券）日终持仓对账，差异自动分类（未交割/错误/缺漏）并推送告警</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>日终对账完成时间&lt;8:00AM，差异识别率100%，自动匹配率&gt;95%</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>中登/中债登结算接口/SFTP</t>
+        </is>
+      </c>
+      <c r="G24" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>E. 对账与数据质量</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>F01-15</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>IBOR-ABOR差异对比</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>投资账薄（实时）与会计账薄（已结算）差异对比，差异原因自动分类（未结算/估值差/计提差），供中台复核</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>IBOR-ABOR差异原因分类准确率&gt;98%，日终净值差=0（已结算口径）</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>会计核算系统(ABOR)/IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G25" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>E. 对账与数据质量</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>F01-16</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>交割失败追踪</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>未交割记录全生命周期管理，T+N逾期告警，补交割流程触发，交割失败率统计分析</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>交割失败识别延迟&lt;1h，补交割触发成功率&gt;95%</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>清算结算系统/中登中债登</t>
+        </is>
+      </c>
+      <c r="G26" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>F. 合规与监管</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>F. 合规与监管</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>F01-17</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>实时合规检查</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>投资授权范围/单券集中度/久期限额/评级限额实时监控，违规自动告警并阻断交易指令</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>合规检查响应&lt;200ms，零漏报，误报率&lt;0.1%</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规系统/投资授权书管理</t>
+        </is>
+      </c>
+      <c r="G28" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>F. 合规与监管</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>F01-18</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>监管报送数据支持</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>按人民银行/证监会/银保监会格式提取持仓/交易/资金数据，支持报表模板配置与定时推送</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>报送数据与IBOR源数据一致性100%，定时推送准时率&gt;99.9%</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>IBOR全域数据/报表引擎</t>
+        </is>
+      </c>
+      <c r="G29" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>G. 数据接入与集成</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>G. 数据接入与集成</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>F01-19</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>行情数据接入</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>接入AMD/Bloomberg/Wind实时行情（中债估值/利率曲线/信用利差/波动率曲面），标准化清洗后推送至IBOR定价层</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>行情延迟&lt;1s，数据完整性&gt;99.9%，异常行情自动过滤告警</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情平台/Bloomberg API/Wind数据接口</t>
+        </is>
+      </c>
+      <c r="G31" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>G. 数据接入与集成</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>F01-20</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>交易数据接入</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>从OMS/交易终端实时获取成交回报（债券/回购/衍生品），含完整交易状态机（报盘/成交/撤单/部分成交）追踪</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>成交回报接收延迟&lt;200ms，数据完整性100%，状态机覆盖全交易生命周期</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>ATP报盘引擎/CFETS银行间接口/交易所接口</t>
+        </is>
+      </c>
+      <c r="G32" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>G. 数据接入与集成</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>F01-21</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>持仓数据获取</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>期初从托管行/清算系统获取存量持仓，日间成交驱动增量更新，支持多来源持仓比对与主数据确认</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>期初持仓加载完成&lt;7:00AM，日间增量延迟&lt;500ms，多源持仓一致性核验通过率&gt;99%</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>中登/中债登/托管行SFTP接口/清算结算系统</t>
+        </is>
+      </c>
+      <c r="G33" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>H. What-if 投资试算</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>H. What-if 投资试算</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>F01-22</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>多时态头寸视图</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>按任意历史as-of/as-on日期提取头寸快照（历史切片），同时支持基于未来现金流和已知事件的预测头寸视图，满足绩效复盘与流动性预判双场景</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>历史快照查询任意日期延迟&lt;3s，预测视图覆盖30日前瞻</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>IBOR事件存储引擎/现金流预测模块</t>
+        </is>
+      </c>
+      <c r="G35" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>H. What-if 投资试算</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>F01-23</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>会计分类估值与稽核</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>按FVTPL（市值法）/FVOCI（可供出售）/AMC（摊余成本法）三类会计分类配置估值方法，颗粒度支持个券维度；内嵌估值稽核规则引擎与ABOR系统定期核对，差异自动预警</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>估值方法配置覆盖全品种，稽核规则命中率&gt;99%，核对差异&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>资产主数据（会计分类标签）/ABOR会计系统/AMD估值数据</t>
+        </is>
+      </c>
+      <c r="G36" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>H. What-if 投资试算</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>F01-24</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>手工补录与审批工作流</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>对上游系统缺失或错误数据支持手工增删改操作，修改后自动触发双级审批工作流，全操作记录审计日志，支持待办集中处理与历史审批检索</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>审批流配置覆盖100%手工操作类型，操作日志不可篡改，审批完成后数据生效&lt;1min</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>权限管理系统/IBOR数据核心层</t>
+        </is>
+      </c>
+      <c r="G37" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>H. What-if 投资试算</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>F01-25</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>当日模拟试算</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>投资经理下达模拟交易指令（不实际成交），IBOR实时计算试算前后组合持仓/MtM/DV01/风险敞口变化，支持多方案并行对比及最优路径推荐</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>模拟指令生效&lt;2s，试算结果与真实成交后结果误差&lt;0.1%，支持≥10方案并行</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>IBOR实时持仓/估值引擎/事前风控系统</t>
+        </is>
+      </c>
+      <c r="G38" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>H. What-if 投资试算</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>F01-26</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>未来情景试算</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>基于假设的未来交易路径和市场情景（利率平移/信用冲击/流动性压力），预测未来N日组合持仓状态、现金流和风险敞口，输出情景P&amp;L分布</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>支持≥3类情景参数配置，N日预测（N≤30）计算完成&lt;30s</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>IBOR现金流预测/量化定价引擎/FICC风险计量平台</t>
+        </is>
+      </c>
+      <c r="G39" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="41" t="inlineStr">
+        <is>
+          <t>合计 27项功能  |  P1: 24项  |  P2: 3项</t>
+        </is>
+      </c>
+      <c r="H40" s="21">
+        <f>SUM(H5:H39)</f>
+        <v/>
+      </c>
+      <c r="I40" s="35" t="inlineStr"/>
+      <c r="J40" s="35" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A11:J11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7211,21 +9477,21 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="39" t="inlineStr">
         <is>
-          <t>系统详情：组合管理+绩效归因  |  Portfolio Management &amp; Performance Attribution</t>
+          <t>系统详情：组合管理+绩效归因  |  Portfolio Mgmt &amp; Perf</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="40" t="inlineStr">
         <is>
-          <t>核心目标（Slide 44）：为FICC投资组合管理提供全面解决方案，通过分析投资组合头寸、风险计量、绩效归因，为投资经理在资产管理、组合构建、组合再平衡、指数投资等方面赋能。</t>
+          <t>战略定位：17项功能含量化底座集成；Slide44全景展开   |   来源：Slide 44   |   数据输入：交易数据 / 头寸数据 / 行情数据 / 估值数据   |   量化底座：定价计算 · 利率曲线 · 因子模型</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="41" t="inlineStr">
         <is>
-          <t>架构层次：  【数据层】交易数据 / 头寸数据 / 行情数据 / 估值数据  →  【量化底座】定价计算 · 利率曲线 · 因子模型  →  【组合分析平台】6大功能域（见下表）</t>
+          <t>模块：组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)  |  优先级：P1  |  竞品：SimCorp/衡泰  |  华锐基础：M9 PMS模块  |  工期：12月  团队：12人</t>
         </is>
       </c>
     </row>
@@ -7247,7 +9513,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>功能描述（来源Slide44）</t>
+          <t>功能描述</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -7306,17 +9572,17 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析，支持日/周/月时间窗口</t>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>横截面信号与实际收益相关性&gt;0.3；时序模型回测夏普&gt;0.5</t>
+          <t>横截面信号与实际收益相关性&gt;0.3</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>AMD行情平台 / 估值数据</t>
+          <t>AMD行情平台/估值数据</t>
         </is>
       </c>
       <c r="G6" s="42" t="inlineStr">
@@ -7332,11 +9598,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Slide44首项分析能力</t>
-        </is>
-      </c>
+      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -7356,17 +9618,17 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别，个券评分</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps；分位数计算覆盖5年历史</t>
+          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>量化定价引擎 / AMD行情</t>
+          <t>量化定价引擎/AMD行情</t>
         </is>
       </c>
       <c r="G7" s="42" t="inlineStr">
@@ -7382,11 +9644,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>投资经理最常用分析工具</t>
-        </is>
-      </c>
+      <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -7406,17 +9664,17 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算（滚动窗口60/120/250日），组合集中度风险识别，分散化系数监控</t>
+          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>相关矩阵计算耗时&lt;30s（500券组合）</t>
+          <t>相关矩阵计算&lt;30s（500券组合）</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>IBOR头寸 / AMD历史行情</t>
+          <t>IBOR头寸/AMD历史行情</t>
         </is>
       </c>
       <c r="G8" s="43" t="inlineStr">
@@ -7459,17 +9717,17 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>利率平移/扭转/蝶式、信用利差扩大、流动性冲击三类情景；自定义情景编辑器；多情景P&amp;L并行对比</t>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>情景P&amp;L计算与手工核算误差&lt;0.5%；支持≥20个情景并行</t>
+          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台 / 量化定价引擎</t>
+          <t>FICC风险计量平台/量化定价引擎</t>
         </is>
       </c>
       <c r="G10" s="42" t="inlineStr">
@@ -7485,11 +9743,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>复用风险计量模块情景库</t>
-        </is>
-      </c>
+      <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -7509,7 +9763,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合层面聚合，对冲比率建议输出</t>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -7555,12 +9809,12 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>内置924行情/2015股灾/2020疫情等8+极端情景，组合尾部损失分布，ES(99%)计算</t>
+          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%；与风险计量平台情景库共享</t>
+          <t>历史情景复现误差&lt;1%</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -7581,11 +9835,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>与风险计量平台共享情景库</t>
-        </is>
-      </c>
+      <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="44" t="inlineStr">
@@ -7612,17 +9862,17 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行/定制基准指数；跟踪误差（TE）日频实时监控；超额Alpha三因子分解</t>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>TE计算误差&lt;1bps；支持≥10个基准指数同时跟踪</t>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>AMD中债估值 / IBOR持仓</t>
+          <t>AMD中债估值/IBOR持仓</t>
         </is>
       </c>
       <c r="G14" s="43" t="inlineStr">
@@ -7638,11 +9888,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>中债指数数据接入为前提</t>
-        </is>
-      </c>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -7657,22 +9903,22 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson模型）</t>
+          <t>绩效归因（Brinson）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应；日/周/月/季多时间维度；报告PDF自动生成</t>
+          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Brinson归因结果与Bloomberg AIM误差&lt;0.1%；报告T+1 9:00前自动生成</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>IBOR持仓 / AMD行情 / 指数数据</t>
+          <t>IBOR持仓/AMD行情/指数数据</t>
         </is>
       </c>
       <c r="G15" s="42" t="inlineStr">
@@ -7688,11 +9934,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>核心差异化功能，对标SimCorp/Aladdin</t>
-        </is>
-      </c>
+      <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="44" t="inlineStr">
@@ -7719,17 +9961,17 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易）；市场冲击成本预估；多方案结果对比展示</t>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟结果与真实执行偏差&lt;0.3%</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>IBOR / 现券交易系统（冲击模型）</t>
+          <t>IBOR/现券交易系统</t>
         </is>
       </c>
       <c r="G17" s="42" t="inlineStr">
@@ -7770,12 +10012,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>QP求解100券组合&lt;5s；约束满足率100%</t>
+          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规 / IBOR / 现券系统</t>
+          <t>事前风控/合规/IBOR/现券系统</t>
         </is>
       </c>
       <c r="G18" s="42" t="inlineStr">
@@ -7791,11 +10033,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>QP求解器选型：CVXPY/Gurobi</t>
-        </is>
-      </c>
+      <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
@@ -7815,17 +10053,17 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>宏观因子（利率周期/信用周期/流动性）驱动大类资产配置模型；动态权重优化建议；历史回测验证</t>
+          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>回测期≥5年；模型收益预测方向胜率&gt;55%</t>
+          <t>回测期≥5年，预测方向胜率&gt;55%</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>AMD宏观数据 / 因子模型</t>
+          <t>AMD宏观数据/因子模型</t>
         </is>
       </c>
       <c r="G19" s="42" t="inlineStr">
@@ -7841,11 +10079,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>Phase 1后期或Phase 2</t>
-        </is>
-      </c>
+      <c r="J19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -7865,7 +10099,7 @@
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+产品净值模拟</t>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -7875,7 +10109,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>IBOR / 利率衍生品系统（Phase 2）</t>
+          <t>IBOR/利率衍生品系统</t>
         </is>
       </c>
       <c r="G20" s="42" t="inlineStr">
@@ -7891,11 +10125,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>依赖利率衍生品模块</t>
-        </is>
-      </c>
+      <c r="J20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
@@ -7915,12 +10145,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控，策略权重优化</t>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>策略容量计算误差&lt;5%；组合Sharpe≥1.2（回测）</t>
+          <t>策略容量计算误差&lt;5%</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -7941,11 +10171,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>与策略投资模块深度整合</t>
-        </is>
-      </c>
+      <c r="J21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="30" t="inlineStr">
@@ -7972,17 +10198,17 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估（日均成交量法），组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>LVaR计算与市场基准误差&lt;5%；日均成交量数据覆盖≥95%持仓</t>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>AMD行情（成交量） / IBOR持仓</t>
+          <t>AMD行情/IBOR持仓</t>
         </is>
       </c>
       <c r="G23" s="43" t="inlineStr">
@@ -7998,11 +10224,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>监管流动性要求驱动</t>
-        </is>
-      </c>
+      <c r="J23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="45" t="inlineStr">
@@ -8029,17 +10251,17 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>调用量化定价引擎实时估值与Greeks；支持含权债/可转债/IRS；结果缓存（Redis）与Kafka推送</t>
+          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms；日终全量估值&lt;30min（10万券）</t>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>量化定价引擎（P2模块）</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="G25" s="42" t="inlineStr">
@@ -8055,11 +10277,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>Phase 1用AMD估值代替，Phase 2升级</t>
-        </is>
-      </c>
+      <c r="J25" s="11" t="inlineStr"/>
     </row>
     <row r="26" ht="48" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -8079,17 +10297,17 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS）；Nelson-Siegel参数提取（水平/斜率/曲率）；敏感度映射</t>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;1s；NS参数拟合R²&gt;0.999</t>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>AMD行情平台 / 量化定价引擎</t>
+          <t>AMD行情平台/量化定价引擎</t>
         </is>
       </c>
       <c r="G26" s="43" t="inlineStr">
@@ -8125,17 +10343,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>多因子风险模型（利率/信用/流动性/行业因子）；Alpha因子库（≥20个因子）；因子暴露实时计算与归因</t>
+          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>因子模型解释方差&gt;80%；Alpha IC均值&gt;0.05</t>
+          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>AMD历史行情 / IBOR持仓</t>
+          <t>AMD历史行情/IBOR持仓</t>
         </is>
       </c>
       <c r="G27" s="42" t="inlineStr">
@@ -8151,16 +10369,12 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>复用策略投资模块因子库</t>
-        </is>
-      </c>
+      <c r="J27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="41" t="inlineStr">
         <is>
-          <t>合计 17项功能  |  P1: 12项  |  P2: 5项  |  来源：Slide 44 + 扩展</t>
+          <t>合计 17项功能  |  P1: 13项  |  P2: 4项</t>
         </is>
       </c>
       <c r="H28" s="21">

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源规划" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P1优先启动计划" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_IBOR投资账薄管理" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_现券交易系统" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$19</definedName>
@@ -931,7 +932,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Bond Trading</t>
+          <t>Bond Trading System</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -990,7 +991,7 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>银行间+交易所双市场覆盖</t>
+          <t>银行间+交易所双市场统一订单模型，28项功能覆盖报价/订单/定价/风控/STP/做市/数据/分析全链路</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3222,7 +3223,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>【P1】 现券交易系统  (Bond Trading)</t>
+          <t>【P1】 现券交易系统  (Bond Trading System)</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3250,12 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>CFETS/X-Bond两板块报价，支持询价（RFQ）和竞价</t>
+          <t>CFETS/X-Bond两板块双边报价，支持询价(RFQ)和竞价模式，报价有效期自动管理，批量报价维护与撤单</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>报价发出到CFETS确认&lt;200ms，批量报价支持≥100条/次</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
@@ -3289,12 +3290,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>上交所/深交所债券买卖下单，支持限价/市价/条件单</t>
+          <t>上交所/深交所债券买卖下单，支持限价/市价/条件单三类订单，撤单与改单，ETF债券联接与综合协议交易</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>委托响应&lt;100ms，撤单成功率&gt;99.5%</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
@@ -3319,22 +3320,22 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>F02-03</t>
+          <t>F02-07</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>收益率/价格计算</t>
+          <t>RFQ询价管理</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>全品种YTM/价格双向转换，含含权债修正久期计算</t>
+          <t>支持发起/接收/应答全链路RFQ流程，询价对象多选，报价有效期倒计时，最优报价自动高亮，历史询价记录检索</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>RFQ全流程(发起到成交)端到端&lt;30s，历史记录保存≥1年</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
@@ -3343,7 +3344,7 @@
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
@@ -3359,31 +3360,31 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>F02-04</t>
+          <t>F02-08</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>交易前风险校验</t>
+          <t>Bond Connect跨境接入</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>调用事前风控接口，单笔限额/集中度/利率风险实时拦截</t>
+          <t>对接香港债券通(北向通)，支持境外机构通过Bond Connect参与银行间债券交易，含SWIFT报文生成与境外结算指令</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G35" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>Bond Connect成交回报处理&lt;500ms，SWIFT报文生成准确率100%</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
@@ -3399,22 +3400,22 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>F02-05</t>
+          <t>F02-09</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>交易确认与指令生成</t>
+          <t>订单全生命周期管理</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>成交确认后自动生成DVP/FOP清算指令，推送清算结算模块</t>
+          <t>订单录入/修改/撤销/挂单状态机，支持部分成交跟踪，订单有效期(GTC/GTD/IOC/FOK)配置，订单历史完整审计</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>订单状态更新延迟&lt;100ms，状态机覆盖全生命周期，历史可回溯≥1年</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
@@ -3423,7 +3424,7 @@
         </is>
       </c>
       <c r="H36" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
@@ -3439,22 +3440,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>F02-06</t>
+          <t>F02-10</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>做市/询价接口</t>
+          <t>大宗/协议交易</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>支持双边报价模式，库存自动刷新，与做市商系统预留接口</t>
+          <t>银行间大宗交易报价协商，双边确认，超大额交易分笔拆单执行，协议交易备案与记录</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>大宗交易协商流程≤5步确认，拆单执行计划自动生成</t>
         </is>
       </c>
       <c r="G37" s="25" t="inlineStr">
@@ -3463,20 +3464,53 @@
         </is>
       </c>
       <c r="H37" s="8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 回购管理  (Repo Management)</t>
-        </is>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>现券交易系统</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>F02-11</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>篮子交易与批量下单</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>多债券组合同时建仓/调仓，篮子订单按权重/金额/数量三种模式分配，批量状态监控与部分失败重试</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>篮子交易支持≥50只债券同批，批量下单耗时&lt;5s</t>
+        </is>
+      </c>
+      <c r="G38" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -3486,22 +3520,22 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>F03-01</t>
+          <t>F02-12</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>正/逆回购全周期</t>
+          <t>条件单与算法单接口</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>协议回购（GC/质押式）发起、续做、到期，双方确认闭环</t>
+          <t>价格触发条件单（达到目标YTM/价格自动下单），预留TWAP/VWAP算法交易接口，算法执行进度实时展示</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>条件触发延迟&lt;1s，算法接口支持主流算法交易供应商标准协议</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
@@ -3516,7 +3550,7 @@
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -3526,37 +3560,37 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>F03-02</t>
+          <t>F02-03</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>质押品篮子管理</t>
+          <t>收益率/价格计算</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>多类质押品估值与折扣率，支持替换与追加保证金（Margin Call）</t>
+          <t>全品种YTM/全价/净价双向转换，含权债修正久期，多计息基准(ACT/365/ACT/360/30/360)精确计算</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>YTM计算与Bloomberg基准误差&lt;0.1bps，含权债定价覆盖主流含权结构</t>
+        </is>
+      </c>
+      <c r="G40" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -3566,37 +3600,37 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>F03-03</t>
+          <t>F02-13</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>资金头寸监控</t>
+          <t>特殊品种定价</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>日内融资头寸实时监控，资金缺口预警，与IBOR现金流对接</t>
+          <t>ABS/ABN资产支持证券、永续债、可转债、可交换债、二级资本债定价，含信用利差/流动性溢价调整</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G41" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>特殊品种覆盖率100%，定价结果与市场成交价偏差统计&lt;5bps</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3606,37 +3640,37 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>F03-04</t>
+          <t>F02-14</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>到期自动提醒</t>
+          <t>实时浮盈浮亏</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>到期前T-1/T-3提醒，支持批量续作规则配置</t>
+          <t>成交后即时PnL计算，含已实现/未实现分拆，按账户/策略/品种多维度汇总，日内PnL归因(价格/利息/汇率)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G42" s="26" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>PnL更新延迟&lt;1s，已实现/未实现分拆误差为零</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>回购管理</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3646,44 +3680,77 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>F03-05</t>
+          <t>F02-15</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CCP/上清所接口</t>
+          <t>利率敏感性指标</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>标准化质押式回购通过上清所CCP清算，接口对接</t>
+          <t>DV01/修正久期/凸性实时计算，组合层面利率风险汇总，BP-level利率冲击情景分析</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>敏感性指标与Bloomberg基准误差&lt;1%，组合汇总更新&lt;2s</t>
+        </is>
+      </c>
+      <c r="G43" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H43" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 FICC风险计量平台  (FICC Risk Measurement)</t>
-        </is>
+    <row r="44" ht="28" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>现券交易系统</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>F02-04</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>交易前风险校验</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>调用事前风控接口，单笔限额/账户集中度/利率风险DV01/信用评级限额实时拦截，风控拦截阻断下单</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>风控校验响应&lt;10ms，零漏拦，误报率&lt;0.05%</t>
+        </is>
+      </c>
+      <c r="G44" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3693,37 +3760,37 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>F04-01</t>
+          <t>F02-16</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>VaR/CVaR/ES计算</t>
+          <t>合规规则嵌入</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>历史模拟法/参数法/蒙特卡洛三模式，置信度99%/99.5%可选</t>
+          <t>投资授权范围/禁投清单/单券集中度上限/评级下限嵌入下单流程，不符合规则自动弹窗说明并阻断，支持规则热更新</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G45" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>合规规则覆盖投资授权书100%条款，规则热更新生效&lt;1min</t>
+        </is>
+      </c>
+      <c r="G45" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H45" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3733,37 +3800,37 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>F04-02</t>
+          <t>F02-17</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>压力测试情景库</t>
+          <t>流动性与市场影响评估</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>内置924行情/2015股灾/2020疫情等10+情景，支持自定义</t>
+          <t>大额交易前评估目标债券流动性（换手率/买卖价差/存量规模），估算市场冲击成本，超阈值触发投资经理二次确认</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>流动性评估结果&lt;500ms，大额阈值可配置，确认记录100%留痕</t>
+        </is>
+      </c>
+      <c r="G46" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3773,22 +3840,22 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>F04-03</t>
+          <t>F02-05</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>限额体系与超限预警</t>
+          <t>交易确认与指令生成</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>交易员/策略/产品/公司4级限额，实时穿透预警，告警推送</t>
+          <t>成交确认后自动生成DVP/FOP清算指令，含托管账户/资金账户/ISIN/结算金额完整要素，推送清算结算模块</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>成交到指令生成延迟&lt;500ms，指令要素完整率100%</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
@@ -3797,13 +3864,13 @@
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3813,37 +3880,37 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>F04-04</t>
+          <t>F02-18</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>信用风险（CCR）</t>
+          <t>STP直通处理</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>交易对手敞口实时聚合，EEPE/PFE/CVA估算</t>
+          <t>成交→IBOR更新→清算指令全链路无人工干预，异常（金额差异/账户不匹配）自动隔离进入人工处理队列，STP率实时监控</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G48" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>STP直通率&gt;98%，异常隔离延迟&lt;1min，人工处理队列可视化</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3853,37 +3920,37 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>F04-05</t>
+          <t>F02-19</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>希腊字母（Greeks）</t>
+          <t>成交修正与错单处理</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/DV01日内实时计算，覆盖固收+衍生品</t>
+          <t>支持T+0错单撤销/修改，含双级审批工作流，修正后重新触发STP链路，错单历史与原因分类统计</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>错单处理T+0完成，审批链≤2级，修正后STP重触发成功率&gt;99%</t>
+        </is>
+      </c>
+      <c r="G49" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H49" s="8" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3893,22 +3960,22 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>F04-06</t>
+          <t>F02-20</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>风险报告自动化</t>
+          <t>跨市场净额轧差</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>每日风险报告（Excel/PDF）自动生成，支持监管报送格式</t>
+          <t>同日同券银行间+交易所成交净额轧差计算，减少资金占用，净额结果推送清算系统，轧差差异自动核对</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>净额轧差计算准确率100%，与清算系统差异核对通过率&gt;99.9%</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
@@ -3920,17 +3987,50 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
-        </is>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>现券交易系统</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>F02-06</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>做市报价接口</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>支持双边报价做市模式，库存实时刷新驱动报价价差自动调整，与做市商系统(Module 15)预留标准接口</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>报价刷新延迟&lt;500ms，做市接口符合Module 15做市商系统对接规范</t>
+        </is>
+      </c>
+      <c r="G51" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3940,37 +4040,37 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>F05-01</t>
+          <t>F02-21</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>实时CEP监控引擎</t>
+          <t>库存管理与头寸监控</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>基于复杂事件处理（CEP），毫秒级事件流检测，滑动窗口聚合</t>
+          <t>做市库存实时监控，目标库存区间配置，超出区间触发预警，库存归零/超限自动暂停报价，日内库存P&amp;L实时展示</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G52" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>库存监控更新&lt;1s，超限预警触发率100%，暂停报价延迟&lt;500ms</t>
+        </is>
+      </c>
+      <c r="G52" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H52" s="8" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3980,37 +4080,37 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>F05-02</t>
+          <t>F02-22</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>异常价格检测</t>
+          <t>报价P&amp;L归因</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>基于历史分位数/实时行情计算价格偏离度，动态阈值自适应</t>
+          <t>做市盈亏拆分（买卖价差收益/库存持有收益/汇率收益），按券种/期限/信用等级多维度统计，日/月做市绩效报告</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>P&amp;L归因覆盖100%做市成交，维度下钻≥4级，日报T+0生成</t>
+        </is>
+      </c>
+      <c r="G53" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H53" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -4020,37 +4120,37 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>F05-03</t>
+          <t>F02-23</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>AI异常识别模型</t>
+          <t>实时行情接入</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>机器学习（XGBoost/LSTM）训练异常交易识别模型，在线推理</t>
+          <t>接入AMD/Bloomberg实时债券成交行情、报价行情，标准化清洗，异常跳价过滤，推送至交易终端与定价层</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>行情延迟&lt;1s，异常行情自动过滤告警，数据完整性&gt;99.9%</t>
+        </is>
+      </c>
+      <c r="G54" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H54" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -4060,22 +4160,22 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>F05-04</t>
+          <t>F02-24</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>规则引擎（可配置）</t>
+          <t>利率曲线与信用利差</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>No-Code规则配置界面，合规人员自助维护检测规则</t>
+          <t>中债估值曲线/国债收益率曲线/信用利差矩阵实时推送至交易终端，支持手动覆盖曲线点位（需审批），历史曲线回放</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>曲线更新延迟&lt;2s，历史曲线回放支持任意交易日，覆盖率100%</t>
         </is>
       </c>
       <c r="G55" s="25" t="inlineStr">
@@ -4090,7 +4190,7 @@
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -4100,44 +4200,77 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>F05-05</t>
+          <t>F02-25</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>监管报送自动化</t>
+          <t>债券基础数据维护</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>一键生成证监会/人行格式异常交易报告，历史追溯查询</t>
+          <t>债券要素（ISIN/票面/期限/评级/含权条款/付息安排/发行人）自动从中债登/Wind同步，异动实时告警，人工维护通道与审批</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G56" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>新券上市后基础数据就绪&lt;2h，要素同步准确率&gt;99.9%</t>
+        </is>
+      </c>
+      <c r="G56" s="26" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>现券交易系统</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>F02-26</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>交易执行质量分析(TCA)</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>成交价vs基准价(VWAP/到达价/中债估值)偏差统计，执行成本量化，滑点分析，按交易员/策略/品种多维度排名</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>TCA覆盖100%成交记录，基准价偏差计算准确，报告T+1生成</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="n">
         <v>25</v>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
-        </is>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -4147,37 +4280,37 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>F06-01</t>
+          <t>F02-27</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>投资策略合规规则库</t>
+          <t>监管报送支持</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
+          <t>按CFETS/人民银行/证监会格式提取成交数据，含日成交报告/大额交易申报/异常交易上报，定时自动推送，报送状态跟踪</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G58" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>报送数据与成交记录一致性100%，定时推送准时率&gt;99.9%，推送失败自动告警重试</t>
+        </is>
+      </c>
+      <c r="G58" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H58" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>现券交易系统</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -4187,77 +4320,44 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>F06-02</t>
+          <t>F02-28</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>实时订单拦截</t>
+          <t>交易统计分析</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
+          <t>日/月/季成交量统计（按品种/期限/评级/账户/交易员维度），换手率趋势，市场份额分析，可视化Dashboard与Excel导出</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G59" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>统计报表T+1生成，支持≥6个分析维度，Excel导出格式标准</t>
+        </is>
+      </c>
+      <c r="G59" s="26" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H59" s="8" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>事前风控/合规</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>F06-03</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>限额多维度检查</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G60" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H60" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 回购管理  (Repo Management)</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>回购管理</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -4267,37 +4367,37 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>F06-04</t>
+          <t>F03-01</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>合规审批工作流</t>
+          <t>正/逆回购全周期</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>超限申请→审批→记录全流程，支持移动端审批</t>
+          <t>协议回购（GC/质押式）发起、续做、到期，双方确认闭环</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G61" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G61" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H61" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>回购管理</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -4307,44 +4407,77 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>F06-05</t>
+          <t>F03-02</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>监管白/黑名单</t>
+          <t>质押品篮子管理</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
+          <t>多类质押品估值与折扣率，支持替换与追加保证金（Margin Call）</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G62" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>回购管理</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>F03-03</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>资金头寸监控</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>日内融资头寸实时监控，资金缺口预警，与IBOR现金流对接</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G62" s="25" t="inlineStr">
+      <c r="G63" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H62" s="8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
-        </is>
+      <c r="H63" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>回购管理</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -4354,37 +4487,37 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>F07-01</t>
+          <t>F03-04</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>债券横截面与时序分析</t>
+          <t>到期自动提醒</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
+          <t>到期前T-1/T-3提醒，支持批量续作规则配置</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>横截面信号与实际收益相关性&gt;0.3</t>
-        </is>
-      </c>
-      <c r="G64" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G64" s="26" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H64" s="8" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>回购管理</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -4394,22 +4527,22 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>F07-02</t>
+          <t>F03-05</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>CCP/上清所接口</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+          <t>标准化质押式回购通过上清所CCP清算，接口对接</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
@@ -4418,53 +4551,20 @@
         </is>
       </c>
       <c r="H65" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>F07-03</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>组合相关度分析</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>相关矩阵计算&lt;30s（500券组合）</t>
-        </is>
-      </c>
-      <c r="G66" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H66" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 FICC风险计量平台  (FICC Risk Measurement)</t>
+        </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -4474,37 +4574,37 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F04-01</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>VaR/CVaR/ES计算</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+          <t>历史模拟法/参数法/蒙特卡洛三模式，置信度99%/99.5%可选</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
-        </is>
-      </c>
-      <c r="G67" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G67" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H67" s="8" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -4514,22 +4614,22 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>F07-05</t>
+          <t>F04-02</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析</t>
+          <t>压力测试情景库</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+          <t>内置924行情/2015股灾/2020疫情等10+情景，支持自定义</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G68" s="24" t="inlineStr">
@@ -4538,13 +4638,13 @@
         </is>
       </c>
       <c r="H68" s="8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -4554,22 +4654,22 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F04-03</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>极端事件分析</t>
+          <t>限额体系与超限预警</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+          <t>交易员/策略/产品/公司4级限额，实时穿透预警，告警推送</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G69" s="24" t="inlineStr">
@@ -4584,7 +4684,7 @@
     <row r="70" ht="28" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -4594,37 +4694,37 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>F07-07</t>
+          <t>F04-04</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>指数比较分析</t>
+          <t>信用风险（CCR）</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
+          <t>交易对手敞口实时聚合，EEPE/PFE/CVA估算</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
-        </is>
-      </c>
-      <c r="G70" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G70" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -4634,22 +4734,22 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F04-05</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>希腊字母（Greeks）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+          <t>Delta/Gamma/Vega/Theta/DV01日内实时计算，覆盖固收+衍生品</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G71" s="24" t="inlineStr">
@@ -4658,13 +4758,13 @@
         </is>
       </c>
       <c r="H71" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -4674,77 +4774,44 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>F07-09</t>
+          <t>F04-06</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>虚拟组合分析</t>
+          <t>风险报告自动化</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+          <t>每日风险报告（Excel/PDF）自动生成，支持监管报送格式</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
-        </is>
-      </c>
-      <c r="G72" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G72" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H72" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="73" ht="28" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>F07-10</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>再平衡方案试算与比较</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
-        </is>
-      </c>
-      <c r="G73" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="n">
-        <v>35</v>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -4754,37 +4821,37 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>F07-11</t>
+          <t>F05-01</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>实时CEP监控引擎</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+          <t>基于复杂事件处理（CEP），毫秒级事件流检测，滑动窗口聚合</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%</t>
-        </is>
-      </c>
-      <c r="G74" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G74" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H74" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4794,22 +4861,22 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>F07-12</t>
+          <t>F05-02</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>固收+策略分析</t>
+          <t>异常价格检测</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+          <t>基于历史分位数/实时行情计算价格偏离度，动态阈值自适应</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G75" s="24" t="inlineStr">
@@ -4818,13 +4885,13 @@
         </is>
       </c>
       <c r="H75" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4834,22 +4901,22 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>F07-13</t>
+          <t>F05-03</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>量化策略组合分析</t>
+          <t>AI异常识别模型</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+          <t>机器学习（XGBoost/LSTM）训练异常交易识别模型，在线推理</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>策略容量计算误差&lt;5%</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G76" s="24" t="inlineStr">
@@ -4858,13 +4925,13 @@
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4874,22 +4941,22 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>F07-14</t>
+          <t>F05-04</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>流动性分析</t>
+          <t>规则引擎（可配置）</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+          <t>No-Code规则配置界面，合规人员自助维护检测规则</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+          <t>功能测试通过/正确率100%</t>
         </is>
       </c>
       <c r="G77" s="25" t="inlineStr">
@@ -4904,7 +4971,7 @@
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4914,77 +4981,44 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>F07-15</t>
+          <t>F05-05</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>定价计算集成</t>
+          <t>监管报送自动化</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+          <t>一键生成证监会/人行格式异常交易报告，历史追溯查询</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
-        </is>
-      </c>
-      <c r="G78" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G78" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H78" s="8" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" ht="28" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>F07-16</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>利率曲线集成</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
-        </is>
-      </c>
-      <c r="G79" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="28" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -4994,22 +5028,22 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>F07-17</t>
+          <t>F06-01</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>因子模型</t>
+          <t>投资策略合规规则库</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G80" s="24" t="inlineStr">
@@ -5018,20 +5052,53 @@
         </is>
       </c>
       <c r="H80" s="8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
-        </is>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>F06-02</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>实时订单拦截</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G81" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -5041,17 +5108,17 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>F08-01</t>
+          <t>F06-03</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>因子模型框架</t>
+          <t>限额多维度检查</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -5065,13 +5132,13 @@
         </is>
       </c>
       <c r="H82" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -5081,37 +5148,37 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F06-04</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>合规审批工作流</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+          <t>超限申请→审批→记录全流程，支持移动端审批</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G83" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G83" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -5121,905 +5188,938 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F06-05</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>信号生成与调度</t>
+          <t>监管白/黑名单</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G84" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G84" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="85" ht="28" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>策略投资/量化</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>F08-04</t>
-        </is>
-      </c>
-      <c r="D85" s="4" t="inlineStr">
-        <is>
-          <t>低延迟执行接口</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G85" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H85" s="8" t="n">
-        <v>45</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
+        </is>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>F07-01</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>债券横截面与时序分析</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>横截面信号与实际收益相关性&gt;0.3</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>F07-02</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>相对价值分析</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>F07-03</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>组合相关度分析</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>相关矩阵计算&lt;30s（500券组合）</t>
+        </is>
+      </c>
+      <c r="G88" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" ht="28" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>F07-04</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>情景分析</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>F07-05</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>敏感度分析</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+        </is>
+      </c>
+      <c r="G90" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" ht="28" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>F07-06</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>极端事件分析</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>历史情景复现误差&lt;1%</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>F07-07</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>指数比较分析</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
+        </is>
+      </c>
+      <c r="G92" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>F07-08</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>绩效归因（Brinson）</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" ht="28" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>F07-09</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>虚拟组合分析</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+        </is>
+      </c>
+      <c r="G94" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" ht="28" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>F07-10</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>再平衡方案试算与比较</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" ht="28" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>F07-11</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>资产配置策略分析</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+        </is>
+      </c>
+      <c r="G96" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97" ht="28" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>F07-12</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>固收+策略分析</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+        </is>
+      </c>
+      <c r="G97" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" ht="28" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>F07-13</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>量化策略组合分析</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>策略容量计算误差&lt;5%</t>
+        </is>
+      </c>
+      <c r="G98" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>F07-14</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>流动性分析</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+        </is>
+      </c>
+      <c r="G99" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>F07-15</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>定价计算集成</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="G100" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G101" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" ht="28" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>F07-17</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>因子模型</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+        </is>
+      </c>
+      <c r="G102" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="23" t="inlineStr">
+        <is>
+          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
           <t>策略投资/量化</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>因子模型框架</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G104" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105" ht="28" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Tick级回测引擎</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G105" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>信号生成与调度</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G106" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="107" ht="28" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>低延迟执行接口</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G107" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>F08-05</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D108" s="4" t="inlineStr">
         <is>
           <t>实时策略监控</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E108" s="5" t="inlineStr">
         <is>
           <t>持仓/PnL/回撤/Sharpe实时看板，风险触发自动平仓</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F108" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G86" s="25" t="inlineStr">
+      <c r="G108" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H86" s="8" t="n">
+      <c r="H108" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="28" t="inlineStr">
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="28" t="inlineStr">
         <is>
           <t>【P2】 量化定价引擎  (Quant Pricing Engine)</t>
         </is>
-      </c>
-    </row>
-    <row r="88" ht="28" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D88" s="29" t="inlineStr">
-        <is>
-          <t>期限结构模型</t>
-        </is>
-      </c>
-      <c r="E88" s="11" t="inlineStr">
-        <is>
-          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
-        </is>
-      </c>
-      <c r="F88" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G88" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H88" s="14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>F09-02</t>
-        </is>
-      </c>
-      <c r="D89" s="29" t="inlineStr">
-        <is>
-          <t>蒙特卡洛求解器</t>
-        </is>
-      </c>
-      <c r="E89" s="11" t="inlineStr">
-        <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
-        </is>
-      </c>
-      <c r="F89" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G89" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H89" s="14" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B90" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C90" s="10" t="inlineStr">
-        <is>
-          <t>F09-03</t>
-        </is>
-      </c>
-      <c r="D90" s="29" t="inlineStr">
-        <is>
-          <t>有限差分（PDE）</t>
-        </is>
-      </c>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
-        </is>
-      </c>
-      <c r="F90" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G90" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H90" s="14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="91" ht="28" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>F09-04</t>
-        </is>
-      </c>
-      <c r="D91" s="29" t="inlineStr">
-        <is>
-          <t>实时Greeks</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
-        </is>
-      </c>
-      <c r="F91" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G91" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H91" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="92" ht="28" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C92" s="10" t="inlineStr">
-        <is>
-          <t>F09-05</t>
-        </is>
-      </c>
-      <c r="D92" s="29" t="inlineStr">
-        <is>
-          <t>定价服务微服务架构</t>
-        </is>
-      </c>
-      <c r="E92" s="11" t="inlineStr">
-        <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
-        </is>
-      </c>
-      <c r="F92" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G92" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H92" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>F09-06</t>
-        </is>
-      </c>
-      <c r="D93" s="29" t="inlineStr">
-        <is>
-          <t>历史估值回测</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="inlineStr">
-        <is>
-          <t>基于历史行情重放定价误差分析，模型验证框架</t>
-        </is>
-      </c>
-      <c r="F93" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G93" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H93" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 利率衍生品  (Interest Rate Derivatives)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="28" customHeight="1">
-      <c r="A95" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B95" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C95" s="10" t="inlineStr">
-        <is>
-          <t>F10-01</t>
-        </is>
-      </c>
-      <c r="D95" s="29" t="inlineStr">
-        <is>
-          <t>IRS/OIS/CCS定价</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="inlineStr">
-        <is>
-          <t>利率互换标准与非标结构定价，折现曲线OIS</t>
-        </is>
-      </c>
-      <c r="F95" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G95" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H95" s="14" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="96" ht="28" customHeight="1">
-      <c r="A96" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B96" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C96" s="10" t="inlineStr">
-        <is>
-          <t>F10-02</t>
-        </is>
-      </c>
-      <c r="D96" s="29" t="inlineStr">
-        <is>
-          <t>久期/DV01/凸度</t>
-        </is>
-      </c>
-      <c r="E96" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品Greeks实时计算，组合对冲比率</t>
-        </is>
-      </c>
-      <c r="F96" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G96" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H96" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="97" ht="28" customHeight="1">
-      <c r="A97" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t>F10-03</t>
-        </is>
-      </c>
-      <c r="D97" s="29" t="inlineStr">
-        <is>
-          <t>LCH/上清所CCP接口</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>标准化IRS中央清算，保证金（IM/VM）计算</t>
-        </is>
-      </c>
-      <c r="F97" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G97" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H97" s="14" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="98" ht="28" customHeight="1">
-      <c r="A98" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B98" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C98" s="10" t="inlineStr">
-        <is>
-          <t>F10-04</t>
-        </is>
-      </c>
-      <c r="D98" s="29" t="inlineStr">
-        <is>
-          <t>压力测试/情景分析</t>
-        </is>
-      </c>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>利率曲线平移/扭转/蝶式情景，组合P&amp;L影响</t>
-        </is>
-      </c>
-      <c r="F98" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G98" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H98" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="99" ht="28" customHeight="1">
-      <c r="A99" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C99" s="10" t="inlineStr">
-        <is>
-          <t>F10-05</t>
-        </is>
-      </c>
-      <c r="D99" s="29" t="inlineStr">
-        <is>
-          <t>利率曲线发布</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>多曲线框架（OIS/中债曲线）实时发布</t>
-        </is>
-      </c>
-      <c r="F99" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G99" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H99" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="A101" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B101" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C101" s="10" t="inlineStr">
-        <is>
-          <t>F11-01</t>
-        </is>
-      </c>
-      <c r="D101" s="29" t="inlineStr">
-        <is>
-          <t>信用利差分析</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="inlineStr">
-        <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
-        </is>
-      </c>
-      <c r="F101" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G101" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H101" s="14" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="102" ht="28" customHeight="1">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B102" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C102" s="10" t="inlineStr">
-        <is>
-          <t>F11-02</t>
-        </is>
-      </c>
-      <c r="D102" s="29" t="inlineStr">
-        <is>
-          <t>CDS/CLN定价</t>
-        </is>
-      </c>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
-        </is>
-      </c>
-      <c r="F102" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G102" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H102" s="14" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="A103" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B103" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C103" s="10" t="inlineStr">
-        <is>
-          <t>F11-03</t>
-        </is>
-      </c>
-      <c r="D103" s="29" t="inlineStr">
-        <is>
-          <t>信用评级动态监控</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="inlineStr">
-        <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
-        </is>
-      </c>
-      <c r="F103" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G103" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H103" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="104" ht="28" customHeight="1">
-      <c r="A104" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B104" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C104" s="10" t="inlineStr">
-        <is>
-          <t>F11-04</t>
-        </is>
-      </c>
-      <c r="D104" s="29" t="inlineStr">
-        <is>
-          <t>违约概率（PD）建模</t>
-        </is>
-      </c>
-      <c r="E104" s="11" t="inlineStr">
-        <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G104" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H104" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="A105" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="inlineStr">
-        <is>
-          <t>F11-05</t>
-        </is>
-      </c>
-      <c r="D105" s="29" t="inlineStr">
-        <is>
-          <t>集中度限额管理</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>行业/发行人/评级集中度多维限额，超限预警</t>
-        </is>
-      </c>
-      <c r="F105" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G105" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H105" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 数据管理/行情平台  (Market Data Platform)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="28" customHeight="1">
-      <c r="A107" s="11" t="inlineStr">
-        <is>
-          <t>数据管理/行情平台</t>
-        </is>
-      </c>
-      <c r="B107" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C107" s="10" t="inlineStr">
-        <is>
-          <t>F12-01</t>
-        </is>
-      </c>
-      <c r="D107" s="29" t="inlineStr">
-        <is>
-          <t>多源行情聚合</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>Bloomberg/Wind/中汇信/Refinitiv多源融合，冲突解析</t>
-        </is>
-      </c>
-      <c r="F107" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G107" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H107" s="14" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="108" ht="28" customHeight="1">
-      <c r="A108" s="11" t="inlineStr">
-        <is>
-          <t>数据管理/行情平台</t>
-        </is>
-      </c>
-      <c r="B108" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C108" s="10" t="inlineStr">
-        <is>
-          <t>F12-02</t>
-        </is>
-      </c>
-      <c r="D108" s="29" t="inlineStr">
-        <is>
-          <t>数据质量校验</t>
-        </is>
-      </c>
-      <c r="E108" s="11" t="inlineStr">
-        <is>
-          <t>异常值/缺失值/跳价自动检测，修复建议与人工审核</t>
-        </is>
-      </c>
-      <c r="F108" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G108" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H108" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="109" ht="28" customHeight="1">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t>数据管理/行情平台</t>
-        </is>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
-        <is>
-          <t>F12-03</t>
-        </is>
-      </c>
-      <c r="D109" s="29" t="inlineStr">
-        <is>
-          <t>历史数据仓库</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>Tick/日频历史行情存储，高效查询（ClickHouse/TimescaleDB）</t>
-        </is>
-      </c>
-      <c r="F109" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G109" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H109" s="14" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -6029,37 +6129,37 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F09-01</t>
         </is>
       </c>
       <c r="D110" s="29" t="inlineStr">
         <is>
-          <t>收益率曲线发布</t>
+          <t>期限结构模型</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>国债/政策行/高等级信用曲线实时发布，Kafka广播</t>
+          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G110" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G110" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H110" s="14" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -6069,44 +6169,77 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F09-02</t>
         </is>
       </c>
       <c r="D111" s="29" t="inlineStr">
         <is>
-          <t>估值价格服务</t>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>非活跃债券估值价格（中债估值基准），API接口提供</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G111" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G111" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H111" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 交易对手管理  (Counterparty Management)</t>
-        </is>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>量化定价引擎</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>F09-03</t>
+        </is>
+      </c>
+      <c r="D112" s="29" t="inlineStr">
+        <is>
+          <t>有限差分（PDE）</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G112" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H112" s="14" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -6116,37 +6249,37 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D113" s="29" t="inlineStr">
         <is>
-          <t>对手方评级与审批</t>
+          <t>实时Greeks</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>内部信用评级模型，新增/变更交易对手审批流</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G113" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H113" s="14" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -6156,17 +6289,17 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D114" s="29" t="inlineStr">
         <is>
-          <t>实时敞口聚合</t>
+          <t>定价服务微服务架构</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>跨产品交易对手名义/MtM敞口实时聚合，压力敞口（EPE）</t>
+          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -6180,13 +6313,13 @@
         </is>
       </c>
       <c r="H114" s="14" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>量化定价引擎</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -6196,17 +6329,17 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D115" s="29" t="inlineStr">
         <is>
-          <t>ISDA/CSA协议管理</t>
+          <t>历史估值回测</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>主协议文档管理，净额结算协议（Netting Set）配置</t>
+          <t>基于历史行情重放定价误差分析，模型验证框架</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr">
@@ -6220,53 +6353,20 @@
         </is>
       </c>
       <c r="H115" s="14" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="116" ht="28" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
-        <is>
-          <t>交易对手管理</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C116" s="10" t="inlineStr">
-        <is>
-          <t>F13-04</t>
-        </is>
-      </c>
-      <c r="D116" s="29" t="inlineStr">
-        <is>
-          <t>CVA/DVA/FVA计算</t>
-        </is>
-      </c>
-      <c r="E116" s="11" t="inlineStr">
-        <is>
-          <t>信用/债务/资金估值调整实时估算，敞口报告</t>
-        </is>
-      </c>
-      <c r="F116" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G116" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H116" s="14" t="n">
-        <v>40</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 利率衍生品  (Interest Rate Derivatives)</t>
+        </is>
       </c>
     </row>
     <row r="117" ht="28" customHeight="1">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
@@ -6276,44 +6376,77 @@
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D117" s="29" t="inlineStr">
         <is>
-          <t>集中度与限额</t>
+          <t>IRS/OIS/CCS定价</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>对手方/集团合并敞口限额，超限审批与记录</t>
+          <t>利率互换标准与非标结构定价，折现曲线OIS</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G117" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G117" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H117" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="28" t="inlineStr">
-        <is>
-          <t>【P2】 清算结算后台  (Clearing &amp; Settlement)</t>
-        </is>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>利率衍生品</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C118" s="10" t="inlineStr">
+        <is>
+          <t>F10-02</t>
+        </is>
+      </c>
+      <c r="D118" s="29" t="inlineStr">
+        <is>
+          <t>久期/DV01/凸度</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>利率衍生品Greeks实时计算，组合对冲比率</t>
+        </is>
+      </c>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G118" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H118" s="14" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -6323,17 +6456,17 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>F14-01</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D119" s="29" t="inlineStr">
         <is>
-          <t>DVP/FOP指令生成</t>
+          <t>LCH/上清所CCP接口</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>成交后自动生成交割指令，批量/单笔支持</t>
+          <t>标准化IRS中央清算，保证金（IM/VM）计算</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
@@ -6347,13 +6480,13 @@
         </is>
       </c>
       <c r="H119" s="14" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -6363,37 +6496,37 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>F14-02</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D120" s="29" t="inlineStr">
         <is>
-          <t>中登/中债登接口</t>
+          <t>压力测试/情景分析</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>银行间债券（中债登）和交易所债券（中登）接口对接</t>
+          <t>利率曲线平移/扭转/蝶式情景，组合P&amp;L影响</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G120" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G120" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H120" s="14" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>利率衍生品</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -6403,17 +6536,17 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>F14-03</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D121" s="29" t="inlineStr">
         <is>
-          <t>待交割明细管理</t>
+          <t>利率曲线发布</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>T+0/T+1待交割跟踪，提前预警可能失败交割</t>
+          <t>多曲线框架（OIS/中债曲线）实时发布</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
@@ -6427,533 +6560,1281 @@
         </is>
       </c>
       <c r="H121" s="14" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="122" ht="28" customHeight="1">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>清算结算后台</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C122" s="10" t="inlineStr">
-        <is>
-          <t>F14-04</t>
-        </is>
-      </c>
-      <c r="D122" s="29" t="inlineStr">
-        <is>
-          <t>资金调拨确认</t>
-        </is>
-      </c>
-      <c r="E122" s="11" t="inlineStr">
-        <is>
-          <t>资金划拨指令生成，银行资金头寸确认，轧差净额</t>
-        </is>
-      </c>
-      <c r="F122" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G122" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H122" s="14" t="n">
-        <v>25</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+        </is>
       </c>
     </row>
     <row r="123" ht="28" customHeight="1">
       <c r="A123" s="11" t="inlineStr">
         <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>F11-01</t>
+        </is>
+      </c>
+      <c r="D123" s="29" t="inlineStr">
+        <is>
+          <t>信用利差分析</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G123" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C124" s="10" t="inlineStr">
+        <is>
+          <t>F11-02</t>
+        </is>
+      </c>
+      <c r="D124" s="29" t="inlineStr">
+        <is>
+          <t>CDS/CLN定价</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G124" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H124" s="14" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>F11-03</t>
+        </is>
+      </c>
+      <c r="D125" s="29" t="inlineStr">
+        <is>
+          <t>信用评级动态监控</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G125" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>F11-04</t>
+        </is>
+      </c>
+      <c r="D126" s="29" t="inlineStr">
+        <is>
+          <t>违约概率（PD）建模</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G126" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C127" s="10" t="inlineStr">
+        <is>
+          <t>F11-05</t>
+        </is>
+      </c>
+      <c r="D127" s="29" t="inlineStr">
+        <is>
+          <t>集中度限额管理</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>行业/发行人/评级集中度多维限额，超限预警</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G127" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H127" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 数据管理/行情平台  (Market Data Platform)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>F12-01</t>
+        </is>
+      </c>
+      <c r="D129" s="29" t="inlineStr">
+        <is>
+          <t>多源行情聚合</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>Bloomberg/Wind/中汇信/Refinitiv多源融合，冲突解析</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G129" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H129" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C130" s="10" t="inlineStr">
+        <is>
+          <t>F12-02</t>
+        </is>
+      </c>
+      <c r="D130" s="29" t="inlineStr">
+        <is>
+          <t>数据质量校验</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>异常值/缺失值/跳价自动检测，修复建议与人工审核</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G130" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H130" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>F12-03</t>
+        </is>
+      </c>
+      <c r="D131" s="29" t="inlineStr">
+        <is>
+          <t>历史数据仓库</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>Tick/日频历史行情存储，高效查询（ClickHouse/TimescaleDB）</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G131" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H131" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C132" s="10" t="inlineStr">
+        <is>
+          <t>F12-04</t>
+        </is>
+      </c>
+      <c r="D132" s="29" t="inlineStr">
+        <is>
+          <t>收益率曲线发布</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>国债/政策行/高等级信用曲线实时发布，Kafka广播</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G132" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H132" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C133" s="10" t="inlineStr">
+        <is>
+          <t>F12-05</t>
+        </is>
+      </c>
+      <c r="D133" s="29" t="inlineStr">
+        <is>
+          <t>估值价格服务</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>非活跃债券估值价格（中债估值基准），API接口提供</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G133" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H133" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 交易对手管理  (Counterparty Management)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D135" s="29" t="inlineStr">
+        <is>
+          <t>对手方评级与审批</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>内部信用评级模型，新增/变更交易对手审批流</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G135" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H135" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" ht="28" customHeight="1">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D136" s="29" t="inlineStr">
+        <is>
+          <t>实时敞口聚合</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>跨产品交易对手名义/MtM敞口实时聚合，压力敞口（EPE）</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G136" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D137" s="29" t="inlineStr">
+        <is>
+          <t>ISDA/CSA协议管理</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>主协议文档管理，净额结算协议（Netting Set）配置</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G137" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H137" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D138" s="29" t="inlineStr">
+        <is>
+          <t>CVA/DVA/FVA计算</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>信用/债务/资金估值调整实时估算，敞口报告</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G138" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H138" s="14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="139" ht="28" customHeight="1">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D139" s="29" t="inlineStr">
+        <is>
+          <t>集中度与限额</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>对手方/集团合并敞口限额，超限审批与记录</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G139" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H139" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="28" t="inlineStr">
+        <is>
+          <t>【P2】 清算结算后台  (Clearing &amp; Settlement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
           <t>清算结算后台</t>
         </is>
       </c>
-      <c r="B123" s="10" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>F14-01</t>
+        </is>
+      </c>
+      <c r="D141" s="29" t="inlineStr">
+        <is>
+          <t>DVP/FOP指令生成</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>成交后自动生成交割指令，批量/单笔支持</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G141" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H141" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="142" ht="28" customHeight="1">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>F14-02</t>
+        </is>
+      </c>
+      <c r="D142" s="29" t="inlineStr">
+        <is>
+          <t>中登/中债登接口</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>银行间债券（中债登）和交易所债券（中登）接口对接</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G142" s="27" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H142" s="14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>F14-03</t>
+        </is>
+      </c>
+      <c r="D143" s="29" t="inlineStr">
+        <is>
+          <t>待交割明细管理</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>T+0/T+1待交割跟踪，提前预警可能失败交割</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G143" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H143" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>F14-04</t>
+        </is>
+      </c>
+      <c r="D144" s="29" t="inlineStr">
+        <is>
+          <t>资金调拨确认</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>资金划拨指令生成，银行资金头寸确认，轧差净额</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G144" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
         <is>
           <t>F14-05</t>
         </is>
       </c>
-      <c r="D123" s="29" t="inlineStr">
+      <c r="D145" s="29" t="inlineStr">
         <is>
           <t>交割失败处理</t>
         </is>
       </c>
-      <c r="E123" s="11" t="inlineStr">
+      <c r="E145" s="11" t="inlineStr">
         <is>
           <t>失败交割自动识别，补交割流程，罚息计算</t>
         </is>
       </c>
-      <c r="F123" s="11" t="inlineStr">
+      <c r="F145" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G123" s="25" t="inlineStr">
+      <c r="G145" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H123" s="14" t="n">
+      <c r="H145" s="14" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="30" t="inlineStr">
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="30" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="A125" s="17" t="inlineStr">
+    <row r="147" ht="28" customHeight="1">
+      <c r="A147" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B125" s="16" t="inlineStr">
+      <c r="B147" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C125" s="16" t="inlineStr">
+      <c r="C147" s="16" t="inlineStr">
         <is>
           <t>F15-01</t>
         </is>
       </c>
-      <c r="D125" s="31" t="inlineStr">
+      <c r="D147" s="31" t="inlineStr">
         <is>
           <t>双边报价引擎</t>
         </is>
       </c>
-      <c r="E125" s="17" t="inlineStr">
+      <c r="E147" s="17" t="inlineStr">
         <is>
           <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
-      <c r="F125" s="17" t="inlineStr">
+      <c r="F147" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G125" s="27" t="inlineStr">
+      <c r="G147" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H125" s="19" t="n">
+      <c r="H147" s="19" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="126" ht="28" customHeight="1">
-      <c r="A126" s="17" t="inlineStr">
+    <row r="148" ht="28" customHeight="1">
+      <c r="A148" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B126" s="16" t="inlineStr">
+      <c r="B148" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C126" s="16" t="inlineStr">
+      <c r="C148" s="16" t="inlineStr">
         <is>
           <t>F15-02</t>
         </is>
       </c>
-      <c r="D126" s="31" t="inlineStr">
+      <c r="D148" s="31" t="inlineStr">
         <is>
           <t>库存风险实时管理</t>
         </is>
       </c>
-      <c r="E126" s="17" t="inlineStr">
+      <c r="E148" s="17" t="inlineStr">
         <is>
           <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
-      <c r="F126" s="17" t="inlineStr">
+      <c r="F148" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G126" s="27" t="inlineStr">
+      <c r="G148" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H126" s="19" t="n">
+      <c r="H148" s="19" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="127" ht="28" customHeight="1">
-      <c r="A127" s="17" t="inlineStr">
+    <row r="149" ht="28" customHeight="1">
+      <c r="A149" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B127" s="16" t="inlineStr">
+      <c r="B149" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C127" s="16" t="inlineStr">
+      <c r="C149" s="16" t="inlineStr">
         <is>
           <t>F15-03</t>
         </is>
       </c>
-      <c r="D127" s="31" t="inlineStr">
+      <c r="D149" s="31" t="inlineStr">
         <is>
           <t>报价优化算法</t>
         </is>
       </c>
-      <c r="E127" s="17" t="inlineStr">
+      <c r="E149" s="17" t="inlineStr">
         <is>
           <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
-      <c r="F127" s="17" t="inlineStr">
+      <c r="F149" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G127" s="27" t="inlineStr">
+      <c r="G149" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H127" s="19" t="n">
+      <c r="H149" s="19" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="128" ht="28" customHeight="1">
-      <c r="A128" s="17" t="inlineStr">
+    <row r="150" ht="28" customHeight="1">
+      <c r="A150" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B128" s="16" t="inlineStr">
+      <c r="B150" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C128" s="16" t="inlineStr">
+      <c r="C150" s="16" t="inlineStr">
         <is>
           <t>F15-04</t>
         </is>
       </c>
-      <c r="D128" s="31" t="inlineStr">
+      <c r="D150" s="31" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E128" s="17" t="inlineStr">
+      <c r="E150" s="17" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，策略调优</t>
         </is>
       </c>
-      <c r="F128" s="17" t="inlineStr">
+      <c r="F150" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G128" s="24" t="inlineStr">
+      <c r="G150" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H128" s="19" t="n">
+      <c r="H150" s="19" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="17" t="inlineStr">
+    <row r="151" ht="28" customHeight="1">
+      <c r="A151" s="17" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B129" s="16" t="inlineStr">
+      <c r="B151" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C129" s="16" t="inlineStr">
+      <c r="C151" s="16" t="inlineStr">
         <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D129" s="31" t="inlineStr">
+      <c r="D151" s="31" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E129" s="17" t="inlineStr">
+      <c r="E151" s="17" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F129" s="17" t="inlineStr">
+      <c r="F151" s="17" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G129" s="25" t="inlineStr">
+      <c r="G151" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H129" s="19" t="n">
+      <c r="H151" s="19" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="30" t="inlineStr">
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="30" t="inlineStr">
         <is>
           <t>【P3】 外汇/外汇衍生品  (FX &amp; FX Derivatives)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="28" customHeight="1">
-      <c r="A131" s="17" t="inlineStr">
+    <row r="153" ht="28" customHeight="1">
+      <c r="A153" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B131" s="16" t="inlineStr">
+      <c r="B153" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C131" s="16" t="inlineStr">
+      <c r="C153" s="16" t="inlineStr">
         <is>
           <t>F16-01</t>
         </is>
       </c>
-      <c r="D131" s="31" t="inlineStr">
+      <c r="D153" s="31" t="inlineStr">
         <is>
           <t>即期/远期报价</t>
         </is>
       </c>
-      <c r="E131" s="17" t="inlineStr">
+      <c r="E153" s="17" t="inlineStr">
         <is>
           <t>USD/CNY等主要货币对即期汇率+远期点数报价</t>
         </is>
       </c>
-      <c r="F131" s="17" t="inlineStr">
+      <c r="F153" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G131" s="24" t="inlineStr">
+      <c r="G153" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H131" s="19" t="n">
+      <c r="H153" s="19" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="132" ht="28" customHeight="1">
-      <c r="A132" s="17" t="inlineStr">
+    <row r="154" ht="28" customHeight="1">
+      <c r="A154" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B132" s="16" t="inlineStr">
+      <c r="B154" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C132" s="16" t="inlineStr">
+      <c r="C154" s="16" t="inlineStr">
         <is>
           <t>F16-02</t>
         </is>
       </c>
-      <c r="D132" s="31" t="inlineStr">
+      <c r="D154" s="31" t="inlineStr">
         <is>
           <t>外汇期权（FXO）</t>
         </is>
       </c>
-      <c r="E132" s="17" t="inlineStr">
+      <c r="E154" s="17" t="inlineStr">
         <is>
           <t>欧式/美式FXO定价（Garman-Kohlhagen），Greeks</t>
         </is>
       </c>
-      <c r="F132" s="17" t="inlineStr">
+      <c r="F154" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G132" s="27" t="inlineStr">
+      <c r="G154" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H132" s="19" t="n">
+      <c r="H154" s="19" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="133" ht="28" customHeight="1">
-      <c r="A133" s="17" t="inlineStr">
+    <row r="155" ht="28" customHeight="1">
+      <c r="A155" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B133" s="16" t="inlineStr">
+      <c r="B155" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C133" s="16" t="inlineStr">
+      <c r="C155" s="16" t="inlineStr">
         <is>
           <t>F16-03</t>
         </is>
       </c>
-      <c r="D133" s="31" t="inlineStr">
+      <c r="D155" s="31" t="inlineStr">
         <is>
           <t>NDF/NDO定价</t>
         </is>
       </c>
-      <c r="E133" s="17" t="inlineStr">
+      <c r="E155" s="17" t="inlineStr">
         <is>
           <t>不可交割远期/期权定价，境外对手对接</t>
         </is>
       </c>
-      <c r="F133" s="17" t="inlineStr">
+      <c r="F155" s="17" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G133" s="27" t="inlineStr">
+      <c r="G155" s="27" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H133" s="19" t="n">
+      <c r="H155" s="19" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="134" ht="28" customHeight="1">
-      <c r="A134" s="17" t="inlineStr">
+    <row r="156" ht="28" customHeight="1">
+      <c r="A156" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B134" s="16" t="inlineStr">
+      <c r="B156" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C134" s="16" t="inlineStr">
+      <c r="C156" s="16" t="inlineStr">
         <is>
           <t>F16-04</t>
         </is>
       </c>
-      <c r="D134" s="31" t="inlineStr">
+      <c r="D156" s="31" t="inlineStr">
         <is>
           <t>跨货币敞口汇总</t>
         </is>
       </c>
-      <c r="E134" s="17" t="inlineStr">
+      <c r="E156" s="17" t="inlineStr">
         <is>
           <t>多币种资产折算人民币敞口，汇率风险VaR</t>
         </is>
       </c>
-      <c r="F134" s="17" t="inlineStr">
+      <c r="F156" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G134" s="24" t="inlineStr">
+      <c r="G156" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H134" s="19" t="n">
+      <c r="H156" s="19" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="135" ht="28" customHeight="1">
-      <c r="A135" s="17" t="inlineStr">
+    <row r="157" ht="28" customHeight="1">
+      <c r="A157" s="17" t="inlineStr">
         <is>
           <t>外汇/外汇衍生品</t>
         </is>
       </c>
-      <c r="B135" s="16" t="inlineStr">
+      <c r="B157" s="16" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C135" s="16" t="inlineStr">
+      <c r="C157" s="16" t="inlineStr">
         <is>
           <t>F16-05</t>
         </is>
       </c>
-      <c r="D135" s="31" t="inlineStr">
+      <c r="D157" s="31" t="inlineStr">
         <is>
           <t>CFETS/外汇局接口</t>
         </is>
       </c>
-      <c r="E135" s="17" t="inlineStr">
+      <c r="E157" s="17" t="inlineStr">
         <is>
           <t>银行间外汇市场CFETS接口，外汇局合规报送</t>
         </is>
       </c>
-      <c r="F135" s="17" t="inlineStr">
+      <c r="F157" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G135" s="24" t="inlineStr">
+      <c r="G157" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H135" s="19" t="n">
+      <c r="H157" s="19" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="20" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="20" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H136" s="21">
-        <f>SUM(H3:H135)</f>
+      <c r="H158" s="21">
+        <f>SUM(H3:H157)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A94:H94"/>
-    <mergeCell ref="A100:H100"/>
+    <mergeCell ref="A146:H146"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A106:H106"/>
-    <mergeCell ref="A124:H124"/>
-    <mergeCell ref="A130:H130"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A136:G136"/>
-    <mergeCell ref="A112:H112"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="A118:H118"/>
+    <mergeCell ref="A122:H122"/>
+    <mergeCell ref="A140:H140"/>
+    <mergeCell ref="A109:H109"/>
+    <mergeCell ref="A134:H134"/>
+    <mergeCell ref="A158:G158"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A152:H152"/>
+    <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A116:H116"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A79:H79"/>
     <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9459,6 +10340,1477 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>系统详情：现券交易系统  |  Bond Trading System</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>战略定位：银行间+交易所双市场统一订单模型，28项功能覆盖报价/订单/定价/风控/STP/做市/数据/分析全链路   |   数据输入：CFETS/X-Bond行情与成交回报 / 上交所/深交所债券接口回报 / AMD/Bloomberg实时行情 / 中债估值曲线   |   量化底座：ATP报盘引擎 · IBOR持仓账薄 · 事前风控/合规系统 · 清算结算后台</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>模块：现券交易系统  (Bond Trading System)  |  优先级：P1  |  竞品：恒生/金证  |  华锐基础：ATP债券报盘引擎  |  工期：6月  团队：8人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>A. 市场接入与报价</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A. 市场接入与报价</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>F02-01</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>银行间双边报价</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CFETS/X-Bond两板块双边报价，支持询价(RFQ)和竞价模式，报价有效期自动管理，批量报价维护与撤单</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>报价发出到CFETS确认&lt;200ms，批量报价支持≥100条/次</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>CFETS API/X-Bond API</t>
+        </is>
+      </c>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A. 市场接入与报价</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>F02-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>交易所债券委托</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>上交所/深交所债券买卖下单，支持限价/市价/条件单三类订单，撤单与改单，ETF债券联接与综合协议交易</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>委托响应&lt;100ms，撤单成功率&gt;99.5%</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>上交所/深交所债券接口</t>
+        </is>
+      </c>
+      <c r="G7" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A. 市场接入与报价</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F02-07</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>RFQ询价管理</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>支持发起/接收/应答全链路RFQ流程，询价对象多选，报价有效期倒计时，最优报价自动高亮，历史询价记录检索</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>RFQ全流程(发起到成交)端到端&lt;30s，历史记录保存≥1年</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>CFETS RFQ接口</t>
+        </is>
+      </c>
+      <c r="G8" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>A. 市场接入与报价</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>F02-08</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>Bond Connect跨境接入</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>对接香港债券通(北向通)，支持境外机构通过Bond Connect参与银行间债券交易，含SWIFT报文生成与境外结算指令</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Bond Connect成交回报处理&lt;500ms，SWIFT报文生成准确率100%</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Bond Connect CFETS接口/SWIFT网关</t>
+        </is>
+      </c>
+      <c r="G9" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>B. 订单管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>B. 订单管理</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>F02-09</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>订单全生命周期管理</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>订单录入/修改/撤销/挂单状态机，支持部分成交跟踪，订单有效期(GTC/GTD/IOC/FOK)配置，订单历史完整审计</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>订单状态更新延迟&lt;100ms，状态机覆盖全生命周期，历史可回溯≥1年</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>CFETS/交易所接口/事前风控</t>
+        </is>
+      </c>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>B. 订单管理</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>F02-10</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>大宗/协议交易</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>银行间大宗交易报价协商，双边确认，超大额交易分笔拆单执行，协议交易备案与记录</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>大宗交易协商流程≤5步确认，拆单执行计划自动生成</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>CFETS大宗交易模块</t>
+        </is>
+      </c>
+      <c r="G12" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>B. 订单管理</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>F02-11</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>篮子交易与批量下单</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>多债券组合同时建仓/调仓，篮子订单按权重/金额/数量三种模式分配，批量状态监控与部分失败重试</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>篮子交易支持≥50只债券同批，批量下单耗时&lt;5s</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>订单引擎/IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G13" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>B. 订单管理</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>F02-12</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>条件单与算法单接口</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>价格触发条件单（达到目标YTM/价格自动下单），预留TWAP/VWAP算法交易接口，算法执行进度实时展示</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>条件触发延迟&lt;1s，算法接口支持主流算法交易供应商标准协议</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>AMD实时行情/量化定价引擎</t>
+        </is>
+      </c>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>C. 定价与计算</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>C. 定价与计算</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>F02-03</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>收益率/价格计算</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>全品种YTM/全价/净价双向转换，含权债修正久期，多计息基准(ACT/365/ACT/360/30/360)精确计算</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>YTM计算与Bloomberg基准误差&lt;0.1bps，含权债定价覆盖主流含权结构</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>量化定价引擎(Module 9)/资产主数据</t>
+        </is>
+      </c>
+      <c r="G16" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>C. 定价与计算</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>F02-13</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>特殊品种定价</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>ABS/ABN资产支持证券、永续债、可转债、可交换债、二级资本债定价，含信用利差/流动性溢价调整</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>特殊品种覆盖率100%，定价结果与市场成交价偏差统计&lt;5bps</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>量化定价引擎/信用利差曲线数据</t>
+        </is>
+      </c>
+      <c r="G17" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>C. 定价与计算</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>F02-14</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>实时浮盈浮亏</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>成交后即时PnL计算，含已实现/未实现分拆，按账户/策略/品种多维度汇总，日内PnL归因(价格/利息/汇率)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>PnL更新延迟&lt;1s，已实现/未实现分拆误差为零</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>IBOR持仓/AMD实时行情</t>
+        </is>
+      </c>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>C. 定价与计算</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>F02-15</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>利率敏感性指标</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>DV01/修正久期/凸性实时计算，组合层面利率风险汇总，BP-level利率冲击情景分析</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>敏感性指标与Bloomberg基准误差&lt;1%，组合汇总更新&lt;2s</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>量化定价引擎/IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G19" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>D. 交易前风控</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>D. 交易前风控</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>F02-04</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>交易前风险校验</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>调用事前风控接口，单笔限额/账户集中度/利率风险DV01/信用评级限额实时拦截，风控拦截阻断下单</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>风控校验响应&lt;10ms，零漏拦，误报率&lt;0.05%</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规系统(Module 6)</t>
+        </is>
+      </c>
+      <c r="G21" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>D. 交易前风控</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>F02-16</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>合规规则嵌入</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>投资授权范围/禁投清单/单券集中度上限/评级下限嵌入下单流程，不符合规则自动弹窗说明并阻断，支持规则热更新</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>合规规则覆盖投资授权书100%条款，规则热更新生效&lt;1min</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规系统(Module 6)/投资授权书管理</t>
+        </is>
+      </c>
+      <c r="G22" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>D. 交易前风控</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>F02-17</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>流动性与市场影响评估</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>大额交易前评估目标债券流动性（换手率/买卖价差/存量规模），估算市场冲击成本，超阈值触发投资经理二次确认</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>流动性评估结果&lt;500ms，大额阈值可配置，确认记录100%留痕</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>AMD行情平台/债券基础数据</t>
+        </is>
+      </c>
+      <c r="G23" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>E. 成交处理与STP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>E. 成交处理与STP</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>F02-05</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>交易确认与指令生成</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>成交确认后自动生成DVP/FOP清算指令，含托管账户/资金账户/ISIN/结算金额完整要素，推送清算结算模块</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>成交到指令生成延迟&lt;500ms，指令要素完整率100%</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>清算结算后台(Module 14)/中登中债登接口</t>
+        </is>
+      </c>
+      <c r="G25" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>E. 成交处理与STP</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>F02-18</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>STP直通处理</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>成交→IBOR更新→清算指令全链路无人工干预，异常（金额差异/账户不匹配）自动隔离进入人工处理队列，STP率实时监控</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>STP直通率&gt;98%，异常隔离延迟&lt;1min，人工处理队列可视化</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>IBOR(Module 1)/清算结算(Module 14)/Kafka</t>
+        </is>
+      </c>
+      <c r="G26" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>E. 成交处理与STP</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>F02-19</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>成交修正与错单处理</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>支持T+0错单撤销/修改，含双级审批工作流，修正后重新触发STP链路，错单历史与原因分类统计</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>错单处理T+0完成，审批链≤2级，修正后STP重触发成功率&gt;99%</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>权限管理/IBOR/清算结算</t>
+        </is>
+      </c>
+      <c r="G27" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>E. 成交处理与STP</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>F02-20</t>
+        </is>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
+        <is>
+          <t>跨市场净额轧差</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>同日同券银行间+交易所成交净额轧差计算，减少资金占用，净额结果推送清算系统，轧差差异自动核对</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>净额轧差计算准确率100%，与清算系统差异核对通过率&gt;99.9%</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台(Module 14)</t>
+        </is>
+      </c>
+      <c r="G28" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>F. 做市与流动性管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>F. 做市与流动性管理</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>F02-06</t>
+        </is>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>做市报价接口</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>支持双边报价做市模式，库存实时刷新驱动报价价差自动调整，与做市商系统(Module 15)预留标准接口</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>报价刷新延迟&lt;500ms，做市接口符合Module 15做市商系统对接规范</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>做市商系统(Module 15)/IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G30" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>F. 做市与流动性管理</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>F02-21</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>库存管理与头寸监控</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>做市库存实时监控，目标库存区间配置，超出区间触发预警，库存归零/超限自动暂停报价，日内库存P&amp;L实时展示</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>库存监控更新&lt;1s，超限预警触发率100%，暂停报价延迟&lt;500ms</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>IBOR持仓(Module 1)/做市商系统(Module 15)</t>
+        </is>
+      </c>
+      <c r="G31" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>F. 做市与流动性管理</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>F02-22</t>
+        </is>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>报价P&amp;L归因</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>做市盈亏拆分（买卖价差收益/库存持有收益/汇率收益），按券种/期限/信用等级多维度统计，日/月做市绩效报告</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>P&amp;L归因覆盖100%做市成交，维度下钻≥4级，日报T+0生成</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>IBOR持仓/实时行情/成交记录</t>
+        </is>
+      </c>
+      <c r="G32" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>G. 行情与数据接入</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>G. 行情与数据接入</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>F02-23</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>实时行情接入</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>接入AMD/Bloomberg实时债券成交行情、报价行情，标准化清洗，异常跳价过滤，推送至交易终端与定价层</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>行情延迟&lt;1s，异常行情自动过滤告警，数据完整性&gt;99.9%</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情平台/Bloomberg API</t>
+        </is>
+      </c>
+      <c r="G34" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>G. 行情与数据接入</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>F02-24</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线与信用利差</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>中债估值曲线/国债收益率曲线/信用利差矩阵实时推送至交易终端，支持手动覆盖曲线点位（需审批），历史曲线回放</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;2s，历史曲线回放支持任意交易日，覆盖率100%</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>中债数据接口/AMD估值平台</t>
+        </is>
+      </c>
+      <c r="G35" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>G. 行情与数据接入</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>F02-25</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>债券基础数据维护</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>债券要素（ISIN/票面/期限/评级/含权条款/付息安排/发行人）自动从中债登/Wind同步，异动实时告警，人工维护通道与审批</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>新券上市后基础数据就绪&lt;2h，要素同步准确率&gt;99.9%</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>中债登/Wind数据接口/资产主数据系统</t>
+        </is>
+      </c>
+      <c r="G36" s="43" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>H. 交易分析与报表</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>H. 交易分析与报表</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>F02-26</t>
+        </is>
+      </c>
+      <c r="C38" s="29" t="inlineStr">
+        <is>
+          <t>交易执行质量分析(TCA)</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>成交价vs基准价(VWAP/到达价/中债估值)偏差统计，执行成本量化，滑点分析，按交易员/策略/品种多维度排名</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>TCA覆盖100%成交记录，基准价偏差计算准确，报告T+1生成</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>成交记录/AMD实时行情/中债估值</t>
+        </is>
+      </c>
+      <c r="G38" s="42" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>H. 交易分析与报表</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>F02-27</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>监管报送支持</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>按CFETS/人民银行/证监会格式提取成交数据，含日成交报告/大额交易申报/异常交易上报，定时自动推送，报送状态跟踪</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>报送数据与成交记录一致性100%，定时推送准时率&gt;99.9%，推送失败自动告警重试</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>成交记录/事前风控系统/报表引擎</t>
+        </is>
+      </c>
+      <c r="G39" s="43" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>H. 交易分析与报表</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>F02-28</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>交易统计分析</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>日/月/季成交量统计（按品种/期限/评级/账户/交易员维度），换手率趋势，市场份额分析，可视化Dashboard与Excel导出</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>统计报表T+1生成，支持≥6个分析维度，Excel导出格式标准</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>成交记录/IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G40" s="43" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>合计 28项功能  |  P1: 19项  |  P2: 9项</t>
+        </is>
+      </c>
+      <c r="H41" s="21">
+        <f>SUM(H5:H40)</f>
+        <v/>
+      </c>
+      <c r="I41" s="35" t="inlineStr"/>
+      <c r="J41" s="35" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A33:J33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -268,10 +268,10 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -310,14 +310,14 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -996,45 +996,45 @@
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>回购管理</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Repo Management</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>FOF投资系统</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>FOF Investment System</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>前台交易</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>★★☆☆☆</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>L4</t>
         </is>
@@ -1044,28 +1044,28 @@
           <t>中</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>恒生/金证</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>M9回购管理模块</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="n">
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>IBOR持仓账薄</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="O5" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>资金融通核心，与IBOR强耦合</t>
+      <c r="O5" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>基金/FOF投资业务系统化管理，覆盖基础信息、交易录入、组合风控全链路；对应PPT Slide 43</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
           <t>L4</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>大</t>
         </is>
@@ -1504,7 +1504,7 @@
       <c r="N11" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="O11" s="14" t="n">
+      <c r="O11" s="13" t="n">
         <v>225</v>
       </c>
       <c r="P11" s="11" t="inlineStr">
@@ -1557,7 +1557,7 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>大</t>
         </is>
@@ -1578,7 +1578,7 @@
       <c r="N12" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="O12" s="14" t="n">
+      <c r="O12" s="13" t="n">
         <v>108</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
@@ -1631,7 +1631,7 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr">
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>大</t>
         </is>
@@ -1652,7 +1652,7 @@
       <c r="N13" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="O13" s="14" t="n">
+      <c r="O13" s="13" t="n">
         <v>80</v>
       </c>
       <c r="P13" s="11" t="inlineStr">
@@ -1726,7 +1726,7 @@
       <c r="N14" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="O14" s="14" t="n">
+      <c r="O14" s="13" t="n">
         <v>22</v>
       </c>
       <c r="P14" s="11" t="inlineStr">
@@ -1800,7 +1800,7 @@
       <c r="N15" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="O15" s="14" t="n">
+      <c r="O15" s="13" t="n">
         <v>56</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
@@ -1874,7 +1874,7 @@
       <c r="N16" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="O16" s="14" t="n">
+      <c r="O16" s="13" t="n">
         <v>50</v>
       </c>
       <c r="P16" s="11" t="inlineStr">
@@ -1927,7 +1927,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>大</t>
         </is>
@@ -2001,7 +2001,7 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>大</t>
         </is>
@@ -2071,7 +2071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4348,257 +4348,257 @@
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
-        <is>
-          <t>【P1】 回购管理  (Repo Management)</t>
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>【P2】 FOF投资系统  (FOF Investment System)</t>
         </is>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>回购管理</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>FOF投资系统</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>F03-01</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>正/逆回购全周期</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>协议回购（GC/质押式）发起、续做、到期，双方确认闭环</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
+      <c r="D61" s="28" t="inlineStr">
+        <is>
+          <t>管理人与基础信息管理</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>管理人黑名单维护，基金策略分类，基金基础要素（规模/净值/评级）录入与更新</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G61" s="26" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>FOF投资系统</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>F03-02</t>
+        </is>
+      </c>
+      <c r="D62" s="28" t="inlineStr">
+        <is>
+          <t>基金资产信息获取</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>通过邮箱/API自动获取基金资产报告，解析持仓明细并入库，多来源数据合并去重</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G62" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H62" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>FOF投资系统</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>F03-03</t>
+        </is>
+      </c>
+      <c r="D63" s="28" t="inlineStr">
+        <is>
+          <t>交易录入与审核</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>申购/赎回/换仓交易录入，交易明细管理，双级审核工作流，审批记录留痕</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G63" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>FOF投资系统</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>F03-04</t>
+        </is>
+      </c>
+      <c r="D64" s="28" t="inlineStr">
+        <is>
+          <t>组合风控报告生成</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>按管理人策略限制/投资占比限制/白名单分类生成风控日报和周报，自动推送给风控人员</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G64" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H64" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>FOF投资系统</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>F03-05</t>
+        </is>
+      </c>
+      <c r="D65" s="28" t="inlineStr">
+        <is>
+          <t>子基金持仓穿透</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>穿透底层基金持仓至个券/个股层面，合并计算组合总敞口，支持集中度与评级分布分析</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G61" s="24" t="inlineStr">
+      <c r="G65" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H61" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>回购管理</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>F03-02</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>质押品篮子管理</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>多类质押品估值与折扣率，支持替换与追加保证金（Margin Call）</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G62" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H62" s="8" t="n">
+      <c r="H65" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>回购管理</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>F03-03</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>资金头寸监控</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>日内融资头寸实时监控，资金缺口预警，与IBOR现金流对接</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>FOF投资系统</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>F03-06</t>
+        </is>
+      </c>
+      <c r="D66" s="28" t="inlineStr">
+        <is>
+          <t>申赎情况跟踪</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>子基金申购/赎回状态全生命周期跟踪，到账确认，净值更新后自动触发持仓重算</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G63" s="25" t="inlineStr">
+      <c r="G66" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H63" s="8" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>回购管理</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>F03-04</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>到期自动提醒</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>到期前T-1/T-3提醒，支持批量续作规则配置</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G64" s="26" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H64" s="8" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>回购管理</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>F03-05</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>CCP/上清所接口</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>标准化质押式回购通过上清所CCP清算，接口对接</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G65" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="23" t="inlineStr">
+      <c r="H66" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="23" t="inlineStr">
         <is>
           <t>【P1】 FICC风险计量平台  (FICC Risk Measurement)</t>
         </is>
-      </c>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>FICC风险计量平台</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>F04-01</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>VaR/CVaR/ES计算</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>历史模拟法/参数法/蒙特卡洛三模式，置信度99%/99.5%可选</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G67" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H67" s="8" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
@@ -4614,31 +4614,31 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>F04-02</t>
+          <t>F04-01</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>压力测试情景库</t>
+          <t>VaR/CVaR/ES计算</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>内置924行情/2015股灾/2020疫情等10+情景，支持自定义</t>
+          <t>历史模拟法/参数法/蒙特卡洛三模式，置信度99%/99.5%可选</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G68" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H68" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
@@ -4654,17 +4654,17 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>F04-03</t>
+          <t>F04-02</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>限额体系与超限预警</t>
+          <t>压力测试情景库</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>交易员/策略/产品/公司4级限额，实时穿透预警，告警推送</t>
+          <t>内置924行情/2015股灾/2020疫情等10+情景，支持自定义</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
@@ -4694,31 +4694,31 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>F04-04</t>
+          <t>F04-03</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>信用风险（CCR）</t>
+          <t>限额体系与超限预警</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>交易对手敞口实时聚合，EEPE/PFE/CVA估算</t>
+          <t>交易员/策略/产品/公司4级限额，实时穿透预警，告警推送</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G70" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
@@ -4734,31 +4734,31 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>F04-05</t>
+          <t>F04-04</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>希腊字母（Greeks）</t>
+          <t>信用风险（CCR）</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/DV01日内实时计算，覆盖固收+衍生品</t>
+          <t>交易对手敞口实时聚合，EEPE/PFE/CVA估算</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G71" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G71" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H71" s="8" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
@@ -4774,78 +4774,78 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
+          <t>F04-05</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>希腊字母（Greeks）</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Delta/Gamma/Vega/Theta/DV01日内实时计算，覆盖固收+衍生品</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
           <t>F04-06</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>风险报告自动化</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>每日风险报告（Excel/PDF）自动生成，支持监管报送格式</t>
         </is>
       </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G72" s="25" t="inlineStr">
+      <c r="G73" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H72" s="8" t="n">
+      <c r="H73" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="23" t="inlineStr">
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="23" t="inlineStr">
         <is>
           <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
         </is>
-      </c>
-    </row>
-    <row r="74" ht="28" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>异常交易风控</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>F05-01</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>实时CEP监控引擎</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>基于复杂事件处理（CEP），毫秒级事件流检测，滑动窗口聚合</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G74" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H74" s="8" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1">
@@ -4861,31 +4861,31 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>F05-02</t>
+          <t>F05-01</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>异常价格检测</t>
+          <t>实时CEP监控引擎</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>基于历史分位数/实时行情计算价格偏离度，动态阈值自适应</t>
+          <t>基于复杂事件处理（CEP），毫秒级事件流检测，滑动窗口聚合</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G75" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G75" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1">
@@ -4901,17 +4901,17 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>F05-03</t>
+          <t>F05-02</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>AI异常识别模型</t>
+          <t>异常价格检测</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>机器学习（XGBoost/LSTM）训练异常交易识别模型，在线推理</t>
+          <t>基于历史分位数/实时行情计算价格偏离度，动态阈值自适应</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" ht="28" customHeight="1">
@@ -4941,31 +4941,31 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>F05-04</t>
+          <t>F05-03</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>规则引擎（可配置）</t>
+          <t>AI异常识别模型</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>No-Code规则配置界面，合规人员自助维护检测规则</t>
+          <t>机器学习（XGBoost/LSTM）训练异常交易识别模型，在线推理</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G77" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" ht="28" customHeight="1">
@@ -4981,78 +4981,78 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
+          <t>F05-04</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>规则引擎（可配置）</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>No-Code规则配置界面，合规人员自助维护检测规则</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G78" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>异常交易风控</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
           <t>F05-05</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>监管报送自动化</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>一键生成证监会/人行格式异常交易报告，历史追溯查询</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G78" s="25" t="inlineStr">
+      <c r="G79" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H78" s="8" t="n">
+      <c r="H79" s="8" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="23" t="inlineStr">
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="23" t="inlineStr">
         <is>
           <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
         </is>
-      </c>
-    </row>
-    <row r="80" ht="28" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>事前风控/合规</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>F06-01</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>投资策略合规规则库</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G80" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H80" s="8" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="81" ht="28" customHeight="1">
@@ -5068,31 +5068,31 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>F06-02</t>
+          <t>F06-01</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>实时订单拦截</t>
+          <t>投资策略合规规则库</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
+          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G81" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="82" ht="28" customHeight="1">
@@ -5108,27 +5108,27 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>F06-03</t>
+          <t>F06-02</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>限额多维度检查</t>
+          <t>实时订单拦截</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
+          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G82" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G82" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
@@ -5148,31 +5148,31 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>F06-04</t>
+          <t>F06-03</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>合规审批工作流</t>
+          <t>限额多维度检查</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>超限申请→审批→记录全流程，支持移动端审批</t>
+          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G83" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>F06-05</t>
+          <t>F06-04</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>监管白/黑名单</t>
+          <t>合规审批工作流</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
+          <t>超限申请→审批→记录全流程，支持移动端审批</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -5215,51 +5215,51 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="23" t="inlineStr">
+    <row r="85" ht="28" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>F06-05</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>监管白/黑名单</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G85" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="23" t="inlineStr">
         <is>
           <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
         </is>
-      </c>
-    </row>
-    <row r="86" ht="28" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>F07-01</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>债券横截面与时序分析</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>横截面信号与实际收益相关性&gt;0.3</t>
-        </is>
-      </c>
-      <c r="G86" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H86" s="8" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="87" ht="28" customHeight="1">
@@ -5275,22 +5275,22 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>F07-02</t>
+          <t>F07-01</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>债券横截面与时序分析</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+          <t>横截面信号与实际收益相关性&gt;0.3</t>
         </is>
       </c>
       <c r="G87" s="24" t="inlineStr">
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="H87" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88" ht="28" customHeight="1">
@@ -5315,31 +5315,31 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>F07-03</t>
+          <t>F07-02</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>组合相关度分析</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>相关矩阵计算&lt;30s（500券组合）</t>
-        </is>
-      </c>
-      <c r="G88" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H88" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1">
@@ -5355,31 +5355,31 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F07-03</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>组合相关度分析</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
-        </is>
-      </c>
-      <c r="G89" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>相关矩阵计算&lt;30s（500券组合）</t>
+        </is>
+      </c>
+      <c r="G89" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H89" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" ht="28" customHeight="1">
@@ -5395,22 +5395,22 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>F07-05</t>
+          <t>F07-04</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析</t>
+          <t>情景分析</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
         </is>
       </c>
       <c r="G90" s="24" t="inlineStr">
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="H90" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" ht="28" customHeight="1">
@@ -5435,22 +5435,22 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F07-05</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>极端事件分析</t>
+          <t>敏感度分析</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%</t>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
         </is>
       </c>
       <c r="G91" s="24" t="inlineStr">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="H91" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" ht="28" customHeight="1">
@@ -5475,31 +5475,31 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>F07-07</t>
+          <t>F07-06</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>指数比较分析</t>
+          <t>极端事件分析</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
+          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
-        </is>
-      </c>
-      <c r="G92" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>历史情景复现误差&lt;1%</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H92" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" ht="28" customHeight="1">
@@ -5515,31 +5515,31 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F07-07</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>指数比较分析</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
-        </is>
-      </c>
-      <c r="G93" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
+        </is>
+      </c>
+      <c r="G93" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H93" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" ht="28" customHeight="1">
@@ -5555,22 +5555,22 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>F07-09</t>
+          <t>F07-08</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>虚拟组合分析</t>
+          <t>绩效归因（Brinson）</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
         </is>
       </c>
       <c r="G94" s="24" t="inlineStr">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="H94" s="8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95" ht="28" customHeight="1">
@@ -5595,22 +5595,22 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>F07-10</t>
+          <t>F07-09</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>再平衡方案试算与比较</t>
+          <t>虚拟组合分析</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
         </is>
       </c>
       <c r="G95" s="24" t="inlineStr">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="H95" s="8" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" ht="28" customHeight="1">
@@ -5635,22 +5635,22 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>F07-11</t>
+          <t>F07-10</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>再平衡方案试算与比较</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
         </is>
       </c>
       <c r="G96" s="24" t="inlineStr">
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="H96" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="97" ht="28" customHeight="1">
@@ -5675,22 +5675,22 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>F07-12</t>
+          <t>F07-11</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>固收+策略分析</t>
+          <t>资产配置策略分析</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+          <t>回测期≥5年，预测方向胜率&gt;55%</t>
         </is>
       </c>
       <c r="G97" s="24" t="inlineStr">
@@ -5699,7 +5699,7 @@
         </is>
       </c>
       <c r="H97" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98" ht="28" customHeight="1">
@@ -5715,22 +5715,22 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>F07-13</t>
+          <t>F07-12</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>量化策略组合分析</t>
+          <t>固收+策略分析</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>策略容量计算误差&lt;5%</t>
+          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
         </is>
       </c>
       <c r="G98" s="24" t="inlineStr">
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="H98" s="8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" ht="28" customHeight="1">
@@ -5755,31 +5755,31 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>F07-14</t>
+          <t>F07-13</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>流动性分析</t>
+          <t>量化策略组合分析</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
-        </is>
-      </c>
-      <c r="G99" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>策略容量计算误差&lt;5%</t>
+        </is>
+      </c>
+      <c r="G99" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H99" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100" ht="28" customHeight="1">
@@ -5795,27 +5795,27 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>F07-15</t>
+          <t>F07-14</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>定价计算集成</t>
+          <t>流动性分析</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
-        </is>
-      </c>
-      <c r="G100" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+        </is>
+      </c>
+      <c r="G100" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H100" s="8" t="n">
@@ -5835,31 +5835,31 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>F07-16</t>
+          <t>F07-15</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>利率曲线集成</t>
+          <t>定价计算集成</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
-        </is>
-      </c>
-      <c r="G101" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="G101" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H101" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" ht="28" customHeight="1">
@@ -5875,78 +5875,78 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G102" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" ht="28" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
           <t>F07-17</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>因子模型</t>
         </is>
       </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="E103" s="5" t="inlineStr">
         <is>
           <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F103" s="5" t="inlineStr">
         <is>
           <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
         </is>
       </c>
-      <c r="G102" s="24" t="inlineStr">
+      <c r="G103" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H102" s="8" t="n">
+      <c r="H103" s="8" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="23" t="inlineStr">
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="23" t="inlineStr">
         <is>
           <t>【P1】 策略投资/量化  (Quant Strategy)</t>
         </is>
-      </c>
-    </row>
-    <row r="104" ht="28" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>策略投资/量化</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>F08-01</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>因子模型框架</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
-        <is>
-          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G104" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H104" s="8" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="105" ht="28" customHeight="1">
@@ -5962,31 +5962,31 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F08-01</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>因子模型框架</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G105" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G105" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H105" s="8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106" ht="28" customHeight="1">
@@ -6002,31 +6002,31 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F08-02</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>信号生成与调度</t>
+          <t>Tick级回测引擎</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G106" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G106" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H106" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107" ht="28" customHeight="1">
@@ -6042,31 +6042,31 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>F08-04</t>
+          <t>F08-03</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>低延迟执行接口</t>
+          <t>信号生成与调度</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G107" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G107" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H107" s="8" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108" ht="28" customHeight="1">
@@ -6082,78 +6082,78 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>低延迟执行接口</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G108" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109" ht="28" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
           <t>F08-05</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>实时策略监控</t>
         </is>
       </c>
-      <c r="E108" s="5" t="inlineStr">
+      <c r="E109" s="5" t="inlineStr">
         <is>
           <t>持仓/PnL/回撤/Sharpe实时看板，风险触发自动平仓</t>
         </is>
       </c>
-      <c r="F108" s="5" t="inlineStr">
+      <c r="F109" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G108" s="25" t="inlineStr">
+      <c r="G109" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H108" s="8" t="n">
+      <c r="H109" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="28" t="inlineStr">
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="27" t="inlineStr">
         <is>
           <t>【P2】 量化定价引擎  (Quant Pricing Engine)</t>
         </is>
-      </c>
-    </row>
-    <row r="110" ht="28" customHeight="1">
-      <c r="A110" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D110" s="29" t="inlineStr">
-        <is>
-          <t>期限结构模型</t>
-        </is>
-      </c>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
-        </is>
-      </c>
-      <c r="F110" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G110" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H110" s="14" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="111" ht="28" customHeight="1">
@@ -6169,17 +6169,17 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>F09-02</t>
-        </is>
-      </c>
-      <c r="D111" s="29" t="inlineStr">
-        <is>
-          <t>蒙特卡洛求解器</t>
+          <t>F09-01</t>
+        </is>
+      </c>
+      <c r="D111" s="28" t="inlineStr">
+        <is>
+          <t>期限结构模型</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
+          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -6187,13 +6187,13 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G111" s="27" t="inlineStr">
+      <c r="G111" s="29" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H111" s="14" t="n">
-        <v>70</v>
+      <c r="H111" s="13" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="112" ht="28" customHeight="1">
@@ -6209,17 +6209,17 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>F09-03</t>
-        </is>
-      </c>
-      <c r="D112" s="29" t="inlineStr">
-        <is>
-          <t>有限差分（PDE）</t>
+          <t>F09-02</t>
+        </is>
+      </c>
+      <c r="D112" s="28" t="inlineStr">
+        <is>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr">
@@ -6227,13 +6227,13 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G112" s="27" t="inlineStr">
+      <c r="G112" s="29" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H112" s="14" t="n">
-        <v>60</v>
+      <c r="H112" s="13" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="113" ht="28" customHeight="1">
@@ -6249,31 +6249,31 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>F09-04</t>
-        </is>
-      </c>
-      <c r="D113" s="29" t="inlineStr">
-        <is>
-          <t>实时Greeks</t>
+          <t>F09-03</t>
+        </is>
+      </c>
+      <c r="D113" s="28" t="inlineStr">
+        <is>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G113" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H113" s="14" t="n">
-        <v>40</v>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G113" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H113" s="13" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>F09-05</t>
-        </is>
-      </c>
-      <c r="D114" s="29" t="inlineStr">
-        <is>
-          <t>定价服务微服务架构</t>
+          <t>F09-04</t>
+        </is>
+      </c>
+      <c r="D114" s="28" t="inlineStr">
+        <is>
+          <t>实时Greeks</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr">
@@ -6312,7 +6312,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H114" s="14" t="n">
+      <c r="H114" s="13" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6329,78 +6329,78 @@
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
+          <t>F09-05</t>
+        </is>
+      </c>
+      <c r="D115" s="28" t="inlineStr">
+        <is>
+          <t>定价服务微服务架构</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G115" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H115" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>量化定价引擎</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
           <t>F09-06</t>
         </is>
       </c>
-      <c r="D115" s="29" t="inlineStr">
+      <c r="D116" s="28" t="inlineStr">
         <is>
           <t>历史估值回测</t>
         </is>
       </c>
-      <c r="E115" s="11" t="inlineStr">
+      <c r="E116" s="11" t="inlineStr">
         <is>
           <t>基于历史行情重放定价误差分析，模型验证框架</t>
         </is>
       </c>
-      <c r="F115" s="11" t="inlineStr">
+      <c r="F116" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G115" s="24" t="inlineStr">
+      <c r="G116" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H115" s="14" t="n">
+      <c r="H116" s="13" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="28" t="inlineStr">
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="27" t="inlineStr">
         <is>
           <t>【P2】 利率衍生品  (Interest Rate Derivatives)</t>
         </is>
-      </c>
-    </row>
-    <row r="117" ht="28" customHeight="1">
-      <c r="A117" s="11" t="inlineStr">
-        <is>
-          <t>利率衍生品</t>
-        </is>
-      </c>
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C117" s="10" t="inlineStr">
-        <is>
-          <t>F10-01</t>
-        </is>
-      </c>
-      <c r="D117" s="29" t="inlineStr">
-        <is>
-          <t>IRS/OIS/CCS定价</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>利率互换标准与非标结构定价，折现曲线OIS</t>
-        </is>
-      </c>
-      <c r="F117" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G117" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H117" s="14" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1">
@@ -6416,31 +6416,31 @@
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>F10-02</t>
-        </is>
-      </c>
-      <c r="D118" s="29" t="inlineStr">
-        <is>
-          <t>久期/DV01/凸度</t>
+          <t>F10-01</t>
+        </is>
+      </c>
+      <c r="D118" s="28" t="inlineStr">
+        <is>
+          <t>IRS/OIS/CCS定价</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>利率衍生品Greeks实时计算，组合对冲比率</t>
+          <t>利率互换标准与非标结构定价，折现曲线OIS</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G118" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H118" s="14" t="n">
-        <v>30</v>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G118" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H118" s="13" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="119" ht="28" customHeight="1">
@@ -6456,17 +6456,17 @@
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>F10-03</t>
-        </is>
-      </c>
-      <c r="D119" s="29" t="inlineStr">
-        <is>
-          <t>LCH/上清所CCP接口</t>
+          <t>F10-02</t>
+        </is>
+      </c>
+      <c r="D119" s="28" t="inlineStr">
+        <is>
+          <t>久期/DV01/凸度</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>标准化IRS中央清算，保证金（IM/VM）计算</t>
+          <t>利率衍生品Greeks实时计算，组合对冲比率</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
@@ -6479,8 +6479,8 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H119" s="14" t="n">
-        <v>35</v>
+      <c r="H119" s="13" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1">
@@ -6496,17 +6496,17 @@
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>F10-04</t>
-        </is>
-      </c>
-      <c r="D120" s="29" t="inlineStr">
-        <is>
-          <t>压力测试/情景分析</t>
+          <t>F10-03</t>
+        </is>
+      </c>
+      <c r="D120" s="28" t="inlineStr">
+        <is>
+          <t>LCH/上清所CCP接口</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>利率曲线平移/扭转/蝶式情景，组合P&amp;L影响</t>
+          <t>标准化IRS中央清算，保证金（IM/VM）计算</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
@@ -6519,8 +6519,8 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H120" s="14" t="n">
-        <v>30</v>
+      <c r="H120" s="13" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1">
@@ -6536,78 +6536,78 @@
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
+          <t>F10-04</t>
+        </is>
+      </c>
+      <c r="D121" s="28" t="inlineStr">
+        <is>
+          <t>压力测试/情景分析</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>利率曲线平移/扭转/蝶式情景，组合P&amp;L影响</t>
+        </is>
+      </c>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G121" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H121" s="13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>利率衍生品</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C122" s="10" t="inlineStr">
+        <is>
           <t>F10-05</t>
         </is>
       </c>
-      <c r="D121" s="29" t="inlineStr">
+      <c r="D122" s="28" t="inlineStr">
         <is>
           <t>利率曲线发布</t>
         </is>
       </c>
-      <c r="E121" s="11" t="inlineStr">
+      <c r="E122" s="11" t="inlineStr">
         <is>
           <t>多曲线框架（OIS/中债曲线）实时发布</t>
         </is>
       </c>
-      <c r="F121" s="11" t="inlineStr">
+      <c r="F122" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G121" s="24" t="inlineStr">
+      <c r="G122" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H121" s="14" t="n">
+      <c r="H122" s="13" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="28" t="inlineStr">
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="27" t="inlineStr">
         <is>
           <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
         </is>
-      </c>
-    </row>
-    <row r="123" ht="28" customHeight="1">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C123" s="10" t="inlineStr">
-        <is>
-          <t>F11-01</t>
-        </is>
-      </c>
-      <c r="D123" s="29" t="inlineStr">
-        <is>
-          <t>信用利差分析</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
-        </is>
-      </c>
-      <c r="F123" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G123" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H123" s="14" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="124" ht="28" customHeight="1">
@@ -6623,31 +6623,31 @@
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
-        </is>
-      </c>
-      <c r="D124" s="29" t="inlineStr">
-        <is>
-          <t>CDS/CLN定价</t>
+          <t>F11-01</t>
+        </is>
+      </c>
+      <c r="D124" s="28" t="inlineStr">
+        <is>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G124" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H124" s="14" t="n">
-        <v>50</v>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G124" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H124" s="13" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
@@ -6663,31 +6663,31 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
-        </is>
-      </c>
-      <c r="D125" s="29" t="inlineStr">
-        <is>
-          <t>信用评级动态监控</t>
+          <t>F11-02</t>
+        </is>
+      </c>
+      <c r="D125" s="28" t="inlineStr">
+        <is>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G125" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H125" s="14" t="n">
-        <v>20</v>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G125" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="126" ht="28" customHeight="1">
@@ -6703,31 +6703,31 @@
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
-        </is>
-      </c>
-      <c r="D126" s="29" t="inlineStr">
-        <is>
-          <t>违约概率（PD）建模</t>
+          <t>F11-03</t>
+        </is>
+      </c>
+      <c r="D126" s="28" t="inlineStr">
+        <is>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G126" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H126" s="14" t="n">
-        <v>40</v>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G126" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H126" s="13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="127" ht="28" customHeight="1">
@@ -6743,78 +6743,78 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
+          <t>F11-04</t>
+        </is>
+      </c>
+      <c r="D127" s="28" t="inlineStr">
+        <is>
+          <t>违约概率（PD）建模</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G127" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H127" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="128" ht="28" customHeight="1">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C128" s="10" t="inlineStr">
+        <is>
           <t>F11-05</t>
         </is>
       </c>
-      <c r="D127" s="29" t="inlineStr">
+      <c r="D128" s="28" t="inlineStr">
         <is>
           <t>集中度限额管理</t>
         </is>
       </c>
-      <c r="E127" s="11" t="inlineStr">
+      <c r="E128" s="11" t="inlineStr">
         <is>
           <t>行业/发行人/评级集中度多维限额，超限预警</t>
         </is>
       </c>
-      <c r="F127" s="11" t="inlineStr">
+      <c r="F128" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G127" s="25" t="inlineStr">
+      <c r="G128" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H127" s="14" t="n">
+      <c r="H128" s="13" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="28" t="inlineStr">
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="27" t="inlineStr">
         <is>
           <t>【P2】 数据管理/行情平台  (Market Data Platform)</t>
         </is>
-      </c>
-    </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>数据管理/行情平台</t>
-        </is>
-      </c>
-      <c r="B129" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
-        <is>
-          <t>F12-01</t>
-        </is>
-      </c>
-      <c r="D129" s="29" t="inlineStr">
-        <is>
-          <t>多源行情聚合</t>
-        </is>
-      </c>
-      <c r="E129" s="11" t="inlineStr">
-        <is>
-          <t>Bloomberg/Wind/中汇信/Refinitiv多源融合，冲突解析</t>
-        </is>
-      </c>
-      <c r="F129" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G129" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H129" s="14" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="130" ht="28" customHeight="1">
@@ -6830,31 +6830,31 @@
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
-        </is>
-      </c>
-      <c r="D130" s="29" t="inlineStr">
-        <is>
-          <t>数据质量校验</t>
+          <t>F12-01</t>
+        </is>
+      </c>
+      <c r="D130" s="28" t="inlineStr">
+        <is>
+          <t>多源行情聚合</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>异常值/缺失值/跳价自动检测，修复建议与人工审核</t>
+          <t>Bloomberg/Wind/中汇信/Refinitiv多源融合，冲突解析</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G130" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H130" s="14" t="n">
-        <v>15</v>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G130" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H130" s="13" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="131" ht="28" customHeight="1">
@@ -6870,31 +6870,31 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
-        </is>
-      </c>
-      <c r="D131" s="29" t="inlineStr">
-        <is>
-          <t>历史数据仓库</t>
+          <t>F12-02</t>
+        </is>
+      </c>
+      <c r="D131" s="28" t="inlineStr">
+        <is>
+          <t>数据质量校验</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>Tick/日频历史行情存储，高效查询（ClickHouse/TimescaleDB）</t>
+          <t>异常值/缺失值/跳价自动检测，修复建议与人工审核</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G131" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H131" s="14" t="n">
-        <v>25</v>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G131" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1">
@@ -6910,17 +6910,17 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
-        </is>
-      </c>
-      <c r="D132" s="29" t="inlineStr">
-        <is>
-          <t>收益率曲线发布</t>
+          <t>F12-03</t>
+        </is>
+      </c>
+      <c r="D132" s="28" t="inlineStr">
+        <is>
+          <t>历史数据仓库</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>国债/政策行/高等级信用曲线实时发布，Kafka广播</t>
+          <t>Tick/日频历史行情存储，高效查询（ClickHouse/TimescaleDB）</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
@@ -6933,8 +6933,8 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H132" s="14" t="n">
-        <v>20</v>
+      <c r="H132" s="13" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="133" ht="28" customHeight="1">
@@ -6950,78 +6950,78 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
+          <t>F12-04</t>
+        </is>
+      </c>
+      <c r="D133" s="28" t="inlineStr">
+        <is>
+          <t>收益率曲线发布</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>国债/政策行/高等级信用曲线实时发布，Kafka广播</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G133" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>数据管理/行情平台</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C134" s="10" t="inlineStr">
+        <is>
           <t>F12-05</t>
         </is>
       </c>
-      <c r="D133" s="29" t="inlineStr">
+      <c r="D134" s="28" t="inlineStr">
         <is>
           <t>估值价格服务</t>
         </is>
       </c>
-      <c r="E133" s="11" t="inlineStr">
+      <c r="E134" s="11" t="inlineStr">
         <is>
           <t>非活跃债券估值价格（中债估值基准），API接口提供</t>
         </is>
       </c>
-      <c r="F133" s="11" t="inlineStr">
+      <c r="F134" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G133" s="25" t="inlineStr">
+      <c r="G134" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H133" s="14" t="n">
+      <c r="H134" s="13" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="28" t="inlineStr">
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="27" t="inlineStr">
         <is>
           <t>【P2】 交易对手管理  (Counterparty Management)</t>
         </is>
-      </c>
-    </row>
-    <row r="135" ht="28" customHeight="1">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t>交易对手管理</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>F13-01</t>
-        </is>
-      </c>
-      <c r="D135" s="29" t="inlineStr">
-        <is>
-          <t>对手方评级与审批</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="inlineStr">
-        <is>
-          <t>内部信用评级模型，新增/变更交易对手审批流</t>
-        </is>
-      </c>
-      <c r="F135" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G135" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H135" s="14" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
@@ -7037,31 +7037,31 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
-        </is>
-      </c>
-      <c r="D136" s="29" t="inlineStr">
-        <is>
-          <t>实时敞口聚合</t>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D136" s="28" t="inlineStr">
+        <is>
+          <t>对手方评级与审批</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>跨产品交易对手名义/MtM敞口实时聚合，压力敞口（EPE）</t>
+          <t>内部信用评级模型，新增/变更交易对手审批流</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G136" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H136" s="14" t="n">
-        <v>35</v>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G136" s="25" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H136" s="13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="137" ht="28" customHeight="1">
@@ -7077,17 +7077,17 @@
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
-        </is>
-      </c>
-      <c r="D137" s="29" t="inlineStr">
-        <is>
-          <t>ISDA/CSA协议管理</t>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D137" s="28" t="inlineStr">
+        <is>
+          <t>实时敞口聚合</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>主协议文档管理，净额结算协议（Netting Set）配置</t>
+          <t>跨产品交易对手名义/MtM敞口实时聚合，压力敞口（EPE）</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr">
@@ -7100,8 +7100,8 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H137" s="14" t="n">
-        <v>25</v>
+      <c r="H137" s="13" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
@@ -7117,31 +7117,31 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
-        </is>
-      </c>
-      <c r="D138" s="29" t="inlineStr">
-        <is>
-          <t>CVA/DVA/FVA计算</t>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D138" s="28" t="inlineStr">
+        <is>
+          <t>ISDA/CSA协议管理</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>信用/债务/资金估值调整实时估算，敞口报告</t>
+          <t>主协议文档管理，净额结算协议（Netting Set）配置</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G138" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H138" s="14" t="n">
-        <v>40</v>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H138" s="13" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="139" ht="28" customHeight="1">
@@ -7157,78 +7157,78 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D139" s="28" t="inlineStr">
+        <is>
+          <t>CVA/DVA/FVA计算</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="inlineStr">
+        <is>
+          <t>信用/债务/资金估值调整实时估算，敞口报告</t>
+        </is>
+      </c>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G139" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H139" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="140" ht="28" customHeight="1">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>交易对手管理</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
           <t>F13-05</t>
         </is>
       </c>
-      <c r="D139" s="29" t="inlineStr">
+      <c r="D140" s="28" t="inlineStr">
         <is>
           <t>集中度与限额</t>
         </is>
       </c>
-      <c r="E139" s="11" t="inlineStr">
+      <c r="E140" s="11" t="inlineStr">
         <is>
           <t>对手方/集团合并敞口限额，超限审批与记录</t>
         </is>
       </c>
-      <c r="F139" s="11" t="inlineStr">
+      <c r="F140" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G139" s="25" t="inlineStr">
+      <c r="G140" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H139" s="14" t="n">
+      <c r="H140" s="13" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="28" t="inlineStr">
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="27" t="inlineStr">
         <is>
           <t>【P2】 清算结算后台  (Clearing &amp; Settlement)</t>
         </is>
-      </c>
-    </row>
-    <row r="141" ht="28" customHeight="1">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t>清算结算后台</t>
-        </is>
-      </c>
-      <c r="B141" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
-        <is>
-          <t>F14-01</t>
-        </is>
-      </c>
-      <c r="D141" s="29" t="inlineStr">
-        <is>
-          <t>DVP/FOP指令生成</t>
-        </is>
-      </c>
-      <c r="E141" s="11" t="inlineStr">
-        <is>
-          <t>成交后自动生成交割指令，批量/单笔支持</t>
-        </is>
-      </c>
-      <c r="F141" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G141" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H141" s="14" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="142" ht="28" customHeight="1">
@@ -7244,31 +7244,31 @@
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>F14-02</t>
-        </is>
-      </c>
-      <c r="D142" s="29" t="inlineStr">
-        <is>
-          <t>中登/中债登接口</t>
+          <t>F14-01</t>
+        </is>
+      </c>
+      <c r="D142" s="28" t="inlineStr">
+        <is>
+          <t>DVP/FOP指令生成</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>银行间债券（中债登）和交易所债券（中登）接口对接</t>
+          <t>成交后自动生成交割指令，批量/单笔支持</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G142" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H142" s="14" t="n">
-        <v>40</v>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G142" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H142" s="13" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="143" ht="28" customHeight="1">
@@ -7284,31 +7284,31 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>F14-03</t>
-        </is>
-      </c>
-      <c r="D143" s="29" t="inlineStr">
-        <is>
-          <t>待交割明细管理</t>
+          <t>F14-02</t>
+        </is>
+      </c>
+      <c r="D143" s="28" t="inlineStr">
+        <is>
+          <t>中登/中债登接口</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>T+0/T+1待交割跟踪，提前预警可能失败交割</t>
+          <t>银行间债券（中债登）和交易所债券（中登）接口对接</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G143" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H143" s="14" t="n">
-        <v>25</v>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G143" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H143" s="13" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="144" ht="28" customHeight="1">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>F14-04</t>
-        </is>
-      </c>
-      <c r="D144" s="29" t="inlineStr">
-        <is>
-          <t>资金调拨确认</t>
+          <t>F14-03</t>
+        </is>
+      </c>
+      <c r="D144" s="28" t="inlineStr">
+        <is>
+          <t>待交割明细管理</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>资金划拨指令生成，银行资金头寸确认，轧差净额</t>
+          <t>T+0/T+1待交割跟踪，提前预警可能失败交割</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr">
@@ -7347,7 +7347,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H144" s="14" t="n">
+      <c r="H144" s="13" t="n">
         <v>25</v>
       </c>
     </row>
@@ -7364,78 +7364,78 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
+          <t>F14-04</t>
+        </is>
+      </c>
+      <c r="D145" s="28" t="inlineStr">
+        <is>
+          <t>资金调拨确认</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>资金划拨指令生成，银行资金头寸确认，轧差净额</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G145" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H145" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>清算结算后台</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
           <t>F14-05</t>
         </is>
       </c>
-      <c r="D145" s="29" t="inlineStr">
+      <c r="D146" s="28" t="inlineStr">
         <is>
           <t>交割失败处理</t>
         </is>
       </c>
-      <c r="E145" s="11" t="inlineStr">
+      <c r="E146" s="11" t="inlineStr">
         <is>
           <t>失败交割自动识别，补交割流程，罚息计算</t>
         </is>
       </c>
-      <c r="F145" s="11" t="inlineStr">
+      <c r="F146" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G145" s="25" t="inlineStr">
+      <c r="G146" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H145" s="14" t="n">
+      <c r="H146" s="13" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="30" t="inlineStr">
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="30" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
-      </c>
-    </row>
-    <row r="147" ht="28" customHeight="1">
-      <c r="A147" s="17" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B147" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>F15-01</t>
-        </is>
-      </c>
-      <c r="D147" s="31" t="inlineStr">
-        <is>
-          <t>双边报价引擎</t>
-        </is>
-      </c>
-      <c r="E147" s="17" t="inlineStr">
-        <is>
-          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
-        </is>
-      </c>
-      <c r="F147" s="17" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G147" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H147" s="19" t="n">
-        <v>70</v>
       </c>
     </row>
     <row r="148" ht="28" customHeight="1">
@@ -7451,17 +7451,17 @@
       </c>
       <c r="C148" s="16" t="inlineStr">
         <is>
-          <t>F15-02</t>
+          <t>F15-01</t>
         </is>
       </c>
       <c r="D148" s="31" t="inlineStr">
         <is>
-          <t>库存风险实时管理</t>
+          <t>双边报价引擎</t>
         </is>
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
       <c r="F148" s="17" t="inlineStr">
@@ -7469,13 +7469,13 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G148" s="27" t="inlineStr">
+      <c r="G148" s="29" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
       <c r="H148" s="19" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="149" ht="28" customHeight="1">
@@ -7491,17 +7491,17 @@
       </c>
       <c r="C149" s="16" t="inlineStr">
         <is>
-          <t>F15-03</t>
+          <t>F15-02</t>
         </is>
       </c>
       <c r="D149" s="31" t="inlineStr">
         <is>
-          <t>报价优化算法</t>
+          <t>库存风险实时管理</t>
         </is>
       </c>
       <c r="E149" s="17" t="inlineStr">
         <is>
-          <t>基于市场微结构理论动态调整bid-ask spread</t>
+          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
       <c r="F149" s="17" t="inlineStr">
@@ -7509,13 +7509,13 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G149" s="27" t="inlineStr">
+      <c r="G149" s="29" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
       <c r="H149" s="19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="150" ht="28" customHeight="1">
@@ -7531,31 +7531,31 @@
       </c>
       <c r="C150" s="16" t="inlineStr">
         <is>
-          <t>F15-04</t>
+          <t>F15-03</t>
         </is>
       </c>
       <c r="D150" s="31" t="inlineStr">
         <is>
-          <t>竞争力分析</t>
+          <t>报价优化算法</t>
         </is>
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>与市场最优报价对比，中签率分析，策略调优</t>
+          <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
       <c r="F150" s="17" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G150" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G150" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H150" s="19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="151" ht="28" customHeight="1">
@@ -7571,78 +7571,78 @@
       </c>
       <c r="C151" s="16" t="inlineStr">
         <is>
+          <t>F15-04</t>
+        </is>
+      </c>
+      <c r="D151" s="31" t="inlineStr">
+        <is>
+          <t>竞争力分析</t>
+        </is>
+      </c>
+      <c r="E151" s="17" t="inlineStr">
+        <is>
+          <t>与市场最优报价对比，中签率分析，策略调优</t>
+        </is>
+      </c>
+      <c r="F151" s="17" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G151" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H151" s="19" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="152" ht="28" customHeight="1">
+      <c r="A152" s="17" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D151" s="31" t="inlineStr">
+      <c r="D152" s="31" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E151" s="17" t="inlineStr">
+      <c r="E152" s="17" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F151" s="17" t="inlineStr">
+      <c r="F152" s="17" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G151" s="25" t="inlineStr">
+      <c r="G152" s="25" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H151" s="19" t="n">
+      <c r="H152" s="19" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="152" ht="20" customHeight="1">
-      <c r="A152" s="30" t="inlineStr">
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="30" t="inlineStr">
         <is>
           <t>【P3】 外汇/外汇衍生品  (FX &amp; FX Derivatives)</t>
         </is>
-      </c>
-    </row>
-    <row r="153" ht="28" customHeight="1">
-      <c r="A153" s="17" t="inlineStr">
-        <is>
-          <t>外汇/外汇衍生品</t>
-        </is>
-      </c>
-      <c r="B153" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C153" s="16" t="inlineStr">
-        <is>
-          <t>F16-01</t>
-        </is>
-      </c>
-      <c r="D153" s="31" t="inlineStr">
-        <is>
-          <t>即期/远期报价</t>
-        </is>
-      </c>
-      <c r="E153" s="17" t="inlineStr">
-        <is>
-          <t>USD/CNY等主要货币对即期汇率+远期点数报价</t>
-        </is>
-      </c>
-      <c r="F153" s="17" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G153" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H153" s="19" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="154" ht="28" customHeight="1">
@@ -7658,31 +7658,31 @@
       </c>
       <c r="C154" s="16" t="inlineStr">
         <is>
-          <t>F16-02</t>
+          <t>F16-01</t>
         </is>
       </c>
       <c r="D154" s="31" t="inlineStr">
         <is>
-          <t>外汇期权（FXO）</t>
+          <t>即期/远期报价</t>
         </is>
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>欧式/美式FXO定价（Garman-Kohlhagen），Greeks</t>
+          <t>USD/CNY等主要货币对即期汇率+远期点数报价</t>
         </is>
       </c>
       <c r="F154" s="17" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G154" s="27" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G154" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H154" s="19" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="155" ht="28" customHeight="1">
@@ -7698,17 +7698,17 @@
       </c>
       <c r="C155" s="16" t="inlineStr">
         <is>
-          <t>F16-03</t>
+          <t>F16-02</t>
         </is>
       </c>
       <c r="D155" s="31" t="inlineStr">
         <is>
-          <t>NDF/NDO定价</t>
+          <t>外汇期权（FXO）</t>
         </is>
       </c>
       <c r="E155" s="17" t="inlineStr">
         <is>
-          <t>不可交割远期/期权定价，境外对手对接</t>
+          <t>欧式/美式FXO定价（Garman-Kohlhagen），Greeks</t>
         </is>
       </c>
       <c r="F155" s="17" t="inlineStr">
@@ -7716,13 +7716,13 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G155" s="27" t="inlineStr">
+      <c r="G155" s="29" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
       <c r="H155" s="19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="156" ht="28" customHeight="1">
@@ -7738,31 +7738,31 @@
       </c>
       <c r="C156" s="16" t="inlineStr">
         <is>
-          <t>F16-04</t>
+          <t>F16-03</t>
         </is>
       </c>
       <c r="D156" s="31" t="inlineStr">
         <is>
-          <t>跨货币敞口汇总</t>
+          <t>NDF/NDO定价</t>
         </is>
       </c>
       <c r="E156" s="17" t="inlineStr">
         <is>
-          <t>多币种资产折算人民币敞口，汇率风险VaR</t>
+          <t>不可交割远期/期权定价，境外对手对接</t>
         </is>
       </c>
       <c r="F156" s="17" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G156" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G156" s="29" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H156" s="19" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="157" ht="28" customHeight="1">
@@ -7778,64 +7778,104 @@
       </c>
       <c r="C157" s="16" t="inlineStr">
         <is>
+          <t>F16-04</t>
+        </is>
+      </c>
+      <c r="D157" s="31" t="inlineStr">
+        <is>
+          <t>跨货币敞口汇总</t>
+        </is>
+      </c>
+      <c r="E157" s="17" t="inlineStr">
+        <is>
+          <t>多币种资产折算人民币敞口，汇率风险VaR</t>
+        </is>
+      </c>
+      <c r="F157" s="17" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G157" s="24" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H157" s="19" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="158" ht="28" customHeight="1">
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t>外汇/外汇衍生品</t>
+        </is>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C158" s="16" t="inlineStr">
+        <is>
           <t>F16-05</t>
         </is>
       </c>
-      <c r="D157" s="31" t="inlineStr">
+      <c r="D158" s="31" t="inlineStr">
         <is>
           <t>CFETS/外汇局接口</t>
         </is>
       </c>
-      <c r="E157" s="17" t="inlineStr">
+      <c r="E158" s="17" t="inlineStr">
         <is>
           <t>银行间外汇市场CFETS接口，外汇局合规报送</t>
         </is>
       </c>
-      <c r="F157" s="17" t="inlineStr">
+      <c r="F158" s="17" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G157" s="24" t="inlineStr">
+      <c r="G158" s="24" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H157" s="19" t="n">
+      <c r="H158" s="19" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="20" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="20" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H158" s="21">
-        <f>SUM(H3:H157)</f>
+      <c r="H159" s="21">
+        <f>SUM(H3:H158)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A146:H146"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A80:H80"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A122:H122"/>
-    <mergeCell ref="A140:H140"/>
-    <mergeCell ref="A109:H109"/>
-    <mergeCell ref="A134:H134"/>
-    <mergeCell ref="A158:G158"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A152:H152"/>
-    <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="A153:H153"/>
+    <mergeCell ref="A159:G159"/>
+    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A147:H147"/>
+    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A117:H117"/>
+    <mergeCell ref="A141:H141"/>
     <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A116:H116"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A79:H79"/>
+    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A123:H123"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A135:H135"/>
+    <mergeCell ref="A74:H74"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7908,54 +7948,54 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>招募(人)</t>
         </is>
       </c>
-      <c r="D3" s="27" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>工期(月)</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>人月</t>
         </is>
       </c>
-      <c r="F3" s="27" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>招募(人)</t>
         </is>
       </c>
-      <c r="G3" s="27" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t>工期(月)</t>
         </is>
       </c>
-      <c r="H3" s="27" t="inlineStr">
+      <c r="H3" s="29" t="inlineStr">
         <is>
           <t>人月</t>
         </is>
       </c>
-      <c r="I3" s="27" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t>招募(人)</t>
         </is>
       </c>
-      <c r="J3" s="27" t="inlineStr">
+      <c r="J3" s="29" t="inlineStr">
         <is>
           <t>工期(月)</t>
         </is>
       </c>
-      <c r="K3" s="27" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t>人月</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>FICC业务架构师
 FICC Business Architect</t>
@@ -7966,7 +8006,7 @@
           <t>负责各模块业务需求与架构设计，需有银行间/衍生品经验</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="10" t="n">
@@ -7976,7 +8016,7 @@
         <f>C4*D4</f>
         <v/>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="13" t="n">
         <v>2</v>
       </c>
       <c r="G4" s="10" t="n">
@@ -7986,7 +8026,7 @@
         <f>F4*G4</f>
         <v/>
       </c>
-      <c r="I4" s="14" t="n">
+      <c r="I4" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="10" t="n">
@@ -8049,7 +8089,7 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>量化研究员
 Quant Researcher</t>
@@ -8060,7 +8100,7 @@
           <t>定价模型、风险计量、因子模型，Python/C++</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="13" t="n">
         <v>6</v>
       </c>
       <c r="D6" s="10" t="n">
@@ -8070,7 +8110,7 @@
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="13" t="n">
         <v>8</v>
       </c>
       <c r="G6" s="10" t="n">
@@ -8080,7 +8120,7 @@
         <f>F6*G6</f>
         <v/>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="13" t="n">
         <v>4</v>
       </c>
       <c r="J6" s="10" t="n">
@@ -8096,7 +8136,7 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>前端研发工程师
 Frontend Engineer</t>
@@ -8107,7 +8147,7 @@
           <t>交易终端UI，React/Vue，实时数据展示</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="13" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="10" t="n">
@@ -8117,7 +8157,7 @@
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="13" t="n">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="n">
@@ -8127,7 +8167,7 @@
         <f>F7*G7</f>
         <v/>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="13" t="n">
         <v>3</v>
       </c>
       <c r="J7" s="10" t="n">
@@ -8143,7 +8183,7 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>数据工程师
 Data Engineer</t>
@@ -8154,7 +8194,7 @@
           <t>行情接入、数据管道、历史数据仓库</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="10" t="n">
@@ -8164,7 +8204,7 @@
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="13" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="n">
@@ -8174,7 +8214,7 @@
         <f>F8*G8</f>
         <v/>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J8" s="10" t="n">
@@ -8190,7 +8230,7 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>测试工程师
 QA Engineer</t>
@@ -8201,7 +8241,7 @@
           <t>自动化测试，压测，合规验证</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="13" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="10" t="n">
@@ -8211,7 +8251,7 @@
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="13" t="n">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="n">
@@ -8221,7 +8261,7 @@
         <f>F9*G9</f>
         <v/>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="13" t="n">
         <v>3</v>
       </c>
       <c r="J9" s="10" t="n">
@@ -8237,7 +8277,7 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>产品经理/BA
 Product Manager / BA</t>
@@ -8248,7 +8288,7 @@
           <t>需求梳理、验收标准、客户沟通</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="13" t="n">
         <v>3</v>
       </c>
       <c r="D10" s="10" t="n">
@@ -8258,7 +8298,7 @@
         <f>C10*D10</f>
         <v/>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="13" t="n">
         <v>3</v>
       </c>
       <c r="G10" s="10" t="n">
@@ -8268,7 +8308,7 @@
         <f>F10*G10</f>
         <v/>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="10" t="n">
@@ -8284,7 +8324,7 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>DevOps/基础设施
 DevOps / Infra</t>
@@ -8295,7 +8335,7 @@
           <t>信创部署、K8s、监控告警体系</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="13" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="10" t="n">
@@ -8305,7 +8345,7 @@
         <f>C11*D11</f>
         <v/>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="13" t="n">
         <v>3</v>
       </c>
       <c r="G11" s="10" t="n">
@@ -8315,7 +8355,7 @@
         <f>F11*G11</f>
         <v/>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="13" t="n">
         <v>2</v>
       </c>
       <c r="J11" s="10" t="n">
@@ -8331,7 +8371,7 @@
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>安全合规专家
 Security &amp; Compliance</t>
@@ -8342,7 +8382,7 @@
           <t>合规规则库维护，监管报送，数据安全</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="10" t="n">
@@ -8352,7 +8392,7 @@
         <f>C12*D12</f>
         <v/>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="13" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="10" t="n">
@@ -8362,7 +8402,7 @@
         <f>F12*G12</f>
         <v/>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="13" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="10" t="n">
@@ -8435,7 +8475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8704,7 +8744,7 @@
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>5. 回购管理</t>
+          <t>5. FICC风险计量平台</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -8714,187 +8754,139 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>上线：正回购全周期，质押替换</t>
+          <t>上线：VaR/压测，监管格式报告</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>某券商质押式回购融资管理</t>
+          <t>某券商FICC组合风险日报</t>
         </is>
       </c>
       <c r="E7" s="37" t="inlineStr">
         <is>
-          <t>中登/上清所接口联调</t>
+          <t>模型精度vs衡泰基准</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>建立完整沙箱测试套件</t>
+          <t>首期仅VaR/ES，CVA后置</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>交易系统组</t>
+          <t>风控平台组</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>与现券交易捆绑，提升粘性</t>
+          <t>直接替代衡泰，高溢价定价</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>6. FICC风险计量平台</t>
+          <t>6. 组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>上线：VaR/压测，监管格式报告</t>
+          <t>上线：Brinson归因，周报自动生成</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>某券商FICC组合风险日报</t>
+          <t>资管公司固收组合绩效分析</t>
         </is>
       </c>
       <c r="E8" s="37" t="inlineStr">
         <is>
-          <t>模型精度vs衡泰基准</t>
+          <t>Brinson模型精度验证</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>首期仅VaR/ES，CVA后置</t>
+          <t>对标Bloomberg绩效分析基准</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>风控平台组</t>
+          <t>投资管理组</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>直接替代衡泰，高溢价定价</t>
+          <t>高端客户差异化，替代SimCorp/衡泰</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>7. 组合管理+绩效归因</t>
+          <t>7. 策略投资/量化</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>上线：Brinson归因，周报自动生成</t>
+          <t>上线：回测引擎，3个策略实盘验证</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>资管公司固收组合绩效分析</t>
+          <t>自营量化部门策略回测平台</t>
         </is>
       </c>
       <c r="E9" s="37" t="inlineStr">
         <is>
-          <t>Brinson模型精度验证</t>
+          <t>Tick回测数据质量</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>对标Bloomberg绩效分析基准</t>
+          <t>先与AMD行情平台深度整合</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>投资管理组</t>
+          <t>量化研究组</t>
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>12</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>高端客户差异化，替代SimCorp/衡泰</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>8. 策略投资/量化</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>上线：回测引擎，3个策略实盘验证</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>自营量化部门策略回测平台</t>
-        </is>
-      </c>
-      <c r="E10" s="37" t="inlineStr">
-        <is>
-          <t>Tick回测数据质量</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>先与AMD行情平台深度整合</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>量化研究组</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
           <t>高壁垒护城河，未来SaaS化</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="38" t="inlineStr">
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>P1阶段战略重心：① 快赢先行（异常风控+事前合规M1并行，6个月见成果）  ② 主干平行（IBOR+现券M2启动，建立账薄主干）  ③ 差异化（量化策略+绩效归因M4-M5，构建高壁垒能力）  ④ 替代衡泰（FICC风险计量M3启动，以信创+精度优势直攻垄断盲区）</t>
         </is>
@@ -8903,7 +8895,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8940,7 +8932,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="40" t="inlineStr">
         <is>
-          <t>战略定位：整个FICC平台的账薄主干，27项功能覆盖持仓/现金/估值/事件/对账/合规/试算全链路   |   数据输入：交易指令数据 / 行情/估值数据 / 资产主数据 / 托管行结算通知   |   量化底座：账户体系(AMI/AMDB) · Kafka实时消息 · Redis分布式缓存</t>
+          <t>战略定位：整个FICC平台的账薄主干，27项功能覆盖持仓/现金/估值/事件/对账/合规/试算全链路   |   来源：Slide 55   |   数据输入：交易指令数据 / 行情/估值数据 / 资产主数据 / 托管行结算通知   |   量化底座：账户体系(AMI/AMDB) · Kafka实时消息 · Redis分布式缓存</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9197,7 @@
           <t>F01-27</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
         <is>
           <t>资产打标与组合树管理</t>
         </is>
@@ -9230,7 +9222,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="13" t="n">
         <v>20</v>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -9350,7 +9342,7 @@
           <t>F01-07</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>多币种资金管理</t>
         </is>
@@ -9375,7 +9367,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="13" t="n">
         <v>20</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -9640,7 +9632,7 @@
           <t>F01-13</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>公司行为通知</t>
         </is>
@@ -9665,7 +9657,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="13" t="n">
         <v>20</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -10365,7 +10357,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="40" t="inlineStr">
         <is>
-          <t>战略定位：银行间+交易所双市场统一订单模型，28项功能覆盖报价/订单/定价/风控/STP/做市/数据/分析全链路   |   数据输入：CFETS/X-Bond行情与成交回报 / 上交所/深交所债券接口回报 / AMD/Bloomberg实时行情 / 中债估值曲线   |   量化底座：ATP报盘引擎 · IBOR持仓账薄 · 事前风控/合规系统 · 清算结算后台</t>
+          <t>战略定位：银行间+交易所双市场统一订单模型，28项功能覆盖报价/订单/定价/风控/STP/做市/数据/分析全链路   |   来源：Slide 40   |   数据输入：CFETS/X-Bond行情与成交回报 / 上交所/深交所债券接口回报 / AMD/Bloomberg实时行情 / 中债估值曲线   |   量化底座：ATP报盘引擎 · IBOR持仓账薄 · 事前风控/合规系统 · 清算结算后台</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10576,7 @@
           <t>F02-08</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t>Bond Connect跨境接入</t>
         </is>
@@ -10609,7 +10601,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="13" t="n">
         <v>40</v>
       </c>
       <c r="I9" s="12" t="inlineStr">
@@ -10775,7 +10767,7 @@
           <t>F02-12</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t>条件单与算法单接口</t>
         </is>
@@ -10800,7 +10792,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="13" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -11111,7 +11103,7 @@
           <t>F02-17</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" s="28" t="inlineStr">
         <is>
           <t>流动性与市场影响评估</t>
         </is>
@@ -11136,7 +11128,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="H23" s="13" t="n">
         <v>20</v>
       </c>
       <c r="I23" s="12" t="inlineStr">
@@ -11302,7 +11294,7 @@
           <t>F02-20</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>跨市场净额轧差</t>
         </is>
@@ -11327,7 +11319,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="13" t="n">
         <v>20</v>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -11355,7 +11347,7 @@
           <t>F02-06</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>做市报价接口</t>
         </is>
@@ -11380,7 +11372,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="H30" s="13" t="n">
         <v>10</v>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -11401,7 +11393,7 @@
           <t>F02-21</t>
         </is>
       </c>
-      <c r="C31" s="29" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>库存管理与头寸监控</t>
         </is>
@@ -11426,7 +11418,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H31" s="14" t="n">
+      <c r="H31" s="13" t="n">
         <v>20</v>
       </c>
       <c r="I31" s="12" t="inlineStr">
@@ -11447,7 +11439,7 @@
           <t>F02-22</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>报价P&amp;L归因</t>
         </is>
@@ -11472,7 +11464,7 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H32" s="14" t="n">
+      <c r="H32" s="13" t="n">
         <v>20</v>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -11645,7 +11637,7 @@
           <t>F02-26</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>交易执行质量分析(TCA)</t>
         </is>
@@ -11670,7 +11662,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H38" s="14" t="n">
+      <c r="H38" s="13" t="n">
         <v>25</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -11737,7 +11729,7 @@
           <t>F02-28</t>
         </is>
       </c>
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C40" s="28" t="inlineStr">
         <is>
           <t>交易统计分析</t>
         </is>
@@ -11762,7 +11754,7 @@
           <t>低</t>
         </is>
       </c>
-      <c r="H40" s="14" t="n">
+      <c r="H40" s="13" t="n">
         <v>15</v>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -12398,7 +12390,7 @@
           <t>F07-11</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="28" t="inlineStr">
         <is>
           <t>资产配置策略分析</t>
         </is>
@@ -12423,7 +12415,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="H19" s="13" t="n">
         <v>40</v>
       </c>
       <c r="I19" s="12" t="inlineStr">
@@ -12444,7 +12436,7 @@
           <t>F07-12</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>固收+策略分析</t>
         </is>
@@ -12469,7 +12461,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="13" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -12490,7 +12482,7 @@
           <t>F07-13</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>量化策略组合分析</t>
         </is>
@@ -12515,7 +12507,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H21" s="14" t="n">
+      <c r="H21" s="13" t="n">
         <v>35</v>
       </c>
       <c r="I21" s="12" t="inlineStr">
@@ -12596,7 +12588,7 @@
           <t>F07-15</t>
         </is>
       </c>
-      <c r="C25" s="29" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>定价计算集成</t>
         </is>
@@ -12621,7 +12613,7 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H25" s="13" t="n">
         <v>20</v>
       </c>
       <c r="I25" s="12" t="inlineStr">

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -272,9 +272,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -730,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1445,12 +1442,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>量化定价引擎</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Quant Pricing Engine</t>
+          <t>Pricing Platform</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1519,17 +1516,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>利率衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Interest Rate Derivatives</t>
+          <t>Sales Trading</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>前台交易</t>
+          <t>客需业务</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -1539,12 +1536,12 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -1557,33 +1554,33 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr">
-        <is>
-          <t>大</t>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>Murex/衡泰</t>
+          <t>金证/顶点</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>无直接基础</t>
+          <t>现券交易系统/IBOR</t>
         </is>
       </c>
       <c r="M12" s="10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>IRS/OIS/CCS，需专业量化团队</t>
+          <t>面向对客服务的销售交易工作台，报价聚合、智能推荐、交易执行一体化；对应PPT Slide 47</t>
         </is>
       </c>
     </row>
@@ -1667,17 +1664,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Market Data Platform</t>
+          <t>Investment Advisory</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>基础数据</t>
+          <t>客需业务</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -1687,51 +1684,51 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>★★★☆☆</t>
+          <t>★★☆☆☆</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>L4</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>小</t>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>Bloomberg/Wind</t>
+          <t>衡泰/金证</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>AMD行情平台</t>
+          <t>IBOR持仓账薄</t>
         </is>
       </c>
       <c r="M14" s="10" t="n">
         <v>4</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
-          <t>多源聚合+估值价格发布，赋能其他模块</t>
+          <t>全链条数字化债券投顾服务，覆盖投资建议、账户分析、投研报告；对应PPT Slide 48</t>
         </is>
       </c>
     </row>
@@ -1741,17 +1738,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>TRS收益互换</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Counterparty Management</t>
+          <t>Total Return Swap</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>中台信用</t>
+          <t>客需业务</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -1761,7 +1758,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -1779,277 +1776,129 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
-        <is>
-          <t>中大</t>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>衡泰/专项系统</t>
+          <t>衡泰/森浦(STC)</t>
         </is>
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>ARC信用模块</t>
+          <t>现券交易系统/IBOR</t>
         </is>
       </c>
       <c r="M15" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>ISDA/CSA管理+CVA/DVA计算</t>
+          <t>场外衍生品主经纪商客需服务，覆盖TRS交易端/客户端/管理端及自动对冲；对应PPT Slide 49</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>清算结算后台</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Clearing &amp; Settlement</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>后台运营</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>★★★★☆</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="A16" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Market Making</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>前台做市</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>★★★☆☆</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>L0</t>
+        </is>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>金证/中台</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>ACP清算平台</t>
-        </is>
-      </c>
-      <c r="M16" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="O16" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="P16" s="11" t="inlineStr">
-        <is>
-          <t>DVP/FOP+中登中债登接口</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Market Making</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>前台做市</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>L0</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="K17" s="17" t="inlineStr">
+      <c r="K16" s="16" t="inlineStr">
         <is>
           <t>Murex/专项</t>
         </is>
       </c>
-      <c r="L17" s="17" t="inlineStr">
+      <c r="L16" s="16" t="inlineStr">
         <is>
           <t>ATP报价接口</t>
         </is>
       </c>
-      <c r="M17" s="16" t="n">
+      <c r="M16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="N17" s="16" t="n">
+      <c r="N16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="O17" s="19" t="n">
+      <c r="O16" s="18" t="n">
         <v>120</v>
       </c>
-      <c r="P17" s="17" t="inlineStr">
+      <c r="P16" s="16" t="inlineStr">
         <is>
           <t>双边报价引擎，需深度市场经验</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>外汇/外汇衍生品</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>FX &amp; FX Derivatives</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>前台交易</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>★★★★★</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>L0</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>大</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>Murex/Bloomberg</t>
-        </is>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="M18" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="N18" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="O18" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="P18" s="17" t="inlineStr">
-        <is>
-          <t>FX/NDF市场门槛极高，建议Phase 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>合计 / Totals</t>
         </is>
       </c>
-      <c r="M19" s="21">
-        <f>SUM(M3:M18)</f>
+      <c r="M17" s="20">
+        <f>SUM(M3:M16)</f>
         <v/>
       </c>
-      <c r="N19" s="21">
-        <f>MAX(N3:N18)</f>
+      <c r="N17" s="20">
+        <f>MAX(N3:N16)</f>
         <v/>
       </c>
-      <c r="O19" s="21">
-        <f>SUM(O3:O18)</f>
+      <c r="O17" s="20">
+        <f>SUM(O3:O16)</f>
         <v/>
       </c>
-      <c r="P19" s="22" t="inlineStr">
+      <c r="P17" s="21" t="inlineStr">
         <is>
           <t>P1: 8模块(6项快赢+2项核心)  |  P2: 6模块  |  P3: 2模块</t>
         </is>
@@ -2057,8 +1906,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A19:L19"/>
     <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A17:L17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -2071,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2134,7 +1983,7 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>【P1】 IBOR投资账薄管理  (IBOR)</t>
         </is>
@@ -2171,7 +2020,7 @@
           <t>持仓更新延迟&lt;500ms，全品种覆盖率100%</t>
         </is>
       </c>
-      <c r="G4" s="24" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2211,7 +2060,7 @@
           <t>层级汇总数据与单账户加总误差为零</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2251,7 +2100,7 @@
           <t>T0/T1持仓差=未交割敞口，自动核验通过率&gt;99%</t>
         </is>
       </c>
-      <c r="G6" s="25" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2291,7 +2140,7 @@
           <t>可用量计算误差为零，冻结事件&lt;30s生效</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2331,7 +2180,7 @@
           <t>标签体系支持≥10维度，组合树层级≥4级，标签变更&lt;1min生效影响所有聚合视图</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2371,7 +2220,7 @@
           <t>现金余额与银行回单误差为零，日中更新频率≥每分钟</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2411,7 +2260,7 @@
           <t>7日现金流预测准确率&gt;95%，流动性预警提前24h触发</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2451,7 +2300,7 @@
           <t>多币种折算汇率误差&lt;0.01%，轧差结果实时刷新</t>
         </is>
       </c>
-      <c r="G11" s="25" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2491,7 +2340,7 @@
           <t>MtM更新延迟&lt;1s，估值覆盖审批留痕100%</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2531,7 +2380,7 @@
           <t>应计利息与Bloomberg基准误差&lt;0.01元/百元面值</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2571,7 +2420,7 @@
           <t>衍生品MtM与对手方差异&lt;0.5bps，Margin Call触发延迟&lt;5min</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2611,7 +2460,7 @@
           <t>付息/到期处理T+0完成，含权债提前5交易日发起行权提示</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2651,7 +2500,7 @@
           <t>到期回购提前1日预警，续作指令生成成功率&gt;99%</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2691,7 +2540,7 @@
           <t>公司行为推送延迟&lt;30min，影响持仓标注覆盖率100%</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2731,7 +2580,7 @@
           <t>日终对账完成时间&lt;8:00AM，差异识别率100%，自动匹配率&gt;95%</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2771,7 +2620,7 @@
           <t>IBOR-ABOR差异原因分类准确率&gt;98%，日终净值差=0（已结算口径）</t>
         </is>
       </c>
-      <c r="G19" s="25" t="inlineStr">
+      <c r="G19" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2811,7 +2660,7 @@
           <t>交割失败识别延迟&lt;1h，补交割触发成功率&gt;95%</t>
         </is>
       </c>
-      <c r="G20" s="25" t="inlineStr">
+      <c r="G20" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2851,7 +2700,7 @@
           <t>合规检查响应&lt;200ms，零漏报，误报率&lt;0.1%</t>
         </is>
       </c>
-      <c r="G21" s="24" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2891,7 +2740,7 @@
           <t>报送数据与IBOR源数据一致性100%，定时推送准时率&gt;99.9%</t>
         </is>
       </c>
-      <c r="G22" s="25" t="inlineStr">
+      <c r="G22" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2931,7 +2780,7 @@
           <t>行情延迟&lt;1s，数据完整性&gt;99.9%，异常行情自动过滤告警</t>
         </is>
       </c>
-      <c r="G23" s="24" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -2971,7 +2820,7 @@
           <t>成交回报接收延迟&lt;200ms，数据完整性100%，状态机覆盖全交易生命周期</t>
         </is>
       </c>
-      <c r="G24" s="25" t="inlineStr">
+      <c r="G24" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3011,7 +2860,7 @@
           <t>期初持仓加载完成&lt;7:00AM，日间增量延迟&lt;500ms，多源持仓一致性核验通过率&gt;99%</t>
         </is>
       </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3051,7 +2900,7 @@
           <t>历史快照查询任意日期延迟&lt;3s，预测视图覆盖30日前瞻</t>
         </is>
       </c>
-      <c r="G26" s="24" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3091,7 +2940,7 @@
           <t>估值方法配置覆盖全品种，稽核规则命中率&gt;99%，核对差异&lt;0.01%</t>
         </is>
       </c>
-      <c r="G27" s="24" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3131,7 +2980,7 @@
           <t>审批流配置覆盖100%手工操作类型，操作日志不可篡改，审批完成后数据生效&lt;1min</t>
         </is>
       </c>
-      <c r="G28" s="25" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3171,7 +3020,7 @@
           <t>模拟指令生效&lt;2s，试算结果与真实成交后结果误差&lt;0.1%，支持≥10方案并行</t>
         </is>
       </c>
-      <c r="G29" s="24" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3211,7 +3060,7 @@
           <t>支持≥3类情景参数配置，N日预测（N≤30）计算完成&lt;30s</t>
         </is>
       </c>
-      <c r="G30" s="24" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3221,7 +3070,7 @@
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>【P1】 现券交易系统  (Bond Trading System)</t>
         </is>
@@ -3258,7 +3107,7 @@
           <t>报价发出到CFETS确认&lt;200ms，批量报价支持≥100条/次</t>
         </is>
       </c>
-      <c r="G32" s="24" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3298,7 +3147,7 @@
           <t>委托响应&lt;100ms，撤单成功率&gt;99.5%</t>
         </is>
       </c>
-      <c r="G33" s="25" t="inlineStr">
+      <c r="G33" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3338,7 +3187,7 @@
           <t>RFQ全流程(发起到成交)端到端&lt;30s，历史记录保存≥1年</t>
         </is>
       </c>
-      <c r="G34" s="25" t="inlineStr">
+      <c r="G34" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3378,7 +3227,7 @@
           <t>Bond Connect成交回报处理&lt;500ms，SWIFT报文生成准确率100%</t>
         </is>
       </c>
-      <c r="G35" s="24" t="inlineStr">
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3418,7 +3267,7 @@
           <t>订单状态更新延迟&lt;100ms，状态机覆盖全生命周期，历史可回溯≥1年</t>
         </is>
       </c>
-      <c r="G36" s="24" t="inlineStr">
+      <c r="G36" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3458,7 +3307,7 @@
           <t>大宗交易协商流程≤5步确认，拆单执行计划自动生成</t>
         </is>
       </c>
-      <c r="G37" s="25" t="inlineStr">
+      <c r="G37" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3498,7 +3347,7 @@
           <t>篮子交易支持≥50只债券同批，批量下单耗时&lt;5s</t>
         </is>
       </c>
-      <c r="G38" s="25" t="inlineStr">
+      <c r="G38" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3538,7 +3387,7 @@
           <t>条件触发延迟&lt;1s，算法接口支持主流算法交易供应商标准协议</t>
         </is>
       </c>
-      <c r="G39" s="24" t="inlineStr">
+      <c r="G39" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3578,7 +3427,7 @@
           <t>YTM计算与Bloomberg基准误差&lt;0.1bps，含权债定价覆盖主流含权结构</t>
         </is>
       </c>
-      <c r="G40" s="25" t="inlineStr">
+      <c r="G40" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3618,7 +3467,7 @@
           <t>特殊品种覆盖率100%，定价结果与市场成交价偏差统计&lt;5bps</t>
         </is>
       </c>
-      <c r="G41" s="24" t="inlineStr">
+      <c r="G41" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3658,7 +3507,7 @@
           <t>PnL更新延迟&lt;1s，已实现/未实现分拆误差为零</t>
         </is>
       </c>
-      <c r="G42" s="24" t="inlineStr">
+      <c r="G42" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3698,7 +3547,7 @@
           <t>敏感性指标与Bloomberg基准误差&lt;1%，组合汇总更新&lt;2s</t>
         </is>
       </c>
-      <c r="G43" s="25" t="inlineStr">
+      <c r="G43" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3738,7 +3587,7 @@
           <t>风控校验响应&lt;10ms，零漏拦，误报率&lt;0.05%</t>
         </is>
       </c>
-      <c r="G44" s="25" t="inlineStr">
+      <c r="G44" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3778,7 +3627,7 @@
           <t>合规规则覆盖投资授权书100%条款，规则热更新生效&lt;1min</t>
         </is>
       </c>
-      <c r="G45" s="25" t="inlineStr">
+      <c r="G45" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3818,7 +3667,7 @@
           <t>流动性评估结果&lt;500ms，大额阈值可配置，确认记录100%留痕</t>
         </is>
       </c>
-      <c r="G46" s="25" t="inlineStr">
+      <c r="G46" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3858,7 +3707,7 @@
           <t>成交到指令生成延迟&lt;500ms，指令要素完整率100%</t>
         </is>
       </c>
-      <c r="G47" s="24" t="inlineStr">
+      <c r="G47" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3898,7 +3747,7 @@
           <t>STP直通率&gt;98%，异常隔离延迟&lt;1min，人工处理队列可视化</t>
         </is>
       </c>
-      <c r="G48" s="24" t="inlineStr">
+      <c r="G48" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -3938,7 +3787,7 @@
           <t>错单处理T+0完成，审批链≤2级，修正后STP重触发成功率&gt;99%</t>
         </is>
       </c>
-      <c r="G49" s="25" t="inlineStr">
+      <c r="G49" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -3978,7 +3827,7 @@
           <t>净额轧差计算准确率100%，与清算系统差异核对通过率&gt;99.9%</t>
         </is>
       </c>
-      <c r="G50" s="25" t="inlineStr">
+      <c r="G50" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4018,7 +3867,7 @@
           <t>报价刷新延迟&lt;500ms，做市接口符合Module 15做市商系统对接规范</t>
         </is>
       </c>
-      <c r="G51" s="25" t="inlineStr">
+      <c r="G51" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4058,7 +3907,7 @@
           <t>库存监控更新&lt;1s，超限预警触发率100%，暂停报价延迟&lt;500ms</t>
         </is>
       </c>
-      <c r="G52" s="25" t="inlineStr">
+      <c r="G52" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4098,7 +3947,7 @@
           <t>P&amp;L归因覆盖100%做市成交，维度下钻≥4级，日报T+0生成</t>
         </is>
       </c>
-      <c r="G53" s="25" t="inlineStr">
+      <c r="G53" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4138,7 +3987,7 @@
           <t>行情延迟&lt;1s，异常行情自动过滤告警，数据完整性&gt;99.9%</t>
         </is>
       </c>
-      <c r="G54" s="25" t="inlineStr">
+      <c r="G54" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4178,7 +4027,7 @@
           <t>曲线更新延迟&lt;2s，历史曲线回放支持任意交易日，覆盖率100%</t>
         </is>
       </c>
-      <c r="G55" s="25" t="inlineStr">
+      <c r="G55" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4218,7 +4067,7 @@
           <t>新券上市后基础数据就绪&lt;2h，要素同步准确率&gt;99.9%</t>
         </is>
       </c>
-      <c r="G56" s="26" t="inlineStr">
+      <c r="G56" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -4258,7 +4107,7 @@
           <t>TCA覆盖100%成交记录，基准价偏差计算准确，报告T+1生成</t>
         </is>
       </c>
-      <c r="G57" s="24" t="inlineStr">
+      <c r="G57" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4298,7 +4147,7 @@
           <t>报送数据与成交记录一致性100%，定时推送准时率&gt;99.9%，推送失败自动告警重试</t>
         </is>
       </c>
-      <c r="G58" s="25" t="inlineStr">
+      <c r="G58" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4338,7 +4187,7 @@
           <t>统计报表T+1生成，支持≥6个分析维度，Excel导出格式标准</t>
         </is>
       </c>
-      <c r="G59" s="26" t="inlineStr">
+      <c r="G59" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -4348,7 +4197,7 @@
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
+      <c r="A60" s="26" t="inlineStr">
         <is>
           <t>【P2】 FOF投资系统  (FOF Investment System)</t>
         </is>
@@ -4370,7 +4219,7 @@
           <t>F03-01</t>
         </is>
       </c>
-      <c r="D61" s="28" t="inlineStr">
+      <c r="D61" s="27" t="inlineStr">
         <is>
           <t>管理人与基础信息管理</t>
         </is>
@@ -4385,7 +4234,7 @@
           <t>功能测试通过</t>
         </is>
       </c>
-      <c r="G61" s="26" t="inlineStr">
+      <c r="G61" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -4410,7 +4259,7 @@
           <t>F03-02</t>
         </is>
       </c>
-      <c r="D62" s="28" t="inlineStr">
+      <c r="D62" s="27" t="inlineStr">
         <is>
           <t>基金资产信息获取</t>
         </is>
@@ -4425,7 +4274,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G62" s="25" t="inlineStr">
+      <c r="G62" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4450,7 +4299,7 @@
           <t>F03-03</t>
         </is>
       </c>
-      <c r="D63" s="28" t="inlineStr">
+      <c r="D63" s="27" t="inlineStr">
         <is>
           <t>交易录入与审核</t>
         </is>
@@ -4465,7 +4314,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G63" s="25" t="inlineStr">
+      <c r="G63" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4490,7 +4339,7 @@
           <t>F03-04</t>
         </is>
       </c>
-      <c r="D64" s="28" t="inlineStr">
+      <c r="D64" s="27" t="inlineStr">
         <is>
           <t>组合风控报告生成</t>
         </is>
@@ -4505,7 +4354,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G64" s="25" t="inlineStr">
+      <c r="G64" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4530,7 +4379,7 @@
           <t>F03-05</t>
         </is>
       </c>
-      <c r="D65" s="28" t="inlineStr">
+      <c r="D65" s="27" t="inlineStr">
         <is>
           <t>子基金持仓穿透</t>
         </is>
@@ -4545,7 +4394,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G65" s="24" t="inlineStr">
+      <c r="G65" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4570,7 +4419,7 @@
           <t>F03-06</t>
         </is>
       </c>
-      <c r="D66" s="28" t="inlineStr">
+      <c r="D66" s="27" t="inlineStr">
         <is>
           <t>申赎情况跟踪</t>
         </is>
@@ -4585,7 +4434,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G66" s="25" t="inlineStr">
+      <c r="G66" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4595,7 +4444,7 @@
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="23" t="inlineStr">
+      <c r="A67" s="22" t="inlineStr">
         <is>
           <t>【P1】 FICC风险计量平台  (FICC Risk Measurement)</t>
         </is>
@@ -4632,7 +4481,7 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G68" s="29" t="inlineStr">
+      <c r="G68" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
@@ -4672,7 +4521,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G69" s="24" t="inlineStr">
+      <c r="G69" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4712,7 +4561,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G70" s="24" t="inlineStr">
+      <c r="G70" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4752,7 +4601,7 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G71" s="29" t="inlineStr">
+      <c r="G71" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
@@ -4792,7 +4641,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G72" s="24" t="inlineStr">
+      <c r="G72" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4832,7 +4681,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G73" s="25" t="inlineStr">
+      <c r="G73" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -4842,7 +4691,7 @@
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="23" t="inlineStr">
+      <c r="A74" s="22" t="inlineStr">
         <is>
           <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
         </is>
@@ -4879,7 +4728,7 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G75" s="29" t="inlineStr">
+      <c r="G75" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
@@ -4919,7 +4768,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G76" s="24" t="inlineStr">
+      <c r="G76" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4959,7 +4808,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G77" s="24" t="inlineStr">
+      <c r="G77" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -4999,7 +4848,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G78" s="25" t="inlineStr">
+      <c r="G78" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5039,7 +4888,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G79" s="25" t="inlineStr">
+      <c r="G79" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5049,7 +4898,7 @@
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="23" t="inlineStr">
+      <c r="A80" s="22" t="inlineStr">
         <is>
           <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
         </is>
@@ -5086,7 +4935,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G81" s="24" t="inlineStr">
+      <c r="G81" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5126,7 +4975,7 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G82" s="29" t="inlineStr">
+      <c r="G82" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
@@ -5166,7 +5015,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G83" s="24" t="inlineStr">
+      <c r="G83" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5206,7 +5055,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G84" s="25" t="inlineStr">
+      <c r="G84" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5246,7 +5095,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G85" s="25" t="inlineStr">
+      <c r="G85" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5256,7 +5105,7 @@
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="23" t="inlineStr">
+      <c r="A86" s="22" t="inlineStr">
         <is>
           <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
         </is>
@@ -5293,7 +5142,7 @@
           <t>横截面信号与实际收益相关性&gt;0.3</t>
         </is>
       </c>
-      <c r="G87" s="24" t="inlineStr">
+      <c r="G87" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5333,7 +5182,7 @@
           <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
         </is>
       </c>
-      <c r="G88" s="24" t="inlineStr">
+      <c r="G88" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5373,7 +5222,7 @@
           <t>相关矩阵计算&lt;30s（500券组合）</t>
         </is>
       </c>
-      <c r="G89" s="25" t="inlineStr">
+      <c r="G89" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5413,7 +5262,7 @@
           <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
         </is>
       </c>
-      <c r="G90" s="24" t="inlineStr">
+      <c r="G90" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5453,7 +5302,7 @@
           <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
         </is>
       </c>
-      <c r="G91" s="24" t="inlineStr">
+      <c r="G91" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5493,7 +5342,7 @@
           <t>历史情景复现误差&lt;1%</t>
         </is>
       </c>
-      <c r="G92" s="24" t="inlineStr">
+      <c r="G92" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5533,7 +5382,7 @@
           <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
         </is>
       </c>
-      <c r="G93" s="25" t="inlineStr">
+      <c r="G93" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5573,7 +5422,7 @@
           <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
         </is>
       </c>
-      <c r="G94" s="24" t="inlineStr">
+      <c r="G94" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5613,7 +5462,7 @@
           <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
         </is>
       </c>
-      <c r="G95" s="24" t="inlineStr">
+      <c r="G95" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5653,7 +5502,7 @@
           <t>QP求解100券组合&lt;5s，约束满足率100%</t>
         </is>
       </c>
-      <c r="G96" s="24" t="inlineStr">
+      <c r="G96" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5693,7 +5542,7 @@
           <t>回测期≥5年，预测方向胜率&gt;55%</t>
         </is>
       </c>
-      <c r="G97" s="24" t="inlineStr">
+      <c r="G97" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5733,7 +5582,7 @@
           <t>固收+净值模拟与实际偏差&lt;0.5%</t>
         </is>
       </c>
-      <c r="G98" s="24" t="inlineStr">
+      <c r="G98" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5773,7 +5622,7 @@
           <t>策略容量计算误差&lt;5%</t>
         </is>
       </c>
-      <c r="G99" s="24" t="inlineStr">
+      <c r="G99" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5813,7 +5662,7 @@
           <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
         </is>
       </c>
-      <c r="G100" s="25" t="inlineStr">
+      <c r="G100" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5853,7 +5702,7 @@
           <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
         </is>
       </c>
-      <c r="G101" s="24" t="inlineStr">
+      <c r="G101" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5893,7 +5742,7 @@
           <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
         </is>
       </c>
-      <c r="G102" s="25" t="inlineStr">
+      <c r="G102" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -5933,7 +5782,7 @@
           <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
         </is>
       </c>
-      <c r="G103" s="24" t="inlineStr">
+      <c r="G103" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -5943,7 +5792,7 @@
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="23" t="inlineStr">
+      <c r="A104" s="22" t="inlineStr">
         <is>
           <t>【P1】 策略投资/量化  (Quant Strategy)</t>
         </is>
@@ -5980,7 +5829,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G105" s="24" t="inlineStr">
+      <c r="G105" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -6020,7 +5869,7 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G106" s="29" t="inlineStr">
+      <c r="G106" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
@@ -6060,7 +5909,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G107" s="24" t="inlineStr">
+      <c r="G107" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -6100,7 +5949,7 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G108" s="29" t="inlineStr">
+      <c r="G108" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
@@ -6140,7 +5989,7 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G109" s="25" t="inlineStr">
+      <c r="G109" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -6150,16 +5999,16 @@
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="27" t="inlineStr">
-        <is>
-          <t>【P2】 量化定价引擎  (Quant Pricing Engine)</t>
+      <c r="A110" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 定价平台  (Pricing Platform)</t>
         </is>
       </c>
     </row>
     <row r="111" ht="28" customHeight="1">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>量化定价引擎</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
@@ -6172,7 +6021,7 @@
           <t>F09-01</t>
         </is>
       </c>
-      <c r="D111" s="28" t="inlineStr">
+      <c r="D111" s="27" t="inlineStr">
         <is>
           <t>期限结构模型</t>
         </is>
@@ -6187,7 +6036,7 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G111" s="29" t="inlineStr">
+      <c r="G111" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
@@ -6199,7 +6048,7 @@
     <row r="112" ht="28" customHeight="1">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>量化定价引擎</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -6212,7 +6061,7 @@
           <t>F09-02</t>
         </is>
       </c>
-      <c r="D112" s="28" t="inlineStr">
+      <c r="D112" s="27" t="inlineStr">
         <is>
           <t>蒙特卡洛求解器</t>
         </is>
@@ -6227,7 +6076,7 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G112" s="29" t="inlineStr">
+      <c r="G112" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
@@ -6239,7 +6088,7 @@
     <row r="113" ht="28" customHeight="1">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>量化定价引擎</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
@@ -6252,7 +6101,7 @@
           <t>F09-03</t>
         </is>
       </c>
-      <c r="D113" s="28" t="inlineStr">
+      <c r="D113" s="27" t="inlineStr">
         <is>
           <t>有限差分（PDE）</t>
         </is>
@@ -6267,7 +6116,7 @@
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G113" s="29" t="inlineStr">
+      <c r="G113" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
@@ -6279,7 +6128,7 @@
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>量化定价引擎</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -6292,7 +6141,7 @@
           <t>F09-04</t>
         </is>
       </c>
-      <c r="D114" s="28" t="inlineStr">
+      <c r="D114" s="27" t="inlineStr">
         <is>
           <t>实时Greeks</t>
         </is>
@@ -6307,7 +6156,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G114" s="24" t="inlineStr">
+      <c r="G114" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -6319,7 +6168,7 @@
     <row r="115" ht="28" customHeight="1">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>量化定价引擎</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
@@ -6332,7 +6181,7 @@
           <t>F09-05</t>
         </is>
       </c>
-      <c r="D115" s="28" t="inlineStr">
+      <c r="D115" s="27" t="inlineStr">
         <is>
           <t>定价服务微服务架构</t>
         </is>
@@ -6347,7 +6196,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G115" s="24" t="inlineStr">
+      <c r="G115" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -6359,7 +6208,7 @@
     <row r="116" ht="28" customHeight="1">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>量化定价引擎</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -6372,7 +6221,7 @@
           <t>F09-06</t>
         </is>
       </c>
-      <c r="D116" s="28" t="inlineStr">
+      <c r="D116" s="27" t="inlineStr">
         <is>
           <t>历史估值回测</t>
         </is>
@@ -6387,7 +6236,7 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G116" s="24" t="inlineStr">
+      <c r="G116" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -6397,16 +6246,16 @@
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="27" t="inlineStr">
-        <is>
-          <t>【P2】 利率衍生品  (Interest Rate Derivatives)</t>
+      <c r="A117" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 销售交易  (Sales Trading)</t>
         </is>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>利率衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -6419,34 +6268,34 @@
           <t>F10-01</t>
         </is>
       </c>
-      <c r="D118" s="28" t="inlineStr">
-        <is>
-          <t>IRS/OIS/CCS定价</t>
+      <c r="D118" s="27" t="inlineStr">
+        <is>
+          <t>销交工作台</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>利率互换标准与非标结构定价，折现曲线OIS</t>
+          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G118" s="29" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G118" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H118" s="13" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>利率衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
@@ -6459,34 +6308,34 @@
           <t>F10-02</t>
         </is>
       </c>
-      <c r="D119" s="28" t="inlineStr">
-        <is>
-          <t>久期/DV01/凸度</t>
+      <c r="D119" s="27" t="inlineStr">
+        <is>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>利率衍生品Greeks实时计算，组合对冲比率</t>
+          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G119" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G119" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H119" s="13" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>利率衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -6499,34 +6348,34 @@
           <t>F10-03</t>
         </is>
       </c>
-      <c r="D120" s="28" t="inlineStr">
-        <is>
-          <t>LCH/上清所CCP接口</t>
+      <c r="D120" s="27" t="inlineStr">
+        <is>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>标准化IRS中央清算，保证金（IM/VM）计算</t>
+          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>功能测试通过/正确率100%</t>
         </is>
       </c>
       <c r="G120" s="24" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H120" s="13" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>利率衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
@@ -6539,34 +6388,34 @@
           <t>F10-04</t>
         </is>
       </c>
-      <c r="D121" s="28" t="inlineStr">
-        <is>
-          <t>压力测试/情景分析</t>
+      <c r="D121" s="27" t="inlineStr">
+        <is>
+          <t>交易执行与审批</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>利率曲线平移/扭转/蝶式情景，组合P&amp;L影响</t>
+          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>功能测试通过/正确率100%</t>
         </is>
       </c>
       <c r="G121" s="24" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H121" s="13" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t>利率衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -6579,75 +6428,75 @@
           <t>F10-05</t>
         </is>
       </c>
-      <c r="D122" s="28" t="inlineStr">
-        <is>
-          <t>利率曲线发布</t>
+      <c r="D122" s="27" t="inlineStr">
+        <is>
+          <t>风控检查</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>多曲线框架（OIS/中债曲线）实时发布</t>
+          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr">
         <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G122" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H122" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>F10-06</t>
+        </is>
+      </c>
+      <c r="D123" s="27" t="inlineStr">
+        <is>
+          <t>智能推荐系统</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G122" s="24" t="inlineStr">
+      <c r="G123" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H122" s="13" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="27" t="inlineStr">
+      <c r="H123" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="26" t="inlineStr">
         <is>
           <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
         </is>
-      </c>
-    </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C124" s="10" t="inlineStr">
-        <is>
-          <t>F11-01</t>
-        </is>
-      </c>
-      <c r="D124" s="28" t="inlineStr">
-        <is>
-          <t>信用利差分析</t>
-        </is>
-      </c>
-      <c r="E124" s="11" t="inlineStr">
-        <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
-        </is>
-      </c>
-      <c r="F124" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G124" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H124" s="13" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
@@ -6663,31 +6512,31 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
-        </is>
-      </c>
-      <c r="D125" s="28" t="inlineStr">
-        <is>
-          <t>CDS/CLN定价</t>
+          <t>F11-01</t>
+        </is>
+      </c>
+      <c r="D125" s="27" t="inlineStr">
+        <is>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G125" s="29" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H125" s="13" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" ht="28" customHeight="1">
@@ -6703,31 +6552,31 @@
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
-        </is>
-      </c>
-      <c r="D126" s="28" t="inlineStr">
-        <is>
-          <t>信用评级动态监控</t>
+          <t>F11-02</t>
+        </is>
+      </c>
+      <c r="D126" s="27" t="inlineStr">
+        <is>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G126" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G126" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H126" s="13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="127" ht="28" customHeight="1">
@@ -6743,31 +6592,31 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
-        </is>
-      </c>
-      <c r="D127" s="28" t="inlineStr">
-        <is>
-          <t>违约概率（PD）建模</t>
+          <t>F11-03</t>
+        </is>
+      </c>
+      <c r="D127" s="27" t="inlineStr">
+        <is>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>功能测试通过/正确率100%</t>
         </is>
       </c>
       <c r="G127" s="24" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H127" s="13" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
@@ -6783,84 +6632,84 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
+          <t>F11-04</t>
+        </is>
+      </c>
+      <c r="D128" s="27" t="inlineStr">
+        <is>
+          <t>违约概率（PD）建模</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G128" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H128" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
           <t>F11-05</t>
         </is>
       </c>
-      <c r="D128" s="28" t="inlineStr">
+      <c r="D129" s="27" t="inlineStr">
         <is>
           <t>集中度限额管理</t>
         </is>
       </c>
-      <c r="E128" s="11" t="inlineStr">
+      <c r="E129" s="11" t="inlineStr">
         <is>
           <t>行业/发行人/评级集中度多维限额，超限预警</t>
         </is>
       </c>
-      <c r="F128" s="11" t="inlineStr">
+      <c r="F129" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G128" s="25" t="inlineStr">
+      <c r="G129" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H128" s="13" t="n">
+      <c r="H129" s="13" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="27" t="inlineStr">
-        <is>
-          <t>【P2】 数据管理/行情平台  (Market Data Platform)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="28" customHeight="1">
-      <c r="A130" s="11" t="inlineStr">
-        <is>
-          <t>数据管理/行情平台</t>
-        </is>
-      </c>
-      <c r="B130" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C130" s="10" t="inlineStr">
-        <is>
-          <t>F12-01</t>
-        </is>
-      </c>
-      <c r="D130" s="28" t="inlineStr">
-        <is>
-          <t>多源行情聚合</t>
-        </is>
-      </c>
-      <c r="E130" s="11" t="inlineStr">
-        <is>
-          <t>Bloomberg/Wind/中汇信/Refinitiv多源融合，冲突解析</t>
-        </is>
-      </c>
-      <c r="F130" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G130" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H130" s="13" t="n">
-        <v>25</v>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 投顾服务  (Investment Advisory)</t>
+        </is>
       </c>
     </row>
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -6870,17 +6719,17 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
-        </is>
-      </c>
-      <c r="D131" s="28" t="inlineStr">
-        <is>
-          <t>数据质量校验</t>
+          <t>F12-01</t>
+        </is>
+      </c>
+      <c r="D131" s="27" t="inlineStr">
+        <is>
+          <t>投顾工作台</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>异常值/缺失值/跳价自动检测，修复建议与人工审核</t>
+          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr">
@@ -6888,19 +6737,19 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G131" s="25" t="inlineStr">
+      <c r="G131" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
       <c r="H131" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -6910,37 +6759,37 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
-        </is>
-      </c>
-      <c r="D132" s="28" t="inlineStr">
-        <is>
-          <t>历史数据仓库</t>
+          <t>F12-02</t>
+        </is>
+      </c>
+      <c r="D132" s="27" t="inlineStr">
+        <is>
+          <t>客户终端</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>Tick/日频历史行情存储，高效查询（ClickHouse/TimescaleDB）</t>
+          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>功能测试通过/正确率100%</t>
         </is>
       </c>
       <c r="G132" s="24" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H132" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -6950,37 +6799,37 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
-        </is>
-      </c>
-      <c r="D133" s="28" t="inlineStr">
-        <is>
-          <t>收益率曲线发布</t>
+          <t>F12-03</t>
+        </is>
+      </c>
+      <c r="D133" s="27" t="inlineStr">
+        <is>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>国债/政策行/高等级信用曲线实时发布，Kafka广播</t>
+          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>功能测试通过/正确率100%</t>
         </is>
       </c>
       <c r="G133" s="24" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H133" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>数据管理/行情平台</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -6990,44 +6839,77 @@
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
+          <t>F12-04</t>
+        </is>
+      </c>
+      <c r="D134" s="27" t="inlineStr">
+        <is>
+          <t>账户分析报告</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G134" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H134" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B135" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
           <t>F12-05</t>
         </is>
       </c>
-      <c r="D134" s="28" t="inlineStr">
-        <is>
-          <t>估值价格服务</t>
-        </is>
-      </c>
-      <c r="E134" s="11" t="inlineStr">
-        <is>
-          <t>非活跃债券估值价格（中债估值基准），API接口提供</t>
-        </is>
-      </c>
-      <c r="F134" s="11" t="inlineStr">
+      <c r="D135" s="27" t="inlineStr">
+        <is>
+          <t>投研报告服务</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G134" s="25" t="inlineStr">
+      <c r="G135" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H134" s="13" t="n">
+      <c r="H135" s="13" t="n">
         <v>15</v>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="27" t="inlineStr">
-        <is>
-          <t>【P2】 交易对手管理  (Counterparty Management)</t>
-        </is>
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -7037,77 +6919,44 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
-        </is>
-      </c>
-      <c r="D136" s="28" t="inlineStr">
-        <is>
-          <t>对手方评级与审批</t>
+          <t>F12-06</t>
+        </is>
+      </c>
+      <c r="D136" s="27" t="inlineStr">
+        <is>
+          <t>客户服务与基础服务</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>内部信用评级模型，新增/变更交易对手审批流</t>
+          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
+          <t>功能测试通过</t>
         </is>
       </c>
       <c r="G136" s="25" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>低</t>
         </is>
       </c>
       <c r="H136" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="137" ht="28" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>交易对手管理</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
-        <is>
-          <t>F13-02</t>
-        </is>
-      </c>
-      <c r="D137" s="28" t="inlineStr">
-        <is>
-          <t>实时敞口聚合</t>
-        </is>
-      </c>
-      <c r="E137" s="11" t="inlineStr">
-        <is>
-          <t>跨产品交易对手名义/MtM敞口实时聚合，压力敞口（EPE）</t>
-        </is>
-      </c>
-      <c r="F137" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G137" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H137" s="13" t="n">
-        <v>35</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+        </is>
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>TRS收益互换</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -7117,17 +6966,17 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
-        </is>
-      </c>
-      <c r="D138" s="28" t="inlineStr">
-        <is>
-          <t>ISDA/CSA协议管理</t>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D138" s="27" t="inlineStr">
+        <is>
+          <t>TRS交易端</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>主协议文档管理，净额结算协议（Netting Set）配置</t>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
@@ -7135,19 +6984,19 @@
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G138" s="24" t="inlineStr">
+      <c r="G138" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="H138" s="13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>TRS收益互换</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -7157,37 +7006,37 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
-        </is>
-      </c>
-      <c r="D139" s="28" t="inlineStr">
-        <is>
-          <t>CVA/DVA/FVA计算</t>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D139" s="27" t="inlineStr">
+        <is>
+          <t>TRS客户端</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>信用/债务/资金估值调整实时估算，敞口报告</t>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G139" s="29" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H139" s="13" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>交易对手管理</t>
+          <t>TRS收益互换</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -7197,17 +7046,17 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
-        </is>
-      </c>
-      <c r="D140" s="28" t="inlineStr">
-        <is>
-          <t>集中度与限额</t>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D140" s="27" t="inlineStr">
+        <is>
+          <t>TRS管理端</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>对手方/集团合并敞口限额，超限审批与记录</t>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr">
@@ -7215,26 +7064,59 @@
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G140" s="25" t="inlineStr">
+      <c r="G140" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
       <c r="H140" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="27" t="inlineStr">
-        <is>
-          <t>【P2】 清算结算后台  (Clearing &amp; Settlement)</t>
-        </is>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C141" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D141" s="27" t="inlineStr">
+        <is>
+          <t>自动对冲</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="inlineStr">
+        <is>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+        </is>
+      </c>
+      <c r="F141" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G141" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H141" s="13" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="142" ht="28" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>TRS收益互换</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -7244,37 +7126,37 @@
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>F14-01</t>
-        </is>
-      </c>
-      <c r="D142" s="28" t="inlineStr">
-        <is>
-          <t>DVP/FOP指令生成</t>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D142" s="27" t="inlineStr">
+        <is>
+          <t>通知与确认文件</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>成交后自动生成交割指令，批量/单笔支持</t>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>功能测试通过/正确率100%</t>
         </is>
       </c>
       <c r="G142" s="24" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="H142" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="143" ht="28" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>清算结算后台</t>
+          <t>TRS收益互换</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -7284,597 +7166,268 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>F14-02</t>
-        </is>
-      </c>
-      <c r="D143" s="28" t="inlineStr">
-        <is>
-          <t>中登/中债登接口</t>
+          <t>F13-06</t>
+        </is>
+      </c>
+      <c r="D143" s="27" t="inlineStr">
+        <is>
+          <t>系统集成</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>银行间债券（中债登）和交易所债券（中登）接口对接</t>
+          <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G143" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H143" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="29" t="inlineStr">
+        <is>
+          <t>【P3】 做市商系统  (Market Making)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B145" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C145" s="15" t="inlineStr">
+        <is>
+          <t>F15-01</t>
+        </is>
+      </c>
+      <c r="D145" s="30" t="inlineStr">
+        <is>
+          <t>双边报价引擎</t>
+        </is>
+      </c>
+      <c r="E145" s="16" t="inlineStr">
+        <is>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
+        </is>
+      </c>
+      <c r="F145" s="16" t="inlineStr">
+        <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G143" s="29" t="inlineStr">
+      <c r="G145" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H143" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="144" ht="28" customHeight="1">
-      <c r="A144" s="11" t="inlineStr">
-        <is>
-          <t>清算结算后台</t>
-        </is>
-      </c>
-      <c r="B144" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C144" s="10" t="inlineStr">
-        <is>
-          <t>F14-03</t>
-        </is>
-      </c>
-      <c r="D144" s="28" t="inlineStr">
-        <is>
-          <t>待交割明细管理</t>
-        </is>
-      </c>
-      <c r="E144" s="11" t="inlineStr">
-        <is>
-          <t>T+0/T+1待交割跟踪，提前预警可能失败交割</t>
-        </is>
-      </c>
-      <c r="F144" s="11" t="inlineStr">
+      <c r="H145" s="18" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B146" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C146" s="15" t="inlineStr">
+        <is>
+          <t>F15-02</t>
+        </is>
+      </c>
+      <c r="D146" s="30" t="inlineStr">
+        <is>
+          <t>库存风险实时管理</t>
+        </is>
+      </c>
+      <c r="E146" s="16" t="inlineStr">
+        <is>
+          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
+        </is>
+      </c>
+      <c r="F146" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G146" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H146" s="18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="147" ht="28" customHeight="1">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B147" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C147" s="15" t="inlineStr">
+        <is>
+          <t>F15-03</t>
+        </is>
+      </c>
+      <c r="D147" s="30" t="inlineStr">
+        <is>
+          <t>报价优化算法</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>基于市场微结构理论动态调整bid-ask spread</t>
+        </is>
+      </c>
+      <c r="F147" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G147" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="148" ht="28" customHeight="1">
+      <c r="A148" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B148" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="inlineStr">
+        <is>
+          <t>F15-04</t>
+        </is>
+      </c>
+      <c r="D148" s="30" t="inlineStr">
+        <is>
+          <t>竞争力分析</t>
+        </is>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>与市场最优报价对比，中签率分析，策略调优</t>
+        </is>
+      </c>
+      <c r="F148" s="16" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G144" s="24" t="inlineStr">
+      <c r="G148" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H144" s="13" t="n">
+      <c r="H148" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="145" ht="28" customHeight="1">
-      <c r="A145" s="11" t="inlineStr">
-        <is>
-          <t>清算结算后台</t>
-        </is>
-      </c>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>F14-04</t>
-        </is>
-      </c>
-      <c r="D145" s="28" t="inlineStr">
-        <is>
-          <t>资金调拨确认</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="inlineStr">
-        <is>
-          <t>资金划拨指令生成，银行资金头寸确认，轧差净额</t>
-        </is>
-      </c>
-      <c r="F145" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G145" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H145" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="146" ht="28" customHeight="1">
-      <c r="A146" s="11" t="inlineStr">
-        <is>
-          <t>清算结算后台</t>
-        </is>
-      </c>
-      <c r="B146" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C146" s="10" t="inlineStr">
-        <is>
-          <t>F14-05</t>
-        </is>
-      </c>
-      <c r="D146" s="28" t="inlineStr">
-        <is>
-          <t>交割失败处理</t>
-        </is>
-      </c>
-      <c r="E146" s="11" t="inlineStr">
-        <is>
-          <t>失败交割自动识别，补交割流程，罚息计算</t>
-        </is>
-      </c>
-      <c r="F146" s="11" t="inlineStr">
+    <row r="149" ht="28" customHeight="1">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B149" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C149" s="15" t="inlineStr">
+        <is>
+          <t>F15-05</t>
+        </is>
+      </c>
+      <c r="D149" s="30" t="inlineStr">
+        <is>
+          <t>交易对手管理集成</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>做市交易对手信用实时检查，额度占用同步更新</t>
+        </is>
+      </c>
+      <c r="F149" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G146" s="25" t="inlineStr">
+      <c r="G149" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H146" s="13" t="n">
+      <c r="H149" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="30" t="inlineStr">
-        <is>
-          <t>【P3】 做市商系统  (Market Making)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="28" customHeight="1">
-      <c r="A148" s="17" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B148" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C148" s="16" t="inlineStr">
-        <is>
-          <t>F15-01</t>
-        </is>
-      </c>
-      <c r="D148" s="31" t="inlineStr">
-        <is>
-          <t>双边报价引擎</t>
-        </is>
-      </c>
-      <c r="E148" s="17" t="inlineStr">
-        <is>
-          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
-        </is>
-      </c>
-      <c r="F148" s="17" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G148" s="29" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H148" s="19" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="149" ht="28" customHeight="1">
-      <c r="A149" s="17" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B149" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C149" s="16" t="inlineStr">
-        <is>
-          <t>F15-02</t>
-        </is>
-      </c>
-      <c r="D149" s="31" t="inlineStr">
-        <is>
-          <t>库存风险实时管理</t>
-        </is>
-      </c>
-      <c r="E149" s="17" t="inlineStr">
-        <is>
-          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
-        </is>
-      </c>
-      <c r="F149" s="17" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G149" s="29" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H149" s="19" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="150" ht="28" customHeight="1">
-      <c r="A150" s="17" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B150" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C150" s="16" t="inlineStr">
-        <is>
-          <t>F15-03</t>
-        </is>
-      </c>
-      <c r="D150" s="31" t="inlineStr">
-        <is>
-          <t>报价优化算法</t>
-        </is>
-      </c>
-      <c r="E150" s="17" t="inlineStr">
-        <is>
-          <t>基于市场微结构理论动态调整bid-ask spread</t>
-        </is>
-      </c>
-      <c r="F150" s="17" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G150" s="29" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H150" s="19" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="151" ht="28" customHeight="1">
-      <c r="A151" s="17" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B151" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C151" s="16" t="inlineStr">
-        <is>
-          <t>F15-04</t>
-        </is>
-      </c>
-      <c r="D151" s="31" t="inlineStr">
-        <is>
-          <t>竞争力分析</t>
-        </is>
-      </c>
-      <c r="E151" s="17" t="inlineStr">
-        <is>
-          <t>与市场最优报价对比，中签率分析，策略调优</t>
-        </is>
-      </c>
-      <c r="F151" s="17" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G151" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H151" s="19" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="152" ht="28" customHeight="1">
-      <c r="A152" s="17" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B152" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C152" s="16" t="inlineStr">
-        <is>
-          <t>F15-05</t>
-        </is>
-      </c>
-      <c r="D152" s="31" t="inlineStr">
-        <is>
-          <t>交易对手管理集成</t>
-        </is>
-      </c>
-      <c r="E152" s="17" t="inlineStr">
-        <is>
-          <t>做市交易对手信用实时检查，额度占用同步更新</t>
-        </is>
-      </c>
-      <c r="F152" s="17" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G152" s="25" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H152" s="19" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="153" ht="20" customHeight="1">
-      <c r="A153" s="30" t="inlineStr">
-        <is>
-          <t>【P3】 外汇/外汇衍生品  (FX &amp; FX Derivatives)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="28" customHeight="1">
-      <c r="A154" s="17" t="inlineStr">
-        <is>
-          <t>外汇/外汇衍生品</t>
-        </is>
-      </c>
-      <c r="B154" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C154" s="16" t="inlineStr">
-        <is>
-          <t>F16-01</t>
-        </is>
-      </c>
-      <c r="D154" s="31" t="inlineStr">
-        <is>
-          <t>即期/远期报价</t>
-        </is>
-      </c>
-      <c r="E154" s="17" t="inlineStr">
-        <is>
-          <t>USD/CNY等主要货币对即期汇率+远期点数报价</t>
-        </is>
-      </c>
-      <c r="F154" s="17" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G154" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H154" s="19" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="155" ht="28" customHeight="1">
-      <c r="A155" s="17" t="inlineStr">
-        <is>
-          <t>外汇/外汇衍生品</t>
-        </is>
-      </c>
-      <c r="B155" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C155" s="16" t="inlineStr">
-        <is>
-          <t>F16-02</t>
-        </is>
-      </c>
-      <c r="D155" s="31" t="inlineStr">
-        <is>
-          <t>外汇期权（FXO）</t>
-        </is>
-      </c>
-      <c r="E155" s="17" t="inlineStr">
-        <is>
-          <t>欧式/美式FXO定价（Garman-Kohlhagen），Greeks</t>
-        </is>
-      </c>
-      <c r="F155" s="17" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G155" s="29" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H155" s="19" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="156" ht="28" customHeight="1">
-      <c r="A156" s="17" t="inlineStr">
-        <is>
-          <t>外汇/外汇衍生品</t>
-        </is>
-      </c>
-      <c r="B156" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C156" s="16" t="inlineStr">
-        <is>
-          <t>F16-03</t>
-        </is>
-      </c>
-      <c r="D156" s="31" t="inlineStr">
-        <is>
-          <t>NDF/NDO定价</t>
-        </is>
-      </c>
-      <c r="E156" s="17" t="inlineStr">
-        <is>
-          <t>不可交割远期/期权定价，境外对手对接</t>
-        </is>
-      </c>
-      <c r="F156" s="17" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G156" s="29" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H156" s="19" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="157" ht="28" customHeight="1">
-      <c r="A157" s="17" t="inlineStr">
-        <is>
-          <t>外汇/外汇衍生品</t>
-        </is>
-      </c>
-      <c r="B157" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C157" s="16" t="inlineStr">
-        <is>
-          <t>F16-04</t>
-        </is>
-      </c>
-      <c r="D157" s="31" t="inlineStr">
-        <is>
-          <t>跨货币敞口汇总</t>
-        </is>
-      </c>
-      <c r="E157" s="17" t="inlineStr">
-        <is>
-          <t>多币种资产折算人民币敞口，汇率风险VaR</t>
-        </is>
-      </c>
-      <c r="F157" s="17" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G157" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H157" s="19" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="158" ht="28" customHeight="1">
-      <c r="A158" s="17" t="inlineStr">
-        <is>
-          <t>外汇/外汇衍生品</t>
-        </is>
-      </c>
-      <c r="B158" s="16" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C158" s="16" t="inlineStr">
-        <is>
-          <t>F16-05</t>
-        </is>
-      </c>
-      <c r="D158" s="31" t="inlineStr">
-        <is>
-          <t>CFETS/外汇局接口</t>
-        </is>
-      </c>
-      <c r="E158" s="17" t="inlineStr">
-        <is>
-          <t>银行间外汇市场CFETS接口，外汇局合规报送</t>
-        </is>
-      </c>
-      <c r="F158" s="17" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G158" s="24" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H158" s="19" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="20" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H159" s="21">
-        <f>SUM(H3:H158)</f>
+      <c r="H150" s="20">
+        <f>SUM(H3:H149)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="A80:H80"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A153:H153"/>
-    <mergeCell ref="A159:G159"/>
+    <mergeCell ref="A124:H124"/>
+    <mergeCell ref="A130:H130"/>
     <mergeCell ref="A86:H86"/>
-    <mergeCell ref="A147:H147"/>
-    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A144:H144"/>
+    <mergeCell ref="A150:G150"/>
     <mergeCell ref="A104:H104"/>
     <mergeCell ref="A117:H117"/>
-    <mergeCell ref="A141:H141"/>
+    <mergeCell ref="A137:H137"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A110:H110"/>
-    <mergeCell ref="A123:H123"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A135:H135"/>
     <mergeCell ref="A74:H74"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7912,35 +7465,35 @@
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>岗位</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>职责说明</t>
         </is>
       </c>
-      <c r="C2" s="32" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>Phase 1（M1-M10）
 P1模块 — 核心平台建设</t>
         </is>
       </c>
-      <c r="F2" s="32" t="inlineStr">
+      <c r="F2" s="31" t="inlineStr">
         <is>
           <t>Phase 2（M11-M20）
 P2模块 — 能力扩展</t>
         </is>
       </c>
-      <c r="I2" s="32" t="inlineStr">
+      <c r="I2" s="31" t="inlineStr">
         <is>
           <t>Phase 3（M21-M27）
 P3模块 — 战略深水区</t>
         </is>
       </c>
-      <c r="L2" s="32" t="inlineStr">
+      <c r="L2" s="31" t="inlineStr">
         <is>
           <t>总招募
 峰值人力</t>
@@ -7948,54 +7501,54 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>招募(人)</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>工期(月)</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>人月</t>
         </is>
       </c>
-      <c r="F3" s="29" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>招募(人)</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>工期(月)</t>
         </is>
       </c>
-      <c r="H3" s="29" t="inlineStr">
+      <c r="H3" s="28" t="inlineStr">
         <is>
           <t>人月</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t>招募(人)</t>
         </is>
       </c>
-      <c r="J3" s="29" t="inlineStr">
+      <c r="J3" s="28" t="inlineStr">
         <is>
           <t>工期(月)</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t>人月</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>FICC业务架构师
 FICC Business Architect</t>
@@ -8036,7 +7589,7 @@
         <f>I4*J4</f>
         <v/>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="32">
         <f>MAX(C4,F4,I4)</f>
         <v/>
       </c>
@@ -8083,13 +7636,13 @@
         <f>I5*J5</f>
         <v/>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="33">
         <f>MAX(C5,F5,I5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>量化研究员
 Quant Researcher</t>
@@ -8130,13 +7683,13 @@
         <f>I6*J6</f>
         <v/>
       </c>
-      <c r="L6" s="33">
+      <c r="L6" s="32">
         <f>MAX(C6,F6,I6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>前端研发工程师
 Frontend Engineer</t>
@@ -8177,13 +7730,13 @@
         <f>I7*J7</f>
         <v/>
       </c>
-      <c r="L7" s="33">
+      <c r="L7" s="32">
         <f>MAX(C7,F7,I7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>数据工程师
 Data Engineer</t>
@@ -8224,13 +7777,13 @@
         <f>I8*J8</f>
         <v/>
       </c>
-      <c r="L8" s="33">
+      <c r="L8" s="32">
         <f>MAX(C8,F8,I8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>测试工程师
 QA Engineer</t>
@@ -8271,13 +7824,13 @@
         <f>I9*J9</f>
         <v/>
       </c>
-      <c r="L9" s="33">
+      <c r="L9" s="32">
         <f>MAX(C9,F9,I9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>产品经理/BA
 Product Manager / BA</t>
@@ -8318,13 +7871,13 @@
         <f>I10*J10</f>
         <v/>
       </c>
-      <c r="L10" s="33">
+      <c r="L10" s="32">
         <f>MAX(C10,F10,I10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>DevOps/基础设施
 DevOps / Infra</t>
@@ -8365,13 +7918,13 @@
         <f>I11*J11</f>
         <v/>
       </c>
-      <c r="L11" s="33">
+      <c r="L11" s="32">
         <f>MAX(C11,F11,I11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>安全合规专家
 Security &amp; Compliance</t>
@@ -8412,42 +7965,42 @@
         <f>I12*J12</f>
         <v/>
       </c>
-      <c r="L12" s="33">
+      <c r="L12" s="32">
         <f>MAX(C12,F12,I12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>合计 Totals</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="20">
         <f>SUM(C4:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="35" t="inlineStr"/>
-      <c r="E13" s="35" t="inlineStr"/>
-      <c r="F13" s="21">
+      <c r="D13" s="34" t="inlineStr"/>
+      <c r="E13" s="34" t="inlineStr"/>
+      <c r="F13" s="20">
         <f>SUM(F4:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="35" t="inlineStr"/>
-      <c r="H13" s="35" t="inlineStr"/>
-      <c r="I13" s="21">
+      <c r="G13" s="34" t="inlineStr"/>
+      <c r="H13" s="34" t="inlineStr"/>
+      <c r="I13" s="20">
         <f>SUM(I4:I12)</f>
         <v/>
       </c>
-      <c r="J13" s="35" t="inlineStr"/>
-      <c r="K13" s="35" t="inlineStr"/>
-      <c r="L13" s="21">
+      <c r="J13" s="34" t="inlineStr"/>
+      <c r="K13" s="34" t="inlineStr"/>
+      <c r="L13" s="20">
         <f>SUM(L4:L12)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>规划假设说明：① 各阶段人力可累计复用（P2团队延续P1人员，适当扩张）  ② 量化研究员稀缺，建议优先招募，外部顾问补充  ③ 信创合规专家建议从监管/银行方引进  ④ 峰值人力约40人（Phase 2），建议2026Q3启动Phase 1招募</t>
         </is>
@@ -8570,7 +8123,7 @@
           <t>某券商债券异常订单旁路检测</t>
         </is>
       </c>
-      <c r="E3" s="37" t="inlineStr">
+      <c r="E3" s="36" t="inlineStr">
         <is>
           <t>CEP引擎低延迟稳定性</t>
         </is>
@@ -8618,7 +8171,7 @@
           <t>某券商自营债券投资合规校验</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="36" t="inlineStr">
         <is>
           <t>规则库完整性</t>
         </is>
@@ -8666,7 +8219,7 @@
           <t>资管公司债券持仓实时账薄</t>
         </is>
       </c>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="E5" s="36" t="inlineStr">
         <is>
           <t>多资产估值覆盖率</t>
         </is>
@@ -8714,7 +8267,7 @@
           <t>替换某券商现有债券交易终端</t>
         </is>
       </c>
-      <c r="E6" s="37" t="inlineStr">
+      <c r="E6" s="36" t="inlineStr">
         <is>
           <t>CFETS接口稳定性</t>
         </is>
@@ -8762,7 +8315,7 @@
           <t>某券商FICC组合风险日报</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>模型精度vs衡泰基准</t>
         </is>
@@ -8810,7 +8363,7 @@
           <t>资管公司固收组合绩效分析</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>Brinson模型精度验证</t>
         </is>
@@ -8858,7 +8411,7 @@
           <t>自营量化部门策略回测平台</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>Tick回测数据质量</t>
         </is>
@@ -8886,7 +8439,7 @@
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="38" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>P1阶段战略重心：① 快赢先行（异常风控+事前合规M1并行，6个月见成果）  ② 主干平行（IBOR+现券M2启动，建立账薄主干）  ③ 差异化（量化策略+绩效归因M4-M5，构建高壁垒能力）  ④ 替代衡泰（FICC风险计量M3启动，以信创+精度优势直攻垄断盲区）</t>
         </is>
@@ -8923,21 +8476,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>系统详情：IBOR投资账薄管理  |  IBOR</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>战略定位：整个FICC平台的账薄主干，27项功能覆盖持仓/现金/估值/事件/对账/合规/试算全链路   |   来源：Slide 55   |   数据输入：交易指令数据 / 行情/估值数据 / 资产主数据 / 托管行结算通知   |   量化底座：账户体系(AMI/AMDB) · Kafka实时消息 · Redis分布式缓存</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="40" t="inlineStr">
         <is>
           <t>模块：IBOR投资账薄管理  (IBOR)  |  优先级：P1  |  竞品：衡泰(老旧)  |  华锐基础：AMI/AMDB账户体系  |  工期：12月  团队：14人</t>
         </is>
@@ -8996,7 +8549,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>A. 实时持仓管理</t>
         </is>
@@ -9033,7 +8586,7 @@
           <t>交易系统OMS/ATP报盘接口</t>
         </is>
       </c>
-      <c r="G6" s="42" t="inlineStr">
+      <c r="G6" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9079,7 +8632,7 @@
           <t>AMI/AMDB账户主数据</t>
         </is>
       </c>
-      <c r="G7" s="43" t="inlineStr">
+      <c r="G7" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9125,7 +8678,7 @@
           <t>中登/中债登结算接口</t>
         </is>
       </c>
-      <c r="G8" s="43" t="inlineStr">
+      <c r="G8" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9171,7 +8724,7 @@
           <t>回购管理系统/风控系统</t>
         </is>
       </c>
-      <c r="G9" s="43" t="inlineStr">
+      <c r="G9" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9197,7 +8750,7 @@
           <t>F01-27</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>资产打标与组合树管理</t>
         </is>
@@ -9217,7 +8770,7 @@
           <t>资产主数据/IBOR持仓引擎/报表系统</t>
         </is>
       </c>
-      <c r="G10" s="43" t="inlineStr">
+      <c r="G10" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9233,7 +8786,7 @@
       <c r="J10" s="11" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>B. 现金管理</t>
         </is>
@@ -9270,7 +8823,7 @@
           <t>资金系统/清算结算接口</t>
         </is>
       </c>
-      <c r="G12" s="42" t="inlineStr">
+      <c r="G12" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9316,7 +8869,7 @@
           <t>回购管理/利率衍生品/IBOR持仓</t>
         </is>
       </c>
-      <c r="G13" s="42" t="inlineStr">
+      <c r="G13" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9342,7 +8895,7 @@
           <t>F01-07</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>多币种资金管理</t>
         </is>
@@ -9362,7 +8915,7 @@
           <t>外汇系统/AMD行情平台</t>
         </is>
       </c>
-      <c r="G14" s="43" t="inlineStr">
+      <c r="G14" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9378,7 +8931,7 @@
       <c r="J14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>C. 估值与净值</t>
         </is>
@@ -9415,7 +8968,7 @@
           <t>AMD行情平台/Bloomberg数据接口</t>
         </is>
       </c>
-      <c r="G16" s="42" t="inlineStr">
+      <c r="G16" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9461,7 +9014,7 @@
           <t>资产主数据（票面率/计息基准/付息频率）</t>
         </is>
       </c>
-      <c r="G17" s="43" t="inlineStr">
+      <c r="G17" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9507,7 +9060,7 @@
           <t>量化定价引擎/交易对手管理</t>
         </is>
       </c>
-      <c r="G18" s="42" t="inlineStr">
+      <c r="G18" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9523,7 +9076,7 @@
       <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>D. 事件处理</t>
         </is>
@@ -9560,7 +9113,7 @@
           <t>资产主数据/托管行结算通知</t>
         </is>
       </c>
-      <c r="G20" s="42" t="inlineStr">
+      <c r="G20" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9606,7 +9159,7 @@
           <t>回购管理系统/IBOR头寸</t>
         </is>
       </c>
-      <c r="G21" s="42" t="inlineStr">
+      <c r="G21" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9632,7 +9185,7 @@
           <t>F01-13</t>
         </is>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>公司行为通知</t>
         </is>
@@ -9652,7 +9205,7 @@
           <t>AMD行情平台/资产主数据</t>
         </is>
       </c>
-      <c r="G22" s="43" t="inlineStr">
+      <c r="G22" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9668,7 +9221,7 @@
       <c r="J22" s="11" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>E. 对账与数据质量</t>
         </is>
@@ -9705,7 +9258,7 @@
           <t>中登/中债登结算接口/SFTP</t>
         </is>
       </c>
-      <c r="G24" s="42" t="inlineStr">
+      <c r="G24" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9751,7 +9304,7 @@
           <t>会计核算系统(ABOR)/IBOR持仓</t>
         </is>
       </c>
-      <c r="G25" s="43" t="inlineStr">
+      <c r="G25" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9797,7 +9350,7 @@
           <t>清算结算系统/中登中债登</t>
         </is>
       </c>
-      <c r="G26" s="43" t="inlineStr">
+      <c r="G26" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9813,7 +9366,7 @@
       <c r="J26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="45" t="inlineStr">
+      <c r="A27" s="44" t="inlineStr">
         <is>
           <t>F. 合规与监管</t>
         </is>
@@ -9850,7 +9403,7 @@
           <t>事前风控/合规系统/投资授权书管理</t>
         </is>
       </c>
-      <c r="G28" s="42" t="inlineStr">
+      <c r="G28" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9896,7 +9449,7 @@
           <t>IBOR全域数据/报表引擎</t>
         </is>
       </c>
-      <c r="G29" s="43" t="inlineStr">
+      <c r="G29" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -9912,7 +9465,7 @@
       <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>G. 数据接入与集成</t>
         </is>
@@ -9949,7 +9502,7 @@
           <t>AMD行情平台/Bloomberg API/Wind数据接口</t>
         </is>
       </c>
-      <c r="G31" s="42" t="inlineStr">
+      <c r="G31" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -9995,7 +9548,7 @@
           <t>ATP报盘引擎/CFETS银行间接口/交易所接口</t>
         </is>
       </c>
-      <c r="G32" s="43" t="inlineStr">
+      <c r="G32" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10041,7 +9594,7 @@
           <t>中登/中债登/托管行SFTP接口/清算结算系统</t>
         </is>
       </c>
-      <c r="G33" s="43" t="inlineStr">
+      <c r="G33" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10057,7 +9610,7 @@
       <c r="J33" s="5" t="inlineStr"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="41" t="inlineStr">
+      <c r="A34" s="40" t="inlineStr">
         <is>
           <t>H. What-if 投资试算</t>
         </is>
@@ -10094,7 +9647,7 @@
           <t>IBOR事件存储引擎/现金流预测模块</t>
         </is>
       </c>
-      <c r="G35" s="42" t="inlineStr">
+      <c r="G35" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10140,7 +9693,7 @@
           <t>资产主数据（会计分类标签）/ABOR会计系统/AMD估值数据</t>
         </is>
       </c>
-      <c r="G36" s="42" t="inlineStr">
+      <c r="G36" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10186,7 +9739,7 @@
           <t>权限管理系统/IBOR数据核心层</t>
         </is>
       </c>
-      <c r="G37" s="43" t="inlineStr">
+      <c r="G37" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10232,7 +9785,7 @@
           <t>IBOR实时持仓/估值引擎/事前风控系统</t>
         </is>
       </c>
-      <c r="G38" s="42" t="inlineStr">
+      <c r="G38" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10278,7 +9831,7 @@
           <t>IBOR现金流预测/量化定价引擎/FICC风险计量平台</t>
         </is>
       </c>
-      <c r="G39" s="42" t="inlineStr">
+      <c r="G39" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10294,17 +9847,17 @@
       <c r="J39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>合计 27项功能  |  P1: 24项  |  P2: 3项</t>
         </is>
       </c>
-      <c r="H40" s="21">
+      <c r="H40" s="20">
         <f>SUM(H5:H39)</f>
         <v/>
       </c>
-      <c r="I40" s="35" t="inlineStr"/>
-      <c r="J40" s="35" t="inlineStr"/>
+      <c r="I40" s="34" t="inlineStr"/>
+      <c r="J40" s="34" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -10348,21 +9901,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>系统详情：现券交易系统  |  Bond Trading System</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>战略定位：银行间+交易所双市场统一订单模型，28项功能覆盖报价/订单/定价/风控/STP/做市/数据/分析全链路   |   来源：Slide 40   |   数据输入：CFETS/X-Bond行情与成交回报 / 上交所/深交所债券接口回报 / AMD/Bloomberg实时行情 / 中债估值曲线   |   量化底座：ATP报盘引擎 · IBOR持仓账薄 · 事前风控/合规系统 · 清算结算后台</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="40" t="inlineStr">
         <is>
           <t>模块：现券交易系统  (Bond Trading System)  |  优先级：P1  |  竞品：恒生/金证  |  华锐基础：ATP债券报盘引擎  |  工期：6月  团队：8人</t>
         </is>
@@ -10421,7 +9974,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>A. 市场接入与报价</t>
         </is>
@@ -10458,7 +10011,7 @@
           <t>CFETS API/X-Bond API</t>
         </is>
       </c>
-      <c r="G6" s="42" t="inlineStr">
+      <c r="G6" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10504,7 +10057,7 @@
           <t>上交所/深交所债券接口</t>
         </is>
       </c>
-      <c r="G7" s="43" t="inlineStr">
+      <c r="G7" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10550,7 +10103,7 @@
           <t>CFETS RFQ接口</t>
         </is>
       </c>
-      <c r="G8" s="43" t="inlineStr">
+      <c r="G8" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10576,7 +10129,7 @@
           <t>F02-08</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Bond Connect跨境接入</t>
         </is>
@@ -10596,7 +10149,7 @@
           <t>Bond Connect CFETS接口/SWIFT网关</t>
         </is>
       </c>
-      <c r="G9" s="42" t="inlineStr">
+      <c r="G9" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10612,7 +10165,7 @@
       <c r="J9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
         <is>
           <t>B. 订单管理</t>
         </is>
@@ -10649,7 +10202,7 @@
           <t>CFETS/交易所接口/事前风控</t>
         </is>
       </c>
-      <c r="G11" s="42" t="inlineStr">
+      <c r="G11" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10695,7 +10248,7 @@
           <t>CFETS大宗交易模块</t>
         </is>
       </c>
-      <c r="G12" s="43" t="inlineStr">
+      <c r="G12" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10741,7 +10294,7 @@
           <t>订单引擎/IBOR持仓</t>
         </is>
       </c>
-      <c r="G13" s="43" t="inlineStr">
+      <c r="G13" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10767,7 +10320,7 @@
           <t>F02-12</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>条件单与算法单接口</t>
         </is>
@@ -10787,7 +10340,7 @@
           <t>AMD实时行情/量化定价引擎</t>
         </is>
       </c>
-      <c r="G14" s="42" t="inlineStr">
+      <c r="G14" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10803,7 +10356,7 @@
       <c r="J14" s="11" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="A15" s="43" t="inlineStr">
         <is>
           <t>C. 定价与计算</t>
         </is>
@@ -10840,7 +10393,7 @@
           <t>量化定价引擎(Module 9)/资产主数据</t>
         </is>
       </c>
-      <c r="G16" s="43" t="inlineStr">
+      <c r="G16" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10886,7 +10439,7 @@
           <t>量化定价引擎/信用利差曲线数据</t>
         </is>
       </c>
-      <c r="G17" s="42" t="inlineStr">
+      <c r="G17" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10932,7 +10485,7 @@
           <t>IBOR持仓/AMD实时行情</t>
         </is>
       </c>
-      <c r="G18" s="42" t="inlineStr">
+      <c r="G18" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -10978,7 +10531,7 @@
           <t>量化定价引擎/IBOR持仓</t>
         </is>
       </c>
-      <c r="G19" s="43" t="inlineStr">
+      <c r="G19" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -10994,7 +10547,7 @@
       <c r="J19" s="5" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>D. 交易前风控</t>
         </is>
@@ -11031,7 +10584,7 @@
           <t>事前风控/合规系统(Module 6)</t>
         </is>
       </c>
-      <c r="G21" s="43" t="inlineStr">
+      <c r="G21" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11077,7 +10630,7 @@
           <t>事前风控/合规系统(Module 6)/投资授权书管理</t>
         </is>
       </c>
-      <c r="G22" s="43" t="inlineStr">
+      <c r="G22" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11103,7 +10656,7 @@
           <t>F02-17</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
         <is>
           <t>流动性与市场影响评估</t>
         </is>
@@ -11123,7 +10676,7 @@
           <t>AMD行情平台/债券基础数据</t>
         </is>
       </c>
-      <c r="G23" s="43" t="inlineStr">
+      <c r="G23" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11139,7 +10692,7 @@
       <c r="J23" s="11" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t>E. 成交处理与STP</t>
         </is>
@@ -11176,7 +10729,7 @@
           <t>清算结算后台(Module 14)/中登中债登接口</t>
         </is>
       </c>
-      <c r="G25" s="42" t="inlineStr">
+      <c r="G25" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -11222,7 +10775,7 @@
           <t>IBOR(Module 1)/清算结算(Module 14)/Kafka</t>
         </is>
       </c>
-      <c r="G26" s="42" t="inlineStr">
+      <c r="G26" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -11268,7 +10821,7 @@
           <t>权限管理/IBOR/清算结算</t>
         </is>
       </c>
-      <c r="G27" s="43" t="inlineStr">
+      <c r="G27" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11294,7 +10847,7 @@
           <t>F02-20</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>跨市场净额轧差</t>
         </is>
@@ -11314,7 +10867,7 @@
           <t>清算结算后台(Module 14)</t>
         </is>
       </c>
-      <c r="G28" s="43" t="inlineStr">
+      <c r="G28" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11330,7 +10883,7 @@
       <c r="J28" s="11" t="inlineStr"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="A29" s="44" t="inlineStr">
         <is>
           <t>F. 做市与流动性管理</t>
         </is>
@@ -11347,7 +10900,7 @@
           <t>F02-06</t>
         </is>
       </c>
-      <c r="C30" s="28" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>做市报价接口</t>
         </is>
@@ -11367,7 +10920,7 @@
           <t>做市商系统(Module 15)/IBOR持仓</t>
         </is>
       </c>
-      <c r="G30" s="43" t="inlineStr">
+      <c r="G30" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11393,7 +10946,7 @@
           <t>F02-21</t>
         </is>
       </c>
-      <c r="C31" s="28" t="inlineStr">
+      <c r="C31" s="27" t="inlineStr">
         <is>
           <t>库存管理与头寸监控</t>
         </is>
@@ -11413,7 +10966,7 @@
           <t>IBOR持仓(Module 1)/做市商系统(Module 15)</t>
         </is>
       </c>
-      <c r="G31" s="43" t="inlineStr">
+      <c r="G31" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11439,7 +10992,7 @@
           <t>F02-22</t>
         </is>
       </c>
-      <c r="C32" s="28" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>报价P&amp;L归因</t>
         </is>
@@ -11459,7 +11012,7 @@
           <t>IBOR持仓/实时行情/成交记录</t>
         </is>
       </c>
-      <c r="G32" s="43" t="inlineStr">
+      <c r="G32" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11475,7 +11028,7 @@
       <c r="J32" s="11" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>G. 行情与数据接入</t>
         </is>
@@ -11512,7 +11065,7 @@
           <t>AMD行情平台/Bloomberg API</t>
         </is>
       </c>
-      <c r="G34" s="43" t="inlineStr">
+      <c r="G34" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11558,7 +11111,7 @@
           <t>中债数据接口/AMD估值平台</t>
         </is>
       </c>
-      <c r="G35" s="43" t="inlineStr">
+      <c r="G35" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11604,7 +11157,7 @@
           <t>中债登/Wind数据接口/资产主数据系统</t>
         </is>
       </c>
-      <c r="G36" s="43" t="inlineStr">
+      <c r="G36" s="42" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -11620,7 +11173,7 @@
       <c r="J36" s="5" t="inlineStr"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="40" t="inlineStr">
         <is>
           <t>H. 交易分析与报表</t>
         </is>
@@ -11637,7 +11190,7 @@
           <t>F02-26</t>
         </is>
       </c>
-      <c r="C38" s="28" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>交易执行质量分析(TCA)</t>
         </is>
@@ -11657,7 +11210,7 @@
           <t>成交记录/AMD实时行情/中债估值</t>
         </is>
       </c>
-      <c r="G38" s="42" t="inlineStr">
+      <c r="G38" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -11703,7 +11256,7 @@
           <t>成交记录/事前风控系统/报表引擎</t>
         </is>
       </c>
-      <c r="G39" s="43" t="inlineStr">
+      <c r="G39" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -11729,7 +11282,7 @@
           <t>F02-28</t>
         </is>
       </c>
-      <c r="C40" s="28" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>交易统计分析</t>
         </is>
@@ -11749,7 +11302,7 @@
           <t>成交记录/IBOR持仓</t>
         </is>
       </c>
-      <c r="G40" s="43" t="inlineStr">
+      <c r="G40" s="42" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -11765,17 +11318,17 @@
       <c r="J40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="41" t="inlineStr">
+      <c r="A41" s="40" t="inlineStr">
         <is>
           <t>合计 28项功能  |  P1: 19项  |  P2: 9项</t>
         </is>
       </c>
-      <c r="H41" s="21">
+      <c r="H41" s="20">
         <f>SUM(H5:H40)</f>
         <v/>
       </c>
-      <c r="I41" s="35" t="inlineStr"/>
-      <c r="J41" s="35" t="inlineStr"/>
+      <c r="I41" s="34" t="inlineStr"/>
+      <c r="J41" s="34" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -11819,21 +11372,21 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="39" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
         <is>
           <t>系统详情：组合管理+绩效归因  |  Portfolio Mgmt &amp; Perf</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>战略定位：17项功能含量化底座集成；Slide44全景展开   |   来源：Slide 44   |   数据输入：交易数据 / 头寸数据 / 行情数据 / 估值数据   |   量化底座：定价计算 · 利率曲线 · 因子模型</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="40" t="inlineStr">
         <is>
           <t>模块：组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)  |  优先级：P1  |  竞品：SimCorp/衡泰  |  华锐基础：M9 PMS模块  |  工期：12月  团队：12人</t>
         </is>
@@ -11892,7 +11445,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>A. 组合分析</t>
         </is>
@@ -11929,7 +11482,7 @@
           <t>AMD行情平台/估值数据</t>
         </is>
       </c>
-      <c r="G6" s="42" t="inlineStr">
+      <c r="G6" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -11975,7 +11528,7 @@
           <t>量化定价引擎/AMD行情</t>
         </is>
       </c>
-      <c r="G7" s="42" t="inlineStr">
+      <c r="G7" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12021,7 +11574,7 @@
           <t>IBOR头寸/AMD历史行情</t>
         </is>
       </c>
-      <c r="G8" s="43" t="inlineStr">
+      <c r="G8" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -12037,7 +11590,7 @@
       <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
         <is>
           <t>B. 风险计量</t>
         </is>
@@ -12074,7 +11627,7 @@
           <t>FICC风险计量平台/量化定价引擎</t>
         </is>
       </c>
-      <c r="G10" s="42" t="inlineStr">
+      <c r="G10" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12120,7 +11673,7 @@
           <t>量化定价引擎Greeks接口</t>
         </is>
       </c>
-      <c r="G11" s="42" t="inlineStr">
+      <c r="G11" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12166,7 +11719,7 @@
           <t>FICC风险计量平台</t>
         </is>
       </c>
-      <c r="G12" s="42" t="inlineStr">
+      <c r="G12" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12182,7 +11735,7 @@
       <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>C. 绩效归因</t>
         </is>
@@ -12219,7 +11772,7 @@
           <t>AMD中债估值/IBOR持仓</t>
         </is>
       </c>
-      <c r="G14" s="43" t="inlineStr">
+      <c r="G14" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -12265,7 +11818,7 @@
           <t>IBOR持仓/AMD行情/指数数据</t>
         </is>
       </c>
-      <c r="G15" s="42" t="inlineStr">
+      <c r="G15" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12281,7 +11834,7 @@
       <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="A16" s="43" t="inlineStr">
         <is>
           <t>D. 组合优化与再平衡</t>
         </is>
@@ -12318,7 +11871,7 @@
           <t>IBOR/现券交易系统</t>
         </is>
       </c>
-      <c r="G17" s="42" t="inlineStr">
+      <c r="G17" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12364,7 +11917,7 @@
           <t>事前风控/合规/IBOR/现券系统</t>
         </is>
       </c>
-      <c r="G18" s="42" t="inlineStr">
+      <c r="G18" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12390,7 +11943,7 @@
           <t>F07-11</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>资产配置策略分析</t>
         </is>
@@ -12410,7 +11963,7 @@
           <t>AMD宏观数据/因子模型</t>
         </is>
       </c>
-      <c r="G19" s="42" t="inlineStr">
+      <c r="G19" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12436,7 +11989,7 @@
           <t>F07-12</t>
         </is>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>固收+策略分析</t>
         </is>
@@ -12456,7 +12009,7 @@
           <t>IBOR/利率衍生品系统</t>
         </is>
       </c>
-      <c r="G20" s="42" t="inlineStr">
+      <c r="G20" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12482,7 +12035,7 @@
           <t>F07-13</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
         <is>
           <t>量化策略组合分析</t>
         </is>
@@ -12502,7 +12055,7 @@
           <t>策略投资/量化系统</t>
         </is>
       </c>
-      <c r="G21" s="42" t="inlineStr">
+      <c r="G21" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12518,7 +12071,7 @@
       <c r="J21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t>E. 流动性管理</t>
         </is>
@@ -12555,7 +12108,7 @@
           <t>AMD行情/IBOR持仓</t>
         </is>
       </c>
-      <c r="G23" s="43" t="inlineStr">
+      <c r="G23" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -12571,7 +12124,7 @@
       <c r="J23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="A24" s="44" t="inlineStr">
         <is>
           <t>F. 量化底座集成</t>
         </is>
@@ -12588,7 +12141,7 @@
           <t>F07-15</t>
         </is>
       </c>
-      <c r="C25" s="28" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
         <is>
           <t>定价计算集成</t>
         </is>
@@ -12608,7 +12161,7 @@
           <t>量化定价引擎</t>
         </is>
       </c>
-      <c r="G25" s="42" t="inlineStr">
+      <c r="G25" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12654,7 +12207,7 @@
           <t>AMD行情平台/量化定价引擎</t>
         </is>
       </c>
-      <c r="G26" s="43" t="inlineStr">
+      <c r="G26" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -12700,7 +12253,7 @@
           <t>AMD历史行情/IBOR持仓</t>
         </is>
       </c>
-      <c r="G27" s="42" t="inlineStr">
+      <c r="G27" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -12716,17 +12269,17 @@
       <c r="J27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="41" t="inlineStr">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>合计 17项功能  |  P1: 13项  |  P2: 4项</t>
         </is>
       </c>
-      <c r="H28" s="21">
+      <c r="H28" s="20">
         <f>SUM(H5:H27)</f>
         <v/>
       </c>
-      <c r="I28" s="35" t="inlineStr"/>
-      <c r="J28" s="35" t="inlineStr"/>
+      <c r="I28" s="34" t="inlineStr"/>
+      <c r="J28" s="34" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P1优先启动计划" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_IBOR投资账薄管理" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_现券交易系统" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_FICC风险计量平台" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1077,7 +1078,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>FICC Risk Measurement</t>
+          <t>FICC Risk Measurement Platform</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1110,9 +1111,9 @@
           <t>L4</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>大</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -1122,21 +1123,21 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>ARC风险引擎</t>
+          <t>ARC风险引擎/IBOR</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>替代衡泰老旧系统，信创切入口</t>
+          <t>替代衡泰老旧系统，信创切入口；覆盖投前/投中/投后全生命周期风险管理；对应PPT Slide 52</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4446,7 +4447,7 @@
     <row r="67" ht="20" customHeight="1">
       <c r="A67" s="22" t="inlineStr">
         <is>
-          <t>【P1】 FICC风险计量平台  (FICC Risk Measurement)</t>
+          <t>【P1】 FICC风险计量平台  (FICC Risk Measurement Platform)</t>
         </is>
       </c>
     </row>
@@ -4468,26 +4469,26 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>VaR/CVaR/ES计算</t>
+          <t>组合What-if分析</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>历史模拟法/参数法/蒙特卡洛三模式，置信度99%/99.5%可选</t>
+          <t>What-if情景建模，Duration &amp; Convexity影响分析，VaR贡献分解，风险因子敞口，集中度分析</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G68" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G68" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H68" s="8" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
@@ -4508,12 +4509,12 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>压力测试情景库</t>
+          <t>授权敞口分析</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>内置924行情/2015股灾/2020疫情等10+情景，支持自定义</t>
+          <t>交易前限额验证，交易对手/集中度/监管/组合约束多维度限额检查，Pre-trade拦截</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -4527,7 +4528,7 @@
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
@@ -4548,26 +4549,26 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>限额体系与超限预警</t>
+          <t>投资预测分析</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>交易员/策略/产品/公司4级限额，实时穿透预警，告警推送</t>
+          <t>P&amp;L与风险归因预测建模，收益率曲线/利差/波动率因子预测，组合构建优化，多情景对比分析</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G70" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G70" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
@@ -4588,12 +4589,12 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>信用风险（CCR）</t>
+          <t>实时风险计量</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>交易对手敞口实时聚合，EEPE/PFE/CVA估算</t>
+          <t>Real-time DV01/CS01，Live VaR，Dynamic Greeks，日内P&amp;L与归因，风险限额利用率实时展示</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -4607,7 +4608,7 @@
         </is>
       </c>
       <c r="H71" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
@@ -4628,12 +4629,12 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>希腊字母（Greeks）</t>
+          <t>交易对手风险实时监控</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/DV01日内实时计算，覆盖固收+衍生品</t>
+          <t>实时敞口聚合，抵押品监控，信用限额使用率，结算风险，净额结算协议管理</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -4647,7 +4648,7 @@
         </is>
       </c>
       <c r="H72" s="8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" ht="28" customHeight="1">
@@ -4668,39 +4669,72 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>风险报告自动化</t>
+          <t>流动性分析与交易成本</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>每日风险报告（Excel/PDF）自动生成，支持监管报送格式</t>
+          <t>执行风险监控，市场冲击分析，流动性成本追踪，滑点计量，最优执行合规</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G73" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H73" s="8" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
-        </is>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>F04-07</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>实时风险全景图</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>实时持仓追踪，流式风险指标，实时限额监控，告警管理，异常跟踪仪表板</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G74" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="75" ht="28" customHeight="1">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -4710,17 +4744,17 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>F05-01</t>
+          <t>F04-08</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>实时CEP监控引擎</t>
+          <t>DV01/CS01计算</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>基于复杂事件处理（CEP），毫秒级事件流检测，滑动窗口聚合</t>
+          <t>dPV/dy价格敏感度，信用利差敏感度，分桶移动与关键期限，平行与非平行冲击</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
@@ -4734,13 +4768,13 @@
         </is>
       </c>
       <c r="H75" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -4750,37 +4784,37 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>F05-02</t>
+          <t>F04-09</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>异常价格检测</t>
+          <t>Greeks与敏感度计算</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>基于历史分位数/实时行情计算价格偏离度，动态阈值自适应</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，覆盖固收全品种与衍生品</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G76" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G76" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" ht="28" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -4790,37 +4824,37 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>F05-03</t>
+          <t>F04-10</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>AI异常识别模型</t>
+          <t>VaR模型</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>机器学习（XGBoost/LSTM）训练异常交易识别模型，在线推理</t>
+          <t>参数法/历史模拟法/蒙特卡洛三模式，Expected Shortfall (ES)，回测与例外检验</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G77" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G77" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" ht="28" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -4830,37 +4864,37 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>F05-04</t>
+          <t>F04-11</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>规则引擎（可配置）</t>
+          <t>压力测试与情景分析</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>No-Code规则配置界面，合规人员自助维护检测规则</t>
+          <t>内置历史情景（GFC/COVID-19/利率冲击），假设情景（曲线扭转/利差走阔），反向压力测试</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G78" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G78" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H78" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" ht="28" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -4870,44 +4904,77 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>F05-05</t>
+          <t>F04-12</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>监管报送自动化</t>
+          <t>估值与盈亏分解</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>一键生成证监会/人行格式异常交易报告，历史追溯查询</t>
+          <t>Carry &amp; Roll-down，曲线效应，信用利差贡献，择券贡献，基于因子的盈亏多维分解</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" ht="28" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>F04-13</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>历史风险回溯</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>历史VaR计算回放，压力测试结果归档，风险趋势分析，限额例外统计，VaR回测报告</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G79" s="24" t="inlineStr">
+      <c r="G80" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H79" s="8" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
-        </is>
+      <c r="H80" s="8" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="81" ht="28" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -4917,17 +4984,17 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>F06-01</t>
+          <t>F04-14</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>投资策略合规规则库</t>
+          <t>绩效归因与风险计量</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
+          <t>收益率曲线效应，信用利差分解，行业配置效应，个券择券，Carry &amp; Roll-down贡献</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -4947,7 +5014,7 @@
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -4957,37 +5024,37 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>F06-02</t>
+          <t>F04-15</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>实时订单拦截</t>
+          <t>监管报表与风控日报</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
+          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G82" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" ht="28" customHeight="1">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -4997,17 +5064,17 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>F06-03</t>
+          <t>F04-16</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>限额多维度检查</t>
+          <t>数据底座与IBOR集成</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
+          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
@@ -5021,13 +5088,13 @@
         </is>
       </c>
       <c r="H83" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -5037,37 +5104,37 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>F06-04</t>
+          <t>F04-17</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>合规审批工作流</t>
+          <t>收益率曲线与波动率曲面</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>超限申请→审批→记录全流程，支持移动端审批</t>
+          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G84" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G84" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" ht="28" customHeight="1">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -5077,84 +5144,84 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>F06-05</t>
+          <t>F04-18</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>监管白/黑名单</t>
+          <t>HPC计算网格</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
+          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G85" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G85" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H85" s="8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="28" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>F07-01</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>债券横截面与时序分析</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>横截面信号与实际收益相关性&gt;0.3</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86" ht="28" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>F04-19</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>AI风险预警</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>异常检测（ML模型），预测性分析，模式识别，智能告警，新业务合规风险预分析</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H87" s="8" t="n">
-        <v>35</v>
+      <c r="H86" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="28" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -5164,37 +5231,37 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>F07-02</t>
+          <t>F05-01</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>实时CEP监控引擎</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+          <t>基于复杂事件处理（CEP），毫秒级事件流检测，滑动窗口聚合</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
-        </is>
-      </c>
-      <c r="G88" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G88" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H88" s="8" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -5204,27 +5271,27 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>F07-03</t>
+          <t>F05-02</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>组合相关度分析</t>
+          <t>异常价格检测</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+          <t>基于历史分位数/实时行情计算价格偏离度，动态阈值自适应</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>相关矩阵计算&lt;30s（500券组合）</t>
-        </is>
-      </c>
-      <c r="G89" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H89" s="8" t="n">
@@ -5234,7 +5301,7 @@
     <row r="90" ht="28" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -5244,22 +5311,22 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F05-03</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>AI异常识别模型</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+          <t>机器学习（XGBoost/LSTM）训练异常交易识别模型，在线推理</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G90" s="23" t="inlineStr">
@@ -5268,13 +5335,13 @@
         </is>
       </c>
       <c r="H90" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91" ht="28" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -5284,37 +5351,37 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>F07-05</t>
+          <t>F05-04</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析</t>
+          <t>规则引擎（可配置）</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+          <t>No-Code规则配置界面，合规人员自助维护检测规则</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H91" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" ht="28" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -5324,77 +5391,44 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F05-05</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>极端事件分析</t>
+          <t>监管报送自动化</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+          <t>一键生成证监会/人行格式异常交易报告，历史追溯查询</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H92" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="93" ht="28" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>F07-07</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>指数比较分析</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
-        </is>
-      </c>
-      <c r="G93" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H93" s="8" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
+        </is>
       </c>
     </row>
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -5404,22 +5438,22 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F06-01</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>投资策略合规规则库</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G94" s="23" t="inlineStr">
@@ -5428,13 +5462,13 @@
         </is>
       </c>
       <c r="H94" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -5444,37 +5478,37 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>F07-09</t>
+          <t>F06-02</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>虚拟组合分析</t>
+          <t>实时订单拦截</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G95" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H95" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -5484,22 +5518,22 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>F07-10</t>
+          <t>F06-03</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>再平衡方案试算与比较</t>
+          <t>限额多维度检查</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G96" s="23" t="inlineStr">
@@ -5508,13 +5542,13 @@
         </is>
       </c>
       <c r="H96" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -5524,37 +5558,37 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>F07-11</t>
+          <t>F06-04</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>合规审批工作流</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+          <t>超限申请→审批→记录全流程，支持移动端审批</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%</t>
-        </is>
-      </c>
-      <c r="G97" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G97" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -5564,71 +5598,38 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>F07-12</t>
+          <t>F06-05</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>固收+策略分析</t>
+          <t>监管白/黑名单</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
-        </is>
-      </c>
-      <c r="G98" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G98" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H98" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="99" ht="28" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>F07-13</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>量化策略组合分析</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>策略容量计算误差&lt;5%</t>
-        </is>
-      </c>
-      <c r="G99" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H99" s="8" t="n">
-        <v>35</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="28" customHeight="1">
@@ -5644,31 +5645,31 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>F07-14</t>
+          <t>F07-01</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>流动性分析</t>
+          <t>债券横截面与时序分析</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
-        </is>
-      </c>
-      <c r="G100" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>横截面信号与实际收益相关性&gt;0.3</t>
+        </is>
+      </c>
+      <c r="G100" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H100" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101" ht="28" customHeight="1">
@@ -5684,22 +5685,22 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>F07-15</t>
+          <t>F07-02</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>定价计算集成</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -5708,7 +5709,7 @@
         </is>
       </c>
       <c r="H101" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102" ht="28" customHeight="1">
@@ -5724,22 +5725,22 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>F07-16</t>
+          <t>F07-03</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>利率曲线集成</t>
+          <t>组合相关度分析</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+          <t>相关矩阵计算&lt;30s（500券组合）</t>
         </is>
       </c>
       <c r="G102" s="24" t="inlineStr">
@@ -5748,7 +5749,7 @@
         </is>
       </c>
       <c r="H102" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" ht="28" customHeight="1">
@@ -5764,22 +5765,22 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>F07-17</t>
+          <t>F07-04</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>因子模型</t>
+          <t>情景分析</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -5788,20 +5789,53 @@
         </is>
       </c>
       <c r="H103" s="8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
-        </is>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>F07-05</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>敏感度分析</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="105" ht="28" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -5811,22 +5845,22 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>F08-01</t>
+          <t>F07-06</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>因子模型框架</t>
+          <t>极端事件分析</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>历史情景复现误差&lt;1%</t>
         </is>
       </c>
       <c r="G105" s="23" t="inlineStr">
@@ -5835,13 +5869,13 @@
         </is>
       </c>
       <c r="H105" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106" ht="28" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -5851,37 +5885,37 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F07-07</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>指数比较分析</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G106" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
+        </is>
+      </c>
+      <c r="G106" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H106" s="8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107" ht="28" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -5891,22 +5925,22 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F07-08</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>信号生成与调度</t>
+          <t>绩效归因（Brinson）</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5921,7 +5955,7 @@
     <row r="108" ht="28" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -5931,578 +5965,611 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>F08-04</t>
+          <t>F07-09</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>低延迟执行接口</t>
+          <t>虚拟组合分析</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G108" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H108" s="8" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>F07-10</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>再平衡方案试算与比较</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="110" ht="28" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>F07-11</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>资产配置策略分析</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+        </is>
+      </c>
+      <c r="G110" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>F07-12</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>固收+策略分析</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+        </is>
+      </c>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>F07-13</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>量化策略组合分析</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>策略容量计算误差&lt;5%</t>
+        </is>
+      </c>
+      <c r="G112" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>F07-14</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>流动性分析</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" ht="28" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>F07-15</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>定价计算集成</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="G114" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" ht="28" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G115" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" ht="28" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>F07-17</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>因子模型</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+        </is>
+      </c>
+      <c r="G116" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="28" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
           <t>策略投资/量化</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>因子模型框架</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G118" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" ht="28" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Tick级回测引擎</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G119" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="120" ht="28" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>信号生成与调度</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G120" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="121" ht="28" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>低延迟执行接口</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G121" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="122" ht="28" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>F08-05</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>实时策略监控</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr">
+      <c r="E122" s="5" t="inlineStr">
         <is>
           <t>持仓/PnL/回撤/Sharpe实时看板，风险触发自动平仓</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
+      <c r="F122" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G109" s="24" t="inlineStr">
+      <c r="G122" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H109" s="8" t="n">
+      <c r="H122" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="26" t="inlineStr">
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="26" t="inlineStr">
         <is>
           <t>【P2】 定价平台  (Pricing Platform)</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="11" t="inlineStr">
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="11" t="inlineStr">
         <is>
           <t>定价平台</t>
         </is>
       </c>
-      <c r="B111" s="10" t="inlineStr">
+      <c r="B124" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C111" s="10" t="inlineStr">
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>F09-01</t>
         </is>
       </c>
-      <c r="D111" s="27" t="inlineStr">
+      <c r="D124" s="27" t="inlineStr">
         <is>
           <t>期限结构模型</t>
         </is>
       </c>
-      <c r="E111" s="11" t="inlineStr">
+      <c r="E124" s="11" t="inlineStr">
         <is>
           <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
         </is>
       </c>
-      <c r="F111" s="11" t="inlineStr">
+      <c r="F124" s="11" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G111" s="28" t="inlineStr">
+      <c r="G124" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H111" s="13" t="n">
+      <c r="H124" s="13" t="n">
         <v>60</v>
-      </c>
-    </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="A112" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C112" s="10" t="inlineStr">
-        <is>
-          <t>F09-02</t>
-        </is>
-      </c>
-      <c r="D112" s="27" t="inlineStr">
-        <is>
-          <t>蒙特卡洛求解器</t>
-        </is>
-      </c>
-      <c r="E112" s="11" t="inlineStr">
-        <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
-        </is>
-      </c>
-      <c r="F112" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G112" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H112" s="13" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="113" ht="28" customHeight="1">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C113" s="10" t="inlineStr">
-        <is>
-          <t>F09-03</t>
-        </is>
-      </c>
-      <c r="D113" s="27" t="inlineStr">
-        <is>
-          <t>有限差分（PDE）</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
-        </is>
-      </c>
-      <c r="F113" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G113" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H113" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="114" ht="28" customHeight="1">
-      <c r="A114" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C114" s="10" t="inlineStr">
-        <is>
-          <t>F09-04</t>
-        </is>
-      </c>
-      <c r="D114" s="27" t="inlineStr">
-        <is>
-          <t>实时Greeks</t>
-        </is>
-      </c>
-      <c r="E114" s="11" t="inlineStr">
-        <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
-        </is>
-      </c>
-      <c r="F114" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G114" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H114" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1">
-      <c r="A115" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B115" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C115" s="10" t="inlineStr">
-        <is>
-          <t>F09-05</t>
-        </is>
-      </c>
-      <c r="D115" s="27" t="inlineStr">
-        <is>
-          <t>定价服务微服务架构</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
-        </is>
-      </c>
-      <c r="F115" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G115" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H115" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="116" ht="28" customHeight="1">
-      <c r="A116" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C116" s="10" t="inlineStr">
-        <is>
-          <t>F09-06</t>
-        </is>
-      </c>
-      <c r="D116" s="27" t="inlineStr">
-        <is>
-          <t>历史估值回测</t>
-        </is>
-      </c>
-      <c r="E116" s="11" t="inlineStr">
-        <is>
-          <t>基于历史行情重放定价误差分析，模型验证框架</t>
-        </is>
-      </c>
-      <c r="F116" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G116" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H116" s="13" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 销售交易  (Sales Trading)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="28" customHeight="1">
-      <c r="A118" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C118" s="10" t="inlineStr">
-        <is>
-          <t>F10-01</t>
-        </is>
-      </c>
-      <c r="D118" s="27" t="inlineStr">
-        <is>
-          <t>销交工作台</t>
-        </is>
-      </c>
-      <c r="E118" s="11" t="inlineStr">
-        <is>
-          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
-        </is>
-      </c>
-      <c r="F118" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G118" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H118" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="119" ht="28" customHeight="1">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C119" s="10" t="inlineStr">
-        <is>
-          <t>F10-02</t>
-        </is>
-      </c>
-      <c r="D119" s="27" t="inlineStr">
-        <is>
-          <t>债券过滤与筛选</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
-        </is>
-      </c>
-      <c r="F119" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G119" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H119" s="13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120" ht="28" customHeight="1">
-      <c r="A120" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C120" s="10" t="inlineStr">
-        <is>
-          <t>F10-03</t>
-        </is>
-      </c>
-      <c r="D120" s="27" t="inlineStr">
-        <is>
-          <t>报价撮合与对价</t>
-        </is>
-      </c>
-      <c r="E120" s="11" t="inlineStr">
-        <is>
-          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
-        </is>
-      </c>
-      <c r="F120" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G120" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H120" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="121" ht="28" customHeight="1">
-      <c r="A121" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
-        <is>
-          <t>F10-04</t>
-        </is>
-      </c>
-      <c r="D121" s="27" t="inlineStr">
-        <is>
-          <t>交易执行与审批</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr">
-        <is>
-          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
-        </is>
-      </c>
-      <c r="F121" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G121" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H121" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="122" ht="28" customHeight="1">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C122" s="10" t="inlineStr">
-        <is>
-          <t>F10-05</t>
-        </is>
-      </c>
-      <c r="D122" s="27" t="inlineStr">
-        <is>
-          <t>风控检查</t>
-        </is>
-      </c>
-      <c r="E122" s="11" t="inlineStr">
-        <is>
-          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
-        </is>
-      </c>
-      <c r="F122" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G122" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H122" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="123" ht="28" customHeight="1">
-      <c r="A123" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C123" s="10" t="inlineStr">
-        <is>
-          <t>F10-06</t>
-        </is>
-      </c>
-      <c r="D123" s="27" t="inlineStr">
-        <is>
-          <t>智能推荐系统</t>
-        </is>
-      </c>
-      <c r="E123" s="11" t="inlineStr">
-        <is>
-          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
-        </is>
-      </c>
-      <c r="F123" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G123" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H123" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
-        </is>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B125" s="10" t="inlineStr">
@@ -6512,37 +6579,37 @@
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>F11-01</t>
+          <t>F09-02</t>
         </is>
       </c>
       <c r="D125" s="27" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G125" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G125" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H125" s="13" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -6552,17 +6619,17 @@
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D126" s="27" t="inlineStr">
         <is>
-          <t>CDS/CLN定价</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr">
@@ -6576,13 +6643,13 @@
         </is>
       </c>
       <c r="H126" s="13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
@@ -6592,37 +6659,37 @@
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D127" s="27" t="inlineStr">
         <is>
-          <t>信用评级动态监控</t>
+          <t>实时Greeks</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G127" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H127" s="13" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B128" s="10" t="inlineStr">
@@ -6632,17 +6699,17 @@
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D128" s="27" t="inlineStr">
         <is>
-          <t>违约概率（PD）建模</t>
+          <t>定价服务微服务架构</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr">
@@ -6662,7 +6729,7 @@
     <row r="129" ht="28" customHeight="1">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
@@ -6672,44 +6739,44 @@
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>F11-05</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D129" s="27" t="inlineStr">
         <is>
-          <t>集中度限额管理</t>
+          <t>历史估值回测</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>行业/发行人/评级集中度多维限额，超限预警</t>
+          <t>基于历史行情重放定价误差分析，模型验证框架</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G129" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G129" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H129" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="26" t="inlineStr">
         <is>
-          <t>【P2】 投顾服务  (Investment Advisory)</t>
+          <t>【P2】 销售交易  (Sales Trading)</t>
         </is>
       </c>
     </row>
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -6719,17 +6786,17 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>F12-01</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D131" s="27" t="inlineStr">
         <is>
-          <t>投顾工作台</t>
+          <t>销交工作台</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
+          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr">
@@ -6749,7 +6816,7 @@
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -6759,37 +6826,37 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D132" s="27" t="inlineStr">
         <is>
-          <t>客户终端</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G132" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G132" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H132" s="13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -6799,17 +6866,17 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D133" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
+          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
@@ -6823,13 +6890,13 @@
         </is>
       </c>
       <c r="H133" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -6839,37 +6906,37 @@
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D134" s="27" t="inlineStr">
         <is>
-          <t>账户分析报告</t>
+          <t>交易执行与审批</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G134" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G134" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H134" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -6879,17 +6946,17 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D135" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>风控检查</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
@@ -6909,7 +6976,7 @@
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -6919,44 +6986,44 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>F12-06</t>
+          <t>F10-06</t>
         </is>
       </c>
       <c r="D136" s="27" t="inlineStr">
         <is>
-          <t>客户服务与基础服务</t>
+          <t>智能推荐系统</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G136" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G136" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H136" s="13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="26" t="inlineStr">
         <is>
-          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
         </is>
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -6966,17 +7033,17 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F11-01</t>
         </is>
       </c>
       <c r="D138" s="27" t="inlineStr">
         <is>
-          <t>TRS交易端</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
@@ -6996,7 +7063,7 @@
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -7006,37 +7073,37 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D139" s="27" t="inlineStr">
         <is>
-          <t>TRS客户端</t>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G139" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G139" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H139" s="13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -7046,17 +7113,17 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D140" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr">
@@ -7076,7 +7143,7 @@
     <row r="141" ht="28" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -7086,17 +7153,17 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F11-04</t>
         </is>
       </c>
       <c r="D141" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>违约概率（PD）建模</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr">
@@ -7110,325 +7177,779 @@
         </is>
       </c>
       <c r="H141" s="13" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142" ht="28" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C142" s="10" t="inlineStr">
+        <is>
+          <t>F11-05</t>
+        </is>
+      </c>
+      <c r="D142" s="27" t="inlineStr">
+        <is>
+          <t>集中度限额管理</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="inlineStr">
+        <is>
+          <t>行业/发行人/评级集中度多维限额，超限预警</t>
+        </is>
+      </c>
+      <c r="F142" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G142" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H142" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 投顾服务  (Investment Advisory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>F12-01</t>
+        </is>
+      </c>
+      <c r="D144" s="27" t="inlineStr">
+        <is>
+          <t>投顾工作台</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G144" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H144" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>F12-02</t>
+        </is>
+      </c>
+      <c r="D145" s="27" t="inlineStr">
+        <is>
+          <t>客户终端</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+        </is>
+      </c>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G145" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H145" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>F12-03</t>
+        </is>
+      </c>
+      <c r="D146" s="27" t="inlineStr">
+        <is>
+          <t>投资建议书管理</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="inlineStr">
+        <is>
+          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
+        </is>
+      </c>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G146" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H146" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" ht="28" customHeight="1">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C147" s="10" t="inlineStr">
+        <is>
+          <t>F12-04</t>
+        </is>
+      </c>
+      <c r="D147" s="27" t="inlineStr">
+        <is>
+          <t>账户分析报告</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr">
+        <is>
+          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+        </is>
+      </c>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H147" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="148" ht="28" customHeight="1">
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>F12-05</t>
+        </is>
+      </c>
+      <c r="D148" s="27" t="inlineStr">
+        <is>
+          <t>投研报告服务</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G148" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H148" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" ht="28" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>F12-06</t>
+        </is>
+      </c>
+      <c r="D149" s="27" t="inlineStr">
+        <is>
+          <t>客户服务与基础服务</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+        </is>
+      </c>
+      <c r="F149" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G149" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H149" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="28" customHeight="1">
+      <c r="A151" s="11" t="inlineStr">
+        <is>
           <t>TRS收益互换</t>
         </is>
       </c>
-      <c r="B142" s="10" t="inlineStr">
+      <c r="B151" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C142" s="10" t="inlineStr">
+      <c r="C151" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D151" s="27" t="inlineStr">
+        <is>
+          <t>TRS交易端</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr">
+        <is>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+        </is>
+      </c>
+      <c r="F151" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G151" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H151" s="13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="152" ht="28" customHeight="1">
+      <c r="A152" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C152" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D152" s="27" t="inlineStr">
+        <is>
+          <t>TRS客户端</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="inlineStr">
+        <is>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+        </is>
+      </c>
+      <c r="F152" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G152" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H152" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="153" ht="28" customHeight="1">
+      <c r="A153" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B153" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C153" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D153" s="27" t="inlineStr">
+        <is>
+          <t>TRS管理端</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="inlineStr">
+        <is>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+        </is>
+      </c>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G153" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H153" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="154" ht="28" customHeight="1">
+      <c r="A154" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D154" s="27" t="inlineStr">
+        <is>
+          <t>自动对冲</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+        </is>
+      </c>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G154" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H154" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155" ht="28" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C155" s="10" t="inlineStr">
         <is>
           <t>F13-05</t>
         </is>
       </c>
-      <c r="D142" s="27" t="inlineStr">
+      <c r="D155" s="27" t="inlineStr">
         <is>
           <t>通知与确认文件</t>
         </is>
       </c>
-      <c r="E142" s="11" t="inlineStr">
+      <c r="E155" s="11" t="inlineStr">
         <is>
           <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
         </is>
       </c>
-      <c r="F142" s="11" t="inlineStr">
+      <c r="F155" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G142" s="24" t="inlineStr">
+      <c r="G155" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H142" s="13" t="n">
+      <c r="H155" s="13" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="143" ht="28" customHeight="1">
-      <c r="A143" s="11" t="inlineStr">
+    <row r="156" ht="28" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
         <is>
           <t>TRS收益互换</t>
         </is>
       </c>
-      <c r="B143" s="10" t="inlineStr">
+      <c r="B156" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C143" s="10" t="inlineStr">
+      <c r="C156" s="10" t="inlineStr">
         <is>
           <t>F13-06</t>
         </is>
       </c>
-      <c r="D143" s="27" t="inlineStr">
+      <c r="D156" s="27" t="inlineStr">
         <is>
           <t>系统集成</t>
         </is>
       </c>
-      <c r="E143" s="11" t="inlineStr">
+      <c r="E156" s="11" t="inlineStr">
         <is>
           <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
         </is>
       </c>
-      <c r="F143" s="11" t="inlineStr">
+      <c r="F156" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G143" s="23" t="inlineStr">
+      <c r="G156" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H143" s="13" t="n">
+      <c r="H156" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="29" t="inlineStr">
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="28" customHeight="1">
-      <c r="A145" s="16" t="inlineStr">
+    <row r="158" ht="28" customHeight="1">
+      <c r="A158" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B145" s="15" t="inlineStr">
+      <c r="B158" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C145" s="15" t="inlineStr">
+      <c r="C158" s="15" t="inlineStr">
         <is>
           <t>F15-01</t>
         </is>
       </c>
-      <c r="D145" s="30" t="inlineStr">
+      <c r="D158" s="30" t="inlineStr">
         <is>
           <t>双边报价引擎</t>
         </is>
       </c>
-      <c r="E145" s="16" t="inlineStr">
+      <c r="E158" s="16" t="inlineStr">
         <is>
           <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
-      <c r="F145" s="16" t="inlineStr">
+      <c r="F158" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G145" s="28" t="inlineStr">
+      <c r="G158" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H145" s="18" t="n">
+      <c r="H158" s="18" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="146" ht="28" customHeight="1">
-      <c r="A146" s="16" t="inlineStr">
+    <row r="159" ht="28" customHeight="1">
+      <c r="A159" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B146" s="15" t="inlineStr">
+      <c r="B159" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C146" s="15" t="inlineStr">
+      <c r="C159" s="15" t="inlineStr">
         <is>
           <t>F15-02</t>
         </is>
       </c>
-      <c r="D146" s="30" t="inlineStr">
+      <c r="D159" s="30" t="inlineStr">
         <is>
           <t>库存风险实时管理</t>
         </is>
       </c>
-      <c r="E146" s="16" t="inlineStr">
+      <c r="E159" s="16" t="inlineStr">
         <is>
           <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
-      <c r="F146" s="16" t="inlineStr">
+      <c r="F159" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G146" s="28" t="inlineStr">
+      <c r="G159" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H146" s="18" t="n">
+      <c r="H159" s="18" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="147" ht="28" customHeight="1">
-      <c r="A147" s="16" t="inlineStr">
+    <row r="160" ht="28" customHeight="1">
+      <c r="A160" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B147" s="15" t="inlineStr">
+      <c r="B160" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C147" s="15" t="inlineStr">
+      <c r="C160" s="15" t="inlineStr">
         <is>
           <t>F15-03</t>
         </is>
       </c>
-      <c r="D147" s="30" t="inlineStr">
+      <c r="D160" s="30" t="inlineStr">
         <is>
           <t>报价优化算法</t>
         </is>
       </c>
-      <c r="E147" s="16" t="inlineStr">
+      <c r="E160" s="16" t="inlineStr">
         <is>
           <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
-      <c r="F147" s="16" t="inlineStr">
+      <c r="F160" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G147" s="28" t="inlineStr">
+      <c r="G160" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H147" s="18" t="n">
+      <c r="H160" s="18" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="148" ht="28" customHeight="1">
-      <c r="A148" s="16" t="inlineStr">
+    <row r="161" ht="28" customHeight="1">
+      <c r="A161" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B148" s="15" t="inlineStr">
+      <c r="B161" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C148" s="15" t="inlineStr">
+      <c r="C161" s="15" t="inlineStr">
         <is>
           <t>F15-04</t>
         </is>
       </c>
-      <c r="D148" s="30" t="inlineStr">
+      <c r="D161" s="30" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E148" s="16" t="inlineStr">
+      <c r="E161" s="16" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，策略调优</t>
         </is>
       </c>
-      <c r="F148" s="16" t="inlineStr">
+      <c r="F161" s="16" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G148" s="23" t="inlineStr">
+      <c r="G161" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H148" s="18" t="n">
+      <c r="H161" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="149" ht="28" customHeight="1">
-      <c r="A149" s="16" t="inlineStr">
+    <row r="162" ht="28" customHeight="1">
+      <c r="A162" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B149" s="15" t="inlineStr">
+      <c r="B162" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C149" s="15" t="inlineStr">
+      <c r="C162" s="15" t="inlineStr">
         <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D149" s="30" t="inlineStr">
+      <c r="D162" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E149" s="16" t="inlineStr">
+      <c r="E162" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F149" s="16" t="inlineStr">
+      <c r="F162" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G149" s="24" t="inlineStr">
+      <c r="G162" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H149" s="18" t="n">
+      <c r="H162" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="19" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H150" s="20">
-        <f>SUM(H3:H149)</f>
+      <c r="H163" s="20">
+        <f>SUM(H3:H162)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A143:H143"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A124:H124"/>
     <mergeCell ref="A130:H130"/>
-    <mergeCell ref="A86:H86"/>
-    <mergeCell ref="A144:H144"/>
-    <mergeCell ref="A150:G150"/>
-    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A157:H157"/>
+    <mergeCell ref="A99:H99"/>
     <mergeCell ref="A117:H117"/>
+    <mergeCell ref="A60:H60"/>
     <mergeCell ref="A137:H137"/>
-    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A163:G163"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A110:H110"/>
+    <mergeCell ref="A150:H150"/>
+    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="A123:H123"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A74:H74"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8331,10 +8852,10 @@
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -11356,6 +11877,887 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：FICC风险计量平台  |  FICC Risk Measurement Platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：替代衡泰老旧系统，信创切入口；覆盖投前/投中/投后全生命周期风险管理；对应PPT Slide 52   |   来源：Slide 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：FICC风险计量平台  (FICC Risk Measurement Platform)  |  优先级：P1  |  竞品：衡泰(垄断)  |  华锐基础：ARC风险引擎/IBOR  |  工期：14月  团队：12人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. 投前风险分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>D1. 投前风险分析</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>F04-01</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>组合What-if分析</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>What-if情景建模，Duration &amp; Convexity影响分析，VaR贡献分解，风险因子敞口，集中度分析</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>D1. 投前风险分析</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>F04-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>授权敞口分析</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>交易前限额验证，交易对手/集中度/监管/组合约束多维度限额检查，Pre-trade拦截</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>D1. 投前风险分析</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F04-03</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>投资预测分析</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>P&amp;L与风险归因预测建模，收益率曲线/利差/波动率因子预测，组合构建优化，多情景对比分析</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D2. 投中实时监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>D2. 投中实时监控</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>F04-04</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>实时风险计量</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Real-time DV01/CS01，Live VaR，Dynamic Greeks，日内P&amp;L与归因，风险限额利用率实时展示</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>D2. 投中实时监控</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>F04-05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>交易对手风险实时监控</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>实时敞口聚合，抵押品监控，信用限额使用率，结算风险，净额结算协议管理</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>D2. 投中实时监控</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>F04-06</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>流动性分析与交易成本</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>执行风险监控，市场冲击分析，流动性成本追踪，滑点计量，最优执行合规</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>D2. 投中实时监控</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>F04-07</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>实时风险全景图</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>实时持仓追踪，流式风险指标，实时限额监控，告警管理，异常跟踪仪表板</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>D3. 风控引擎</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>D3. 风控引擎</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>F04-08</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>DV01/CS01计算</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>dPV/dy价格敏感度，信用利差敏感度，分桶移动与关键期限，平行与非平行冲击</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>D3. 风控引擎</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>F04-09</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Greeks与敏感度计算</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，覆盖固收全品种与衍生品</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>D3. 风控引擎</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>F04-10</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>VaR模型</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>参数法/历史模拟法/蒙特卡洛三模式，Expected Shortfall (ES)，回测与例外检验</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>D3. 风控引擎</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>F04-11</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>压力测试与情景分析</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>内置历史情景（GFC/COVID-19/利率冲击），假设情景（曲线扭转/利差走阔），反向压力测试</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>D3. 风控引擎</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>F04-12</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>估值与盈亏分解</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Carry &amp; Roll-down，曲线效应，信用利差贡献，择券贡献，基于因子的盈亏多维分解</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>D4. 投后风险分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>D4. 投后风险分析</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>F04-13</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>历史风险回溯</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>历史VaR计算回放，压力测试结果归档，风险趋势分析，限额例外统计，VaR回测报告</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>D4. 投后风险分析</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>F04-14</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>绩效归因与风险计量</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>收益率曲线效应，信用利差分解，行业配置效应，个券择券，Carry &amp; Roll-down贡献</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>D4. 投后风险分析</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>F04-15</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>监管报表与风控日报</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>D5. 风控基础设施</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>D5. 风控基础设施</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>F04-16</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>数据底座与IBOR集成</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>D5. 风控基础设施</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>F04-17</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>收益率曲线与波动率曲面</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>D5. 风控基础设施</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>F04-18</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>HPC计算网格</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>D5. 风控基础设施</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>F04-19</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>AI风险预警</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>异常检测（ML模型），预测性分析，模式识别，智能告警，新业务合规风险预分析</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>合计 19项功能  |  P1: 19项  |  P2: 0项</t>
+        </is>
+      </c>
+      <c r="H29" s="20">
+        <f>SUM(H5:H28)</f>
+        <v/>
+      </c>
+      <c r="I29" s="34" t="inlineStr"/>
+      <c r="J29" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A29:G29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_IBOR投资账薄管理" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_现券交易系统" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_FICC风险计量平台" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_异常交易风控" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1201,17 +1202,17 @@
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>8</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>监管驱动，AI差异化，快速商业化</t>
+          <t>监管驱动，AI差异化（LLM+RAG+Agent+MCP），快速商业化；对应PPT Slide 50</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5236,12 +5237,12 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>实时CEP监控引擎</t>
+          <t>LLM大语言模型应用</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>基于复杂事件处理（CEP），毫秒级事件流检测，滑动窗口聚合</t>
+          <t>客户意图识别，自然语言处理交易描述，智能报告自动生成，新规合规解读</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
@@ -5255,7 +5256,7 @@
         </is>
       </c>
       <c r="H88" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1">
@@ -5276,12 +5277,12 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>异常价格检测</t>
+          <t>RAG检索增强生成</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>基于历史分位数/实时行情计算价格偏离度，动态阈值自适应</t>
+          <t>监管规则知识库构建，新规则智能固化，合规智能问答，上下文理解与规则推理</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -5295,7 +5296,7 @@
         </is>
       </c>
       <c r="H89" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" ht="28" customHeight="1">
@@ -5316,12 +5317,12 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>AI异常识别模型</t>
+          <t>Agent智能体</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>机器学习（XGBoost/LSTM）训练异常交易识别模型，在线推理</t>
+          <t>异常处置任务自动化，决策支持工作流，多步骤异常核查流程优化，自动推送处置建议</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -5335,7 +5336,7 @@
         </is>
       </c>
       <c r="H90" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="91" ht="28" customHeight="1">
@@ -5356,12 +5357,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>规则引擎（可配置）</t>
+          <t>MCP外部服务集成</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>No-Code规则配置界面，合规人员自助维护检测规则</t>
+          <t>外部数据源调用接口，固化规则调用标准协议，与行情/持仓/交易系统数据对接</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
@@ -5396,39 +5397,72 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>监管报送自动化</t>
+          <t>代持与反向交易识别</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>一键生成证监会/人行格式异常交易报告，历史追溯查询</t>
+          <t>代持相关交易检测，同券同额反向识别，多日反向低频交易模式识别</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G92" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H92" s="8" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
-        </is>
+    <row r="93" ht="28" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>异常交易风控</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>F05-06</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>价格行为异常检测</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>高买低卖行为识别，信用债价格异常检测，基于历史分位数与实时行情动态偏离度计算</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="94" ht="28" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -5438,17 +5472,17 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>F06-01</t>
+          <t>F05-07</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>投资策略合规规则库</t>
+          <t>交易对手异常监控</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
+          <t>同一交易对手频繁交易预警，多次修改交易对手行为识别，持仓结构异常检测</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -5462,13 +5496,13 @@
         </is>
       </c>
       <c r="H94" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" ht="28" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -5478,37 +5512,37 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>F06-02</t>
+          <t>F05-08</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>实时订单拦截</t>
+          <t>交易量异常检测</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
+          <t>交易量统计异常识别，集中度异常告警，与历史基准对比的量级偏离检测</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G95" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H95" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" ht="28" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -5518,37 +5552,37 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>F06-03</t>
+          <t>F05-09</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>限额多维度检查</t>
+          <t>动态规则管理</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
+          <t>异常模式智能探索与规则固化，No-Code规则配置界面，合规人员自助维护，规则版本管理</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G96" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G96" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H96" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" ht="28" customHeight="1">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -5558,17 +5592,17 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>F06-04</t>
+          <t>F05-10</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>合规审批工作流</t>
+          <t>异常交易定位</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>超限申请→审批→记录全流程，支持移动端审批</t>
+          <t>按时间范围快速查找历史异常交易，标记异常类型，可视化展示异常分布与趋势</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -5588,7 +5622,7 @@
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -5598,17 +5632,17 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>F06-05</t>
+          <t>F05-11</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>监管白/黑名单</t>
+          <t>数据上传校验</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
+          <t>支持用户上传交易数据文件，瞬时完成异常交易校验并输出校验结果报告</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -5625,57 +5659,57 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="28" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>F07-01</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>债券横截面与时序分析</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>横截面信号与实际收益相关性&gt;0.3</t>
-        </is>
-      </c>
-      <c r="G100" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H100" s="8" t="n">
-        <v>35</v>
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>异常交易风控</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>F05-12</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>智能报告生成</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>模板自定义与场景数据一键应用，监管报送格式（证监会/人行），新业务过会合规分析报告</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G99" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
+        </is>
       </c>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -5685,22 +5719,22 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>F07-02</t>
+          <t>F06-01</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>投资策略合规规则库</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G101" s="23" t="inlineStr">
@@ -5715,7 +5749,7 @@
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -5725,27 +5759,27 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>F07-03</t>
+          <t>F06-02</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>组合相关度分析</t>
+          <t>实时订单拦截</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>相关矩阵计算&lt;30s（500券组合）</t>
-        </is>
-      </c>
-      <c r="G102" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G102" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H102" s="8" t="n">
@@ -5755,7 +5789,7 @@
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -5765,22 +5799,22 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F06-03</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>限额多维度检查</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G103" s="23" t="inlineStr">
@@ -5789,13 +5823,13 @@
         </is>
       </c>
       <c r="H103" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -5805,37 +5839,37 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>F07-05</t>
+          <t>F06-04</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析</t>
+          <t>合规审批工作流</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+          <t>超限申请→审批→记录全流程，支持移动端审批</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
-        </is>
-      </c>
-      <c r="G104" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G104" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H104" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" ht="28" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -5845,71 +5879,38 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F06-05</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>极端事件分析</t>
+          <t>监管白/黑名单</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%</t>
-        </is>
-      </c>
-      <c r="G105" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G105" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H105" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="106" ht="28" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>F07-07</t>
-        </is>
-      </c>
-      <c r="D106" s="4" t="inlineStr">
-        <is>
-          <t>指数比较分析</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr">
-        <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="inlineStr">
-        <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
-        </is>
-      </c>
-      <c r="G106" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H106" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
+        </is>
       </c>
     </row>
     <row r="107" ht="28" customHeight="1">
@@ -5925,22 +5926,22 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F07-01</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>债券横截面与时序分析</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
+          <t>横截面信号与实际收益相关性&gt;0.3</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5949,7 +5950,7 @@
         </is>
       </c>
       <c r="H107" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="108" ht="28" customHeight="1">
@@ -5965,22 +5966,22 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>F07-09</t>
+          <t>F07-02</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>虚拟组合分析</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
         </is>
       </c>
       <c r="G108" s="23" t="inlineStr">
@@ -5989,7 +5990,7 @@
         </is>
       </c>
       <c r="H108" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" ht="28" customHeight="1">
@@ -6005,31 +6006,31 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>F07-10</t>
+          <t>F07-03</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>再平衡方案试算与比较</t>
+          <t>组合相关度分析</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
-        </is>
-      </c>
-      <c r="G109" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>相关矩阵计算&lt;30s（500券组合）</t>
+        </is>
+      </c>
+      <c r="G109" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H109" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110" ht="28" customHeight="1">
@@ -6045,22 +6046,22 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>F07-11</t>
+          <t>F07-04</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>情景分析</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
         </is>
       </c>
       <c r="G110" s="23" t="inlineStr">
@@ -6069,7 +6070,7 @@
         </is>
       </c>
       <c r="H110" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="111" ht="28" customHeight="1">
@@ -6085,22 +6086,22 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>F07-12</t>
+          <t>F07-05</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>固收+策略分析</t>
+          <t>敏感度分析</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
         </is>
       </c>
       <c r="G111" s="23" t="inlineStr">
@@ -6109,7 +6110,7 @@
         </is>
       </c>
       <c r="H111" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" ht="28" customHeight="1">
@@ -6125,22 +6126,22 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>F07-13</t>
+          <t>F07-06</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>量化策略组合分析</t>
+          <t>极端事件分析</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>策略容量计算误差&lt;5%</t>
+          <t>历史情景复现误差&lt;1%</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -6149,7 +6150,7 @@
         </is>
       </c>
       <c r="H112" s="8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" ht="28" customHeight="1">
@@ -6165,22 +6166,22 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>F07-14</t>
+          <t>F07-07</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>流动性分析</t>
+          <t>指数比较分析</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
         </is>
       </c>
       <c r="G113" s="24" t="inlineStr">
@@ -6189,7 +6190,7 @@
         </is>
       </c>
       <c r="H113" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
@@ -6205,22 +6206,22 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>F07-15</t>
+          <t>F07-08</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>定价计算集成</t>
+          <t>绩效归因（Brinson）</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -6229,7 +6230,7 @@
         </is>
       </c>
       <c r="H114" s="8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115" ht="28" customHeight="1">
@@ -6245,31 +6246,31 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>F07-16</t>
+          <t>F07-09</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>利率曲线集成</t>
+          <t>虚拟组合分析</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
-        </is>
-      </c>
-      <c r="G115" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" ht="28" customHeight="1">
@@ -6285,22 +6286,22 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>F07-17</t>
+          <t>F07-10</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>因子模型</t>
+          <t>再平衡方案试算与比较</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -6309,20 +6310,53 @@
         </is>
       </c>
       <c r="H116" s="8" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>F07-11</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>资产配置策略分析</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+        </is>
+      </c>
+      <c r="G117" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="n">
         <v>40</v>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
-        </is>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -6332,22 +6366,22 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>F08-01</t>
+          <t>F07-12</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>因子模型框架</t>
+          <t>固收+策略分析</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -6356,13 +6390,13 @@
         </is>
       </c>
       <c r="H118" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" ht="28" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -6372,37 +6406,37 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F07-13</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>量化策略组合分析</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G119" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>策略容量计算误差&lt;5%</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H119" s="8" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -6412,37 +6446,37 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F07-14</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>信号生成与调度</t>
+          <t>流动性分析</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G120" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+        </is>
+      </c>
+      <c r="G120" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H120" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -6452,331 +6486,331 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>F08-04</t>
+          <t>F07-15</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>低延迟执行接口</t>
+          <t>定价计算集成</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G121" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H121" s="8" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" ht="28" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
         <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G122" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" ht="28" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>F07-17</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>因子模型</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+        </is>
+      </c>
+      <c r="G123" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="28" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t>策略投资/量化</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>因子模型框架</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Tick级回测引擎</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G126" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H126" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="127" ht="28" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>信号生成与调度</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="128" ht="28" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>低延迟执行接口</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G128" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>F08-05</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D129" s="4" t="inlineStr">
         <is>
           <t>实时策略监控</t>
         </is>
       </c>
-      <c r="E122" s="5" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>持仓/PnL/回撤/Sharpe实时看板，风险触发自动平仓</t>
         </is>
       </c>
-      <c r="F122" s="5" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G122" s="24" t="inlineStr">
+      <c r="G129" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H122" s="8" t="n">
+      <c r="H129" s="8" t="n">
         <v>20</v>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 定价平台  (Pricing Platform)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="28" customHeight="1">
-      <c r="A124" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C124" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D124" s="27" t="inlineStr">
-        <is>
-          <t>期限结构模型</t>
-        </is>
-      </c>
-      <c r="E124" s="11" t="inlineStr">
-        <is>
-          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
-        </is>
-      </c>
-      <c r="F124" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G124" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H124" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="125" ht="28" customHeight="1">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B125" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
-        <is>
-          <t>F09-02</t>
-        </is>
-      </c>
-      <c r="D125" s="27" t="inlineStr">
-        <is>
-          <t>蒙特卡洛求解器</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="inlineStr">
-        <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
-        </is>
-      </c>
-      <c r="F125" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G125" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H125" s="13" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="126" ht="28" customHeight="1">
-      <c r="A126" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C126" s="10" t="inlineStr">
-        <is>
-          <t>F09-03</t>
-        </is>
-      </c>
-      <c r="D126" s="27" t="inlineStr">
-        <is>
-          <t>有限差分（PDE）</t>
-        </is>
-      </c>
-      <c r="E126" s="11" t="inlineStr">
-        <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
-        </is>
-      </c>
-      <c r="F126" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G126" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H126" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="127" ht="28" customHeight="1">
-      <c r="A127" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B127" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C127" s="10" t="inlineStr">
-        <is>
-          <t>F09-04</t>
-        </is>
-      </c>
-      <c r="D127" s="27" t="inlineStr">
-        <is>
-          <t>实时Greeks</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="inlineStr">
-        <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
-        </is>
-      </c>
-      <c r="F127" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G127" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H127" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="128" ht="28" customHeight="1">
-      <c r="A128" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B128" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C128" s="10" t="inlineStr">
-        <is>
-          <t>F09-05</t>
-        </is>
-      </c>
-      <c r="D128" s="27" t="inlineStr">
-        <is>
-          <t>定价服务微服务架构</t>
-        </is>
-      </c>
-      <c r="E128" s="11" t="inlineStr">
-        <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
-        </is>
-      </c>
-      <c r="F128" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G128" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H128" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B129" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C129" s="10" t="inlineStr">
-        <is>
-          <t>F09-06</t>
-        </is>
-      </c>
-      <c r="D129" s="27" t="inlineStr">
-        <is>
-          <t>历史估值回测</t>
-        </is>
-      </c>
-      <c r="E129" s="11" t="inlineStr">
-        <is>
-          <t>基于历史行情重放定价误差分析，模型验证框架</t>
-        </is>
-      </c>
-      <c r="F129" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G129" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H129" s="13" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130" s="26" t="inlineStr">
         <is>
-          <t>【P2】 销售交易  (Sales Trading)</t>
+          <t>【P2】 定价平台  (Pricing Platform)</t>
         </is>
       </c>
     </row>
     <row r="131" ht="28" customHeight="1">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
@@ -6786,37 +6820,37 @@
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>F10-01</t>
+          <t>F09-01</t>
         </is>
       </c>
       <c r="D131" s="27" t="inlineStr">
         <is>
-          <t>销交工作台</t>
+          <t>期限结构模型</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
+          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G131" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G131" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H131" s="13" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
@@ -6826,37 +6860,37 @@
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>F10-02</t>
+          <t>F09-02</t>
         </is>
       </c>
       <c r="D132" s="27" t="inlineStr">
         <is>
-          <t>债券过滤与筛选</t>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G132" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G132" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H132" s="13" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="133" ht="28" customHeight="1">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
@@ -6866,37 +6900,37 @@
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>F10-03</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D133" s="27" t="inlineStr">
         <is>
-          <t>报价撮合与对价</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G133" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G133" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H133" s="13" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134" ht="28" customHeight="1">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
@@ -6906,37 +6940,37 @@
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>F10-04</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D134" s="27" t="inlineStr">
         <is>
-          <t>交易执行与审批</t>
+          <t>实时Greeks</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G134" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G134" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H134" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135" ht="28" customHeight="1">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
@@ -6946,37 +6980,37 @@
       </c>
       <c r="C135" s="10" t="inlineStr">
         <is>
-          <t>F10-05</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D135" s="27" t="inlineStr">
         <is>
-          <t>风控检查</t>
+          <t>定价服务微服务架构</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
+          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G135" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G135" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H135" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
@@ -6986,17 +7020,17 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>F10-06</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D136" s="27" t="inlineStr">
         <is>
-          <t>智能推荐系统</t>
+          <t>历史估值回测</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
+          <t>基于历史行情重放定价误差分析，模型验证框架</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr">
@@ -7010,20 +7044,20 @@
         </is>
       </c>
       <c r="H136" s="13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137" s="26" t="inlineStr">
         <is>
-          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+          <t>【P2】 销售交易  (Sales Trading)</t>
         </is>
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -7033,37 +7067,37 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>F11-01</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D138" s="27" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>销交工作台</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G138" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H138" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -7073,37 +7107,37 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D139" s="27" t="inlineStr">
         <is>
-          <t>CDS/CLN定价</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G139" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G139" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H139" s="13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -7113,17 +7147,17 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D140" s="27" t="inlineStr">
         <is>
-          <t>信用评级动态监控</t>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr">
@@ -7143,7 +7177,7 @@
     <row r="141" ht="28" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -7153,37 +7187,37 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D141" s="27" t="inlineStr">
         <is>
-          <t>违约概率（PD）建模</t>
+          <t>交易执行与审批</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G141" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G141" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H141" s="13" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142" ht="28" customHeight="1">
       <c r="A142" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
@@ -7193,17 +7227,17 @@
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>F11-05</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D142" s="27" t="inlineStr">
         <is>
-          <t>集中度限额管理</t>
+          <t>风控检查</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>行业/发行人/评级集中度多维限额，超限预警</t>
+          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr">
@@ -7217,60 +7251,60 @@
         </is>
       </c>
       <c r="H142" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 投顾服务  (Investment Advisory)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="28" customHeight="1">
-      <c r="A144" s="11" t="inlineStr">
-        <is>
-          <t>投顾服务</t>
-        </is>
-      </c>
-      <c r="B144" s="10" t="inlineStr">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B143" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C144" s="10" t="inlineStr">
-        <is>
-          <t>F12-01</t>
-        </is>
-      </c>
-      <c r="D144" s="27" t="inlineStr">
-        <is>
-          <t>投顾工作台</t>
-        </is>
-      </c>
-      <c r="E144" s="11" t="inlineStr">
-        <is>
-          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
-        </is>
-      </c>
-      <c r="F144" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G144" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H144" s="13" t="n">
-        <v>20</v>
+      <c r="C143" s="10" t="inlineStr">
+        <is>
+          <t>F10-06</t>
+        </is>
+      </c>
+      <c r="D143" s="27" t="inlineStr">
+        <is>
+          <t>智能推荐系统</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
+        </is>
+      </c>
+      <c r="F143" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G143" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H143" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+        </is>
       </c>
     </row>
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -7280,37 +7314,37 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F11-01</t>
         </is>
       </c>
       <c r="D145" s="27" t="inlineStr">
         <is>
-          <t>客户终端</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G145" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G145" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H145" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -7320,37 +7354,37 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D146" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G146" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G146" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H146" s="13" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -7360,37 +7394,37 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D147" s="27" t="inlineStr">
         <is>
-          <t>账户分析报告</t>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G147" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G147" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H147" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148" ht="28" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
@@ -7400,37 +7434,37 @@
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F11-04</t>
         </is>
       </c>
       <c r="D148" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>违约概率（PD）建模</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G148" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G148" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H148" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="149" ht="28" customHeight="1">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
@@ -7440,44 +7474,44 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>F12-06</t>
+          <t>F11-05</t>
         </is>
       </c>
       <c r="D149" s="27" t="inlineStr">
         <is>
-          <t>客户服务与基础服务</t>
+          <t>集中度限额管理</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+          <t>行业/发行人/评级集中度多维限额，超限预警</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G149" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G149" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H149" s="13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="26" t="inlineStr">
         <is>
-          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+          <t>【P2】 投顾服务  (Investment Advisory)</t>
         </is>
       </c>
     </row>
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -7487,37 +7521,37 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F12-01</t>
         </is>
       </c>
       <c r="D151" s="27" t="inlineStr">
         <is>
-          <t>TRS交易端</t>
+          <t>投顾工作台</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G151" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G151" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H151" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -7527,37 +7561,37 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D152" s="27" t="inlineStr">
         <is>
-          <t>TRS客户端</t>
+          <t>客户终端</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G152" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G152" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H152" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
@@ -7567,17 +7601,17 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
@@ -7591,13 +7625,13 @@
         </is>
       </c>
       <c r="H153" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
@@ -7607,17 +7641,17 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D154" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>账户分析报告</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
@@ -7637,7 +7671,7 @@
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
@@ -7647,17 +7681,17 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F12-05</t>
         </is>
       </c>
       <c r="D155" s="27" t="inlineStr">
         <is>
-          <t>通知与确认文件</t>
+          <t>投研报告服务</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr">
@@ -7677,278 +7711,525 @@
     <row r="156" ht="28" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
+          <t>F12-06</t>
+        </is>
+      </c>
+      <c r="D156" s="27" t="inlineStr">
+        <is>
+          <t>客户服务与基础服务</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="inlineStr">
+        <is>
+          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+        </is>
+      </c>
+      <c r="F156" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G156" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H156" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="28" customHeight="1">
+      <c r="A158" s="11" t="inlineStr">
+        <is>
           <t>TRS收益互换</t>
         </is>
       </c>
-      <c r="B156" s="10" t="inlineStr">
+      <c r="B158" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C156" s="10" t="inlineStr">
+      <c r="C158" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D158" s="27" t="inlineStr">
+        <is>
+          <t>TRS交易端</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+        </is>
+      </c>
+      <c r="F158" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G158" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H158" s="13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="159" ht="28" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D159" s="27" t="inlineStr">
+        <is>
+          <t>TRS客户端</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+        </is>
+      </c>
+      <c r="F159" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G159" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H159" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" ht="28" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D160" s="27" t="inlineStr">
+        <is>
+          <t>TRS管理端</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+        </is>
+      </c>
+      <c r="F160" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G160" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H160" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="161" ht="28" customHeight="1">
+      <c r="A161" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C161" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D161" s="27" t="inlineStr">
+        <is>
+          <t>自动对冲</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H161" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" ht="28" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D162" s="27" t="inlineStr">
+        <is>
+          <t>通知与确认文件</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="F162" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G162" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H162" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" ht="28" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
         <is>
           <t>F13-06</t>
         </is>
       </c>
-      <c r="D156" s="27" t="inlineStr">
+      <c r="D163" s="27" t="inlineStr">
         <is>
           <t>系统集成</t>
         </is>
       </c>
-      <c r="E156" s="11" t="inlineStr">
+      <c r="E163" s="11" t="inlineStr">
         <is>
           <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
         </is>
       </c>
-      <c r="F156" s="11" t="inlineStr">
+      <c r="F163" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G156" s="23" t="inlineStr">
+      <c r="G163" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H156" s="13" t="n">
+      <c r="H163" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="29" t="inlineStr">
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="28" customHeight="1">
-      <c r="A158" s="16" t="inlineStr">
+    <row r="165" ht="28" customHeight="1">
+      <c r="A165" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B158" s="15" t="inlineStr">
+      <c r="B165" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C158" s="15" t="inlineStr">
+      <c r="C165" s="15" t="inlineStr">
         <is>
           <t>F15-01</t>
         </is>
       </c>
-      <c r="D158" s="30" t="inlineStr">
+      <c r="D165" s="30" t="inlineStr">
         <is>
           <t>双边报价引擎</t>
         </is>
       </c>
-      <c r="E158" s="16" t="inlineStr">
+      <c r="E165" s="16" t="inlineStr">
         <is>
           <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
-      <c r="F158" s="16" t="inlineStr">
+      <c r="F165" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G158" s="28" t="inlineStr">
+      <c r="G165" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H158" s="18" t="n">
+      <c r="H165" s="18" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="159" ht="28" customHeight="1">
-      <c r="A159" s="16" t="inlineStr">
+    <row r="166" ht="28" customHeight="1">
+      <c r="A166" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B159" s="15" t="inlineStr">
+      <c r="B166" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C159" s="15" t="inlineStr">
+      <c r="C166" s="15" t="inlineStr">
         <is>
           <t>F15-02</t>
         </is>
       </c>
-      <c r="D159" s="30" t="inlineStr">
+      <c r="D166" s="30" t="inlineStr">
         <is>
           <t>库存风险实时管理</t>
         </is>
       </c>
-      <c r="E159" s="16" t="inlineStr">
+      <c r="E166" s="16" t="inlineStr">
         <is>
           <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
-      <c r="F159" s="16" t="inlineStr">
+      <c r="F166" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G159" s="28" t="inlineStr">
+      <c r="G166" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H159" s="18" t="n">
+      <c r="H166" s="18" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="160" ht="28" customHeight="1">
-      <c r="A160" s="16" t="inlineStr">
+    <row r="167" ht="28" customHeight="1">
+      <c r="A167" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B160" s="15" t="inlineStr">
+      <c r="B167" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C160" s="15" t="inlineStr">
+      <c r="C167" s="15" t="inlineStr">
         <is>
           <t>F15-03</t>
         </is>
       </c>
-      <c r="D160" s="30" t="inlineStr">
+      <c r="D167" s="30" t="inlineStr">
         <is>
           <t>报价优化算法</t>
         </is>
       </c>
-      <c r="E160" s="16" t="inlineStr">
+      <c r="E167" s="16" t="inlineStr">
         <is>
           <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
-      <c r="F160" s="16" t="inlineStr">
+      <c r="F167" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G160" s="28" t="inlineStr">
+      <c r="G167" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H160" s="18" t="n">
+      <c r="H167" s="18" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="161" ht="28" customHeight="1">
-      <c r="A161" s="16" t="inlineStr">
+    <row r="168" ht="28" customHeight="1">
+      <c r="A168" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B161" s="15" t="inlineStr">
+      <c r="B168" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C161" s="15" t="inlineStr">
+      <c r="C168" s="15" t="inlineStr">
         <is>
           <t>F15-04</t>
         </is>
       </c>
-      <c r="D161" s="30" t="inlineStr">
+      <c r="D168" s="30" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E161" s="16" t="inlineStr">
+      <c r="E168" s="16" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，策略调优</t>
         </is>
       </c>
-      <c r="F161" s="16" t="inlineStr">
+      <c r="F168" s="16" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G161" s="23" t="inlineStr">
+      <c r="G168" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H161" s="18" t="n">
+      <c r="H168" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="162" ht="28" customHeight="1">
-      <c r="A162" s="16" t="inlineStr">
+    <row r="169" ht="28" customHeight="1">
+      <c r="A169" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B162" s="15" t="inlineStr">
+      <c r="B169" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C162" s="15" t="inlineStr">
+      <c r="C169" s="15" t="inlineStr">
         <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D162" s="30" t="inlineStr">
+      <c r="D169" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E162" s="16" t="inlineStr">
+      <c r="E169" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F162" s="16" t="inlineStr">
+      <c r="F169" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G162" s="24" t="inlineStr">
+      <c r="G169" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H162" s="18" t="n">
+      <c r="H169" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="19" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H163" s="20">
-        <f>SUM(H3:H162)</f>
+      <c r="H170" s="20">
+        <f>SUM(H3:H169)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A170:G170"/>
     <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A100:H100"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A106:H106"/>
+    <mergeCell ref="A124:H124"/>
     <mergeCell ref="A130:H130"/>
     <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A144:H144"/>
     <mergeCell ref="A157:H157"/>
-    <mergeCell ref="A99:H99"/>
-    <mergeCell ref="A117:H117"/>
+    <mergeCell ref="A164:H164"/>
+    <mergeCell ref="A137:H137"/>
     <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A137:H137"/>
-    <mergeCell ref="A163:G163"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A150:H150"/>
-    <mergeCell ref="A93:H93"/>
-    <mergeCell ref="A123:H123"/>
     <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8660,7 +8941,7 @@
         </is>
       </c>
       <c r="H3" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I3" s="8" t="n">
         <v>8</v>
@@ -12758,6 +13039,605 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：异常交易风控  |  Abnormal Trade Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：监管驱动，AI差异化（LLM+RAG+Agent+MCP），快速商业化；对应PPT Slide 50   |   来源：Slide 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：异常交易风控  (Abnormal Trade Monitor)  |  优先级：P1  |  竞品：无主导者  |  华锐基础：ARC+AI规则引擎  |  工期：8月  团队：8人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. AI智能引擎</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>D1. AI智能引擎</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>F05-01</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>LLM大语言模型应用</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>客户意图识别，自然语言处理交易描述，智能报告自动生成，新规合规解读</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>D1. AI智能引擎</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>F05-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>RAG检索增强生成</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>监管规则知识库构建，新规则智能固化，合规智能问答，上下文理解与规则推理</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>D1. AI智能引擎</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F05-03</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Agent智能体</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>异常处置任务自动化，决策支持工作流，多步骤异常核查流程优化，自动推送处置建议</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>D1. AI智能引擎</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>F05-04</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>MCP外部服务集成</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>外部数据源调用接口，固化规则调用标准协议，与行情/持仓/交易系统数据对接</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>D2. 异常识别引擎</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>D2. 异常识别引擎</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>F05-05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>代持与反向交易识别</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>代持相关交易检测，同券同额反向识别，多日反向低频交易模式识别</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>D2. 异常识别引擎</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>F05-06</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>价格行为异常检测</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>高买低卖行为识别，信用债价格异常检测，基于历史分位数与实时行情动态偏离度计算</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>D2. 异常识别引擎</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>F05-07</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>交易对手异常监控</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>同一交易对手频繁交易预警，多次修改交易对手行为识别，持仓结构异常检测</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>D2. 异常识别引擎</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>F05-08</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>交易量异常检测</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>交易量统计异常识别，集中度异常告警，与历史基准对比的量级偏离检测</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>D2. 异常识别引擎</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>F05-09</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>动态规则管理</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>异常模式智能探索与规则固化，No-Code规则配置界面，合规人员自助维护，规则版本管理</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>D3. 运营与报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>D3. 运营与报告</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>F05-10</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>异常交易定位</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>按时间范围快速查找历史异常交易，标记异常类型，可视化展示异常分布与趋势</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>D3. 运营与报告</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>F05-11</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>数据上传校验</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>支持用户上传交易数据文件，瞬时完成异常交易校验并输出校验结果报告</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>D3. 运营与报告</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>F05-12</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>智能报告生成</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>模板自定义与场景数据一键应用，监管报送格式（证监会/人行），新业务过会合规分析报告</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>合计 12项功能  |  P1: 12项  |  P2: 0项</t>
+        </is>
+      </c>
+      <c r="H20" s="20">
+        <f>SUM(H5:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="34" t="inlineStr"/>
+      <c r="J20" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A10:J10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -15,7 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_现券交易系统" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_FICC风险计量平台" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_异常交易风控" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_事前风控_合规" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1227,7 +1228,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Pre-trade Risk</t>
+          <t>Pre-trade Risk &amp; Compliance</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1276,17 +1277,17 @@
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>6</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>嵌入交易前拦截，合规刚需</t>
+          <t>嵌入交易前拦截，三端架构（风控/用户/管理），AI聊天合规监控为核心差异化；对应PPT Slide 51</t>
         </is>
       </c>
     </row>
@@ -1910,6 +1911,955 @@
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A17:L17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：组合管理+绩效归因  |  Portfolio Mgmt &amp; Perf</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：17项功能含量化底座集成；Slide44全景展开   |   来源：Slide 44   |   数据输入：交易数据 / 头寸数据 / 行情数据 / 估值数据   |   量化底座：定价计算 · 利率曲线 · 因子模型</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)  |  优先级：P1  |  竞品：SimCorp/衡泰  |  华锐基础：M9 PMS模块  |  工期：12月  团队：12人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>A. 组合分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>A. 组合分析</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>F07-01</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>债券横截面与时序分析</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>横截面信号与实际收益相关性&gt;0.3</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情平台/估值数据</t>
+        </is>
+      </c>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>A. 组合分析</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>F07-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>相对价值分析</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>量化定价引擎/AMD行情</t>
+        </is>
+      </c>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>A. 组合分析</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F07-03</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>组合相关度分析</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>相关矩阵计算&lt;30s（500券组合）</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>IBOR头寸/AMD历史行情</t>
+        </is>
+      </c>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>B. 风险计量</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>B. 风险计量</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>F07-04</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>情景分析</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台/量化定价引擎</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>B. 风险计量</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>F07-05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>敏感度分析</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>量化定价引擎Greeks接口</t>
+        </is>
+      </c>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>B. 风险计量</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>F07-06</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>极端事件分析</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>历史情景复现误差&lt;1%</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台</t>
+        </is>
+      </c>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>C. 绩效归因</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>C. 绩效归因</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>F07-07</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>指数比较分析</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>AMD中债估值/IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>C. 绩效归因</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>F07-08</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>绩效归因（Brinson）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>IBOR持仓/AMD行情/指数数据</t>
+        </is>
+      </c>
+      <c r="G15" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>F07-09</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>虚拟组合分析</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>IBOR/现券交易系统</t>
+        </is>
+      </c>
+      <c r="G17" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>F07-10</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>再平衡方案试算与比较</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规/IBOR/现券系统</t>
+        </is>
+      </c>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>F07-11</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>资产配置策略分析</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>AMD宏观数据/因子模型</t>
+        </is>
+      </c>
+      <c r="G19" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>F07-12</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>固收+策略分析</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>IBOR/利率衍生品系统</t>
+        </is>
+      </c>
+      <c r="G20" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>D. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>F07-13</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>量化策略组合分析</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>策略容量计算误差&lt;5%</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>策略投资/量化系统</t>
+        </is>
+      </c>
+      <c r="G21" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>E. 流动性管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>E. 流动性管理</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>F07-14</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>流动性分析</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情/IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G23" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>F07-15</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>定价计算集成</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>量化定价引擎</t>
+        </is>
+      </c>
+      <c r="G25" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情平台/量化定价引擎</t>
+        </is>
+      </c>
+      <c r="G26" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>F07-17</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>因子模型</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>AMD历史行情/IBOR持仓</t>
+        </is>
+      </c>
+      <c r="G27" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>合计 17项功能  |  P1: 13项  |  P2: 4项</t>
+        </is>
+      </c>
+      <c r="H28" s="20">
+        <f>SUM(H5:H27)</f>
+        <v/>
+      </c>
+      <c r="I28" s="34" t="inlineStr"/>
+      <c r="J28" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
@@ -1922,7 +2872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5702,7 +6652,7 @@
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="22" t="inlineStr">
         <is>
-          <t>【P1】 事前风控/合规  (Pre-trade Risk)</t>
+          <t>【P1】 事前风控/合规  (Pre-trade Risk &amp; Compliance)</t>
         </is>
       </c>
     </row>
@@ -5724,12 +6674,12 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>投资策略合规规则库</t>
+          <t>风控规则配置</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>内置1000+条监管规则（投资指引/证监会规定），支持新增</t>
+          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
@@ -5764,22 +6714,22 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>实时订单拦截</t>
+          <t>多维度限额配置</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>在交易指令提交前同步校验，不满足规则则拦截+原因告知</t>
+          <t>交易对手/交易员/券三维度限额设置，集中度/净敞口/利率敏感度/单笔名义多类型限额</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G102" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G102" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H102" s="8" t="n">
@@ -5804,26 +6754,26 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>限额多维度检查</t>
+          <t>白黑名单管理</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>单笔名义/资产类别/集中度/净敞口/利率敏感度多维并行检查</t>
+          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G103" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H103" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" ht="28" customHeight="1">
@@ -5844,26 +6794,26 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>合规审批工作流</t>
+          <t>实时事前风控拦截</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>超限申请→审批→记录全流程，支持移动端审批</t>
+          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G104" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G104" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H104" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105" ht="28" customHeight="1">
@@ -5884,12 +6834,12 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>监管白/黑名单</t>
+          <t>异常报备工作流</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>证券/交易对手监管限制名单实时同步，拦截违规交易</t>
+          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
@@ -5903,20 +6853,53 @@
         </is>
       </c>
       <c r="H105" s="8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
-        </is>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="106" ht="28" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>F06-06</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>AI聊天合规监控</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="107" ht="28" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -5926,22 +6909,22 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>F07-01</t>
+          <t>F06-07</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>债券横截面与时序分析</t>
+          <t>AI交易要素提取</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
+          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>横截面信号与实际收益相关性&gt;0.3</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G107" s="23" t="inlineStr">
@@ -5950,13 +6933,13 @@
         </is>
       </c>
       <c r="H107" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" ht="28" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -5966,37 +6949,37 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>F07-02</t>
+          <t>F06-08</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>日内异常统计看板</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
-        </is>
-      </c>
-      <c r="G108" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G108" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H108" s="8" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109" ht="28" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -6006,22 +6989,22 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>F07-03</t>
+          <t>F06-09</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>组合相关度分析</t>
+          <t>合规审批工作流</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>相关矩阵计算&lt;30s（500券组合）</t>
+          <t>功能测试通过/正确率100%</t>
         </is>
       </c>
       <c r="G109" s="24" t="inlineStr">
@@ -6030,13 +7013,13 @@
         </is>
       </c>
       <c r="H109" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" ht="28" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -6046,71 +7029,38 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F06-10</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>责任留痕与审计追踪</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
-        </is>
-      </c>
-      <c r="G110" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G110" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H110" s="8" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>F07-05</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>敏感度分析</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
-        </is>
-      </c>
-      <c r="G111" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
+        </is>
       </c>
     </row>
     <row r="112" ht="28" customHeight="1">
@@ -6126,22 +7076,22 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F07-01</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>极端事件分析</t>
+          <t>债券横截面与时序分析</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%</t>
+          <t>横截面信号与实际收益相关性&gt;0.3</t>
         </is>
       </c>
       <c r="G112" s="23" t="inlineStr">
@@ -6150,7 +7100,7 @@
         </is>
       </c>
       <c r="H112" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113" ht="28" customHeight="1">
@@ -6166,31 +7116,31 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>F07-07</t>
+          <t>F07-02</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>指数比较分析</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
-        </is>
-      </c>
-      <c r="G113" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+        </is>
+      </c>
+      <c r="G113" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H113" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
@@ -6206,31 +7156,31 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F07-03</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>组合相关度分析</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
-        </is>
-      </c>
-      <c r="G114" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>相关矩阵计算&lt;30s（500券组合）</t>
+        </is>
+      </c>
+      <c r="G114" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H114" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115" ht="28" customHeight="1">
@@ -6246,22 +7196,22 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>F07-09</t>
+          <t>F07-04</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>虚拟组合分析</t>
+          <t>情景分析</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -6270,7 +7220,7 @@
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="116" ht="28" customHeight="1">
@@ -6286,22 +7236,22 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>F07-10</t>
+          <t>F07-05</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>再平衡方案试算与比较</t>
+          <t>敏感度分析</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -6310,7 +7260,7 @@
         </is>
       </c>
       <c r="H116" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" ht="28" customHeight="1">
@@ -6326,22 +7276,22 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>F07-11</t>
+          <t>F07-06</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>极端事件分析</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+          <t>历史情景复现误差&lt;1%</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -6350,7 +7300,7 @@
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1">
@@ -6366,31 +7316,31 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>F07-12</t>
+          <t>F07-07</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>固收+策略分析</t>
+          <t>指数比较分析</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
-        </is>
-      </c>
-      <c r="G118" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
+        </is>
+      </c>
+      <c r="G118" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H118" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" ht="28" customHeight="1">
@@ -6406,22 +7356,22 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>F07-13</t>
+          <t>F07-08</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>量化策略组合分析</t>
+          <t>绩效归因（Brinson）</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>策略容量计算误差&lt;5%</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -6430,7 +7380,7 @@
         </is>
       </c>
       <c r="H119" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1">
@@ -6446,27 +7396,27 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>F07-14</t>
+          <t>F07-09</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>流动性分析</t>
+          <t>虚拟组合分析</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
-        </is>
-      </c>
-      <c r="G120" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+        </is>
+      </c>
+      <c r="G120" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H120" s="8" t="n">
@@ -6486,22 +7436,22 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>F07-15</t>
+          <t>F07-10</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>定价计算集成</t>
+          <t>再平衡方案试算与比较</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -6510,7 +7460,7 @@
         </is>
       </c>
       <c r="H121" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="122" ht="28" customHeight="1">
@@ -6526,31 +7476,31 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>F07-16</t>
+          <t>F07-11</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>利率曲线集成</t>
+          <t>资产配置策略分析</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
-        </is>
-      </c>
-      <c r="G122" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+        </is>
+      </c>
+      <c r="G122" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H122" s="8" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="123" ht="28" customHeight="1">
@@ -6566,22 +7516,22 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>F07-17</t>
+          <t>F07-12</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>因子模型</t>
+          <t>固收+策略分析</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -6590,20 +7540,53 @@
         </is>
       </c>
       <c r="H123" s="8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
-        </is>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>F07-13</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>量化策略组合分析</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>策略容量计算误差&lt;5%</t>
+        </is>
+      </c>
+      <c r="G124" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -6613,37 +7596,37 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>F08-01</t>
+          <t>F07-14</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>因子模型框架</t>
+          <t>流动性分析</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G125" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+        </is>
+      </c>
+      <c r="G125" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H125" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" ht="28" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -6653,37 +7636,37 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F07-15</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>定价计算集成</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G126" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="G126" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H126" s="8" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" ht="28" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -6693,318 +7676,285 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F07-16</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>信号生成与调度</t>
+          <t>利率曲线集成</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G127" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G127" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H127" s="8" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>F07-17</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>因子模型</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
+        </is>
+      </c>
+      <c r="G128" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
           <t>策略投资/量化</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>因子模型框架</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G130" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H130" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>Tick级回测引擎</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G131" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="132" ht="28" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>信号生成与调度</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G132" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H132" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="133" ht="28" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>F08-04</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D133" s="4" t="inlineStr">
         <is>
           <t>低延迟执行接口</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G128" s="28" t="inlineStr">
+      <c r="G133" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H128" s="8" t="n">
+      <c r="H133" s="8" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
+    <row r="134" ht="28" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>策略投资/量化</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>F08-05</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D134" s="4" t="inlineStr">
         <is>
           <t>实时策略监控</t>
         </is>
       </c>
-      <c r="E129" s="5" t="inlineStr">
+      <c r="E134" s="5" t="inlineStr">
         <is>
           <t>持仓/PnL/回撤/Sharpe实时看板，风险触发自动平仓</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
+      <c r="F134" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G129" s="24" t="inlineStr">
+      <c r="G134" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H129" s="8" t="n">
+      <c r="H134" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="26" t="inlineStr">
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="26" t="inlineStr">
         <is>
           <t>【P2】 定价平台  (Pricing Platform)</t>
         </is>
-      </c>
-    </row>
-    <row r="131" ht="28" customHeight="1">
-      <c r="A131" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B131" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C131" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D131" s="27" t="inlineStr">
-        <is>
-          <t>期限结构模型</t>
-        </is>
-      </c>
-      <c r="E131" s="11" t="inlineStr">
-        <is>
-          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
-        </is>
-      </c>
-      <c r="F131" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G131" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H131" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="132" ht="28" customHeight="1">
-      <c r="A132" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B132" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C132" s="10" t="inlineStr">
-        <is>
-          <t>F09-02</t>
-        </is>
-      </c>
-      <c r="D132" s="27" t="inlineStr">
-        <is>
-          <t>蒙特卡洛求解器</t>
-        </is>
-      </c>
-      <c r="E132" s="11" t="inlineStr">
-        <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
-        </is>
-      </c>
-      <c r="F132" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G132" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H132" s="13" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="133" ht="28" customHeight="1">
-      <c r="A133" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B133" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C133" s="10" t="inlineStr">
-        <is>
-          <t>F09-03</t>
-        </is>
-      </c>
-      <c r="D133" s="27" t="inlineStr">
-        <is>
-          <t>有限差分（PDE）</t>
-        </is>
-      </c>
-      <c r="E133" s="11" t="inlineStr">
-        <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
-        </is>
-      </c>
-      <c r="F133" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G133" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H133" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="134" ht="28" customHeight="1">
-      <c r="A134" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B134" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
-        <is>
-          <t>F09-04</t>
-        </is>
-      </c>
-      <c r="D134" s="27" t="inlineStr">
-        <is>
-          <t>实时Greeks</t>
-        </is>
-      </c>
-      <c r="E134" s="11" t="inlineStr">
-        <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
-        </is>
-      </c>
-      <c r="F134" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G134" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H134" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="135" ht="28" customHeight="1">
-      <c r="A135" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>F09-05</t>
-        </is>
-      </c>
-      <c r="D135" s="27" t="inlineStr">
-        <is>
-          <t>定价服务微服务架构</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="inlineStr">
-        <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
-        </is>
-      </c>
-      <c r="F135" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G135" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H135" s="13" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
@@ -7020,44 +7970,77 @@
       </c>
       <c r="C136" s="10" t="inlineStr">
         <is>
-          <t>F09-06</t>
+          <t>F09-01</t>
         </is>
       </c>
       <c r="D136" s="27" t="inlineStr">
         <is>
-          <t>历史估值回测</t>
+          <t>期限结构模型</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>基于历史行情重放定价误差分析，模型验证框架</t>
+          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G136" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G136" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H136" s="13" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 销售交易  (Sales Trading)</t>
-        </is>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>定价平台</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C137" s="10" t="inlineStr">
+        <is>
+          <t>F09-02</t>
+        </is>
+      </c>
+      <c r="D137" s="27" t="inlineStr">
+        <is>
+          <t>蒙特卡洛求解器</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G137" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H137" s="13" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
@@ -7067,37 +8050,37 @@
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>F10-01</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D138" s="27" t="inlineStr">
         <is>
-          <t>销交工作台</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G138" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G138" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H138" s="13" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="139" ht="28" customHeight="1">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
@@ -7107,37 +8090,37 @@
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>F10-02</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D139" s="27" t="inlineStr">
         <is>
-          <t>债券过滤与筛选</t>
+          <t>实时Greeks</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G139" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H139" s="13" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="140" ht="28" customHeight="1">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
@@ -7147,37 +8130,37 @@
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>F10-03</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D140" s="27" t="inlineStr">
         <is>
-          <t>报价撮合与对价</t>
+          <t>定价服务微服务架构</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
+          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G140" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G140" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H140" s="13" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141" ht="28" customHeight="1">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
@@ -7187,71 +8170,38 @@
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>F10-04</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D141" s="27" t="inlineStr">
         <is>
-          <t>交易执行与审批</t>
+          <t>历史估值回测</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
+          <t>基于历史行情重放定价误差分析，模型验证框架</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G141" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G141" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H141" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="142" ht="28" customHeight="1">
-      <c r="A142" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B142" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C142" s="10" t="inlineStr">
-        <is>
-          <t>F10-05</t>
-        </is>
-      </c>
-      <c r="D142" s="27" t="inlineStr">
-        <is>
-          <t>风控检查</t>
-        </is>
-      </c>
-      <c r="E142" s="11" t="inlineStr">
-        <is>
-          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
-        </is>
-      </c>
-      <c r="F142" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G142" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H142" s="13" t="n">
-        <v>15</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 销售交易  (Sales Trading)</t>
+        </is>
       </c>
     </row>
     <row r="143" ht="28" customHeight="1">
@@ -7267,44 +8217,77 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>F10-06</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D143" s="27" t="inlineStr">
         <is>
-          <t>智能推荐系统</t>
+          <t>销交工作台</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
+          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G143" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G143" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H143" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
-        </is>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>F10-02</t>
+        </is>
+      </c>
+      <c r="D144" s="27" t="inlineStr">
+        <is>
+          <t>债券过滤与筛选</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G144" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H144" s="13" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -7314,37 +8297,37 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>F11-01</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D145" s="27" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G145" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G145" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H145" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -7354,37 +8337,37 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D146" s="27" t="inlineStr">
         <is>
-          <t>CDS/CLN定价</t>
+          <t>交易执行与审批</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G146" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G146" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H146" s="13" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -7394,17 +8377,17 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D147" s="27" t="inlineStr">
         <is>
-          <t>信用评级动态监控</t>
+          <t>风控检查</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr">
@@ -7418,100 +8401,100 @@
         </is>
       </c>
       <c r="H147" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148" ht="28" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B148" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="inlineStr">
+        <is>
+          <t>F10-06</t>
+        </is>
+      </c>
+      <c r="D148" s="27" t="inlineStr">
+        <is>
+          <t>智能推荐系统</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G148" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H148" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="28" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
           <t>信用债/信用衍生品</t>
         </is>
       </c>
-      <c r="B148" s="10" t="inlineStr">
+      <c r="B150" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C148" s="10" t="inlineStr">
-        <is>
-          <t>F11-04</t>
-        </is>
-      </c>
-      <c r="D148" s="27" t="inlineStr">
-        <is>
-          <t>违约概率（PD）建模</t>
-        </is>
-      </c>
-      <c r="E148" s="11" t="inlineStr">
-        <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
-        </is>
-      </c>
-      <c r="F148" s="11" t="inlineStr">
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>F11-01</t>
+        </is>
+      </c>
+      <c r="D150" s="27" t="inlineStr">
+        <is>
+          <t>信用利差分析</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+        </is>
+      </c>
+      <c r="F150" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G148" s="23" t="inlineStr">
+      <c r="G150" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H148" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="149" ht="28" customHeight="1">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B149" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>F11-05</t>
-        </is>
-      </c>
-      <c r="D149" s="27" t="inlineStr">
-        <is>
-          <t>集中度限额管理</t>
-        </is>
-      </c>
-      <c r="E149" s="11" t="inlineStr">
-        <is>
-          <t>行业/发行人/评级集中度多维限额，超限预警</t>
-        </is>
-      </c>
-      <c r="F149" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G149" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H149" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 投顾服务  (Investment Advisory)</t>
-        </is>
+      <c r="H150" s="13" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -7521,37 +8504,37 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>F12-01</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D151" s="27" t="inlineStr">
         <is>
-          <t>投顾工作台</t>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G151" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G151" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H151" s="13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -7561,17 +8544,17 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D152" s="27" t="inlineStr">
         <is>
-          <t>客户终端</t>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
@@ -7591,7 +8574,7 @@
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
@@ -7601,37 +8584,37 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F11-04</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>违约概率（PD）建模</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G153" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H153" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
@@ -7641,71 +8624,38 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F11-05</t>
         </is>
       </c>
       <c r="D154" s="27" t="inlineStr">
         <is>
-          <t>账户分析报告</t>
+          <t>集中度限额管理</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+          <t>行业/发行人/评级集中度多维限额，超限预警</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G154" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G154" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H154" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="155" ht="28" customHeight="1">
-      <c r="A155" s="11" t="inlineStr">
-        <is>
-          <t>投顾服务</t>
-        </is>
-      </c>
-      <c r="B155" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C155" s="10" t="inlineStr">
-        <is>
-          <t>F12-05</t>
-        </is>
-      </c>
-      <c r="D155" s="27" t="inlineStr">
-        <is>
-          <t>投研报告服务</t>
-        </is>
-      </c>
-      <c r="E155" s="11" t="inlineStr">
-        <is>
-          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
-        </is>
-      </c>
-      <c r="F155" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G155" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H155" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 投顾服务  (Investment Advisory)</t>
+        </is>
       </c>
     </row>
     <row r="156" ht="28" customHeight="1">
@@ -7721,44 +8671,77 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>F12-06</t>
+          <t>F12-01</t>
         </is>
       </c>
       <c r="D156" s="27" t="inlineStr">
         <is>
-          <t>客户服务与基础服务</t>
+          <t>投顾工作台</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G156" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G156" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H156" s="13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
-        </is>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" ht="28" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>F12-02</t>
+        </is>
+      </c>
+      <c r="D157" s="27" t="inlineStr">
+        <is>
+          <t>客户终端</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G157" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H157" s="13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
@@ -7768,37 +8751,37 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D158" s="27" t="inlineStr">
         <is>
-          <t>TRS交易端</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G158" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G158" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H158" s="13" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="159" ht="28" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
@@ -7808,17 +8791,17 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D159" s="27" t="inlineStr">
         <is>
-          <t>TRS客户端</t>
+          <t>账户分析报告</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr">
@@ -7838,7 +8821,7 @@
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
@@ -7848,17 +8831,17 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F12-05</t>
         </is>
       </c>
       <c r="D160" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>投研报告服务</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr">
@@ -7872,13 +8855,13 @@
         </is>
       </c>
       <c r="H160" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
@@ -7888,71 +8871,38 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F12-06</t>
         </is>
       </c>
       <c r="D161" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>客户服务与基础服务</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G161" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G161" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H161" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="162" ht="28" customHeight="1">
-      <c r="A162" s="11" t="inlineStr">
-        <is>
-          <t>TRS收益互换</t>
-        </is>
-      </c>
-      <c r="B162" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C162" s="10" t="inlineStr">
-        <is>
-          <t>F13-05</t>
-        </is>
-      </c>
-      <c r="D162" s="27" t="inlineStr">
-        <is>
-          <t>通知与确认文件</t>
-        </is>
-      </c>
-      <c r="E162" s="11" t="inlineStr">
-        <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
-        </is>
-      </c>
-      <c r="F162" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G162" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H162" s="13" t="n">
-        <v>15</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+        </is>
       </c>
     </row>
     <row r="163" ht="28" customHeight="1">
@@ -7968,269 +8918,469 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D163" s="27" t="inlineStr">
+        <is>
+          <t>TRS交易端</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G163" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H163" s="13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164" ht="28" customHeight="1">
+      <c r="A164" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D164" s="27" t="inlineStr">
+        <is>
+          <t>TRS客户端</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+        </is>
+      </c>
+      <c r="F164" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G164" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H164" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" ht="28" customHeight="1">
+      <c r="A165" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D165" s="27" t="inlineStr">
+        <is>
+          <t>TRS管理端</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+        </is>
+      </c>
+      <c r="F165" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G165" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H165" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" ht="28" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D166" s="27" t="inlineStr">
+        <is>
+          <t>自动对冲</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G166" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H166" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" ht="28" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D167" s="27" t="inlineStr">
+        <is>
+          <t>通知与确认文件</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G167" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H167" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" ht="28" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
           <t>F13-06</t>
         </is>
       </c>
-      <c r="D163" s="27" t="inlineStr">
+      <c r="D168" s="27" t="inlineStr">
         <is>
           <t>系统集成</t>
         </is>
       </c>
-      <c r="E163" s="11" t="inlineStr">
+      <c r="E168" s="11" t="inlineStr">
         <is>
           <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
         </is>
       </c>
-      <c r="F163" s="11" t="inlineStr">
+      <c r="F168" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G163" s="23" t="inlineStr">
+      <c r="G168" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H163" s="13" t="n">
+      <c r="H168" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="164" ht="20" customHeight="1">
-      <c r="A164" s="29" t="inlineStr">
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="28" customHeight="1">
-      <c r="A165" s="16" t="inlineStr">
+    <row r="170" ht="28" customHeight="1">
+      <c r="A170" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B165" s="15" t="inlineStr">
+      <c r="B170" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C165" s="15" t="inlineStr">
+      <c r="C170" s="15" t="inlineStr">
         <is>
           <t>F15-01</t>
         </is>
       </c>
-      <c r="D165" s="30" t="inlineStr">
+      <c r="D170" s="30" t="inlineStr">
         <is>
           <t>双边报价引擎</t>
         </is>
       </c>
-      <c r="E165" s="16" t="inlineStr">
+      <c r="E170" s="16" t="inlineStr">
         <is>
           <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
-      <c r="F165" s="16" t="inlineStr">
+      <c r="F170" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G165" s="28" t="inlineStr">
+      <c r="G170" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H165" s="18" t="n">
+      <c r="H170" s="18" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="166" ht="28" customHeight="1">
-      <c r="A166" s="16" t="inlineStr">
+    <row r="171" ht="28" customHeight="1">
+      <c r="A171" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B166" s="15" t="inlineStr">
+      <c r="B171" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C166" s="15" t="inlineStr">
+      <c r="C171" s="15" t="inlineStr">
         <is>
           <t>F15-02</t>
         </is>
       </c>
-      <c r="D166" s="30" t="inlineStr">
+      <c r="D171" s="30" t="inlineStr">
         <is>
           <t>库存风险实时管理</t>
         </is>
       </c>
-      <c r="E166" s="16" t="inlineStr">
+      <c r="E171" s="16" t="inlineStr">
         <is>
           <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
-      <c r="F166" s="16" t="inlineStr">
+      <c r="F171" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G166" s="28" t="inlineStr">
+      <c r="G171" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H166" s="18" t="n">
+      <c r="H171" s="18" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="167" ht="28" customHeight="1">
-      <c r="A167" s="16" t="inlineStr">
+    <row r="172" ht="28" customHeight="1">
+      <c r="A172" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B167" s="15" t="inlineStr">
+      <c r="B172" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C167" s="15" t="inlineStr">
+      <c r="C172" s="15" t="inlineStr">
         <is>
           <t>F15-03</t>
         </is>
       </c>
-      <c r="D167" s="30" t="inlineStr">
+      <c r="D172" s="30" t="inlineStr">
         <is>
           <t>报价优化算法</t>
         </is>
       </c>
-      <c r="E167" s="16" t="inlineStr">
+      <c r="E172" s="16" t="inlineStr">
         <is>
           <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
-      <c r="F167" s="16" t="inlineStr">
+      <c r="F172" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G167" s="28" t="inlineStr">
+      <c r="G172" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H167" s="18" t="n">
+      <c r="H172" s="18" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="168" ht="28" customHeight="1">
-      <c r="A168" s="16" t="inlineStr">
+    <row r="173" ht="28" customHeight="1">
+      <c r="A173" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B168" s="15" t="inlineStr">
+      <c r="B173" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C168" s="15" t="inlineStr">
+      <c r="C173" s="15" t="inlineStr">
         <is>
           <t>F15-04</t>
         </is>
       </c>
-      <c r="D168" s="30" t="inlineStr">
+      <c r="D173" s="30" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E168" s="16" t="inlineStr">
+      <c r="E173" s="16" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，策略调优</t>
         </is>
       </c>
-      <c r="F168" s="16" t="inlineStr">
+      <c r="F173" s="16" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G168" s="23" t="inlineStr">
+      <c r="G173" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H168" s="18" t="n">
+      <c r="H173" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="169" ht="28" customHeight="1">
-      <c r="A169" s="16" t="inlineStr">
+    <row r="174" ht="28" customHeight="1">
+      <c r="A174" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B169" s="15" t="inlineStr">
+      <c r="B174" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C169" s="15" t="inlineStr">
+      <c r="C174" s="15" t="inlineStr">
         <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D169" s="30" t="inlineStr">
+      <c r="D174" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E169" s="16" t="inlineStr">
+      <c r="E174" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F169" s="16" t="inlineStr">
+      <c r="F174" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G169" s="24" t="inlineStr">
+      <c r="G174" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H169" s="18" t="n">
+      <c r="H174" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="19" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H170" s="20">
-        <f>SUM(H3:H169)</f>
+      <c r="H175" s="20">
+        <f>SUM(H3:H174)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A170:G170"/>
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="A100:H100"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A106:H106"/>
-    <mergeCell ref="A124:H124"/>
-    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A155:H155"/>
+    <mergeCell ref="A162:H162"/>
     <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A144:H144"/>
-    <mergeCell ref="A157:H157"/>
-    <mergeCell ref="A164:H164"/>
-    <mergeCell ref="A137:H137"/>
+    <mergeCell ref="A175:G175"/>
+    <mergeCell ref="A129:H129"/>
     <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A142:H142"/>
+    <mergeCell ref="A169:H169"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A150:H150"/>
+    <mergeCell ref="A111:H111"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A149:H149"/>
+    <mergeCell ref="A135:H135"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8989,7 +10139,7 @@
         </is>
       </c>
       <c r="H4" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="8" t="n">
         <v>6</v>
@@ -13638,7 +14788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13656,21 +14806,21 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="38" t="inlineStr">
         <is>
-          <t>系统详情：组合管理+绩效归因  |  Portfolio Mgmt &amp; Perf</t>
+          <t>系统详情：事前风控/合规  |  Pre-trade Risk &amp; Compliance</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>战略定位：17项功能含量化底座集成；Slide44全景展开   |   来源：Slide 44   |   数据输入：交易数据 / 头寸数据 / 行情数据 / 估值数据   |   量化底座：定价计算 · 利率曲线 · 因子模型</t>
+          <t>战略定位：嵌入交易前拦截，三端架构（风控/用户/管理），AI聊天合规监控为核心差异化；对应PPT Slide 51   |   来源：Slide 51</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="40" t="inlineStr">
         <is>
-          <t>模块：组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)  |  优先级：P1  |  竞品：SimCorp/衡泰  |  华锐基础：M9 PMS模块  |  工期：12月  团队：12人</t>
+          <t>模块：事前风控/合规  (Pre-trade Risk &amp; Compliance)  |  优先级：P1  |  竞品：恒生/金证  |  华锐基础：ARC合规模块  |  工期：6月  团队：6人</t>
         </is>
       </c>
     </row>
@@ -13729,48 +14879,40 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>A. 组合分析</t>
+          <t>D1. 规则配置（风控端）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>A. 组合分析</t>
+          <t>D1. 规则配置（风控端）</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F07-01</t>
+          <t>F06-01</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>债券横截面与时序分析</t>
+          <t>风控规则配置</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>横截面信号与实际收益相关性&gt;0.3</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>AMD行情平台/估值数据</t>
-        </is>
-      </c>
+          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -13782,41 +14924,33 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>A. 组合分析</t>
+          <t>D1. 规则配置（风控端）</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F07-02</t>
+          <t>F06-02</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>多维度限额配置</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>量化定价引擎/AMD行情</t>
-        </is>
-      </c>
+          <t>交易对手/交易员/券三维度限额设置，集中度/净敞口/利率敏感度/单笔名义多类型限额</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="H7" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -13828,41 +14962,33 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>A. 组合分析</t>
+          <t>D1. 规则配置（风控端）</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F07-03</t>
+          <t>F06-03</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>组合相关度分析</t>
+          <t>白黑名单管理</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>相关矩阵计算&lt;30s（500券组合）</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>IBOR头寸/AMD历史行情</t>
-        </is>
-      </c>
+          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="42" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -13874,48 +15000,40 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>B. 风险计量</t>
+          <t>D2. 交易前拦截（用户端）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>B. 风险计量</t>
+          <t>D2. 交易前拦截（用户端）</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F06-04</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>实时事前风控拦截</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>FICC风险计量平台/量化定价引擎</t>
-        </is>
-      </c>
-      <c r="G10" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -13927,41 +15045,33 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>B. 风险计量</t>
+          <t>D2. 交易前拦截（用户端）</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F07-05</t>
+          <t>F06-05</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析</t>
+          <t>异常报备工作流</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>量化定价引擎Greeks接口</t>
-        </is>
-      </c>
-      <c r="G11" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -13973,34 +15083,26 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>B. 风险计量</t>
+          <t>D2. 交易前拦截（用户端）</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F06-06</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>极端事件分析</t>
+          <t>AI聊天合规监控</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>历史情景复现误差&lt;1%</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>FICC风险计量平台</t>
-        </is>
-      </c>
+          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="41" t="inlineStr">
         <is>
           <t>高</t>
@@ -14016,97 +15118,81 @@
       </c>
       <c r="J12" s="5" t="inlineStr"/>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="43" t="inlineStr">
-        <is>
-          <t>C. 绩效归因</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>C. 绩效归因</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>F07-07</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>指数比较分析</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>AMD中债估值/IBOR持仓</t>
-        </is>
-      </c>
-      <c r="G14" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>D2. 交易前拦截（用户端）</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>F06-07</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>AI交易要素提取</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>D3. 统计与审计（管理端）</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C. 绩效归因</t>
+          <t>D3. 统计与审计（管理端）</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F06-08</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>日内异常统计看板</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>IBOR持仓/AMD行情/指数数据</t>
-        </is>
-      </c>
-      <c r="G15" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -14115,51 +15201,74 @@
       </c>
       <c r="J15" s="5" t="inlineStr"/>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>D3. 统计与审计（管理端）</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>F06-09</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>合规审批工作流</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>D. 组合优化与再平衡</t>
+          <t>D3. 统计与审计（管理端）</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F07-09</t>
+          <t>F06-10</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>虚拟组合分析</t>
+          <t>责任留痕与审计追踪</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>IBOR/现券交易系统</t>
-        </is>
-      </c>
-      <c r="G17" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -14168,413 +15277,28 @@
       </c>
       <c r="J17" s="5" t="inlineStr"/>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>F07-10</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>再平衡方案试算与比较</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>事前风控/合规/IBOR/现券系统</t>
-        </is>
-      </c>
-      <c r="G18" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>F07-11</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>资产配置策略分析</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>AMD宏观数据/因子模型</t>
-        </is>
-      </c>
-      <c r="G19" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>F07-12</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>固收+策略分析</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>IBOR/利率衍生品系统</t>
-        </is>
-      </c>
-      <c r="G20" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>F07-13</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>量化策略组合分析</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>策略容量计算误差&lt;5%</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>策略投资/量化系统</t>
-        </is>
-      </c>
-      <c r="G21" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>E. 流动性管理</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>E. 流动性管理</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>F07-14</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>流动性分析</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>AMD行情/IBOR持仓</t>
-        </is>
-      </c>
-      <c r="G23" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="44" t="inlineStr">
-        <is>
-          <t>F. 量化底座集成</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>F. 量化底座集成</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>F07-15</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>定价计算集成</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="G25" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>F. 量化底座集成</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>F07-16</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>利率曲线集成</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>AMD行情平台/量化定价引擎</t>
-        </is>
-      </c>
-      <c r="G26" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr"/>
-    </row>
-    <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>F. 量化底座集成</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>F07-17</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>因子模型</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>AMD历史行情/IBOR持仓</t>
-        </is>
-      </c>
-      <c r="G27" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="40" t="inlineStr">
-        <is>
-          <t>合计 17项功能  |  P1: 13项  |  P2: 4项</t>
-        </is>
-      </c>
-      <c r="H28" s="20">
-        <f>SUM(H5:H27)</f>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>合计 10项功能  |  P1: 10项  |  P2: 0项</t>
+        </is>
+      </c>
+      <c r="H18" s="20">
+        <f>SUM(H5:H17)</f>
         <v/>
       </c>
-      <c r="I28" s="34" t="inlineStr"/>
-      <c r="J28" s="34" t="inlineStr"/>
+      <c r="I18" s="34" t="inlineStr"/>
+      <c r="J18" s="34" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A24:J24"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_异常交易风控" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_事前风控_合规" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_策略投资_量化" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1421,21 +1422,21 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>低延迟ATP执行层</t>
+          <t>低延迟ATP执行层/定价平台</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>12</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="P10" s="5" t="inlineStr">
         <is>
-          <t>因子框架+回测引擎，低延迟执行</t>
+          <t>因子框架+回测引擎+模拟盘+AI辅助开发，覆盖利差/基差/跨市场套利等固收量化策略全流程；对应PPT Slide 41</t>
         </is>
       </c>
     </row>
@@ -2866,13 +2867,628 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：策略投资/量化  |  Quant Strategy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：因子框架+回测引擎+模拟盘+AI辅助开发，覆盖利差/基差/跨市场套利等固收量化策略全流程；对应PPT Slide 41   |   来源：Slide 41</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：策略投资/量化  (Quant Strategy)  |  优先级：P1  |  竞品：无主导者  |  华锐基础：低延迟ATP执行层/定价平台  |  工期：12月  团队：12人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. 策略研发</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>D1. 策略研发</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>策略编写与版本管理</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>D1. 策略研发</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>F08-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>AI辅助策略开发</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>D1. 策略研发</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F08-03</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>因子挖掘与管理</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>因子编写，信号生成，因子库管理，AlphaLens因子有效性分析，量化模型库，宏观/技术/基本面因子</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D2. 回测与模拟验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>D2. 回测与模拟验证</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>F08-04</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Tick级回测引擎</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>D2. 回测与模拟验证</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>F08-05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>模拟盘验证</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>D3. 策略上线管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>D3. 策略上线管理</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>F08-06</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>策略上线审批</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>D3. 策略上线管理</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>F08-07</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>策略运行管理</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>D3. 策略上线管理</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>F08-08</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>策略绩效分析</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>D4. 行情分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>D4. 行情分析</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>F08-09</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>实时多市场行情</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>D4. 行情分析</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>F08-10</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>历史行情回放</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>D5. 量化底座</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>D5. 量化底座</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>F08-11</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>CEP流引擎与信号调度</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>D5. 量化底座</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>F08-12</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>基础数据与模型底座</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>宏观因子库，债券曲线模型，估值数据接入，账户权限管理，AI引擎集成接口</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>合计 12项功能  |  P1: 12项  |  P2: 0项</t>
+        </is>
+      </c>
+      <c r="H22" s="20">
+        <f>SUM(H5:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="34" t="inlineStr"/>
+      <c r="J22" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A19:J19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7768,12 +8384,12 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>因子模型框架</t>
+          <t>策略编写与版本管理</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>多因子Alpha模型+风险因子，支持自定义因子上传与测试</t>
+          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -7808,26 +8424,26 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>AI辅助策略开发</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化</t>
+          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G131" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G131" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H131" s="8" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1">
@@ -7848,12 +8464,12 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>信号生成与调度</t>
+          <t>因子挖掘与管理</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>策略信号实时计算，支持Python/C++策略脚本沙箱运行</t>
+          <t>因子编写，信号生成，因子库管理，AlphaLens因子有效性分析，量化模型库，宏观/技术/基本面因子</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -7888,12 +8504,12 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>低延迟执行接口</t>
+          <t>Tick级回测引擎</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>与ATP超低延迟执行层对接，算法拆单（TWAP/VWAP/IS）</t>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -7907,7 +8523,7 @@
         </is>
       </c>
       <c r="H133" s="8" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134" ht="28" customHeight="1">
@@ -7928,286 +8544,319 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>实时策略监控</t>
+          <t>模拟盘验证</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>持仓/PnL/回撤/Sharpe实时看板，风险触发自动平仓</t>
+          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G134" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>F08-06</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>策略上线审批</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G134" s="24" t="inlineStr">
+      <c r="G135" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H134" s="8" t="n">
+      <c r="H135" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 定价平台  (Pricing Platform)</t>
-        </is>
-      </c>
-    </row>
     <row r="136" ht="28" customHeight="1">
-      <c r="A136" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B136" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D136" s="27" t="inlineStr">
-        <is>
-          <t>期限结构模型</t>
-        </is>
-      </c>
-      <c r="E136" s="11" t="inlineStr">
-        <is>
-          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
-        </is>
-      </c>
-      <c r="F136" s="11" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>F08-07</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>策略运行管理</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G136" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H136" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>F08-08</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>策略绩效分析</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G137" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>F08-09</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>实时多市场行情</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H138" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" ht="28" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>F08-10</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>历史行情回放</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G139" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" ht="28" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>F08-11</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>CEP流引擎与信号调度</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G136" s="28" t="inlineStr">
+      <c r="G140" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H136" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="137" ht="28" customHeight="1">
-      <c r="A137" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C137" s="10" t="inlineStr">
-        <is>
-          <t>F09-02</t>
-        </is>
-      </c>
-      <c r="D137" s="27" t="inlineStr">
-        <is>
-          <t>蒙特卡洛求解器</t>
-        </is>
-      </c>
-      <c r="E137" s="11" t="inlineStr">
-        <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
-        </is>
-      </c>
-      <c r="F137" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G137" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H137" s="13" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="138" ht="28" customHeight="1">
-      <c r="A138" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B138" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C138" s="10" t="inlineStr">
-        <is>
-          <t>F09-03</t>
-        </is>
-      </c>
-      <c r="D138" s="27" t="inlineStr">
-        <is>
-          <t>有限差分（PDE）</t>
-        </is>
-      </c>
-      <c r="E138" s="11" t="inlineStr">
-        <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
-        </is>
-      </c>
-      <c r="F138" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G138" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H138" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="139" ht="28" customHeight="1">
-      <c r="A139" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B139" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C139" s="10" t="inlineStr">
-        <is>
-          <t>F09-04</t>
-        </is>
-      </c>
-      <c r="D139" s="27" t="inlineStr">
-        <is>
-          <t>实时Greeks</t>
-        </is>
-      </c>
-      <c r="E139" s="11" t="inlineStr">
-        <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
-        </is>
-      </c>
-      <c r="F139" s="11" t="inlineStr">
+      <c r="H140" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>F08-12</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>基础数据与模型底座</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>宏观因子库，债券曲线模型，估值数据接入，账户权限管理，AI引擎集成接口</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G139" s="23" t="inlineStr">
+      <c r="G141" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H139" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="140" ht="28" customHeight="1">
-      <c r="A140" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B140" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C140" s="10" t="inlineStr">
-        <is>
-          <t>F09-05</t>
-        </is>
-      </c>
-      <c r="D140" s="27" t="inlineStr">
-        <is>
-          <t>定价服务微服务架构</t>
-        </is>
-      </c>
-      <c r="E140" s="11" t="inlineStr">
-        <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
-        </is>
-      </c>
-      <c r="F140" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G140" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H140" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="141" ht="28" customHeight="1">
-      <c r="A141" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B141" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C141" s="10" t="inlineStr">
-        <is>
-          <t>F09-06</t>
-        </is>
-      </c>
-      <c r="D141" s="27" t="inlineStr">
-        <is>
-          <t>历史估值回测</t>
-        </is>
-      </c>
-      <c r="E141" s="11" t="inlineStr">
-        <is>
-          <t>基于历史行情重放定价误差分析，模型验证框架</t>
-        </is>
-      </c>
-      <c r="F141" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G141" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H141" s="13" t="n">
+      <c r="H141" s="8" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="26" t="inlineStr">
         <is>
-          <t>【P2】 销售交易  (Sales Trading)</t>
+          <t>【P2】 定价平台  (Pricing Platform)</t>
         </is>
       </c>
     </row>
     <row r="143" ht="28" customHeight="1">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
@@ -8217,37 +8866,37 @@
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>F10-01</t>
+          <t>F09-01</t>
         </is>
       </c>
       <c r="D143" s="27" t="inlineStr">
         <is>
-          <t>销交工作台</t>
+          <t>期限结构模型</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
+          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G143" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G143" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H143" s="13" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144" ht="28" customHeight="1">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
@@ -8257,37 +8906,37 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>F10-02</t>
+          <t>F09-02</t>
         </is>
       </c>
       <c r="D144" s="27" t="inlineStr">
         <is>
-          <t>债券过滤与筛选</t>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G144" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G144" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H144" s="13" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
     </row>
     <row r="145" ht="28" customHeight="1">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
@@ -8297,37 +8946,37 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>F10-03</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D145" s="27" t="inlineStr">
         <is>
-          <t>报价撮合与对价</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G145" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G145" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H145" s="13" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="146" ht="28" customHeight="1">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
@@ -8337,37 +8986,37 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>F10-04</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D146" s="27" t="inlineStr">
         <is>
-          <t>交易执行与审批</t>
+          <t>实时Greeks</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G146" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G146" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H146" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147" ht="28" customHeight="1">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
@@ -8377,37 +9026,37 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>F10-05</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D147" s="27" t="inlineStr">
         <is>
-          <t>风控检查</t>
+          <t>定价服务微服务架构</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
+          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G147" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H147" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148" ht="28" customHeight="1">
       <c r="A148" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
@@ -8417,17 +9066,17 @@
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>F10-06</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D148" s="27" t="inlineStr">
         <is>
-          <t>智能推荐系统</t>
+          <t>历史估值回测</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
+          <t>基于历史行情重放定价误差分析，模型验证框架</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
@@ -8441,20 +9090,20 @@
         </is>
       </c>
       <c r="H148" s="13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="26" t="inlineStr">
         <is>
-          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+          <t>【P2】 销售交易  (Sales Trading)</t>
         </is>
       </c>
     </row>
     <row r="150" ht="28" customHeight="1">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
@@ -8464,37 +9113,37 @@
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>F11-01</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D150" s="27" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>销交工作台</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G150" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G150" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H150" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -8504,37 +9153,37 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D151" s="27" t="inlineStr">
         <is>
-          <t>CDS/CLN定价</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G151" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G151" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H151" s="13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -8544,17 +9193,17 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D152" s="27" t="inlineStr">
         <is>
-          <t>信用评级动态监控</t>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
@@ -8574,7 +9223,7 @@
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
@@ -8584,37 +9233,37 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>违约概率（PD）建模</t>
+          <t>交易执行与审批</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G153" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G153" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H153" s="13" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
     </row>
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
@@ -8624,17 +9273,17 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>F11-05</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D154" s="27" t="inlineStr">
         <is>
-          <t>集中度限额管理</t>
+          <t>风控检查</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>行业/发行人/评级集中度多维限额，超限预警</t>
+          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
@@ -8648,60 +9297,60 @@
         </is>
       </c>
       <c r="H154" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 投顾服务  (Investment Advisory)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="28" customHeight="1">
-      <c r="A156" s="11" t="inlineStr">
-        <is>
-          <t>投顾服务</t>
-        </is>
-      </c>
-      <c r="B156" s="10" t="inlineStr">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" ht="28" customHeight="1">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C156" s="10" t="inlineStr">
-        <is>
-          <t>F12-01</t>
-        </is>
-      </c>
-      <c r="D156" s="27" t="inlineStr">
-        <is>
-          <t>投顾工作台</t>
-        </is>
-      </c>
-      <c r="E156" s="11" t="inlineStr">
-        <is>
-          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
-        </is>
-      </c>
-      <c r="F156" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G156" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H156" s="13" t="n">
-        <v>20</v>
+      <c r="C155" s="10" t="inlineStr">
+        <is>
+          <t>F10-06</t>
+        </is>
+      </c>
+      <c r="D155" s="27" t="inlineStr">
+        <is>
+          <t>智能推荐系统</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H155" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+        </is>
       </c>
     </row>
     <row r="157" ht="28" customHeight="1">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
@@ -8711,37 +9360,37 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F11-01</t>
         </is>
       </c>
       <c r="D157" s="27" t="inlineStr">
         <is>
-          <t>客户终端</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G157" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G157" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H157" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
@@ -8751,37 +9400,37 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D158" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G158" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G158" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H158" s="13" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="159" ht="28" customHeight="1">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
@@ -8791,37 +9440,37 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D159" s="27" t="inlineStr">
         <is>
-          <t>账户分析报告</t>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G159" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G159" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H159" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
@@ -8831,37 +9480,37 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F11-04</t>
         </is>
       </c>
       <c r="D160" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>违约概率（PD）建模</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G160" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G160" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H160" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
@@ -8871,44 +9520,44 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>F12-06</t>
+          <t>F11-05</t>
         </is>
       </c>
       <c r="D161" s="27" t="inlineStr">
         <is>
-          <t>客户服务与基础服务</t>
+          <t>集中度限额管理</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+          <t>行业/发行人/评级集中度多维限额，超限预警</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G161" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G161" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H161" s="13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="26" t="inlineStr">
         <is>
-          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+          <t>【P2】 投顾服务  (Investment Advisory)</t>
         </is>
       </c>
     </row>
     <row r="163" ht="28" customHeight="1">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
@@ -8918,37 +9567,37 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F12-01</t>
         </is>
       </c>
       <c r="D163" s="27" t="inlineStr">
         <is>
-          <t>TRS交易端</t>
+          <t>投顾工作台</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G163" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G163" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H163" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" ht="28" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
@@ -8958,37 +9607,37 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D164" s="27" t="inlineStr">
         <is>
-          <t>TRS客户端</t>
+          <t>客户终端</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G164" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G164" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H164" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165" ht="28" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
@@ -8998,17 +9647,17 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D165" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr">
@@ -9022,13 +9671,13 @@
         </is>
       </c>
       <c r="H165" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="166" ht="28" customHeight="1">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B166" s="10" t="inlineStr">
@@ -9038,17 +9687,17 @@
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D166" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>账户分析报告</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr">
@@ -9068,7 +9717,7 @@
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B167" s="10" t="inlineStr">
@@ -9078,17 +9727,17 @@
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F12-05</t>
         </is>
       </c>
       <c r="D167" s="27" t="inlineStr">
         <is>
-          <t>通知与确认文件</t>
+          <t>投研报告服务</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr">
@@ -9108,258 +9757,505 @@
     <row r="168" ht="28" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>F12-06</t>
+        </is>
+      </c>
+      <c r="D168" s="27" t="inlineStr">
+        <is>
+          <t>客户服务与基础服务</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+        </is>
+      </c>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G168" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H168" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="28" customHeight="1">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
           <t>TRS收益互换</t>
         </is>
       </c>
-      <c r="B168" s="10" t="inlineStr">
+      <c r="B170" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C168" s="10" t="inlineStr">
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D170" s="27" t="inlineStr">
+        <is>
+          <t>TRS交易端</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+        </is>
+      </c>
+      <c r="F170" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H170" s="13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="171" ht="28" customHeight="1">
+      <c r="A171" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B171" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C171" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D171" s="27" t="inlineStr">
+        <is>
+          <t>TRS客户端</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G171" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H171" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" ht="28" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D172" s="27" t="inlineStr">
+        <is>
+          <t>TRS管理端</t>
+        </is>
+      </c>
+      <c r="E172" s="11" t="inlineStr">
+        <is>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+        </is>
+      </c>
+      <c r="F172" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G172" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H172" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="173" ht="28" customHeight="1">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D173" s="27" t="inlineStr">
+        <is>
+          <t>自动对冲</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G173" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H173" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" ht="28" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B174" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D174" s="27" t="inlineStr">
+        <is>
+          <t>通知与确认文件</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="F174" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G174" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H174" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175" ht="28" customHeight="1">
+      <c r="A175" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B175" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C175" s="10" t="inlineStr">
         <is>
           <t>F13-06</t>
         </is>
       </c>
-      <c r="D168" s="27" t="inlineStr">
+      <c r="D175" s="27" t="inlineStr">
         <is>
           <t>系统集成</t>
         </is>
       </c>
-      <c r="E168" s="11" t="inlineStr">
+      <c r="E175" s="11" t="inlineStr">
         <is>
           <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
         </is>
       </c>
-      <c r="F168" s="11" t="inlineStr">
+      <c r="F175" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G168" s="23" t="inlineStr">
+      <c r="G175" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H168" s="13" t="n">
+      <c r="H175" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="29" t="inlineStr">
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="28" customHeight="1">
-      <c r="A170" s="16" t="inlineStr">
+    <row r="177" ht="28" customHeight="1">
+      <c r="A177" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B170" s="15" t="inlineStr">
+      <c r="B177" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C170" s="15" t="inlineStr">
+      <c r="C177" s="15" t="inlineStr">
         <is>
           <t>F15-01</t>
         </is>
       </c>
-      <c r="D170" s="30" t="inlineStr">
+      <c r="D177" s="30" t="inlineStr">
         <is>
           <t>双边报价引擎</t>
         </is>
       </c>
-      <c r="E170" s="16" t="inlineStr">
+      <c r="E177" s="16" t="inlineStr">
         <is>
           <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
-      <c r="F170" s="16" t="inlineStr">
+      <c r="F177" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G170" s="28" t="inlineStr">
+      <c r="G177" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H170" s="18" t="n">
+      <c r="H177" s="18" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="171" ht="28" customHeight="1">
-      <c r="A171" s="16" t="inlineStr">
+    <row r="178" ht="28" customHeight="1">
+      <c r="A178" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B171" s="15" t="inlineStr">
+      <c r="B178" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C171" s="15" t="inlineStr">
+      <c r="C178" s="15" t="inlineStr">
         <is>
           <t>F15-02</t>
         </is>
       </c>
-      <c r="D171" s="30" t="inlineStr">
+      <c r="D178" s="30" t="inlineStr">
         <is>
           <t>库存风险实时管理</t>
         </is>
       </c>
-      <c r="E171" s="16" t="inlineStr">
+      <c r="E178" s="16" t="inlineStr">
         <is>
           <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
-      <c r="F171" s="16" t="inlineStr">
+      <c r="F178" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G171" s="28" t="inlineStr">
+      <c r="G178" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H171" s="18" t="n">
+      <c r="H178" s="18" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="172" ht="28" customHeight="1">
-      <c r="A172" s="16" t="inlineStr">
+    <row r="179" ht="28" customHeight="1">
+      <c r="A179" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B172" s="15" t="inlineStr">
+      <c r="B179" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C172" s="15" t="inlineStr">
+      <c r="C179" s="15" t="inlineStr">
         <is>
           <t>F15-03</t>
         </is>
       </c>
-      <c r="D172" s="30" t="inlineStr">
+      <c r="D179" s="30" t="inlineStr">
         <is>
           <t>报价优化算法</t>
         </is>
       </c>
-      <c r="E172" s="16" t="inlineStr">
+      <c r="E179" s="16" t="inlineStr">
         <is>
           <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
-      <c r="F172" s="16" t="inlineStr">
+      <c r="F179" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G172" s="28" t="inlineStr">
+      <c r="G179" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H172" s="18" t="n">
+      <c r="H179" s="18" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="173" ht="28" customHeight="1">
-      <c r="A173" s="16" t="inlineStr">
+    <row r="180" ht="28" customHeight="1">
+      <c r="A180" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B173" s="15" t="inlineStr">
+      <c r="B180" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C173" s="15" t="inlineStr">
+      <c r="C180" s="15" t="inlineStr">
         <is>
           <t>F15-04</t>
         </is>
       </c>
-      <c r="D173" s="30" t="inlineStr">
+      <c r="D180" s="30" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E173" s="16" t="inlineStr">
+      <c r="E180" s="16" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，策略调优</t>
         </is>
       </c>
-      <c r="F173" s="16" t="inlineStr">
+      <c r="F180" s="16" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G173" s="23" t="inlineStr">
+      <c r="G180" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H173" s="18" t="n">
+      <c r="H180" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="174" ht="28" customHeight="1">
-      <c r="A174" s="16" t="inlineStr">
+    <row r="181" ht="28" customHeight="1">
+      <c r="A181" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B174" s="15" t="inlineStr">
+      <c r="B181" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C174" s="15" t="inlineStr">
+      <c r="C181" s="15" t="inlineStr">
         <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D174" s="30" t="inlineStr">
+      <c r="D181" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E174" s="16" t="inlineStr">
+      <c r="E181" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F174" s="16" t="inlineStr">
+      <c r="F181" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G174" s="24" t="inlineStr">
+      <c r="G181" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H174" s="18" t="n">
+      <c r="H181" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="19" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H175" s="20">
-        <f>SUM(H3:H174)</f>
+      <c r="H182" s="20">
+        <f>SUM(H3:H181)</f>
         <v/>
       </c>
     </row>
@@ -9368,19 +10264,19 @@
     <mergeCell ref="A67:H67"/>
     <mergeCell ref="A100:H100"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A155:H155"/>
     <mergeCell ref="A162:H162"/>
+    <mergeCell ref="A176:H176"/>
     <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A175:G175"/>
+    <mergeCell ref="A156:H156"/>
     <mergeCell ref="A129:H129"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A142:H142"/>
     <mergeCell ref="A169:H169"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A182:G182"/>
     <mergeCell ref="A111:H111"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A149:H149"/>
-    <mergeCell ref="A135:H135"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10379,7 +11275,7 @@
         </is>
       </c>
       <c r="H9" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>12</v>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -13,11 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P1优先启动计划" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_IBOR投资账薄管理" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_现券交易系统" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_FICC风险计量平台" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_异常交易风控" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_事前风控_合规" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_策略投资_量化" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_FOF投资系统" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_FICC风险计量平台" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_异常交易风控" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_事前风控_合规" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_策略投资_量化" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1924,6 +1925,529 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：事前风控/合规  |  Pre-trade Risk &amp; Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：嵌入交易前拦截，三端架构（风控/用户/管理），AI聊天合规监控为核心差异化；对应PPT Slide 51   |   来源：Slide 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：事前风控/合规  (Pre-trade Risk &amp; Compliance)  |  优先级：P1  |  竞品：恒生/金证  |  华锐基础：ARC合规模块  |  工期：6月  团队：6人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. 规则配置（风控端）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>D1. 规则配置（风控端）</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>F06-01</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>风控规则配置</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>D1. 规则配置（风控端）</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>F06-02</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>多维度限额配置</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>交易对手/交易员/券三维度限额设置，集中度/净敞口/利率敏感度/单笔名义多类型限额</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>D1. 规则配置（风控端）</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>F06-03</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>白黑名单管理</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D2. 交易前拦截（用户端）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>D2. 交易前拦截（用户端）</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>F06-04</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>实时事前风控拦截</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr"/>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>D2. 交易前拦截（用户端）</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>F06-05</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>异常报备工作流</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>D2. 交易前拦截（用户端）</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>F06-06</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>AI聊天合规监控</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>D2. 交易前拦截（用户端）</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>F06-07</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>AI交易要素提取</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>D3. 统计与审计（管理端）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>D3. 统计与审计（管理端）</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>F06-08</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>日内异常统计看板</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>D3. 统计与审计（管理端）</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>F06-09</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>合规审批工作流</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>D3. 统计与审计（管理端）</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>F06-10</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>责任留痕与审计追踪</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>合计 10项功能  |  P1: 10项  |  P2: 0项</t>
+        </is>
+      </c>
+      <c r="H18" s="20">
+        <f>SUM(H5:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="34" t="inlineStr"/>
+      <c r="J18" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2867,7 +3391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3488,7 +4012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5789,12 +6313,12 @@
       </c>
       <c r="D61" s="27" t="inlineStr">
         <is>
-          <t>管理人与基础信息管理</t>
+          <t>管理人与基金基础信息</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>管理人黑名单维护，基金策略分类，基金基础要素（规模/净值/评级）录入与更新</t>
+          <t>管理人黑名单维护，基金策略分类，基金基础要素（规模/净值/评级）录入与更新，管理人信息库</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5834,7 +6358,7 @@
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>通过邮箱/API自动获取基金资产报告，解析持仓明细并入库，多来源数据合并去重</t>
+          <t>通过邮箱/API自动获取基金资产报告，解析持仓明细并入库，多来源数据合并去重，导入工具</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
@@ -5869,26 +6393,26 @@
       </c>
       <c r="D63" s="27" t="inlineStr">
         <is>
-          <t>交易录入与审核</t>
+          <t>子基金持仓穿透</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>申购/赎回/换仓交易录入，交易明细管理，双级审核工作流，审批记录留痕</t>
+          <t>穿透底层基金持仓至个券/个股层面，合并计算组合总敞口，支持集中度与评级分布分析</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G63" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H63" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
@@ -5909,12 +6433,12 @@
       </c>
       <c r="D64" s="27" t="inlineStr">
         <is>
-          <t>组合风控报告生成</t>
+          <t>交易录入与审核</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>按管理人策略限制/投资占比限制/白名单分类生成风控日报和周报，自动推送给风控人员</t>
+          <t>申购/赎回/换仓交易录入，交易明细管理，双级审核工作流（投资助理录入→风控复核），审批记录留痕</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -5949,26 +6473,26 @@
       </c>
       <c r="D65" s="27" t="inlineStr">
         <is>
-          <t>子基金持仓穿透</t>
+          <t>申赎情况跟踪</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>穿透底层基金持仓至个券/个股层面，合并计算组合总敞口，支持集中度与评级分布分析</t>
+          <t>子基金申购/赎回状态全生命周期跟踪，到账确认，净值更新后自动触发持仓重算</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G65" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H65" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
@@ -5989,12 +6513,12 @@
       </c>
       <c r="D66" s="27" t="inlineStr">
         <is>
-          <t>申赎情况跟踪</t>
+          <t>组合风控报告生成</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>子基金申购/赎回状态全生命周期跟踪，到账确认，净值更新后自动触发持仓重算</t>
+          <t>按管理人策略限制/投资占比限制/白名单分类/子基金申赎情况生成风控日报和周报</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr">
@@ -6008,54 +6532,54 @@
         </is>
       </c>
       <c r="H66" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="22" t="inlineStr">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>FOF投资系统</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>F03-07</t>
+        </is>
+      </c>
+      <c r="D67" s="27" t="inlineStr">
+        <is>
+          <t>报告推送与查阅</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>风控日报/周报自动推送给风控人员，支持在线查看与下载，历史报告归档查询</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G67" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="22" t="inlineStr">
         <is>
           <t>【P1】 FICC风险计量平台  (FICC Risk Measurement Platform)</t>
         </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>FICC风险计量平台</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>F04-01</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>组合What-if分析</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>What-if情景建模，Duration &amp; Convexity影响分析，VaR贡献分解，风险因子敞口，集中度分析</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
@@ -6071,17 +6595,17 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>F04-02</t>
+          <t>F04-01</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>授权敞口分析</t>
+          <t>组合What-if分析</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>交易前限额验证，交易对手/集中度/监管/组合约束多维度限额检查，Pre-trade拦截</t>
+          <t>What-if情景建模，Duration &amp; Convexity影响分析，VaR贡献分解，风险因子敞口，集中度分析</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -6095,7 +6619,7 @@
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
@@ -6111,31 +6635,31 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>F04-03</t>
+          <t>F04-02</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>投资预测分析</t>
+          <t>授权敞口分析</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>P&amp;L与风险归因预测建模，收益率曲线/利差/波动率因子预测，组合构建优化，多情景对比分析</t>
+          <t>交易前限额验证，交易对手/集中度/监管/组合约束多维度限额检查，Pre-trade拦截</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G70" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
@@ -6151,17 +6675,17 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>F04-04</t>
+          <t>F04-03</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>实时风险计量</t>
+          <t>投资预测分析</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Real-time DV01/CS01，Live VaR，Dynamic Greeks，日内P&amp;L与归因，风险限额利用率实时展示</t>
+          <t>P&amp;L与风险归因预测建模，收益率曲线/利差/波动率因子预测，组合构建优化，多情景对比分析</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -6175,7 +6699,7 @@
         </is>
       </c>
       <c r="H71" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
@@ -6191,31 +6715,31 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>F04-05</t>
+          <t>F04-04</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>交易对手风险实时监控</t>
+          <t>实时风险计量</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>实时敞口聚合，抵押品监控，信用限额使用率，结算风险，净额结算协议管理</t>
+          <t>Real-time DV01/CS01，Live VaR，Dynamic Greeks，日内P&amp;L与归因，风险限额利用率实时展示</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G72" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H72" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" ht="28" customHeight="1">
@@ -6231,17 +6755,17 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>F04-06</t>
+          <t>F04-05</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>流动性分析与交易成本</t>
+          <t>交易对手风险实时监控</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>执行风险监控，市场冲击分析，流动性成本追踪，滑点计量，最优执行合规</t>
+          <t>实时敞口聚合，抵押品监控，信用限额使用率，结算风险，净额结算协议管理</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -6255,7 +6779,7 @@
         </is>
       </c>
       <c r="H73" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1">
@@ -6271,17 +6795,17 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>F04-07</t>
+          <t>F04-06</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>实时风险全景图</t>
+          <t>流动性分析与交易成本</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>实时持仓追踪，流式风险指标，实时限额监控，告警管理，异常跟踪仪表板</t>
+          <t>执行风险监控，市场冲击分析，流动性成本追踪，滑点计量，最优执行合规</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -6311,31 +6835,31 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>F04-08</t>
+          <t>F04-07</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>DV01/CS01计算</t>
+          <t>实时风险全景图</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>dPV/dy价格敏感度，信用利差敏感度，分桶移动与关键期限，平行与非平行冲击</t>
+          <t>实时持仓追踪，流式风险指标，实时限额监控，告警管理，异常跟踪仪表板</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G75" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1">
@@ -6351,17 +6875,17 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>F04-09</t>
+          <t>F04-08</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Greeks与敏感度计算</t>
+          <t>DV01/CS01计算</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，覆盖固收全品种与衍生品</t>
+          <t>dPV/dy价格敏感度，信用利差敏感度，分桶移动与关键期限，平行与非平行冲击</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -6375,7 +6899,7 @@
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" ht="28" customHeight="1">
@@ -6391,17 +6915,17 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>F04-10</t>
+          <t>F04-09</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>VaR模型</t>
+          <t>Greeks与敏感度计算</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>参数法/历史模拟法/蒙特卡洛三模式，Expected Shortfall (ES)，回测与例外检验</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，覆盖固收全品种与衍生品</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -6415,7 +6939,7 @@
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" ht="28" customHeight="1">
@@ -6431,31 +6955,31 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>F04-11</t>
+          <t>F04-10</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>压力测试与情景分析</t>
+          <t>VaR模型</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>内置历史情景（GFC/COVID-19/利率冲击），假设情景（曲线扭转/利差走阔），反向压力测试</t>
+          <t>参数法/历史模拟法/蒙特卡洛三模式，Expected Shortfall (ES)，回测与例外检验</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G78" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H78" s="8" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" ht="28" customHeight="1">
@@ -6471,17 +6995,17 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>F04-12</t>
+          <t>F04-11</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>估值与盈亏分解</t>
+          <t>压力测试与情景分析</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Carry &amp; Roll-down，曲线效应，信用利差贡献，择券贡献，基于因子的盈亏多维分解</t>
+          <t>内置历史情景（GFC/COVID-19/利率冲击），假设情景（曲线扭转/利差走阔），反向压力测试</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -6495,7 +7019,7 @@
         </is>
       </c>
       <c r="H79" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" ht="28" customHeight="1">
@@ -6511,31 +7035,31 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>F04-13</t>
+          <t>F04-12</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>历史风险回溯</t>
+          <t>估值与盈亏分解</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>历史VaR计算回放，压力测试结果归档，风险趋势分析，限额例外统计，VaR回测报告</t>
+          <t>Carry &amp; Roll-down，曲线效应，信用利差贡献，择券贡献，基于因子的盈亏多维分解</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G80" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H80" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" ht="28" customHeight="1">
@@ -6551,31 +7075,31 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>F04-14</t>
+          <t>F04-13</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>绩效归因与风险计量</t>
+          <t>历史风险回溯</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>收益率曲线效应，信用利差分解，行业配置效应，个券择券，Carry &amp; Roll-down贡献</t>
+          <t>历史VaR计算回放，压力测试结果归档，风险趋势分析，限额例外统计，VaR回测报告</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" ht="28" customHeight="1">
@@ -6591,31 +7115,31 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>F04-15</t>
+          <t>F04-14</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>监管报表与风控日报</t>
+          <t>绩效归因与风险计量</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
+          <t>收益率曲线效应，信用利差分解，行业配置效应，个券择券，Carry &amp; Roll-down贡献</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G82" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" ht="28" customHeight="1">
@@ -6631,31 +7155,31 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>F04-16</t>
+          <t>F04-15</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>数据底座与IBOR集成</t>
+          <t>监管报表与风控日报</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
+          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G83" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1">
@@ -6671,17 +7195,17 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>F04-17</t>
+          <t>F04-16</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>收益率曲线与波动率曲面</t>
+          <t>数据底座与IBOR集成</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
+          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -6711,31 +7235,31 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>F04-18</t>
+          <t>F04-17</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>HPC计算网格</t>
+          <t>收益率曲线与波动率曲面</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
+          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G85" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H85" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1">
@@ -6751,78 +7275,78 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
+          <t>F04-18</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>HPC计算网格</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G86" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87" ht="28" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
           <t>F04-19</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>AI风险预警</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>异常检测（ML模型），预测性分析，模式识别，智能告警，新业务合规风险预分析</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F87" s="5" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G86" s="23" t="inlineStr">
+      <c r="G87" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H86" s="8" t="n">
+      <c r="H87" s="8" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="22" t="inlineStr">
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="22" t="inlineStr">
         <is>
           <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
         </is>
-      </c>
-    </row>
-    <row r="88" ht="28" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>异常交易风控</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>F05-01</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
-        <is>
-          <t>LLM大语言模型应用</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
-        <is>
-          <t>客户意图识别，自然语言处理交易描述，智能报告自动生成，新规合规解读</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G88" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H88" s="8" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1">
@@ -6838,31 +7362,31 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>F05-02</t>
+          <t>F05-01</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>RAG检索增强生成</t>
+          <t>LLM大语言模型应用</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>监管规则知识库构建，新规则智能固化，合规智能问答，上下文理解与规则推理</t>
+          <t>客户意图识别，自然语言处理交易描述，智能报告自动生成，新规合规解读</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G89" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G89" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H89" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90" ht="28" customHeight="1">
@@ -6878,17 +7402,17 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>F05-03</t>
+          <t>F05-02</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Agent智能体</t>
+          <t>RAG检索增强生成</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>异常处置任务自动化，决策支持工作流，多步骤异常核查流程优化，自动推送处置建议</t>
+          <t>监管规则知识库构建，新规则智能固化，合规智能问答，上下文理解与规则推理</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -6918,31 +7442,31 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>F05-04</t>
+          <t>F05-03</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>MCP外部服务集成</t>
+          <t>Agent智能体</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>外部数据源调用接口，固化规则调用标准协议，与行情/持仓/交易系统数据对接</t>
+          <t>异常处置任务自动化，决策支持工作流，多步骤异常核查流程优化，自动推送处置建议</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G91" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H91" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92" ht="28" customHeight="1">
@@ -6958,31 +7482,31 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>F05-05</t>
+          <t>F05-04</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>代持与反向交易识别</t>
+          <t>MCP外部服务集成</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>代持相关交易检测，同券同额反向识别，多日反向低频交易模式识别</t>
+          <t>外部数据源调用接口，固化规则调用标准协议，与行情/持仓/交易系统数据对接</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H92" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" ht="28" customHeight="1">
@@ -6998,17 +7522,17 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>F05-06</t>
+          <t>F05-05</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>价格行为异常检测</t>
+          <t>代持与反向交易识别</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>高买低卖行为识别，信用债价格异常检测，基于历史分位数与实时行情动态偏离度计算</t>
+          <t>代持相关交易检测，同券同额反向识别，多日反向低频交易模式识别</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -7038,17 +7562,17 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>F05-07</t>
+          <t>F05-06</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>交易对手异常监控</t>
+          <t>价格行为异常检测</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>同一交易对手频繁交易预警，多次修改交易对手行为识别，持仓结构异常检测</t>
+          <t>高买低卖行为识别，信用债价格异常检测，基于历史分位数与实时行情动态偏离度计算</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -7062,7 +7586,7 @@
         </is>
       </c>
       <c r="H94" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" ht="28" customHeight="1">
@@ -7078,31 +7602,31 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>F05-08</t>
+          <t>F05-07</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>交易量异常检测</t>
+          <t>交易对手异常监控</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>交易量统计异常识别，集中度异常告警，与历史基准对比的量级偏离检测</t>
+          <t>同一交易对手频繁交易预警，多次修改交易对手行为识别，持仓结构异常检测</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G95" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G95" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H95" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" ht="28" customHeight="1">
@@ -7118,17 +7642,17 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>F05-09</t>
+          <t>F05-08</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>动态规则管理</t>
+          <t>交易量异常检测</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>异常模式智能探索与规则固化，No-Code规则配置界面，合规人员自助维护，规则版本管理</t>
+          <t>交易量统计异常识别，集中度异常告警，与历史基准对比的量级偏离检测</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -7142,7 +7666,7 @@
         </is>
       </c>
       <c r="H96" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" ht="28" customHeight="1">
@@ -7158,17 +7682,17 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>F05-10</t>
+          <t>F05-09</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>异常交易定位</t>
+          <t>动态规则管理</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>按时间范围快速查找历史异常交易，标记异常类型，可视化展示异常分布与趋势</t>
+          <t>异常模式智能探索与规则固化，No-Code规则配置界面，合规人员自助维护，规则版本管理</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -7182,7 +7706,7 @@
         </is>
       </c>
       <c r="H97" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" ht="28" customHeight="1">
@@ -7198,17 +7722,17 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>F05-11</t>
+          <t>F05-10</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>数据上传校验</t>
+          <t>异常交易定位</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>支持用户上传交易数据文件，瞬时完成异常交易校验并输出校验结果报告</t>
+          <t>按时间范围快速查找历史异常交易，标记异常类型，可视化展示异常分布与趋势</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -7238,78 +7762,78 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
+          <t>F05-11</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>数据上传校验</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>支持用户上传交易数据文件，瞬时完成异常交易校验并输出校验结果报告</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G99" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" ht="28" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>异常交易风控</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
           <t>F05-12</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>智能报告生成</t>
         </is>
       </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>模板自定义与场景数据一键应用，监管报送格式（证监会/人行），新业务过会合规分析报告</t>
         </is>
       </c>
-      <c r="F99" s="5" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G99" s="24" t="inlineStr">
+      <c r="G100" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H99" s="8" t="n">
+      <c r="H100" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="22" t="inlineStr">
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="22" t="inlineStr">
         <is>
           <t>【P1】 事前风控/合规  (Pre-trade Risk &amp; Compliance)</t>
         </is>
-      </c>
-    </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>事前风控/合规</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>F06-01</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>风控规则配置</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G101" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H101" s="8" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="102" ht="28" customHeight="1">
@@ -7325,17 +7849,17 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>F06-02</t>
+          <t>F06-01</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>多维度限额配置</t>
+          <t>风控规则配置</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>交易对手/交易员/券三维度限额设置，集中度/净敞口/利率敏感度/单笔名义多类型限额</t>
+          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -7349,7 +7873,7 @@
         </is>
       </c>
       <c r="H102" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" ht="28" customHeight="1">
@@ -7365,31 +7889,31 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>F06-03</t>
+          <t>F06-02</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>白黑名单管理</t>
+          <t>多维度限额配置</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
+          <t>交易对手/交易员/券三维度限额设置，集中度/净敞口/利率敏感度/单笔名义多类型限额</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G103" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G103" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H103" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104" ht="28" customHeight="1">
@@ -7405,31 +7929,31 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>F06-04</t>
+          <t>F06-03</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>实时事前风控拦截</t>
+          <t>白黑名单管理</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
+          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G104" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G104" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H104" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" ht="28" customHeight="1">
@@ -7445,31 +7969,31 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>F06-05</t>
+          <t>F06-04</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>异常报备工作流</t>
+          <t>实时事前风控拦截</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
+          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G105" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G105" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H105" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="106" ht="28" customHeight="1">
@@ -7485,31 +8009,31 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>F06-06</t>
+          <t>F06-05</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>AI聊天合规监控</t>
+          <t>异常报备工作流</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
+          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G106" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G106" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H106" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" ht="28" customHeight="1">
@@ -7525,17 +8049,17 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>F06-07</t>
+          <t>F06-06</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>AI交易要素提取</t>
+          <t>AI聊天合规监控</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
+          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -7549,7 +8073,7 @@
         </is>
       </c>
       <c r="H107" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" ht="28" customHeight="1">
@@ -7565,31 +8089,31 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>F06-08</t>
+          <t>F06-07</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>日内异常统计看板</t>
+          <t>AI交易要素提取</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
+          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G108" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G108" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H108" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" ht="28" customHeight="1">
@@ -7605,17 +8129,17 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>F06-09</t>
+          <t>F06-08</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>合规审批工作流</t>
+          <t>日内异常统计看板</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
+          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -7645,17 +8169,17 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>F06-10</t>
+          <t>F06-09</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>责任留痕与审计追踪</t>
+          <t>合规审批工作流</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
+          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -7672,51 +8196,51 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="22" t="inlineStr">
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>F06-10</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>责任留痕与审计追踪</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G111" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="22" t="inlineStr">
         <is>
           <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
         </is>
-      </c>
-    </row>
-    <row r="112" ht="28" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>F07-01</t>
-        </is>
-      </c>
-      <c r="D112" s="4" t="inlineStr">
-        <is>
-          <t>债券横截面与时序分析</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr">
-        <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
-        </is>
-      </c>
-      <c r="F112" s="5" t="inlineStr">
-        <is>
-          <t>横截面信号与实际收益相关性&gt;0.3</t>
-        </is>
-      </c>
-      <c r="G112" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H112" s="8" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="113" ht="28" customHeight="1">
@@ -7732,22 +8256,22 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>F07-02</t>
+          <t>F07-01</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>债券横截面与时序分析</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+          <t>横截面信号与实际收益相关性&gt;0.3</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -7756,7 +8280,7 @@
         </is>
       </c>
       <c r="H113" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
@@ -7772,31 +8296,31 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>F07-03</t>
+          <t>F07-02</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>组合相关度分析</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>相关矩阵计算&lt;30s（500券组合）</t>
-        </is>
-      </c>
-      <c r="G114" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+        </is>
+      </c>
+      <c r="G114" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H114" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" ht="28" customHeight="1">
@@ -7812,31 +8336,31 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F07-03</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>组合相关度分析</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
-        </is>
-      </c>
-      <c r="G115" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>相关矩阵计算&lt;30s（500券组合）</t>
+        </is>
+      </c>
+      <c r="G115" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="116" ht="28" customHeight="1">
@@ -7852,22 +8376,22 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>F07-05</t>
+          <t>F07-04</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析</t>
+          <t>情景分析</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -7876,7 +8400,7 @@
         </is>
       </c>
       <c r="H116" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="117" ht="28" customHeight="1">
@@ -7892,22 +8416,22 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F07-05</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>极端事件分析</t>
+          <t>敏感度分析</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%</t>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -7916,7 +8440,7 @@
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1">
@@ -7932,31 +8456,31 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>F07-07</t>
+          <t>F07-06</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>指数比较分析</t>
+          <t>极端事件分析</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
+          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
-        </is>
-      </c>
-      <c r="G118" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>历史情景复现误差&lt;1%</t>
+        </is>
+      </c>
+      <c r="G118" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H118" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" ht="28" customHeight="1">
@@ -7972,31 +8496,31 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F07-07</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>指数比较分析</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
-        </is>
-      </c>
-      <c r="G119" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
+        </is>
+      </c>
+      <c r="G119" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H119" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1">
@@ -8012,22 +8536,22 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>F07-09</t>
+          <t>F07-08</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>虚拟组合分析</t>
+          <t>绩效归因（Brinson）</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -8036,7 +8560,7 @@
         </is>
       </c>
       <c r="H120" s="8" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1">
@@ -8052,22 +8576,22 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>F07-10</t>
+          <t>F07-09</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>再平衡方案试算与比较</t>
+          <t>虚拟组合分析</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -8076,7 +8600,7 @@
         </is>
       </c>
       <c r="H121" s="8" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" ht="28" customHeight="1">
@@ -8092,22 +8616,22 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>F07-11</t>
+          <t>F07-10</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>再平衡方案试算与比较</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -8116,7 +8640,7 @@
         </is>
       </c>
       <c r="H122" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="123" ht="28" customHeight="1">
@@ -8132,22 +8656,22 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>F07-12</t>
+          <t>F07-11</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>固收+策略分析</t>
+          <t>资产配置策略分析</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+          <t>回测期≥5年，预测方向胜率&gt;55%</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -8156,7 +8680,7 @@
         </is>
       </c>
       <c r="H123" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124" ht="28" customHeight="1">
@@ -8172,22 +8696,22 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>F07-13</t>
+          <t>F07-12</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>量化策略组合分析</t>
+          <t>固收+策略分析</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>策略容量计算误差&lt;5%</t>
+          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -8196,7 +8720,7 @@
         </is>
       </c>
       <c r="H124" s="8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
@@ -8212,31 +8736,31 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>F07-14</t>
+          <t>F07-13</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>流动性分析</t>
+          <t>量化策略组合分析</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
-        </is>
-      </c>
-      <c r="G125" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>策略容量计算误差&lt;5%</t>
+        </is>
+      </c>
+      <c r="G125" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H125" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="126" ht="28" customHeight="1">
@@ -8252,27 +8776,27 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>F07-15</t>
+          <t>F07-14</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>定价计算集成</t>
+          <t>流动性分析</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
-        </is>
-      </c>
-      <c r="G126" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+        </is>
+      </c>
+      <c r="G126" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H126" s="8" t="n">
@@ -8292,31 +8816,31 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>F07-16</t>
+          <t>F07-15</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>利率曲线集成</t>
+          <t>定价计算集成</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
-        </is>
-      </c>
-      <c r="G127" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H127" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
@@ -8332,78 +8856,78 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G128" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
           <t>F07-17</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D129" s="4" t="inlineStr">
         <is>
           <t>因子模型</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr">
         <is>
           <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
         </is>
       </c>
-      <c r="G128" s="23" t="inlineStr">
+      <c r="G129" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H128" s="8" t="n">
+      <c r="H129" s="8" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="22" t="inlineStr">
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="22" t="inlineStr">
         <is>
           <t>【P1】 策略投资/量化  (Quant Strategy)</t>
         </is>
-      </c>
-    </row>
-    <row r="130" ht="28" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>策略投资/量化</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>F08-01</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>策略编写与版本管理</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G130" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H130" s="8" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="131" ht="28" customHeight="1">
@@ -8419,17 +8943,17 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F08-01</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>AI辅助策略开发</t>
+          <t>策略编写与版本管理</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
+          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -8443,7 +8967,7 @@
         </is>
       </c>
       <c r="H131" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1">
@@ -8459,17 +8983,17 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F08-02</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>因子挖掘与管理</t>
+          <t>AI辅助策略开发</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>因子编写，信号生成，因子库管理，AlphaLens因子有效性分析，量化模型库，宏观/技术/基本面因子</t>
+          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -8483,7 +9007,7 @@
         </is>
       </c>
       <c r="H132" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="133" ht="28" customHeight="1">
@@ -8499,31 +9023,31 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>F08-04</t>
+          <t>F08-03</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>因子挖掘与管理</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
+          <t>因子编写，信号生成，因子库管理，AlphaLens因子有效性分析，量化模型库，宏观/技术/基本面因子</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G133" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G133" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H133" s="8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134" ht="28" customHeight="1">
@@ -8539,31 +9063,31 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>F08-05</t>
+          <t>F08-04</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>模拟盘验证</t>
+          <t>Tick级回测引擎</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G134" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G134" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H134" s="8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135" ht="28" customHeight="1">
@@ -8579,31 +9103,31 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>F08-06</t>
+          <t>F08-05</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>策略上线审批</t>
+          <t>模拟盘验证</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
+          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G135" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G135" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H135" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
@@ -8619,31 +9143,31 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>F08-07</t>
+          <t>F08-06</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>策略运行管理</t>
+          <t>策略上线审批</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
+          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G136" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G136" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H136" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" ht="28" customHeight="1">
@@ -8659,31 +9183,31 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>F08-08</t>
+          <t>F08-07</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>策略绩效分析</t>
+          <t>策略运行管理</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
+          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G137" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G137" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H137" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
@@ -8699,17 +9223,17 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>F08-09</t>
+          <t>F08-08</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>实时多市场行情</t>
+          <t>策略绩效分析</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
+          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -8723,7 +9247,7 @@
         </is>
       </c>
       <c r="H138" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139" ht="28" customHeight="1">
@@ -8739,17 +9263,17 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>F08-10</t>
+          <t>F08-09</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>历史行情回放</t>
+          <t>实时多市场行情</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
+          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
@@ -8779,31 +9303,31 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>F08-11</t>
+          <t>F08-10</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>CEP流引擎与信号调度</t>
+          <t>历史行情回放</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
+          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G140" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G140" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H140" s="8" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" ht="28" customHeight="1">
@@ -8819,78 +9343,78 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
+          <t>F08-11</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>CEP流引擎与信号调度</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G141" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="142" ht="28" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
           <t>F08-12</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr">
         <is>
           <t>基础数据与模型底座</t>
         </is>
       </c>
-      <c r="E141" s="5" t="inlineStr">
+      <c r="E142" s="5" t="inlineStr">
         <is>
           <t>宏观因子库，债券曲线模型，估值数据接入，账户权限管理，AI引擎集成接口</t>
         </is>
       </c>
-      <c r="F141" s="5" t="inlineStr">
+      <c r="F142" s="5" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G141" s="23" t="inlineStr">
+      <c r="G142" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H141" s="8" t="n">
+      <c r="H142" s="8" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="26" t="inlineStr">
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="26" t="inlineStr">
         <is>
           <t>【P2】 定价平台  (Pricing Platform)</t>
         </is>
-      </c>
-    </row>
-    <row r="143" ht="28" customHeight="1">
-      <c r="A143" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B143" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D143" s="27" t="inlineStr">
-        <is>
-          <t>期限结构模型</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="inlineStr">
-        <is>
-          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
-        </is>
-      </c>
-      <c r="F143" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G143" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H143" s="13" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="144" ht="28" customHeight="1">
@@ -8906,17 +9430,17 @@
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>F09-02</t>
+          <t>F09-01</t>
         </is>
       </c>
       <c r="D144" s="27" t="inlineStr">
         <is>
-          <t>蒙特卡洛求解器</t>
+          <t>期限结构模型</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
+          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr">
@@ -8930,7 +9454,7 @@
         </is>
       </c>
       <c r="H144" s="13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="145" ht="28" customHeight="1">
@@ -8946,17 +9470,17 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>F09-03</t>
+          <t>F09-02</t>
         </is>
       </c>
       <c r="D145" s="27" t="inlineStr">
         <is>
-          <t>有限差分（PDE）</t>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
@@ -8970,7 +9494,7 @@
         </is>
       </c>
       <c r="H145" s="13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="146" ht="28" customHeight="1">
@@ -8986,31 +9510,31 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>F09-04</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D146" s="27" t="inlineStr">
         <is>
-          <t>实时Greeks</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G146" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G146" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H146" s="13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="147" ht="28" customHeight="1">
@@ -9026,17 +9550,17 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>F09-05</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D147" s="27" t="inlineStr">
         <is>
-          <t>定价服务微服务架构</t>
+          <t>实时Greeks</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr">
@@ -9066,78 +9590,78 @@
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
+          <t>F09-05</t>
+        </is>
+      </c>
+      <c r="D148" s="27" t="inlineStr">
+        <is>
+          <t>定价服务微服务架构</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="inlineStr">
+        <is>
+          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
+        </is>
+      </c>
+      <c r="F148" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G148" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H148" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="149" ht="28" customHeight="1">
+      <c r="A149" s="11" t="inlineStr">
+        <is>
+          <t>定价平台</t>
+        </is>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
           <t>F09-06</t>
         </is>
       </c>
-      <c r="D148" s="27" t="inlineStr">
+      <c r="D149" s="27" t="inlineStr">
         <is>
           <t>历史估值回测</t>
         </is>
       </c>
-      <c r="E148" s="11" t="inlineStr">
+      <c r="E149" s="11" t="inlineStr">
         <is>
           <t>基于历史行情重放定价误差分析，模型验证框架</t>
         </is>
       </c>
-      <c r="F148" s="11" t="inlineStr">
+      <c r="F149" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G148" s="23" t="inlineStr">
+      <c r="G149" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H148" s="13" t="n">
+      <c r="H149" s="13" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="26" t="inlineStr">
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="26" t="inlineStr">
         <is>
           <t>【P2】 销售交易  (Sales Trading)</t>
         </is>
-      </c>
-    </row>
-    <row r="150" ht="28" customHeight="1">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B150" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
-        <is>
-          <t>F10-01</t>
-        </is>
-      </c>
-      <c r="D150" s="27" t="inlineStr">
-        <is>
-          <t>销交工作台</t>
-        </is>
-      </c>
-      <c r="E150" s="11" t="inlineStr">
-        <is>
-          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
-        </is>
-      </c>
-      <c r="F150" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G150" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H150" s="13" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="151" ht="28" customHeight="1">
@@ -9153,31 +9677,31 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>F10-02</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D151" s="27" t="inlineStr">
         <is>
-          <t>债券过滤与筛选</t>
+          <t>销交工作台</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
+          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G151" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G151" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H151" s="13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152" ht="28" customHeight="1">
@@ -9193,31 +9717,31 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>F10-03</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D152" s="27" t="inlineStr">
         <is>
-          <t>报价撮合与对价</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
+          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G152" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G152" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H152" s="13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153" ht="28" customHeight="1">
@@ -9233,17 +9757,17 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>F10-04</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>交易执行与审批</t>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
+          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
@@ -9257,7 +9781,7 @@
         </is>
       </c>
       <c r="H153" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154" ht="28" customHeight="1">
@@ -9273,17 +9797,17 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>F10-05</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D154" s="27" t="inlineStr">
         <is>
-          <t>风控检查</t>
+          <t>交易执行与审批</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
+          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
@@ -9313,78 +9837,78 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
+          <t>F10-05</t>
+        </is>
+      </c>
+      <c r="D155" s="27" t="inlineStr">
+        <is>
+          <t>风控检查</t>
+        </is>
+      </c>
+      <c r="E155" s="11" t="inlineStr">
+        <is>
+          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
+        </is>
+      </c>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G155" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H155" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" ht="28" customHeight="1">
+      <c r="A156" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C156" s="10" t="inlineStr">
+        <is>
           <t>F10-06</t>
         </is>
       </c>
-      <c r="D155" s="27" t="inlineStr">
+      <c r="D156" s="27" t="inlineStr">
         <is>
           <t>智能推荐系统</t>
         </is>
       </c>
-      <c r="E155" s="11" t="inlineStr">
+      <c r="E156" s="11" t="inlineStr">
         <is>
           <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
         </is>
       </c>
-      <c r="F155" s="11" t="inlineStr">
+      <c r="F156" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G155" s="23" t="inlineStr">
+      <c r="G156" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H155" s="13" t="n">
+      <c r="H156" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="156" ht="20" customHeight="1">
-      <c r="A156" s="26" t="inlineStr">
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="26" t="inlineStr">
         <is>
           <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
         </is>
-      </c>
-    </row>
-    <row r="157" ht="28" customHeight="1">
-      <c r="A157" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B157" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C157" s="10" t="inlineStr">
-        <is>
-          <t>F11-01</t>
-        </is>
-      </c>
-      <c r="D157" s="27" t="inlineStr">
-        <is>
-          <t>信用利差分析</t>
-        </is>
-      </c>
-      <c r="E157" s="11" t="inlineStr">
-        <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
-        </is>
-      </c>
-      <c r="F157" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G157" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H157" s="13" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="158" ht="28" customHeight="1">
@@ -9400,31 +9924,31 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
+          <t>F11-01</t>
         </is>
       </c>
       <c r="D158" s="27" t="inlineStr">
         <is>
-          <t>CDS/CLN定价</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G158" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G158" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H158" s="13" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159" ht="28" customHeight="1">
@@ -9440,31 +9964,31 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D159" s="27" t="inlineStr">
         <is>
-          <t>信用评级动态监控</t>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G159" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G159" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H159" s="13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="160" ht="28" customHeight="1">
@@ -9480,31 +10004,31 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D160" s="27" t="inlineStr">
         <is>
-          <t>违约概率（PD）建模</t>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G160" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G160" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H160" s="13" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="161" ht="28" customHeight="1">
@@ -9520,78 +10044,78 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
+          <t>F11-04</t>
+        </is>
+      </c>
+      <c r="D161" s="27" t="inlineStr">
+        <is>
+          <t>违约概率（PD）建模</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+        </is>
+      </c>
+      <c r="F161" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G161" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H161" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="162" ht="28" customHeight="1">
+      <c r="A162" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C162" s="10" t="inlineStr">
+        <is>
           <t>F11-05</t>
         </is>
       </c>
-      <c r="D161" s="27" t="inlineStr">
+      <c r="D162" s="27" t="inlineStr">
         <is>
           <t>集中度限额管理</t>
         </is>
       </c>
-      <c r="E161" s="11" t="inlineStr">
+      <c r="E162" s="11" t="inlineStr">
         <is>
           <t>行业/发行人/评级集中度多维限额，超限预警</t>
         </is>
       </c>
-      <c r="F161" s="11" t="inlineStr">
+      <c r="F162" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G161" s="24" t="inlineStr">
+      <c r="G162" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H161" s="13" t="n">
+      <c r="H162" s="13" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="26" t="inlineStr">
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="26" t="inlineStr">
         <is>
           <t>【P2】 投顾服务  (Investment Advisory)</t>
         </is>
-      </c>
-    </row>
-    <row r="163" ht="28" customHeight="1">
-      <c r="A163" s="11" t="inlineStr">
-        <is>
-          <t>投顾服务</t>
-        </is>
-      </c>
-      <c r="B163" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C163" s="10" t="inlineStr">
-        <is>
-          <t>F12-01</t>
-        </is>
-      </c>
-      <c r="D163" s="27" t="inlineStr">
-        <is>
-          <t>投顾工作台</t>
-        </is>
-      </c>
-      <c r="E163" s="11" t="inlineStr">
-        <is>
-          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
-        </is>
-      </c>
-      <c r="F163" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G163" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H163" s="13" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="164" ht="28" customHeight="1">
@@ -9607,17 +10131,17 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F12-01</t>
         </is>
       </c>
       <c r="D164" s="27" t="inlineStr">
         <is>
-          <t>客户终端</t>
+          <t>投顾工作台</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr">
@@ -9647,17 +10171,17 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D165" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>客户终端</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
+          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr">
@@ -9671,7 +10195,7 @@
         </is>
       </c>
       <c r="H165" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" ht="28" customHeight="1">
@@ -9687,31 +10211,31 @@
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D166" s="27" t="inlineStr">
         <is>
-          <t>账户分析报告</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G166" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G166" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H166" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="167" ht="28" customHeight="1">
@@ -9727,31 +10251,31 @@
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D167" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>账户分析报告</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G167" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G167" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H167" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="168" ht="28" customHeight="1">
@@ -9767,78 +10291,78 @@
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
+          <t>F12-05</t>
+        </is>
+      </c>
+      <c r="D168" s="27" t="inlineStr">
+        <is>
+          <t>投研报告服务</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+        </is>
+      </c>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G168" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H168" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" ht="28" customHeight="1">
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C169" s="10" t="inlineStr">
+        <is>
           <t>F12-06</t>
         </is>
       </c>
-      <c r="D168" s="27" t="inlineStr">
+      <c r="D169" s="27" t="inlineStr">
         <is>
           <t>客户服务与基础服务</t>
         </is>
       </c>
-      <c r="E168" s="11" t="inlineStr">
+      <c r="E169" s="11" t="inlineStr">
         <is>
           <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
         </is>
       </c>
-      <c r="F168" s="11" t="inlineStr">
+      <c r="F169" s="11" t="inlineStr">
         <is>
           <t>功能测试通过</t>
         </is>
       </c>
-      <c r="G168" s="25" t="inlineStr">
+      <c r="G169" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H168" s="13" t="n">
+      <c r="H169" s="13" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="26" t="inlineStr">
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="26" t="inlineStr">
         <is>
           <t>【P2】 TRS收益互换  (Total Return Swap)</t>
         </is>
-      </c>
-    </row>
-    <row r="170" ht="28" customHeight="1">
-      <c r="A170" s="11" t="inlineStr">
-        <is>
-          <t>TRS收益互换</t>
-        </is>
-      </c>
-      <c r="B170" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C170" s="10" t="inlineStr">
-        <is>
-          <t>F13-01</t>
-        </is>
-      </c>
-      <c r="D170" s="27" t="inlineStr">
-        <is>
-          <t>TRS交易端</t>
-        </is>
-      </c>
-      <c r="E170" s="11" t="inlineStr">
-        <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
-        </is>
-      </c>
-      <c r="F170" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G170" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H170" s="13" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="171" ht="28" customHeight="1">
@@ -9854,17 +10378,17 @@
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F13-01</t>
         </is>
       </c>
       <c r="D171" s="27" t="inlineStr">
         <is>
-          <t>TRS客户端</t>
+          <t>TRS交易端</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr">
@@ -9878,7 +10402,7 @@
         </is>
       </c>
       <c r="H171" s="13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" ht="28" customHeight="1">
@@ -9894,31 +10418,31 @@
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F13-02</t>
         </is>
       </c>
       <c r="D172" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>TRS客户端</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G172" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G172" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H172" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="173" ht="28" customHeight="1">
@@ -9934,31 +10458,31 @@
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F13-03</t>
         </is>
       </c>
       <c r="D173" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>TRS管理端</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G173" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G173" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H173" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" ht="28" customHeight="1">
@@ -9974,31 +10498,31 @@
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F13-04</t>
         </is>
       </c>
       <c r="D174" s="27" t="inlineStr">
         <is>
-          <t>通知与确认文件</t>
+          <t>自动对冲</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G174" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G174" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H174" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="175" ht="28" customHeight="1">
@@ -10014,78 +10538,78 @@
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D175" s="27" t="inlineStr">
+        <is>
+          <t>通知与确认文件</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G175" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H175" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" ht="28" customHeight="1">
+      <c r="A176" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B176" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C176" s="10" t="inlineStr">
+        <is>
           <t>F13-06</t>
         </is>
       </c>
-      <c r="D175" s="27" t="inlineStr">
+      <c r="D176" s="27" t="inlineStr">
         <is>
           <t>系统集成</t>
         </is>
       </c>
-      <c r="E175" s="11" t="inlineStr">
+      <c r="E176" s="11" t="inlineStr">
         <is>
           <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
         </is>
       </c>
-      <c r="F175" s="11" t="inlineStr">
+      <c r="F176" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G175" s="23" t="inlineStr">
+      <c r="G176" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H175" s="13" t="n">
+      <c r="H176" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="29" t="inlineStr">
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
-      </c>
-    </row>
-    <row r="177" ht="28" customHeight="1">
-      <c r="A177" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B177" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C177" s="15" t="inlineStr">
-        <is>
-          <t>F15-01</t>
-        </is>
-      </c>
-      <c r="D177" s="30" t="inlineStr">
-        <is>
-          <t>双边报价引擎</t>
-        </is>
-      </c>
-      <c r="E177" s="16" t="inlineStr">
-        <is>
-          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
-        </is>
-      </c>
-      <c r="F177" s="16" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G177" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H177" s="18" t="n">
-        <v>70</v>
       </c>
     </row>
     <row r="178" ht="28" customHeight="1">
@@ -10101,17 +10625,17 @@
       </c>
       <c r="C178" s="15" t="inlineStr">
         <is>
-          <t>F15-02</t>
+          <t>F15-01</t>
         </is>
       </c>
       <c r="D178" s="30" t="inlineStr">
         <is>
-          <t>库存风险实时管理</t>
+          <t>双边报价引擎</t>
         </is>
       </c>
       <c r="E178" s="16" t="inlineStr">
         <is>
-          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
       <c r="F178" s="16" t="inlineStr">
@@ -10125,7 +10649,7 @@
         </is>
       </c>
       <c r="H178" s="18" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="179" ht="28" customHeight="1">
@@ -10141,17 +10665,17 @@
       </c>
       <c r="C179" s="15" t="inlineStr">
         <is>
-          <t>F15-03</t>
+          <t>F15-02</t>
         </is>
       </c>
       <c r="D179" s="30" t="inlineStr">
         <is>
-          <t>报价优化算法</t>
+          <t>库存风险实时管理</t>
         </is>
       </c>
       <c r="E179" s="16" t="inlineStr">
         <is>
-          <t>基于市场微结构理论动态调整bid-ask spread</t>
+          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
       <c r="F179" s="16" t="inlineStr">
@@ -10165,7 +10689,7 @@
         </is>
       </c>
       <c r="H179" s="18" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="180" ht="28" customHeight="1">
@@ -10181,31 +10705,31 @@
       </c>
       <c r="C180" s="15" t="inlineStr">
         <is>
-          <t>F15-04</t>
+          <t>F15-03</t>
         </is>
       </c>
       <c r="D180" s="30" t="inlineStr">
         <is>
-          <t>竞争力分析</t>
+          <t>报价优化算法</t>
         </is>
       </c>
       <c r="E180" s="16" t="inlineStr">
         <is>
-          <t>与市场最优报价对比，中签率分析，策略调优</t>
+          <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
       <c r="F180" s="16" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G180" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G180" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H180" s="18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="181" ht="28" customHeight="1">
@@ -10221,62 +10745,102 @@
       </c>
       <c r="C181" s="15" t="inlineStr">
         <is>
+          <t>F15-04</t>
+        </is>
+      </c>
+      <c r="D181" s="30" t="inlineStr">
+        <is>
+          <t>竞争力分析</t>
+        </is>
+      </c>
+      <c r="E181" s="16" t="inlineStr">
+        <is>
+          <t>与市场最优报价对比，中签率分析，策略调优</t>
+        </is>
+      </c>
+      <c r="F181" s="16" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G181" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H181" s="18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" ht="28" customHeight="1">
+      <c r="A182" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B182" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C182" s="15" t="inlineStr">
+        <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D181" s="30" t="inlineStr">
+      <c r="D182" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E181" s="16" t="inlineStr">
+      <c r="E182" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F181" s="16" t="inlineStr">
+      <c r="F182" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G181" s="24" t="inlineStr">
+      <c r="G182" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H181" s="18" t="n">
+      <c r="H182" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="19" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H182" s="20">
-        <f>SUM(H3:H181)</f>
+      <c r="H183" s="20">
+        <f>SUM(H3:H182)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A100:H100"/>
+    <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A163:H163"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A162:H162"/>
-    <mergeCell ref="A176:H176"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A156:H156"/>
-    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A101:H101"/>
+    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A157:H157"/>
     <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A142:H142"/>
-    <mergeCell ref="A169:H169"/>
+    <mergeCell ref="A112:H112"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A170:H170"/>
+    <mergeCell ref="A177:H177"/>
+    <mergeCell ref="A183:G183"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A182:G182"/>
-    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="A150:H150"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A149:H149"/>
+    <mergeCell ref="A88:H88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14204,6 +14768,415 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：FOF投资系统  |  FOF Investment System</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：基金/FOF投资业务系统化管理，覆盖基础信息、交易录入、组合风控全链路；对应PPT Slide 43   |   来源：Slide 43</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：FOF投资系统  (FOF Investment System)  |  优先级：P2  |  竞品：恒生/金证  |  华锐基础：IBOR持仓账薄  |  工期：4月  团队：5人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. 基础信息管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>D1. 基础信息管理</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>F03-01</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>管理人与基金基础信息</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>管理人黑名单维护，基金策略分类，基金基础要素（规模/净值/评级）录入与更新，管理人信息库</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>D1. 基础信息管理</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>F03-02</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>基金资产信息获取</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>通过邮箱/API自动获取基金资产报告，解析持仓明细并入库，多来源数据合并去重，导入工具</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>D1. 基础信息管理</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>F03-03</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>子基金持仓穿透</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>穿透底层基金持仓至个券/个股层面，合并计算组合总敞口，支持集中度与评级分布分析</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr"/>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D2. 交易管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>D2. 交易管理</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>F03-04</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>交易录入与审核</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>申购/赎回/换仓交易录入，交易明细管理，双级审核工作流（投资助理录入→风控复核），审批记录留痕</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr"/>
+      <c r="G10" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>D2. 交易管理</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>F03-05</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>申赎情况跟踪</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>子基金申购/赎回状态全生命周期跟踪，到账确认，净值更新后自动触发持仓重算</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>D3. 风控报告</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>D3. 风控报告</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>F03-06</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>组合风控报告生成</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>按管理人策略限制/投资占比限制/白名单分类/子基金申赎情况生成风控日报和周报</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr"/>
+      <c r="G13" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>D3. 风控报告</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>F03-07</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>报告推送与查阅</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>风控日报/周报自动推送给风控人员，支持在线查看与下载，历史报告归档查询</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr"/>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>合计 7项功能  |  P1: 0项  |  P2: 7项</t>
+        </is>
+      </c>
+      <c r="H15" s="20">
+        <f>SUM(H5:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="34" t="inlineStr"/>
+      <c r="J15" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15079,7 +16052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15676,527 +16649,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
-        <is>
-          <t>系统详情：事前风控/合规  |  Pre-trade Risk &amp; Compliance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>战略定位：嵌入交易前拦截，三端架构（风控/用户/管理），AI聊天合规监控为核心差异化；对应PPT Slide 51   |   来源：Slide 51</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="40" t="inlineStr">
-        <is>
-          <t>模块：事前风控/合规  (Pre-trade Risk &amp; Compliance)  |  优先级：P1  |  竞品：恒生/金证  |  华锐基础：ARC合规模块  |  工期：6月  团队：6人</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>功能域</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>功能名称</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>功能描述</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>验收标准</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>集成依赖</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>复杂度</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>预估(人天)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>D1. 规则配置（风控端）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>D1. 规则配置（风控端）</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>F06-01</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>风控规则配置</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>D1. 规则配置（风控端）</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>F06-02</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>多维度限额配置</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>交易对手/交易员/券三维度限额设置，集中度/净敞口/利率敏感度/单笔名义多类型限额</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>D1. 规则配置（风控端）</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>F06-03</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>白黑名单管理</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="40" t="inlineStr">
-        <is>
-          <t>D2. 交易前拦截（用户端）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>D2. 交易前拦截（用户端）</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>F06-04</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>实时事前风控拦截</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>D2. 交易前拦截（用户端）</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>F06-05</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>异常报备工作流</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>D2. 交易前拦截（用户端）</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>F06-06</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>AI聊天合规监控</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>D2. 交易前拦截（用户端）</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>F06-07</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>AI交易要素提取</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t>D3. 统计与审计（管理端）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>D3. 统计与审计（管理端）</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>F06-08</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>日内异常统计看板</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>D3. 统计与审计（管理端）</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>F06-09</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>合规审批工作流</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H16" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>D3. 统计与审计（管理端）</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>F06-10</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>责任留痕与审计追踪</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>合计 10项功能  |  P1: 10项  |  P2: 0项</t>
-        </is>
-      </c>
-      <c r="H18" s="20">
-        <f>SUM(H5:H17)</f>
-        <v/>
-      </c>
-      <c r="I18" s="34" t="inlineStr"/>
-      <c r="J18" s="34" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_事前风控_合规" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_策略投资_量化" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_定价平台" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1511,7 +1512,7 @@
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>蒙特卡洛/有限差分，替代衡泰核心</t>
+          <t>蒙特卡洛/有限差分，替代衡泰核心，覆盖权益/利率/大宗商品/外汇/衍生品全品种；对应PPT Slide 56</t>
         </is>
       </c>
     </row>
@@ -4006,13 +4007,742 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：定价平台  |  Pricing Platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：蒙特卡洛/有限差分，替代衡泰核心，覆盖权益/利率/大宗商品/外汇/衍生品全品种；对应PPT Slide 56   |   来源：Slide 56</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：定价平台  (Pricing Platform)  |  优先级：P2  |  竞品：衡泰(垄断)  |  华锐基础：ARC基础数值库  |  工期：18月  团队：15人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. 金融产品覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>D1. 金融产品覆盖</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>F09-01</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>期权收益结构定价</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>香草期权/价差期权/欧式/美式/雪球/自定义期权定价，挂钩标的覆盖国债/期货/股票/指数/商品</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>D1. 金融产品覆盖</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>F09-02</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>结构化产品定价</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>场外期权/远期/收益凭证/收益互换/融资融券/合约型互换定价，支持自定义结构化产品</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>D1. 金融产品覆盖</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>F09-03</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>固收品种定价</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>固息/浮息国债，含权债，可转债精确定价，信用债估值，ABS定价</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr"/>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D2. 市场数据底座</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>D2. 市场数据底座</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>F09-04</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>利率与信用曲线构建</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr"/>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>D2. 市场数据底座</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>F09-05</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>波动率曲面构建</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>隐含波动率曲面，红利曲线，汇率曲线，Local Volatility曲面，波动率微笑校准</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>D2. 市场数据底座</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>F09-06</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>市场数据管理</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>境内外权益/债券/外汇/商品资讯统一接入，数据清洗，异常值处理，数据质量监控</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>D3. 定价模型引擎</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>D3. 定价模型引擎</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>F09-07</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>蒙特卡洛求解器</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价，并行情景模拟</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr"/>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>D3. 定价模型引擎</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>F09-08</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>解析解与数值解</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Black-Scholes解析解，Hull-White利率模型，SABR波动率模型，二叉树/三叉树数值解</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>D3. 定价模型引擎</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>F09-09</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>有限差分（PDE）</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价，局部波动率模型数值解</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr"/>
+      <c r="F16" s="11" t="inlineStr"/>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>D3. 定价模型引擎</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>F09-10</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>实时Greeks计算</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，DV01/CS01，分桶敏感度</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr"/>
+      <c r="G17" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>D4. 定价应用场景</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>D4. 定价应用场景</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>F09-11</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>估值与结算计算</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>日终估值，盯市计算，保证金计算，结算价格，历史估值回测与误差分析</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr"/>
+      <c r="G19" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>D4. 定价应用场景</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>F09-12</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>风控与情景计算</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>风险计量（VaR/压力测试）调用，情景分析，保证金计算，为风控平台提供统一定价接口</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr"/>
+      <c r="G20" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>D4. 定价应用场景</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>F09-13</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>客需报价服务</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>为销售交易/TRS系统提供实时报价，一站式报价接口，支持结构化产品定制化快速报价</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr"/>
+      <c r="F21" s="11" t="inlineStr"/>
+      <c r="G21" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>D5. 平台基础设施</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>D5. 平台基础设施</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>F09-14</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>定价微服务架构</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>REST/gRPC定价API，横向弹性扩容，p99&lt;100ms，模型插件化注册，版本管理</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr"/>
+      <c r="F23" s="11" t="inlineStr"/>
+      <c r="G23" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>D5. 平台基础设施</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>F09-15</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>灵活二次开发能力</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>全平台级/单功能模块级/系统框架级可扩展，支持自定义模型接入，策略团队自助扩展</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr"/>
+      <c r="F24" s="11" t="inlineStr"/>
+      <c r="G24" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>合计 15项功能  |  P1: 0项  |  P2: 15项</t>
+        </is>
+      </c>
+      <c r="H25" s="20">
+        <f>SUM(H5:H24)</f>
+        <v/>
+      </c>
+      <c r="I25" s="34" t="inlineStr"/>
+      <c r="J25" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A13:J13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9435,12 +10165,12 @@
       </c>
       <c r="D144" s="27" t="inlineStr">
         <is>
-          <t>期限结构模型</t>
+          <t>期权收益结构定价</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>Nelson-Siegel/Svensson/HJM等多模型参数拟合，实时曲线</t>
+          <t>香草期权/价差期权/欧式/美式/雪球/自定义期权定价，挂钩标的覆盖国债/期货/股票/指数/商品</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr">
@@ -9475,12 +10205,12 @@
       </c>
       <c r="D145" s="27" t="inlineStr">
         <is>
-          <t>蒙特卡洛求解器</t>
+          <t>结构化产品定价</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价</t>
+          <t>场外期权/远期/收益凭证/收益互换/融资融券/合约型互换定价，支持自定义结构化产品</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
@@ -9494,7 +10224,7 @@
         </is>
       </c>
       <c r="H145" s="13" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="146" ht="28" customHeight="1">
@@ -9515,26 +10245,26 @@
       </c>
       <c r="D146" s="27" t="inlineStr">
         <is>
-          <t>有限差分（PDE）</t>
+          <t>固收品种定价</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价</t>
+          <t>固息/浮息国债，含权债，可转债精确定价，信用债估值，ABS定价</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G146" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G146" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H146" s="13" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147" ht="28" customHeight="1">
@@ -9555,26 +10285,26 @@
       </c>
       <c r="D147" s="27" t="inlineStr">
         <is>
-          <t>实时Greeks</t>
+          <t>利率与信用曲线构建</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算</t>
+          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G147" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G147" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H147" s="13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="148" ht="28" customHeight="1">
@@ -9595,26 +10325,26 @@
       </c>
       <c r="D148" s="27" t="inlineStr">
         <is>
-          <t>定价服务微服务架构</t>
+          <t>波动率曲面构建</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>REST/gRPC定价API，支持横向扩展，p99&lt;100ms</t>
+          <t>隐含波动率曲面，红利曲线，汇率曲线，Local Volatility曲面，波动率微笑校准</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G148" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G148" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H148" s="13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="149" ht="28" customHeight="1">
@@ -9635,12 +10365,12 @@
       </c>
       <c r="D149" s="27" t="inlineStr">
         <is>
-          <t>历史估值回测</t>
+          <t>市场数据管理</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>基于历史行情重放定价误差分析，模型验证框架</t>
+          <t>境内外权益/债券/外汇/商品资讯统一接入，数据清洗，异常值处理，数据质量监控</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr">
@@ -9657,17 +10387,50 @@
         <v>30</v>
       </c>
     </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 销售交易  (Sales Trading)</t>
-        </is>
+    <row r="150" ht="28" customHeight="1">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>定价平台</t>
+        </is>
+      </c>
+      <c r="B150" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="inlineStr">
+        <is>
+          <t>F09-07</t>
+        </is>
+      </c>
+      <c r="D150" s="27" t="inlineStr">
+        <is>
+          <t>蒙特卡洛求解器</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="inlineStr">
+        <is>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价，并行情景模拟</t>
+        </is>
+      </c>
+      <c r="F150" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G150" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H150" s="13" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="151" ht="28" customHeight="1">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
@@ -9677,37 +10440,37 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>F10-01</t>
+          <t>F09-08</t>
         </is>
       </c>
       <c r="D151" s="27" t="inlineStr">
         <is>
-          <t>销交工作台</t>
+          <t>解析解与数值解</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
+          <t>Black-Scholes解析解，Hull-White利率模型，SABR波动率模型，二叉树/三叉树数值解</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G151" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G151" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H151" s="13" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152" ht="28" customHeight="1">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
@@ -9717,37 +10480,37 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>F10-02</t>
+          <t>F09-09</t>
         </is>
       </c>
       <c r="D152" s="27" t="inlineStr">
         <is>
-          <t>债券过滤与筛选</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价，局部波动率模型数值解</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G152" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G152" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H152" s="13" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="153" ht="28" customHeight="1">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
@@ -9757,37 +10520,37 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>F10-03</t>
+          <t>F09-10</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>报价撮合与对价</t>
+          <t>实时Greeks计算</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，DV01/CS01，分桶敏感度</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G153" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H153" s="13" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154" ht="28" customHeight="1">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
@@ -9797,37 +10560,37 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>F10-04</t>
+          <t>F09-11</t>
         </is>
       </c>
       <c r="D154" s="27" t="inlineStr">
         <is>
-          <t>交易执行与审批</t>
+          <t>估值与结算计算</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
+          <t>日终估值，盯市计算，保证金计算，结算价格，历史估值回测与误差分析</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G154" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G154" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H154" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="155" ht="28" customHeight="1">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
@@ -9837,37 +10600,37 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>F10-05</t>
+          <t>F09-12</t>
         </is>
       </c>
       <c r="D155" s="27" t="inlineStr">
         <is>
-          <t>风控检查</t>
+          <t>风控与情景计算</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
+          <t>风险计量（VaR/压力测试）调用，情景分析，保证金计算，为风控平台提供统一定价接口</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G155" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G155" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H155" s="13" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="156" ht="28" customHeight="1">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
@@ -9877,17 +10640,17 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>F10-06</t>
+          <t>F09-13</t>
         </is>
       </c>
       <c r="D156" s="27" t="inlineStr">
         <is>
-          <t>智能推荐系统</t>
+          <t>客需报价服务</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
+          <t>为销售交易/TRS系统提供实时报价，一站式报价接口，支持结构化产品定制化快速报价</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr">
@@ -9901,20 +10664,53 @@
         </is>
       </c>
       <c r="H156" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="157" ht="20" customHeight="1">
-      <c r="A157" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
-        </is>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="157" ht="28" customHeight="1">
+      <c r="A157" s="11" t="inlineStr">
+        <is>
+          <t>定价平台</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C157" s="10" t="inlineStr">
+        <is>
+          <t>F09-14</t>
+        </is>
+      </c>
+      <c r="D157" s="27" t="inlineStr">
+        <is>
+          <t>定价微服务架构</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="inlineStr">
+        <is>
+          <t>REST/gRPC定价API，横向弹性扩容，p99&lt;100ms，模型插件化注册，版本管理</t>
+        </is>
+      </c>
+      <c r="F157" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G157" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H157" s="13" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="158" ht="28" customHeight="1">
       <c r="A158" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
@@ -9924,17 +10720,17 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>F11-01</t>
+          <t>F09-15</t>
         </is>
       </c>
       <c r="D158" s="27" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>灵活二次开发能力</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+          <t>全平台级/单功能模块级/系统框架级可扩展，支持自定义模型接入，策略团队自助扩展</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr">
@@ -9951,50 +10747,17 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" ht="28" customHeight="1">
-      <c r="A159" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B159" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C159" s="10" t="inlineStr">
-        <is>
-          <t>F11-02</t>
-        </is>
-      </c>
-      <c r="D159" s="27" t="inlineStr">
-        <is>
-          <t>CDS/CLN定价</t>
-        </is>
-      </c>
-      <c r="E159" s="11" t="inlineStr">
-        <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
-        </is>
-      </c>
-      <c r="F159" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G159" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H159" s="13" t="n">
-        <v>50</v>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 销售交易  (Sales Trading)</t>
+        </is>
       </c>
     </row>
     <row r="160" ht="28" customHeight="1">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
@@ -10004,17 +10767,17 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D160" s="27" t="inlineStr">
         <is>
-          <t>信用评级动态监控</t>
+          <t>销交工作台</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr">
@@ -10034,7 +10797,7 @@
     <row r="161" ht="28" customHeight="1">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
@@ -10044,37 +10807,37 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D161" s="27" t="inlineStr">
         <is>
-          <t>违约概率（PD）建模</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G161" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G161" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H161" s="13" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" ht="28" customHeight="1">
       <c r="A162" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
@@ -10084,17 +10847,17 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>F11-05</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D162" s="27" t="inlineStr">
         <is>
-          <t>集中度限额管理</t>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>行业/发行人/评级集中度多维限额，超限预警</t>
+          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr">
@@ -10111,17 +10874,50 @@
         <v>20</v>
       </c>
     </row>
-    <row r="163" ht="20" customHeight="1">
-      <c r="A163" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 投顾服务  (Investment Advisory)</t>
-        </is>
+    <row r="163" ht="28" customHeight="1">
+      <c r="A163" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>F10-04</t>
+        </is>
+      </c>
+      <c r="D163" s="27" t="inlineStr">
+        <is>
+          <t>交易执行与审批</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
+        </is>
+      </c>
+      <c r="F163" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G163" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H163" s="13" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="164" ht="28" customHeight="1">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
@@ -10131,17 +10927,17 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>F12-01</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D164" s="27" t="inlineStr">
         <is>
-          <t>投顾工作台</t>
+          <t>风控检查</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
+          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr">
@@ -10155,13 +10951,13 @@
         </is>
       </c>
       <c r="H164" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="165" ht="28" customHeight="1">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
@@ -10171,77 +10967,44 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F10-06</t>
         </is>
       </c>
       <c r="D165" s="27" t="inlineStr">
         <is>
-          <t>客户终端</t>
+          <t>智能推荐系统</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G165" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G165" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H165" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="166" ht="28" customHeight="1">
-      <c r="A166" s="11" t="inlineStr">
-        <is>
-          <t>投顾服务</t>
-        </is>
-      </c>
-      <c r="B166" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C166" s="10" t="inlineStr">
-        <is>
-          <t>F12-03</t>
-        </is>
-      </c>
-      <c r="D166" s="27" t="inlineStr">
-        <is>
-          <t>投资建议书管理</t>
-        </is>
-      </c>
-      <c r="E166" s="11" t="inlineStr">
-        <is>
-          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
-        </is>
-      </c>
-      <c r="F166" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G166" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H166" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+        </is>
       </c>
     </row>
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B167" s="10" t="inlineStr">
@@ -10251,17 +11014,17 @@
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F11-01</t>
         </is>
       </c>
       <c r="D167" s="27" t="inlineStr">
         <is>
-          <t>账户分析报告</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr">
@@ -10275,13 +11038,13 @@
         </is>
       </c>
       <c r="H167" s="13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="168" ht="28" customHeight="1">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B168" s="10" t="inlineStr">
@@ -10291,37 +11054,37 @@
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D168" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G168" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G168" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H168" s="13" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169" ht="28" customHeight="1">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B169" s="10" t="inlineStr">
@@ -10331,44 +11094,77 @@
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>F12-06</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D169" s="27" t="inlineStr">
         <is>
-          <t>客户服务与基础服务</t>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G169" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G169" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H169" s="13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="170" ht="20" customHeight="1">
-      <c r="A170" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
-        </is>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" ht="28" customHeight="1">
+      <c r="A170" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C170" s="10" t="inlineStr">
+        <is>
+          <t>F11-04</t>
+        </is>
+      </c>
+      <c r="D170" s="27" t="inlineStr">
+        <is>
+          <t>违约概率（PD）建模</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="inlineStr">
+        <is>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+        </is>
+      </c>
+      <c r="F170" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H170" s="13" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="171" ht="28" customHeight="1">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B171" s="10" t="inlineStr">
@@ -10378,77 +11174,44 @@
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F11-05</t>
         </is>
       </c>
       <c r="D171" s="27" t="inlineStr">
         <is>
-          <t>TRS交易端</t>
+          <t>集中度限额管理</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+          <t>行业/发行人/评级集中度多维限额，超限预警</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G171" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G171" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H171" s="13" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="172" ht="28" customHeight="1">
-      <c r="A172" s="11" t="inlineStr">
-        <is>
-          <t>TRS收益互换</t>
-        </is>
-      </c>
-      <c r="B172" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C172" s="10" t="inlineStr">
-        <is>
-          <t>F13-02</t>
-        </is>
-      </c>
-      <c r="D172" s="27" t="inlineStr">
-        <is>
-          <t>TRS客户端</t>
-        </is>
-      </c>
-      <c r="E172" s="11" t="inlineStr">
-        <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
-        </is>
-      </c>
-      <c r="F172" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G172" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H172" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 投顾服务  (Investment Advisory)</t>
+        </is>
       </c>
     </row>
     <row r="173" ht="28" customHeight="1">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B173" s="10" t="inlineStr">
@@ -10458,17 +11221,17 @@
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F12-01</t>
         </is>
       </c>
       <c r="D173" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>投顾工作台</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr">
@@ -10488,7 +11251,7 @@
     <row r="174" ht="28" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B174" s="10" t="inlineStr">
@@ -10498,37 +11261,37 @@
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D174" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>客户终端</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G174" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G174" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H174" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175" ht="28" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B175" s="10" t="inlineStr">
@@ -10538,17 +11301,17 @@
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D175" s="27" t="inlineStr">
         <is>
-          <t>通知与确认文件</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr">
@@ -10568,7 +11331,7 @@
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B176" s="10" t="inlineStr">
@@ -10578,17 +11341,17 @@
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>F13-06</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D176" s="27" t="inlineStr">
         <is>
-          <t>系统集成</t>
+          <t>账户分析报告</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
+          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr">
@@ -10605,241 +11368,568 @@
         <v>25</v>
       </c>
     </row>
-    <row r="177" ht="20" customHeight="1">
-      <c r="A177" s="29" t="inlineStr">
+    <row r="177" ht="28" customHeight="1">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B177" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C177" s="10" t="inlineStr">
+        <is>
+          <t>F12-05</t>
+        </is>
+      </c>
+      <c r="D177" s="27" t="inlineStr">
+        <is>
+          <t>投研报告服务</t>
+        </is>
+      </c>
+      <c r="E177" s="11" t="inlineStr">
+        <is>
+          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+        </is>
+      </c>
+      <c r="F177" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G177" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H177" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" ht="28" customHeight="1">
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B178" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C178" s="10" t="inlineStr">
+        <is>
+          <t>F12-06</t>
+        </is>
+      </c>
+      <c r="D178" s="27" t="inlineStr">
+        <is>
+          <t>客户服务与基础服务</t>
+        </is>
+      </c>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+        </is>
+      </c>
+      <c r="F178" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G178" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H178" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="28" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D180" s="27" t="inlineStr">
+        <is>
+          <t>TRS交易端</t>
+        </is>
+      </c>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+        </is>
+      </c>
+      <c r="F180" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G180" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H180" s="13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="181" ht="28" customHeight="1">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D181" s="27" t="inlineStr">
+        <is>
+          <t>TRS客户端</t>
+        </is>
+      </c>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+        </is>
+      </c>
+      <c r="F181" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G181" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H181" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" ht="28" customHeight="1">
+      <c r="A182" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B182" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D182" s="27" t="inlineStr">
+        <is>
+          <t>TRS管理端</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="inlineStr">
+        <is>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+        </is>
+      </c>
+      <c r="F182" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G182" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H182" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" ht="28" customHeight="1">
+      <c r="A183" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B183" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C183" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D183" s="27" t="inlineStr">
+        <is>
+          <t>自动对冲</t>
+        </is>
+      </c>
+      <c r="E183" s="11" t="inlineStr">
+        <is>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+        </is>
+      </c>
+      <c r="F183" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G183" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H183" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="184" ht="28" customHeight="1">
+      <c r="A184" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D184" s="27" t="inlineStr">
+        <is>
+          <t>通知与确认文件</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="F184" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G184" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H184" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" ht="28" customHeight="1">
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>F13-06</t>
+        </is>
+      </c>
+      <c r="D185" s="27" t="inlineStr">
+        <is>
+          <t>系统集成</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
+        </is>
+      </c>
+      <c r="F185" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G185" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H185" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="28" customHeight="1">
-      <c r="A178" s="16" t="inlineStr">
+    <row r="187" ht="28" customHeight="1">
+      <c r="A187" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B178" s="15" t="inlineStr">
+      <c r="B187" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C178" s="15" t="inlineStr">
+      <c r="C187" s="15" t="inlineStr">
         <is>
           <t>F15-01</t>
         </is>
       </c>
-      <c r="D178" s="30" t="inlineStr">
+      <c r="D187" s="30" t="inlineStr">
         <is>
           <t>双边报价引擎</t>
         </is>
       </c>
-      <c r="E178" s="16" t="inlineStr">
+      <c r="E187" s="16" t="inlineStr">
         <is>
           <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
-      <c r="F178" s="16" t="inlineStr">
+      <c r="F187" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G178" s="28" t="inlineStr">
+      <c r="G187" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H178" s="18" t="n">
+      <c r="H187" s="18" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="179" ht="28" customHeight="1">
-      <c r="A179" s="16" t="inlineStr">
+    <row r="188" ht="28" customHeight="1">
+      <c r="A188" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B179" s="15" t="inlineStr">
+      <c r="B188" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C179" s="15" t="inlineStr">
+      <c r="C188" s="15" t="inlineStr">
         <is>
           <t>F15-02</t>
         </is>
       </c>
-      <c r="D179" s="30" t="inlineStr">
+      <c r="D188" s="30" t="inlineStr">
         <is>
           <t>库存风险实时管理</t>
         </is>
       </c>
-      <c r="E179" s="16" t="inlineStr">
+      <c r="E188" s="16" t="inlineStr">
         <is>
           <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
-      <c r="F179" s="16" t="inlineStr">
+      <c r="F188" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G179" s="28" t="inlineStr">
+      <c r="G188" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H179" s="18" t="n">
+      <c r="H188" s="18" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="180" ht="28" customHeight="1">
-      <c r="A180" s="16" t="inlineStr">
+    <row r="189" ht="28" customHeight="1">
+      <c r="A189" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B180" s="15" t="inlineStr">
+      <c r="B189" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C180" s="15" t="inlineStr">
+      <c r="C189" s="15" t="inlineStr">
         <is>
           <t>F15-03</t>
         </is>
       </c>
-      <c r="D180" s="30" t="inlineStr">
+      <c r="D189" s="30" t="inlineStr">
         <is>
           <t>报价优化算法</t>
         </is>
       </c>
-      <c r="E180" s="16" t="inlineStr">
+      <c r="E189" s="16" t="inlineStr">
         <is>
           <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
-      <c r="F180" s="16" t="inlineStr">
+      <c r="F189" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G180" s="28" t="inlineStr">
+      <c r="G189" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H180" s="18" t="n">
+      <c r="H189" s="18" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="181" ht="28" customHeight="1">
-      <c r="A181" s="16" t="inlineStr">
+    <row r="190" ht="28" customHeight="1">
+      <c r="A190" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B181" s="15" t="inlineStr">
+      <c r="B190" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C181" s="15" t="inlineStr">
+      <c r="C190" s="15" t="inlineStr">
         <is>
           <t>F15-04</t>
         </is>
       </c>
-      <c r="D181" s="30" t="inlineStr">
+      <c r="D190" s="30" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E181" s="16" t="inlineStr">
+      <c r="E190" s="16" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，策略调优</t>
         </is>
       </c>
-      <c r="F181" s="16" t="inlineStr">
+      <c r="F190" s="16" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G181" s="23" t="inlineStr">
+      <c r="G190" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H181" s="18" t="n">
+      <c r="H190" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="182" ht="28" customHeight="1">
-      <c r="A182" s="16" t="inlineStr">
+    <row r="191" ht="28" customHeight="1">
+      <c r="A191" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B182" s="15" t="inlineStr">
+      <c r="B191" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C182" s="15" t="inlineStr">
+      <c r="C191" s="15" t="inlineStr">
         <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D182" s="30" t="inlineStr">
+      <c r="D191" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E182" s="16" t="inlineStr">
+      <c r="E191" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F182" s="16" t="inlineStr">
+      <c r="F191" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G182" s="24" t="inlineStr">
+      <c r="G191" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H182" s="18" t="n">
+      <c r="H191" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="19" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H183" s="20">
-        <f>SUM(H3:H182)</f>
+      <c r="H192" s="20">
+        <f>SUM(H3:H191)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A143:H143"/>
-    <mergeCell ref="A163:H163"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A101:H101"/>
     <mergeCell ref="A130:H130"/>
-    <mergeCell ref="A157:H157"/>
+    <mergeCell ref="A179:H179"/>
+    <mergeCell ref="A166:H166"/>
+    <mergeCell ref="A186:H186"/>
+    <mergeCell ref="A172:H172"/>
+    <mergeCell ref="A192:G192"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A112:H112"/>
     <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A170:H170"/>
-    <mergeCell ref="A177:H177"/>
-    <mergeCell ref="A183:G183"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A150:H150"/>
     <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A159:H159"/>
     <mergeCell ref="A88:H88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -20,6 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_组合管理+绩效归因" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_策略投资_量化" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_定价平台" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_销售交易" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1576,13 +1577,13 @@
         </is>
       </c>
       <c r="M12" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P12" s="11" t="inlineStr">
         <is>
@@ -4736,13 +4737,422 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：销售交易  |  Sales Trading</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：面向对客服务的销售交易工作台，报价聚合、智能推荐、交易执行一体化；对应PPT Slide 47   |   来源：Slide 47</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：销售交易  (Sales Trading)  |  优先级：P2  |  竞品：金证/顶点  |  华锐基础：现券交易系统/IBOR  |  工期：5月  团队：5人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. 报价管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>D1. 报价管理</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>F10-01</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>报价工作台</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer，报价提醒功能</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>D1. 报价管理</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>F10-02</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>债券过滤与筛选</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>信用债全品种过滤，利率债（国债/证金债/地方债）过滤，精确识别与模糊识别双模式</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>D1. 报价管理</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>F10-03</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>报价撮合与对价</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>对价/最优报价聚合展示，撮合对价，交易包管理，报价成交确认，一键成交</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr"/>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D2. 交易执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>D2. 交易执行</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>F10-04</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>交易执行与要素校验</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>意向达成，交易要素自动校验，手工价录入，业务审批流程，交易记录管理</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr"/>
+      <c r="G10" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>D2. 交易执行</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>F10-05</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>风控检查</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>交易前风控规则同步校验，限额检查，合规拦截，风控记录留痕，不通过自动拦截</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>D3. 智能服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>D3. 智能服务</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>F10-06</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>智能推荐系统</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>基于客户画像与历史交易数据主动推荐券种，从被动服务转向主动服务，提升客户响应效率</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr"/>
+      <c r="G13" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>D3. 智能服务</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>F10-07</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>综合业务平台</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>解决交易员分散办公与客户交易信息共享问题，报价聚合展示，客户快速服务，多地协同</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr"/>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>合计 7项功能  |  P1: 0项  |  P2: 7项</t>
+        </is>
+      </c>
+      <c r="H15" s="20">
+        <f>SUM(H5:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="34" t="inlineStr"/>
+      <c r="J15" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10772,12 +11182,12 @@
       </c>
       <c r="D160" s="27" t="inlineStr">
         <is>
-          <t>销交工作台</t>
+          <t>报价工作台</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>报价管理主界面，历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer操作</t>
+          <t>历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer，报价提醒功能</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr">
@@ -10817,7 +11227,7 @@
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>信用债/利率债过滤，信用债全品种过滤，利率债国债/证金债/地方债分类过滤，精确与模糊识别</t>
+          <t>信用债全品种过滤，利率债（国债/证金债/地方债）过滤，精确识别与模糊识别双模式</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr">
@@ -10857,7 +11267,7 @@
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>报价展示（对价/最优报价），撮合对价，报价提醒，交易包管理，报价成交确认</t>
+          <t>对价/最优报价聚合展示，撮合对价，交易包管理，报价成交确认，一键成交</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr">
@@ -10892,12 +11302,12 @@
       </c>
       <c r="D163" s="27" t="inlineStr">
         <is>
-          <t>交易执行与审批</t>
+          <t>交易执行与要素校验</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>意向达成，交易要素校验，手工价录入，业务审批流程，交易执行</t>
+          <t>意向达成，交易要素自动校验，手工价录入，业务审批流程，交易记录管理</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr">
@@ -10937,7 +11347,7 @@
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>交易前风控规则校验，限额检查，合规拦截，风控记录留痕</t>
+          <t>交易前风控规则同步校验，限额检查，合规拦截，风控记录留痕，不通过自动拦截</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr">
@@ -10977,7 +11387,7 @@
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>从被动客户服务转向主动服务，基于客户画像与持仓分析智能推荐券种，提升客户响应效率</t>
+          <t>基于客户画像与历史交易数据主动推荐券种，从被动服务转向主动服务，提升客户响应效率</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr">
@@ -10994,51 +11404,51 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="26" t="inlineStr">
+    <row r="166" ht="28" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>F10-07</t>
+        </is>
+      </c>
+      <c r="D166" s="27" t="inlineStr">
+        <is>
+          <t>综合业务平台</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>解决交易员分散办公与客户交易信息共享问题，报价聚合展示，客户快速服务，多地协同</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G166" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H166" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="26" t="inlineStr">
         <is>
           <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
         </is>
-      </c>
-    </row>
-    <row r="167" ht="28" customHeight="1">
-      <c r="A167" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B167" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C167" s="10" t="inlineStr">
-        <is>
-          <t>F11-01</t>
-        </is>
-      </c>
-      <c r="D167" s="27" t="inlineStr">
-        <is>
-          <t>信用利差分析</t>
-        </is>
-      </c>
-      <c r="E167" s="11" t="inlineStr">
-        <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
-        </is>
-      </c>
-      <c r="F167" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G167" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H167" s="13" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="168" ht="28" customHeight="1">
@@ -11054,31 +11464,31 @@
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
+          <t>F11-01</t>
         </is>
       </c>
       <c r="D168" s="27" t="inlineStr">
         <is>
-          <t>CDS/CLN定价</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G168" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G168" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H168" s="13" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169" ht="28" customHeight="1">
@@ -11094,31 +11504,31 @@
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D169" s="27" t="inlineStr">
         <is>
-          <t>信用评级动态监控</t>
+          <t>CDS/CLN定价</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G169" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G169" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H169" s="13" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="170" ht="28" customHeight="1">
@@ -11134,31 +11544,31 @@
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D170" s="27" t="inlineStr">
         <is>
-          <t>违约概率（PD）建模</t>
+          <t>信用评级动态监控</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G170" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G170" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H170" s="13" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" ht="28" customHeight="1">
@@ -11174,78 +11584,78 @@
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
+          <t>F11-04</t>
+        </is>
+      </c>
+      <c r="D171" s="27" t="inlineStr">
+        <is>
+          <t>违约概率（PD）建模</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="inlineStr">
+        <is>
+          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+        </is>
+      </c>
+      <c r="F171" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G171" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H171" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="172" ht="28" customHeight="1">
+      <c r="A172" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C172" s="10" t="inlineStr">
+        <is>
           <t>F11-05</t>
         </is>
       </c>
-      <c r="D171" s="27" t="inlineStr">
+      <c r="D172" s="27" t="inlineStr">
         <is>
           <t>集中度限额管理</t>
         </is>
       </c>
-      <c r="E171" s="11" t="inlineStr">
+      <c r="E172" s="11" t="inlineStr">
         <is>
           <t>行业/发行人/评级集中度多维限额，超限预警</t>
         </is>
       </c>
-      <c r="F171" s="11" t="inlineStr">
+      <c r="F172" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G171" s="24" t="inlineStr">
+      <c r="G172" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H171" s="13" t="n">
+      <c r="H172" s="13" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="26" t="inlineStr">
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="26" t="inlineStr">
         <is>
           <t>【P2】 投顾服务  (Investment Advisory)</t>
         </is>
-      </c>
-    </row>
-    <row r="173" ht="28" customHeight="1">
-      <c r="A173" s="11" t="inlineStr">
-        <is>
-          <t>投顾服务</t>
-        </is>
-      </c>
-      <c r="B173" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C173" s="10" t="inlineStr">
-        <is>
-          <t>F12-01</t>
-        </is>
-      </c>
-      <c r="D173" s="27" t="inlineStr">
-        <is>
-          <t>投顾工作台</t>
-        </is>
-      </c>
-      <c r="E173" s="11" t="inlineStr">
-        <is>
-          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
-        </is>
-      </c>
-      <c r="F173" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G173" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H173" s="13" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="174" ht="28" customHeight="1">
@@ -11261,17 +11671,17 @@
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F12-01</t>
         </is>
       </c>
       <c r="D174" s="27" t="inlineStr">
         <is>
-          <t>客户终端</t>
+          <t>投顾工作台</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr">
@@ -11301,17 +11711,17 @@
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D175" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>客户终端</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
+          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr">
@@ -11325,7 +11735,7 @@
         </is>
       </c>
       <c r="H175" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" ht="28" customHeight="1">
@@ -11341,31 +11751,31 @@
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D176" s="27" t="inlineStr">
         <is>
-          <t>账户分析报告</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G176" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G176" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H176" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" ht="28" customHeight="1">
@@ -11381,31 +11791,31 @@
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D177" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>账户分析报告</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G177" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G177" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H177" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="178" ht="28" customHeight="1">
@@ -11421,78 +11831,78 @@
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
+          <t>F12-05</t>
+        </is>
+      </c>
+      <c r="D178" s="27" t="inlineStr">
+        <is>
+          <t>投研报告服务</t>
+        </is>
+      </c>
+      <c r="E178" s="11" t="inlineStr">
+        <is>
+          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+        </is>
+      </c>
+      <c r="F178" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G178" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H178" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" ht="28" customHeight="1">
+      <c r="A179" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B179" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C179" s="10" t="inlineStr">
+        <is>
           <t>F12-06</t>
         </is>
       </c>
-      <c r="D178" s="27" t="inlineStr">
+      <c r="D179" s="27" t="inlineStr">
         <is>
           <t>客户服务与基础服务</t>
         </is>
       </c>
-      <c r="E178" s="11" t="inlineStr">
+      <c r="E179" s="11" t="inlineStr">
         <is>
           <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
         </is>
       </c>
-      <c r="F178" s="11" t="inlineStr">
+      <c r="F179" s="11" t="inlineStr">
         <is>
           <t>功能测试通过</t>
         </is>
       </c>
-      <c r="G178" s="25" t="inlineStr">
+      <c r="G179" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H178" s="13" t="n">
+      <c r="H179" s="13" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="26" t="inlineStr">
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="26" t="inlineStr">
         <is>
           <t>【P2】 TRS收益互换  (Total Return Swap)</t>
         </is>
-      </c>
-    </row>
-    <row r="180" ht="28" customHeight="1">
-      <c r="A180" s="11" t="inlineStr">
-        <is>
-          <t>TRS收益互换</t>
-        </is>
-      </c>
-      <c r="B180" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C180" s="10" t="inlineStr">
-        <is>
-          <t>F13-01</t>
-        </is>
-      </c>
-      <c r="D180" s="27" t="inlineStr">
-        <is>
-          <t>TRS交易端</t>
-        </is>
-      </c>
-      <c r="E180" s="11" t="inlineStr">
-        <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
-        </is>
-      </c>
-      <c r="F180" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G180" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H180" s="13" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="181" ht="28" customHeight="1">
@@ -11508,17 +11918,17 @@
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F13-01</t>
         </is>
       </c>
       <c r="D181" s="27" t="inlineStr">
         <is>
-          <t>TRS客户端</t>
+          <t>TRS交易端</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr">
@@ -11532,7 +11942,7 @@
         </is>
       </c>
       <c r="H181" s="13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="182" ht="28" customHeight="1">
@@ -11548,31 +11958,31 @@
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F13-02</t>
         </is>
       </c>
       <c r="D182" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>TRS客户端</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G182" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G182" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H182" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="183" ht="28" customHeight="1">
@@ -11588,31 +11998,31 @@
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F13-03</t>
         </is>
       </c>
       <c r="D183" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>TRS管理端</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G183" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G183" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H183" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" ht="28" customHeight="1">
@@ -11628,31 +12038,31 @@
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F13-04</t>
         </is>
       </c>
       <c r="D184" s="27" t="inlineStr">
         <is>
-          <t>通知与确认文件</t>
+          <t>自动对冲</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G184" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G184" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H184" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="185" ht="28" customHeight="1">
@@ -11668,78 +12078,78 @@
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D185" s="27" t="inlineStr">
+        <is>
+          <t>通知与确认文件</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="F185" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G185" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H185" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" ht="28" customHeight="1">
+      <c r="A186" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C186" s="10" t="inlineStr">
+        <is>
           <t>F13-06</t>
         </is>
       </c>
-      <c r="D185" s="27" t="inlineStr">
+      <c r="D186" s="27" t="inlineStr">
         <is>
           <t>系统集成</t>
         </is>
       </c>
-      <c r="E185" s="11" t="inlineStr">
+      <c r="E186" s="11" t="inlineStr">
         <is>
           <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
         </is>
       </c>
-      <c r="F185" s="11" t="inlineStr">
+      <c r="F186" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G185" s="23" t="inlineStr">
+      <c r="G186" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H185" s="13" t="n">
+      <c r="H186" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="29" t="inlineStr">
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
-      </c>
-    </row>
-    <row r="187" ht="28" customHeight="1">
-      <c r="A187" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B187" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C187" s="15" t="inlineStr">
-        <is>
-          <t>F15-01</t>
-        </is>
-      </c>
-      <c r="D187" s="30" t="inlineStr">
-        <is>
-          <t>双边报价引擎</t>
-        </is>
-      </c>
-      <c r="E187" s="16" t="inlineStr">
-        <is>
-          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
-        </is>
-      </c>
-      <c r="F187" s="16" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G187" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H187" s="18" t="n">
-        <v>70</v>
       </c>
     </row>
     <row r="188" ht="28" customHeight="1">
@@ -11755,17 +12165,17 @@
       </c>
       <c r="C188" s="15" t="inlineStr">
         <is>
-          <t>F15-02</t>
+          <t>F15-01</t>
         </is>
       </c>
       <c r="D188" s="30" t="inlineStr">
         <is>
-          <t>库存风险实时管理</t>
+          <t>双边报价引擎</t>
         </is>
       </c>
       <c r="E188" s="16" t="inlineStr">
         <is>
-          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
       <c r="F188" s="16" t="inlineStr">
@@ -11779,7 +12189,7 @@
         </is>
       </c>
       <c r="H188" s="18" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="189" ht="28" customHeight="1">
@@ -11795,17 +12205,17 @@
       </c>
       <c r="C189" s="15" t="inlineStr">
         <is>
-          <t>F15-03</t>
+          <t>F15-02</t>
         </is>
       </c>
       <c r="D189" s="30" t="inlineStr">
         <is>
-          <t>报价优化算法</t>
+          <t>库存风险实时管理</t>
         </is>
       </c>
       <c r="E189" s="16" t="inlineStr">
         <is>
-          <t>基于市场微结构理论动态调整bid-ask spread</t>
+          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
       <c r="F189" s="16" t="inlineStr">
@@ -11819,7 +12229,7 @@
         </is>
       </c>
       <c r="H189" s="18" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="190" ht="28" customHeight="1">
@@ -11835,31 +12245,31 @@
       </c>
       <c r="C190" s="15" t="inlineStr">
         <is>
-          <t>F15-04</t>
+          <t>F15-03</t>
         </is>
       </c>
       <c r="D190" s="30" t="inlineStr">
         <is>
-          <t>竞争力分析</t>
+          <t>报价优化算法</t>
         </is>
       </c>
       <c r="E190" s="16" t="inlineStr">
         <is>
-          <t>与市场最优报价对比，中签率分析，策略调优</t>
+          <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
       <c r="F190" s="16" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G190" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G190" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H190" s="18" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="191" ht="28" customHeight="1">
@@ -11875,62 +12285,102 @@
       </c>
       <c r="C191" s="15" t="inlineStr">
         <is>
+          <t>F15-04</t>
+        </is>
+      </c>
+      <c r="D191" s="30" t="inlineStr">
+        <is>
+          <t>竞争力分析</t>
+        </is>
+      </c>
+      <c r="E191" s="16" t="inlineStr">
+        <is>
+          <t>与市场最优报价对比，中签率分析，策略调优</t>
+        </is>
+      </c>
+      <c r="F191" s="16" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H191" s="18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="192" ht="28" customHeight="1">
+      <c r="A192" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr">
+        <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D191" s="30" t="inlineStr">
+      <c r="D192" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E191" s="16" t="inlineStr">
+      <c r="E192" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F191" s="16" t="inlineStr">
+      <c r="F192" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G191" s="24" t="inlineStr">
+      <c r="G192" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H191" s="18" t="n">
+      <c r="H192" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="19" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H192" s="20">
-        <f>SUM(H3:H191)</f>
+      <c r="H193" s="20">
+        <f>SUM(H3:H192)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A193:G193"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A101:H101"/>
     <mergeCell ref="A130:H130"/>
-    <mergeCell ref="A179:H179"/>
-    <mergeCell ref="A166:H166"/>
-    <mergeCell ref="A186:H186"/>
-    <mergeCell ref="A172:H172"/>
-    <mergeCell ref="A192:G192"/>
+    <mergeCell ref="A180:H180"/>
+    <mergeCell ref="A187:H187"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A112:H112"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A173:H173"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A159:H159"/>
     <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A167:H167"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -21,6 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_策略投资_量化" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_定价平台" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_销售交易" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_信用债_信用衍生品" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1602,7 +1603,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Credit &amp; CDS</t>
+          <t>Credit Bond &amp; CDS</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1622,46 +1623,46 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>★★★★☆</t>
+          <t>★★★☆☆</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
-        <is>
-          <t>大</t>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>衡泰/Bloomberg</t>
+          <t>衡泰/恒生</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>ARC信用风险框架</t>
+          <t>IBOR持仓账薄/定价平台</t>
         </is>
       </c>
       <c r="M13" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>CDS定价+信用利差分析</t>
+          <t>信用评级/投资池/全生命周期信用风险管理，打通从评级审批到交易下单全链路；对应PPT Slide 42</t>
         </is>
       </c>
     </row>
@@ -5146,13 +5147,620 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：信用债/信用衍生品  |  Credit Bond &amp; CDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：信用评级/投资池/全生命周期信用风险管理，打通从评级审批到交易下单全链路；对应PPT Slide 42   |   来源：Slide 42</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：信用债/信用衍生品  (Credit Bond &amp; CDS)  |  优先级：P2  |  竞品：衡泰/恒生  |  华锐基础：IBOR持仓账薄/定价平台  |  工期：8月  团队：8人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. 信用数据与评估</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>D1. 信用数据与评估</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>F11-01</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>信用风险数据接入</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>外部信用数据服务接入（Wind/中诚信/联合评级等），内部数据整合，数据质量检查，信用风险数据集市</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>D1. 信用数据与评估</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>F11-02</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>信用评估引擎</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>持续迭代信用评价引擎，资产证券化评价，交易对手评价，违约概率（PD）建模，信用评分</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>D1. 信用数据与评估</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>F11-03</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>信用预警系统</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>市场数据自动触发预警，评级下调动态预警，投后预警跟踪与信号处理，预警规则配置</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr"/>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D2. 投资池与准入管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>D2. 投资池与准入管理</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>F11-04</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>投资池管理</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>债券池配置与维护，债券准入/退出规则，白名单/黑名单管理，池状态实时更新</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr"/>
+      <c r="G10" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>D2. 投资池与准入管理</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>F11-05</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>评级管理</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>内部评级录入与更新，外部评级同步（中诚信/联合/大公），评级变更历史追踪，评级模型管理</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>D2. 投资池与准入管理</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>F11-06</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>投前审批管理</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>新券投资准入审批流程，信用额度申请，投资决策材料生成，审批记录留痕</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>D3. 持仓与风险监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>D3. 持仓与风险监控</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>F11-07</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>持仓与敞口管理</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>信用债持仓实时查询，敞口管理，集中度分析（行业/评级/发行人），到期提醒</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr"/>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>D3. 持仓与风险监控</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>F11-08</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>信用风险监控看板</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>多维度风险指标实时监控，信用利差走势，主体信用事件推送，指标监控与查询统计</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>D3. 持仓与风险监控</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>F11-09</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>违约管理</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>违约事件记录，违约债券处置跟踪，损失估算，监管报送，违约主体黑名单自动更新</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr"/>
+      <c r="F16" s="11" t="inlineStr"/>
+      <c r="G16" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>D4. 信用利差与衍生品</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>D4. 信用利差与衍生品</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>F11-10</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>信用利差分析</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析，利差走势，相对价值分析</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr"/>
+      <c r="F18" s="11" t="inlineStr"/>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>D4. 信用利差与衍生品</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>F11-11</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>CDS定价与管理</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>信用违约互换定价（ISDA标准），生存概率曲线校准，CDS交易录入与持仓管理</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr"/>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>D4. 信用利差与衍生品</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>F11-12</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>配置与权限管理</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>预警规则配置，指标库管理，评级模型管理，用户权限管理，债券池配置管理</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr"/>
+      <c r="G20" s="42" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>合计 12项功能  |  P1: 0项  |  P2: 12项</t>
+        </is>
+      </c>
+      <c r="H21" s="20">
+        <f>SUM(H5:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="34" t="inlineStr"/>
+      <c r="J21" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A13:J13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11447,7 +12055,7 @@
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="26" t="inlineStr">
         <is>
-          <t>【P2】 信用债/信用衍生品  (Credit &amp; CDS)</t>
+          <t>【P2】 信用债/信用衍生品  (Credit Bond &amp; CDS)</t>
         </is>
       </c>
     </row>
@@ -11469,12 +12077,12 @@
       </c>
       <c r="D168" s="27" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>信用风险数据接入</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析</t>
+          <t>外部信用数据服务接入（Wind/中诚信/联合评级等），内部数据整合，数据质量检查，信用风险数据集市</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr">
@@ -11509,12 +12117,12 @@
       </c>
       <c r="D169" s="27" t="inlineStr">
         <is>
-          <t>CDS/CLN定价</t>
+          <t>信用评估引擎</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价，ISDA标准，生存概率曲线校准</t>
+          <t>持续迭代信用评价引擎，资产证券化评价，交易对手评价，违约概率（PD）建模，信用评分</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr">
@@ -11528,7 +12136,7 @@
         </is>
       </c>
       <c r="H169" s="13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="170" ht="28" customHeight="1">
@@ -11549,26 +12157,26 @@
       </c>
       <c r="D170" s="27" t="inlineStr">
         <is>
-          <t>信用评级动态监控</t>
+          <t>信用预警系统</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>对接外部评级机构（中诚信/联合/大公），评级下调预警</t>
+          <t>市场数据自动触发预警，评级下调动态预警，投后预警跟踪与信号处理，预警规则配置</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G170" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H170" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" ht="28" customHeight="1">
@@ -11589,26 +12197,26 @@
       </c>
       <c r="D171" s="27" t="inlineStr">
         <is>
-          <t>违约概率（PD）建模</t>
+          <t>投资池管理</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>结构化Merton模型+市场隐含PD，信用风险计量</t>
+          <t>债券池配置与维护，债券准入/退出规则，白名单/黑名单管理，池状态实时更新</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G171" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G171" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H171" s="13" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" ht="28" customHeight="1">
@@ -11629,12 +12237,12 @@
       </c>
       <c r="D172" s="27" t="inlineStr">
         <is>
-          <t>集中度限额管理</t>
+          <t>评级管理</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>行业/发行人/评级集中度多维限额，超限预警</t>
+          <t>内部评级录入与更新，外部评级同步（中诚信/联合/大公），评级变更历史追踪，评级模型管理</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr">
@@ -11651,17 +12259,50 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173" ht="20" customHeight="1">
-      <c r="A173" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 投顾服务  (Investment Advisory)</t>
-        </is>
+    <row r="173" ht="28" customHeight="1">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>F11-06</t>
+        </is>
+      </c>
+      <c r="D173" s="27" t="inlineStr">
+        <is>
+          <t>投前审批管理</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>新券投资准入审批流程，信用额度申请，投资决策材料生成，审批记录留痕</t>
+        </is>
+      </c>
+      <c r="F173" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G173" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H173" s="13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="174" ht="28" customHeight="1">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B174" s="10" t="inlineStr">
@@ -11671,17 +12312,17 @@
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>F12-01</t>
+          <t>F11-07</t>
         </is>
       </c>
       <c r="D174" s="27" t="inlineStr">
         <is>
-          <t>投顾工作台</t>
+          <t>持仓与敞口管理</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
+          <t>信用债持仓实时查询，敞口管理，集中度分析（行业/评级/发行人），到期提醒</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr">
@@ -11701,7 +12342,7 @@
     <row r="175" ht="28" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B175" s="10" t="inlineStr">
@@ -11711,37 +12352,37 @@
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F11-08</t>
         </is>
       </c>
       <c r="D175" s="27" t="inlineStr">
         <is>
-          <t>客户终端</t>
+          <t>信用风险监控看板</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+          <t>多维度风险指标实时监控，信用利差走势，主体信用事件推送，指标监控与查询统计</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G175" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G175" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H175" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="176" ht="28" customHeight="1">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B176" s="10" t="inlineStr">
@@ -11751,37 +12392,37 @@
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F11-09</t>
         </is>
       </c>
       <c r="D176" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>违约管理</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
+          <t>违约事件记录，违约债券处置跟踪，损失估算，监管报送，违约主体黑名单自动更新</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G176" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G176" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H176" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="177" ht="28" customHeight="1">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
@@ -11791,17 +12432,17 @@
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F11-10</t>
         </is>
       </c>
       <c r="D177" s="27" t="inlineStr">
         <is>
-          <t>账户分析报告</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析，利差走势，相对价值分析</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr">
@@ -11815,13 +12456,13 @@
         </is>
       </c>
       <c r="H177" s="13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="178" ht="28" customHeight="1">
       <c r="A178" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B178" s="10" t="inlineStr">
@@ -11831,37 +12472,37 @@
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F11-11</t>
         </is>
       </c>
       <c r="D178" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>CDS定价与管理</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+          <t>信用违约互换定价（ISDA标准），生存概率曲线校准，CDS交易录入与持仓管理</t>
         </is>
       </c>
       <c r="F178" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G178" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G178" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H178" s="13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="179" ht="28" customHeight="1">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B179" s="10" t="inlineStr">
@@ -11871,17 +12512,17 @@
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>F12-06</t>
+          <t>F11-12</t>
         </is>
       </c>
       <c r="D179" s="27" t="inlineStr">
         <is>
-          <t>客户服务与基础服务</t>
+          <t>配置与权限管理</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+          <t>预警规则配置，指标库管理，评级模型管理，用户权限管理，债券池配置管理</t>
         </is>
       </c>
       <c r="F179" s="11" t="inlineStr">
@@ -11895,20 +12536,20 @@
         </is>
       </c>
       <c r="H179" s="13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="26" t="inlineStr">
         <is>
-          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+          <t>【P2】 投顾服务  (Investment Advisory)</t>
         </is>
       </c>
     </row>
     <row r="181" ht="28" customHeight="1">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B181" s="10" t="inlineStr">
@@ -11918,37 +12559,37 @@
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F12-01</t>
         </is>
       </c>
       <c r="D181" s="27" t="inlineStr">
         <is>
-          <t>TRS交易端</t>
+          <t>投顾工作台</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G181" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G181" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H181" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" ht="28" customHeight="1">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B182" s="10" t="inlineStr">
@@ -11958,37 +12599,37 @@
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D182" s="27" t="inlineStr">
         <is>
-          <t>TRS客户端</t>
+          <t>客户终端</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G182" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G182" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H182" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" ht="28" customHeight="1">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B183" s="10" t="inlineStr">
@@ -11998,17 +12639,17 @@
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D183" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr">
@@ -12022,13 +12663,13 @@
         </is>
       </c>
       <c r="H183" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="184" ht="28" customHeight="1">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B184" s="10" t="inlineStr">
@@ -12038,17 +12679,17 @@
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D184" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>账户分析报告</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr">
@@ -12068,7 +12709,7 @@
     <row r="185" ht="28" customHeight="1">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B185" s="10" t="inlineStr">
@@ -12078,17 +12719,17 @@
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F12-05</t>
         </is>
       </c>
       <c r="D185" s="27" t="inlineStr">
         <is>
-          <t>通知与确认文件</t>
+          <t>投研报告服务</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr">
@@ -12108,275 +12749,522 @@
     <row r="186" ht="28" customHeight="1">
       <c r="A186" s="11" t="inlineStr">
         <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C186" s="10" t="inlineStr">
+        <is>
+          <t>F12-06</t>
+        </is>
+      </c>
+      <c r="D186" s="27" t="inlineStr">
+        <is>
+          <t>客户服务与基础服务</t>
+        </is>
+      </c>
+      <c r="E186" s="11" t="inlineStr">
+        <is>
+          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+        </is>
+      </c>
+      <c r="F186" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G186" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H186" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="28" customHeight="1">
+      <c r="A188" s="11" t="inlineStr">
+        <is>
           <t>TRS收益互换</t>
         </is>
       </c>
-      <c r="B186" s="10" t="inlineStr">
+      <c r="B188" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C186" s="10" t="inlineStr">
+      <c r="C188" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D188" s="27" t="inlineStr">
+        <is>
+          <t>TRS交易端</t>
+        </is>
+      </c>
+      <c r="E188" s="11" t="inlineStr">
+        <is>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+        </is>
+      </c>
+      <c r="F188" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G188" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H188" s="13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="189" ht="28" customHeight="1">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B189" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="D189" s="27" t="inlineStr">
+        <is>
+          <t>TRS客户端</t>
+        </is>
+      </c>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+        </is>
+      </c>
+      <c r="F189" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G189" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H189" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190" ht="28" customHeight="1">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B190" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C190" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="D190" s="27" t="inlineStr">
+        <is>
+          <t>TRS管理端</t>
+        </is>
+      </c>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+        </is>
+      </c>
+      <c r="F190" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G190" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H190" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="191" ht="28" customHeight="1">
+      <c r="A191" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B191" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C191" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="D191" s="27" t="inlineStr">
+        <is>
+          <t>自动对冲</t>
+        </is>
+      </c>
+      <c r="E191" s="11" t="inlineStr">
+        <is>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+        </is>
+      </c>
+      <c r="F191" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G191" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H191" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="192" ht="28" customHeight="1">
+      <c r="A192" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B192" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C192" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D192" s="27" t="inlineStr">
+        <is>
+          <t>通知与确认文件</t>
+        </is>
+      </c>
+      <c r="E192" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="F192" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G192" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H192" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193" ht="28" customHeight="1">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B193" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
         <is>
           <t>F13-06</t>
         </is>
       </c>
-      <c r="D186" s="27" t="inlineStr">
+      <c r="D193" s="27" t="inlineStr">
         <is>
           <t>系统集成</t>
         </is>
       </c>
-      <c r="E186" s="11" t="inlineStr">
+      <c r="E193" s="11" t="inlineStr">
         <is>
           <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
         </is>
       </c>
-      <c r="F186" s="11" t="inlineStr">
+      <c r="F193" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G186" s="23" t="inlineStr">
+      <c r="G193" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H186" s="13" t="n">
+      <c r="H193" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="187" ht="20" customHeight="1">
-      <c r="A187" s="29" t="inlineStr">
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="28" customHeight="1">
-      <c r="A188" s="16" t="inlineStr">
+    <row r="195" ht="28" customHeight="1">
+      <c r="A195" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B188" s="15" t="inlineStr">
+      <c r="B195" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C188" s="15" t="inlineStr">
+      <c r="C195" s="15" t="inlineStr">
         <is>
           <t>F15-01</t>
         </is>
       </c>
-      <c r="D188" s="30" t="inlineStr">
+      <c r="D195" s="30" t="inlineStr">
         <is>
           <t>双边报价引擎</t>
         </is>
       </c>
-      <c r="E188" s="16" t="inlineStr">
+      <c r="E195" s="16" t="inlineStr">
         <is>
           <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
-      <c r="F188" s="16" t="inlineStr">
+      <c r="F195" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G188" s="28" t="inlineStr">
+      <c r="G195" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H188" s="18" t="n">
+      <c r="H195" s="18" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="189" ht="28" customHeight="1">
-      <c r="A189" s="16" t="inlineStr">
+    <row r="196" ht="28" customHeight="1">
+      <c r="A196" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B189" s="15" t="inlineStr">
+      <c r="B196" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C189" s="15" t="inlineStr">
+      <c r="C196" s="15" t="inlineStr">
         <is>
           <t>F15-02</t>
         </is>
       </c>
-      <c r="D189" s="30" t="inlineStr">
+      <c r="D196" s="30" t="inlineStr">
         <is>
           <t>库存风险实时管理</t>
         </is>
       </c>
-      <c r="E189" s="16" t="inlineStr">
+      <c r="E196" s="16" t="inlineStr">
         <is>
           <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
-      <c r="F189" s="16" t="inlineStr">
+      <c r="F196" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G189" s="28" t="inlineStr">
+      <c r="G196" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H189" s="18" t="n">
+      <c r="H196" s="18" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="190" ht="28" customHeight="1">
-      <c r="A190" s="16" t="inlineStr">
+    <row r="197" ht="28" customHeight="1">
+      <c r="A197" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B190" s="15" t="inlineStr">
+      <c r="B197" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C190" s="15" t="inlineStr">
+      <c r="C197" s="15" t="inlineStr">
         <is>
           <t>F15-03</t>
         </is>
       </c>
-      <c r="D190" s="30" t="inlineStr">
+      <c r="D197" s="30" t="inlineStr">
         <is>
           <t>报价优化算法</t>
         </is>
       </c>
-      <c r="E190" s="16" t="inlineStr">
+      <c r="E197" s="16" t="inlineStr">
         <is>
           <t>基于市场微结构理论动态调整bid-ask spread</t>
         </is>
       </c>
-      <c r="F190" s="16" t="inlineStr">
+      <c r="F197" s="16" t="inlineStr">
         <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G190" s="28" t="inlineStr">
+      <c r="G197" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H190" s="18" t="n">
+      <c r="H197" s="18" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="191" ht="28" customHeight="1">
-      <c r="A191" s="16" t="inlineStr">
+    <row r="198" ht="28" customHeight="1">
+      <c r="A198" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B191" s="15" t="inlineStr">
+      <c r="B198" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C191" s="15" t="inlineStr">
+      <c r="C198" s="15" t="inlineStr">
         <is>
           <t>F15-04</t>
         </is>
       </c>
-      <c r="D191" s="30" t="inlineStr">
+      <c r="D198" s="30" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E191" s="16" t="inlineStr">
+      <c r="E198" s="16" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，策略调优</t>
         </is>
       </c>
-      <c r="F191" s="16" t="inlineStr">
+      <c r="F198" s="16" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G191" s="23" t="inlineStr">
+      <c r="G198" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H191" s="18" t="n">
+      <c r="H198" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="192" ht="28" customHeight="1">
-      <c r="A192" s="16" t="inlineStr">
+    <row r="199" ht="28" customHeight="1">
+      <c r="A199" s="16" t="inlineStr">
         <is>
           <t>做市商系统</t>
         </is>
       </c>
-      <c r="B192" s="15" t="inlineStr">
+      <c r="B199" s="15" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C192" s="15" t="inlineStr">
+      <c r="C199" s="15" t="inlineStr">
         <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D192" s="30" t="inlineStr">
+      <c r="D199" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E192" s="16" t="inlineStr">
+      <c r="E199" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F192" s="16" t="inlineStr">
+      <c r="F199" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G192" s="24" t="inlineStr">
+      <c r="G199" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H192" s="18" t="n">
+      <c r="H199" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="19" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H193" s="20">
-        <f>SUM(H3:H192)</f>
+      <c r="H200" s="20">
+        <f>SUM(H3:H199)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A143:H143"/>
-    <mergeCell ref="A193:G193"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A101:H101"/>
     <mergeCell ref="A130:H130"/>
     <mergeCell ref="A180:H180"/>
     <mergeCell ref="A187:H187"/>
+    <mergeCell ref="A200:G200"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A112:H112"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A173:H173"/>
+    <mergeCell ref="A194:H194"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A159:H159"/>
     <mergeCell ref="A88:H88"/>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -22,6 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_定价平台" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_销售交易" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_信用债_信用衍生品" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_投顾服务" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1726,13 +1727,13 @@
         </is>
       </c>
       <c r="M14" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P14" s="11" t="inlineStr">
         <is>
@@ -5754,13 +5755,460 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：投顾服务  |  Investment Advisory</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：全链条数字化债券投顾服务，覆盖投资建议、账户分析、投研报告；对应PPT Slide 48   |   来源：Slide 48</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：投顾服务  (Investment Advisory)  |  优先级：P2  |  竞品：衡泰/金证  |  华锐基础：IBOR持仓账薄  |  工期：5月  团队：5人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. 投顾工作台</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>D1. 投顾工作台</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>F12-01</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>投顾操作工作台</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>投顾人员管理客户委托，上传研究报告，发送投资建议，查看客户反馈与确认状态</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>D1. 投顾工作台</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>F12-02</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>投资建议书管理</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>投资建议书线上生成与审批，客户确认全流程，留痕追溯，电子签收，历史建议书归档</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>D1. 投顾工作台</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>F12-03</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>投研报告服务</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>日/周/月研究报告上传与定向推送，RPA自动获取基础数据，报告分类管理与检索</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr"/>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D2. 客户终端</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>D2. 客户终端</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>F12-04</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>客户投资服务界面</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>客户查看投资建议与分析报告，发送确认，查看账户净值走势、持仓明细、交易明细</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr"/>
+      <c r="G10" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>D2. 客户终端</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>F12-05</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>账户深度分析</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>账户净值走势，久期走势，归因分析，估值台账，持仓明细，交易明细，定期分析报告生成</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>D2. 客户终端</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>F12-06</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>交易服务对接</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>客户查看投资建议后直接触发交易委托，与销售交易系统对接，全程数字化交易确认</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>D3. 基础服务</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>D3. 基础服务</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>F12-07</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>客户服务中心</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>服务中心，消息中心，常见问题，问卷系统，客户满意度管理</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr"/>
+      <c r="G14" s="42" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>D3. 基础服务</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>F12-08</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>平台基础管理</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>用户管理，账户管理，数据管理，消息群发，登录注册，权限控制</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="42" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>合计 8项功能  |  P1: 0项  |  P2: 8项</t>
+        </is>
+      </c>
+      <c r="H16" s="20">
+        <f>SUM(H5:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="34" t="inlineStr"/>
+      <c r="J16" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A13:J13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12564,12 +13012,12 @@
       </c>
       <c r="D181" s="27" t="inlineStr">
         <is>
-          <t>投顾工作台</t>
+          <t>投顾操作工作台</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>投顾人员操作界面，管理客户委托，上传研究报告，发送投资建议，查看客户反馈</t>
+          <t>投顾人员管理客户委托，上传研究报告，发送投资建议，查看客户反馈与确认状态</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr">
@@ -12604,12 +13052,12 @@
       </c>
       <c r="D182" s="27" t="inlineStr">
         <is>
-          <t>客户终端</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，确认交易服务，查看账户净值走势、持仓明细、交易明细</t>
+          <t>投资建议书线上生成与审批，客户确认全流程，留痕追溯，电子签收，历史建议书归档</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr">
@@ -12644,12 +13092,12 @@
       </c>
       <c r="D183" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>投研报告服务</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成、审批、确认全流程，留痕追溯，客户电子签收</t>
+          <t>日/周/月研究报告上传与定向推送，RPA自动获取基础数据，报告分类管理与检索</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr">
@@ -12684,26 +13132,26 @@
       </c>
       <c r="D184" s="27" t="inlineStr">
         <is>
-          <t>账户分析报告</t>
+          <t>客户投资服务界面</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势、久期走势、归因分析、估值台账等核心数据展示及定期报告生成</t>
+          <t>客户查看投资建议与分析报告，发送确认，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G184" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G184" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H184" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="185" ht="28" customHeight="1">
@@ -12724,26 +13172,26 @@
       </c>
       <c r="D185" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>账户深度分析</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与推送，RPA自动获取基础数据，报告分类管理</t>
+          <t>账户净值走势，久期走势，归因分析，估值台账，持仓明细，交易明细，定期分析报告生成</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G185" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G185" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H185" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="186" ht="28" customHeight="1">
@@ -12764,39 +13212,72 @@
       </c>
       <c r="D186" s="27" t="inlineStr">
         <is>
-          <t>客户服务与基础服务</t>
+          <t>交易服务对接</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>服务中心、消息中心、问卷系统；用户/账户/数据管理，消息群发，登录注册</t>
+          <t>客户查看投资建议后直接触发交易委托，与销售交易系统对接，全程数字化交易确认</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr">
         <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G186" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H186" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" ht="28" customHeight="1">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B187" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>F12-07</t>
+        </is>
+      </c>
+      <c r="D187" s="27" t="inlineStr">
+        <is>
+          <t>客户服务中心</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>服务中心，消息中心，常见问题，问卷系统，客户满意度管理</t>
+        </is>
+      </c>
+      <c r="F187" s="11" t="inlineStr">
+        <is>
           <t>功能测试通过</t>
         </is>
       </c>
-      <c r="G186" s="25" t="inlineStr">
+      <c r="G187" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H186" s="13" t="n">
+      <c r="H187" s="13" t="n">
         <v>10</v>
-      </c>
-    </row>
-    <row r="187" ht="20" customHeight="1">
-      <c r="A187" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
-        </is>
       </c>
     </row>
     <row r="188" ht="28" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>TRS收益互换</t>
+          <t>投顾服务</t>
         </is>
       </c>
       <c r="B188" s="10" t="inlineStr">
@@ -12806,71 +13287,38 @@
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F12-08</t>
         </is>
       </c>
       <c r="D188" s="27" t="inlineStr">
         <is>
-          <t>TRS交易端</t>
+          <t>平台基础管理</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+          <t>用户管理，账户管理，数据管理，消息群发，登录注册，权限控制</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G188" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G188" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H188" s="13" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="189" ht="28" customHeight="1">
-      <c r="A189" s="11" t="inlineStr">
-        <is>
-          <t>TRS收益互换</t>
-        </is>
-      </c>
-      <c r="B189" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C189" s="10" t="inlineStr">
-        <is>
-          <t>F13-02</t>
-        </is>
-      </c>
-      <c r="D189" s="27" t="inlineStr">
-        <is>
-          <t>TRS客户端</t>
-        </is>
-      </c>
-      <c r="E189" s="11" t="inlineStr">
-        <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
-        </is>
-      </c>
-      <c r="F189" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G189" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H189" s="13" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+        </is>
       </c>
     </row>
     <row r="190" ht="28" customHeight="1">
@@ -12886,31 +13334,31 @@
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F13-01</t>
         </is>
       </c>
       <c r="D190" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>TRS交易端</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
         </is>
       </c>
       <c r="F190" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G190" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G190" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H190" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="191" ht="28" customHeight="1">
@@ -12926,17 +13374,17 @@
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F13-02</t>
         </is>
       </c>
       <c r="D191" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>TRS客户端</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr">
@@ -12966,17 +13414,17 @@
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F13-03</t>
         </is>
       </c>
       <c r="D192" s="27" t="inlineStr">
         <is>
-          <t>通知与确认文件</t>
+          <t>TRS管理端</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
         </is>
       </c>
       <c r="F192" s="11" t="inlineStr">
@@ -12990,7 +13438,7 @@
         </is>
       </c>
       <c r="H192" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" ht="28" customHeight="1">
@@ -13006,17 +13454,17 @@
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>F13-06</t>
+          <t>F13-04</t>
         </is>
       </c>
       <c r="D193" s="27" t="inlineStr">
         <is>
-          <t>系统集成</t>
+          <t>自动对冲</t>
         </is>
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
         </is>
       </c>
       <c r="F193" s="11" t="inlineStr">
@@ -13033,91 +13481,91 @@
         <v>25</v>
       </c>
     </row>
-    <row r="194" ht="20" customHeight="1">
-      <c r="A194" s="29" t="inlineStr">
+    <row r="194" ht="28" customHeight="1">
+      <c r="A194" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B194" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="D194" s="27" t="inlineStr">
+        <is>
+          <t>通知与确认文件</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="F194" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G194" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H194" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="195" ht="28" customHeight="1">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B195" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C195" s="10" t="inlineStr">
+        <is>
+          <t>F13-06</t>
+        </is>
+      </c>
+      <c r="D195" s="27" t="inlineStr">
+        <is>
+          <t>系统集成</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
+        </is>
+      </c>
+      <c r="F195" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G195" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H195" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
-      </c>
-    </row>
-    <row r="195" ht="28" customHeight="1">
-      <c r="A195" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B195" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C195" s="15" t="inlineStr">
-        <is>
-          <t>F15-01</t>
-        </is>
-      </c>
-      <c r="D195" s="30" t="inlineStr">
-        <is>
-          <t>双边报价引擎</t>
-        </is>
-      </c>
-      <c r="E195" s="16" t="inlineStr">
-        <is>
-          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
-        </is>
-      </c>
-      <c r="F195" s="16" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G195" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H195" s="18" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="196" ht="28" customHeight="1">
-      <c r="A196" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B196" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C196" s="15" t="inlineStr">
-        <is>
-          <t>F15-02</t>
-        </is>
-      </c>
-      <c r="D196" s="30" t="inlineStr">
-        <is>
-          <t>库存风险实时管理</t>
-        </is>
-      </c>
-      <c r="E196" s="16" t="inlineStr">
-        <is>
-          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
-        </is>
-      </c>
-      <c r="F196" s="16" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G196" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H196" s="18" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="197" ht="28" customHeight="1">
@@ -13133,17 +13581,17 @@
       </c>
       <c r="C197" s="15" t="inlineStr">
         <is>
-          <t>F15-03</t>
+          <t>F15-01</t>
         </is>
       </c>
       <c r="D197" s="30" t="inlineStr">
         <is>
-          <t>报价优化算法</t>
+          <t>双边报价引擎</t>
         </is>
       </c>
       <c r="E197" s="16" t="inlineStr">
         <is>
-          <t>基于市场微结构理论动态调整bid-ask spread</t>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
         </is>
       </c>
       <c r="F197" s="16" t="inlineStr">
@@ -13157,7 +13605,7 @@
         </is>
       </c>
       <c r="H197" s="18" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="198" ht="28" customHeight="1">
@@ -13173,31 +13621,31 @@
       </c>
       <c r="C198" s="15" t="inlineStr">
         <is>
-          <t>F15-04</t>
+          <t>F15-02</t>
         </is>
       </c>
       <c r="D198" s="30" t="inlineStr">
         <is>
-          <t>竞争力分析</t>
+          <t>库存风险实时管理</t>
         </is>
       </c>
       <c r="E198" s="16" t="inlineStr">
         <is>
-          <t>与市场最优报价对比，中签率分析，策略调优</t>
+          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
         </is>
       </c>
       <c r="F198" s="16" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G198" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G198" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H198" s="18" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="199" ht="28" customHeight="1">
@@ -13213,58 +13661,138 @@
       </c>
       <c r="C199" s="15" t="inlineStr">
         <is>
+          <t>F15-03</t>
+        </is>
+      </c>
+      <c r="D199" s="30" t="inlineStr">
+        <is>
+          <t>报价优化算法</t>
+        </is>
+      </c>
+      <c r="E199" s="16" t="inlineStr">
+        <is>
+          <t>基于市场微结构理论动态调整bid-ask spread</t>
+        </is>
+      </c>
+      <c r="F199" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G199" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H199" s="18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="200" ht="28" customHeight="1">
+      <c r="A200" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B200" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C200" s="15" t="inlineStr">
+        <is>
+          <t>F15-04</t>
+        </is>
+      </c>
+      <c r="D200" s="30" t="inlineStr">
+        <is>
+          <t>竞争力分析</t>
+        </is>
+      </c>
+      <c r="E200" s="16" t="inlineStr">
+        <is>
+          <t>与市场最优报价对比，中签率分析，策略调优</t>
+        </is>
+      </c>
+      <c r="F200" s="16" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G200" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H200" s="18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="201" ht="28" customHeight="1">
+      <c r="A201" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B201" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C201" s="15" t="inlineStr">
+        <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D199" s="30" t="inlineStr">
+      <c r="D201" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E199" s="16" t="inlineStr">
+      <c r="E201" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F199" s="16" t="inlineStr">
+      <c r="F201" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G199" s="24" t="inlineStr">
+      <c r="G201" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H199" s="18" t="n">
+      <c r="H201" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="19" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H200" s="20">
-        <f>SUM(H3:H199)</f>
+      <c r="H202" s="20">
+        <f>SUM(H3:H201)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A202:G202"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A101:H101"/>
     <mergeCell ref="A130:H130"/>
     <mergeCell ref="A180:H180"/>
-    <mergeCell ref="A187:H187"/>
-    <mergeCell ref="A200:G200"/>
+    <mergeCell ref="A196:H196"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A112:H112"/>
     <mergeCell ref="A68:H68"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A194:H194"/>
+    <mergeCell ref="A189:H189"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A159:H159"/>
     <mergeCell ref="A88:H88"/>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -23,6 +23,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_销售交易" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_信用债_信用衍生品" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_投顾服务" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_TRS收益互换" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1797,21 +1798,21 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>现券交易系统/IBOR</t>
+          <t>现券交易系统/IBOR/定价平台</t>
         </is>
       </c>
       <c r="M15" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>场外衍生品主经纪商客需服务，覆盖TRS交易端/客户端/管理端及自动对冲；对应PPT Slide 49</t>
+          <t>场外衍生品主经纪商客需服务，三端架构（交易端/客户端/管理端），自动对冲与运营一体化；对应PPT Slide 49</t>
         </is>
       </c>
     </row>
@@ -6202,13 +6203,544 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：TRS收益互换  |  Total Return Swap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：场外衍生品主经纪商客需服务，三端架构（交易端/客户端/管理端），自动对冲与运营一体化；对应PPT Slide 49   |   来源：Slide 49</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：TRS收益互换  (Total Return Swap)  |  优先级：P2  |  竞品：衡泰/森浦(STC)  |  华锐基础：现券交易系统/IBOR/定价平台  |  工期：6月  团队：6人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. TRS交易端（内部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>D1. TRS交易端（内部）</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>报价与成交管理</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>一站式报价（市场各渠道 + 内部自营），成交回报处理，请求报价（RFQ），历史确认查询</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>D1. TRS交易端（内部）</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>F13-02</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>自动对冲</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置，对冲策略配置</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>D1. TRS交易端（内部）</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>F13-03</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>行情与资讯</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>实时行情矩阵展示，债券行情，我的关注，历史行情，资讯推送</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr"/>
+      <c r="G8" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>D2. TRS客户端（外部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>D2. TRS客户端（外部）</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>F13-04</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>开户与账户管理</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>客户开户申请，账户信息管理，出入金申请，银行账号绑定，资金管理</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr"/>
+      <c r="F10" s="11" t="inlineStr"/>
+      <c r="G10" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr"/>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>D2. TRS客户端（外部）</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>F13-05</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>客户自主交易</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>客户委托下单，合约持仓查询，标的持仓查询，当日委托，行情矩阵，历史确认，开平仓设置</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>D3. TRS管理端（运营）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>D3. TRS管理端（运营）</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>F13-06</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>审批管理</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>开户申请审批，出入金审批，合约成交审核，多级审批工作流，审批留痕</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr"/>
+      <c r="G13" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>D3. TRS管理端（运营）</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>F13-07</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>运营管理</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>对账，库存管理，对冲录入，合约生命周期管理，日终结算处理</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr"/>
+      <c r="F14" s="11" t="inlineStr"/>
+      <c r="G14" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>D3. TRS管理端（运营）</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>F13-08</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>通知与文件生成</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>D4. 系统集成</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>D4. 系统集成</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>F13-09</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>外部系统集成</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>衡泰系统客户信息同步，QTrade聊天记录同步，银行流水对接，公司邮箱系统集成</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr"/>
+      <c r="F17" s="11" t="inlineStr"/>
+      <c r="G17" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>D4. 系统集成</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>F13-10</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>内部系统集成</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>现券交易系统（对冲交易执行），IBOR（持仓记录），定价平台（估值报告），事前风控（合规校验）</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr"/>
+      <c r="F18" s="11" t="inlineStr"/>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>合计 10项功能  |  P1: 0项  |  P2: 10项</t>
+        </is>
+      </c>
+      <c r="H19" s="20">
+        <f>SUM(H5:H18)</f>
+        <v/>
+      </c>
+      <c r="I19" s="34" t="inlineStr"/>
+      <c r="J19" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A19:G19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -13339,12 +13871,12 @@
       </c>
       <c r="D190" s="27" t="inlineStr">
         <is>
-          <t>TRS交易端</t>
+          <t>报价与成交管理</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
         <is>
-          <t>报价提供，成交回报，对冲委托与自动对冲，请求报价，行情与资讯，历史确认</t>
+          <t>一站式报价（市场各渠道 + 内部自营），成交回报处理，请求报价（RFQ），历史确认查询</t>
         </is>
       </c>
       <c r="F190" s="11" t="inlineStr">
@@ -13379,12 +13911,12 @@
       </c>
       <c r="D191" s="27" t="inlineStr">
         <is>
-          <t>TRS客户端</t>
+          <t>自动对冲</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>开户申请，客户委托，出入金申请，合约持仓，标的持仓，资金管理，行情矩阵，自主下单</t>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置，对冲策略配置</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr">
@@ -13398,7 +13930,7 @@
         </is>
       </c>
       <c r="H191" s="13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="192" ht="28" customHeight="1">
@@ -13419,12 +13951,12 @@
       </c>
       <c r="D192" s="27" t="inlineStr">
         <is>
-          <t>TRS管理端</t>
+          <t>行情与资讯</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，合约成交管理，出入金审批，运营管理，对账，库存，对冲录入</t>
+          <t>实时行情矩阵展示，债券行情，我的关注，历史行情，资讯推送</t>
         </is>
       </c>
       <c r="F192" s="11" t="inlineStr">
@@ -13438,7 +13970,7 @@
         </is>
       </c>
       <c r="H192" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193" ht="28" customHeight="1">
@@ -13459,26 +13991,26 @@
       </c>
       <c r="D193" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>开户与账户管理</t>
         </is>
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置</t>
+          <t>客户开户申请，账户信息管理，出入金申请，银行账号绑定，资金管理</t>
         </is>
       </c>
       <c r="F193" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G193" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G193" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H193" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194" ht="28" customHeight="1">
@@ -13499,26 +14031,26 @@
       </c>
       <c r="D194" s="27" t="inlineStr">
         <is>
-          <t>通知与确认文件</t>
+          <t>客户自主交易</t>
         </is>
       </c>
       <c r="E194" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>客户委托下单，合约持仓查询，标的持仓查询，当日委托，行情矩阵，历史确认，开平仓设置</t>
         </is>
       </c>
       <c r="F194" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G194" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G194" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H194" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="195" ht="28" customHeight="1">
@@ -13539,193 +14071,193 @@
       </c>
       <c r="D195" s="27" t="inlineStr">
         <is>
-          <t>系统集成</t>
+          <t>审批管理</t>
         </is>
       </c>
       <c r="E195" s="11" t="inlineStr">
         <is>
-          <t>与衡泰系统客户信息同步，QTrade聊天记录同步，交易管理系统对接，银行流水对接</t>
+          <t>开户申请审批，出入金审批，合约成交审核，多级审批工作流，审批留痕</t>
         </is>
       </c>
       <c r="F195" s="11" t="inlineStr">
         <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G195" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H195" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="196" ht="28" customHeight="1">
+      <c r="A196" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B196" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C196" s="10" t="inlineStr">
+        <is>
+          <t>F13-07</t>
+        </is>
+      </c>
+      <c r="D196" s="27" t="inlineStr">
+        <is>
+          <t>运营管理</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="inlineStr">
+        <is>
+          <t>对账，库存管理，对冲录入，合约生命周期管理，日终结算处理</t>
+        </is>
+      </c>
+      <c r="F196" s="11" t="inlineStr">
+        <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G195" s="23" t="inlineStr">
+      <c r="G196" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H195" s="13" t="n">
+      <c r="H196" s="13" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="196" ht="20" customHeight="1">
-      <c r="A196" s="29" t="inlineStr">
+    <row r="197" ht="28" customHeight="1">
+      <c r="A197" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B197" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C197" s="10" t="inlineStr">
+        <is>
+          <t>F13-08</t>
+        </is>
+      </c>
+      <c r="D197" s="27" t="inlineStr">
+        <is>
+          <t>通知与文件生成</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="inlineStr">
+        <is>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+        </is>
+      </c>
+      <c r="F197" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G197" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H197" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" ht="28" customHeight="1">
+      <c r="A198" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B198" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C198" s="10" t="inlineStr">
+        <is>
+          <t>F13-09</t>
+        </is>
+      </c>
+      <c r="D198" s="27" t="inlineStr">
+        <is>
+          <t>外部系统集成</t>
+        </is>
+      </c>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>衡泰系统客户信息同步，QTrade聊天记录同步，银行流水对接，公司邮箱系统集成</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G198" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H198" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" ht="28" customHeight="1">
+      <c r="A199" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B199" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C199" s="10" t="inlineStr">
+        <is>
+          <t>F13-10</t>
+        </is>
+      </c>
+      <c r="D199" s="27" t="inlineStr">
+        <is>
+          <t>内部系统集成</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>现券交易系统（对冲交易执行），IBOR（持仓记录），定价平台（估值报告），事前风控（合规校验）</t>
+        </is>
+      </c>
+      <c r="F199" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G199" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H199" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
-      </c>
-    </row>
-    <row r="197" ht="28" customHeight="1">
-      <c r="A197" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B197" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C197" s="15" t="inlineStr">
-        <is>
-          <t>F15-01</t>
-        </is>
-      </c>
-      <c r="D197" s="30" t="inlineStr">
-        <is>
-          <t>双边报价引擎</t>
-        </is>
-      </c>
-      <c r="E197" s="16" t="inlineStr">
-        <is>
-          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
-        </is>
-      </c>
-      <c r="F197" s="16" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G197" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H197" s="18" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="198" ht="28" customHeight="1">
-      <c r="A198" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B198" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C198" s="15" t="inlineStr">
-        <is>
-          <t>F15-02</t>
-        </is>
-      </c>
-      <c r="D198" s="30" t="inlineStr">
-        <is>
-          <t>库存风险实时管理</t>
-        </is>
-      </c>
-      <c r="E198" s="16" t="inlineStr">
-        <is>
-          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
-        </is>
-      </c>
-      <c r="F198" s="16" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G198" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H198" s="18" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="199" ht="28" customHeight="1">
-      <c r="A199" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B199" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C199" s="15" t="inlineStr">
-        <is>
-          <t>F15-03</t>
-        </is>
-      </c>
-      <c r="D199" s="30" t="inlineStr">
-        <is>
-          <t>报价优化算法</t>
-        </is>
-      </c>
-      <c r="E199" s="16" t="inlineStr">
-        <is>
-          <t>基于市场微结构理论动态调整bid-ask spread</t>
-        </is>
-      </c>
-      <c r="F199" s="16" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G199" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H199" s="18" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="200" ht="28" customHeight="1">
-      <c r="A200" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B200" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C200" s="15" t="inlineStr">
-        <is>
-          <t>F15-04</t>
-        </is>
-      </c>
-      <c r="D200" s="30" t="inlineStr">
-        <is>
-          <t>竞争力分析</t>
-        </is>
-      </c>
-      <c r="E200" s="16" t="inlineStr">
-        <is>
-          <t>与市场最优报价对比，中签率分析，策略调优</t>
-        </is>
-      </c>
-      <c r="F200" s="16" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G200" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H200" s="18" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="201" ht="28" customHeight="1">
@@ -13741,53 +14273,213 @@
       </c>
       <c r="C201" s="15" t="inlineStr">
         <is>
+          <t>F15-01</t>
+        </is>
+      </c>
+      <c r="D201" s="30" t="inlineStr">
+        <is>
+          <t>双边报价引擎</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="inlineStr">
+        <is>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
+        </is>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G201" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H201" s="18" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="202" ht="28" customHeight="1">
+      <c r="A202" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B202" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C202" s="15" t="inlineStr">
+        <is>
+          <t>F15-02</t>
+        </is>
+      </c>
+      <c r="D202" s="30" t="inlineStr">
+        <is>
+          <t>库存风险实时管理</t>
+        </is>
+      </c>
+      <c r="E202" s="16" t="inlineStr">
+        <is>
+          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
+        </is>
+      </c>
+      <c r="F202" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G202" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H202" s="18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="203" ht="28" customHeight="1">
+      <c r="A203" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B203" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C203" s="15" t="inlineStr">
+        <is>
+          <t>F15-03</t>
+        </is>
+      </c>
+      <c r="D203" s="30" t="inlineStr">
+        <is>
+          <t>报价优化算法</t>
+        </is>
+      </c>
+      <c r="E203" s="16" t="inlineStr">
+        <is>
+          <t>基于市场微结构理论动态调整bid-ask spread</t>
+        </is>
+      </c>
+      <c r="F203" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G203" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H203" s="18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="204" ht="28" customHeight="1">
+      <c r="A204" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B204" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C204" s="15" t="inlineStr">
+        <is>
+          <t>F15-04</t>
+        </is>
+      </c>
+      <c r="D204" s="30" t="inlineStr">
+        <is>
+          <t>竞争力分析</t>
+        </is>
+      </c>
+      <c r="E204" s="16" t="inlineStr">
+        <is>
+          <t>与市场最优报价对比，中签率分析，策略调优</t>
+        </is>
+      </c>
+      <c r="F204" s="16" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G204" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H204" s="18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" ht="28" customHeight="1">
+      <c r="A205" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B205" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C205" s="15" t="inlineStr">
+        <is>
           <t>F15-05</t>
         </is>
       </c>
-      <c r="D201" s="30" t="inlineStr">
+      <c r="D205" s="30" t="inlineStr">
         <is>
           <t>交易对手管理集成</t>
         </is>
       </c>
-      <c r="E201" s="16" t="inlineStr">
+      <c r="E205" s="16" t="inlineStr">
         <is>
           <t>做市交易对手信用实时检查，额度占用同步更新</t>
         </is>
       </c>
-      <c r="F201" s="16" t="inlineStr">
+      <c r="F205" s="16" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G201" s="24" t="inlineStr">
+      <c r="G205" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H201" s="18" t="n">
+      <c r="H205" s="18" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="19" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H202" s="20">
-        <f>SUM(H3:H201)</f>
+      <c r="H206" s="20">
+        <f>SUM(H3:H205)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A143:H143"/>
-    <mergeCell ref="A202:G202"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A101:H101"/>
     <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A200:H200"/>
     <mergeCell ref="A180:H180"/>
-    <mergeCell ref="A196:H196"/>
+    <mergeCell ref="A206:G206"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A112:H112"/>
     <mergeCell ref="A68:H68"/>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_信用债_信用衍生品" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_投顾服务" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_TRS收益互换" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="详情_做市商系统" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'差距分析总表'!$A$1:$P$17</definedName>
@@ -1876,17 +1877,17 @@
         </is>
       </c>
       <c r="M16" s="15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N16" s="15" t="n">
         <v>12</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="P16" s="16" t="inlineStr">
         <is>
-          <t>双边报价引擎，需深度市场经验</t>
+          <t>双边报价引擎，做市义务监控，报价策略自动优化，支持双边/TRS/RFQ/API四种做市模式；对应PPT Slide 53-54</t>
         </is>
       </c>
     </row>
@@ -6734,13 +6735,620 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>系统详情：做市商系统  |  Market Making</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>战略定位：双边报价引擎，做市义务监控，报价策略自动优化，支持双边/TRS/RFQ/API四种做市模式；对应PPT Slide 53-54   |   来源：Slide 53</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>模块：做市商系统  (Market Making)  |  优先级：P3  |  竞品：Murex/专项  |  华锐基础：ATP报价接口  |  工期：14月  团队：12人</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>功能域</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>功能名称</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能描述</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>验收标准</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>集成依赖</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>复杂度</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>预估(人天)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>D1. 做市模式管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>D1. 做市模式管理</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>F15-01</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>双边报价做市</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化，支持国债/信用债/利率互换多品种做市</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr"/>
+      <c r="F6" s="11" t="inlineStr"/>
+      <c r="G6" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>D1. 做市模式管理</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>F15-02</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>TRS做市服务</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>TRS产品双边报价，与TRS收益互换系统深度集成，对冲报价敞口，支持客户TRS交易</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+      <c r="F7" s="11" t="inlineStr"/>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>D1. 做市模式管理</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>F15-03</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>RFQ询价响应</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>接收客户询价请求，自动生成报价，报价有效期管理，成交确认，询价历史记录</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr"/>
+      <c r="F8" s="11" t="inlineStr"/>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr"/>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>D1. 做市模式管理</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>F15-04</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>API程序化做市</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>对外提供做市API接口，支持程序化交易对手接入，流式报价推送，API鉴权与频率限制</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr"/>
+      <c r="F9" s="11" t="inlineStr"/>
+      <c r="G9" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>D2. 报价策略管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>D2. 报价策略管理</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>F15-05</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>报价策略配置</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>各品种做市参数配置（报价宽度/报价量/报价频率），分时段策略，按交易对手差异化报价</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr"/>
+      <c r="F11" s="11" t="inlineStr"/>
+      <c r="G11" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>D2. 报价策略管理</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>F15-06</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>报价优化算法</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>基于市场微结构理论动态调整bid-ask spread，流动性自适应调节，机器学习辅助报价优化</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>D2. 报价策略管理</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>F15-07</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>债券过滤与筛选</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>做市标的券池管理，流动性分级筛选，黑名单管理，临时暂停做市规则</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr"/>
+      <c r="F13" s="11" t="inlineStr"/>
+      <c r="G13" s="42" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>D3. 做市义务监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>D3. 做市义务监控</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>F15-08</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>做市义务实时监控</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>实时监控做市义务完成情况（报价连续性/报价宽度/报价量达标），义务违规预警，监管报告生成</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>D3. 做市义务监控</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>F15-09</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>做市行情展示</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>做市报价行情矩阵，实时价格展示，报价历史回放，市场最优报价对比，中签率统计</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr"/>
+      <c r="F16" s="11" t="inlineStr"/>
+      <c r="G16" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>D4. 订单与风险管理</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>D4. 订单与风险管理</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>F15-10</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>做市订单管理</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>做市委托生成、撤改、成交回报处理，订单状态实时跟踪，批量撤单，做市台账</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr"/>
+      <c r="F18" s="11" t="inlineStr"/>
+      <c r="G18" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>D4. 订单与风险管理</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>F15-11</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>库存风险实时管理</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>做市库存PnL实时监控，Delta对冲自动触发，库存敞口上限控制，实时盯市损益</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr"/>
+      <c r="F19" s="11" t="inlineStr"/>
+      <c r="G19" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>D4. 订单与风险管理</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>F15-12</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>竞争力分析</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>与市场最优报价对比，中签率分析，报价表现统计，策略调优建议，竞争对手报价分析</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr"/>
+      <c r="F20" s="11" t="inlineStr"/>
+      <c r="G20" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>合计 12项功能  |  P1: 0项  |  P2: 12项</t>
+        </is>
+      </c>
+      <c r="H21" s="20">
+        <f>SUM(H5:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="34" t="inlineStr"/>
+      <c r="J21" s="34" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A10:J10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14278,12 +14886,12 @@
       </c>
       <c r="D201" s="30" t="inlineStr">
         <is>
-          <t>双边报价引擎</t>
+          <t>双边报价做市</t>
         </is>
       </c>
       <c r="E201" s="16" t="inlineStr">
         <is>
-          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化</t>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化，支持国债/信用债/利率互换多品种做市</t>
         </is>
       </c>
       <c r="F201" s="16" t="inlineStr">
@@ -14318,12 +14926,12 @@
       </c>
       <c r="D202" s="30" t="inlineStr">
         <is>
-          <t>库存风险实时管理</t>
+          <t>TRS做市服务</t>
         </is>
       </c>
       <c r="E202" s="16" t="inlineStr">
         <is>
-          <t>做市库存PnL实时监控，Delta对冲自动触发</t>
+          <t>TRS产品双边报价，与TRS收益互换系统深度集成，对冲报价敞口，支持客户TRS交易</t>
         </is>
       </c>
       <c r="F202" s="16" t="inlineStr">
@@ -14337,7 +14945,7 @@
         </is>
       </c>
       <c r="H202" s="18" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="203" ht="28" customHeight="1">
@@ -14358,26 +14966,26 @@
       </c>
       <c r="D203" s="30" t="inlineStr">
         <is>
-          <t>报价优化算法</t>
+          <t>RFQ询价响应</t>
         </is>
       </c>
       <c r="E203" s="16" t="inlineStr">
         <is>
-          <t>基于市场微结构理论动态调整bid-ask spread</t>
+          <t>接收客户询价请求，自动生成报价，报价有效期管理，成交确认，询价历史记录</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G203" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G203" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H203" s="18" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="204" ht="28" customHeight="1">
@@ -14398,12 +15006,12 @@
       </c>
       <c r="D204" s="30" t="inlineStr">
         <is>
-          <t>竞争力分析</t>
+          <t>API程序化做市</t>
         </is>
       </c>
       <c r="E204" s="16" t="inlineStr">
         <is>
-          <t>与市场最优报价对比，中签率分析，策略调优</t>
+          <t>对外提供做市API接口，支持程序化交易对手接入，流式报价推送，API鉴权与频率限制</t>
         </is>
       </c>
       <c r="F204" s="16" t="inlineStr">
@@ -14438,12 +15046,12 @@
       </c>
       <c r="D205" s="30" t="inlineStr">
         <is>
-          <t>交易对手管理集成</t>
+          <t>报价策略配置</t>
         </is>
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>做市交易对手信用实时检查，额度占用同步更新</t>
+          <t>各品种做市参数配置（报价宽度/报价量/报价频率），分时段策略，按交易对手差异化报价</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
@@ -14460,14 +15068,294 @@
         <v>20</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="19" t="inlineStr">
+    <row r="206" ht="28" customHeight="1">
+      <c r="A206" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B206" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C206" s="15" t="inlineStr">
+        <is>
+          <t>F15-06</t>
+        </is>
+      </c>
+      <c r="D206" s="30" t="inlineStr">
+        <is>
+          <t>报价优化算法</t>
+        </is>
+      </c>
+      <c r="E206" s="16" t="inlineStr">
+        <is>
+          <t>基于市场微结构理论动态调整bid-ask spread，流动性自适应调节，机器学习辅助报价优化</t>
+        </is>
+      </c>
+      <c r="F206" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G206" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H206" s="18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="207" ht="28" customHeight="1">
+      <c r="A207" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B207" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C207" s="15" t="inlineStr">
+        <is>
+          <t>F15-07</t>
+        </is>
+      </c>
+      <c r="D207" s="30" t="inlineStr">
+        <is>
+          <t>债券过滤与筛选</t>
+        </is>
+      </c>
+      <c r="E207" s="16" t="inlineStr">
+        <is>
+          <t>做市标的券池管理，流动性分级筛选，黑名单管理，临时暂停做市规则</t>
+        </is>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G207" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H207" s="18" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="208" ht="28" customHeight="1">
+      <c r="A208" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B208" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C208" s="15" t="inlineStr">
+        <is>
+          <t>F15-08</t>
+        </is>
+      </c>
+      <c r="D208" s="30" t="inlineStr">
+        <is>
+          <t>做市义务实时监控</t>
+        </is>
+      </c>
+      <c r="E208" s="16" t="inlineStr">
+        <is>
+          <t>实时监控做市义务完成情况（报价连续性/报价宽度/报价量达标），义务违规预警，监管报告生成</t>
+        </is>
+      </c>
+      <c r="F208" s="16" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G208" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H208" s="18" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="209" ht="28" customHeight="1">
+      <c r="A209" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B209" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C209" s="15" t="inlineStr">
+        <is>
+          <t>F15-09</t>
+        </is>
+      </c>
+      <c r="D209" s="30" t="inlineStr">
+        <is>
+          <t>做市行情展示</t>
+        </is>
+      </c>
+      <c r="E209" s="16" t="inlineStr">
+        <is>
+          <t>做市报价行情矩阵，实时价格展示，报价历史回放，市场最优报价对比，中签率统计</t>
+        </is>
+      </c>
+      <c r="F209" s="16" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G209" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H209" s="18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="210" ht="28" customHeight="1">
+      <c r="A210" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B210" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C210" s="15" t="inlineStr">
+        <is>
+          <t>F15-10</t>
+        </is>
+      </c>
+      <c r="D210" s="30" t="inlineStr">
+        <is>
+          <t>做市订单管理</t>
+        </is>
+      </c>
+      <c r="E210" s="16" t="inlineStr">
+        <is>
+          <t>做市委托生成、撤改、成交回报处理，订单状态实时跟踪，批量撤单，做市台账</t>
+        </is>
+      </c>
+      <c r="F210" s="16" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G210" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H210" s="18" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" ht="28" customHeight="1">
+      <c r="A211" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B211" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C211" s="15" t="inlineStr">
+        <is>
+          <t>F15-11</t>
+        </is>
+      </c>
+      <c r="D211" s="30" t="inlineStr">
+        <is>
+          <t>库存风险实时管理</t>
+        </is>
+      </c>
+      <c r="E211" s="16" t="inlineStr">
+        <is>
+          <t>做市库存PnL实时监控，Delta对冲自动触发，库存敞口上限控制，实时盯市损益</t>
+        </is>
+      </c>
+      <c r="F211" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G211" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H211" s="18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="212" ht="28" customHeight="1">
+      <c r="A212" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B212" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C212" s="15" t="inlineStr">
+        <is>
+          <t>F15-12</t>
+        </is>
+      </c>
+      <c r="D212" s="30" t="inlineStr">
+        <is>
+          <t>竞争力分析</t>
+        </is>
+      </c>
+      <c r="E212" s="16" t="inlineStr">
+        <is>
+          <t>与市场最优报价对比，中签率分析，报价表现统计，策略调优建议，竞争对手报价分析</t>
+        </is>
+      </c>
+      <c r="F212" s="16" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G212" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H212" s="18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H206" s="20">
-        <f>SUM(H3:H205)</f>
+      <c r="H213" s="20">
+        <f>SUM(H3:H212)</f>
         <v/>
       </c>
     </row>
@@ -14477,9 +15365,9 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A101:H101"/>
     <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A213:G213"/>
     <mergeCell ref="A200:H200"/>
     <mergeCell ref="A180:H180"/>
-    <mergeCell ref="A206:G206"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A112:H112"/>
     <mergeCell ref="A68:H68"/>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -1359,17 +1359,17 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
-          <t>17项功能含量化底座集成；Slide44全景展开</t>
+          <t>全资产组合管理驾驶舱，十大核心能力：全资产持仓模型/QP优化/Shadow Portfolio/Campisi 2.0固收归因/Brinson归因/因子风险分解+MCTR/Component VaR/敏感度/情景压测/流动性；对应PPT Slide 44 + gy_solution 4.4.1</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2479,14 +2479,14 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>战略定位：17项功能含量化底座集成；Slide44全景展开   |   来源：Slide 44   |   数据输入：交易数据 / 头寸数据 / 行情数据 / 估值数据   |   量化底座：定价计算 · 利率曲线 · 因子模型</t>
+          <t>战略定位：全资产组合管理驾驶舱，十大核心能力：全资产持仓模型/QP优化/Shadow Portfolio/Campisi 2.0固收归因/Brinson归因/因子风险分解+MCTR/Component VaR/敏感度/情景压测/流动性；对应PPT Slide 44 + gy_solution 4.4.1   |   来源：Slide 44   |   数据输入：交易数据 / 头寸数据 / 行情数据 / 估值数据   |   量化底座：定价计算 · 利率曲线 · 因子模型(2200+风险因子)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="40" t="inlineStr">
         <is>
-          <t>模块：组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)  |  优先级：P1  |  竞品：SimCorp/衡泰  |  华锐基础：M9 PMS模块  |  工期：12月  团队：12人</t>
+          <t>模块：组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)  |  优先级：P1  |  竞品：SimCorp/衡泰  |  华锐基础：M9 PMS模块  |  工期：14月  团队：14人</t>
         </is>
       </c>
     </row>
@@ -2545,14 +2545,14 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>A. 组合分析</t>
+          <t>A. 全资产持仓管理</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>A. 组合分析</t>
+          <t>A. 全资产持仓管理</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2562,22 +2562,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>债券横截面与时序分析</t>
+          <t>全资产统一持仓模型</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
+          <t>八类资产（利率债/信用债/权益/基金/黄金/商品/衍生品/非标）实时T+0持仓，多层组合树（公司→部门→策略→子组合→投资经理），穿透式敞口展示（品种/久期/评级/行业/地区分布），真实组合+Shadow Portfolio并行展示</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>横截面信号与实际收益相关性&gt;0.3</t>
+          <t>T+0持仓实时刷新，穿透层级≥5层，数据与IBOR差异&lt;0.01%</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>AMD行情平台/估值数据</t>
+          <t>IBOR持仓账薄/AMD行情</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="H6" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>A. 组合分析</t>
+          <t>A. 全资产持仓管理</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2608,22 +2608,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>跨资产相关性分析</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+          <t>全持仓跨资产相关矩阵（股/债/商品/衍生品/基金），多窗口滚动（20/60/252日），压力情景相关性vs历史相关性对比，动态相关性漂移预警，分散化比率(Diversification Ratio)计算，低相关候选资产推荐</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+          <t>相关矩阵计算&lt;30s（500券组合），动态漂移预警阈值可配</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>量化定价引擎/AMD行情</t>
+          <t>IBOR头寸/AMD历史行情</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2644,7 +2644,7 @@
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>A. 组合分析</t>
+          <t>A. 全资产持仓管理</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2654,31 +2654,31 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>组合相关度分析</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位（覆盖5年），跨品种套利信号识别，债券横截面信号挖掘（利差/久期偏差），时序均值回归分析</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>相关矩阵计算&lt;30s（500券组合）</t>
+          <t>OAS计算误差&lt;1bps，历史分位数覆盖5年，横截面信号与实际收益相关性&gt;0.3</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>IBOR头寸/AMD历史行情</t>
-        </is>
-      </c>
-      <c r="G8" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>定价平台/AMD行情</t>
+        </is>
+      </c>
+      <c r="G8" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -2690,14 +2690,14 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>B. 风险计量</t>
+          <t>B. 组合优化与再平衡</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>B. 风险计量</t>
+          <t>B. 组合优化与再平衡</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>QP智能再平衡引擎</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+          <t>二次规划多目标优化（最小化跟踪误差+交易摩擦+融资成本+IFRS9波动），500+约束（合规/风险预算/流动性/IFRS9），2000+持仓毫秒级求解，支持整数规划（面值/手数取整），多期优化（含到期券），三种触发（定时/事件/手动），一键生成交易指令</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
+          <t>QP求解2000持仓&lt;200ms，约束满足率100%，调仓前后TE对比即时输出</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台/量化定价引擎</t>
+          <t>事前风控/合规/IBOR/现券系统/定价平台</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="H10" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>B. 风险计量</t>
+          <t>B. 组合优化与再平衡</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2753,22 +2753,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析</t>
+          <t>Shadow Portfolio虚拟试算</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+          <t>100+虚拟组合与真实组合并行运行，多维试算（增减仓/换仓/加杠杆/新资产类别），即时显示试算后风险指标/归因/相关性/预期收益，真实vs虚拟所有指标差异对比视图，冲击成本预估</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%，秒级响应</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>量化定价引擎Greeks接口</t>
+          <t>IBOR/定价平台/现券交易系统</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="H11" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -2787,34 +2787,34 @@
       <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>B. 风险计量</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>B. 组合优化与再平衡</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>F07-06</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>极端事件分析</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>历史情景复现误差&lt;1%</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>FICC风险计量平台</t>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>资产配置策略分析</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>SAA战略→TAA战术精准联动（投委会指令直接转化为因子约束输入QP引擎），宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证（≥5年），固收+策略P&amp;L归因（债券底仓+衍生品增强）</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>回测期≥5年，预测方向胜率&gt;55%，SAA→TAA指令转化全程无人工干预</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>AMD宏观数据/因子模型/IBOR</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2822,15 +2822,15 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H12" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="H12" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="43" t="inlineStr">
@@ -2852,31 +2852,31 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>指数比较分析</t>
+          <t>Campisi 2.0 固收绩效归因</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
+          <t>固定收益五效应完整拆解：①收入效应（票息+摊销），②国债效应（利率平移/曲线斜率/曲率三效应分离，用Key Rate Duration精确映射），③利差效应（DTS贡献/行业配置效应/个券选择效应），④交易效应（择时Alpha或损耗量化），⑤残差校验（&lt;5bp合格）；日/周/月/季多维度报告自动生成</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
+          <t>五效应合计与实际收益残差&lt;5bps，T+1 9:00前自动报告</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>AMD中债估值/IBOR持仓</t>
-        </is>
-      </c>
-      <c r="G14" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>IBOR持仓/AMD行情/定价平台</t>
+        </is>
+      </c>
+      <c r="G14" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>Brinson 资产组合绩效归因</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+          <t>三效应：大类资产配置效应（超/低配决策贡献）/个券选择效应（同类标的选择Alpha）/交互效应，支持多层穿透（资产大类→行业→子行业→个股/个基），FOF基金穿透底层持仓，日/月/季/年累计归因趋势，投资经理能力量化排名</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，穿透层级≥4层</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2922,7 +2922,7 @@
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -2931,63 +2931,63 @@
       </c>
       <c r="J15" s="5" t="inlineStr"/>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>C. 绩效归因</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>F07-09</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>虚拟组合分析</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>IBOR/现券交易系统</t>
-        </is>
-      </c>
-      <c r="G17" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>指数跟踪误差与主动风险归因</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>对标中债综合/信用/政策行等基准指数，跟踪误差（TE）日频监控，TE分解（配置效应TE+选券效应TE+协方差），信息比率（IR）实时监控（目标IR&gt;0.5，预警IR连续3月&lt;0），超额Alpha三因子分解</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数，IR预警自动推送</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>AMD中债估值/IBOR持仓/因子模型</t>
+        </is>
+      </c>
+      <c r="G16" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>D. 风险计量</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>D. 组合优化与再平衡</t>
+          <t>D. 风险计量</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2997,22 +2997,22 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>再平衡方案试算与比较</t>
+          <t>因子风险分解 + MCTR边际风险贡献</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+          <t>全持仓分解为2200+风险因子（利率/信用/权益/商品/汇率），系统性风险+特异性风险分离；MCTR边际风险贡献（∂组合波动率/∂持仓权重），风险消耗排名（识别"风险大户"），减仓/加仓优先级引导，风险预算仪表盘（已用/剩余/预警线三档）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+          <t>因子模型解释方差&gt;80%，MCTR实时更新延迟&lt;5s，Alpha IC均值&gt;0.05</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规/IBOR/现券系统</t>
+          <t>AMD历史行情/IBOR持仓/定价平台</t>
         </is>
       </c>
       <c r="G18" s="41" t="inlineStr">
@@ -3021,164 +3021,164 @@
         </is>
       </c>
       <c r="H18" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>D. 风险计量</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>F07-11</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Component VaR 四层穿透分析</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>VaR四层穿透：资产类别VaR→行业/子市场VaR→评级/信用质量VaR→单一发行人Component VaR，含跨类分散化收益量化；三种方法互验（历史模拟500日99%置信度/Monte Carlo 10000次/参数解析法），方法差异超阈值自动预警</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>三方法VaR差异&lt;10%，穿透至发行人层，全量计算&lt;1min</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台/定价平台/IBOR</t>
+        </is>
+      </c>
+      <c r="G19" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>F07-11</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>资产配置策略分析</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>AMD宏观数据/因子模型</t>
-        </is>
-      </c>
-      <c r="G19" s="41" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>D. 风险计量</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>F07-12</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>敏感度分析（多维Shock Grid）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>利率敏感度（DV01/关键期限点KRD/凸性），信用敏感度（CS01/DTS分评级/分行业），权益敏感度（Delta/Beta/行业Beta），商品汇率敏感度；利率×信用利差二维冲击矩阵（Shock Grid），识别最脆弱组合方向，对冲比率建议</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps，Shock Grid 5×5矩阵实时刷新</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>定价平台Greeks接口/IBOR</t>
+        </is>
+      </c>
+      <c r="G20" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H19" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="I19" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>F07-12</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>固收+策略分析</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>IBOR/利率衍生品系统</t>
-        </is>
-      </c>
-      <c r="G20" s="41" t="inlineStr">
+      <c r="H20" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>D. 风险计量</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>F07-13</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>情景分析与压力测试</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>三层：①历史情景重演（924行情/2019包商/2013钱荒/2015股灾等8+事件，含冲击参数还原），②假设情景模拟（自定义任意冲击组合，即时P&amp;L输出+应急对冲建议），③反向压力测试（倒推触发止损线的临界市场情景+历史发生频率），≥20情景并行</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>历史情景复现误差&lt;1%，情景P&amp;L误差&lt;0.5%，支持≥20情景并行</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台/定价平台</t>
+        </is>
+      </c>
+      <c r="G21" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H20" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>D. 组合优化与再平衡</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>F07-13</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>量化策略组合分析</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>策略容量计算误差&lt;5%</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>策略投资/量化系统</t>
-        </is>
-      </c>
-      <c r="G21" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="I21" s="12" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>E. 流动性管理</t>
+          <t>E. 流动性与对冲管理</t>
         </is>
       </c>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>E. 流动性管理</t>
+          <t>E. 流动性与对冲管理</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -3188,17 +3188,17 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>流动性分析</t>
+          <t>流动性风险管理（LVaR）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+          <t>逐持仓变现能力评估（规模/日均成交量→变现天数），Almgren-Chriss市场冲击成本模型，流动性压力测试（X天内变现Y亿最优路径+成本），流动性调整VaR（LVaR=传统VaR+流动性溢价），流动性覆盖率/缓冲监控（1/3/5/10日分层），回购到期日历</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓，变现路径建议&lt;3s</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3212,113 +3212,113 @@
         </is>
       </c>
       <c r="H23" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>E. 流动性与对冲管理</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>F07-15</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="inlineStr">
+        <is>
+          <t>衍生品对冲决策引擎</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>七类工具矩阵（国债期货2/5/10/30Y/IRS/CDS/股指期货IF/IH/IC/IM/股指期权/黄金期货/外汇远掉期），系统推荐最优对冲方案（成本最小约束），一键生成对冲指令，对冲效果追踪（前后风险指标对比/效率/执行滑点）；支持快速/精细/尾部/跨资产四种场景</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>对冲方案推荐&lt;5s，DV01对冲误差&lt;5%，指令自动流转执行引擎</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>衍生品交易系统/IBOR/定价平台/事前风控</t>
+        </is>
+      </c>
+      <c r="G24" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J24" s="11" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>F07-16</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="inlineStr">
+        <is>
+          <t>定价计算集成</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>调用定价平台实时估值与Greeks（含权债/可转债/IRS），Redis缓存结果，Kafka推送持仓+估值变化事件，日终全量估值批处理</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>定价平台</t>
+        </is>
+      </c>
+      <c r="G26" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="44" t="inlineStr">
-        <is>
-          <t>F. 量化底座集成</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>F. 量化底座集成</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>F07-15</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>定价计算集成</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
-        <is>
-          <t>量化定价引擎</t>
-        </is>
-      </c>
-      <c r="G25" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr"/>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>F. 量化底座集成</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>F07-16</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>利率曲线集成</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>AMD行情平台/量化定价引擎</t>
-        </is>
-      </c>
-      <c r="G26" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr"/>
+      <c r="J26" s="11" t="inlineStr"/>
     </row>
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -3333,63 +3333,109 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），关键期限点敏感度映射，曲线版本快照（供归因历史复现）</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>AMD行情平台/定价平台</t>
+        </is>
+      </c>
+      <c r="G27" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>F. 量化底座集成</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>F07-18</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
           <t>因子模型</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（2200+风险因子：利率/信用/流动性/权益Beta/行业/风格/商品/汇率），Alpha因子库（≥20因子，IC均值&gt;0.05），因子暴露实时计算与历史追踪，因子风险贡献预算管理</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>因子模型解释方差&gt;80%，因子暴露更新延迟&lt;10s</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>AMD历史行情/IBOR持仓</t>
         </is>
       </c>
-      <c r="G27" s="41" t="inlineStr">
+      <c r="G28" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H28" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="40" t="inlineStr">
-        <is>
-          <t>合计 17项功能  |  P1: 13项  |  P2: 4项</t>
-        </is>
-      </c>
-      <c r="H28" s="20">
-        <f>SUM(H5:H27)</f>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>合计 18项功能  |  P1: 15项  |  P2: 3项</t>
+        </is>
+      </c>
+      <c r="H29" s="20">
+        <f>SUM(H5:H28)</f>
         <v/>
       </c>
-      <c r="I28" s="34" t="inlineStr"/>
-      <c r="J28" s="34" t="inlineStr"/>
+      <c r="I29" s="34" t="inlineStr"/>
+      <c r="J29" s="34" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A25:J25"/>
     <mergeCell ref="A13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7348,7 +7394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:H214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7435,7 +7481,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>跨资产实时头寸</t>
+          <t>全资产实时头寸</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11597,17 +11643,17 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>债券横截面与时序分析</t>
+          <t>全资产统一持仓模型</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>跨品种横截面信号挖掘（利差/久期偏差），历史时序趋势与均值回归分析</t>
+          <t>八类资产（利率债/信用债/权益/基金/黄金/商品/衍生品/非标）实时T+0持仓，多层组合树（公司→部门→策略→子组合→投资经理），穿透式敞口展示（品种/久期/评级/行业/地区分布），真实组合+Shadow Portfolio并行展示</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>横截面信号与实际收益相关性&gt;0.3</t>
+          <t>T+0持仓实时刷新，穿透层级≥5层，数据与IBOR差异&lt;0.01%</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11616,7 +11662,7 @@
         </is>
       </c>
       <c r="H113" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
@@ -11637,17 +11683,17 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>跨资产相关性分析</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位，跨品种套利信号识别</t>
+          <t>全持仓跨资产相关矩阵（股/债/商品/衍生品/基金），多窗口滚动（20/60/252日），压力情景相关性vs历史相关性对比，动态相关性漂移预警，分散化比率(Diversification Ratio)计算，低相关候选资产推荐</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，分位数覆盖5年历史</t>
+          <t>相关矩阵计算&lt;30s（500券组合），动态漂移预警阈值可配</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11677,26 +11723,26 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>组合相关度分析</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>资产间收益相关矩阵计算（滚动60/120/250日），组合集中度风险识别，分散化系数监控</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位（覆盖5年），跨品种套利信号识别，债券横截面信号挖掘（利差/久期偏差），时序均值回归分析</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>相关矩阵计算&lt;30s（500券组合）</t>
-        </is>
-      </c>
-      <c r="G115" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>OAS计算误差&lt;1bps，历史分位数覆盖5年，横截面信号与实际收益相关性&gt;0.3</t>
+        </is>
+      </c>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" ht="28" customHeight="1">
@@ -11717,17 +11763,17 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>情景分析</t>
+          <t>QP智能再平衡引擎</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>利率/信用/流动性三类自定义情景，组合P&amp;L影响量化，多情景并行对比</t>
+          <t>二次规划多目标优化（最小化跟踪误差+交易摩擦+融资成本+IFRS9波动），500+约束（合规/风险预算/流动性/IFRS9），2000+持仓毫秒级求解，支持整数规划（面值/手数取整），多期优化（含到期券），三种触发（定时/事件/手动），一键生成交易指令</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>情景P&amp;L与手工核算误差&lt;0.5%，支持≥20情景并行</t>
+          <t>QP求解2000持仓&lt;200ms，约束满足率100%，调仓前后TE对比即时输出</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11736,7 +11782,7 @@
         </is>
       </c>
       <c r="H116" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117" ht="28" customHeight="1">
@@ -11757,17 +11803,17 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析</t>
+          <t>Shadow Portfolio虚拟试算</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>久期/DV01/凸度/利差/Vega敏感度多因子并行计算，组合对冲比率建议</t>
+          <t>100+虚拟组合与真实组合并行运行，多维试算（增减仓/换仓/加杠杆/新资产类别），即时显示试算后风险指标/归因/相关性/预期收益，真实vs虚拟所有指标差异对比视图，冲击成本预估</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%，秒级响应</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11776,7 +11822,7 @@
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1">
@@ -11797,17 +11843,17 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>极端事件分析</t>
+          <t>资产配置策略分析</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>历史极端情景（924行情/2015股灾/2020疫情等8+情景），组合尾部损失分布，ES(99%)计算</t>
+          <t>SAA战略→TAA战术精准联动（投委会指令直接转化为因子约束输入QP引擎），宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证（≥5年），固收+策略P&amp;L归因（债券底仓+衍生品增强）</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%</t>
+          <t>回测期≥5年，预测方向胜率&gt;55%，SAA→TAA指令转化全程无人工干预</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11816,7 +11862,7 @@
         </is>
       </c>
       <c r="H118" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="119" ht="28" customHeight="1">
@@ -11837,26 +11883,26 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>指数比较分析</t>
+          <t>Campisi 2.0 固收绩效归因</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行等指数，跟踪误差（TE）日频监控，超额Alpha三因子分解</t>
+          <t>固定收益五效应完整拆解：①收入效应（票息+摊销），②国债效应（利率平移/曲线斜率/曲率三效应分离，用Key Rate Duration精确映射），③利差效应（DTS贡献/行业配置效应/个券选择效应），④交易效应（择时Alpha或损耗量化），⑤残差校验（&lt;5bp合格）；日/周/月/季多维度报告自动生成</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数</t>
-        </is>
-      </c>
-      <c r="G119" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>五效应合计与实际收益残差&lt;5bps，T+1 9:00前自动报告</t>
+        </is>
+      </c>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H119" s="8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1">
@@ -11877,17 +11923,17 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>绩效归因（Brinson）</t>
+          <t>Brinson 资产组合绩效归因</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>BHB三效应：资产配置/个券选择/交互效应，日/周/月/季多维度，报告PDF自动生成</t>
+          <t>三效应：大类资产配置效应（超/低配决策贡献）/个券选择效应（同类标的选择Alpha）/交互效应，支持多层穿透（资产大类→行业→子行业→个股/个基），FOF基金穿透底层持仓，日/月/季/年累计归因趋势，投资经理能力量化排名</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，T+1 9:00前自动报告</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，穿透层级≥4层</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -11896,7 +11942,7 @@
         </is>
       </c>
       <c r="H120" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1">
@@ -11917,26 +11963,26 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>虚拟组合分析</t>
+          <t>指数跟踪误差与主动风险归因</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>组合调整前后净值/风险/收益效果模拟（纸面交易），冲击成本预估，多方案对比</t>
+          <t>对标中债综合/信用/政策行等基准指数，跟踪误差（TE）日频监控，TE分解（配置效应TE+选券效应TE+协方差），信息比率（IR）实时监控（目标IR&gt;0.5，预警IR连续3月&lt;0），超额Alpha三因子分解</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%</t>
-        </is>
-      </c>
-      <c r="G121" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数，IR预警自动推送</t>
+        </is>
+      </c>
+      <c r="G121" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H121" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122" ht="28" customHeight="1">
@@ -11957,17 +12003,17 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>再平衡方案试算与比较</t>
+          <t>因子风险分解 + MCTR边际风险贡献</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>久期/集中度/流动性/合规约束联合优化（二次规划QP），多方案并行试算，最优路径推荐</t>
+          <t>全持仓分解为2200+风险因子（利率/信用/权益/商品/汇率），系统性风险+特异性风险分离；MCTR边际风险贡献（∂组合波动率/∂持仓权重），风险消耗排名（识别"风险大户"），减仓/加仓优先级引导，风险预算仪表盘（已用/剩余/预警线三档）</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>QP求解100券组合&lt;5s，约束满足率100%</t>
+          <t>因子模型解释方差&gt;80%，MCTR实时更新延迟&lt;5s，Alpha IC均值&gt;0.05</t>
         </is>
       </c>
       <c r="G122" s="23" t="inlineStr">
@@ -11976,7 +12022,7 @@
         </is>
       </c>
       <c r="H122" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="123" ht="28" customHeight="1">
@@ -11997,17 +12043,17 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>Component VaR 四层穿透分析</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证</t>
+          <t>VaR四层穿透：资产类别VaR→行业/子市场VaR→评级/信用质量VaR→单一发行人Component VaR，含跨类分散化收益量化；三种方法互验（历史模拟500日99%置信度/Monte Carlo 10000次/参数解析法），方法差异超阈值自动预警</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%</t>
+          <t>三方法VaR差异&lt;10%，穿透至发行人层，全量计算&lt;1min</t>
         </is>
       </c>
       <c r="G123" s="23" t="inlineStr">
@@ -12016,7 +12062,7 @@
         </is>
       </c>
       <c r="H123" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124" ht="28" customHeight="1">
@@ -12037,17 +12083,17 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>固收+策略分析</t>
+          <t>敏感度分析（多维Shock Grid）</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>债券底仓+衍生品增强策略P&amp;L归因，风险分解（利率/信用/期权贡献），固收+净值模拟</t>
+          <t>利率敏感度（DV01/关键期限点KRD/凸性），信用敏感度（CS01/DTS分评级/分行业），权益敏感度（Delta/Beta/行业Beta），商品汇率敏感度；利率×信用利差二维冲击矩阵（Shock Grid），识别最脆弱组合方向，对冲比率建议</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>固收+净值模拟与实际偏差&lt;0.5%</t>
+          <t>DV01与Bloomberg基准误差&lt;0.5bps，Shock Grid 5×5矩阵实时刷新</t>
         </is>
       </c>
       <c r="G124" s="23" t="inlineStr">
@@ -12077,17 +12123,17 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>量化策略组合分析</t>
+          <t>情景分析与压力测试</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>多策略组合叠加容量约束，策略相关性管理，Sharpe/最大回撤/Calmar实时监控</t>
+          <t>三层：①历史情景重演（924行情/2019包商/2013钱荒/2015股灾等8+事件，含冲击参数还原），②假设情景模拟（自定义任意冲击组合，即时P&amp;L输出+应急对冲建议），③反向压力测试（倒推触发止损线的临界市场情景+历史发生频率），≥20情景并行</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>策略容量计算误差&lt;5%</t>
+          <t>历史情景复现误差&lt;1%，情景P&amp;L误差&lt;0.5%，支持≥20情景并行</t>
         </is>
       </c>
       <c r="G125" s="23" t="inlineStr">
@@ -12117,17 +12163,17 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>流动性分析</t>
+          <t>流动性风险管理（LVaR）</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>逐券换手率/市场深度评估，组合变现能力分析，流动性压力下变现损失（LVaR）估算</t>
+          <t>逐持仓变现能力评估（规模/日均成交量→变现天数），Almgren-Chriss市场冲击成本模型，流动性压力测试（X天内变现Y亿最优路径+成本），流动性调整VaR（LVaR=传统VaR+流动性溢价），流动性覆盖率/缓冲监控（1/3/5/10日分层），回购到期日历</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓</t>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓，变现路径建议&lt;3s</t>
         </is>
       </c>
       <c r="G126" s="24" t="inlineStr">
@@ -12136,7 +12182,7 @@
         </is>
       </c>
       <c r="H126" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127" ht="28" customHeight="1">
@@ -12157,17 +12203,17 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>定价计算集成</t>
+          <t>衍生品对冲决策引擎</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>调用量化定价引擎实时估值与Greeks，含权债/可转债/IRS，结果缓存（Redis）与Kafka推送</t>
+          <t>七类工具矩阵（国债期货2/5/10/30Y/IRS/CDS/股指期货IF/IH/IC/IM/股指期权/黄金期货/外汇远掉期），系统推荐最优对冲方案（成本最小约束），一键生成对冲指令，对冲效果追踪（前后风险指标对比/效率/执行滑点）；支持快速/精细/尾部/跨资产四种场景</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+          <t>对冲方案推荐&lt;5s，DV01对冲误差&lt;5%，指令自动流转执行引擎</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12176,7 +12222,7 @@
         </is>
       </c>
       <c r="H127" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
@@ -12197,26 +12243,26 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>利率曲线集成</t>
+          <t>定价计算集成</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），敏感度映射</t>
+          <t>调用定价平台实时估值与Greeks（含权债/可转债/IRS），Redis缓存结果，Kafka推送持仓+估值变化事件，日终全量估值批处理</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
-        </is>
-      </c>
-      <c r="G128" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="G128" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H128" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" ht="28" customHeight="1">
@@ -12237,73 +12283,73 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），关键期限点敏感度映射，曲线版本快照（供归因历史复现）</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G129" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>F07-18</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
           <t>因子模型</t>
         </is>
       </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>多因子风险模型（利率/信用/流动性/行业因子），Alpha因子库（≥20因子），因子暴露实时计算</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>因子模型解释方差&gt;80%，Alpha IC均值&gt;0.05</t>
-        </is>
-      </c>
-      <c r="G129" s="23" t="inlineStr">
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>多因子风险模型（2200+风险因子：利率/信用/流动性/权益Beta/行业/风格/商品/汇率），Alpha因子库（≥20因子，IC均值&gt;0.05），因子暴露实时计算与历史追踪，因子风险贡献预算管理</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>因子模型解释方差&gt;80%，因子暴露更新延迟&lt;10s</t>
+        </is>
+      </c>
+      <c r="G130" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H129" s="8" t="n">
+      <c r="H130" s="8" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="22" t="inlineStr">
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="22" t="inlineStr">
         <is>
           <t>【P1】 策略投资/量化  (Quant Strategy)</t>
         </is>
-      </c>
-    </row>
-    <row r="131" ht="28" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
-        <is>
-          <t>策略投资/量化</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>F08-01</t>
-        </is>
-      </c>
-      <c r="D131" s="4" t="inlineStr">
-        <is>
-          <t>策略编写与版本管理</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G131" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H131" s="8" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1">
@@ -12319,17 +12365,17 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F08-01</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>AI辅助策略开发</t>
+          <t>策略编写与版本管理</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
+          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -12343,7 +12389,7 @@
         </is>
       </c>
       <c r="H132" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133" ht="28" customHeight="1">
@@ -12359,17 +12405,17 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F08-02</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>因子挖掘与管理</t>
+          <t>AI辅助策略开发</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>因子编写，信号生成，因子库管理，AlphaLens因子有效性分析，量化模型库，宏观/技术/基本面因子</t>
+          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -12383,7 +12429,7 @@
         </is>
       </c>
       <c r="H133" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="134" ht="28" customHeight="1">
@@ -12399,31 +12445,31 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>F08-04</t>
+          <t>F08-03</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>因子挖掘与管理</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
+          <t>因子编写，信号生成，因子库管理，AlphaLens因子有效性分析，量化模型库，宏观/技术/基本面因子</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G134" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G134" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H134" s="8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135" ht="28" customHeight="1">
@@ -12439,31 +12485,31 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>F08-05</t>
+          <t>F08-04</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>模拟盘验证</t>
+          <t>Tick级回测引擎</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G135" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G135" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H135" s="8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
@@ -12479,31 +12525,31 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>F08-06</t>
+          <t>F08-05</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>策略上线审批</t>
+          <t>模拟盘验证</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
+          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G136" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G136" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H136" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" ht="28" customHeight="1">
@@ -12519,31 +12565,31 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>F08-07</t>
+          <t>F08-06</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>策略运行管理</t>
+          <t>策略上线审批</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
+          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G137" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G137" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H137" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
@@ -12559,31 +12605,31 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>F08-08</t>
+          <t>F08-07</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>策略绩效分析</t>
+          <t>策略运行管理</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
+          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G138" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G138" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H138" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="139" ht="28" customHeight="1">
@@ -12599,17 +12645,17 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>F08-09</t>
+          <t>F08-08</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>实时多市场行情</t>
+          <t>策略绩效分析</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
+          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
@@ -12623,7 +12669,7 @@
         </is>
       </c>
       <c r="H139" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" ht="28" customHeight="1">
@@ -12639,17 +12685,17 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>F08-10</t>
+          <t>F08-09</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>历史行情回放</t>
+          <t>实时多市场行情</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
+          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -12679,31 +12725,31 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>F08-11</t>
+          <t>F08-10</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>CEP流引擎与信号调度</t>
+          <t>历史行情回放</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
+          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G141" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G141" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H141" s="8" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" ht="28" customHeight="1">
@@ -12719,78 +12765,78 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
+          <t>F08-11</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>CEP流引擎与信号调度</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G142" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="143" ht="28" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
           <t>F08-12</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D143" s="4" t="inlineStr">
         <is>
           <t>基础数据与模型底座</t>
         </is>
       </c>
-      <c r="E142" s="5" t="inlineStr">
+      <c r="E143" s="5" t="inlineStr">
         <is>
           <t>宏观因子库，债券曲线模型，估值数据接入，账户权限管理，AI引擎集成接口</t>
         </is>
       </c>
-      <c r="F142" s="5" t="inlineStr">
+      <c r="F143" s="5" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G142" s="23" t="inlineStr">
+      <c r="G143" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H142" s="8" t="n">
+      <c r="H143" s="8" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="26" t="inlineStr">
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="26" t="inlineStr">
         <is>
           <t>【P2】 定价平台  (Pricing Platform)</t>
         </is>
-      </c>
-    </row>
-    <row r="144" ht="28" customHeight="1">
-      <c r="A144" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B144" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C144" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D144" s="27" t="inlineStr">
-        <is>
-          <t>期权收益结构定价</t>
-        </is>
-      </c>
-      <c r="E144" s="11" t="inlineStr">
-        <is>
-          <t>香草期权/价差期权/欧式/美式/雪球/自定义期权定价，挂钩标的覆盖国债/期货/股票/指数/商品</t>
-        </is>
-      </c>
-      <c r="F144" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G144" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H144" s="13" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="145" ht="28" customHeight="1">
@@ -12806,17 +12852,17 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>F09-02</t>
+          <t>F09-01</t>
         </is>
       </c>
       <c r="D145" s="27" t="inlineStr">
         <is>
-          <t>结构化产品定价</t>
+          <t>期权收益结构定价</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>场外期权/远期/收益凭证/收益互换/融资融券/合约型互换定价，支持自定义结构化产品</t>
+          <t>香草期权/价差期权/欧式/美式/雪球/自定义期权定价，挂钩标的覆盖国债/期货/股票/指数/商品</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
@@ -12830,7 +12876,7 @@
         </is>
       </c>
       <c r="H145" s="13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="146" ht="28" customHeight="1">
@@ -12846,31 +12892,31 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>F09-03</t>
+          <t>F09-02</t>
         </is>
       </c>
       <c r="D146" s="27" t="inlineStr">
         <is>
-          <t>固收品种定价</t>
+          <t>结构化产品定价</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>固息/浮息国债，含权债，可转债精确定价，信用债估值，ABS定价</t>
+          <t>场外期权/远期/收益凭证/收益互换/融资融券/合约型互换定价，支持自定义结构化产品</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G146" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G146" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H146" s="13" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147" ht="28" customHeight="1">
@@ -12886,31 +12932,31 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>F09-04</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D147" s="27" t="inlineStr">
         <is>
-          <t>利率与信用曲线构建</t>
+          <t>固收品种定价</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务</t>
+          <t>固息/浮息国债，含权债，可转债精确定价，信用债估值，ABS定价</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G147" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G147" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H147" s="13" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148" ht="28" customHeight="1">
@@ -12926,17 +12972,17 @@
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>F09-05</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D148" s="27" t="inlineStr">
         <is>
-          <t>波动率曲面构建</t>
+          <t>利率与信用曲线构建</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>隐含波动率曲面，红利曲线，汇率曲线，Local Volatility曲面，波动率微笑校准</t>
+          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
@@ -12950,7 +12996,7 @@
         </is>
       </c>
       <c r="H148" s="13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="149" ht="28" customHeight="1">
@@ -12966,31 +13012,31 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>F09-06</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D149" s="27" t="inlineStr">
         <is>
-          <t>市场数据管理</t>
+          <t>波动率曲面构建</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>境内外权益/债券/外汇/商品资讯统一接入，数据清洗，异常值处理，数据质量监控</t>
+          <t>隐含波动率曲面，红利曲线，汇率曲线，Local Volatility曲面，波动率微笑校准</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G149" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G149" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H149" s="13" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="150" ht="28" customHeight="1">
@@ -13006,31 +13052,31 @@
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>F09-07</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D150" s="27" t="inlineStr">
         <is>
-          <t>蒙特卡洛求解器</t>
+          <t>市场数据管理</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价，并行情景模拟</t>
+          <t>境内外权益/债券/外汇/商品资讯统一接入，数据清洗，异常值处理，数据质量监控</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G150" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G150" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H150" s="13" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151" ht="28" customHeight="1">
@@ -13046,17 +13092,17 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>F09-08</t>
+          <t>F09-07</t>
         </is>
       </c>
       <c r="D151" s="27" t="inlineStr">
         <is>
-          <t>解析解与数值解</t>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>Black-Scholes解析解，Hull-White利率模型，SABR波动率模型，二叉树/三叉树数值解</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价，并行情景模拟</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
@@ -13070,7 +13116,7 @@
         </is>
       </c>
       <c r="H151" s="13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="152" ht="28" customHeight="1">
@@ -13086,17 +13132,17 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>F09-09</t>
+          <t>F09-08</t>
         </is>
       </c>
       <c r="D152" s="27" t="inlineStr">
         <is>
-          <t>有限差分（PDE）</t>
+          <t>解析解与数值解</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价，局部波动率模型数值解</t>
+          <t>Black-Scholes解析解，Hull-White利率模型，SABR波动率模型，二叉树/三叉树数值解</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
@@ -13126,31 +13172,31 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>F09-10</t>
+          <t>F09-09</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>实时Greeks计算</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，DV01/CS01，分桶敏感度</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价，局部波动率模型数值解</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G153" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G153" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H153" s="13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="154" ht="28" customHeight="1">
@@ -13166,17 +13212,17 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>F09-11</t>
+          <t>F09-10</t>
         </is>
       </c>
       <c r="D154" s="27" t="inlineStr">
         <is>
-          <t>估值与结算计算</t>
+          <t>实时Greeks计算</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>日终估值，盯市计算，保证金计算，结算价格，历史估值回测与误差分析</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，DV01/CS01，分桶敏感度</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
@@ -13206,17 +13252,17 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>F09-12</t>
+          <t>F09-11</t>
         </is>
       </c>
       <c r="D155" s="27" t="inlineStr">
         <is>
-          <t>风控与情景计算</t>
+          <t>估值与结算计算</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>风险计量（VaR/压力测试）调用，情景分析，保证金计算，为风控平台提供统一定价接口</t>
+          <t>日终估值，盯市计算，保证金计算，结算价格，历史估值回测与误差分析</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr">
@@ -13230,7 +13276,7 @@
         </is>
       </c>
       <c r="H155" s="13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="156" ht="28" customHeight="1">
@@ -13246,17 +13292,17 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>F09-13</t>
+          <t>F09-12</t>
         </is>
       </c>
       <c r="D156" s="27" t="inlineStr">
         <is>
-          <t>客需报价服务</t>
+          <t>风控与情景计算</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>为销售交易/TRS系统提供实时报价，一站式报价接口，支持结构化产品定制化快速报价</t>
+          <t>风险计量（VaR/压力测试）调用，情景分析，保证金计算，为风控平台提供统一定价接口</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr">
@@ -13286,17 +13332,17 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>F09-14</t>
+          <t>F09-13</t>
         </is>
       </c>
       <c r="D157" s="27" t="inlineStr">
         <is>
-          <t>定价微服务架构</t>
+          <t>客需报价服务</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>REST/gRPC定价API，横向弹性扩容，p99&lt;100ms，模型插件化注册，版本管理</t>
+          <t>为销售交易/TRS系统提供实时报价，一站式报价接口，支持结构化产品定制化快速报价</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr">
@@ -13310,7 +13356,7 @@
         </is>
       </c>
       <c r="H157" s="13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="158" ht="28" customHeight="1">
@@ -13326,78 +13372,78 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
+          <t>F09-14</t>
+        </is>
+      </c>
+      <c r="D158" s="27" t="inlineStr">
+        <is>
+          <t>定价微服务架构</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="inlineStr">
+        <is>
+          <t>REST/gRPC定价API，横向弹性扩容，p99&lt;100ms，模型插件化注册，版本管理</t>
+        </is>
+      </c>
+      <c r="F158" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G158" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H158" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="159" ht="28" customHeight="1">
+      <c r="A159" s="11" t="inlineStr">
+        <is>
+          <t>定价平台</t>
+        </is>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
           <t>F09-15</t>
         </is>
       </c>
-      <c r="D158" s="27" t="inlineStr">
+      <c r="D159" s="27" t="inlineStr">
         <is>
           <t>灵活二次开发能力</t>
         </is>
       </c>
-      <c r="E158" s="11" t="inlineStr">
+      <c r="E159" s="11" t="inlineStr">
         <is>
           <t>全平台级/单功能模块级/系统框架级可扩展，支持自定义模型接入，策略团队自助扩展</t>
         </is>
       </c>
-      <c r="F158" s="11" t="inlineStr">
+      <c r="F159" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G158" s="23" t="inlineStr">
+      <c r="G159" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H158" s="13" t="n">
+      <c r="H159" s="13" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="159" ht="20" customHeight="1">
-      <c r="A159" s="26" t="inlineStr">
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="26" t="inlineStr">
         <is>
           <t>【P2】 销售交易  (Sales Trading)</t>
         </is>
-      </c>
-    </row>
-    <row r="160" ht="28" customHeight="1">
-      <c r="A160" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B160" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C160" s="10" t="inlineStr">
-        <is>
-          <t>F10-01</t>
-        </is>
-      </c>
-      <c r="D160" s="27" t="inlineStr">
-        <is>
-          <t>报价工作台</t>
-        </is>
-      </c>
-      <c r="E160" s="11" t="inlineStr">
-        <is>
-          <t>历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer，报价提醒功能</t>
-        </is>
-      </c>
-      <c r="F160" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G160" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H160" s="13" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="161" ht="28" customHeight="1">
@@ -13413,31 +13459,31 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>F10-02</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D161" s="27" t="inlineStr">
         <is>
-          <t>债券过滤与筛选</t>
+          <t>报价工作台</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>信用债全品种过滤，利率债（国债/证金债/地方债）过滤，精确识别与模糊识别双模式</t>
+          <t>历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer，报价提醒功能</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G161" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G161" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H161" s="13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" ht="28" customHeight="1">
@@ -13453,31 +13499,31 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>F10-03</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D162" s="27" t="inlineStr">
         <is>
-          <t>报价撮合与对价</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>对价/最优报价聚合展示，撮合对价，交易包管理，报价成交确认，一键成交</t>
+          <t>信用债全品种过滤，利率债（国债/证金债/地方债）过滤，精确识别与模糊识别双模式</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G162" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G162" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H162" s="13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163" ht="28" customHeight="1">
@@ -13493,17 +13539,17 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>F10-04</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D163" s="27" t="inlineStr">
         <is>
-          <t>交易执行与要素校验</t>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>意向达成，交易要素自动校验，手工价录入，业务审批流程，交易记录管理</t>
+          <t>对价/最优报价聚合展示，撮合对价，交易包管理，报价成交确认，一键成交</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr">
@@ -13517,7 +13563,7 @@
         </is>
       </c>
       <c r="H163" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164" ht="28" customHeight="1">
@@ -13533,17 +13579,17 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>F10-05</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D164" s="27" t="inlineStr">
         <is>
-          <t>风控检查</t>
+          <t>交易执行与要素校验</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>交易前风控规则同步校验，限额检查，合规拦截，风控记录留痕，不通过自动拦截</t>
+          <t>意向达成，交易要素自动校验，手工价录入，业务审批流程，交易记录管理</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr">
@@ -13573,31 +13619,31 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>F10-06</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D165" s="27" t="inlineStr">
         <is>
-          <t>智能推荐系统</t>
+          <t>风控检查</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>基于客户画像与历史交易数据主动推荐券种，从被动服务转向主动服务，提升客户响应效率</t>
+          <t>交易前风控规则同步校验，限额检查，合规拦截，风控记录留痕，不通过自动拦截</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G165" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G165" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H165" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="166" ht="28" customHeight="1">
@@ -13613,78 +13659,78 @@
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
+          <t>F10-06</t>
+        </is>
+      </c>
+      <c r="D166" s="27" t="inlineStr">
+        <is>
+          <t>智能推荐系统</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>基于客户画像与历史交易数据主动推荐券种，从被动服务转向主动服务，提升客户响应效率</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G166" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H166" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" ht="28" customHeight="1">
+      <c r="A167" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C167" s="10" t="inlineStr">
+        <is>
           <t>F10-07</t>
         </is>
       </c>
-      <c r="D166" s="27" t="inlineStr">
+      <c r="D167" s="27" t="inlineStr">
         <is>
           <t>综合业务平台</t>
         </is>
       </c>
-      <c r="E166" s="11" t="inlineStr">
+      <c r="E167" s="11" t="inlineStr">
         <is>
           <t>解决交易员分散办公与客户交易信息共享问题，报价聚合展示，客户快速服务，多地协同</t>
         </is>
       </c>
-      <c r="F166" s="11" t="inlineStr">
+      <c r="F167" s="11" t="inlineStr">
         <is>
           <t>功能测试通过/正确率100%</t>
         </is>
       </c>
-      <c r="G166" s="24" t="inlineStr">
+      <c r="G167" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H166" s="13" t="n">
+      <c r="H167" s="13" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="167" ht="20" customHeight="1">
-      <c r="A167" s="26" t="inlineStr">
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="26" t="inlineStr">
         <is>
           <t>【P2】 信用债/信用衍生品  (Credit Bond &amp; CDS)</t>
         </is>
-      </c>
-    </row>
-    <row r="168" ht="28" customHeight="1">
-      <c r="A168" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B168" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C168" s="10" t="inlineStr">
-        <is>
-          <t>F11-01</t>
-        </is>
-      </c>
-      <c r="D168" s="27" t="inlineStr">
-        <is>
-          <t>信用风险数据接入</t>
-        </is>
-      </c>
-      <c r="E168" s="11" t="inlineStr">
-        <is>
-          <t>外部信用数据服务接入（Wind/中诚信/联合评级等），内部数据整合，数据质量检查，信用风险数据集市</t>
-        </is>
-      </c>
-      <c r="F168" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G168" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H168" s="13" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="169" ht="28" customHeight="1">
@@ -13700,31 +13746,31 @@
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
+          <t>F11-01</t>
         </is>
       </c>
       <c r="D169" s="27" t="inlineStr">
         <is>
-          <t>信用评估引擎</t>
+          <t>信用风险数据接入</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>持续迭代信用评价引擎，资产证券化评价，交易对手评价，违约概率（PD）建模，信用评分</t>
+          <t>外部信用数据服务接入（Wind/中诚信/联合评级等），内部数据整合，数据质量检查，信用风险数据集市</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G169" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G169" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H169" s="13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" ht="28" customHeight="1">
@@ -13740,31 +13786,31 @@
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D170" s="27" t="inlineStr">
         <is>
-          <t>信用预警系统</t>
+          <t>信用评估引擎</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>市场数据自动触发预警，评级下调动态预警，投后预警跟踪与信号处理，预警规则配置</t>
+          <t>持续迭代信用评价引擎，资产证券化评价，交易对手评价，违约概率（PD）建模，信用评分</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G170" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G170" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H170" s="13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="171" ht="28" customHeight="1">
@@ -13780,31 +13826,31 @@
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D171" s="27" t="inlineStr">
         <is>
-          <t>投资池管理</t>
+          <t>信用预警系统</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>债券池配置与维护，债券准入/退出规则，白名单/黑名单管理，池状态实时更新</t>
+          <t>市场数据自动触发预警，评级下调动态预警，投后预警跟踪与信号处理，预警规则配置</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G171" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G171" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H171" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="172" ht="28" customHeight="1">
@@ -13820,17 +13866,17 @@
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>F11-05</t>
+          <t>F11-04</t>
         </is>
       </c>
       <c r="D172" s="27" t="inlineStr">
         <is>
-          <t>评级管理</t>
+          <t>投资池管理</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>内部评级录入与更新，外部评级同步（中诚信/联合/大公），评级变更历史追踪，评级模型管理</t>
+          <t>债券池配置与维护，债券准入/退出规则，白名单/黑名单管理，池状态实时更新</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr">
@@ -13860,17 +13906,17 @@
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>F11-06</t>
+          <t>F11-05</t>
         </is>
       </c>
       <c r="D173" s="27" t="inlineStr">
         <is>
-          <t>投前审批管理</t>
+          <t>评级管理</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>新券投资准入审批流程，信用额度申请，投资决策材料生成，审批记录留痕</t>
+          <t>内部评级录入与更新，外部评级同步（中诚信/联合/大公），评级变更历史追踪，评级模型管理</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr">
@@ -13900,17 +13946,17 @@
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>F11-07</t>
+          <t>F11-06</t>
         </is>
       </c>
       <c r="D174" s="27" t="inlineStr">
         <is>
-          <t>持仓与敞口管理</t>
+          <t>投前审批管理</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>信用债持仓实时查询，敞口管理，集中度分析（行业/评级/发行人），到期提醒</t>
+          <t>新券投资准入审批流程，信用额度申请，投资决策材料生成，审批记录留痕</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr">
@@ -13940,31 +13986,31 @@
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>F11-08</t>
+          <t>F11-07</t>
         </is>
       </c>
       <c r="D175" s="27" t="inlineStr">
         <is>
-          <t>信用风险监控看板</t>
+          <t>持仓与敞口管理</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>多维度风险指标实时监控，信用利差走势，主体信用事件推送，指标监控与查询统计</t>
+          <t>信用债持仓实时查询，敞口管理，集中度分析（行业/评级/发行人），到期提醒</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G175" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G175" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H175" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" ht="28" customHeight="1">
@@ -13980,17 +14026,17 @@
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>F11-09</t>
+          <t>F11-08</t>
         </is>
       </c>
       <c r="D176" s="27" t="inlineStr">
         <is>
-          <t>违约管理</t>
+          <t>信用风险监控看板</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>违约事件记录，违约债券处置跟踪，损失估算，监管报送，违约主体黑名单自动更新</t>
+          <t>多维度风险指标实时监控，信用利差走势，主体信用事件推送，指标监控与查询统计</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr">
@@ -14020,17 +14066,17 @@
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>F11-10</t>
+          <t>F11-09</t>
         </is>
       </c>
       <c r="D177" s="27" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>违约管理</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析，利差走势，相对价值分析</t>
+          <t>违约事件记录，违约债券处置跟踪，损失估算，监管报送，违约主体黑名单自动更新</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr">
@@ -14044,7 +14090,7 @@
         </is>
       </c>
       <c r="H177" s="13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="178" ht="28" customHeight="1">
@@ -14060,31 +14106,31 @@
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>F11-11</t>
+          <t>F11-10</t>
         </is>
       </c>
       <c r="D178" s="27" t="inlineStr">
         <is>
-          <t>CDS定价与管理</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价（ISDA标准），生存概率曲线校准，CDS交易录入与持仓管理</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析，利差走势，相对价值分析</t>
         </is>
       </c>
       <c r="F178" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G178" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G178" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H178" s="13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="179" ht="28" customHeight="1">
@@ -14100,78 +14146,78 @@
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
+          <t>F11-11</t>
+        </is>
+      </c>
+      <c r="D179" s="27" t="inlineStr">
+        <is>
+          <t>CDS定价与管理</t>
+        </is>
+      </c>
+      <c r="E179" s="11" t="inlineStr">
+        <is>
+          <t>信用违约互换定价（ISDA标准），生存概率曲线校准，CDS交易录入与持仓管理</t>
+        </is>
+      </c>
+      <c r="F179" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G179" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H179" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="180" ht="28" customHeight="1">
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
           <t>F11-12</t>
         </is>
       </c>
-      <c r="D179" s="27" t="inlineStr">
+      <c r="D180" s="27" t="inlineStr">
         <is>
           <t>配置与权限管理</t>
         </is>
       </c>
-      <c r="E179" s="11" t="inlineStr">
+      <c r="E180" s="11" t="inlineStr">
         <is>
           <t>预警规则配置，指标库管理，评级模型管理，用户权限管理，债券池配置管理</t>
         </is>
       </c>
-      <c r="F179" s="11" t="inlineStr">
+      <c r="F180" s="11" t="inlineStr">
         <is>
           <t>功能测试通过</t>
         </is>
       </c>
-      <c r="G179" s="25" t="inlineStr">
+      <c r="G180" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H179" s="13" t="n">
+      <c r="H180" s="13" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="180" ht="20" customHeight="1">
-      <c r="A180" s="26" t="inlineStr">
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="26" t="inlineStr">
         <is>
           <t>【P2】 投顾服务  (Investment Advisory)</t>
         </is>
-      </c>
-    </row>
-    <row r="181" ht="28" customHeight="1">
-      <c r="A181" s="11" t="inlineStr">
-        <is>
-          <t>投顾服务</t>
-        </is>
-      </c>
-      <c r="B181" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C181" s="10" t="inlineStr">
-        <is>
-          <t>F12-01</t>
-        </is>
-      </c>
-      <c r="D181" s="27" t="inlineStr">
-        <is>
-          <t>投顾操作工作台</t>
-        </is>
-      </c>
-      <c r="E181" s="11" t="inlineStr">
-        <is>
-          <t>投顾人员管理客户委托，上传研究报告，发送投资建议，查看客户反馈与确认状态</t>
-        </is>
-      </c>
-      <c r="F181" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G181" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H181" s="13" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="182" ht="28" customHeight="1">
@@ -14187,17 +14233,17 @@
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F12-01</t>
         </is>
       </c>
       <c r="D182" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>投顾操作工作台</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成与审批，客户确认全流程，留痕追溯，电子签收，历史建议书归档</t>
+          <t>投顾人员管理客户委托，上传研究报告，发送投资建议，查看客户反馈与确认状态</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr">
@@ -14227,17 +14273,17 @@
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D183" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与定向推送，RPA自动获取基础数据，报告分类管理与检索</t>
+          <t>投资建议书线上生成与审批，客户确认全流程，留痕追溯，电子签收，历史建议书归档</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr">
@@ -14251,7 +14297,7 @@
         </is>
       </c>
       <c r="H183" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" ht="28" customHeight="1">
@@ -14267,17 +14313,17 @@
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D184" s="27" t="inlineStr">
         <is>
-          <t>客户投资服务界面</t>
+          <t>投研报告服务</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，发送确认，查看账户净值走势、持仓明细、交易明细</t>
+          <t>日/周/月研究报告上传与定向推送，RPA自动获取基础数据，报告分类管理与检索</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr">
@@ -14291,7 +14337,7 @@
         </is>
       </c>
       <c r="H184" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="185" ht="28" customHeight="1">
@@ -14307,31 +14353,31 @@
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D185" s="27" t="inlineStr">
         <is>
-          <t>账户深度分析</t>
+          <t>客户投资服务界面</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势，久期走势，归因分析，估值台账，持仓明细，交易明细，定期分析报告生成</t>
+          <t>客户查看投资建议与分析报告，发送确认，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G185" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G185" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H185" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="186" ht="28" customHeight="1">
@@ -14347,31 +14393,31 @@
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>F12-06</t>
+          <t>F12-05</t>
         </is>
       </c>
       <c r="D186" s="27" t="inlineStr">
         <is>
-          <t>交易服务对接</t>
+          <t>账户深度分析</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议后直接触发交易委托，与销售交易系统对接，全程数字化交易确认</t>
+          <t>账户净值走势，久期走势，归因分析，估值台账，持仓明细，交易明细，定期分析报告生成</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G186" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G186" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H186" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="187" ht="28" customHeight="1">
@@ -14387,31 +14433,31 @@
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>F12-07</t>
+          <t>F12-06</t>
         </is>
       </c>
       <c r="D187" s="27" t="inlineStr">
         <is>
-          <t>客户服务中心</t>
+          <t>交易服务对接</t>
         </is>
       </c>
       <c r="E187" s="11" t="inlineStr">
         <is>
-          <t>服务中心，消息中心，常见问题，问卷系统，客户满意度管理</t>
+          <t>客户查看投资建议后直接触发交易委托，与销售交易系统对接，全程数字化交易确认</t>
         </is>
       </c>
       <c r="F187" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G187" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G187" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H187" s="13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188" ht="28" customHeight="1">
@@ -14427,17 +14473,17 @@
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>F12-08</t>
+          <t>F12-07</t>
         </is>
       </c>
       <c r="D188" s="27" t="inlineStr">
         <is>
-          <t>平台基础管理</t>
+          <t>客户服务中心</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>用户管理，账户管理，数据管理，消息群发，登录注册，权限控制</t>
+          <t>服务中心，消息中心，常见问题，问卷系统，客户满意度管理</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr">
@@ -14454,51 +14500,51 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" ht="20" customHeight="1">
-      <c r="A189" s="26" t="inlineStr">
+    <row r="189" ht="28" customHeight="1">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B189" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr">
+        <is>
+          <t>F12-08</t>
+        </is>
+      </c>
+      <c r="D189" s="27" t="inlineStr">
+        <is>
+          <t>平台基础管理</t>
+        </is>
+      </c>
+      <c r="E189" s="11" t="inlineStr">
+        <is>
+          <t>用户管理，账户管理，数据管理，消息群发，登录注册，权限控制</t>
+        </is>
+      </c>
+      <c r="F189" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G189" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H189" s="13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="26" t="inlineStr">
         <is>
           <t>【P2】 TRS收益互换  (Total Return Swap)</t>
         </is>
-      </c>
-    </row>
-    <row r="190" ht="28" customHeight="1">
-      <c r="A190" s="11" t="inlineStr">
-        <is>
-          <t>TRS收益互换</t>
-        </is>
-      </c>
-      <c r="B190" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C190" s="10" t="inlineStr">
-        <is>
-          <t>F13-01</t>
-        </is>
-      </c>
-      <c r="D190" s="27" t="inlineStr">
-        <is>
-          <t>报价与成交管理</t>
-        </is>
-      </c>
-      <c r="E190" s="11" t="inlineStr">
-        <is>
-          <t>一站式报价（市场各渠道 + 内部自营），成交回报处理，请求报价（RFQ），历史确认查询</t>
-        </is>
-      </c>
-      <c r="F190" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G190" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H190" s="13" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="191" ht="28" customHeight="1">
@@ -14514,17 +14560,17 @@
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F13-01</t>
         </is>
       </c>
       <c r="D191" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>报价与成交管理</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置，对冲策略配置</t>
+          <t>一站式报价（市场各渠道 + 内部自营），成交回报处理，请求报价（RFQ），历史确认查询</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr">
@@ -14554,31 +14600,31 @@
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F13-02</t>
         </is>
       </c>
       <c r="D192" s="27" t="inlineStr">
         <is>
-          <t>行情与资讯</t>
+          <t>自动对冲</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>实时行情矩阵展示，债券行情，我的关注，历史行情，资讯推送</t>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置，对冲策略配置</t>
         </is>
       </c>
       <c r="F192" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G192" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G192" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H192" s="13" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="193" ht="28" customHeight="1">
@@ -14594,17 +14640,17 @@
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F13-03</t>
         </is>
       </c>
       <c r="D193" s="27" t="inlineStr">
         <is>
-          <t>开户与账户管理</t>
+          <t>行情与资讯</t>
         </is>
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>客户开户申请，账户信息管理，出入金申请，银行账号绑定，资金管理</t>
+          <t>实时行情矩阵展示，债券行情，我的关注，历史行情，资讯推送</t>
         </is>
       </c>
       <c r="F193" s="11" t="inlineStr">
@@ -14618,7 +14664,7 @@
         </is>
       </c>
       <c r="H193" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="194" ht="28" customHeight="1">
@@ -14634,31 +14680,31 @@
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F13-04</t>
         </is>
       </c>
       <c r="D194" s="27" t="inlineStr">
         <is>
-          <t>客户自主交易</t>
+          <t>开户与账户管理</t>
         </is>
       </c>
       <c r="E194" s="11" t="inlineStr">
         <is>
-          <t>客户委托下单，合约持仓查询，标的持仓查询，当日委托，行情矩阵，历史确认，开平仓设置</t>
+          <t>客户开户申请，账户信息管理，出入金申请，银行账号绑定，资金管理</t>
         </is>
       </c>
       <c r="F194" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G194" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G194" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H194" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" ht="28" customHeight="1">
@@ -14674,31 +14720,31 @@
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>F13-06</t>
+          <t>F13-05</t>
         </is>
       </c>
       <c r="D195" s="27" t="inlineStr">
         <is>
-          <t>审批管理</t>
+          <t>客户自主交易</t>
         </is>
       </c>
       <c r="E195" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，出入金审批，合约成交审核，多级审批工作流，审批留痕</t>
+          <t>客户委托下单，合约持仓查询，标的持仓查询，当日委托，行情矩阵，历史确认，开平仓设置</t>
         </is>
       </c>
       <c r="F195" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G195" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G195" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H195" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="196" ht="28" customHeight="1">
@@ -14714,31 +14760,31 @@
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>F13-07</t>
+          <t>F13-06</t>
         </is>
       </c>
       <c r="D196" s="27" t="inlineStr">
         <is>
-          <t>运营管理</t>
+          <t>审批管理</t>
         </is>
       </c>
       <c r="E196" s="11" t="inlineStr">
         <is>
-          <t>对账，库存管理，对冲录入，合约生命周期管理，日终结算处理</t>
+          <t>开户申请审批，出入金审批，合约成交审核，多级审批工作流，审批留痕</t>
         </is>
       </c>
       <c r="F196" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G196" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G196" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H196" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="197" ht="28" customHeight="1">
@@ -14754,31 +14800,31 @@
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>F13-08</t>
+          <t>F13-07</t>
         </is>
       </c>
       <c r="D197" s="27" t="inlineStr">
         <is>
-          <t>通知与文件生成</t>
+          <t>运营管理</t>
         </is>
       </c>
       <c r="E197" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>对账，库存管理，对冲录入，合约生命周期管理，日终结算处理</t>
         </is>
       </c>
       <c r="F197" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G197" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G197" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H197" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="198" ht="28" customHeight="1">
@@ -14794,31 +14840,31 @@
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>F13-09</t>
+          <t>F13-08</t>
         </is>
       </c>
       <c r="D198" s="27" t="inlineStr">
         <is>
-          <t>外部系统集成</t>
+          <t>通知与文件生成</t>
         </is>
       </c>
       <c r="E198" s="11" t="inlineStr">
         <is>
-          <t>衡泰系统客户信息同步，QTrade聊天记录同步，银行流水对接，公司邮箱系统集成</t>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
         </is>
       </c>
       <c r="F198" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G198" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G198" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H198" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="199" ht="28" customHeight="1">
@@ -14834,78 +14880,78 @@
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
+          <t>F13-09</t>
+        </is>
+      </c>
+      <c r="D199" s="27" t="inlineStr">
+        <is>
+          <t>外部系统集成</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>衡泰系统客户信息同步，QTrade聊天记录同步，银行流水对接，公司邮箱系统集成</t>
+        </is>
+      </c>
+      <c r="F199" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G199" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H199" s="13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" ht="28" customHeight="1">
+      <c r="A200" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B200" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C200" s="10" t="inlineStr">
+        <is>
           <t>F13-10</t>
         </is>
       </c>
-      <c r="D199" s="27" t="inlineStr">
+      <c r="D200" s="27" t="inlineStr">
         <is>
           <t>内部系统集成</t>
         </is>
       </c>
-      <c r="E199" s="11" t="inlineStr">
+      <c r="E200" s="11" t="inlineStr">
         <is>
           <t>现券交易系统（对冲交易执行），IBOR（持仓记录），定价平台（估值报告），事前风控（合规校验）</t>
         </is>
       </c>
-      <c r="F199" s="11" t="inlineStr">
+      <c r="F200" s="11" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G199" s="23" t="inlineStr">
+      <c r="G200" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H199" s="13" t="n">
+      <c r="H200" s="13" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="200" ht="20" customHeight="1">
-      <c r="A200" s="29" t="inlineStr">
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
-      </c>
-    </row>
-    <row r="201" ht="28" customHeight="1">
-      <c r="A201" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B201" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C201" s="15" t="inlineStr">
-        <is>
-          <t>F15-01</t>
-        </is>
-      </c>
-      <c r="D201" s="30" t="inlineStr">
-        <is>
-          <t>双边报价做市</t>
-        </is>
-      </c>
-      <c r="E201" s="16" t="inlineStr">
-        <is>
-          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化，支持国债/信用债/利率互换多品种做市</t>
-        </is>
-      </c>
-      <c r="F201" s="16" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G201" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H201" s="18" t="n">
-        <v>70</v>
       </c>
     </row>
     <row r="202" ht="28" customHeight="1">
@@ -14921,17 +14967,17 @@
       </c>
       <c r="C202" s="15" t="inlineStr">
         <is>
-          <t>F15-02</t>
+          <t>F15-01</t>
         </is>
       </c>
       <c r="D202" s="30" t="inlineStr">
         <is>
-          <t>TRS做市服务</t>
+          <t>双边报价做市</t>
         </is>
       </c>
       <c r="E202" s="16" t="inlineStr">
         <is>
-          <t>TRS产品双边报价，与TRS收益互换系统深度集成，对冲报价敞口，支持客户TRS交易</t>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化，支持国债/信用债/利率互换多品种做市</t>
         </is>
       </c>
       <c r="F202" s="16" t="inlineStr">
@@ -14945,7 +14991,7 @@
         </is>
       </c>
       <c r="H202" s="18" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
     </row>
     <row r="203" ht="28" customHeight="1">
@@ -14961,31 +15007,31 @@
       </c>
       <c r="C203" s="15" t="inlineStr">
         <is>
-          <t>F15-03</t>
+          <t>F15-02</t>
         </is>
       </c>
       <c r="D203" s="30" t="inlineStr">
         <is>
-          <t>RFQ询价响应</t>
+          <t>TRS做市服务</t>
         </is>
       </c>
       <c r="E203" s="16" t="inlineStr">
         <is>
-          <t>接收客户询价请求，自动生成报价，报价有效期管理，成交确认，询价历史记录</t>
+          <t>TRS产品双边报价，与TRS收益互换系统深度集成，对冲报价敞口，支持客户TRS交易</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G203" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G203" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H203" s="18" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="204" ht="28" customHeight="1">
@@ -15001,17 +15047,17 @@
       </c>
       <c r="C204" s="15" t="inlineStr">
         <is>
-          <t>F15-04</t>
+          <t>F15-03</t>
         </is>
       </c>
       <c r="D204" s="30" t="inlineStr">
         <is>
-          <t>API程序化做市</t>
+          <t>RFQ询价响应</t>
         </is>
       </c>
       <c r="E204" s="16" t="inlineStr">
         <is>
-          <t>对外提供做市API接口，支持程序化交易对手接入，流式报价推送，API鉴权与频率限制</t>
+          <t>接收客户询价请求，自动生成报价，报价有效期管理，成交确认，询价历史记录</t>
         </is>
       </c>
       <c r="F204" s="16" t="inlineStr">
@@ -15041,31 +15087,31 @@
       </c>
       <c r="C205" s="15" t="inlineStr">
         <is>
-          <t>F15-05</t>
+          <t>F15-04</t>
         </is>
       </c>
       <c r="D205" s="30" t="inlineStr">
         <is>
-          <t>报价策略配置</t>
+          <t>API程序化做市</t>
         </is>
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>各品种做市参数配置（报价宽度/报价量/报价频率），分时段策略，按交易对手差异化报价</t>
+          <t>对外提供做市API接口，支持程序化交易对手接入，流式报价推送，API鉴权与频率限制</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G205" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G205" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H205" s="18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="206" ht="28" customHeight="1">
@@ -15081,31 +15127,31 @@
       </c>
       <c r="C206" s="15" t="inlineStr">
         <is>
-          <t>F15-06</t>
+          <t>F15-05</t>
         </is>
       </c>
       <c r="D206" s="30" t="inlineStr">
         <is>
-          <t>报价优化算法</t>
+          <t>报价策略配置</t>
         </is>
       </c>
       <c r="E206" s="16" t="inlineStr">
         <is>
-          <t>基于市场微结构理论动态调整bid-ask spread，流动性自适应调节，机器学习辅助报价优化</t>
+          <t>各品种做市参数配置（报价宽度/报价量/报价频率），分时段策略，按交易对手差异化报价</t>
         </is>
       </c>
       <c r="F206" s="16" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G206" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G206" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H206" s="18" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="207" ht="28" customHeight="1">
@@ -15121,31 +15167,31 @@
       </c>
       <c r="C207" s="15" t="inlineStr">
         <is>
-          <t>F15-07</t>
+          <t>F15-06</t>
         </is>
       </c>
       <c r="D207" s="30" t="inlineStr">
         <is>
-          <t>债券过滤与筛选</t>
+          <t>报价优化算法</t>
         </is>
       </c>
       <c r="E207" s="16" t="inlineStr">
         <is>
-          <t>做市标的券池管理，流动性分级筛选，黑名单管理，临时暂停做市规则</t>
+          <t>基于市场微结构理论动态调整bid-ask spread，流动性自适应调节，机器学习辅助报价优化</t>
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G207" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G207" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H207" s="18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="208" ht="28" customHeight="1">
@@ -15161,31 +15207,31 @@
       </c>
       <c r="C208" s="15" t="inlineStr">
         <is>
-          <t>F15-08</t>
+          <t>F15-07</t>
         </is>
       </c>
       <c r="D208" s="30" t="inlineStr">
         <is>
-          <t>做市义务实时监控</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E208" s="16" t="inlineStr">
         <is>
-          <t>实时监控做市义务完成情况（报价连续性/报价宽度/报价量达标），义务违规预警，监管报告生成</t>
+          <t>做市标的券池管理，流动性分级筛选，黑名单管理，临时暂停做市规则</t>
         </is>
       </c>
       <c r="F208" s="16" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G208" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G208" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H208" s="18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209" ht="28" customHeight="1">
@@ -15201,31 +15247,31 @@
       </c>
       <c r="C209" s="15" t="inlineStr">
         <is>
-          <t>F15-09</t>
+          <t>F15-08</t>
         </is>
       </c>
       <c r="D209" s="30" t="inlineStr">
         <is>
-          <t>做市行情展示</t>
+          <t>做市义务实时监控</t>
         </is>
       </c>
       <c r="E209" s="16" t="inlineStr">
         <is>
-          <t>做市报价行情矩阵，实时价格展示，报价历史回放，市场最优报价对比，中签率统计</t>
+          <t>实时监控做市义务完成情况（报价连续性/报价宽度/报价量达标），义务违规预警，监管报告生成</t>
         </is>
       </c>
       <c r="F209" s="16" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G209" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G209" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H209" s="18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="210" ht="28" customHeight="1">
@@ -15241,31 +15287,31 @@
       </c>
       <c r="C210" s="15" t="inlineStr">
         <is>
-          <t>F15-10</t>
+          <t>F15-09</t>
         </is>
       </c>
       <c r="D210" s="30" t="inlineStr">
         <is>
-          <t>做市订单管理</t>
+          <t>做市行情展示</t>
         </is>
       </c>
       <c r="E210" s="16" t="inlineStr">
         <is>
-          <t>做市委托生成、撤改、成交回报处理，订单状态实时跟踪，批量撤单，做市台账</t>
+          <t>做市报价行情矩阵，实时价格展示，报价历史回放，市场最优报价对比，中签率统计</t>
         </is>
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G210" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G210" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H210" s="18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="211" ht="28" customHeight="1">
@@ -15281,31 +15327,31 @@
       </c>
       <c r="C211" s="15" t="inlineStr">
         <is>
-          <t>F15-11</t>
+          <t>F15-10</t>
         </is>
       </c>
       <c r="D211" s="30" t="inlineStr">
         <is>
-          <t>库存风险实时管理</t>
+          <t>做市订单管理</t>
         </is>
       </c>
       <c r="E211" s="16" t="inlineStr">
         <is>
-          <t>做市库存PnL实时监控，Delta对冲自动触发，库存敞口上限控制，实时盯市损益</t>
+          <t>做市委托生成、撤改、成交回报处理，订单状态实时跟踪，批量撤单，做市台账</t>
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G211" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G211" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H211" s="18" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="212" ht="28" customHeight="1">
@@ -15321,62 +15367,102 @@
       </c>
       <c r="C212" s="15" t="inlineStr">
         <is>
+          <t>F15-11</t>
+        </is>
+      </c>
+      <c r="D212" s="30" t="inlineStr">
+        <is>
+          <t>库存风险实时管理</t>
+        </is>
+      </c>
+      <c r="E212" s="16" t="inlineStr">
+        <is>
+          <t>做市库存PnL实时监控，Delta对冲自动触发，库存敞口上限控制，实时盯市损益</t>
+        </is>
+      </c>
+      <c r="F212" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G212" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H212" s="18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="213" ht="28" customHeight="1">
+      <c r="A213" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B213" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C213" s="15" t="inlineStr">
+        <is>
           <t>F15-12</t>
         </is>
       </c>
-      <c r="D212" s="30" t="inlineStr">
+      <c r="D213" s="30" t="inlineStr">
         <is>
           <t>竞争力分析</t>
         </is>
       </c>
-      <c r="E212" s="16" t="inlineStr">
+      <c r="E213" s="16" t="inlineStr">
         <is>
           <t>与市场最优报价对比，中签率分析，报价表现统计，策略调优建议，竞争对手报价分析</t>
         </is>
       </c>
-      <c r="F212" s="16" t="inlineStr">
+      <c r="F213" s="16" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G212" s="23" t="inlineStr">
+      <c r="G213" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H212" s="18" t="n">
+      <c r="H213" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="19" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H213" s="20">
-        <f>SUM(H3:H212)</f>
+      <c r="H214" s="20">
+        <f>SUM(H3:H213)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A131:H131"/>
+    <mergeCell ref="A144:H144"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A130:H130"/>
-    <mergeCell ref="A213:G213"/>
-    <mergeCell ref="A200:H200"/>
-    <mergeCell ref="A180:H180"/>
+    <mergeCell ref="A201:H201"/>
+    <mergeCell ref="A190:H190"/>
+    <mergeCell ref="A214:G214"/>
+    <mergeCell ref="A160:H160"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A112:H112"/>
     <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A181:H181"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A189:H189"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A159:H159"/>
+    <mergeCell ref="A168:H168"/>
     <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A167:H167"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16327,10 +16413,10 @@
         </is>
       </c>
       <c r="H8" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -16516,7 +16602,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>跨资产实时头寸</t>
+          <t>全资产实时头寸</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -16623,7 +16709,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>中登/中债登结算接口</t>
+          <t>中登/中债登/上清结算接口</t>
         </is>
       </c>
       <c r="G8" s="42" t="inlineStr">

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -1819,7 +1819,7 @@
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -3043,31 +3043,31 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Component VaR 四层穿透分析</t>
+          <t>Component VaR 四层穿透展示（调用M04引擎）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>VaR四层穿透：资产类别VaR→行业/子市场VaR→评级/信用质量VaR→单一发行人Component VaR，含跨类分散化收益量化；三种方法互验（历史模拟500日99%置信度/Monte Carlo 10000次/参数解析法），方法差异超阈值自动预警</t>
+          <t>PM决策展示层——调用M04(F04-10)VaR计算引擎获取三方法结果，在本模块实现四层穿透钻取：资产类别VaR→行业/子市场VaR→评级/信用质量VaR→单一发行人Component VaR，含跨类分散化收益量化；本模块不重复实现VaR计算，专注投资决策视角的风险溯源与持仓优化引导</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>三方法VaR差异&lt;10%，穿透至发行人层，全量计算&lt;1min</t>
+          <t>穿透至发行人层展示&lt;3s，三方法差异预警由M04提供，本模块直接透传</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台/定价平台/IBOR</t>
-        </is>
-      </c>
-      <c r="G19" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>FICC风险计量平台(M04 F04-10)/IBOR</t>
+        </is>
+      </c>
+      <c r="G19" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -3089,31 +3089,31 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析（多维Shock Grid）</t>
+          <t>敏感度展示（多维Shock Grid，调用M04引擎）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>利率敏感度（DV01/关键期限点KRD/凸性），信用敏感度（CS01/DTS分评级/分行业），权益敏感度（Delta/Beta/行业Beta），商品汇率敏感度；利率×信用利差二维冲击矩阵（Shock Grid），识别最脆弱组合方向，对冲比率建议</t>
+          <t>PM决策展示层——M04(F04-08/09)计算DV01/CS01/Greeks，本模块负责：组合层面聚合（按资产类别/行业/评级汇总），构建利率×信用利差二维冲击矩阵（Shock Grid 5×5），识别最脆弱组合方向，输出对冲比率建议；本模块不重复实现敏感度计算</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps，Shock Grid 5×5矩阵实时刷新</t>
+          <t>Shock Grid 5×5矩阵实时刷新，组合DV01聚合与M04单券结果误差&lt;0.1bps</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>定价平台Greeks接口/IBOR</t>
-        </is>
-      </c>
-      <c r="G20" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>FICC风险计量平台(M04 F04-08/09)/定价平台(M09 KRD)/IBOR</t>
+        </is>
+      </c>
+      <c r="G20" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -3135,31 +3135,31 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>情景分析与压力测试</t>
+          <t>情景分析PM决策层（调用M04场景库）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>三层：①历史情景重演（924行情/2019包商/2013钱荒/2015股灾等8+事件，含冲击参数还原），②假设情景模拟（自定义任意冲击组合，即时P&amp;L输出+应急对冲建议），③反向压力测试（倒推触发止损线的临界市场情景+历史发生频率），≥20情景并行</t>
+          <t>PM投资决策层——M04(F04-11)维护历史场景库并提供计算API，本模块负责：①调用M04获取场景P&amp;L结果（924行情/包商/钱荒/股灾等8+历史场景+自定义场景），②PM工作流：基于场景结果生成对冲建议、触发再平衡方案、输出持仓调整优先级，③反向压力测试（倒推临界情景→止损线设计依据）；场景库维护与全公司治理由M04负责</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%，情景P&amp;L误差&lt;0.5%，支持≥20情景并行</t>
+          <t>调用M04 API获取场景P&amp;L&lt;2s，PM决策输出（对冲建议）&lt;5s，≥20情景并行</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>FICC风险计量平台/定价平台</t>
-        </is>
-      </c>
-      <c r="G21" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>FICC风险计量平台(M04 F04-11 场景API)/定价平台</t>
+        </is>
+      </c>
+      <c r="G21" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H21" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H214"/>
+  <dimension ref="A1:H213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10497,31 +10497,31 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>F04-14</t>
+          <t>F04-15</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>绩效归因与风险计量</t>
+          <t>监管报表与风控日报</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>收益率曲线效应，信用利差分解，行业配置效应，个券择券，Carry &amp; Roll-down贡献</t>
+          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H82" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" ht="28" customHeight="1">
@@ -10537,31 +10537,31 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>F04-15</t>
+          <t>F04-16</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>监管报表与风控日报</t>
+          <t>数据底座与IBOR集成</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
+          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G83" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G83" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H83" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" ht="28" customHeight="1">
@@ -10577,17 +10577,17 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>F04-16</t>
+          <t>F04-17</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>数据底座与IBOR集成</t>
+          <t>收益率曲线与波动率曲面</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
+          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
@@ -10617,31 +10617,31 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>F04-17</t>
+          <t>F04-18</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>收益率曲线与波动率曲面</t>
+          <t>HPC计算网格</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
+          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G85" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H85" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1">
@@ -10657,78 +10657,78 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>F04-18</t>
+          <t>F04-19</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>HPC计算网格</t>
+          <t>AI风险预警</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
+          <t>异常检测（ML模型），预测性分析，模式识别，智能告警，新业务合规风险预分析</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>异常交易风控</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>F05-01</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>LLM大语言模型应用</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>客户意图识别，自然语言处理交易描述，智能报告自动生成，新规合规解读</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G86" s="28" t="inlineStr">
+      <c r="G88" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H86" s="8" t="n">
+      <c r="H88" s="8" t="n">
         <v>40</v>
-      </c>
-    </row>
-    <row r="87" ht="28" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>FICC风险计量平台</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>F04-19</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>AI风险预警</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>异常检测（ML模型），预测性分析，模式识别，智能告警，新业务合规风险预分析</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
-        </is>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1">
@@ -10744,31 +10744,31 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>F05-01</t>
+          <t>F05-02</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>LLM大语言模型应用</t>
+          <t>RAG检索增强生成</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>客户意图识别，自然语言处理交易描述，智能报告自动生成，新规合规解读</t>
+          <t>监管规则知识库构建，新规则智能固化，合规智能问答，上下文理解与规则推理</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G89" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H89" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" ht="28" customHeight="1">
@@ -10784,17 +10784,17 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>F05-02</t>
+          <t>F05-03</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>RAG检索增强生成</t>
+          <t>Agent智能体</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>监管规则知识库构建，新规则智能固化，合规智能问答，上下文理解与规则推理</t>
+          <t>异常处置任务自动化，决策支持工作流，多步骤异常核查流程优化，自动推送处置建议</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
@@ -10824,31 +10824,31 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>F05-03</t>
+          <t>F05-04</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Agent智能体</t>
+          <t>MCP外部服务集成</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>异常处置任务自动化，决策支持工作流，多步骤异常核查流程优化，自动推送处置建议</t>
+          <t>外部数据源调用接口，固化规则调用标准协议，与行情/持仓/交易系统数据对接</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H91" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" ht="28" customHeight="1">
@@ -10864,31 +10864,31 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>F05-04</t>
+          <t>F05-05</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>MCP外部服务集成</t>
+          <t>代持与反向交易识别</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>外部数据源调用接口，固化规则调用标准协议，与行情/持仓/交易系统数据对接</t>
+          <t>代持相关交易检测，同券同额反向识别，多日反向低频交易模式识别</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G92" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H92" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" ht="28" customHeight="1">
@@ -10904,17 +10904,17 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>F05-05</t>
+          <t>F05-06</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>代持与反向交易识别</t>
+          <t>价格行为异常检测</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>代持相关交易检测，同券同额反向识别，多日反向低频交易模式识别</t>
+          <t>高买低卖行为识别，信用债价格异常检测，基于历史分位数与实时行情动态偏离度计算</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -10944,17 +10944,17 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>F05-06</t>
+          <t>F05-07</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>价格行为异常检测</t>
+          <t>交易对手异常监控</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>高买低卖行为识别，信用债价格异常检测，基于历史分位数与实时行情动态偏离度计算</t>
+          <t>同一交易对手频繁交易预警，多次修改交易对手行为识别，持仓结构异常检测</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="H94" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" ht="28" customHeight="1">
@@ -10984,31 +10984,31 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>F05-07</t>
+          <t>F05-08</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>交易对手异常监控</t>
+          <t>交易量异常检测</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>同一交易对手频繁交易预警，多次修改交易对手行为识别，持仓结构异常检测</t>
+          <t>交易量统计异常识别，集中度异常告警，与历史基准对比的量级偏离检测</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G95" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H95" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" ht="28" customHeight="1">
@@ -11024,17 +11024,17 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>F05-08</t>
+          <t>F05-09</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>交易量异常检测</t>
+          <t>动态规则管理</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>交易量统计异常识别，集中度异常告警，与历史基准对比的量级偏离检测</t>
+          <t>异常模式智能探索与规则固化，No-Code规则配置界面，合规人员自助维护，规则版本管理</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="H96" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" ht="28" customHeight="1">
@@ -11064,17 +11064,17 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>F05-09</t>
+          <t>F05-10</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>动态规则管理</t>
+          <t>异常交易定位</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>异常模式智能探索与规则固化，No-Code规则配置界面，合规人员自助维护，规则版本管理</t>
+          <t>按时间范围快速查找历史异常交易，标记异常类型，可视化展示异常分布与趋势</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
@@ -11088,7 +11088,7 @@
         </is>
       </c>
       <c r="H97" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" ht="28" customHeight="1">
@@ -11104,17 +11104,17 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>F05-10</t>
+          <t>F05-11</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>异常交易定位</t>
+          <t>数据上传校验</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>按时间范围快速查找历史异常交易，标记异常类型，可视化展示异常分布与趋势</t>
+          <t>支持用户上传交易数据文件，瞬时完成异常交易校验并输出校验结果报告</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -11144,17 +11144,17 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>F05-11</t>
+          <t>F05-12</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>数据上传校验</t>
+          <t>智能报告生成</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>支持用户上传交易数据文件，瞬时完成异常交易校验并输出校验结果报告</t>
+          <t>模板自定义与场景数据一键应用，监管报送格式（证监会/人行），新业务过会合规分析报告</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -11168,54 +11168,54 @@
         </is>
       </c>
       <c r="H99" s="8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100" ht="28" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>异常交易风控</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>F05-12</t>
-        </is>
-      </c>
-      <c r="D100" s="4" t="inlineStr">
-        <is>
-          <t>智能报告生成</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
-        <is>
-          <t>模板自定义与场景数据一键应用，监管报送格式（证监会/人行），新业务过会合规分析报告</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G100" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H100" s="8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="22" t="inlineStr">
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>【P1】 事前风控/合规  (Pre-trade Risk &amp; Compliance)</t>
         </is>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>F06-01</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>风控规则配置</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G101" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="102" ht="28" customHeight="1">
@@ -11231,17 +11231,17 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>F06-01</t>
+          <t>F06-02</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>风控规则配置</t>
+          <t>多维度限额配置</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
+          <t>交易对手/交易员/券三维度限额设置，集中度/净敞口/利率敏感度/单笔名义多类型限额</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="H102" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" ht="28" customHeight="1">
@@ -11271,31 +11271,31 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>F06-02</t>
+          <t>F06-03</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>多维度限额配置</t>
+          <t>白黑名单管理</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>交易对手/交易员/券三维度限额设置，集中度/净敞口/利率敏感度/单笔名义多类型限额</t>
+          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G103" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H103" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" ht="28" customHeight="1">
@@ -11311,31 +11311,31 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>F06-03</t>
+          <t>F06-04</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>白黑名单管理</t>
+          <t>实时事前风控拦截</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
+          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G104" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G104" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H104" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105" ht="28" customHeight="1">
@@ -11351,31 +11351,31 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>F06-04</t>
+          <t>F06-05</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>实时事前风控拦截</t>
+          <t>异常报备工作流</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
+          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G105" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G105" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H105" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" ht="28" customHeight="1">
@@ -11391,31 +11391,31 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>F06-05</t>
+          <t>F06-06</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>异常报备工作流</t>
+          <t>AI聊天合规监控</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
+          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G106" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G106" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H106" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" ht="28" customHeight="1">
@@ -11431,17 +11431,17 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>F06-06</t>
+          <t>F06-07</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>AI聊天合规监控</t>
+          <t>AI交易要素提取</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
+          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="H107" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" ht="28" customHeight="1">
@@ -11471,31 +11471,31 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>F06-07</t>
+          <t>F06-08</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>AI交易要素提取</t>
+          <t>日内异常统计看板</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
+          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G108" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G108" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H108" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="109" ht="28" customHeight="1">
@@ -11511,17 +11511,17 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>F06-08</t>
+          <t>F06-09</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>日内异常统计看板</t>
+          <t>合规审批工作流</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
+          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
@@ -11551,17 +11551,17 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>F06-09</t>
+          <t>F06-10</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>合规审批工作流</t>
+          <t>责任留痕与审计追踪</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
+          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
@@ -11578,51 +11578,51 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>事前风控/合规</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>F06-10</t>
-        </is>
-      </c>
-      <c r="D111" s="4" t="inlineStr">
-        <is>
-          <t>责任留痕与审计追踪</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G111" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H111" s="8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="22" t="inlineStr">
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="22" t="inlineStr">
         <is>
           <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
         </is>
+      </c>
+    </row>
+    <row r="112" ht="28" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>F07-01</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>全资产统一持仓模型</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>八类资产（利率债/信用债/权益/基金/黄金/商品/衍生品/非标）实时T+0持仓，多层组合树（公司→部门→策略→子组合→投资经理），穿透式敞口展示（品种/久期/评级/行业/地区分布），真实组合+Shadow Portfolio并行展示</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>T+0持仓实时刷新，穿透层级≥5层，数据与IBOR差异&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="G112" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="113" ht="28" customHeight="1">
@@ -11638,22 +11638,22 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>F07-01</t>
+          <t>F07-02</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>全资产统一持仓模型</t>
+          <t>跨资产相关性分析</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>八类资产（利率债/信用债/权益/基金/黄金/商品/衍生品/非标）实时T+0持仓，多层组合树（公司→部门→策略→子组合→投资经理），穿透式敞口展示（品种/久期/评级/行业/地区分布），真实组合+Shadow Portfolio并行展示</t>
+          <t>全持仓跨资产相关矩阵（股/债/商品/衍生品/基金），多窗口滚动（20/60/252日），压力情景相关性vs历史相关性对比，动态相关性漂移预警，分散化比率(Diversification Ratio)计算，低相关候选资产推荐</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>T+0持仓实时刷新，穿透层级≥5层，数据与IBOR差异&lt;0.01%</t>
+          <t>相关矩阵计算&lt;30s（500券组合），动态漂移预警阈值可配</t>
         </is>
       </c>
       <c r="G113" s="23" t="inlineStr">
@@ -11662,7 +11662,7 @@
         </is>
       </c>
       <c r="H113" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
@@ -11678,22 +11678,22 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>F07-02</t>
+          <t>F07-03</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>跨资产相关性分析</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>全持仓跨资产相关矩阵（股/债/商品/衍生品/基金），多窗口滚动（20/60/252日），压力情景相关性vs历史相关性对比，动态相关性漂移预警，分散化比率(Diversification Ratio)计算，低相关候选资产推荐</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位（覆盖5年），跨品种套利信号识别，债券横截面信号挖掘（利差/久期偏差），时序均值回归分析</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>相关矩阵计算&lt;30s（500券组合），动态漂移预警阈值可配</t>
+          <t>OAS计算误差&lt;1bps，历史分位数覆盖5年，横截面信号与实际收益相关性&gt;0.3</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11718,22 +11718,22 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>F07-03</t>
+          <t>F07-04</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>QP智能再平衡引擎</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位（覆盖5年），跨品种套利信号识别，债券横截面信号挖掘（利差/久期偏差），时序均值回归分析</t>
+          <t>二次规划多目标优化（最小化跟踪误差+交易摩擦+融资成本+IFRS9波动），500+约束（合规/风险预算/流动性/IFRS9），2000+持仓毫秒级求解，支持整数规划（面值/手数取整），多期优化（含到期券），三种触发（定时/事件/手动），一键生成交易指令</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，历史分位数覆盖5年，横截面信号与实际收益相关性&gt;0.3</t>
+          <t>QP求解2000持仓&lt;200ms，约束满足率100%，调仓前后TE对比即时输出</t>
         </is>
       </c>
       <c r="G115" s="23" t="inlineStr">
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="H115" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="116" ht="28" customHeight="1">
@@ -11758,22 +11758,22 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F07-05</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>QP智能再平衡引擎</t>
+          <t>Shadow Portfolio虚拟试算</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>二次规划多目标优化（最小化跟踪误差+交易摩擦+融资成本+IFRS9波动），500+约束（合规/风险预算/流动性/IFRS9），2000+持仓毫秒级求解，支持整数规划（面值/手数取整），多期优化（含到期券），三种触发（定时/事件/手动），一键生成交易指令</t>
+          <t>100+虚拟组合与真实组合并行运行，多维试算（增减仓/换仓/加杠杆/新资产类别），即时显示试算后风险指标/归因/相关性/预期收益，真实vs虚拟所有指标差异对比视图，冲击成本预估</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>QP求解2000持仓&lt;200ms，约束满足率100%，调仓前后TE对比即时输出</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%，秒级响应</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -11782,7 +11782,7 @@
         </is>
       </c>
       <c r="H116" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" ht="28" customHeight="1">
@@ -11798,22 +11798,22 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>F07-05</t>
+          <t>F07-06</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Shadow Portfolio虚拟试算</t>
+          <t>资产配置策略分析</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>100+虚拟组合与真实组合并行运行，多维试算（增减仓/换仓/加杠杆/新资产类别），即时显示试算后风险指标/归因/相关性/预期收益，真实vs虚拟所有指标差异对比视图，冲击成本预估</t>
+          <t>SAA战略→TAA战术精准联动（投委会指令直接转化为因子约束输入QP引擎），宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证（≥5年），固收+策略P&amp;L归因（债券底仓+衍生品增强）</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%，秒级响应</t>
+          <t>回测期≥5年，预测方向胜率&gt;55%，SAA→TAA指令转化全程无人工干预</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -11822,7 +11822,7 @@
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1">
@@ -11838,22 +11838,22 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F07-07</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>Campisi 2.0 固收绩效归因</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>SAA战略→TAA战术精准联动（投委会指令直接转化为因子约束输入QP引擎），宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证（≥5年），固收+策略P&amp;L归因（债券底仓+衍生品增强）</t>
+          <t>固定收益五效应完整拆解：①收入效应（票息+摊销），②国债效应（利率平移/曲线斜率/曲率三效应分离，用Key Rate Duration精确映射），③利差效应（DTS贡献/行业配置效应/个券选择效应），④交易效应（择时Alpha或损耗量化），⑤残差校验（&lt;5bp合格）；日/周/月/季多维度报告自动生成</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%，SAA→TAA指令转化全程无人工干预</t>
+          <t>五效应合计与实际收益残差&lt;5bps，T+1 9:00前自动报告</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -11878,22 +11878,22 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>F07-07</t>
+          <t>F07-08</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Campisi 2.0 固收绩效归因</t>
+          <t>Brinson 资产组合绩效归因</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>固定收益五效应完整拆解：①收入效应（票息+摊销），②国债效应（利率平移/曲线斜率/曲率三效应分离，用Key Rate Duration精确映射），③利差效应（DTS贡献/行业配置效应/个券选择效应），④交易效应（择时Alpha或损耗量化），⑤残差校验（&lt;5bp合格）；日/周/月/季多维度报告自动生成</t>
+          <t>三效应：大类资产配置效应（超/低配决策贡献）/个券选择效应（同类标的选择Alpha）/交互效应，支持多层穿透（资产大类→行业→子行业→个股/个基），FOF基金穿透底层持仓，日/月/季/年累计归因趋势，投资经理能力量化排名</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>五效应合计与实际收益残差&lt;5bps，T+1 9:00前自动报告</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，穿透层级≥4层</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="H119" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="120" ht="28" customHeight="1">
@@ -11918,31 +11918,31 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F07-09</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Brinson 资产组合绩效归因</t>
+          <t>指数跟踪误差与主动风险归因</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>三效应：大类资产配置效应（超/低配决策贡献）/个券选择效应（同类标的选择Alpha）/交互效应，支持多层穿透（资产大类→行业→子行业→个股/个基），FOF基金穿透底层持仓，日/月/季/年累计归因趋势，投资经理能力量化排名</t>
+          <t>对标中债综合/信用/政策行等基准指数，跟踪误差（TE）日频监控，TE分解（配置效应TE+选券效应TE+协方差），信息比率（IR）实时监控（目标IR&gt;0.5，预警IR连续3月&lt;0），超额Alpha三因子分解</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，穿透层级≥4层</t>
-        </is>
-      </c>
-      <c r="G120" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数，IR预警自动推送</t>
+        </is>
+      </c>
+      <c r="G120" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H120" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1">
@@ -11958,31 +11958,31 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>F07-09</t>
+          <t>F07-10</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>指数跟踪误差与主动风险归因</t>
+          <t>因子风险分解 + MCTR边际风险贡献</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行等基准指数，跟踪误差（TE）日频监控，TE分解（配置效应TE+选券效应TE+协方差），信息比率（IR）实时监控（目标IR&gt;0.5，预警IR连续3月&lt;0），超额Alpha三因子分解</t>
+          <t>全持仓分解为2200+风险因子（利率/信用/权益/商品/汇率），系统性风险+特异性风险分离；MCTR边际风险贡献（∂组合波动率/∂持仓权重），风险消耗排名（识别"风险大户"），减仓/加仓优先级引导，风险预算仪表盘（已用/剩余/预警线三档）</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数，IR预警自动推送</t>
-        </is>
-      </c>
-      <c r="G121" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>因子模型解释方差&gt;80%，MCTR实时更新延迟&lt;5s，Alpha IC均值&gt;0.05</t>
+        </is>
+      </c>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H121" s="8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="122" ht="28" customHeight="1">
@@ -11998,31 +11998,31 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>F07-10</t>
+          <t>F07-11</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>因子风险分解 + MCTR边际风险贡献</t>
+          <t>Component VaR 四层穿透展示（调用M04引擎）</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>全持仓分解为2200+风险因子（利率/信用/权益/商品/汇率），系统性风险+特异性风险分离；MCTR边际风险贡献（∂组合波动率/∂持仓权重），风险消耗排名（识别"风险大户"），减仓/加仓优先级引导，风险预算仪表盘（已用/剩余/预警线三档）</t>
+          <t>PM决策展示层——调用M04(F04-10)VaR计算引擎获取三方法结果，在本模块实现四层穿透钻取：资产类别VaR→行业/子市场VaR→评级/信用质量VaR→单一发行人Component VaR，含跨类分散化收益量化；本模块不重复实现VaR计算，专注投资决策视角的风险溯源与持仓优化引导</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>因子模型解释方差&gt;80%，MCTR实时更新延迟&lt;5s，Alpha IC均值&gt;0.05</t>
-        </is>
-      </c>
-      <c r="G122" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>穿透至发行人层展示&lt;3s，三方法差异预警由M04提供，本模块直接透传</t>
+        </is>
+      </c>
+      <c r="G122" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H122" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" ht="28" customHeight="1">
@@ -12038,31 +12038,31 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>F07-11</t>
+          <t>F07-12</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Component VaR 四层穿透分析</t>
+          <t>敏感度展示（多维Shock Grid，调用M04引擎）</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>VaR四层穿透：资产类别VaR→行业/子市场VaR→评级/信用质量VaR→单一发行人Component VaR，含跨类分散化收益量化；三种方法互验（历史模拟500日99%置信度/Monte Carlo 10000次/参数解析法），方法差异超阈值自动预警</t>
+          <t>PM决策展示层——M04(F04-08/09)计算DV01/CS01/Greeks，本模块负责：组合层面聚合（按资产类别/行业/评级汇总），构建利率×信用利差二维冲击矩阵（Shock Grid 5×5），识别最脆弱组合方向，输出对冲比率建议；本模块不重复实现敏感度计算</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>三方法VaR差异&lt;10%，穿透至发行人层，全量计算&lt;1min</t>
-        </is>
-      </c>
-      <c r="G123" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>Shock Grid 5×5矩阵实时刷新，组合DV01聚合与M04单券结果误差&lt;0.1bps</t>
+        </is>
+      </c>
+      <c r="G123" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H123" s="8" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" ht="28" customHeight="1">
@@ -12078,31 +12078,31 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>F07-12</t>
+          <t>F07-13</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>敏感度分析（多维Shock Grid）</t>
+          <t>情景分析PM决策层（调用M04场景库）</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>利率敏感度（DV01/关键期限点KRD/凸性），信用敏感度（CS01/DTS分评级/分行业），权益敏感度（Delta/Beta/行业Beta），商品汇率敏感度；利率×信用利差二维冲击矩阵（Shock Grid），识别最脆弱组合方向，对冲比率建议</t>
+          <t>PM投资决策层——M04(F04-11)维护历史场景库并提供计算API，本模块负责：①调用M04获取场景P&amp;L结果（924行情/包商/钱荒/股灾等8+历史场景+自定义场景），②PM工作流：基于场景结果生成对冲建议、触发再平衡方案、输出持仓调整优先级，③反向压力测试（倒推临界情景→止损线设计依据）；场景库维护与全公司治理由M04负责</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>DV01与Bloomberg基准误差&lt;0.5bps，Shock Grid 5×5矩阵实时刷新</t>
-        </is>
-      </c>
-      <c r="G124" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>调用M04 API获取场景P&amp;L&lt;2s，PM决策输出（对冲建议）&lt;5s，≥20情景并行</t>
+        </is>
+      </c>
+      <c r="G124" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H124" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
@@ -12118,31 +12118,31 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>F07-13</t>
+          <t>F07-14</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>情景分析与压力测试</t>
+          <t>流动性风险管理（LVaR）</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>三层：①历史情景重演（924行情/2019包商/2013钱荒/2015股灾等8+事件，含冲击参数还原），②假设情景模拟（自定义任意冲击组合，即时P&amp;L输出+应急对冲建议），③反向压力测试（倒推触发止损线的临界市场情景+历史发生频率），≥20情景并行</t>
+          <t>逐持仓变现能力评估（规模/日均成交量→变现天数），Almgren-Chriss市场冲击成本模型，流动性压力测试（X天内变现Y亿最优路径+成本），流动性调整VaR（LVaR=传统VaR+流动性溢价），流动性覆盖率/缓冲监控（1/3/5/10日分层），回购到期日历</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>历史情景复现误差&lt;1%，情景P&amp;L误差&lt;0.5%，支持≥20情景并行</t>
-        </is>
-      </c>
-      <c r="G125" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓，变现路径建议&lt;3s</t>
+        </is>
+      </c>
+      <c r="G125" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H125" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126" ht="28" customHeight="1">
@@ -12158,31 +12158,31 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>F07-14</t>
+          <t>F07-15</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>流动性风险管理（LVaR）</t>
+          <t>衍生品对冲决策引擎</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>逐持仓变现能力评估（规模/日均成交量→变现天数），Almgren-Chriss市场冲击成本模型，流动性压力测试（X天内变现Y亿最优路径+成本），流动性调整VaR（LVaR=传统VaR+流动性溢价），流动性覆盖率/缓冲监控（1/3/5/10日分层），回购到期日历</t>
+          <t>七类工具矩阵（国债期货2/5/10/30Y/IRS/CDS/股指期货IF/IH/IC/IM/股指期权/黄金期货/外汇远掉期），系统推荐最优对冲方案（成本最小约束），一键生成对冲指令，对冲效果追踪（前后风险指标对比/效率/执行滑点）；支持快速/精细/尾部/跨资产四种场景</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓，变现路径建议&lt;3s</t>
-        </is>
-      </c>
-      <c r="G126" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>对冲方案推荐&lt;5s，DV01对冲误差&lt;5%，指令自动流转执行引擎</t>
+        </is>
+      </c>
+      <c r="G126" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H126" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127" ht="28" customHeight="1">
@@ -12198,22 +12198,22 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>F07-15</t>
+          <t>F07-16</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>衍生品对冲决策引擎</t>
+          <t>定价计算集成</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>七类工具矩阵（国债期货2/5/10/30Y/IRS/CDS/股指期货IF/IH/IC/IM/股指期权/黄金期货/外汇远掉期），系统推荐最优对冲方案（成本最小约束），一键生成对冲指令，对冲效果追踪（前后风险指标对比/效率/执行滑点）；支持快速/精细/尾部/跨资产四种场景</t>
+          <t>调用定价平台实时估值与Greeks（含权债/可转债/IRS），Redis缓存结果，Kafka推送持仓+估值变化事件，日终全量估值批处理</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>对冲方案推荐&lt;5s，DV01对冲误差&lt;5%，指令自动流转执行引擎</t>
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
         </is>
       </c>
       <c r="G127" s="23" t="inlineStr">
@@ -12222,7 +12222,7 @@
         </is>
       </c>
       <c r="H127" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
@@ -12238,31 +12238,31 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>F07-16</t>
+          <t>F07-17</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>定价计算集成</t>
+          <t>利率曲线集成</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>调用定价平台实时估值与Greeks（含权债/可转债/IRS），Redis缓存结果，Kafka推送持仓+估值变化事件，日终全量估值批处理</t>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），关键期限点敏感度映射，曲线版本快照（供归因历史复现）</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
-        </is>
-      </c>
-      <c r="G128" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G128" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H128" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" ht="28" customHeight="1">
@@ -12278,78 +12278,78 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>F07-17</t>
+          <t>F07-18</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>利率曲线集成</t>
+          <t>因子模型</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），关键期限点敏感度映射，曲线版本快照（供归因历史复现）</t>
+          <t>多因子风险模型（2200+风险因子：利率/信用/流动性/权益Beta/行业/风格/商品/汇率），Alpha因子库（≥20因子，IC均值&gt;0.05），因子暴露实时计算与历史追踪，因子风险贡献预算管理</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
-        </is>
-      </c>
-      <c r="G129" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>因子模型解释方差&gt;80%，因子暴露更新延迟&lt;10s</t>
+        </is>
+      </c>
+      <c r="G129" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H129" s="8" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="130" ht="28" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>F07-18</t>
-        </is>
-      </c>
-      <c r="D130" s="4" t="inlineStr">
-        <is>
-          <t>因子模型</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr">
-        <is>
-          <t>多因子风险模型（2200+风险因子：利率/信用/流动性/权益Beta/行业/风格/商品/汇率），Alpha因子库（≥20因子，IC均值&gt;0.05），因子暴露实时计算与历史追踪，因子风险贡献预算管理</t>
-        </is>
-      </c>
-      <c r="F130" s="5" t="inlineStr">
-        <is>
-          <t>因子模型解释方差&gt;80%，因子暴露更新延迟&lt;10s</t>
-        </is>
-      </c>
-      <c r="G130" s="23" t="inlineStr">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>F08-01</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>策略编写与版本管理</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G131" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H130" s="8" t="n">
+      <c r="H131" s="8" t="n">
         <v>40</v>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
-        </is>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>F08-01</t>
+          <t>F08-02</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>策略编写与版本管理</t>
+          <t>AI辅助策略开发</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
+          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="H132" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="133" ht="28" customHeight="1">
@@ -12405,17 +12405,17 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>F08-02</t>
+          <t>F08-03</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>AI辅助策略开发</t>
+          <t>因子挖掘与管理</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
+          <t>因子编写，信号生成，因子库管理，AlphaLens因子有效性分析，量化模型库，宏观/技术/基本面因子</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="H133" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134" ht="28" customHeight="1">
@@ -12445,31 +12445,31 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F08-04</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>因子挖掘与管理</t>
+          <t>Tick级回测引擎</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>因子编写，信号生成，因子库管理，AlphaLens因子有效性分析，量化模型库，宏观/技术/基本面因子</t>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G134" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G134" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H134" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135" ht="28" customHeight="1">
@@ -12485,31 +12485,31 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>F08-04</t>
+          <t>F08-05</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>模拟盘验证</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
+          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G135" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G135" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H135" s="8" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
@@ -12525,31 +12525,31 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>F08-05</t>
+          <t>F08-06</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>模拟盘验证</t>
+          <t>策略上线审批</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
+          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G136" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G136" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H136" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" ht="28" customHeight="1">
@@ -12565,31 +12565,31 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>F08-06</t>
+          <t>F08-07</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>策略上线审批</t>
+          <t>策略运行管理</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
+          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G137" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G137" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H137" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
@@ -12605,31 +12605,31 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>F08-07</t>
+          <t>F08-08</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>策略运行管理</t>
+          <t>策略绩效分析</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
+          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G138" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H138" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139" ht="28" customHeight="1">
@@ -12645,17 +12645,17 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>F08-08</t>
+          <t>F08-09</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>策略绩效分析</t>
+          <t>实时多市场行情</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
+          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
@@ -12669,7 +12669,7 @@
         </is>
       </c>
       <c r="H139" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" ht="28" customHeight="1">
@@ -12685,17 +12685,17 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>F08-09</t>
+          <t>F08-10</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>实时多市场行情</t>
+          <t>历史行情回放</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
+          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -12725,31 +12725,31 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>F08-10</t>
+          <t>F08-11</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>历史行情回放</t>
+          <t>CEP流引擎与信号调度</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
+          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G141" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G141" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H141" s="8" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="142" ht="28" customHeight="1">
@@ -12765,78 +12765,78 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>F08-11</t>
+          <t>F08-12</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>CEP流引擎与信号调度</t>
+          <t>基础数据与模型底座</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
+          <t>宏观因子库，债券曲线模型，估值数据接入，账户权限管理，AI引擎集成接口</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G142" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 定价平台  (Pricing Platform)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="28" customHeight="1">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>定价平台</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>F09-01</t>
+        </is>
+      </c>
+      <c r="D144" s="27" t="inlineStr">
+        <is>
+          <t>期权收益结构定价</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>香草期权/价差期权/欧式/美式/雪球/自定义期权定价，挂钩标的覆盖国债/期货/股票/指数/商品</t>
+        </is>
+      </c>
+      <c r="F144" s="11" t="inlineStr">
+        <is>
           <t>p99延迟/误差率/精度验证/压测10k TPS</t>
         </is>
       </c>
-      <c r="G142" s="28" t="inlineStr">
+      <c r="G144" s="28" t="inlineStr">
         <is>
           <t>极高</t>
         </is>
       </c>
-      <c r="H142" s="8" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="143" ht="28" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>策略投资/量化</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>F08-12</t>
-        </is>
-      </c>
-      <c r="D143" s="4" t="inlineStr">
-        <is>
-          <t>基础数据与模型底座</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>宏观因子库，债券曲线模型，估值数据接入，账户权限管理，AI引擎集成接口</t>
-        </is>
-      </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G143" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H143" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 定价平台  (Pricing Platform)</t>
-        </is>
+      <c r="H144" s="13" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="145" ht="28" customHeight="1">
@@ -12852,17 +12852,17 @@
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>F09-01</t>
+          <t>F09-02</t>
         </is>
       </c>
       <c r="D145" s="27" t="inlineStr">
         <is>
-          <t>期权收益结构定价</t>
+          <t>结构化产品定价</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>香草期权/价差期权/欧式/美式/雪球/自定义期权定价，挂钩标的覆盖国债/期货/股票/指数/商品</t>
+          <t>场外期权/远期/收益凭证/收益互换/融资融券/合约型互换定价，支持自定义结构化产品</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
@@ -12876,7 +12876,7 @@
         </is>
       </c>
       <c r="H145" s="13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="146" ht="28" customHeight="1">
@@ -12892,31 +12892,31 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>F09-02</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D146" s="27" t="inlineStr">
         <is>
-          <t>结构化产品定价</t>
+          <t>固收品种定价</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>场外期权/远期/收益凭证/收益互换/融资融券/合约型互换定价，支持自定义结构化产品</t>
+          <t>固息/浮息国债，含权债，可转债精确定价，信用债估值，ABS定价</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G146" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G146" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H146" s="13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147" ht="28" customHeight="1">
@@ -12932,31 +12932,31 @@
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>F09-03</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D147" s="27" t="inlineStr">
         <is>
-          <t>固收品种定价</t>
+          <t>利率与信用曲线构建</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>固息/浮息国债，含权债，可转债精确定价，信用债估值，ABS定价</t>
+          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G147" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G147" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H147" s="13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="148" ht="28" customHeight="1">
@@ -12972,17 +12972,17 @@
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>F09-04</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D148" s="27" t="inlineStr">
         <is>
-          <t>利率与信用曲线构建</t>
+          <t>波动率曲面构建</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务</t>
+          <t>隐含波动率曲面，红利曲线，汇率曲线，Local Volatility曲面，波动率微笑校准</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr">
@@ -12996,7 +12996,7 @@
         </is>
       </c>
       <c r="H148" s="13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="149" ht="28" customHeight="1">
@@ -13012,31 +13012,31 @@
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>F09-05</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D149" s="27" t="inlineStr">
         <is>
-          <t>波动率曲面构建</t>
+          <t>市场数据管理</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>隐含波动率曲面，红利曲线，汇率曲线，Local Volatility曲面，波动率微笑校准</t>
+          <t>境内外权益/债券/外汇/商品资讯统一接入，数据清洗，异常值处理，数据质量监控</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G149" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G149" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H149" s="13" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150" ht="28" customHeight="1">
@@ -13052,31 +13052,31 @@
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>F09-06</t>
+          <t>F09-07</t>
         </is>
       </c>
       <c r="D150" s="27" t="inlineStr">
         <is>
-          <t>市场数据管理</t>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>境内外权益/债券/外汇/商品资讯统一接入，数据清洗，异常值处理，数据质量监控</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价，并行情景模拟</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G150" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G150" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H150" s="13" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151" ht="28" customHeight="1">
@@ -13092,17 +13092,17 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>F09-07</t>
+          <t>F09-08</t>
         </is>
       </c>
       <c r="D151" s="27" t="inlineStr">
         <is>
-          <t>蒙特卡洛求解器</t>
+          <t>解析解与数值解</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价，并行情景模拟</t>
+          <t>Black-Scholes解析解，Hull-White利率模型，SABR波动率模型，二叉树/三叉树数值解</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="H151" s="13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152" ht="28" customHeight="1">
@@ -13132,17 +13132,17 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>F09-08</t>
+          <t>F09-09</t>
         </is>
       </c>
       <c r="D152" s="27" t="inlineStr">
         <is>
-          <t>解析解与数值解</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>Black-Scholes解析解，Hull-White利率模型，SABR波动率模型，二叉树/三叉树数值解</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价，局部波动率模型数值解</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
@@ -13172,31 +13172,31 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>F09-09</t>
+          <t>F09-10</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>有限差分（PDE）</t>
+          <t>实时Greeks计算</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价，局部波动率模型数值解</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，DV01/CS01，分桶敏感度</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G153" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H153" s="13" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154" ht="28" customHeight="1">
@@ -13212,17 +13212,17 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>F09-10</t>
+          <t>F09-11</t>
         </is>
       </c>
       <c r="D154" s="27" t="inlineStr">
         <is>
-          <t>实时Greeks计算</t>
+          <t>估值与结算计算</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，DV01/CS01，分桶敏感度</t>
+          <t>日终估值，盯市计算，保证金计算，结算价格，历史估值回测与误差分析</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
@@ -13252,17 +13252,17 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>F09-11</t>
+          <t>F09-12</t>
         </is>
       </c>
       <c r="D155" s="27" t="inlineStr">
         <is>
-          <t>估值与结算计算</t>
+          <t>风控与情景计算</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>日终估值，盯市计算，保证金计算，结算价格，历史估值回测与误差分析</t>
+          <t>风险计量（VaR/压力测试）调用，情景分析，保证金计算，为风控平台提供统一定价接口</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr">
@@ -13276,7 +13276,7 @@
         </is>
       </c>
       <c r="H155" s="13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="156" ht="28" customHeight="1">
@@ -13292,17 +13292,17 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>F09-12</t>
+          <t>F09-13</t>
         </is>
       </c>
       <c r="D156" s="27" t="inlineStr">
         <is>
-          <t>风控与情景计算</t>
+          <t>客需报价服务</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>风险计量（VaR/压力测试）调用，情景分析，保证金计算，为风控平台提供统一定价接口</t>
+          <t>为销售交易/TRS系统提供实时报价，一站式报价接口，支持结构化产品定制化快速报价</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr">
@@ -13332,17 +13332,17 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>F09-13</t>
+          <t>F09-14</t>
         </is>
       </c>
       <c r="D157" s="27" t="inlineStr">
         <is>
-          <t>客需报价服务</t>
+          <t>定价微服务架构</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>为销售交易/TRS系统提供实时报价，一站式报价接口，支持结构化产品定制化快速报价</t>
+          <t>REST/gRPC定价API，横向弹性扩容，p99&lt;100ms，模型插件化注册，版本管理</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr">
@@ -13356,7 +13356,7 @@
         </is>
       </c>
       <c r="H157" s="13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="158" ht="28" customHeight="1">
@@ -13372,17 +13372,17 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>F09-14</t>
+          <t>F09-15</t>
         </is>
       </c>
       <c r="D158" s="27" t="inlineStr">
         <is>
-          <t>定价微服务架构</t>
+          <t>灵活二次开发能力</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>REST/gRPC定价API，横向弹性扩容，p99&lt;100ms，模型插件化注册，版本管理</t>
+          <t>全平台级/单功能模块级/系统框架级可扩展，支持自定义模型接入，策略团队自助扩展</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr">
@@ -13396,54 +13396,54 @@
         </is>
       </c>
       <c r="H158" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="159" ht="28" customHeight="1">
-      <c r="A159" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B159" s="10" t="inlineStr">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 销售交易  (Sales Trading)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="28" customHeight="1">
+      <c r="A160" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C159" s="10" t="inlineStr">
-        <is>
-          <t>F09-15</t>
-        </is>
-      </c>
-      <c r="D159" s="27" t="inlineStr">
-        <is>
-          <t>灵活二次开发能力</t>
-        </is>
-      </c>
-      <c r="E159" s="11" t="inlineStr">
-        <is>
-          <t>全平台级/单功能模块级/系统框架级可扩展，支持自定义模型接入，策略团队自助扩展</t>
-        </is>
-      </c>
-      <c r="F159" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G159" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H159" s="13" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="160" ht="20" customHeight="1">
-      <c r="A160" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 销售交易  (Sales Trading)</t>
-        </is>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>F10-01</t>
+        </is>
+      </c>
+      <c r="D160" s="27" t="inlineStr">
+        <is>
+          <t>报价工作台</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="inlineStr">
+        <is>
+          <t>历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer，报价提醒功能</t>
+        </is>
+      </c>
+      <c r="F160" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G160" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H160" s="13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="161" ht="28" customHeight="1">
@@ -13459,31 +13459,31 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>F10-01</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D161" s="27" t="inlineStr">
         <is>
-          <t>报价工作台</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer，报价提醒功能</t>
+          <t>信用债全品种过滤，利率债（国债/证金债/地方债）过滤，精确识别与模糊识别双模式</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G161" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G161" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H161" s="13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" ht="28" customHeight="1">
@@ -13499,31 +13499,31 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>F10-02</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D162" s="27" t="inlineStr">
         <is>
-          <t>债券过滤与筛选</t>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>信用债全品种过滤，利率债（国债/证金债/地方债）过滤，精确识别与模糊识别双模式</t>
+          <t>对价/最优报价聚合展示，撮合对价，交易包管理，报价成交确认，一键成交</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G162" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G162" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H162" s="13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" ht="28" customHeight="1">
@@ -13539,17 +13539,17 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>F10-03</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D163" s="27" t="inlineStr">
         <is>
-          <t>报价撮合与对价</t>
+          <t>交易执行与要素校验</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>对价/最优报价聚合展示，撮合对价，交易包管理，报价成交确认，一键成交</t>
+          <t>意向达成，交易要素自动校验，手工价录入，业务审批流程，交易记录管理</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr">
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="H163" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" ht="28" customHeight="1">
@@ -13579,17 +13579,17 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>F10-04</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D164" s="27" t="inlineStr">
         <is>
-          <t>交易执行与要素校验</t>
+          <t>风控检查</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>意向达成，交易要素自动校验，手工价录入，业务审批流程，交易记录管理</t>
+          <t>交易前风控规则同步校验，限额检查，合规拦截，风控记录留痕，不通过自动拦截</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr">
@@ -13619,31 +13619,31 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>F10-05</t>
+          <t>F10-06</t>
         </is>
       </c>
       <c r="D165" s="27" t="inlineStr">
         <is>
-          <t>风控检查</t>
+          <t>智能推荐系统</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>交易前风控规则同步校验，限额检查，合规拦截，风控记录留痕，不通过自动拦截</t>
+          <t>基于客户画像与历史交易数据主动推荐券种，从被动服务转向主动服务，提升客户响应效率</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G165" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G165" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H165" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="166" ht="28" customHeight="1">
@@ -13659,78 +13659,78 @@
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>F10-06</t>
+          <t>F10-07</t>
         </is>
       </c>
       <c r="D166" s="27" t="inlineStr">
         <is>
-          <t>智能推荐系统</t>
+          <t>综合业务平台</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>基于客户画像与历史交易数据主动推荐券种，从被动服务转向主动服务，提升客户响应效率</t>
+          <t>解决交易员分散办公与客户交易信息共享问题，报价聚合展示，客户快速服务，多地协同</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr">
         <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G166" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H166" s="13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 信用债/信用衍生品  (Credit Bond &amp; CDS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="28" customHeight="1">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>F11-01</t>
+        </is>
+      </c>
+      <c r="D168" s="27" t="inlineStr">
+        <is>
+          <t>信用风险数据接入</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>外部信用数据服务接入（Wind/中诚信/联合评级等），内部数据整合，数据质量检查，信用风险数据集市</t>
+        </is>
+      </c>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G166" s="23" t="inlineStr">
+      <c r="G168" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H166" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="167" ht="28" customHeight="1">
-      <c r="A167" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B167" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C167" s="10" t="inlineStr">
-        <is>
-          <t>F10-07</t>
-        </is>
-      </c>
-      <c r="D167" s="27" t="inlineStr">
-        <is>
-          <t>综合业务平台</t>
-        </is>
-      </c>
-      <c r="E167" s="11" t="inlineStr">
-        <is>
-          <t>解决交易员分散办公与客户交易信息共享问题，报价聚合展示，客户快速服务，多地协同</t>
-        </is>
-      </c>
-      <c r="F167" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G167" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H167" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 信用债/信用衍生品  (Credit Bond &amp; CDS)</t>
-        </is>
+      <c r="H168" s="13" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="169" ht="28" customHeight="1">
@@ -13746,31 +13746,31 @@
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>F11-01</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D169" s="27" t="inlineStr">
         <is>
-          <t>信用风险数据接入</t>
+          <t>信用评估引擎</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>外部信用数据服务接入（Wind/中诚信/联合评级等），内部数据整合，数据质量检查，信用风险数据集市</t>
+          <t>持续迭代信用评价引擎，资产证券化评价，交易对手评价，违约概率（PD）建模，信用评分</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G169" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G169" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H169" s="13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="170" ht="28" customHeight="1">
@@ -13786,31 +13786,31 @@
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>F11-02</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D170" s="27" t="inlineStr">
         <is>
-          <t>信用评估引擎</t>
+          <t>信用预警系统</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>持续迭代信用评价引擎，资产证券化评价，交易对手评价，违约概率（PD）建模，信用评分</t>
+          <t>市场数据自动触发预警，评级下调动态预警，投后预警跟踪与信号处理，预警规则配置</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G170" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G170" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H170" s="13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="171" ht="28" customHeight="1">
@@ -13826,31 +13826,31 @@
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F11-04</t>
         </is>
       </c>
       <c r="D171" s="27" t="inlineStr">
         <is>
-          <t>信用预警系统</t>
+          <t>投资池管理</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>市场数据自动触发预警，评级下调动态预警，投后预警跟踪与信号处理，预警规则配置</t>
+          <t>债券池配置与维护，债券准入/退出规则，白名单/黑名单管理，池状态实时更新</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G171" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G171" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H171" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" ht="28" customHeight="1">
@@ -13866,17 +13866,17 @@
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F11-05</t>
         </is>
       </c>
       <c r="D172" s="27" t="inlineStr">
         <is>
-          <t>投资池管理</t>
+          <t>评级管理</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>债券池配置与维护，债券准入/退出规则，白名单/黑名单管理，池状态实时更新</t>
+          <t>内部评级录入与更新，外部评级同步（中诚信/联合/大公），评级变更历史追踪，评级模型管理</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr">
@@ -13906,17 +13906,17 @@
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>F11-05</t>
+          <t>F11-06</t>
         </is>
       </c>
       <c r="D173" s="27" t="inlineStr">
         <is>
-          <t>评级管理</t>
+          <t>投前审批管理</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>内部评级录入与更新，外部评级同步（中诚信/联合/大公），评级变更历史追踪，评级模型管理</t>
+          <t>新券投资准入审批流程，信用额度申请，投资决策材料生成，审批记录留痕</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr">
@@ -13946,17 +13946,17 @@
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>F11-06</t>
+          <t>F11-07</t>
         </is>
       </c>
       <c r="D174" s="27" t="inlineStr">
         <is>
-          <t>投前审批管理</t>
+          <t>持仓与敞口管理</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>新券投资准入审批流程，信用额度申请，投资决策材料生成，审批记录留痕</t>
+          <t>信用债持仓实时查询，敞口管理，集中度分析（行业/评级/发行人），到期提醒</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr">
@@ -13986,31 +13986,31 @@
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>F11-07</t>
+          <t>F11-08</t>
         </is>
       </c>
       <c r="D175" s="27" t="inlineStr">
         <is>
-          <t>持仓与敞口管理</t>
+          <t>信用风险监控看板</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>信用债持仓实时查询，敞口管理，集中度分析（行业/评级/发行人），到期提醒</t>
+          <t>多维度风险指标实时监控，信用利差走势，主体信用事件推送，指标监控与查询统计</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G175" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G175" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H175" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="176" ht="28" customHeight="1">
@@ -14026,17 +14026,17 @@
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>F11-08</t>
+          <t>F11-09</t>
         </is>
       </c>
       <c r="D176" s="27" t="inlineStr">
         <is>
-          <t>信用风险监控看板</t>
+          <t>违约管理</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>多维度风险指标实时监控，信用利差走势，主体信用事件推送，指标监控与查询统计</t>
+          <t>违约事件记录，违约债券处置跟踪，损失估算，监管报送，违约主体黑名单自动更新</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr">
@@ -14066,17 +14066,17 @@
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>F11-09</t>
+          <t>F11-10</t>
         </is>
       </c>
       <c r="D177" s="27" t="inlineStr">
         <is>
-          <t>违约管理</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>违约事件记录，违约债券处置跟踪，损失估算，监管报送，违约主体黑名单自动更新</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析，利差走势，相对价值分析</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr">
@@ -14090,7 +14090,7 @@
         </is>
       </c>
       <c r="H177" s="13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="178" ht="28" customHeight="1">
@@ -14106,31 +14106,31 @@
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>F11-10</t>
+          <t>F11-11</t>
         </is>
       </c>
       <c r="D178" s="27" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>CDS定价与管理</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析，利差走势，相对价值分析</t>
+          <t>信用违约互换定价（ISDA标准），生存概率曲线校准，CDS交易录入与持仓管理</t>
         </is>
       </c>
       <c r="F178" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G178" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G178" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H178" s="13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="179" ht="28" customHeight="1">
@@ -14146,78 +14146,78 @@
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>F11-11</t>
+          <t>F11-12</t>
         </is>
       </c>
       <c r="D179" s="27" t="inlineStr">
         <is>
-          <t>CDS定价与管理</t>
+          <t>配置与权限管理</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价（ISDA标准），生存概率曲线校准，CDS交易录入与持仓管理</t>
+          <t>预警规则配置，指标库管理，评级模型管理，用户权限管理，债券池配置管理</t>
         </is>
       </c>
       <c r="F179" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G179" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G179" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H179" s="13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="180" ht="28" customHeight="1">
-      <c r="A180" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B180" s="10" t="inlineStr">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 投顾服务  (Investment Advisory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="28" customHeight="1">
+      <c r="A181" s="11" t="inlineStr">
+        <is>
+          <t>投顾服务</t>
+        </is>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C180" s="10" t="inlineStr">
-        <is>
-          <t>F11-12</t>
-        </is>
-      </c>
-      <c r="D180" s="27" t="inlineStr">
-        <is>
-          <t>配置与权限管理</t>
-        </is>
-      </c>
-      <c r="E180" s="11" t="inlineStr">
-        <is>
-          <t>预警规则配置，指标库管理，评级模型管理，用户权限管理，债券池配置管理</t>
-        </is>
-      </c>
-      <c r="F180" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G180" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H180" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="181" ht="20" customHeight="1">
-      <c r="A181" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 投顾服务  (Investment Advisory)</t>
-        </is>
+      <c r="C181" s="10" t="inlineStr">
+        <is>
+          <t>F12-01</t>
+        </is>
+      </c>
+      <c r="D181" s="27" t="inlineStr">
+        <is>
+          <t>投顾操作工作台</t>
+        </is>
+      </c>
+      <c r="E181" s="11" t="inlineStr">
+        <is>
+          <t>投顾人员管理客户委托，上传研究报告，发送投资建议，查看客户反馈与确认状态</t>
+        </is>
+      </c>
+      <c r="F181" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G181" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H181" s="13" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="182" ht="28" customHeight="1">
@@ -14233,17 +14233,17 @@
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>F12-01</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D182" s="27" t="inlineStr">
         <is>
-          <t>投顾操作工作台</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>投顾人员管理客户委托，上传研究报告，发送投资建议，查看客户反馈与确认状态</t>
+          <t>投资建议书线上生成与审批，客户确认全流程，留痕追溯，电子签收，历史建议书归档</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr">
@@ -14273,17 +14273,17 @@
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>F12-02</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D183" s="27" t="inlineStr">
         <is>
-          <t>投资建议书管理</t>
+          <t>投研报告服务</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>投资建议书线上生成与审批，客户确认全流程，留痕追溯，电子签收，历史建议书归档</t>
+          <t>日/周/月研究报告上传与定向推送，RPA自动获取基础数据，报告分类管理与检索</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr">
@@ -14297,7 +14297,7 @@
         </is>
       </c>
       <c r="H183" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="184" ht="28" customHeight="1">
@@ -14313,17 +14313,17 @@
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F12-04</t>
         </is>
       </c>
       <c r="D184" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>客户投资服务界面</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与定向推送，RPA自动获取基础数据，报告分类管理与检索</t>
+          <t>客户查看投资建议与分析报告，发送确认，查看账户净值走势、持仓明细、交易明细</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr">
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="H184" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="185" ht="28" customHeight="1">
@@ -14353,31 +14353,31 @@
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F12-05</t>
         </is>
       </c>
       <c r="D185" s="27" t="inlineStr">
         <is>
-          <t>客户投资服务界面</t>
+          <t>账户深度分析</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，发送确认，查看账户净值走势、持仓明细、交易明细</t>
+          <t>账户净值走势，久期走势，归因分析，估值台账，持仓明细，交易明细，定期分析报告生成</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G185" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G185" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H185" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="186" ht="28" customHeight="1">
@@ -14393,31 +14393,31 @@
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F12-06</t>
         </is>
       </c>
       <c r="D186" s="27" t="inlineStr">
         <is>
-          <t>账户深度分析</t>
+          <t>交易服务对接</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势，久期走势，归因分析，估值台账，持仓明细，交易明细，定期分析报告生成</t>
+          <t>客户查看投资建议后直接触发交易委托，与销售交易系统对接，全程数字化交易确认</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G186" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G186" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H186" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="187" ht="28" customHeight="1">
@@ -14433,31 +14433,31 @@
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>F12-06</t>
+          <t>F12-07</t>
         </is>
       </c>
       <c r="D187" s="27" t="inlineStr">
         <is>
-          <t>交易服务对接</t>
+          <t>客户服务中心</t>
         </is>
       </c>
       <c r="E187" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议后直接触发交易委托，与销售交易系统对接，全程数字化交易确认</t>
+          <t>服务中心，消息中心，常见问题，问卷系统，客户满意度管理</t>
         </is>
       </c>
       <c r="F187" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G187" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G187" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H187" s="13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188" ht="28" customHeight="1">
@@ -14473,17 +14473,17 @@
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>F12-07</t>
+          <t>F12-08</t>
         </is>
       </c>
       <c r="D188" s="27" t="inlineStr">
         <is>
-          <t>客户服务中心</t>
+          <t>平台基础管理</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>服务中心，消息中心，常见问题，问卷系统，客户满意度管理</t>
+          <t>用户管理，账户管理，数据管理，消息群发，登录注册，权限控制</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr">
@@ -14500,51 +14500,51 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" ht="28" customHeight="1">
-      <c r="A189" s="11" t="inlineStr">
-        <is>
-          <t>投顾服务</t>
-        </is>
-      </c>
-      <c r="B189" s="10" t="inlineStr">
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="28" customHeight="1">
+      <c r="A190" s="11" t="inlineStr">
+        <is>
+          <t>TRS收益互换</t>
+        </is>
+      </c>
+      <c r="B190" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C189" s="10" t="inlineStr">
-        <is>
-          <t>F12-08</t>
-        </is>
-      </c>
-      <c r="D189" s="27" t="inlineStr">
-        <is>
-          <t>平台基础管理</t>
-        </is>
-      </c>
-      <c r="E189" s="11" t="inlineStr">
-        <is>
-          <t>用户管理，账户管理，数据管理，消息群发，登录注册，权限控制</t>
-        </is>
-      </c>
-      <c r="F189" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G189" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H189" s="13" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="190" ht="20" customHeight="1">
-      <c r="A190" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 TRS收益互换  (Total Return Swap)</t>
-        </is>
+      <c r="C190" s="10" t="inlineStr">
+        <is>
+          <t>F13-01</t>
+        </is>
+      </c>
+      <c r="D190" s="27" t="inlineStr">
+        <is>
+          <t>报价与成交管理</t>
+        </is>
+      </c>
+      <c r="E190" s="11" t="inlineStr">
+        <is>
+          <t>一站式报价（市场各渠道 + 内部自营），成交回报处理，请求报价（RFQ），历史确认查询</t>
+        </is>
+      </c>
+      <c r="F190" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G190" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H190" s="13" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="191" ht="28" customHeight="1">
@@ -14560,17 +14560,17 @@
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>F13-01</t>
+          <t>F13-02</t>
         </is>
       </c>
       <c r="D191" s="27" t="inlineStr">
         <is>
-          <t>报价与成交管理</t>
+          <t>自动对冲</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>一站式报价（市场各渠道 + 内部自营），成交回报处理，请求报价（RFQ），历史确认查询</t>
+          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置，对冲策略配置</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr">
@@ -14600,31 +14600,31 @@
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>F13-02</t>
+          <t>F13-03</t>
         </is>
       </c>
       <c r="D192" s="27" t="inlineStr">
         <is>
-          <t>自动对冲</t>
+          <t>行情与资讯</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>对冲委托自动触发，对冲回报处理，风险校验，组合重叠分析，开平仓设置，对冲策略配置</t>
+          <t>实时行情矩阵展示，债券行情，我的关注，历史行情，资讯推送</t>
         </is>
       </c>
       <c r="F192" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G192" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G192" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H192" s="13" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193" ht="28" customHeight="1">
@@ -14640,17 +14640,17 @@
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>F13-03</t>
+          <t>F13-04</t>
         </is>
       </c>
       <c r="D193" s="27" t="inlineStr">
         <is>
-          <t>行情与资讯</t>
+          <t>开户与账户管理</t>
         </is>
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>实时行情矩阵展示，债券行情，我的关注，历史行情，资讯推送</t>
+          <t>客户开户申请，账户信息管理，出入金申请，银行账号绑定，资金管理</t>
         </is>
       </c>
       <c r="F193" s="11" t="inlineStr">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="H193" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194" ht="28" customHeight="1">
@@ -14680,31 +14680,31 @@
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>F13-04</t>
+          <t>F13-05</t>
         </is>
       </c>
       <c r="D194" s="27" t="inlineStr">
         <is>
-          <t>开户与账户管理</t>
+          <t>客户自主交易</t>
         </is>
       </c>
       <c r="E194" s="11" t="inlineStr">
         <is>
-          <t>客户开户申请，账户信息管理，出入金申请，银行账号绑定，资金管理</t>
+          <t>客户委托下单，合约持仓查询，标的持仓查询，当日委托，行情矩阵，历史确认，开平仓设置</t>
         </is>
       </c>
       <c r="F194" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G194" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G194" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H194" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="195" ht="28" customHeight="1">
@@ -14720,31 +14720,31 @@
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>F13-05</t>
+          <t>F13-06</t>
         </is>
       </c>
       <c r="D195" s="27" t="inlineStr">
         <is>
-          <t>客户自主交易</t>
+          <t>审批管理</t>
         </is>
       </c>
       <c r="E195" s="11" t="inlineStr">
         <is>
-          <t>客户委托下单，合约持仓查询，标的持仓查询，当日委托，行情矩阵，历史确认，开平仓设置</t>
+          <t>开户申请审批，出入金审批，合约成交审核，多级审批工作流，审批留痕</t>
         </is>
       </c>
       <c r="F195" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G195" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G195" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H195" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="196" ht="28" customHeight="1">
@@ -14760,31 +14760,31 @@
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>F13-06</t>
+          <t>F13-07</t>
         </is>
       </c>
       <c r="D196" s="27" t="inlineStr">
         <is>
-          <t>审批管理</t>
+          <t>运营管理</t>
         </is>
       </c>
       <c r="E196" s="11" t="inlineStr">
         <is>
-          <t>开户申请审批，出入金审批，合约成交审核，多级审批工作流，审批留痕</t>
+          <t>对账，库存管理，对冲录入，合约生命周期管理，日终结算处理</t>
         </is>
       </c>
       <c r="F196" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G196" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G196" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H196" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="197" ht="28" customHeight="1">
@@ -14800,31 +14800,31 @@
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>F13-07</t>
+          <t>F13-08</t>
         </is>
       </c>
       <c r="D197" s="27" t="inlineStr">
         <is>
-          <t>运营管理</t>
+          <t>通知与文件生成</t>
         </is>
       </c>
       <c r="E197" s="11" t="inlineStr">
         <is>
-          <t>对账，库存管理，对冲录入，合约生命周期管理，日终结算处理</t>
+          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
         </is>
       </c>
       <c r="F197" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G197" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G197" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H197" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="198" ht="28" customHeight="1">
@@ -14840,31 +14840,31 @@
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>F13-08</t>
+          <t>F13-09</t>
         </is>
       </c>
       <c r="D198" s="27" t="inlineStr">
         <is>
-          <t>通知与文件生成</t>
+          <t>外部系统集成</t>
         </is>
       </c>
       <c r="E198" s="11" t="inlineStr">
         <is>
-          <t>企微通知提醒，确认书/结算单/估值报告/出入金通知自动生成并通过邮箱发送</t>
+          <t>衡泰系统客户信息同步，QTrade聊天记录同步，银行流水对接，公司邮箱系统集成</t>
         </is>
       </c>
       <c r="F198" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G198" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G198" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H198" s="13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="199" ht="28" customHeight="1">
@@ -14880,17 +14880,17 @@
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>F13-09</t>
+          <t>F13-10</t>
         </is>
       </c>
       <c r="D199" s="27" t="inlineStr">
         <is>
-          <t>外部系统集成</t>
+          <t>内部系统集成</t>
         </is>
       </c>
       <c r="E199" s="11" t="inlineStr">
         <is>
-          <t>衡泰系统客户信息同步，QTrade聊天记录同步，银行流水对接，公司邮箱系统集成</t>
+          <t>现券交易系统（对冲交易执行），IBOR（持仓记录），定价平台（估值报告），事前风控（合规校验）</t>
         </is>
       </c>
       <c r="F199" s="11" t="inlineStr">
@@ -14904,54 +14904,54 @@
         </is>
       </c>
       <c r="H199" s="13" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="200" ht="28" customHeight="1">
-      <c r="A200" s="11" t="inlineStr">
-        <is>
-          <t>TRS收益互换</t>
-        </is>
-      </c>
-      <c r="B200" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C200" s="10" t="inlineStr">
-        <is>
-          <t>F13-10</t>
-        </is>
-      </c>
-      <c r="D200" s="27" t="inlineStr">
-        <is>
-          <t>内部系统集成</t>
-        </is>
-      </c>
-      <c r="E200" s="11" t="inlineStr">
-        <is>
-          <t>现券交易系统（对冲交易执行），IBOR（持仓记录），定价平台（估值报告），事前风控（合规校验）</t>
-        </is>
-      </c>
-      <c r="F200" s="11" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G200" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H200" s="13" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="201" ht="20" customHeight="1">
-      <c r="A201" s="29" t="inlineStr">
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="29" t="inlineStr">
         <is>
           <t>【P3】 做市商系统  (Market Making)</t>
         </is>
+      </c>
+    </row>
+    <row r="201" ht="28" customHeight="1">
+      <c r="A201" s="16" t="inlineStr">
+        <is>
+          <t>做市商系统</t>
+        </is>
+      </c>
+      <c r="B201" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C201" s="15" t="inlineStr">
+        <is>
+          <t>F15-01</t>
+        </is>
+      </c>
+      <c r="D201" s="30" t="inlineStr">
+        <is>
+          <t>双边报价做市</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="inlineStr">
+        <is>
+          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化，支持国债/信用债/利率互换多品种做市</t>
+        </is>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G201" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H201" s="18" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="202" ht="28" customHeight="1">
@@ -14967,17 +14967,17 @@
       </c>
       <c r="C202" s="15" t="inlineStr">
         <is>
-          <t>F15-01</t>
+          <t>F15-02</t>
         </is>
       </c>
       <c r="D202" s="30" t="inlineStr">
         <is>
-          <t>双边报价做市</t>
+          <t>TRS做市服务</t>
         </is>
       </c>
       <c r="E202" s="16" t="inlineStr">
         <is>
-          <t>多品种同时双边报价，延迟&lt;5ms，报价宽度动态优化，支持国债/信用债/利率互换多品种做市</t>
+          <t>TRS产品双边报价，与TRS收益互换系统深度集成，对冲报价敞口，支持客户TRS交易</t>
         </is>
       </c>
       <c r="F202" s="16" t="inlineStr">
@@ -14991,7 +14991,7 @@
         </is>
       </c>
       <c r="H202" s="18" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="203" ht="28" customHeight="1">
@@ -15007,31 +15007,31 @@
       </c>
       <c r="C203" s="15" t="inlineStr">
         <is>
-          <t>F15-02</t>
+          <t>F15-03</t>
         </is>
       </c>
       <c r="D203" s="30" t="inlineStr">
         <is>
-          <t>TRS做市服务</t>
+          <t>RFQ询价响应</t>
         </is>
       </c>
       <c r="E203" s="16" t="inlineStr">
         <is>
-          <t>TRS产品双边报价，与TRS收益互换系统深度集成，对冲报价敞口，支持客户TRS交易</t>
+          <t>接收客户询价请求，自动生成报价，报价有效期管理，成交确认，询价历史记录</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G203" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G203" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H203" s="18" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="204" ht="28" customHeight="1">
@@ -15047,17 +15047,17 @@
       </c>
       <c r="C204" s="15" t="inlineStr">
         <is>
-          <t>F15-03</t>
+          <t>F15-04</t>
         </is>
       </c>
       <c r="D204" s="30" t="inlineStr">
         <is>
-          <t>RFQ询价响应</t>
+          <t>API程序化做市</t>
         </is>
       </c>
       <c r="E204" s="16" t="inlineStr">
         <is>
-          <t>接收客户询价请求，自动生成报价，报价有效期管理，成交确认，询价历史记录</t>
+          <t>对外提供做市API接口，支持程序化交易对手接入，流式报价推送，API鉴权与频率限制</t>
         </is>
       </c>
       <c r="F204" s="16" t="inlineStr">
@@ -15087,31 +15087,31 @@
       </c>
       <c r="C205" s="15" t="inlineStr">
         <is>
-          <t>F15-04</t>
+          <t>F15-05</t>
         </is>
       </c>
       <c r="D205" s="30" t="inlineStr">
         <is>
-          <t>API程序化做市</t>
+          <t>报价策略配置</t>
         </is>
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>对外提供做市API接口，支持程序化交易对手接入，流式报价推送，API鉴权与频率限制</t>
+          <t>各品种做市参数配置（报价宽度/报价量/报价频率），分时段策略，按交易对手差异化报价</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G205" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G205" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H205" s="18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206" ht="28" customHeight="1">
@@ -15127,31 +15127,31 @@
       </c>
       <c r="C206" s="15" t="inlineStr">
         <is>
-          <t>F15-05</t>
+          <t>F15-06</t>
         </is>
       </c>
       <c r="D206" s="30" t="inlineStr">
         <is>
-          <t>报价策略配置</t>
+          <t>报价优化算法</t>
         </is>
       </c>
       <c r="E206" s="16" t="inlineStr">
         <is>
-          <t>各品种做市参数配置（报价宽度/报价量/报价频率），分时段策略，按交易对手差异化报价</t>
+          <t>基于市场微结构理论动态调整bid-ask spread，流动性自适应调节，机器学习辅助报价优化</t>
         </is>
       </c>
       <c r="F206" s="16" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G206" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G206" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H206" s="18" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="207" ht="28" customHeight="1">
@@ -15167,31 +15167,31 @@
       </c>
       <c r="C207" s="15" t="inlineStr">
         <is>
-          <t>F15-06</t>
+          <t>F15-07</t>
         </is>
       </c>
       <c r="D207" s="30" t="inlineStr">
         <is>
-          <t>报价优化算法</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E207" s="16" t="inlineStr">
         <is>
-          <t>基于市场微结构理论动态调整bid-ask spread，流动性自适应调节，机器学习辅助报价优化</t>
+          <t>做市标的券池管理，流动性分级筛选，黑名单管理，临时暂停做市规则</t>
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G207" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G207" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H207" s="18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208" ht="28" customHeight="1">
@@ -15207,31 +15207,31 @@
       </c>
       <c r="C208" s="15" t="inlineStr">
         <is>
-          <t>F15-07</t>
+          <t>F15-08</t>
         </is>
       </c>
       <c r="D208" s="30" t="inlineStr">
         <is>
-          <t>债券过滤与筛选</t>
+          <t>做市义务实时监控</t>
         </is>
       </c>
       <c r="E208" s="16" t="inlineStr">
         <is>
-          <t>做市标的券池管理，流动性分级筛选，黑名单管理，临时暂停做市规则</t>
+          <t>实时监控做市义务完成情况（报价连续性/报价宽度/报价量达标），义务违规预警，监管报告生成</t>
         </is>
       </c>
       <c r="F208" s="16" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G208" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G208" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H208" s="18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="209" ht="28" customHeight="1">
@@ -15247,31 +15247,31 @@
       </c>
       <c r="C209" s="15" t="inlineStr">
         <is>
-          <t>F15-08</t>
+          <t>F15-09</t>
         </is>
       </c>
       <c r="D209" s="30" t="inlineStr">
         <is>
-          <t>做市义务实时监控</t>
+          <t>做市行情展示</t>
         </is>
       </c>
       <c r="E209" s="16" t="inlineStr">
         <is>
-          <t>实时监控做市义务完成情况（报价连续性/报价宽度/报价量达标），义务违规预警，监管报告生成</t>
+          <t>做市报价行情矩阵，实时价格展示，报价历史回放，市场最优报价对比，中签率统计</t>
         </is>
       </c>
       <c r="F209" s="16" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G209" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G209" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H209" s="18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="210" ht="28" customHeight="1">
@@ -15287,31 +15287,31 @@
       </c>
       <c r="C210" s="15" t="inlineStr">
         <is>
-          <t>F15-09</t>
+          <t>F15-10</t>
         </is>
       </c>
       <c r="D210" s="30" t="inlineStr">
         <is>
-          <t>做市行情展示</t>
+          <t>做市订单管理</t>
         </is>
       </c>
       <c r="E210" s="16" t="inlineStr">
         <is>
-          <t>做市报价行情矩阵，实时价格展示，报价历史回放，市场最优报价对比，中签率统计</t>
+          <t>做市委托生成、撤改、成交回报处理，订单状态实时跟踪，批量撤单，做市台账</t>
         </is>
       </c>
       <c r="F210" s="16" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G210" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G210" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H210" s="18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="211" ht="28" customHeight="1">
@@ -15327,31 +15327,31 @@
       </c>
       <c r="C211" s="15" t="inlineStr">
         <is>
-          <t>F15-10</t>
+          <t>F15-11</t>
         </is>
       </c>
       <c r="D211" s="30" t="inlineStr">
         <is>
-          <t>做市订单管理</t>
+          <t>库存风险实时管理</t>
         </is>
       </c>
       <c r="E211" s="16" t="inlineStr">
         <is>
-          <t>做市委托生成、撤改、成交回报处理，订单状态实时跟踪，批量撤单，做市台账</t>
+          <t>做市库存PnL实时监控，Delta对冲自动触发，库存敞口上限控制，实时盯市损益</t>
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G211" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G211" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H211" s="18" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="212" ht="28" customHeight="1">
@@ -15367,102 +15367,62 @@
       </c>
       <c r="C212" s="15" t="inlineStr">
         <is>
-          <t>F15-11</t>
+          <t>F15-12</t>
         </is>
       </c>
       <c r="D212" s="30" t="inlineStr">
         <is>
-          <t>库存风险实时管理</t>
+          <t>竞争力分析</t>
         </is>
       </c>
       <c r="E212" s="16" t="inlineStr">
         <is>
-          <t>做市库存PnL实时监控，Delta对冲自动触发，库存敞口上限控制，实时盯市损益</t>
+          <t>与市场最优报价对比，中签率分析，报价表现统计，策略调优建议，竞争对手报价分析</t>
         </is>
       </c>
       <c r="F212" s="16" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G212" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G212" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H212" s="18" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="213" ht="28" customHeight="1">
-      <c r="A213" s="16" t="inlineStr">
-        <is>
-          <t>做市商系统</t>
-        </is>
-      </c>
-      <c r="B213" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="C213" s="15" t="inlineStr">
-        <is>
-          <t>F15-12</t>
-        </is>
-      </c>
-      <c r="D213" s="30" t="inlineStr">
-        <is>
-          <t>竞争力分析</t>
-        </is>
-      </c>
-      <c r="E213" s="16" t="inlineStr">
-        <is>
-          <t>与市场最优报价对比，中签率分析，报价表现统计，策略调优建议，竞争对手报价分析</t>
-        </is>
-      </c>
-      <c r="F213" s="16" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G213" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H213" s="18" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="19" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="19" t="inlineStr">
         <is>
           <t>总计功能数 / Total Function Points</t>
         </is>
       </c>
-      <c r="H214" s="20">
-        <f>SUM(H3:H213)</f>
+      <c r="H213" s="20">
+        <f>SUM(H3:H212)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A131:H131"/>
-    <mergeCell ref="A144:H144"/>
+    <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A100:H100"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A201:H201"/>
-    <mergeCell ref="A190:H190"/>
-    <mergeCell ref="A214:G214"/>
-    <mergeCell ref="A160:H160"/>
+    <mergeCell ref="A130:H130"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A180:H180"/>
+    <mergeCell ref="A200:H200"/>
     <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A112:H112"/>
     <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A181:H181"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A189:H189"/>
+    <mergeCell ref="A111:H111"/>
     <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A168:H168"/>
-    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A159:H159"/>
+    <mergeCell ref="A213:G213"/>
+    <mergeCell ref="A167:H167"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19799,7 +19759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -20417,80 +20377,80 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F04-14</t>
+          <t>F04-15</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>绩效归因与风险计量</t>
+          <t>监管报表与风控日报</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>收益率曲线效应，信用利差分解，行业配置效应，个券择券，Carry &amp; Roll-down贡献</t>
+          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="41" t="inlineStr">
+      <c r="G22" s="42" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>D5. 风控基础设施</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>D5. 风控基础设施</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>F04-16</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>数据底座与IBOR集成</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="41" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H24" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>D4. 投后风险分析</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>F04-15</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>监管报表与风控日报</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="42" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>D5. 风控基础设施</t>
-        </is>
-      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="48" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -20500,17 +20460,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F04-16</t>
+          <t>F04-17</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>数据底座与IBOR集成</t>
+          <t>收益率曲线与波动率曲面</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
+          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr"/>
@@ -20538,28 +20498,28 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F04-17</t>
+          <t>F04-18</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>收益率曲线与波动率曲面</t>
+          <t>HPC计算网格</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
+          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H26" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -20576,28 +20536,28 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F04-18</t>
+          <t>F04-19</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>HPC计算网格</t>
+          <t>AI风险预警</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
+          <t>异常检测（ML模型），预测性分析，模式识别，智能告警，新业务合规风险预分析</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+      <c r="G27" s="41" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H27" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -20606,68 +20566,30 @@
       </c>
       <c r="J27" s="5" t="inlineStr"/>
     </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>D5. 风控基础设施</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>F04-19</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>AI风险预警</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>异常检测（ML模型），预测性分析，模式识别，智能告警，新业务合规风险预分析</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="41" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="40" t="inlineStr">
-        <is>
-          <t>合计 19项功能  |  P1: 19项  |  P2: 0项</t>
-        </is>
-      </c>
-      <c r="H29" s="20">
-        <f>SUM(H5:H28)</f>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>合计 18项功能  |  P1: 18项  |  P2: 0项</t>
+        </is>
+      </c>
+      <c r="H28" s="20">
+        <f>SUM(H5:H27)</f>
         <v/>
       </c>
-      <c r="I29" s="34" t="inlineStr"/>
-      <c r="J29" s="34" t="inlineStr"/>
+      <c r="I28" s="34" t="inlineStr"/>
+      <c r="J28" s="34" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A23:J23"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A24:J24"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -1143,7 +1143,7 @@
         <v>12</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>14</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>

--- a/Feasibility_analysis/FICC_Gap_Analysis.xlsx
+++ b/Feasibility_analysis/FICC_Gap_Analysis.xlsx
@@ -925,7 +925,7 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>整个FICC平台的账薄主干，26项功能覆盖持仓/现金/估值/事件/对账/监管报送/试算/抵押品管理全链路；合规检查规则与执行由M06负责，情景P&amp;L分析由M04+M07负责，IBOR仅提供数据</t>
+          <t>整个FICC平台的账薄主干，27项功能（新增F01-29数据质量监控）覆盖持仓/现金/估值/事件/对账/监管报送/试算/抵押品/数据质量全链路；核心创新：ML-based reconciliation (F01-14)，DQ-first foundation (F01-29)，CA-aware sandbox (F01-25)；合规检查规则与执行由M06负责，情景P&amp;L分析由M04+M07负责，IBOR为SSoT数据源</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>替代衡泰老旧系统，信创切入口；覆盖投前/投中/投后全生命周期风险管理，新增信用风险计量（CVA/PD/LGD/IFRS9 ECL）和限额治理全生命周期工作流；对应PPT Slide 52</t>
+          <t>替代衡泰老旧系统，信创切入口；覆盖投前/投中/投后全生命周期风险管理，新增信用风险计量（CVA/PD/LGD/IFRS9 ECL）、限额治理全生命周期、VaR回测框架（F04-10增强）、模型治理（新增F04-23）、pre-trade impact（Phase 2 F04-22）；对应PPT Slide 52</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>蒙特卡洛/有限差分，替代衡泰核心，覆盖权益/利率/大宗商品/外汇/衍生品全品种，新增XVA引擎（CVA/DVA/FVA）和模型验证/P&amp;L Explain；对应PPT Slide 56</t>
+          <t>蒙特卡洛/有限差分，替代衡泰核心，覆盖权益/利率/大宗商品/外汇/衍生品全品种；Phase 1强化：曲线平滑+套利检测（F09-04增强），DQ-first数据治理；新增XVA引擎（CVA/DVA/FVA）、模型验证/P&amp;L Explain、多曲线折扣(Phase 3)；对应PPT Slide 56</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>战略定位：蒙特卡洛/有限差分，替代衡泰核心，覆盖权益/利率/大宗商品/外汇/衍生品全品种，新增XVA引擎（CVA/DVA/FVA）和模型验证/P&amp;L Explain；对应PPT Slide 56   |   来源：Slide 56</t>
+          <t>战略定位：蒙特卡洛/有限差分，替代衡泰核心，覆盖权益/利率/大宗商品/外汇/衍生品全品种；Phase 1强化：曲线平滑+套利检测（F09-04增强），DQ-first数据治理；新增XVA引擎（CVA/DVA/FVA）、模型验证/P&amp;L Explain、多曲线折扣(Phase 3)；对应PPT Slide 56   |   来源：Slide 56</t>
         </is>
       </c>
     </row>
@@ -4482,10 +4482,14 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr"/>
+          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务；新增automated curve smoothing（spline tension controls, Piecewise-Linear Moneyness interpolation）保证曲线平滑性；arbitrage validation pipeline：overnight batch after daily curve recalibration进行：(1)negative forward detection（无负利率），(2)cheap bond detection（price &lt; dirty price floor），(3)cross-curve arbitrage checks；validation failure自动trigger manual review workflow；clean curve snapshot materialized in Redis for intraday consumption；smoothness metrics + arbitrage violations reported to F01-29 DQ Dashboard</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Curve smoothing ensures no arbitrage violations for consecutive &gt;30 days，negative forward detection accuracy 100%，cheap bond detection accuracy &gt;99%，arbitrage validation completion &lt;10min after overnight curve build，clean curve snapshots ready by 6:30am for market open，DQ metrics push to F01-29 real-time</t>
+        </is>
+      </c>
       <c r="F10" s="11" t="inlineStr"/>
       <c r="G10" s="28" t="inlineStr">
         <is>
@@ -4493,7 +4497,7 @@
         </is>
       </c>
       <c r="H10" s="13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
@@ -7670,7 +7674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8322,12 +8326,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>与中登（交易所债券）、中债登（银行间债券）日终持仓对账，差异自动分类（未交割/错误/缺漏）并推送告警</t>
+          <t>与中登（交易所债券）、中债登（银行间债券）日终持仓对账，差异自动分类（未交割/错误/缺漏）并推送告警；新增ML-based break matching（容差窗口/多规则自动路由）、Temporal-backed exception workflow（自动→经理审批→CRO升级）、Reconciliation Dashboard（实时break aging/SLA追踪）；集成F01-29 DQ监控作为前置条件，确保数据质量后再进行对账</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>日终对账完成时间&lt;8:00AM，差异识别率100%，自动匹配率&gt;95%</t>
+          <t>日终对账完成时间&lt;6:00AM，差异识别率&gt;98%，break自动解决率&gt;80%（ML匹配），exception routing &lt;30s，manager review trigger by T+2</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -8336,7 +8340,7 @@
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
@@ -8362,7 +8366,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>投资账薄（实时）与会计账薄（已结算）差异对比，差异原因自动分类（未结算/估值差/计提差），供中台复核</t>
+          <t>投资账薄（实时）与会计账薄（已结算）差异对比，差异原因自动分类（未结算/估值差/计提差），供中台复核；exception workflow集成：差异超阈值自动流转F01-14工作流；数据质量指标推送至F01-29 DQ Dashboard</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -8727,7 +8731,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>沙箱持仓生效&lt;2s，MtM误差&lt;0.1%，≥10方案并行无数据污染</t>
+          <t>沙箱持仓生效&lt;2s，MtM误差&lt;0.1%，≥10方案并行无数据污染，scenario P&amp;L计算&lt;5s，数据流向M04/M07 &lt;1s，支持≥5种公司行为(split/merge/distribution/rights/spinoff)，支持10+市场冲击场景(yield curve parallel/butterfly/bear/bull, FX moves, spread moves)</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
@@ -8736,7 +8740,7 @@
         </is>
       </c>
       <c r="H28" s="8" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1">
@@ -8779,51 +8783,51 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>IBOR投资账薄管理</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>F01-29</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>数据质量监控与SLA治理</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>跨层级实时监控IBOR数据质量：staleness监控（行情/估值超过5s老化触发告警），completeness检测（缺失持仓&gt;1%触发告警），continuity检测（Kafka dropped events/consumer lag detection）；Dashboard展示：数据源实时健康度、SLA compliance heatmap（按行情/估值/托管行接口分别追踪），alert路由至duty team；集成至F01-14 reconciliation engine（作为DQ issues前置条件）和M04风险计量平台（signal data freshness问题，防止垃圾数据进入风险计算）；支持Great Expectations + Deequ开源数据质量框架</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Staleness detection &lt;10s，completeness check &lt;30s，alert transmission &lt;1min，DQ dashboard real-time刷新&lt;5s，覆盖全部data_model层级(Transaction/Trade/Position/Asset/MarketData/Collateral)，告警路由命中率&gt;99%</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>【P1】 现券交易系统  (Bond Trading System)</t>
         </is>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>现券交易系统</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>F02-01</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>银行间双边报价</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>CFETS/X-Bond两板块双边报价，支持询价(RFQ)和竞价模式，报价有效期自动管理，批量报价维护与撤单</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>报价发出到CFETS确认&lt;200ms，批量报价支持≥100条/次</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
@@ -8839,31 +8843,31 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>F02-02</t>
+          <t>F02-01</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>交易所债券委托</t>
+          <t>银行间双边报价</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>上交所/深交所债券买卖下单，支持限价/市价/条件单三类订单，撤单与改单，ETF债券联接与综合协议交易</t>
+          <t>CFETS/X-Bond两板块双边报价，支持询价(RFQ)和竞价模式，报价有效期自动管理，批量报价维护与撤单</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>委托响应&lt;100ms，撤单成功率&gt;99.5%</t>
-        </is>
-      </c>
-      <c r="G32" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>报价发出到CFETS确认&lt;200ms，批量报价支持≥100条/次</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H32" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
@@ -8879,22 +8883,22 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>F02-07</t>
+          <t>F02-02</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>RFQ询价管理</t>
+          <t>交易所债券委托</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>支持发起/接收/应答全链路RFQ流程，询价对象多选，报价有效期倒计时，最优报价自动高亮，历史询价记录检索</t>
+          <t>上交所/深交所债券买卖下单，支持限价/市价/条件单三类订单，撤单与改单，ETF债券联接与综合协议交易</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>RFQ全流程(发起到成交)端到端&lt;30s，历史记录保存≥1年</t>
+          <t>委托响应&lt;100ms，撤单成功率&gt;99.5%</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
@@ -8919,31 +8923,31 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>F02-08</t>
+          <t>F02-07</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Bond Connect跨境接入</t>
+          <t>RFQ询价管理</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>对接香港债券通(北向通)，支持境外机构通过Bond Connect参与银行间债券交易，含SWIFT报文生成与境外结算指令</t>
+          <t>支持发起/接收/应答全链路RFQ流程，询价对象多选，报价有效期倒计时，最优报价自动高亮，历史询价记录检索</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Bond Connect成交回报处理&lt;500ms，SWIFT报文生成准确率100%</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>RFQ全流程(发起到成交)端到端&lt;30s，历史记录保存≥1年</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H34" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
@@ -8959,22 +8963,22 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>F02-09</t>
+          <t>F02-08</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>订单全生命周期管理</t>
+          <t>Bond Connect跨境接入</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>订单录入/修改/撤销/挂单状态机，支持部分成交跟踪，订单有效期(GTC/GTD/IOC/FOK)配置，订单历史完整审计</t>
+          <t>对接香港债券通(北向通)，支持境外机构通过Bond Connect参与银行间债券交易，含SWIFT报文生成与境外结算指令</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>订单状态更新延迟&lt;100ms，状态机覆盖全生命周期，历史可回溯≥1年</t>
+          <t>Bond Connect成交回报处理&lt;500ms，SWIFT报文生成准确率100%</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
@@ -8983,7 +8987,7 @@
         </is>
       </c>
       <c r="H35" s="8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
@@ -8999,31 +9003,31 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>F02-10</t>
+          <t>F02-09</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>大宗/协议交易</t>
+          <t>订单全生命周期管理</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>银行间大宗交易报价协商，双边确认，超大额交易分笔拆单执行，协议交易备案与记录</t>
+          <t>订单录入/修改/撤销/挂单状态机，支持部分成交跟踪，订单有效期(GTC/GTD/IOC/FOK)配置，订单历史完整审计</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>大宗交易协商流程≤5步确认，拆单执行计划自动生成</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>订单状态更新延迟&lt;100ms，状态机覆盖全生命周期，历史可回溯≥1年</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H36" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
@@ -9039,22 +9043,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>F02-11</t>
+          <t>F02-10</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>篮子交易与批量下单</t>
+          <t>大宗/协议交易</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>多债券组合同时建仓/调仓，篮子订单按权重/金额/数量三种模式分配，批量状态监控与部分失败重试</t>
+          <t>银行间大宗交易报价协商，双边确认，超大额交易分笔拆单执行，协议交易备案与记录</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>篮子交易支持≥50只债券同批，批量下单耗时&lt;5s</t>
+          <t>大宗交易协商流程≤5步确认，拆单执行计划自动生成</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
@@ -9079,31 +9083,31 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>F02-12</t>
+          <t>F02-11</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>条件单与算法单接口</t>
+          <t>篮子交易与批量下单</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>价格触发条件单（达到目标YTM/价格自动下单），预留TWAP/VWAP算法交易接口，算法执行进度实时展示</t>
+          <t>多债券组合同时建仓/调仓，篮子订单按权重/金额/数量三种模式分配，批量状态监控与部分失败重试</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>条件触发延迟&lt;1s，算法接口支持主流算法交易供应商标准协议</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>篮子交易支持≥50只债券同批，批量下单耗时&lt;5s</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H38" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
@@ -9119,31 +9123,31 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>F02-03</t>
+          <t>F02-12</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>收益率/价格计算</t>
+          <t>条件单与算法单接口</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>全品种YTM/全价/净价双向转换，含权债修正久期，多计息基准(ACT/365/ACT/360/30/360)精确计算</t>
+          <t>价格触发条件单（达到目标YTM/价格自动下单），预留TWAP/VWAP算法交易接口，算法执行进度实时展示</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>YTM计算与Bloomberg基准误差&lt;0.1bps，含权债定价覆盖主流含权结构</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>条件触发延迟&lt;1s，算法接口支持主流算法交易供应商标准协议</t>
+        </is>
+      </c>
+      <c r="G39" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H39" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
@@ -9159,31 +9163,31 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>F02-13</t>
+          <t>F02-03</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>特殊品种定价</t>
+          <t>收益率/价格计算</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>ABS/ABN资产支持证券、永续债、可转债、可交换债、二级资本债定价，含信用利差/流动性溢价调整</t>
+          <t>全品种YTM/全价/净价双向转换，含权债修正久期，多计息基准(ACT/365/ACT/360/30/360)精确计算</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>特殊品种覆盖率100%，定价结果与市场成交价偏差统计&lt;5bps</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>YTM计算与Bloomberg基准误差&lt;0.1bps，含权债定价覆盖主流含权结构</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H40" s="8" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
@@ -9199,22 +9203,22 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>F02-14</t>
+          <t>F02-13</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>实时浮盈浮亏</t>
+          <t>特殊品种定价</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>成交后即时PnL计算，含已实现/未实现分拆，按账户/策略/品种多维度汇总，日内PnL归因(价格/利息/汇率)</t>
+          <t>ABS/ABN资产支持证券、永续债、可转债、可交换债、二级资本债定价，含信用利差/流动性溢价调整</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>PnL更新延迟&lt;1s，已实现/未实现分拆误差为零</t>
+          <t>特殊品种覆盖率100%，定价结果与市场成交价偏差统计&lt;5bps</t>
         </is>
       </c>
       <c r="G41" s="23" t="inlineStr">
@@ -9223,7 +9227,7 @@
         </is>
       </c>
       <c r="H41" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
@@ -9239,31 +9243,31 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>F02-15</t>
+          <t>F02-14</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>利率敏感性指标</t>
+          <t>实时浮盈浮亏</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>DV01/修正久期/凸性实时计算，组合层面利率风险汇总，BP-level利率冲击情景分析</t>
+          <t>成交后即时PnL计算，含已实现/未实现分拆，按账户/策略/品种多维度汇总，日内PnL归因(价格/利息/汇率)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>敏感性指标与Bloomberg基准误差&lt;1%，组合汇总更新&lt;2s</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>PnL更新延迟&lt;1s，已实现/未实现分拆误差为零</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H42" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1">
@@ -9279,22 +9283,22 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>F02-04</t>
+          <t>F02-15</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>交易前风险校验</t>
+          <t>利率敏感性指标</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>调用事前风控接口，单笔限额/账户集中度/利率风险DV01/信用评级限额实时拦截，风控拦截阻断下单</t>
+          <t>DV01/修正久期/凸性实时计算，组合层面利率风险汇总，BP-level利率冲击情景分析</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>风控校验响应&lt;10ms，零漏拦，误报率&lt;0.05%</t>
+          <t>敏感性指标与Bloomberg基准误差&lt;1%，组合汇总更新&lt;2s</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
@@ -9303,7 +9307,7 @@
         </is>
       </c>
       <c r="H43" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
@@ -9319,22 +9323,22 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>F02-16</t>
+          <t>F02-04</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>合规规则嵌入</t>
+          <t>交易前风险校验</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>投资授权范围/禁投清单/单券集中度上限/评级下限嵌入下单流程，不符合规则自动弹窗说明并阻断，支持规则热更新</t>
+          <t>调用事前风控接口，单笔限额/账户集中度/利率风险DV01/信用评级限额实时拦截，风控拦截阻断下单</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>合规规则覆盖投资授权书100%条款，规则热更新生效&lt;1min</t>
+          <t>风控校验响应&lt;10ms，零漏拦，误报率&lt;0.05%</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
@@ -9343,7 +9347,7 @@
         </is>
       </c>
       <c r="H44" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
@@ -9359,22 +9363,22 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>F02-17</t>
+          <t>F02-16</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>流动性与市场影响评估</t>
+          <t>合规规则嵌入</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>大额交易前评估目标债券流动性（换手率/买卖价差/存量规模），估算市场冲击成本，超阈值触发投资经理二次确认</t>
+          <t>投资授权范围/禁投清单/单券集中度上限/评级下限嵌入下单流程，不符合规则自动弹窗说明并阻断，支持规则热更新</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>流动性评估结果&lt;500ms，大额阈值可配置，确认记录100%留痕</t>
+          <t>合规规则覆盖投资授权书100%条款，规则热更新生效&lt;1min</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
@@ -9399,27 +9403,27 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>F02-05</t>
+          <t>F02-17</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>交易确认与指令生成</t>
+          <t>流动性与市场影响评估</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>成交确认后自动生成DVP/FOP清算指令，含托管账户/资金账户/ISIN/结算金额完整要素，推送清算结算模块</t>
+          <t>大额交易前评估目标债券流动性（换手率/买卖价差/存量规模），估算市场冲击成本，超阈值触发投资经理二次确认</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>成交到指令生成延迟&lt;500ms，指令要素完整率100%</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>流动性评估结果&lt;500ms，大额阈值可配置，确认记录100%留痕</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H46" s="8" t="n">
@@ -9439,22 +9443,22 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>F02-18</t>
+          <t>F02-05</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>STP直通处理</t>
+          <t>交易确认与指令生成</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>成交→IBOR更新→清算指令全链路无人工干预，异常（金额差异/账户不匹配）自动隔离进入人工处理队列，STP率实时监控</t>
+          <t>成交确认后自动生成DVP/FOP清算指令，含托管账户/资金账户/ISIN/结算金额完整要素，推送清算结算模块</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>STP直通率&gt;98%，异常隔离延迟&lt;1min，人工处理队列可视化</t>
+          <t>成交到指令生成延迟&lt;500ms，指令要素完整率100%</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
@@ -9463,7 +9467,7 @@
         </is>
       </c>
       <c r="H47" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
@@ -9479,31 +9483,31 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>F02-19</t>
+          <t>F02-18</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>成交修正与错单处理</t>
+          <t>STP直通处理</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>支持T+0错单撤销/修改，含双级审批工作流，修正后重新触发STP链路，错单历史与原因分类统计</t>
+          <t>成交→IBOR更新→清算指令全链路无人工干预，异常（金额差异/账户不匹配）自动隔离进入人工处理队列，STP率实时监控</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>错单处理T+0完成，审批链≤2级，修正后STP重触发成功率&gt;99%</t>
-        </is>
-      </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>STP直通率&gt;98%，异常隔离延迟&lt;1min，人工处理队列可视化</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H48" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
@@ -9519,22 +9523,22 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>F02-20</t>
+          <t>F02-19</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>跨市场净额轧差</t>
+          <t>成交修正与错单处理</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>同日同券银行间+交易所成交净额轧差计算，减少资金占用，净额结果推送清算系统，轧差差异自动核对</t>
+          <t>支持T+0错单撤销/修改，含双级审批工作流，修正后重新触发STP链路，错单历史与原因分类统计</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>净额轧差计算准确率100%，与清算系统差异核对通过率&gt;99.9%</t>
+          <t>错单处理T+0完成，审批链≤2级，修正后STP重触发成功率&gt;99%</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
@@ -9559,22 +9563,22 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>F02-06</t>
+          <t>F02-20</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>做市报价接口</t>
+          <t>跨市场净额轧差</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>支持双边报价做市模式，库存实时刷新驱动报价价差自动调整，与做市商系统(Module 15)预留标准接口</t>
+          <t>同日同券银行间+交易所成交净额轧差计算，减少资金占用，净额结果推送清算系统，轧差差异自动核对</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>报价刷新延迟&lt;500ms，做市接口符合Module 15做市商系统对接规范</t>
+          <t>净额轧差计算准确率100%，与清算系统差异核对通过率&gt;99.9%</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
@@ -9583,7 +9587,7 @@
         </is>
       </c>
       <c r="H50" s="8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
@@ -9599,22 +9603,22 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>F02-21</t>
+          <t>F02-06</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>库存管理与头寸监控</t>
+          <t>做市报价接口</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>做市库存实时监控，目标库存区间配置，超出区间触发预警，库存归零/超限自动暂停报价，日内库存P&amp;L实时展示</t>
+          <t>支持双边报价做市模式，库存实时刷新驱动报价价差自动调整，与做市商系统(Module 15)预留标准接口</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>库存监控更新&lt;1s，超限预警触发率100%，暂停报价延迟&lt;500ms</t>
+          <t>报价刷新延迟&lt;500ms，做市接口符合Module 15做市商系统对接规范</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
@@ -9623,7 +9627,7 @@
         </is>
       </c>
       <c r="H51" s="8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1">
@@ -9639,22 +9643,22 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>F02-22</t>
+          <t>F02-21</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>报价P&amp;L归因</t>
+          <t>库存管理与头寸监控</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>做市盈亏拆分（买卖价差收益/库存持有收益/汇率收益），按券种/期限/信用等级多维度统计，日/月做市绩效报告</t>
+          <t>做市库存实时监控，目标库存区间配置，超出区间触发预警，库存归零/超限自动暂停报价，日内库存P&amp;L实时展示</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>P&amp;L归因覆盖100%做市成交，维度下钻≥4级，日报T+0生成</t>
+          <t>库存监控更新&lt;1s，超限预警触发率100%，暂停报价延迟&lt;500ms</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
@@ -9679,22 +9683,22 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>F02-23</t>
+          <t>F02-22</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>实时行情接入</t>
+          <t>报价P&amp;L归因</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>接入AMD/Bloomberg实时债券成交行情、报价行情，标准化清洗，异常跳价过滤，推送至交易终端与定价层</t>
+          <t>做市盈亏拆分（买卖价差收益/库存持有收益/汇率收益），按券种/期限/信用等级多维度统计，日/月做市绩效报告</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>行情延迟&lt;1s，异常行情自动过滤告警，数据完整性&gt;99.9%</t>
+          <t>P&amp;L归因覆盖100%做市成交，维度下钻≥4级，日报T+0生成</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
@@ -9719,22 +9723,22 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>F02-24</t>
+          <t>F02-23</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>利率曲线与信用利差</t>
+          <t>实时行情接入</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>中债估值曲线/国债收益率曲线/信用利差矩阵实时推送至交易终端，支持手动覆盖曲线点位（需审批），历史曲线回放</t>
+          <t>接入AMD/Bloomberg实时债券成交行情、报价行情，标准化清洗，异常跳价过滤，推送至交易终端与定价层</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;2s，历史曲线回放支持任意交易日，覆盖率100%</t>
+          <t>行情延迟&lt;1s，异常行情自动过滤告警，数据完整性&gt;99.9%</t>
         </is>
       </c>
       <c r="G54" s="24" t="inlineStr">
@@ -9759,31 +9763,31 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>F02-25</t>
+          <t>F02-24</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>债券基础数据维护</t>
+          <t>利率曲线与信用利差</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>债券要素（ISIN/票面/期限/评级/含权条款/付息安排/发行人）自动从中债登/Wind同步，异动实时告警，人工维护通道与审批</t>
+          <t>中债估值曲线/国债收益率曲线/信用利差矩阵实时推送至交易终端，支持手动覆盖曲线点位（需审批），历史曲线回放</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>新券上市后基础数据就绪&lt;2h，要素同步准确率&gt;99.9%</t>
-        </is>
-      </c>
-      <c r="G55" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>曲线更新延迟&lt;2s，历史曲线回放支持任意交易日，覆盖率100%</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H55" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
@@ -9799,31 +9803,31 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>F02-26</t>
+          <t>F02-25</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>交易执行质量分析(TCA)</t>
+          <t>债券基础数据维护</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>成交价vs基准价(VWAP/到达价/中债估值)偏差统计，执行成本量化，滑点分析，按交易员/策略/品种多维度排名</t>
+          <t>债券要素（ISIN/票面/期限/评级/含权条款/付息安排/发行人）自动从中债登/Wind同步，异动实时告警，人工维护通道与审批</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>TCA覆盖100%成交记录，基准价偏差计算准确，报告T+1生成</t>
-        </is>
-      </c>
-      <c r="G56" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>新券上市后基础数据就绪&lt;2h，要素同步准确率&gt;99.9%</t>
+        </is>
+      </c>
+      <c r="G56" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H56" s="8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1">
@@ -9839,31 +9843,31 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>F02-27</t>
+          <t>F02-26</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>监管报送支持</t>
+          <t>交易执行质量分析(TCA)</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>按CFETS/人民银行/证监会格式提取成交数据，含日成交报告/大额交易申报/异常交易上报，定时自动推送，报送状态跟踪</t>
+          <t>成交价vs基准价(VWAP/到达价/中债估值)偏差统计，执行成本量化，滑点分析，按交易员/策略/品种多维度排名</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>报送数据与成交记录一致性100%，定时推送准时率&gt;99.9%，推送失败自动告警重试</t>
-        </is>
-      </c>
-      <c r="G57" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>TCA覆盖100%成交记录，基准价偏差计算准确，报告T+1生成</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H57" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1">
@@ -9879,78 +9883,78 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
+          <t>F02-27</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>监管报送支持</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>按CFETS/人民银行/证监会格式提取成交数据，含日成交报告/大额交易申报/异常交易上报，定时自动推送，报送状态跟踪</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>报送数据与成交记录一致性100%，定时推送准时率&gt;99.9%，推送失败自动告警重试</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>现券交易系统</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
           <t>F02-28</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>交易统计分析</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>日/月/季成交量统计（按品种/期限/评级/账户/交易员维度），换手率趋势，市场份额分析，可视化Dashboard与Excel导出</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>统计报表T+1生成，支持≥6个分析维度，Excel导出格式标准</t>
         </is>
       </c>
-      <c r="G58" s="25" t="inlineStr">
+      <c r="G59" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H58" s="8" t="n">
+      <c r="H59" s="8" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="26" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="26" t="inlineStr">
         <is>
           <t>【P2】 FOF投资系统  (FOF Investment System)</t>
         </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
-        <is>
-          <t>FOF投资系统</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>F03-01</t>
-        </is>
-      </c>
-      <c r="D60" s="27" t="inlineStr">
-        <is>
-          <t>管理人与基金基础信息</t>
-        </is>
-      </c>
-      <c r="E60" s="11" t="inlineStr">
-        <is>
-          <t>管理人黑名单维护，基金策略分类，基金基础要素（规模/净值/评级）录入与更新，管理人信息库</t>
-        </is>
-      </c>
-      <c r="F60" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G60" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H60" s="13" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1">
@@ -9966,31 +9970,31 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>F03-02</t>
+          <t>F03-01</t>
         </is>
       </c>
       <c r="D61" s="27" t="inlineStr">
         <is>
-          <t>基金资产信息获取</t>
+          <t>管理人与基金基础信息</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>通过邮箱/API自动获取基金资产报告，解析持仓明细并入库，多来源数据合并去重，导入工具</t>
+          <t>管理人黑名单维护，基金策略分类，基金基础要素（规模/净值/评级）录入与更新，管理人信息库</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G61" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G61" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H61" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1">
@@ -10006,31 +10010,31 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>F03-03</t>
+          <t>F03-02</t>
         </is>
       </c>
       <c r="D62" s="27" t="inlineStr">
         <is>
-          <t>子基金持仓穿透</t>
+          <t>基金资产信息获取</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>穿透底层基金持仓至个券/个股层面，合并计算组合总敞口，支持集中度与评级分布分析</t>
+          <t>通过邮箱/API自动获取基金资产报告，解析持仓明细并入库，多来源数据合并去重，导入工具</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G62" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G62" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H62" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1">
@@ -10046,31 +10050,31 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>F03-04</t>
+          <t>F03-03</t>
         </is>
       </c>
       <c r="D63" s="27" t="inlineStr">
         <is>
-          <t>交易录入与审核</t>
+          <t>子基金持仓穿透</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>申购/赎回/换仓交易录入，交易明细管理，双级审核工作流（投资助理录入→风控复核），审批记录留痕</t>
+          <t>穿透底层基金持仓至个券/个股层面，合并计算组合总敞口，支持集中度与评级分布分析</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G63" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G63" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H63" s="13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
@@ -10086,17 +10090,17 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>F03-05</t>
+          <t>F03-04</t>
         </is>
       </c>
       <c r="D64" s="27" t="inlineStr">
         <is>
-          <t>申赎情况跟踪</t>
+          <t>交易录入与审核</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>子基金申购/赎回状态全生命周期跟踪，到账确认，净值更新后自动触发持仓重算</t>
+          <t>申购/赎回/换仓交易录入，交易明细管理，双级审核工作流（投资助理录入→风控复核），审批记录留痕</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr">
@@ -10110,7 +10114,7 @@
         </is>
       </c>
       <c r="H64" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
@@ -10126,17 +10130,17 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>F03-06</t>
+          <t>F03-05</t>
         </is>
       </c>
       <c r="D65" s="27" t="inlineStr">
         <is>
-          <t>组合风控报告生成</t>
+          <t>申赎情况跟踪</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>按管理人策略限制/投资占比限制/白名单分类/子基金申赎情况生成风控日报和周报</t>
+          <t>子基金申购/赎回状态全生命周期跟踪，到账确认，净值更新后自动触发持仓重算</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -10150,7 +10154,7 @@
         </is>
       </c>
       <c r="H65" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
@@ -10166,78 +10170,78 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
+          <t>F03-06</t>
+        </is>
+      </c>
+      <c r="D66" s="27" t="inlineStr">
+        <is>
+          <t>组合风控报告生成</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>按管理人策略限制/投资占比限制/白名单分类/子基金申赎情况生成风控日报和周报</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G66" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H66" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>FOF投资系统</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
           <t>F03-07</t>
         </is>
       </c>
-      <c r="D66" s="27" t="inlineStr">
+      <c r="D67" s="27" t="inlineStr">
         <is>
           <t>报告推送与查阅</t>
         </is>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E67" s="11" t="inlineStr">
         <is>
           <t>风控日报/周报自动推送给风控人员，支持在线查看与下载，历史报告归档查询</t>
         </is>
       </c>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F67" s="11" t="inlineStr">
         <is>
           <t>功能测试通过</t>
         </is>
       </c>
-      <c r="G66" s="25" t="inlineStr">
+      <c r="G67" s="25" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H66" s="13" t="n">
+      <c r="H67" s="13" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="22" t="inlineStr">
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="22" t="inlineStr">
         <is>
           <t>【P1】 FICC风险计量平台  (FICC Risk Measurement Platform)</t>
         </is>
-      </c>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>FICC风险计量平台</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>F04-01</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>组合What-if分析</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>What-if情景建模，Duration &amp; Convexity影响分析，VaR贡献分解，风险因子敞口，集中度分析</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G68" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
@@ -10253,17 +10257,17 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>F04-02</t>
+          <t>F04-01</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>授权敞口分析</t>
+          <t>组合What-if分析</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>交易前限额验证，交易对手/集中度/监管/组合约束多维度限额检查，Pre-trade拦截</t>
+          <t>What-if情景建模，Duration &amp; Convexity影响分析，VaR贡献分解，风险因子敞口，集中度分析</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
@@ -10277,7 +10281,7 @@
         </is>
       </c>
       <c r="H69" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1">
@@ -10293,31 +10297,31 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>F04-03</t>
+          <t>F04-02</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>投资预测分析</t>
+          <t>授权敞口分析</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>P&amp;L与风险归因预测建模，收益率曲线/利差/波动率因子预测，组合构建优化，多情景对比分析</t>
+          <t>交易前限额验证，交易对手/集中度/监管/组合约束多维度限额检查，Pre-trade拦截</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G70" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G70" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H70" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1">
@@ -10333,17 +10337,17 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>F04-04</t>
+          <t>F04-03</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>实时风险计量</t>
+          <t>投资预测分析</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Real-time DV01/CS01，Live VaR，Dynamic Greeks，日内P&amp;L与归因，风险限额利用率实时展示</t>
+          <t>P&amp;L与风险归因预测建模，收益率曲线/利差/波动率因子预测，组合构建优化，多情景对比分析</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -10357,7 +10361,7 @@
         </is>
       </c>
       <c r="H71" s="8" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" ht="28" customHeight="1">
@@ -10373,31 +10377,31 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>F04-05</t>
+          <t>F04-04</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>交易对手风险实时监控</t>
+          <t>实时风险计量</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>实时敞口聚合，抵押品监控，信用限额使用率，结算风险，净额结算协议管理</t>
+          <t>Real-time DV01/CS01，Live VaR，Dynamic Greeks，日内P&amp;L与归因，风险限额利用率实时展示</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G72" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G72" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H72" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" ht="28" customHeight="1">
@@ -10413,17 +10417,17 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>F04-06</t>
+          <t>F04-05</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>流动性分析与交易成本</t>
+          <t>交易对手风险实时监控</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>执行风险监控，市场冲击分析，流动性成本追踪，滑点计量，最优执行合规</t>
+          <t>实时敞口聚合，抵押品监控，信用限额使用率，结算风险，净额结算协议管理</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -10437,7 +10441,7 @@
         </is>
       </c>
       <c r="H73" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" ht="28" customHeight="1">
@@ -10453,17 +10457,17 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>F04-07</t>
+          <t>F04-06</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>实时风险全景图</t>
+          <t>流动性分析与交易成本</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>实时持仓追踪，流式风险指标，实时限额监控，告警管理，异常跟踪仪表板</t>
+          <t>执行风险监控，市场冲击分析，流动性成本追踪，滑点计量，最优执行合规</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
@@ -10493,31 +10497,31 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>F04-08</t>
+          <t>F04-07</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>DV01/CS01计算</t>
+          <t>实时风险全景图</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>dPV/dy价格敏感度，信用利差敏感度，分桶移动与关键期限，平行与非平行冲击</t>
+          <t>实时持仓追踪，流式风险指标，实时限额监控，告警管理，异常跟踪仪表板</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G75" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G75" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H75" s="8" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" ht="28" customHeight="1">
@@ -10533,17 +10537,17 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>F04-09</t>
+          <t>F04-08</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Greeks与敏感度计算</t>
+          <t>DV01/CS01计算</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，覆盖固收全品种与衍生品</t>
+          <t>dPV/dy价格敏感度，信用利差敏感度，分桶移动与关键期限，平行与非平行冲击</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -10557,7 +10561,7 @@
         </is>
       </c>
       <c r="H76" s="8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" ht="28" customHeight="1">
@@ -10573,17 +10577,17 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>F04-10</t>
+          <t>F04-09</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>VaR模型</t>
+          <t>Greeks与敏感度计算</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>参数法/历史模拟法/蒙特卡洛三模式，Expected Shortfall (ES)，回测与例外检验</t>
+          <t>Delta/Gamma/Vega/Theta/Rho分布式实时计算，覆盖固收全品种与衍生品</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -10597,7 +10601,7 @@
         </is>
       </c>
       <c r="H77" s="8" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" ht="28" customHeight="1">
@@ -10613,31 +10617,31 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>F04-11</t>
+          <t>F04-10</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>压力测试与情景分析</t>
+          <t>VaR模型</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>内置历史情景（GFC/COVID-19/利率冲击），假设情景（曲线扭转/利差走阔），反向压力测试</t>
+          <t>参数法/历史模拟法/蒙特卡洛三模式，Expected Shortfall；integrated daily backtesting framework：daily actual P&amp;L vs predicted VaR tracking，exception flagging and reporting；quarterly Kupiec POF (Proportion of Failures) statistical test per regulatory standard；model exception log with severity levels，&gt;3 exceptions/quarter triggers automatic re-calibration workflow to F04-23；VaR model validation reports auto-generated for regulatory submission (Basel III backtesting rules, FRTB internal model requirements)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G78" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>Daily backtest completion &lt;6:00AM，exception detection accuracy &gt;95%，Kupiec POF test run quarterly with statistical documentation，regulatory reports auto-generated for compliance，model exception escalation &lt;1h from detection</t>
+        </is>
+      </c>
+      <c r="G78" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H78" s="8" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" ht="28" customHeight="1">
@@ -10653,17 +10657,17 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>F04-12</t>
+          <t>F04-11</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>估值与盈亏分解</t>
+          <t>压力测试与情景分析</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Carry &amp; Roll-down，曲线效应，信用利差贡献，择券贡献，基于因子的盈亏多维分解</t>
+          <t>内置历史情景（GFC/COVID-19/利率冲击），假设情景（曲线扭转/利差走阔），反向压力测试</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -10677,7 +10681,7 @@
         </is>
       </c>
       <c r="H79" s="8" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" ht="28" customHeight="1">
@@ -10693,31 +10697,31 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>F04-20</t>
+          <t>F04-12</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>信用风险计量（CVA/PD/LGD）</t>
+          <t>估值与盈亏分解</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>债券组合信用风险：基于历史迁移矩阵的发行人PD（违约概率）/LGD（违约损失率）估算，IFRS 9三阶段分类（Stage 1/2/3）预期信用损失（ECL）计算；OTC衍生品CVA（信用估值调整）/DVA（借方估值调整）：基于蒙特卡洛模拟的预期正敞口EPE × PD × LGD，信用迁移风险（1年/3年迁移矩阵压力测试）</t>
+          <t>Carry &amp; Roll-down，曲线效应，信用利差贡献，择券贡献，基于因子的盈亏多维分解</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>CVA计算与对手方差异&lt;1%，IFRS 9 ECL覆盖全债券持仓，PD/LGD数据源可追溯</t>
-        </is>
-      </c>
-      <c r="G80" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H80" s="8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" ht="28" customHeight="1">
@@ -10733,31 +10737,31 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>F04-13</t>
+          <t>F04-20</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>历史风险回溯</t>
+          <t>信用风险计量（CVA/PD/LGD）</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>历史VaR计算回放，压力测试结果归档，风险趋势分析，限额例外统计，VaR回测报告</t>
+          <t>债券组合信用风险：基于历史迁移矩阵的发行人PD（违约概率）/LGD（违约损失率）估算，IFRS 9三阶段分类（Stage 1/2/3）预期信用损失（ECL）计算；OTC衍生品CVA（信用估值调整）/DVA（借方估值调整）：基于蒙特卡洛模拟的预期正敞口EPE × PD × LGD，信用迁移风险（1年/3年迁移矩阵压力测试）</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G81" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>CVA计算与对手方差异&lt;1%，IFRS 9 ECL覆盖全债券持仓，PD/LGD数据源可追溯</t>
+        </is>
+      </c>
+      <c r="G81" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H81" s="8" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" ht="28" customHeight="1">
@@ -10773,17 +10777,17 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>F04-15</t>
+          <t>F04-13</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>监管报表与风控日报</t>
+          <t>历史风险回溯</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
+          <t>历史VaR计算回放，压力测试结果归档，风险趋势分析，限额例外统计，VaR回测报告</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -10813,22 +10817,22 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>F04-21</t>
+          <t>F04-15</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>限额治理工作流</t>
+          <t>监管报表与风控日报</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>全生命周期限额治理：新限额申请→风控审批→激活→日常利用率监控→超限告警（三级：预警/黄线/红线）→超限处置记录（豁免/压缩/升级审批）→定期复审（季度/年度自动触发）；限额与实际敞口双向穿透溯源；限额版本管理，历史变更审计，监管核查一键导出</t>
+          <t>日/周/月风险报告自动生成，监管资本计算，Basel III/FRTB报送，压力测试摘要，风险归因仪表板</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>超限告警延迟&lt;1min，限额利用率仪表盘实时刷新，限额变更全程留痕，监管核查导出&lt;5min</t>
+          <t>功能测试通过/正确率100%</t>
         </is>
       </c>
       <c r="G83" s="24" t="inlineStr">
@@ -10853,31 +10857,31 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>F04-16</t>
+          <t>F04-21</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>数据底座与IBOR集成</t>
+          <t>限额治理工作流</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
+          <t>全生命周期限额治理：新限额申请→风控审批→激活→日常利用率监控→超限告警（三级：预警/黄线/红线）→超限处置记录（豁免/压缩/升级审批）→定期复审（季度/年度自动触发）；限额与实际敞口双向穿透溯源；限额版本管理，历史变更审计，监管核查一键导出</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>超限告警延迟&lt;1min，限额利用率仪表盘实时刷新，限额变更全程留痕，监管核查导出&lt;5min</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H84" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" ht="28" customHeight="1">
@@ -10893,31 +10897,31 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>F04-17</t>
+          <t>F04-23</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>收益率曲线与波动率曲面</t>
+          <t>模型治理与回测框架</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
+          <t>Independent model risk governance infrastructure：daily backtesting of all risk models (VaR/Greeks/CVA/CVA)，exception tracking with severity classification；Kupiec POF statistical test performed quarterly；model exception investigation workflow with auto-escalation to quant team if &gt;3 exceptions/quarter；regulatory model governance documentation (Basel III backtesting audit trail，FRTB internal model approval requirements)；exception resolution and model re-calibration scheduling；complete model inventory with version control，parameter audit trail，and approval workflow</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G85" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>Daily backtest by 6am，exception report accuracy &gt;95%，model governance documentation audit-ready for regulator review，exception escalation &lt;1h from trigger，model parameter changes tracked with approval chain，Kupiec POF test results documented quarterly</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H85" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" ht="28" customHeight="1">
@@ -10933,31 +10937,31 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>F04-18</t>
+          <t>F04-16</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>HPC计算网格</t>
+          <t>数据底座与IBOR集成</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
+          <t>实时持仓追踪（事件溯源架构），全公司持仓聚合，实时数据验证与自动清洗，审计追踪</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G86" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H86" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" ht="28" customHeight="1">
@@ -10973,17 +10977,17 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>F04-19</t>
+          <t>F04-17</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>AI风险预警</t>
+          <t>收益率曲线与波动率曲面</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>异常检测（ML模型），预测性分析，模式识别，智能告警，新业务合规风险预分析</t>
+          <t>利率曲线构建（多方法），波动率曲面，信用利差曲线，红利曲线，全公司一致性保障</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -11000,17 +11004,50 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
-        </is>
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>FICC风险计量平台</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>F04-18</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>HPC计算网格</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>分布式计算引擎，并行蒙特卡洛，压力测试网格调度，弹性扩容，p99计算延迟&lt;5s</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G88" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="89" ht="28" customHeight="1">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>异常交易风控</t>
+          <t>FICC风险计量平台</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -11020,71 +11057,38 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>F05-01</t>
+          <t>F04-19</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>LLM大语言模型应用</t>
+          <t>AI风险预警</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>客户意图识别，自然语言处理交易描述，智能报告自动生成，新规合规解读</t>
+          <t>异常检测（ML模型），预测性分析，模式识别，智能告警，新业务合规风险预分析</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G89" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H89" s="8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>异常交易风控</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>F05-02</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
-        <is>
-          <t>RAG检索增强生成</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>监管规则知识库构建，新规则智能固化，合规智能问答，上下文理解与规则推理</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G90" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H90" s="8" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 异常交易风控  (Abnormal Trade Monitor)</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="28" customHeight="1">
@@ -11100,31 +11104,31 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>F05-03</t>
+          <t>F05-01</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Agent智能体</t>
+          <t>LLM大语言模型应用</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>异常处置任务自动化，决策支持工作流，多步骤异常核查流程优化，自动推送处置建议</t>
+          <t>客户意图识别，自然语言处理交易描述，智能报告自动生成，新规合规解读</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G91" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G91" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H91" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" ht="28" customHeight="1">
@@ -11140,31 +11144,31 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>F05-04</t>
+          <t>F05-02</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>MCP外部服务集成</t>
+          <t>RAG检索增强生成</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>外部数据源调用接口，固化规则调用标准协议，与行情/持仓/交易系统数据对接</t>
+          <t>监管规则知识库构建，新规则智能固化，合规智能问答，上下文理解与规则推理</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G92" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G92" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H92" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" ht="28" customHeight="1">
@@ -11180,17 +11184,17 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>F05-05</t>
+          <t>F05-03</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>代持与反向交易识别</t>
+          <t>Agent智能体</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>代持相关交易检测，同券同额反向识别，多日反向低频交易模式识别</t>
+          <t>异常处置任务自动化，决策支持工作流，多步骤异常核查流程优化，自动推送处置建议</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
@@ -11204,7 +11208,7 @@
         </is>
       </c>
       <c r="H93" s="8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" ht="28" customHeight="1">
@@ -11220,31 +11224,31 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>F05-06</t>
+          <t>F05-04</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>价格行为异常检测</t>
+          <t>MCP外部服务集成</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>高买低卖行为识别，信用债价格异常检测，基于历史分位数与实时行情动态偏离度计算</t>
+          <t>外部数据源调用接口，固化规则调用标准协议，与行情/持仓/交易系统数据对接</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G94" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G94" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H94" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" ht="28" customHeight="1">
@@ -11260,17 +11264,17 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>F05-07</t>
+          <t>F05-05</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>交易对手异常监控</t>
+          <t>代持与反向交易识别</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>同一交易对手频繁交易预警，多次修改交易对手行为识别，持仓结构异常检测</t>
+          <t>代持相关交易检测，同券同额反向识别，多日反向低频交易模式识别</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -11284,7 +11288,7 @@
         </is>
       </c>
       <c r="H95" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" ht="28" customHeight="1">
@@ -11300,31 +11304,31 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>F05-08</t>
+          <t>F05-06</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>交易量异常检测</t>
+          <t>价格行为异常检测</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>交易量统计异常识别，集中度异常告警，与历史基准对比的量级偏离检测</t>
+          <t>高买低卖行为识别，信用债价格异常检测，基于历史分位数与实时行情动态偏离度计算</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G96" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H96" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97" ht="28" customHeight="1">
@@ -11340,27 +11344,27 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>F05-09</t>
+          <t>F05-07</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>动态规则管理</t>
+          <t>交易对手异常监控</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>异常模式智能探索与规则固化，No-Code规则配置界面，合规人员自助维护，规则版本管理</t>
+          <t>同一交易对手频繁交易预警，多次修改交易对手行为识别，持仓结构异常检测</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G97" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H97" s="8" t="n">
@@ -11380,17 +11384,17 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>F05-10</t>
+          <t>F05-08</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>异常交易定位</t>
+          <t>交易量异常检测</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>按时间范围快速查找历史异常交易，标记异常类型，可视化展示异常分布与趋势</t>
+          <t>交易量统计异常识别，集中度异常告警，与历史基准对比的量级偏离检测</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -11420,17 +11424,17 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>F05-11</t>
+          <t>F05-09</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>数据上传校验</t>
+          <t>动态规则管理</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>支持用户上传交易数据文件，瞬时完成异常交易校验并输出校验结果报告</t>
+          <t>异常模式智能探索与规则固化，No-Code规则配置界面，合规人员自助维护，规则版本管理</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -11444,7 +11448,7 @@
         </is>
       </c>
       <c r="H99" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" ht="28" customHeight="1">
@@ -11460,17 +11464,17 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>F05-12</t>
+          <t>F05-10</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>智能报告生成</t>
+          <t>异常交易定位</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>模板自定义与场景数据一键应用，监管报送格式（证监会/人行），新业务过会合规分析报告</t>
+          <t>按时间范围快速查找历史异常交易，标记异常类型，可视化展示异常分布与趋势</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -11484,20 +11488,53 @@
         </is>
       </c>
       <c r="H100" s="8" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 事前风控/合规  (Pre-trade Risk &amp; Compliance)</t>
-        </is>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>异常交易风控</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>F05-11</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>数据上传校验</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>支持用户上传交易数据文件，瞬时完成异常交易校验并输出校验结果报告</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G101" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>事前风控/合规</t>
+          <t>异常交易风控</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -11507,71 +11544,38 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>F06-01</t>
+          <t>F05-12</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>风控规则配置</t>
+          <t>智能报告生成</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
+          <t>模板自定义与场景数据一键应用，监管报送格式（证监会/人行），新业务过会合规分析报告</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G102" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G102" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H102" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="103" ht="28" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>事前风控/合规</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>F06-02</t>
-        </is>
-      </c>
-      <c r="D103" s="4" t="inlineStr">
-        <is>
-          <t>多维度限额配置</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>交易对手/交易员/券三维度交易限额设置（集中度/净敞口/利率敏感度/单笔名义）；同时覆盖投资授权范围规则（单券集中度上限/组合久期区间/评级门槛/资产类别限制），作为F06-04交易时点拦截和F06-11持仓持续监控的统一规则来源</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G103" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H103" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 事前风控/合规  (Pre-trade Risk &amp; Compliance)</t>
+        </is>
       </c>
     </row>
     <row r="104" ht="28" customHeight="1">
@@ -11587,31 +11591,31 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>F06-03</t>
+          <t>F06-01</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>白黑名单管理</t>
+          <t>风控规则配置</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
+          <t>风控人员在页面配置事前风控条款，支持按需调整，规则版本管理，内置监管规则库（1000+条）</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G104" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G104" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H104" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105" ht="28" customHeight="1">
@@ -11627,27 +11631,27 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>F06-04</t>
+          <t>F06-02</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>实时事前风控拦截</t>
+          <t>多维度限额配置</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
+          <t>交易对手/交易员/券三维度交易限额设置（集中度/净敞口/利率敏感度/单笔名义）；同时覆盖投资授权范围规则（单券集中度上限/组合久期区间/评级门槛/资产类别限制），作为F06-04交易时点拦截和F06-11持仓持续监控的统一规则来源</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G105" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G105" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H105" s="8" t="n">
@@ -11667,17 +11671,17 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>F06-05</t>
+          <t>F06-03</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>异常报备工作流</t>
+          <t>白黑名单管理</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
+          <t>证券/交易对手监管限制名单实时同步，支持手工维护，拦截违规交易</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -11691,7 +11695,7 @@
         </is>
       </c>
       <c r="H106" s="8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" ht="28" customHeight="1">
@@ -11707,31 +11711,31 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>F06-06</t>
+          <t>F06-04</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>AI聊天合规监控</t>
+          <t>实时事前风控拦截</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
+          <t>交易录入时同步三维度校验（交易对手/交易员/券），不通过即时拦截并告知原因，支持发衡泰前校验</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G107" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G107" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H107" s="8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" ht="28" customHeight="1">
@@ -11747,31 +11751,31 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>F06-07</t>
+          <t>F06-05</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>AI交易要素提取</t>
+          <t>异常报备工作流</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
+          <t>触发异常条款后交易界面即时弹出提示，用户填写异常报备信息后方可提交，确保合规留痕</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G108" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G108" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H108" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" ht="28" customHeight="1">
@@ -11787,31 +11791,31 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>F06-08</t>
+          <t>F06-06</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>日内异常统计看板</t>
+          <t>AI聊天合规监控</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
+          <t>AI自动抓取所有交易对手聊天记录，按客户/券归类并保持时间顺序，实时监控潜在聊天违规并提醒交易员</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G109" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H109" s="8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110" ht="28" customHeight="1">
@@ -11827,31 +11831,31 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>F06-09</t>
+          <t>F06-07</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>合规审批工作流</t>
+          <t>AI交易要素提取</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
+          <t>询价意向达成后AI自动从聊天记录生成交易要素（债券/数量/价格/对手方），减少手工录入错误</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G110" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G110" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H110" s="8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" ht="28" customHeight="1">
@@ -11867,17 +11871,17 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>F06-10</t>
+          <t>F06-08</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>责任留痕与审计追踪</t>
+          <t>日内异常统计看板</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
+          <t>实时查看日内异常触发记录及处理情况，全面掌握团队执行进度与风控落实效果</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
@@ -11907,44 +11911,77 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>F06-11</t>
+          <t>F06-09</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>持仓合规状态持续监控（原M01 F01-17迁移）</t>
+          <t>合规审批工作流</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>【持仓层面持续监控，区别于F06-04交易时点拦截】订阅IBOR实时持仓事件，基于F06-02规则持续检测：投资授权范围越限/单券集中度漂移/久期区间偏离/评级门槛击穿（因市价波动而非新交易导致的违规）；违规自动告警并推送责任人；合规状态写回IBOR Position的complianceFlag字段，供组合管理系统展示</t>
+          <t>超限申请→多级审批→记录全流程，支持移动端审批，审批结果实时推送</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>持仓合规状态刷新延迟&lt;30s，零漏报，误报率&lt;0.1%，状态写回IBOR&lt;5s</t>
-        </is>
-      </c>
-      <c r="G112" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G112" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H112" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
-        </is>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" ht="28" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>事前风控/合规</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>F06-10</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>责任留痕与审计追踪</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>所有交易录入、拦截、报备、审批操作全程留痕，可追溯，监管现场检查时一键提取证据包</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G113" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="114" ht="28" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>组合管理+绩效归因</t>
+          <t>事前风控/合规</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -11954,22 +11991,22 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>F07-01</t>
+          <t>F06-11</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>全资产统一持仓模型</t>
+          <t>持仓合规状态持续监控（原M01 F01-17迁移）</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>八类资产（利率债/信用债/权益/基金/黄金/商品/衍生品/非标）实时T+0持仓，多层组合树（公司→部门→策略→子组合→投资经理），穿透式敞口展示（品种/久期/评级/行业/地区分布），真实组合+Shadow Portfolio并行展示</t>
+          <t>【持仓层面持续监控，区别于F06-04交易时点拦截】订阅IBOR实时持仓事件，基于F06-02规则持续检测：投资授权范围越限/单券集中度漂移/久期区间偏离/评级门槛击穿（因市价波动而非新交易导致的违规）；违规自动告警并推送责任人；合规状态写回IBOR Position的complianceFlag字段，供组合管理系统展示</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>T+0持仓实时刷新，穿透层级≥5层，数据与IBOR差异&lt;0.01%</t>
+          <t>持仓合规状态刷新延迟&lt;30s，零漏报，误报率&lt;0.1%，状态写回IBOR&lt;5s</t>
         </is>
       </c>
       <c r="G114" s="23" t="inlineStr">
@@ -11978,47 +12015,14 @@
         </is>
       </c>
       <c r="H114" s="8" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="115" ht="28" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>组合管理+绩效归因</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>F07-02</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>跨资产相关性分析</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>全持仓跨资产相关矩阵（股/债/商品/衍生品/基金），多窗口滚动（20/60/252日），压力情景相关性vs历史相关性对比，动态相关性漂移预警，分散化比率(Diversification Ratio)计算，低相关候选资产推荐</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>相关矩阵计算&lt;30s（500券组合），动态漂移预警阈值可配</t>
-        </is>
-      </c>
-      <c r="G115" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H115" s="8" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 组合管理+绩效归因  (Portfolio Mgmt &amp; Perf)</t>
+        </is>
       </c>
     </row>
     <row r="116" ht="28" customHeight="1">
@@ -12034,22 +12038,22 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>F07-03</t>
+          <t>F07-01</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>相对价值分析</t>
+          <t>全资产统一持仓模型</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位（覆盖5年），跨品种套利信号识别，债券横截面信号挖掘（利差/久期偏差），时序均值回归分析</t>
+          <t>八类资产（利率债/信用债/权益/基金/黄金/商品/衍生品/非标）实时T+0持仓，多层组合树（公司→部门→策略→子组合→投资经理），穿透式敞口展示（品种/久期/评级/行业/地区分布），真实组合+Shadow Portfolio并行展示</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>OAS计算误差&lt;1bps，历史分位数覆盖5年，横截面信号与实际收益相关性&gt;0.3</t>
+          <t>T+0持仓实时刷新，穿透层级≥5层，数据与IBOR差异&lt;0.01%</t>
         </is>
       </c>
       <c r="G116" s="23" t="inlineStr">
@@ -12058,7 +12062,7 @@
         </is>
       </c>
       <c r="H116" s="8" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" ht="28" customHeight="1">
@@ -12074,22 +12078,22 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>F07-04</t>
+          <t>F07-02</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>QP智能再平衡引擎</t>
+          <t>跨资产相关性分析</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>二次规划多目标优化（最小化跟踪误差+交易摩擦+融资成本+IFRS9波动），500+约束（合规/风险预算/流动性/IFRS9），2000+持仓毫秒级求解，支持整数规划（面值/手数取整），多期优化（含到期券），三种触发（定时/事件/手动），一键生成交易指令</t>
+          <t>全持仓跨资产相关矩阵（股/债/商品/衍生品/基金），多窗口滚动（20/60/252日），压力情景相关性vs历史相关性对比，动态相关性漂移预警，分散化比率(Diversification Ratio)计算，低相关候选资产推荐</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>QP求解2000持仓&lt;200ms，约束满足率100%，调仓前后TE对比即时输出</t>
+          <t>相关矩阵计算&lt;30s（500券组合），动态漂移预警阈值可配</t>
         </is>
       </c>
       <c r="G117" s="23" t="inlineStr">
@@ -12098,7 +12102,7 @@
         </is>
       </c>
       <c r="H117" s="8" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" ht="28" customHeight="1">
@@ -12114,22 +12118,22 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>F07-05</t>
+          <t>F07-03</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Shadow Portfolio虚拟试算（调用M01持仓沙箱）</t>
+          <t>相对价值分析</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>【PM投资分析层】调用M01 F01-25 What-if持仓沙箱获取假设成交后的持仓快照，在此基础上本模块完成全套投资分析：100+虚拟组合并行（写时复制快照），多维试算（增减仓/换仓/加杠杆/新资产类别），即时计算试算后风险指标/因子暴露/归因/相关性/预期收益，真实vs虚拟差异对比视图，冲击成本预估。持仓计算层在M01，分析层在本模块</t>
+          <t>利差/Z-spread/OAS相对价值计算，历史分位数定位（覆盖5年），跨品种套利信号识别，债券横截面信号挖掘（利差/久期偏差），时序均值回归分析</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>虚拟组合模拟与真实执行偏差&lt;0.3%，秒级响应，100+并行无数据污染</t>
+          <t>OAS计算误差&lt;1bps，历史分位数覆盖5年，横截面信号与实际收益相关性&gt;0.3</t>
         </is>
       </c>
       <c r="G118" s="23" t="inlineStr">
@@ -12138,7 +12142,7 @@
         </is>
       </c>
       <c r="H118" s="8" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" ht="28" customHeight="1">
@@ -12154,22 +12158,22 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>F07-06</t>
+          <t>F07-04</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>资产配置策略分析</t>
+          <t>QP智能再平衡引擎</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>SAA战略→TAA战术精准联动（投委会指令直接转化为因子约束输入QP引擎），宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证（≥5年），固收+策略P&amp;L归因（债券底仓+衍生品增强）</t>
+          <t>二次规划多目标优化（最小化跟踪误差+交易摩擦+融资成本+IFRS9波动），500+约束（合规/风险预算/流动性/IFRS9），2000+持仓毫秒级求解，支持整数规划（面值/手数取整），多期优化（含到期券），三种触发（定时/事件/手动），一键生成交易指令</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>回测期≥5年，预测方向胜率&gt;55%，SAA→TAA指令转化全程无人工干预</t>
+          <t>QP求解2000持仓&lt;200ms，约束满足率100%，调仓前后TE对比即时输出</t>
         </is>
       </c>
       <c r="G119" s="23" t="inlineStr">
@@ -12194,22 +12198,22 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>F07-07</t>
+          <t>F07-05</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Campisi 2.0 固收绩效归因</t>
+          <t>Shadow Portfolio虚拟试算（调用M01持仓沙箱）</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>固定收益五效应完整拆解：①收入效应（票息+摊销），②国债效应（利率平移/曲线斜率/曲率三效应分离，用Key Rate Duration精确映射），③利差效应（DTS贡献/行业配置效应/个券选择效应），④交易效应（择时Alpha或损耗量化），⑤残差校验（&lt;5bp合格）；日/周/月/季多维度报告自动生成</t>
+          <t>【PM投资分析层】调用M01 F01-25 What-if持仓沙箱获取假设成交后的持仓快照，在此基础上本模块完成全套投资分析：100+虚拟组合并行（写时复制快照），多维试算（增减仓/换仓/加杠杆/新资产类别），即时计算试算后风险指标/因子暴露/归因/相关性/预期收益，真实vs虚拟差异对比视图，冲击成本预估。持仓计算层在M01，分析层在本模块</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>五效应合计与实际收益残差&lt;5bps，T+1 9:00前自动报告</t>
+          <t>虚拟组合模拟与真实执行偏差&lt;0.3%，秒级响应，100+并行无数据污染</t>
         </is>
       </c>
       <c r="G120" s="23" t="inlineStr">
@@ -12218,7 +12222,7 @@
         </is>
       </c>
       <c r="H120" s="8" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121" ht="28" customHeight="1">
@@ -12234,22 +12238,22 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>F07-08</t>
+          <t>F07-06</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Brinson 资产组合绩效归因</t>
+          <t>资产配置策略分析</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>三效应：大类资产配置效应（超/低配决策贡献）/个券选择效应（同类标的选择Alpha）/交互效应，支持多层穿透（资产大类→行业→子行业→个股/个基），FOF基金穿透底层持仓，日/月/季/年累计归因趋势，投资经理能力量化排名</t>
+          <t>SAA战略→TAA战术精准联动（投委会指令直接转化为因子约束输入QP引擎），宏观因子（利率/信用/流动性周期）驱动大类资产配置模型，动态权重优化，历史回测验证（≥5年），固收+策略P&amp;L归因（债券底仓+衍生品增强）</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，穿透层级≥4层</t>
+          <t>回测期≥5年，预测方向胜率&gt;55%，SAA→TAA指令转化全程无人工干预</t>
         </is>
       </c>
       <c r="G121" s="23" t="inlineStr">
@@ -12258,7 +12262,7 @@
         </is>
       </c>
       <c r="H121" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="122" ht="28" customHeight="1">
@@ -12274,31 +12278,31 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>F07-09</t>
+          <t>F07-07</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>指数跟踪误差与主动风险归因</t>
+          <t>Campisi 2.0 固收绩效归因</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>对标中债综合/信用/政策行等基准指数，跟踪误差（TE）日频监控，TE分解（配置效应TE+选券效应TE+协方差），信息比率（IR）实时监控（目标IR&gt;0.5，预警IR连续3月&lt;0），超额Alpha三因子分解</t>
+          <t>固定收益五效应完整拆解：①收入效应（票息+摊销），②国债效应（利率平移/曲线斜率/曲率三效应分离，用Key Rate Duration精确映射），③利差效应（DTS贡献/行业配置效应/个券选择效应），④交易效应（择时Alpha或损耗量化），⑤残差校验（&lt;5bp合格）；日/周/月/季多维度报告自动生成</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>TE计算误差&lt;1bps，支持≥10基准指数，IR预警自动推送</t>
-        </is>
-      </c>
-      <c r="G122" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>五效应合计与实际收益残差&lt;5bps，T+1 9:00前自动报告</t>
+        </is>
+      </c>
+      <c r="G122" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H122" s="8" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123" ht="28" customHeight="1">
@@ -12314,31 +12318,31 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>F07-19</t>
+          <t>F07-08</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>净利差与Carry预算分析</t>
+          <t>Brinson 资产组合绩效归因</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>逐券Carry分解（票息收入−回购成本−摊销损益）与Roll-down P&amp;L，构建组合Carry热力图（信用类vs利率类carry对比）；Carry预算与实际消耗追踪，偏离超阈值自动预警；Carry归因拆分（利率carry/信用carry/久期carry）供投委会汇报</t>
+          <t>三效应：大类资产配置效应（超/低配决策贡献）/个券选择效应（同类标的选择Alpha）/交互效应，支持多层穿透（资产大类→行业→子行业→个股/个基），FOF基金穿透底层持仓，日/月/季/年累计归因趋势，投资经理能力量化排名</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>逐券Carry计算与实际票息收入误差&lt;1bps，Carry预算仪表盘T+1 9:00前自动刷新</t>
-        </is>
-      </c>
-      <c r="G123" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>Brinson结果与Bloomberg AIM误差&lt;0.1%，穿透层级≥4层</t>
+        </is>
+      </c>
+      <c r="G123" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H123" s="8" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124" ht="28" customHeight="1">
@@ -12354,22 +12358,22 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>F07-21</t>
+          <t>F07-09</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>绩效报告生成</t>
+          <t>指数跟踪误差与主动风险归因</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>TWR（时间加权收益率）/MWR（资金加权收益率）多期计算，Grap算法多期归因链接（月度→季度→年度），PM工作台标准化绩效仪表盘（夏普/IR/最大回撤/信息比率），自动生成投委会汇报材料（PDF/PPT），历史归因报告版本存档与对比</t>
+          <t>对标中债综合/信用/政策行等基准指数，跟踪误差（TE）日频监控，TE分解（配置效应TE+选券效应TE+协方差），信息比率（IR）实时监控（目标IR&gt;0.5，预警IR连续3月&lt;0），超额Alpha三因子分解</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>TWR/MWR与Bloomberg AIM误差&lt;0.1%，月度报告T+1 9:00前自动生成，支持≥12期累计归因</t>
+          <t>TE计算误差&lt;1bps，支持≥10基准指数，IR预警自动推送</t>
         </is>
       </c>
       <c r="G124" s="24" t="inlineStr">
@@ -12378,7 +12382,7 @@
         </is>
       </c>
       <c r="H124" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" ht="28" customHeight="1">
@@ -12394,31 +12398,31 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>F07-10</t>
+          <t>F07-19</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>因子风险分解 + MCTR边际风险贡献（消费M08因子暴露）</t>
+          <t>净利差与Carry预算分析</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>【消费M08因子暴露结果】将组合持仓分解为系统性风险（2200+因子，来自M08）+特异性风险；计算MCTR边际风险贡献（∂组合波动率/∂持仓权重，热路径用C++矩阵求导），输出风险消耗排名（识别「风险大户」），驱动减仓/加仓优先级，提供QP再平衡的风险预算约束输入。本模块不计算因子协方差矩阵，协方差矩阵由M08维护</t>
+          <t>逐券Carry分解（票息收入−回购成本−摊销损益）与Roll-down P&amp;L，构建组合Carry热力图（信用类vs利率类carry对比）；Carry预算与实际消耗追踪，偏离超阈值自动预警；Carry归因拆分（利率carry/信用carry/久期carry）供投委会汇报</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>因子模型解释方差&gt;80%（由M08保证），MCTR实时更新延迟&lt;5s，风险预算仪表盘刷新延迟&lt;5s</t>
-        </is>
-      </c>
-      <c r="G125" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>逐券Carry计算与实际票息收入误差&lt;1bps，Carry预算仪表盘T+1 9:00前自动刷新</t>
+        </is>
+      </c>
+      <c r="G125" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H125" s="8" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126" ht="28" customHeight="1">
@@ -12434,22 +12438,22 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>F07-11</t>
+          <t>F07-21</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Component VaR 四层穿透展示（调用M04引擎）</t>
+          <t>绩效报告生成</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>PM决策展示层——调用M04(F04-10)VaR计算引擎获取三方法结果，在本模块实现四层穿透钻取：资产类别VaR→行业/子市场VaR→评级/信用质量VaR→单一发行人Component VaR，含跨类分散化收益量化；本模块不重复实现VaR计算，专注投资决策视角的风险溯源与持仓优化引导</t>
+          <t>TWR（时间加权收益率）/MWR（资金加权收益率）多期计算，Grap算法多期归因链接（月度→季度→年度），PM工作台标准化绩效仪表盘（夏普/IR/最大回撤/信息比率），自动生成投委会汇报材料（PDF/PPT），历史归因报告版本存档与对比</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>穿透至发行人层展示&lt;3s，三方法差异预警由M04提供，本模块直接透传</t>
+          <t>TWR/MWR与Bloomberg AIM误差&lt;0.1%，月度报告T+1 9:00前自动生成，支持≥12期累计归因</t>
         </is>
       </c>
       <c r="G126" s="24" t="inlineStr">
@@ -12458,7 +12462,7 @@
         </is>
       </c>
       <c r="H126" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" ht="28" customHeight="1">
@@ -12474,31 +12478,31 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>F07-12</t>
+          <t>F07-10</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>敏感度展示（多维Shock Grid，调用M04引擎）</t>
+          <t>因子风险分解 + MCTR边际风险贡献（消费M08因子暴露）</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>PM决策展示层——M04(F04-08/09)计算DV01/CS01/Greeks，本模块负责：组合层面聚合（按资产类别/行业/评级汇总），构建利率×信用利差二维冲击矩阵（Shock Grid 5×5），识别最脆弱组合方向，输出对冲比率建议；本模块不重复实现敏感度计算</t>
+          <t>【消费M08因子暴露结果】将组合持仓分解为系统性风险（2200+因子，来自M08）+特异性风险；计算MCTR边际风险贡献（∂组合波动率/∂持仓权重，热路径用C++矩阵求导），输出风险消耗排名（识别「风险大户」），驱动减仓/加仓优先级，提供QP再平衡的风险预算约束输入。本模块不计算因子协方差矩阵，协方差矩阵由M08维护</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Shock Grid 5×5矩阵实时刷新，组合DV01聚合与M04单券结果误差&lt;0.1bps</t>
-        </is>
-      </c>
-      <c r="G127" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>因子模型解释方差&gt;80%（由M08保证），MCTR实时更新延迟&lt;5s，风险预算仪表盘刷新延迟&lt;5s</t>
+        </is>
+      </c>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H127" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128" ht="28" customHeight="1">
@@ -12514,22 +12518,22 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>F07-13</t>
+          <t>F07-11</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>情景分析PM决策层（调用M04场景库）</t>
+          <t>Component VaR 四层穿透展示（调用M04引擎）</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>PM投资决策层——M04(F04-11)维护历史场景库并提供计算API，本模块负责：①调用M04获取场景P&amp;L结果（924行情/包商/钱荒/股灾等8+历史场景+自定义场景），②PM工作流：基于场景结果生成对冲建议、触发再平衡方案、输出持仓调整优先级，③反向压力测试（倒推临界情景→止损线设计依据）；场景库维护与全公司治理由M04负责</t>
+          <t>PM决策展示层——调用M04(F04-10)VaR计算引擎获取三方法结果，在本模块实现四层穿透钻取：资产类别VaR→行业/子市场VaR→评级/信用质量VaR→单一发行人Component VaR，含跨类分散化收益量化；本模块不重复实现VaR计算，专注投资决策视角的风险溯源与持仓优化引导</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>调用M04 API获取场景P&amp;L&lt;2s，PM决策输出（对冲建议）&lt;5s，≥20情景并行</t>
+          <t>穿透至发行人层展示&lt;3s，三方法差异预警由M04提供，本模块直接透传</t>
         </is>
       </c>
       <c r="G128" s="24" t="inlineStr">
@@ -12538,7 +12542,7 @@
         </is>
       </c>
       <c r="H128" s="8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="129" ht="28" customHeight="1">
@@ -12554,22 +12558,22 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>F07-14</t>
+          <t>F07-12</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>流动性风险管理（LVaR）</t>
+          <t>敏感度展示（多维Shock Grid，调用M04引擎）</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>逐持仓变现能力评估（规模/日均成交量→变现天数），Almgren-Chriss市场冲击成本模型，流动性压力测试（X天内变现Y亿最优路径+成本），流动性调整VaR（LVaR=传统VaR+流动性溢价），流动性覆盖率/缓冲监控（1/3/5/10日分层），回购到期日历</t>
+          <t>PM决策展示层——M04(F04-08/09)计算DV01/CS01/Greeks，本模块负责：组合层面聚合（按资产类别/行业/评级汇总），构建利率×信用利差二维冲击矩阵（Shock Grid 5×5），识别最脆弱组合方向，输出对冲比率建议；本模块不重复实现敏感度计算</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓，变现路径建议&lt;3s</t>
+          <t>Shock Grid 5×5矩阵实时刷新，组合DV01聚合与M04单券结果误差&lt;0.1bps</t>
         </is>
       </c>
       <c r="G129" s="24" t="inlineStr">
@@ -12578,7 +12582,7 @@
         </is>
       </c>
       <c r="H129" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="130" ht="28" customHeight="1">
@@ -12594,31 +12598,31 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>F07-15</t>
+          <t>F07-13</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>衍生品对冲决策引擎</t>
+          <t>情景分析PM决策层（调用M04场景库）</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>七类工具矩阵（国债期货2/5/10/30Y/IRS/CDS/股指期货IF/IH/IC/IM/股指期权/黄金期货/外汇远掉期），系统推荐最优对冲方案（成本最小约束），一键生成对冲指令，对冲效果追踪（前后风险指标对比/效率/执行滑点）；支持快速/精细/尾部/跨资产四种场景</t>
+          <t>PM投资决策层——M04(F04-11)维护历史场景库并提供计算API，本模块负责：①调用M04获取场景P&amp;L结果（924行情/包商/钱荒/股灾等8+历史场景+自定义场景），②PM工作流：基于场景结果生成对冲建议、触发再平衡方案、输出持仓调整优先级，③反向压力测试（倒推临界情景→止损线设计依据）；场景库维护与全公司治理由M04负责</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>对冲方案推荐&lt;5s，DV01对冲误差&lt;5%，指令自动流转执行引擎</t>
-        </is>
-      </c>
-      <c r="G130" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>调用M04 API获取场景P&amp;L&lt;2s，PM决策输出（对冲建议）&lt;5s，≥20情景并行</t>
+        </is>
+      </c>
+      <c r="G130" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H130" s="8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="131" ht="28" customHeight="1">
@@ -12634,22 +12638,22 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>F07-20</t>
+          <t>F07-14</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>交易成本分析TCA</t>
+          <t>流动性风险管理（LVaR）</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>事后TCA：实施成本差（Implementation Shortfall = 决策时盘中价−成交均价）、VWAP/TWAP基准偏差，滑点分解（市场冲击+时机成本+价差成本）；经纪商执行质量排名（月度），超额成本自动触发路由策略优化建议；TCA结果回写F07-07归因（提升交易效应精确度）</t>
+          <t>逐持仓变现能力评估（规模/日均成交量→变现天数），Almgren-Chriss市场冲击成本模型，流动性压力测试（X天内变现Y亿最优路径+成本），流动性调整VaR（LVaR=传统VaR+流动性溢价），流动性覆盖率/缓冲监控（1/3/5/10日分层），回购到期日历</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>TCA报告T+1生成，经纪商排名覆盖≥90%成交量，实施成本差计算与外部TCA服务误差&lt;1bps</t>
+          <t>LVaR与市场基准误差&lt;5%，日均成交量覆盖≥95%持仓，变现路径建议&lt;3s</t>
         </is>
       </c>
       <c r="G131" s="24" t="inlineStr">
@@ -12658,7 +12662,7 @@
         </is>
       </c>
       <c r="H131" s="8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="132" ht="28" customHeight="1">
@@ -12674,22 +12678,22 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>F07-16</t>
+          <t>F07-15</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>定价计算集成</t>
+          <t>衍生品对冲决策引擎</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>调用定价平台实时估值与Greeks（含权债/可转债/IRS），Redis缓存结果，Kafka推送持仓+估值变化事件，日终全量估值批处理</t>
+          <t>七类工具矩阵（国债期货2/5/10/30Y/IRS/CDS/股指期货IF/IH/IC/IM/股指期权/黄金期货/外汇远掉期），系统推荐最优对冲方案（成本最小约束），一键生成对冲指令，对冲效果追踪（前后风险指标对比/效率/执行滑点）；支持快速/精细/尾部/跨资产四种场景</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+          <t>对冲方案推荐&lt;5s，DV01对冲误差&lt;5%，指令自动流转执行引擎</t>
         </is>
       </c>
       <c r="G132" s="23" t="inlineStr">
@@ -12698,7 +12702,7 @@
         </is>
       </c>
       <c r="H132" s="8" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="133" ht="28" customHeight="1">
@@ -12714,22 +12718,22 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>F07-17</t>
+          <t>F07-20</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>利率曲线集成</t>
+          <t>交易成本分析TCA</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），关键期限点敏感度映射，曲线版本快照（供归因历史复现）</t>
+          <t>事后TCA：实施成本差（Implementation Shortfall = 决策时盘中价−成交均价）、VWAP/TWAP基准偏差，滑点分解（市场冲击+时机成本+价差成本）；经纪商执行质量排名（月度），超额成本自动触发路由策略优化建议；TCA结果回写F07-07归因（提升交易效应精确度）</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+          <t>TCA报告T+1生成，经纪商排名覆盖≥90%成交量，实施成本差计算与外部TCA服务误差&lt;1bps</t>
         </is>
       </c>
       <c r="G133" s="24" t="inlineStr">
@@ -12738,7 +12742,7 @@
         </is>
       </c>
       <c r="H133" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" ht="28" customHeight="1">
@@ -12754,44 +12758,77 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>F07-18</t>
+          <t>F07-16</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>因子暴露集成（消费M08，不建模）</t>
+          <t>定价计算集成</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>【消费方】消费M08发布的逐券因子载荷与协方差矩阵，本模块负责：①按持仓权重聚合组合层面2200+风险因子暴露（利率/信用/流动性/权益Beta/行业/风格/商品/汇率八类），②因子暴露历史追踪与漂移预警，③因子风险预算仪表盘（已用/剩余/三档预警）。因子定义/协方差矩阵/逐券载荷计算全部由M08负责，本模块零重复建设</t>
+          <t>调用定价平台实时估值与Greeks（含权债/可转债/IRS），Redis缓存结果，Kafka推送持仓+估值变化事件，日终全量估值批处理</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>组合因子暴露聚合延迟&lt;10s，因子模型解释方差&gt;80%（由M08保证），风险预算仪表盘实时刷新</t>
-        </is>
-      </c>
-      <c r="G134" s="24" t="inlineStr">
+          <t>定价API p99&lt;200ms，日终全量估值&lt;30min（10万券）</t>
+        </is>
+      </c>
+      <c r="G134" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="135" ht="28" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>组合管理+绩效归因</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>F07-17</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>利率曲线集成</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>多曲线实时消费（国债/政策行/AAA信用/OIS），NS参数提取（水平/斜率/曲率），关键期限点敏感度映射，曲线版本快照（供归因历史复现）</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>曲线更新延迟&lt;1s，NS拟合R²&gt;0.999</t>
+        </is>
+      </c>
+      <c r="G135" s="24" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H134" s="8" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="22" t="inlineStr">
-        <is>
-          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
-        </is>
+      <c r="H135" s="8" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="136" ht="28" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>策略投资/量化</t>
+          <t>组合管理+绩效归因</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -12801,71 +12838,38 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>F08-01</t>
+          <t>F07-18</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>策略编写与版本管理</t>
+          <t>因子暴露集成（消费M08，不建模）</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
+          <t>【消费方】消费M08发布的逐券因子载荷与协方差矩阵，本模块负责：①按持仓权重聚合组合层面2200+风险因子暴露（利率/信用/流动性/权益Beta/行业/风格/商品/汇率八类），②因子暴露历史追踪与漂移预警，③因子风险预算仪表盘（已用/剩余/三档预警）。因子定义/协方差矩阵/逐券载荷计算全部由M08负责，本模块零重复建设</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G136" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>组合因子暴露聚合延迟&lt;10s，因子模型解释方差&gt;80%（由M08保证），风险预算仪表盘实时刷新</t>
+        </is>
+      </c>
+      <c r="G136" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H136" s="8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="137" ht="28" customHeight="1">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>策略投资/量化</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>F08-02</t>
-        </is>
-      </c>
-      <c r="D137" s="4" t="inlineStr">
-        <is>
-          <t>AI辅助策略开发</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G137" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H137" s="8" t="n">
-        <v>35</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="22" t="inlineStr">
+        <is>
+          <t>【P1】 策略投资/量化  (Quant Strategy)</t>
+        </is>
       </c>
     </row>
     <row r="138" ht="28" customHeight="1">
@@ -12881,17 +12885,17 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>F08-03</t>
+          <t>F08-01</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>因子模型建设与管理（全公司SSoT）</t>
+          <t>策略编写与版本管理</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>【全公司因子语言SSoT】统一维护2200+风险因子定义（利率/信用/流动性/权益Beta/行业/风格/商品/汇率八类）及Alpha因子库（≥20个，IC均值&gt;0.05）；计算逐券因子载荷与因子协方差矩阵（利率/信用类载荷消费M09输出的DV01/CS01/KRD/Greeks，本模块不重新定价）；通过内部因子暴露API发布结果，M07组合管理和M04风险计量只消费，不重复建模；AlphaLens有效性分析、信号生成、宏观/技术/基本面因子挖掘均在本模块进行</t>
+          <t>Python/C++策略脚本编写，沙箱隔离运行，策略版本管理，策略库分类管理（利差/基差/跨市场套利/网格/固收/量价）</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
@@ -12905,7 +12909,7 @@
         </is>
       </c>
       <c r="H138" s="8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="139" ht="28" customHeight="1">
@@ -12921,31 +12925,31 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>F08-04</t>
+          <t>F08-02</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Tick级回测引擎</t>
+          <t>AI辅助策略开发</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
+          <t>AI代码生成辅助，AI因子生成，AI参数优化建议，自然语言描述策略逻辑转代码</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G139" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G139" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H139" s="8" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="140" ht="28" customHeight="1">
@@ -12961,17 +12965,17 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>F08-05</t>
+          <t>F08-03</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>模拟盘验证</t>
+          <t>因子模型建设与管理（全公司SSoT）</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
+          <t>【全公司因子语言SSoT】统一维护2200+风险因子定义（利率/信用/流动性/权益Beta/行业/风格/商品/汇率八类）及Alpha因子库（≥20个，IC均值&gt;0.05）；计算逐券因子载荷与因子协方差矩阵（利率/信用类载荷消费M09输出的DV01/CS01/KRD/Greeks，本模块不重新定价）；通过内部因子暴露API发布结果，M07组合管理和M04风险计量只消费，不重复建模；AlphaLens有效性分析、信号生成、宏观/技术/基本面因子挖掘均在本模块进行</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -12985,7 +12989,7 @@
         </is>
       </c>
       <c r="H140" s="8" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="141" ht="28" customHeight="1">
@@ -13001,31 +13005,31 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>F08-06</t>
+          <t>F08-04</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>策略上线审批</t>
+          <t>Tick级回测引擎</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
+          <t>Tick数据驱动回测，真实滑点/冲击模型，批量参数优化，风险计量，绩效归因，AlphaLens分析集成</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G141" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G141" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H141" s="8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" ht="28" customHeight="1">
@@ -13041,17 +13045,17 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>F08-07</t>
+          <t>F08-05</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>策略运行管理</t>
+          <t>模拟盘验证</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
+          <t>情景模拟，敏感度模拟，极端场景模拟，性能测试，模拟盘与实盘结果对比分析</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -13081,17 +13085,17 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>F08-08</t>
+          <t>F08-06</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>策略绩效分析</t>
+          <t>策略上线审批</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
+          <t>模拟盘通过后触发上线审批流程，多级合规审核，审批留痕，参数锁定后方可实盘运行</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
@@ -13105,7 +13109,7 @@
         </is>
       </c>
       <c r="H143" s="8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" ht="28" customHeight="1">
@@ -13121,31 +13125,31 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>F08-09</t>
+          <t>F08-07</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>实时多市场行情</t>
+          <t>策略运行管理</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
+          <t>实盘策略启停管理，策略状态实时监控，支持手动干预和自动触发停止，多策略并发调度</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G144" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G144" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H144" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" ht="28" customHeight="1">
@@ -13161,17 +13165,17 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>F08-10</t>
+          <t>F08-08</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>历史行情回放</t>
+          <t>策略绩效分析</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
+          <t>实时PnL/持仓/回撤/Sharpe看板，策略归因分析，与基准对比，风险触发自动平仓</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
@@ -13185,7 +13189,7 @@
         </is>
       </c>
       <c r="H145" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146" ht="28" customHeight="1">
@@ -13201,31 +13205,31 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>F08-11</t>
+          <t>F08-09</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>CEP流引擎与信号调度</t>
+          <t>实时多市场行情</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
+          <t>现券/国债期货/股票/商品实时行情聚合展示，实时利差分析，跨市场价差监控，行情小窗</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G146" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G146" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H146" s="8" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" ht="28" customHeight="1">
@@ -13241,118 +13245,118 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
+          <t>F08-10</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>历史行情回放</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>现券/国债期货/股票/商品历史行情回放，支持任意时间点快照，用于回测验证和策略复盘</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G147" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" ht="28" customHeight="1">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>F08-11</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>CEP流引擎与信号调度</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>复杂事件处理引擎，策略信号实时计算与调度，低延迟执行接口对接ATP超低延迟执行层</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G148" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="149" ht="28" customHeight="1">
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>策略投资/量化</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
           <t>F08-12</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D149" s="4" t="inlineStr">
         <is>
           <t>量化数据底座</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
+      <c r="E149" s="5" t="inlineStr">
         <is>
           <t>宏观因子数据接入与清洗（GDP/CPI/央行操作/信用利差等）；消费M09曲线/估值数据（不自建曲线模型）；账户与策略权限管理；AI引擎集成接口（LangChain/LLM）；统一数据对齐（asOf时间戳），确保回测与实盘使用同一套数据快照</t>
         </is>
       </c>
-      <c r="F147" s="5" t="inlineStr">
+      <c r="F149" s="5" t="inlineStr">
         <is>
           <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
-      <c r="G147" s="23" t="inlineStr">
+      <c r="G149" s="23" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H147" s="8" t="n">
+      <c r="H149" s="8" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="26" t="inlineStr">
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="26" t="inlineStr">
         <is>
           <t>【P2】 定价平台  (Pricing Platform)</t>
         </is>
-      </c>
-    </row>
-    <row r="149" ht="28" customHeight="1">
-      <c r="A149" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B149" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>F09-01</t>
-        </is>
-      </c>
-      <c r="D149" s="27" t="inlineStr">
-        <is>
-          <t>期权收益结构定价</t>
-        </is>
-      </c>
-      <c r="E149" s="11" t="inlineStr">
-        <is>
-          <t>香草期权/价差期权/欧式/美式/雪球/自定义期权定价，挂钩标的覆盖国债/期货/股票/指数/商品</t>
-        </is>
-      </c>
-      <c r="F149" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G149" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H149" s="13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="150" ht="28" customHeight="1">
-      <c r="A150" s="11" t="inlineStr">
-        <is>
-          <t>定价平台</t>
-        </is>
-      </c>
-      <c r="B150" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C150" s="10" t="inlineStr">
-        <is>
-          <t>F09-02</t>
-        </is>
-      </c>
-      <c r="D150" s="27" t="inlineStr">
-        <is>
-          <t>结构化产品定价</t>
-        </is>
-      </c>
-      <c r="E150" s="11" t="inlineStr">
-        <is>
-          <t>场外期权/远期/收益凭证/收益互换/融资融券/合约型互换定价，支持自定义结构化产品</t>
-        </is>
-      </c>
-      <c r="F150" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G150" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H150" s="13" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="151" ht="28" customHeight="1">
@@ -13368,31 +13372,31 @@
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>F09-03</t>
+          <t>F09-01</t>
         </is>
       </c>
       <c r="D151" s="27" t="inlineStr">
         <is>
-          <t>固收品种定价</t>
+          <t>期权收益结构定价</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>固息/浮息国债，含权债，可转债精确定价，信用债估值，ABS定价</t>
+          <t>香草期权/价差期权/欧式/美式/雪球/自定义期权定价，挂钩标的覆盖国债/期货/股票/指数/商品</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G151" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G151" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H151" s="13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152" ht="28" customHeight="1">
@@ -13408,17 +13412,17 @@
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>F09-04</t>
+          <t>F09-02</t>
         </is>
       </c>
       <c r="D152" s="27" t="inlineStr">
         <is>
-          <t>利率与信用曲线构建</t>
+          <t>结构化产品定价</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务</t>
+          <t>场外期权/远期/收益凭证/收益互换/融资融券/合约型互换定价，支持自定义结构化产品</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr">
@@ -13432,7 +13436,7 @@
         </is>
       </c>
       <c r="H152" s="13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="153" ht="28" customHeight="1">
@@ -13448,31 +13452,31 @@
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>F09-05</t>
+          <t>F09-03</t>
         </is>
       </c>
       <c r="D153" s="27" t="inlineStr">
         <is>
-          <t>波动率曲面构建</t>
+          <t>固收品种定价</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>隐含波动率曲面，红利曲线，汇率曲线，Local Volatility曲面，波动率微笑校准</t>
+          <t>固息/浮息国债，含权债，可转债精确定价，信用债估值，ABS定价</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G153" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G153" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H153" s="13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154" ht="28" customHeight="1">
@@ -13488,31 +13492,31 @@
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>F09-06</t>
+          <t>F09-04</t>
         </is>
       </c>
       <c r="D154" s="27" t="inlineStr">
         <is>
-          <t>市场数据管理</t>
+          <t>利率与信用曲线构建</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>境内外权益/债券/外汇/商品资讯统一接入，数据清洗，异常值处理，数据质量监控</t>
+          <t>利率曲线（多插值方法），信用利差曲线，利差曲线，违约曲线，全品种统一曲线服务；新增automated curve smoothing（spline tension controls, Piecewise-Linear Moneyness interpolation）保证曲线平滑性；arbitrage validation pipeline：overnight batch after daily curve recalibration进行：(1)negative forward detection（无负利率），(2)cheap bond detection（price &lt; dirty price floor），(3)cross-curve arbitrage checks；validation failure自动trigger manual review workflow；clean curve snapshot materialized in Redis for intraday consumption；smoothness metrics + arbitrage violations reported to F01-29 DQ Dashboard</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G154" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>Curve smoothing ensures no arbitrage violations for consecutive &gt;30 days，negative forward detection accuracy 100%，cheap bond detection accuracy &gt;99%，arbitrage validation completion &lt;10min after overnight curve build，clean curve snapshots ready by 6:30am for market open，DQ metrics push to F01-29 real-time</t>
+        </is>
+      </c>
+      <c r="G154" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H154" s="13" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="155" ht="28" customHeight="1">
@@ -13528,17 +13532,17 @@
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>F09-07</t>
+          <t>F09-05</t>
         </is>
       </c>
       <c r="D155" s="27" t="inlineStr">
         <is>
-          <t>蒙特卡洛求解器</t>
+          <t>波动率曲面构建</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价，并行情景模拟</t>
+          <t>隐含波动率曲面，红利曲线，汇率曲线，Local Volatility曲面，波动率微笑校准</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr">
@@ -13552,7 +13556,7 @@
         </is>
       </c>
       <c r="H155" s="13" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="156" ht="28" customHeight="1">
@@ -13568,31 +13572,31 @@
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>F09-08</t>
+          <t>F09-06</t>
         </is>
       </c>
       <c r="D156" s="27" t="inlineStr">
         <is>
-          <t>解析解与数值解</t>
+          <t>市场数据管理</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>Black-Scholes解析解，Hull-White利率模型，SABR波动率模型，二叉树/三叉树数值解</t>
+          <t>境内外权益/债券/外汇/商品资讯统一接入，数据清洗，异常值处理，数据质量监控</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G156" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G156" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H156" s="13" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" ht="28" customHeight="1">
@@ -13608,17 +13612,17 @@
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>F09-09</t>
+          <t>F09-07</t>
         </is>
       </c>
       <c r="D157" s="27" t="inlineStr">
         <is>
-          <t>有限差分（PDE）</t>
+          <t>蒙特卡洛求解器</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价，局部波动率模型数值解</t>
+          <t>GPU加速MC，QMC低差异序列，支持路径相关期权定价，并行情景模拟</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr">
@@ -13632,7 +13636,7 @@
         </is>
       </c>
       <c r="H157" s="13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="158" ht="28" customHeight="1">
@@ -13648,31 +13652,31 @@
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>F09-10</t>
+          <t>F09-08</t>
         </is>
       </c>
       <c r="D158" s="27" t="inlineStr">
         <is>
-          <t>实时Greeks与敏感度计算（M07/M08/M04共用基础）</t>
+          <t>解析解与数值解</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>分布式实时计算全品种逐券敏感度，结果为M07归因、M08因子载荷、M04风险计量三方共用权威数据源：Delta/Gamma/Vega/Theta/Rho（期权/结构化产品），DV01/CS01/Key Rate Duration分桶（KRD，覆盖含权债/可转债/利率债全品种），分桶利差敏感度。本模块为唯一定价计算权威，消费方不重复计算</t>
+          <t>Black-Scholes解析解，Hull-White利率模型，SABR波动率模型，二叉树/三叉树数值解</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G158" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G158" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H158" s="13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="159" ht="28" customHeight="1">
@@ -13688,31 +13692,31 @@
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>F09-11</t>
+          <t>F09-09</t>
         </is>
       </c>
       <c r="D159" s="27" t="inlineStr">
         <is>
-          <t>估值与结算计算</t>
+          <t>有限差分（PDE）</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>日终估值，盯市计算，保证金计算，结算价格，历史估值回测与误差分析</t>
+          <t>Crank-Nicolson/ADI方法，含权债/可转债精确定价，局部波动率模型数值解</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G159" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G159" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H159" s="13" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="160" ht="28" customHeight="1">
@@ -13728,17 +13732,17 @@
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>F09-12</t>
+          <t>F09-10</t>
         </is>
       </c>
       <c r="D160" s="27" t="inlineStr">
         <is>
-          <t>风控与情景计算</t>
+          <t>实时Greeks与敏感度计算（M07/M08/M04共用基础）</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>风险计量（VaR/压力测试）调用，情景分析，保证金计算，为风控平台提供统一定价接口</t>
+          <t>分布式实时计算全品种逐券敏感度，结果为M07归因、M08因子载荷、M04风险计量三方共用权威数据源：Delta/Gamma/Vega/Theta/Rho（期权/结构化产品），DV01/CS01/Key Rate Duration分桶（KRD，覆盖含权债/可转债/利率债全品种），分桶利差敏感度。本模块为唯一定价计算权威，消费方不重复计算</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr">
@@ -13752,7 +13756,7 @@
         </is>
       </c>
       <c r="H160" s="13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="161" ht="28" customHeight="1">
@@ -13768,17 +13772,17 @@
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>F09-13</t>
+          <t>F09-11</t>
         </is>
       </c>
       <c r="D161" s="27" t="inlineStr">
         <is>
-          <t>客需报价服务</t>
+          <t>估值与结算计算</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>为销售交易/TRS系统提供实时报价，一站式报价接口，支持结构化产品定制化快速报价</t>
+          <t>日终估值，盯市计算，保证金计算，结算价格，历史估值回测与误差分析</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr">
@@ -13792,7 +13796,7 @@
         </is>
       </c>
       <c r="H161" s="13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162" ht="28" customHeight="1">
@@ -13808,31 +13812,31 @@
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>F09-16</t>
+          <t>F09-12</t>
         </is>
       </c>
       <c r="D162" s="27" t="inlineStr">
         <is>
-          <t>XVA计算引擎（CVA/DVA/FVA）</t>
+          <t>风控与情景计算</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>场外衍生品全套XVA计算：CVA（信用估值调整）= EPE × 对手方PD × LGD；DVA（借方估值调整）= ENE × 自身PD × LGD；FVA（融资估值调整）= 融资利差 × 资金净敞口；蒙特卡洛路径模拟（1000+路径，支持GPU加速），IFRS 13第三层级公允价值合规；CVA/DVA结果供M04 F04-20信用风险计量消费，FVA供交易定价和P&amp;L Explain消费</t>
+          <t>风险计量（VaR/压力测试）调用，情景分析，保证金计算，为风控平台提供统一定价接口</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr">
         <is>
-          <t>CVA计算单笔IRS p99&lt;1s，EPE曲线与行业工具误差&lt;2%，IFRS 13文档输出满足审计要求</t>
-        </is>
-      </c>
-      <c r="G162" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G162" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H162" s="13" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="163" ht="28" customHeight="1">
@@ -13848,17 +13852,17 @@
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>F09-14</t>
+          <t>F09-13</t>
         </is>
       </c>
       <c r="D163" s="27" t="inlineStr">
         <is>
-          <t>定价微服务架构</t>
+          <t>客需报价服务</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>REST/gRPC定价API，横向弹性扩容，p99&lt;100ms，模型插件化注册，版本管理</t>
+          <t>为销售交易/TRS系统提供实时报价，一站式报价接口，支持结构化产品定制化快速报价</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr">
@@ -13872,7 +13876,7 @@
         </is>
       </c>
       <c r="H163" s="13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="164" ht="28" customHeight="1">
@@ -13888,31 +13892,31 @@
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>F09-15</t>
+          <t>F09-16</t>
         </is>
       </c>
       <c r="D164" s="27" t="inlineStr">
         <is>
-          <t>灵活二次开发能力</t>
+          <t>XVA计算引擎（CVA/DVA/FVA）</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>全平台级/单功能模块级/系统框架级可扩展，支持自定义模型接入，策略团队自助扩展</t>
+          <t>场外衍生品全套XVA计算：CVA（信用估值调整）= EPE × 对手方PD × LGD；DVA（借方估值调整）= ENE × 自身PD × LGD；FVA（融资估值调整）= 融资利差 × 资金净敞口；蒙特卡洛路径模拟（1000+路径，支持GPU加速），IFRS 13第三层级公允价值合规；CVA/DVA结果供M04 F04-20信用风险计量消费，FVA供交易定价和P&amp;L Explain消费</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G164" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>CVA计算单笔IRS p99&lt;1s，EPE曲线与行业工具误差&lt;2%，IFRS 13文档输出满足审计要求</t>
+        </is>
+      </c>
+      <c r="G164" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H164" s="13" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165" ht="28" customHeight="1">
@@ -13928,22 +13932,22 @@
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>F09-17</t>
+          <t>F09-14</t>
         </is>
       </c>
       <c r="D165" s="27" t="inlineStr">
         <is>
-          <t>定价模型验证与P&amp;L Explain</t>
+          <t>定价微服务架构</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>每日P&amp;L Explain：理论P&amp;L（Greeks × 市场因子变动）与实际P&amp;L对比，逐笔差异分类（模型误差/交易摩擦/数据质量/新交易），差异超阈值自动告警；模型回测：定价模型预测价格 vs 市场成交价，统计检验（Kupiec/Christoffersen），回测报告按模型类型（BS/HW/SABR等）分类归档；价格争议审计追踪：逐笔定价记录+参数快照存档，支持T+5内完整再现定价过程</t>
+          <t>REST/gRPC定价API，横向弹性扩容，p99&lt;100ms，模型插件化注册，版本管理</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr">
         <is>
-          <t>P&amp;L Explain覆盖率≥95%持仓，差异阈值可配，争议定价T+5内完整复现，模型回测报告月度自动生成</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
         </is>
       </c>
       <c r="G165" s="23" t="inlineStr">
@@ -13952,20 +13956,53 @@
         </is>
       </c>
       <c r="H165" s="13" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="166" ht="28" customHeight="1">
+      <c r="A166" s="11" t="inlineStr">
+        <is>
+          <t>定价平台</t>
+        </is>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C166" s="10" t="inlineStr">
+        <is>
+          <t>F09-15</t>
+        </is>
+      </c>
+      <c r="D166" s="27" t="inlineStr">
+        <is>
+          <t>灵活二次开发能力</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>全平台级/单功能模块级/系统框架级可扩展，支持自定义模型接入，策略团队自助扩展</t>
+        </is>
+      </c>
+      <c r="F166" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G166" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H166" s="13" t="n">
         <v>30</v>
-      </c>
-    </row>
-    <row r="166" ht="20" customHeight="1">
-      <c r="A166" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 销售交易  (Sales Trading)</t>
-        </is>
       </c>
     </row>
     <row r="167" ht="28" customHeight="1">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>销售交易</t>
+          <t>定价平台</t>
         </is>
       </c>
       <c r="B167" s="10" t="inlineStr">
@@ -13975,71 +14012,38 @@
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>F10-01</t>
+          <t>F09-17</t>
         </is>
       </c>
       <c r="D167" s="27" t="inlineStr">
         <is>
-          <t>报价工作台</t>
+          <t>定价模型验证与P&amp;L Explain</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer，报价提醒功能</t>
+          <t>每日P&amp;L Explain：理论P&amp;L（Greeks × 市场因子变动）与实际P&amp;L对比，逐笔差异分类（模型误差/交易摩擦/数据质量/新交易），差异超阈值自动告警；模型回测：定价模型预测价格 vs 市场成交价，统计检验（Kupiec/Christoffersen），回测报告按模型类型（BS/HW/SABR等）分类归档；价格争议审计追踪：逐笔定价记录+参数快照存档，支持T+5内完整再现定价过程</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G167" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>P&amp;L Explain覆盖率≥95%持仓，差异阈值可配，争议定价T+5内完整复现，模型回测报告月度自动生成</t>
+        </is>
+      </c>
+      <c r="G167" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H167" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="168" ht="28" customHeight="1">
-      <c r="A168" s="11" t="inlineStr">
-        <is>
-          <t>销售交易</t>
-        </is>
-      </c>
-      <c r="B168" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C168" s="10" t="inlineStr">
-        <is>
-          <t>F10-02</t>
-        </is>
-      </c>
-      <c r="D168" s="27" t="inlineStr">
-        <is>
-          <t>债券过滤与筛选</t>
-        </is>
-      </c>
-      <c r="E168" s="11" t="inlineStr">
-        <is>
-          <t>信用债全品种过滤，利率债（国债/证金债/地方债）过滤，精确识别与模糊识别双模式</t>
-        </is>
-      </c>
-      <c r="F168" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G168" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H168" s="13" t="n">
-        <v>10</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 销售交易  (Sales Trading)</t>
+        </is>
       </c>
     </row>
     <row r="169" ht="28" customHeight="1">
@@ -14055,17 +14059,17 @@
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>F10-03</t>
+          <t>F10-01</t>
         </is>
       </c>
       <c r="D169" s="27" t="inlineStr">
         <is>
-          <t>报价撮合与对价</t>
+          <t>报价工作台</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>对价/最优报价聚合展示，撮合对价，交易包管理，报价成交确认，一键成交</t>
+          <t>历史报价管理，当日报价快捷操作，导入/导出报价，一键unrefer，报价提醒功能</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr">
@@ -14095,31 +14099,31 @@
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>F10-04</t>
+          <t>F10-02</t>
         </is>
       </c>
       <c r="D170" s="27" t="inlineStr">
         <is>
-          <t>交易执行与要素校验</t>
+          <t>债券过滤与筛选</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>意向达成，交易要素自动校验，手工价录入，业务审批流程，交易记录管理</t>
+          <t>信用债全品种过滤，利率债（国债/证金债/地方债）过滤，精确识别与模糊识别双模式</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G170" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G170" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H170" s="13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171" ht="28" customHeight="1">
@@ -14135,17 +14139,17 @@
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>F10-05</t>
+          <t>F10-03</t>
         </is>
       </c>
       <c r="D171" s="27" t="inlineStr">
         <is>
-          <t>风控检查</t>
+          <t>报价撮合与对价</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>交易前风控规则同步校验，限额检查，合规拦截，风控记录留痕，不通过自动拦截</t>
+          <t>对价/最优报价聚合展示，撮合对价，交易包管理，报价成交确认，一键成交</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr">
@@ -14159,7 +14163,7 @@
         </is>
       </c>
       <c r="H171" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" ht="28" customHeight="1">
@@ -14175,31 +14179,31 @@
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>F10-06</t>
+          <t>F10-04</t>
         </is>
       </c>
       <c r="D172" s="27" t="inlineStr">
         <is>
-          <t>智能推荐系统</t>
+          <t>交易执行与要素校验</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>基于客户画像与历史交易数据主动推荐券种，从被动服务转向主动服务，提升客户响应效率</t>
+          <t>意向达成，交易要素自动校验，手工价录入，业务审批流程，交易记录管理</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G172" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G172" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H172" s="13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" ht="28" customHeight="1">
@@ -14215,17 +14219,17 @@
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>F10-07</t>
+          <t>F10-05</t>
         </is>
       </c>
       <c r="D173" s="27" t="inlineStr">
         <is>
-          <t>综合业务平台</t>
+          <t>风控检查</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>解决交易员分散办公与客户交易信息共享问题，报价聚合展示，客户快速服务，多地协同</t>
+          <t>交易前风控规则同步校验，限额检查，合规拦截，风控记录留痕，不通过自动拦截</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr">
@@ -14242,17 +14246,50 @@
         <v>15</v>
       </c>
     </row>
-    <row r="174" ht="20" customHeight="1">
-      <c r="A174" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 信用债/信用衍生品  (Credit Bond &amp; CDS)</t>
-        </is>
+    <row r="174" ht="28" customHeight="1">
+      <c r="A174" s="11" t="inlineStr">
+        <is>
+          <t>销售交易</t>
+        </is>
+      </c>
+      <c r="B174" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="inlineStr">
+        <is>
+          <t>F10-06</t>
+        </is>
+      </c>
+      <c r="D174" s="27" t="inlineStr">
+        <is>
+          <t>智能推荐系统</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="inlineStr">
+        <is>
+          <t>基于客户画像与历史交易数据主动推荐券种，从被动服务转向主动服务，提升客户响应效率</t>
+        </is>
+      </c>
+      <c r="F174" s="11" t="inlineStr">
+        <is>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G174" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H174" s="13" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="175" ht="28" customHeight="1">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>信用债/信用衍生品</t>
+          <t>销售交易</t>
         </is>
       </c>
       <c r="B175" s="10" t="inlineStr">
@@ -14262,71 +14299,38 @@
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>F11-01</t>
+          <t>F10-07</t>
         </is>
       </c>
       <c r="D175" s="27" t="inlineStr">
         <is>
-          <t>信用风险数据接入</t>
+          <t>综合业务平台</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>外部信用数据服务接入（Wind/中诚信/联合评级等），内部数据整合，数据质量检查，信用风险数据集市</t>
+          <t>解决交易员分散办公与客户交易信息共享问题，报价聚合展示，客户快速服务，多地协同</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G175" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G175" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H175" s="13" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="176" ht="28" customHeight="1">
-      <c r="A176" s="11" t="inlineStr">
-        <is>
-          <t>信用债/信用衍生品</t>
-        </is>
-      </c>
-      <c r="B176" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C176" s="10" t="inlineStr">
-        <is>
-          <t>F11-02</t>
-        </is>
-      </c>
-      <c r="D176" s="27" t="inlineStr">
-        <is>
-          <t>信用评估引擎</t>
-        </is>
-      </c>
-      <c r="E176" s="11" t="inlineStr">
-        <is>
-          <t>持续迭代信用评价引擎，资产证券化评价，交易对手评价，违约概率（PD）建模，信用评分</t>
-        </is>
-      </c>
-      <c r="F176" s="11" t="inlineStr">
-        <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G176" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
-        </is>
-      </c>
-      <c r="H176" s="13" t="n">
-        <v>40</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 信用债/信用衍生品  (Credit Bond &amp; CDS)</t>
+        </is>
       </c>
     </row>
     <row r="177" ht="28" customHeight="1">
@@ -14342,17 +14346,17 @@
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>F11-03</t>
+          <t>F11-01</t>
         </is>
       </c>
       <c r="D177" s="27" t="inlineStr">
         <is>
-          <t>信用预警系统</t>
+          <t>信用风险数据接入</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>市场数据自动触发预警，评级下调动态预警，投后预警跟踪与信号处理，预警规则配置</t>
+          <t>外部信用数据服务接入（Wind/中诚信/联合评级等），内部数据整合，数据质量检查，信用风险数据集市</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr">
@@ -14382,31 +14386,31 @@
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>F11-04</t>
+          <t>F11-02</t>
         </is>
       </c>
       <c r="D178" s="27" t="inlineStr">
         <is>
-          <t>投资池管理</t>
+          <t>信用评估引擎</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
         <is>
-          <t>债券池配置与维护，债券准入/退出规则，白名单/黑名单管理，池状态实时更新</t>
+          <t>持续迭代信用评价引擎，资产证券化评价，交易对手评价，违约概率（PD）建模，信用评分</t>
         </is>
       </c>
       <c r="F178" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G178" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G178" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
         </is>
       </c>
       <c r="H178" s="13" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="179" ht="28" customHeight="1">
@@ -14422,31 +14426,31 @@
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>F11-05</t>
+          <t>F11-03</t>
         </is>
       </c>
       <c r="D179" s="27" t="inlineStr">
         <is>
-          <t>评级管理</t>
+          <t>信用预警系统</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>内部评级录入与更新，外部评级同步（中诚信/联合/大公），评级变更历史追踪，评级模型管理</t>
+          <t>市场数据自动触发预警，评级下调动态预警，投后预警跟踪与信号处理，预警规则配置</t>
         </is>
       </c>
       <c r="F179" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G179" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G179" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H179" s="13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="180" ht="28" customHeight="1">
@@ -14462,17 +14466,17 @@
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>F11-06</t>
+          <t>F11-04</t>
         </is>
       </c>
       <c r="D180" s="27" t="inlineStr">
         <is>
-          <t>投前审批管理</t>
+          <t>投资池管理</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
         <is>
-          <t>新券投资准入审批流程，信用额度申请，投资决策材料生成，审批记录留痕</t>
+          <t>债券池配置与维护，债券准入/退出规则，白名单/黑名单管理，池状态实时更新</t>
         </is>
       </c>
       <c r="F180" s="11" t="inlineStr">
@@ -14502,17 +14506,17 @@
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>F11-07</t>
+          <t>F11-05</t>
         </is>
       </c>
       <c r="D181" s="27" t="inlineStr">
         <is>
-          <t>持仓与敞口管理</t>
+          <t>评级管理</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>信用债持仓实时查询，敞口管理，集中度分析（行业/评级/发行人），到期提醒</t>
+          <t>内部评级录入与更新，外部评级同步（中诚信/联合/大公），评级变更历史追踪，评级模型管理</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr">
@@ -14542,31 +14546,31 @@
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>F11-08</t>
+          <t>F11-06</t>
         </is>
       </c>
       <c r="D182" s="27" t="inlineStr">
         <is>
-          <t>信用风险监控看板</t>
+          <t>投前审批管理</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>多维度风险指标实时监控，信用利差走势，主体信用事件推送，指标监控与查询统计</t>
+          <t>新券投资准入审批流程，信用额度申请，投资决策材料生成，审批记录留痕</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G182" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G182" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H182" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183" ht="28" customHeight="1">
@@ -14582,31 +14586,31 @@
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>F11-09</t>
+          <t>F11-07</t>
         </is>
       </c>
       <c r="D183" s="27" t="inlineStr">
         <is>
-          <t>违约管理</t>
+          <t>持仓与敞口管理</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>违约事件记录，违约债券处置跟踪，损失估算，监管报送，违约主体黑名单自动更新</t>
+          <t>信用债持仓实时查询，敞口管理，集中度分析（行业/评级/发行人），到期提醒</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G183" s="23" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>功能测试通过/正确率100%</t>
+        </is>
+      </c>
+      <c r="G183" s="24" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H183" s="13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" ht="28" customHeight="1">
@@ -14622,17 +14626,17 @@
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>F11-10</t>
+          <t>F11-08</t>
         </is>
       </c>
       <c r="D184" s="27" t="inlineStr">
         <is>
-          <t>信用利差分析</t>
+          <t>信用风险监控看板</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析，利差走势，相对价值分析</t>
+          <t>多维度风险指标实时监控，信用利差走势，主体信用事件推送，指标监控与查询统计</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr">
@@ -14646,7 +14650,7 @@
         </is>
       </c>
       <c r="H184" s="13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="185" ht="28" customHeight="1">
@@ -14662,31 +14666,31 @@
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>F11-11</t>
+          <t>F11-09</t>
         </is>
       </c>
       <c r="D185" s="27" t="inlineStr">
         <is>
-          <t>CDS定价与管理</t>
+          <t>违约管理</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>信用违约互换定价（ISDA标准），生存概率曲线校准，CDS交易录入与持仓管理</t>
+          <t>违约事件记录，违约债券处置跟踪，损失估算，监管报送，违约主体黑名单自动更新</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr">
         <is>
-          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
-        </is>
-      </c>
-      <c r="G185" s="28" t="inlineStr">
-        <is>
-          <t>极高</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G185" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H185" s="13" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="186" ht="28" customHeight="1">
@@ -14702,44 +14706,77 @@
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>F11-12</t>
+          <t>F11-10</t>
         </is>
       </c>
       <c r="D186" s="27" t="inlineStr">
         <is>
-          <t>配置与权限管理</t>
+          <t>信用利差分析</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>预警规则配置，指标库管理，评级模型管理，用户权限管理，债券池配置管理</t>
+          <t>行业/评级/期限信用利差曲线实时计算，历史分位数分析，利差走势，相对价值分析</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过</t>
-        </is>
-      </c>
-      <c r="G186" s="25" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>功能完整/边界测试/集成冒烟/性能基线</t>
+        </is>
+      </c>
+      <c r="G186" s="23" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H186" s="13" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="187" ht="20" customHeight="1">
-      <c r="A187" s="26" t="inlineStr">
-        <is>
-          <t>【P2】 投顾服务  (Investment Advisory)</t>
-        </is>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="187" ht="28" customHeight="1">
+      <c r="A187" s="11" t="inlineStr">
+        <is>
+          <t>信用债/信用衍生品</t>
+        </is>
+      </c>
+      <c r="B187" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>F11-11</t>
+        </is>
+      </c>
+      <c r="D187" s="27" t="inlineStr">
+        <is>
+          <t>CDS定价与管理</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="inlineStr">
+        <is>
+          <t>信用违约互换定价（ISDA标准），生存概率曲线校准，CDS交易录入与持仓管理</t>
+        </is>
+      </c>
+      <c r="F187" s="11" t="inlineStr">
+        <is>
+          <t>p99延迟/误差率/精度验证/压测10k TPS</t>
+        </is>
+      </c>
+      <c r="G187" s="28" t="inlineStr">
+        <is>
+          <t>极高</t>
+        </is>
+      </c>
+      <c r="H187" s="13" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="188" ht="28" customHeight="1">
       <c r="A188" s="11" t="inlineStr">
         <is>
-          <t>投顾服务</t>
+          <t>信用债/信用衍生品</t>
         </is>
       </c>
       <c r="B188" s="10" t="inlineStr">
@@ -14749,71 +14786,38 @@
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>F12-01</t>
+          <t>F11-12</t>
         </is>
       </c>
       <c r="D188" s="27" t="inlineStr">
         <is>
-          <t>投顾操作工作台</t>
+          <t>配置与权限管理</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>投顾人员管理客户委托，上传研究报告，发送投资建议，查看客户反馈与确认状态</t>
+          <t>预警规则配置，指标库管理，评级模型管理，用户权限管理，债券池配置管理</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr">
         <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G188" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>功能测试通过</t>
+        </is>
+      </c>
+      <c r="G188" s="25" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H188" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="189" ht="28" customHeight="1">
-      <c r="A189" s="11" t="inlineStr">
-        <is>
-          <t>投顾服务</t>
-        </is>
-      </c>
-      <c r="B189" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="C189" s="10" t="inlineStr">
-        <is>
-          <t>F12-02</t>
-        </is>
-      </c>
-      <c r="D189" s="27" t="inlineStr">
-        <is>
-          <t>投资建议书管理</t>
-        </is>
-      </c>
-      <c r="E189" s="11" t="inlineStr">
-        <is>
-          <t>投资建议书线上生成与审批，客户确认全流程，留痕追溯，电子签收，历史建议书归档</t>
-        </is>
-      </c>
-      <c r="F189" s="11" t="inlineStr">
-        <is>
-          <t>功能测试通过/正确率100%</t>
-        </is>
-      </c>
-      <c r="G189" s="24" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H189" s="13" t="n">
-        <v>20</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="26" t="inlineStr">
+        <is>
+          <t>【P2】 投顾服务  (Investment Advisory)</t>
+        </is>
       </c>
     </row>
     <row r="190" ht="28" customHeight="1">
@@ -14829,17 +14833,17 @@
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>F12-03</t>
+          <t>F12-01</t>
         </is>
       </c>
       <c r="D190" s="27" t="inlineStr">
         <is>
-          <t>投研报告服务</t>
+          <t>投顾操作工作台</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
         <is>
-          <t>日/周/月研究报告上传与定向推送，RPA自动获取基础数据，报告分类管理与检索</t>
+          <t>投顾人员管理客户委托，上传研究报告，发送投资建议，查看客户反馈与确认状态</t>
         </is>
       </c>
       <c r="F190" s="11" t="inlineStr">
@@ -14853,7 +14857,7 @@
         </is>
       </c>
       <c r="H190" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="191" ht="28" customHeight="1">
@@ -14869,17 +14873,17 @@
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>F12-04</t>
+          <t>F12-02</t>
         </is>
       </c>
       <c r="D191" s="27" t="inlineStr">
         <is>
-          <t>客户投资服务界面</t>
+          <t>投资建议书管理</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>客户查看投资建议与分析报告，发送确认，查看账户净值走势、持仓明细、交易明细</t>
+          <t>投资建议书线上生成与审批，客户确认全流程，留痕追溯，电子签收，历史建议书归档</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr">
@@ -14909,31 +14913,31 @@
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>F12-05</t>
+          <t>F12-03</t>
         </is>
       </c>
       <c r="D192" s="27" t="inlineStr">
         <is>
-          <t>账户深度分析</t>
+          <t>投研报告服务</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>账户净值走势，久期走势，归因分析，估值台账，持仓明细，交易明细，定期分析报告生成</t>
+          <t>日/周/月研究报告上传与定向推送，RPA自动获取基础数据，报告分类管理与检索</t>
         </is>
       </c>
       <c r="F192" s="11" t="inlineStr">
         <is>
-          <t>功能完整/边界测试/集成冒烟/性能基线</t>
-        </is>
-      </c>
-      <c r="G192" s="23" t="